--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\新技能配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCE073B-562D-405E-9D1B-3F7221776E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BDE029-8C36-4FFA-AA52-91BEC0C8961C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4761,7 +4761,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.15">
@@ -5283,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.15">
@@ -5631,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.15">
@@ -5979,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.15">
@@ -6298,7 +6298,7 @@
         <v>2</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.15">
@@ -6897,7 +6897,7 @@
         <v>2</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.15">
@@ -7100,7 +7100,7 @@
         <v>2</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.15">
@@ -7419,7 +7419,7 @@
         <v>2</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.15">
@@ -7738,7 +7738,7 @@
         <v>2</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.15">
@@ -8057,7 +8057,7 @@
         <v>2</v>
       </c>
       <c r="I140">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.15">
@@ -20034,7 +20034,7 @@
         <v>2</v>
       </c>
       <c r="I553">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\新技能配置\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BDE029-8C36-4FFA-AA52-91BEC0C8961C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F549CC6-FB4D-4DA6-8D93-A10003A76B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3308" uniqueCount="967">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3342,6 +3342,36 @@
   <si>
     <t>迷宫怪物掉落经验</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域_获得</t>
+  </si>
+  <si>
+    <t>炎域_冷却</t>
+  </si>
+  <si>
+    <t>炎域_最近释放距离</t>
+  </si>
+  <si>
+    <t>炎域_最远释放距离</t>
+  </si>
+  <si>
+    <t>炎域_技能效果半径</t>
+  </si>
+  <si>
+    <t>炎域_目标数量</t>
+  </si>
+  <si>
+    <t>炎域_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>炎域_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>炎域_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>炎域_非主目标直接伤害系数</t>
   </si>
 </sst>
 </file>
@@ -4015,7 +4045,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1078"/>
+  <dimension ref="A1:I1088"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -34982,6 +35012,236 @@
       </c>
       <c r="I1078">
         <v>24000</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1079">
+        <v>920001</v>
+      </c>
+      <c r="B1079" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1079">
+        <v>0</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>957</v>
+      </c>
+      <c r="F1079" t="s">
+        <v>957</v>
+      </c>
+      <c r="H1079" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1079">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1080">
+        <v>1920001</v>
+      </c>
+      <c r="B1080" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1080">
+        <v>0</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>958</v>
+      </c>
+      <c r="F1080" t="s">
+        <v>958</v>
+      </c>
+      <c r="H1080" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1080">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1081">
+        <v>2920001</v>
+      </c>
+      <c r="B1081" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1081">
+        <v>0</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>959</v>
+      </c>
+      <c r="F1081" t="s">
+        <v>959</v>
+      </c>
+      <c r="H1081" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1081">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1082">
+        <v>3920001</v>
+      </c>
+      <c r="B1082" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1082">
+        <v>0</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>960</v>
+      </c>
+      <c r="F1082" t="s">
+        <v>960</v>
+      </c>
+      <c r="H1082" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1082">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1083">
+        <v>4920001</v>
+      </c>
+      <c r="B1083" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1083">
+        <v>0</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>961</v>
+      </c>
+      <c r="F1083" t="s">
+        <v>961</v>
+      </c>
+      <c r="H1083" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1083">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1084">
+        <v>5920001</v>
+      </c>
+      <c r="B1084" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1084">
+        <v>0</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>962</v>
+      </c>
+      <c r="F1084" t="s">
+        <v>962</v>
+      </c>
+      <c r="H1084" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1084">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1085">
+        <v>6920001</v>
+      </c>
+      <c r="B1085" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1085">
+        <v>0</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>963</v>
+      </c>
+      <c r="F1085" t="s">
+        <v>963</v>
+      </c>
+      <c r="H1085" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1085">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1086">
+        <v>7920001</v>
+      </c>
+      <c r="B1086" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1086">
+        <v>0</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>964</v>
+      </c>
+      <c r="F1086" t="s">
+        <v>964</v>
+      </c>
+      <c r="H1086" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1086">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1087">
+        <v>8920001</v>
+      </c>
+      <c r="B1087" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1087">
+        <v>0</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>965</v>
+      </c>
+      <c r="F1087" t="s">
+        <v>965</v>
+      </c>
+      <c r="H1087" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1087">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1088">
+        <v>9920001</v>
+      </c>
+      <c r="B1088" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1088">
+        <v>0</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>966</v>
+      </c>
+      <c r="F1088" t="s">
+        <v>966</v>
+      </c>
+      <c r="H1088" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1088">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F549CC6-FB4D-4DA6-8D93-A10003A76B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65EE660-8560-4A9F-9DD8-DAFC971B12A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3308" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="972">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3372,13 +3372,33 @@
   </si>
   <si>
     <t>炎域_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>炎域-燃烧-逻辑id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域-燃烧-火元素伤害万分比系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域-燃烧-火元素伤害固定值系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域-燃烧-持续时长毫秒</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域-燃烧-伤害间隔毫秒</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3516,6 +3536,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -3662,7 +3690,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3733,6 +3761,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4045,7 +4076,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1088"/>
+  <dimension ref="A1:I1093"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -32684,7 +32715,7 @@
       <c r="C989">
         <v>0</v>
       </c>
-      <c r="D989" t="s">
+      <c r="D989" s="30" t="s">
         <v>776</v>
       </c>
       <c r="F989" s="14" t="s">
@@ -32710,7 +32741,7 @@
       <c r="C990">
         <v>0</v>
       </c>
-      <c r="D990" t="s">
+      <c r="D990" s="30" t="s">
         <v>777</v>
       </c>
       <c r="F990" s="14" t="s">
@@ -32736,7 +32767,7 @@
       <c r="C991">
         <v>0</v>
       </c>
-      <c r="D991" t="s">
+      <c r="D991" s="30" t="s">
         <v>778</v>
       </c>
       <c r="F991" s="14" t="s">
@@ -32762,7 +32793,7 @@
       <c r="C992">
         <v>0</v>
       </c>
-      <c r="D992" t="s">
+      <c r="D992" s="30" t="s">
         <v>779</v>
       </c>
       <c r="F992" s="14" t="s">
@@ -32788,7 +32819,7 @@
       <c r="C993">
         <v>0</v>
       </c>
-      <c r="D993" t="s">
+      <c r="D993" s="30" t="s">
         <v>780</v>
       </c>
       <c r="F993" s="14" t="s">
@@ -32814,7 +32845,7 @@
       <c r="C994">
         <v>0</v>
       </c>
-      <c r="D994" t="s">
+      <c r="D994" s="30" t="s">
         <v>781</v>
       </c>
       <c r="F994" s="14" t="s">
@@ -32840,7 +32871,7 @@
       <c r="C995">
         <v>0</v>
       </c>
-      <c r="D995" t="s">
+      <c r="D995" s="30" t="s">
         <v>782</v>
       </c>
       <c r="F995" s="14" t="s">
@@ -32866,7 +32897,7 @@
       <c r="C996">
         <v>0</v>
       </c>
-      <c r="D996" t="s">
+      <c r="D996" s="30" t="s">
         <v>783</v>
       </c>
       <c r="F996" s="14" t="s">
@@ -32892,7 +32923,7 @@
       <c r="C997">
         <v>0</v>
       </c>
-      <c r="D997" t="s">
+      <c r="D997" s="30" t="s">
         <v>784</v>
       </c>
       <c r="F997" s="14" t="s">
@@ -32918,7 +32949,7 @@
       <c r="C998">
         <v>0</v>
       </c>
-      <c r="D998" t="s">
+      <c r="D998" s="30" t="s">
         <v>785</v>
       </c>
       <c r="F998" s="14" t="s">
@@ -32944,7 +32975,7 @@
       <c r="C999">
         <v>0</v>
       </c>
-      <c r="D999" t="s">
+      <c r="D999" s="30" t="s">
         <v>786</v>
       </c>
       <c r="F999" s="14" t="s">
@@ -32970,7 +33001,7 @@
       <c r="C1000">
         <v>0</v>
       </c>
-      <c r="D1000" t="s">
+      <c r="D1000" s="30" t="s">
         <v>787</v>
       </c>
       <c r="F1000" s="14" t="s">
@@ -32996,7 +33027,7 @@
       <c r="C1001">
         <v>0</v>
       </c>
-      <c r="D1001" t="s">
+      <c r="D1001" s="30" t="s">
         <v>788</v>
       </c>
       <c r="F1001" s="14" t="s">
@@ -33022,7 +33053,7 @@
       <c r="C1002">
         <v>0</v>
       </c>
-      <c r="D1002" t="s">
+      <c r="D1002" s="30" t="s">
         <v>789</v>
       </c>
       <c r="F1002" s="14" t="s">
@@ -33048,7 +33079,7 @@
       <c r="C1003">
         <v>0</v>
       </c>
-      <c r="D1003" t="s">
+      <c r="D1003" s="30" t="s">
         <v>790</v>
       </c>
       <c r="F1003" s="14" t="s">
@@ -33074,7 +33105,7 @@
       <c r="C1004">
         <v>0</v>
       </c>
-      <c r="D1004" t="s">
+      <c r="D1004" s="30" t="s">
         <v>791</v>
       </c>
       <c r="F1004" s="14" t="s">
@@ -33100,7 +33131,7 @@
       <c r="C1005">
         <v>0</v>
       </c>
-      <c r="D1005" t="s">
+      <c r="D1005" s="30" t="s">
         <v>792</v>
       </c>
       <c r="F1005" s="14" t="s">
@@ -33126,7 +33157,7 @@
       <c r="C1006">
         <v>0</v>
       </c>
-      <c r="D1006" t="s">
+      <c r="D1006" s="30" t="s">
         <v>793</v>
       </c>
       <c r="F1006" s="14" t="s">
@@ -33152,7 +33183,7 @@
       <c r="C1007">
         <v>0</v>
       </c>
-      <c r="D1007" t="s">
+      <c r="D1007" s="30" t="s">
         <v>794</v>
       </c>
       <c r="F1007" s="14" t="s">
@@ -33178,7 +33209,7 @@
       <c r="C1008">
         <v>0</v>
       </c>
-      <c r="D1008" t="s">
+      <c r="D1008" s="30" t="s">
         <v>795</v>
       </c>
       <c r="F1008" s="14" t="s">
@@ -33204,7 +33235,7 @@
       <c r="C1009">
         <v>0</v>
       </c>
-      <c r="D1009" t="s">
+      <c r="D1009" s="30" t="s">
         <v>796</v>
       </c>
       <c r="F1009" s="14" t="s">
@@ -33230,7 +33261,7 @@
       <c r="C1010">
         <v>0</v>
       </c>
-      <c r="D1010" t="s">
+      <c r="D1010" s="30" t="s">
         <v>797</v>
       </c>
       <c r="F1010" s="14" t="s">
@@ -33256,7 +33287,7 @@
       <c r="C1011">
         <v>0</v>
       </c>
-      <c r="D1011" t="s">
+      <c r="D1011" s="30" t="s">
         <v>798</v>
       </c>
       <c r="F1011" s="14" t="s">
@@ -33282,7 +33313,7 @@
       <c r="C1012">
         <v>0</v>
       </c>
-      <c r="D1012" t="s">
+      <c r="D1012" s="30" t="s">
         <v>799</v>
       </c>
       <c r="F1012" s="14" t="s">
@@ -33308,7 +33339,7 @@
       <c r="C1013">
         <v>0</v>
       </c>
-      <c r="D1013" t="s">
+      <c r="D1013" s="30" t="s">
         <v>800</v>
       </c>
       <c r="F1013" s="14" t="s">
@@ -33334,7 +33365,7 @@
       <c r="C1014">
         <v>0</v>
       </c>
-      <c r="D1014" t="s">
+      <c r="D1014" s="30" t="s">
         <v>801</v>
       </c>
       <c r="F1014" s="14" t="s">
@@ -33360,7 +33391,7 @@
       <c r="C1015">
         <v>0</v>
       </c>
-      <c r="D1015" t="s">
+      <c r="D1015" s="30" t="s">
         <v>802</v>
       </c>
       <c r="F1015" s="14" t="s">
@@ -33386,7 +33417,7 @@
       <c r="C1016">
         <v>0</v>
       </c>
-      <c r="D1016" t="s">
+      <c r="D1016" s="30" t="s">
         <v>803</v>
       </c>
       <c r="F1016" s="14" t="s">
@@ -33412,7 +33443,7 @@
       <c r="C1017">
         <v>0</v>
       </c>
-      <c r="D1017" t="s">
+      <c r="D1017" s="30" t="s">
         <v>804</v>
       </c>
       <c r="F1017" s="14" t="s">
@@ -33438,7 +33469,7 @@
       <c r="C1018">
         <v>0</v>
       </c>
-      <c r="D1018" t="s">
+      <c r="D1018" s="30" t="s">
         <v>805</v>
       </c>
       <c r="F1018" s="14" t="s">
@@ -33464,7 +33495,7 @@
       <c r="C1019">
         <v>0</v>
       </c>
-      <c r="D1019" t="s">
+      <c r="D1019" s="30" t="s">
         <v>806</v>
       </c>
       <c r="F1019" s="14" t="s">
@@ -33490,7 +33521,7 @@
       <c r="C1020">
         <v>0</v>
       </c>
-      <c r="D1020" t="s">
+      <c r="D1020" s="30" t="s">
         <v>807</v>
       </c>
       <c r="F1020" s="14" t="s">
@@ -33516,7 +33547,7 @@
       <c r="C1021">
         <v>0</v>
       </c>
-      <c r="D1021" t="s">
+      <c r="D1021" s="30" t="s">
         <v>808</v>
       </c>
       <c r="F1021" s="14" t="s">
@@ -33542,7 +33573,7 @@
       <c r="C1022">
         <v>0</v>
       </c>
-      <c r="D1022" t="s">
+      <c r="D1022" s="30" t="s">
         <v>809</v>
       </c>
       <c r="F1022" s="14" t="s">
@@ -33568,7 +33599,7 @@
       <c r="C1023">
         <v>0</v>
       </c>
-      <c r="D1023" t="s">
+      <c r="D1023" s="30" t="s">
         <v>810</v>
       </c>
       <c r="F1023" s="14" t="s">
@@ -33594,7 +33625,7 @@
       <c r="C1024">
         <v>0</v>
       </c>
-      <c r="D1024" t="s">
+      <c r="D1024" s="30" t="s">
         <v>811</v>
       </c>
       <c r="F1024" s="14" t="s">
@@ -33620,7 +33651,7 @@
       <c r="C1025">
         <v>0</v>
       </c>
-      <c r="D1025" t="s">
+      <c r="D1025" s="30" t="s">
         <v>812</v>
       </c>
       <c r="F1025" s="14" t="s">
@@ -33646,7 +33677,7 @@
       <c r="C1026">
         <v>0</v>
       </c>
-      <c r="D1026" t="s">
+      <c r="D1026" s="30" t="s">
         <v>813</v>
       </c>
       <c r="F1026" s="14" t="s">
@@ -33672,7 +33703,7 @@
       <c r="C1027">
         <v>0</v>
       </c>
-      <c r="D1027" t="s">
+      <c r="D1027" s="30" t="s">
         <v>814</v>
       </c>
       <c r="F1027" s="14" t="s">
@@ -33698,7 +33729,7 @@
       <c r="C1028">
         <v>0</v>
       </c>
-      <c r="D1028" t="s">
+      <c r="D1028" s="30" t="s">
         <v>815</v>
       </c>
       <c r="F1028" s="14" t="s">
@@ -33724,7 +33755,7 @@
       <c r="C1029">
         <v>0</v>
       </c>
-      <c r="D1029" t="s">
+      <c r="D1029" s="30" t="s">
         <v>816</v>
       </c>
       <c r="F1029" s="14" t="s">
@@ -33750,7 +33781,7 @@
       <c r="C1030">
         <v>0</v>
       </c>
-      <c r="D1030" t="s">
+      <c r="D1030" s="30" t="s">
         <v>817</v>
       </c>
       <c r="F1030" s="14" t="s">
@@ -33776,7 +33807,7 @@
       <c r="C1031">
         <v>0</v>
       </c>
-      <c r="D1031" t="s">
+      <c r="D1031" s="30" t="s">
         <v>818</v>
       </c>
       <c r="F1031" s="14" t="s">
@@ -33802,7 +33833,7 @@
       <c r="C1032">
         <v>0</v>
       </c>
-      <c r="D1032" t="s">
+      <c r="D1032" s="30" t="s">
         <v>819</v>
       </c>
       <c r="F1032" s="14" t="s">
@@ -33828,7 +33859,7 @@
       <c r="C1033">
         <v>0</v>
       </c>
-      <c r="D1033" t="s">
+      <c r="D1033" s="30" t="s">
         <v>820</v>
       </c>
       <c r="F1033" s="14" t="s">
@@ -33854,7 +33885,7 @@
       <c r="C1034">
         <v>0</v>
       </c>
-      <c r="D1034" t="s">
+      <c r="D1034" s="30" t="s">
         <v>821</v>
       </c>
       <c r="F1034" s="14" t="s">
@@ -33880,7 +33911,7 @@
       <c r="C1035">
         <v>0</v>
       </c>
-      <c r="D1035" t="s">
+      <c r="D1035" s="30" t="s">
         <v>822</v>
       </c>
       <c r="F1035" s="14" t="s">
@@ -33906,7 +33937,7 @@
       <c r="C1036">
         <v>0</v>
       </c>
-      <c r="D1036" t="s">
+      <c r="D1036" s="30" t="s">
         <v>823</v>
       </c>
       <c r="F1036" s="14" t="s">
@@ -33932,7 +33963,7 @@
       <c r="C1037">
         <v>0</v>
       </c>
-      <c r="D1037" t="s">
+      <c r="D1037" s="30" t="s">
         <v>824</v>
       </c>
       <c r="F1037" s="14" t="s">
@@ -33958,7 +33989,7 @@
       <c r="C1038">
         <v>0</v>
       </c>
-      <c r="D1038" t="s">
+      <c r="D1038" s="30" t="s">
         <v>825</v>
       </c>
       <c r="F1038" s="14" t="s">
@@ -33984,7 +34015,7 @@
       <c r="C1039">
         <v>0</v>
       </c>
-      <c r="D1039" t="s">
+      <c r="D1039" s="30" t="s">
         <v>826</v>
       </c>
       <c r="F1039" s="14" t="s">
@@ -34010,7 +34041,7 @@
       <c r="C1040">
         <v>0</v>
       </c>
-      <c r="D1040" t="s">
+      <c r="D1040" s="30" t="s">
         <v>827</v>
       </c>
       <c r="F1040" s="14" t="s">
@@ -34036,7 +34067,7 @@
       <c r="C1041">
         <v>0</v>
       </c>
-      <c r="D1041" t="s">
+      <c r="D1041" s="30" t="s">
         <v>828</v>
       </c>
       <c r="F1041" s="14" t="s">
@@ -34062,7 +34093,7 @@
       <c r="C1042">
         <v>0</v>
       </c>
-      <c r="D1042" t="s">
+      <c r="D1042" s="30" t="s">
         <v>829</v>
       </c>
       <c r="F1042" s="14" t="s">
@@ -34088,7 +34119,7 @@
       <c r="C1043">
         <v>0</v>
       </c>
-      <c r="D1043" t="s">
+      <c r="D1043" s="30" t="s">
         <v>830</v>
       </c>
       <c r="F1043" s="14" t="s">
@@ -34114,7 +34145,7 @@
       <c r="C1044">
         <v>0</v>
       </c>
-      <c r="D1044" t="s">
+      <c r="D1044" s="30" t="s">
         <v>831</v>
       </c>
       <c r="F1044" s="14" t="s">
@@ -34140,7 +34171,7 @@
       <c r="C1045">
         <v>0</v>
       </c>
-      <c r="D1045" t="s">
+      <c r="D1045" s="30" t="s">
         <v>832</v>
       </c>
       <c r="F1045" s="14" t="s">
@@ -34166,7 +34197,7 @@
       <c r="C1046">
         <v>0</v>
       </c>
-      <c r="D1046" t="s">
+      <c r="D1046" s="30" t="s">
         <v>833</v>
       </c>
       <c r="F1046" s="14" t="s">
@@ -34192,7 +34223,7 @@
       <c r="C1047">
         <v>0</v>
       </c>
-      <c r="D1047" t="s">
+      <c r="D1047" s="30" t="s">
         <v>834</v>
       </c>
       <c r="F1047" s="14" t="s">
@@ -34218,7 +34249,7 @@
       <c r="C1048">
         <v>0</v>
       </c>
-      <c r="D1048" t="s">
+      <c r="D1048" s="30" t="s">
         <v>835</v>
       </c>
       <c r="F1048" s="14" t="s">
@@ -34244,7 +34275,7 @@
       <c r="C1049">
         <v>0</v>
       </c>
-      <c r="D1049" t="s">
+      <c r="D1049" s="30" t="s">
         <v>836</v>
       </c>
       <c r="F1049" s="14" t="s">
@@ -34270,7 +34301,7 @@
       <c r="C1050">
         <v>0</v>
       </c>
-      <c r="D1050" t="s">
+      <c r="D1050" s="30" t="s">
         <v>837</v>
       </c>
       <c r="F1050" s="14" t="s">
@@ -34296,7 +34327,7 @@
       <c r="C1051">
         <v>0</v>
       </c>
-      <c r="D1051" t="s">
+      <c r="D1051" s="30" t="s">
         <v>838</v>
       </c>
       <c r="F1051" s="14" t="s">
@@ -34322,7 +34353,7 @@
       <c r="C1052">
         <v>0</v>
       </c>
-      <c r="D1052" t="s">
+      <c r="D1052" s="30" t="s">
         <v>839</v>
       </c>
       <c r="F1052" s="14" t="s">
@@ -34348,7 +34379,7 @@
       <c r="C1053">
         <v>0</v>
       </c>
-      <c r="D1053" t="s">
+      <c r="D1053" s="30" t="s">
         <v>840</v>
       </c>
       <c r="F1053" s="14" t="s">
@@ -34374,7 +34405,7 @@
       <c r="C1054">
         <v>0</v>
       </c>
-      <c r="D1054" t="s">
+      <c r="D1054" s="30" t="s">
         <v>841</v>
       </c>
       <c r="F1054" s="14" t="s">
@@ -34400,7 +34431,7 @@
       <c r="C1055">
         <v>0</v>
       </c>
-      <c r="D1055" t="s">
+      <c r="D1055" s="30" t="s">
         <v>842</v>
       </c>
       <c r="F1055" s="14" t="s">
@@ -34426,7 +34457,7 @@
       <c r="C1056">
         <v>0</v>
       </c>
-      <c r="D1056" t="s">
+      <c r="D1056" s="30" t="s">
         <v>843</v>
       </c>
       <c r="F1056" s="14" t="s">
@@ -34452,7 +34483,7 @@
       <c r="C1057">
         <v>0</v>
       </c>
-      <c r="D1057" t="s">
+      <c r="D1057" s="30" t="s">
         <v>844</v>
       </c>
       <c r="F1057" s="14" t="s">
@@ -34478,7 +34509,7 @@
       <c r="C1058">
         <v>0</v>
       </c>
-      <c r="D1058" t="s">
+      <c r="D1058" s="30" t="s">
         <v>845</v>
       </c>
       <c r="F1058" s="14" t="s">
@@ -34504,7 +34535,7 @@
       <c r="C1059">
         <v>0</v>
       </c>
-      <c r="D1059" t="s">
+      <c r="D1059" s="30" t="s">
         <v>846</v>
       </c>
       <c r="F1059" s="14" t="s">
@@ -34530,7 +34561,7 @@
       <c r="C1060">
         <v>0</v>
       </c>
-      <c r="D1060" t="s">
+      <c r="D1060" s="30" t="s">
         <v>847</v>
       </c>
       <c r="F1060" s="14" t="s">
@@ -34556,7 +34587,7 @@
       <c r="C1061">
         <v>0</v>
       </c>
-      <c r="D1061" t="s">
+      <c r="D1061" s="30" t="s">
         <v>848</v>
       </c>
       <c r="F1061" s="14" t="s">
@@ -34582,7 +34613,7 @@
       <c r="C1062">
         <v>0</v>
       </c>
-      <c r="D1062" t="s">
+      <c r="D1062" s="30" t="s">
         <v>849</v>
       </c>
       <c r="F1062" s="14" t="s">
@@ -34608,7 +34639,7 @@
       <c r="C1063">
         <v>0</v>
       </c>
-      <c r="D1063" t="s">
+      <c r="D1063" s="30" t="s">
         <v>850</v>
       </c>
       <c r="F1063" s="14" t="s">
@@ -34634,7 +34665,7 @@
       <c r="C1064">
         <v>0</v>
       </c>
-      <c r="D1064" t="s">
+      <c r="D1064" s="30" t="s">
         <v>851</v>
       </c>
       <c r="F1064" s="14" t="s">
@@ -34660,7 +34691,7 @@
       <c r="C1065">
         <v>0</v>
       </c>
-      <c r="D1065" t="s">
+      <c r="D1065" s="30" t="s">
         <v>852</v>
       </c>
       <c r="F1065" s="14" t="s">
@@ -34686,7 +34717,7 @@
       <c r="C1066">
         <v>0</v>
       </c>
-      <c r="D1066" t="s">
+      <c r="D1066" s="30" t="s">
         <v>853</v>
       </c>
       <c r="F1066" s="14" t="s">
@@ -34712,7 +34743,7 @@
       <c r="C1067">
         <v>0</v>
       </c>
-      <c r="D1067" t="s">
+      <c r="D1067" s="30" t="s">
         <v>854</v>
       </c>
       <c r="F1067" s="14" t="s">
@@ -34738,7 +34769,7 @@
       <c r="C1068">
         <v>0</v>
       </c>
-      <c r="D1068" t="s">
+      <c r="D1068" s="30" t="s">
         <v>855</v>
       </c>
       <c r="F1068" s="14" t="s">
@@ -34764,7 +34795,7 @@
       <c r="C1069">
         <v>0</v>
       </c>
-      <c r="D1069" t="s">
+      <c r="D1069" s="30" t="s">
         <v>856</v>
       </c>
       <c r="F1069" s="14" t="s">
@@ -34790,7 +34821,7 @@
       <c r="C1070">
         <v>0</v>
       </c>
-      <c r="D1070" t="s">
+      <c r="D1070" s="30" t="s">
         <v>857</v>
       </c>
       <c r="F1070" s="14" t="s">
@@ -34816,7 +34847,7 @@
       <c r="C1071">
         <v>0</v>
       </c>
-      <c r="D1071" t="s">
+      <c r="D1071" s="30" t="s">
         <v>858</v>
       </c>
       <c r="F1071" s="14" t="s">
@@ -34842,7 +34873,7 @@
       <c r="C1072">
         <v>0</v>
       </c>
-      <c r="D1072" t="s">
+      <c r="D1072" s="30" t="s">
         <v>859</v>
       </c>
       <c r="F1072" s="14" t="s">
@@ -34868,7 +34899,7 @@
       <c r="C1073">
         <v>0</v>
       </c>
-      <c r="D1073" t="s">
+      <c r="D1073" s="30" t="s">
         <v>860</v>
       </c>
       <c r="F1073" s="14" t="s">
@@ -34894,7 +34925,7 @@
       <c r="C1074">
         <v>0</v>
       </c>
-      <c r="D1074" t="s">
+      <c r="D1074" s="30" t="s">
         <v>861</v>
       </c>
       <c r="F1074" s="14" t="s">
@@ -34920,7 +34951,7 @@
       <c r="C1075">
         <v>0</v>
       </c>
-      <c r="D1075" t="s">
+      <c r="D1075" s="30" t="s">
         <v>862</v>
       </c>
       <c r="F1075" s="14" t="s">
@@ -34946,7 +34977,7 @@
       <c r="C1076">
         <v>0</v>
       </c>
-      <c r="D1076" t="s">
+      <c r="D1076" s="30" t="s">
         <v>863</v>
       </c>
       <c r="F1076" s="14" t="s">
@@ -34972,7 +35003,7 @@
       <c r="C1077">
         <v>0</v>
       </c>
-      <c r="D1077" t="s">
+      <c r="D1077" s="30" t="s">
         <v>864</v>
       </c>
       <c r="F1077" s="14" t="s">
@@ -34998,7 +35029,7 @@
       <c r="C1078">
         <v>0</v>
       </c>
-      <c r="D1078" t="s">
+      <c r="D1078" s="30" t="s">
         <v>865</v>
       </c>
       <c r="F1078" s="14" t="s">
@@ -35024,7 +35055,7 @@
       <c r="C1079">
         <v>0</v>
       </c>
-      <c r="D1079" t="s">
+      <c r="D1079" s="30" t="s">
         <v>957</v>
       </c>
       <c r="F1079" t="s">
@@ -35047,7 +35078,7 @@
       <c r="C1080">
         <v>0</v>
       </c>
-      <c r="D1080" t="s">
+      <c r="D1080" s="30" t="s">
         <v>958</v>
       </c>
       <c r="F1080" t="s">
@@ -35070,7 +35101,7 @@
       <c r="C1081">
         <v>0</v>
       </c>
-      <c r="D1081" t="s">
+      <c r="D1081" s="30" t="s">
         <v>959</v>
       </c>
       <c r="F1081" t="s">
@@ -35093,7 +35124,7 @@
       <c r="C1082">
         <v>0</v>
       </c>
-      <c r="D1082" t="s">
+      <c r="D1082" s="30" t="s">
         <v>960</v>
       </c>
       <c r="F1082" t="s">
@@ -35116,7 +35147,7 @@
       <c r="C1083">
         <v>0</v>
       </c>
-      <c r="D1083" t="s">
+      <c r="D1083" s="30" t="s">
         <v>961</v>
       </c>
       <c r="F1083" t="s">
@@ -35139,7 +35170,7 @@
       <c r="C1084">
         <v>0</v>
       </c>
-      <c r="D1084" t="s">
+      <c r="D1084" s="30" t="s">
         <v>962</v>
       </c>
       <c r="F1084" t="s">
@@ -35162,7 +35193,7 @@
       <c r="C1085">
         <v>0</v>
       </c>
-      <c r="D1085" t="s">
+      <c r="D1085" s="30" t="s">
         <v>963</v>
       </c>
       <c r="F1085" t="s">
@@ -35185,7 +35216,7 @@
       <c r="C1086">
         <v>0</v>
       </c>
-      <c r="D1086" t="s">
+      <c r="D1086" s="30" t="s">
         <v>964</v>
       </c>
       <c r="F1086" t="s">
@@ -35208,7 +35239,7 @@
       <c r="C1087">
         <v>0</v>
       </c>
-      <c r="D1087" t="s">
+      <c r="D1087" s="30" t="s">
         <v>965</v>
       </c>
       <c r="F1087" t="s">
@@ -35231,7 +35262,7 @@
       <c r="C1088">
         <v>0</v>
       </c>
-      <c r="D1088" t="s">
+      <c r="D1088" s="30" t="s">
         <v>966</v>
       </c>
       <c r="F1088" t="s">
@@ -35241,6 +35272,121 @@
         <v>2</v>
       </c>
       <c r="I1088">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1089">
+        <v>820001</v>
+      </c>
+      <c r="B1089" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1089">
+        <v>0</v>
+      </c>
+      <c r="D1089" s="30" t="s">
+        <v>967</v>
+      </c>
+      <c r="G1089">
+        <v>9</v>
+      </c>
+      <c r="H1089" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1089">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1090">
+        <v>8200011</v>
+      </c>
+      <c r="B1090" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1090">
+        <v>0</v>
+      </c>
+      <c r="D1090" s="30" t="s">
+        <v>968</v>
+      </c>
+      <c r="G1090">
+        <v>9</v>
+      </c>
+      <c r="H1090" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1090">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1091">
+        <v>8200012</v>
+      </c>
+      <c r="B1091" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1091">
+        <v>0</v>
+      </c>
+      <c r="D1091" s="30" t="s">
+        <v>969</v>
+      </c>
+      <c r="G1091">
+        <v>9</v>
+      </c>
+      <c r="H1091" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1091">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1092">
+        <v>8200015</v>
+      </c>
+      <c r="B1092" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1092">
+        <v>0</v>
+      </c>
+      <c r="D1092" s="30" t="s">
+        <v>970</v>
+      </c>
+      <c r="G1092">
+        <v>9</v>
+      </c>
+      <c r="H1092" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1092">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1093">
+        <v>8200018</v>
+      </c>
+      <c r="B1093" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1093">
+        <v>0</v>
+      </c>
+      <c r="D1093" s="30" t="s">
+        <v>971</v>
+      </c>
+      <c r="G1093">
+        <v>9</v>
+      </c>
+      <c r="H1093" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1093">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65EE660-8560-4A9F-9DD8-DAFC971B12A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A9F149-F62D-40E0-B2E3-51F23EEA9273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3323" uniqueCount="982">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3392,6 +3392,36 @@
   <si>
     <t>炎域-燃烧-伤害间隔毫秒</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中回血_获得</t>
+  </si>
+  <si>
+    <t>击中回血_冷却</t>
+  </si>
+  <si>
+    <t>击中回血_最近释放距离</t>
+  </si>
+  <si>
+    <t>击中回血_最远释放距离</t>
+  </si>
+  <si>
+    <t>击中回血_技能效果半径</t>
+  </si>
+  <si>
+    <t>击中回血_目标数量</t>
+  </si>
+  <si>
+    <t>击中回血_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>击中回血_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>击中回血_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>击中回血_非主目标直接伤害系数</t>
   </si>
 </sst>
 </file>
@@ -4076,7 +4106,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1093"/>
+  <dimension ref="A1:I1103"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -35387,6 +35417,236 @@
         <v>1</v>
       </c>
       <c r="I1093">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1094">
+        <v>3592200</v>
+      </c>
+      <c r="B1094" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1094">
+        <v>0</v>
+      </c>
+      <c r="D1094" s="30" t="s">
+        <v>972</v>
+      </c>
+      <c r="G1094">
+        <v>9</v>
+      </c>
+      <c r="H1094" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1094">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1095">
+        <v>159260001</v>
+      </c>
+      <c r="B1095" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1095">
+        <v>0</v>
+      </c>
+      <c r="D1095" s="30" t="s">
+        <v>973</v>
+      </c>
+      <c r="G1095">
+        <v>9</v>
+      </c>
+      <c r="H1095" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1095">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1096">
+        <v>259260001</v>
+      </c>
+      <c r="B1096" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1096">
+        <v>0</v>
+      </c>
+      <c r="D1096" s="30" t="s">
+        <v>974</v>
+      </c>
+      <c r="G1096">
+        <v>9</v>
+      </c>
+      <c r="H1096" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1096">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1097">
+        <v>359260001</v>
+      </c>
+      <c r="B1097" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1097">
+        <v>0</v>
+      </c>
+      <c r="D1097" s="30" t="s">
+        <v>975</v>
+      </c>
+      <c r="G1097">
+        <v>9</v>
+      </c>
+      <c r="H1097" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1097">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1098">
+        <v>459260001</v>
+      </c>
+      <c r="B1098" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1098">
+        <v>0</v>
+      </c>
+      <c r="D1098" s="30" t="s">
+        <v>976</v>
+      </c>
+      <c r="G1098">
+        <v>9</v>
+      </c>
+      <c r="H1098" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1098">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1099">
+        <v>559260001</v>
+      </c>
+      <c r="B1099" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1099">
+        <v>0</v>
+      </c>
+      <c r="D1099" s="30" t="s">
+        <v>977</v>
+      </c>
+      <c r="G1099">
+        <v>9</v>
+      </c>
+      <c r="H1099" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1099">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1100">
+        <v>659260001</v>
+      </c>
+      <c r="B1100" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1100">
+        <v>0</v>
+      </c>
+      <c r="D1100" s="30" t="s">
+        <v>978</v>
+      </c>
+      <c r="G1100">
+        <v>9</v>
+      </c>
+      <c r="H1100" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1101">
+        <v>759260001</v>
+      </c>
+      <c r="B1101" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1101">
+        <v>0</v>
+      </c>
+      <c r="D1101" s="30" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1101">
+        <v>9</v>
+      </c>
+      <c r="H1101" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1102">
+        <v>859260001</v>
+      </c>
+      <c r="B1102" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1102">
+        <v>0</v>
+      </c>
+      <c r="D1102" s="30" t="s">
+        <v>980</v>
+      </c>
+      <c r="G1102">
+        <v>9</v>
+      </c>
+      <c r="H1102" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1103">
+        <v>959260001</v>
+      </c>
+      <c r="B1103" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1103">
+        <v>0</v>
+      </c>
+      <c r="D1103" s="30" t="s">
+        <v>981</v>
+      </c>
+      <c r="G1103">
+        <v>9</v>
+      </c>
+      <c r="H1103" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1103">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A9F149-F62D-40E0-B2E3-51F23EEA9273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A307467-7FF0-4487-87CD-498AE048CBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35091,6 +35091,9 @@
       <c r="F1079" t="s">
         <v>957</v>
       </c>
+      <c r="G1079">
+        <v>9</v>
+      </c>
       <c r="H1079" s="28">
         <v>1</v>
       </c>
@@ -35114,6 +35117,9 @@
       <c r="F1080" t="s">
         <v>958</v>
       </c>
+      <c r="G1080">
+        <v>9</v>
+      </c>
       <c r="H1080" s="28">
         <v>1</v>
       </c>
@@ -35137,6 +35143,9 @@
       <c r="F1081" t="s">
         <v>959</v>
       </c>
+      <c r="G1081">
+        <v>9</v>
+      </c>
       <c r="H1081" s="28">
         <v>1</v>
       </c>
@@ -35160,6 +35169,9 @@
       <c r="F1082" t="s">
         <v>960</v>
       </c>
+      <c r="G1082">
+        <v>9</v>
+      </c>
       <c r="H1082" s="28">
         <v>1</v>
       </c>
@@ -35183,6 +35195,9 @@
       <c r="F1083" t="s">
         <v>961</v>
       </c>
+      <c r="G1083">
+        <v>9</v>
+      </c>
       <c r="H1083" s="28">
         <v>1</v>
       </c>
@@ -35206,6 +35221,9 @@
       <c r="F1084" t="s">
         <v>962</v>
       </c>
+      <c r="G1084">
+        <v>9</v>
+      </c>
       <c r="H1084" s="28">
         <v>1</v>
       </c>
@@ -35229,6 +35247,9 @@
       <c r="F1085" t="s">
         <v>963</v>
       </c>
+      <c r="G1085">
+        <v>9</v>
+      </c>
       <c r="H1085" s="28">
         <v>1</v>
       </c>
@@ -35252,6 +35273,9 @@
       <c r="F1086" t="s">
         <v>964</v>
       </c>
+      <c r="G1086">
+        <v>9</v>
+      </c>
       <c r="H1086" s="28">
         <v>2</v>
       </c>
@@ -35275,6 +35299,9 @@
       <c r="F1087" t="s">
         <v>965</v>
       </c>
+      <c r="G1087">
+        <v>9</v>
+      </c>
       <c r="H1087" s="28">
         <v>1</v>
       </c>
@@ -35297,6 +35324,9 @@
       </c>
       <c r="F1088" t="s">
         <v>966</v>
+      </c>
+      <c r="G1088">
+        <v>9</v>
       </c>
       <c r="H1088" s="28">
         <v>2</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A307467-7FF0-4487-87CD-498AE048CBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B285B8-CD0C-4E0D-ADD2-F3A5599FCEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6070,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B285B8-CD0C-4E0D-ADD2-F3A5599FCEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB693128-FE03-4E66-88EC-6F61661066AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3323" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3368" uniqueCount="1007">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3422,6 +3422,83 @@
   </si>
   <si>
     <t>击中回血_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_获得</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_冷却</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_最近释放距离</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_最远释放距离</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_技能效果半径</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_目标数量</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>普攻附加毒爆_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒爆_获得</t>
+  </si>
+  <si>
+    <t>毒爆_冷却</t>
+  </si>
+  <si>
+    <t>毒爆_最近释放距离</t>
+  </si>
+  <si>
+    <t>毒爆_最远释放距离</t>
+  </si>
+  <si>
+    <t>毒爆_技能效果半径</t>
+  </si>
+  <si>
+    <t>毒爆_目标数量</t>
+  </si>
+  <si>
+    <t>毒爆_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒爆_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒爆_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒爆_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒爆-逻辑id</t>
+  </si>
+  <si>
+    <t>毒爆-持续时长毫秒</t>
+  </si>
+  <si>
+    <t>毒爆-伤害间隔毫秒</t>
+  </si>
+  <si>
+    <t>毒爆-毒元素伤害万分比系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒爆-毒元素伤害固定值系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4106,7 +4183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1103"/>
+  <dimension ref="A1:I1128"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -32752,7 +32829,7 @@
         <v>776</v>
       </c>
       <c r="G989">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H989" s="28">
         <v>1</v>
@@ -32778,7 +32855,7 @@
         <v>777</v>
       </c>
       <c r="G990">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H990" s="28">
         <v>1</v>
@@ -32804,7 +32881,7 @@
         <v>778</v>
       </c>
       <c r="G991">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H991" s="28">
         <v>1</v>
@@ -32830,7 +32907,7 @@
         <v>779</v>
       </c>
       <c r="G992">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H992" s="28">
         <v>1</v>
@@ -32856,7 +32933,7 @@
         <v>780</v>
       </c>
       <c r="G993">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H993" s="28">
         <v>1</v>
@@ -32882,7 +32959,7 @@
         <v>781</v>
       </c>
       <c r="G994">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H994" s="28">
         <v>1</v>
@@ -32908,7 +32985,7 @@
         <v>782</v>
       </c>
       <c r="G995">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H995" s="28">
         <v>1</v>
@@ -32934,7 +33011,7 @@
         <v>783</v>
       </c>
       <c r="G996">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H996" s="28">
         <v>1</v>
@@ -32960,7 +33037,7 @@
         <v>784</v>
       </c>
       <c r="G997">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H997" s="28">
         <v>1</v>
@@ -32986,7 +33063,7 @@
         <v>785</v>
       </c>
       <c r="G998">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H998" s="28">
         <v>1</v>
@@ -33012,7 +33089,7 @@
         <v>786</v>
       </c>
       <c r="G999">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H999" s="28">
         <v>1</v>
@@ -33038,7 +33115,7 @@
         <v>787</v>
       </c>
       <c r="G1000">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1000" s="28">
         <v>1</v>
@@ -33064,7 +33141,7 @@
         <v>788</v>
       </c>
       <c r="G1001">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1001" s="28">
         <v>1</v>
@@ -33090,7 +33167,7 @@
         <v>789</v>
       </c>
       <c r="G1002">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1002" s="28">
         <v>1</v>
@@ -33116,7 +33193,7 @@
         <v>790</v>
       </c>
       <c r="G1003">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1003" s="28">
         <v>1</v>
@@ -33142,7 +33219,7 @@
         <v>791</v>
       </c>
       <c r="G1004">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1004" s="28">
         <v>1</v>
@@ -33168,7 +33245,7 @@
         <v>792</v>
       </c>
       <c r="G1005">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1005" s="28">
         <v>1</v>
@@ -33194,7 +33271,7 @@
         <v>793</v>
       </c>
       <c r="G1006">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1006" s="28">
         <v>1</v>
@@ -33220,7 +33297,7 @@
         <v>794</v>
       </c>
       <c r="G1007">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1007" s="28">
         <v>1</v>
@@ -33246,7 +33323,7 @@
         <v>795</v>
       </c>
       <c r="G1008">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1008" s="28">
         <v>1</v>
@@ -33272,7 +33349,7 @@
         <v>796</v>
       </c>
       <c r="G1009">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1009" s="28">
         <v>1</v>
@@ -33298,7 +33375,7 @@
         <v>797</v>
       </c>
       <c r="G1010">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1010" s="28">
         <v>1</v>
@@ -33324,7 +33401,7 @@
         <v>798</v>
       </c>
       <c r="G1011">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1011" s="28">
         <v>1</v>
@@ -33350,7 +33427,7 @@
         <v>799</v>
       </c>
       <c r="G1012">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1012" s="28">
         <v>1</v>
@@ -33376,7 +33453,7 @@
         <v>800</v>
       </c>
       <c r="G1013">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1013" s="28">
         <v>1</v>
@@ -33402,7 +33479,7 @@
         <v>801</v>
       </c>
       <c r="G1014">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1014" s="28">
         <v>1</v>
@@ -33428,7 +33505,7 @@
         <v>802</v>
       </c>
       <c r="G1015">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1015" s="28">
         <v>1</v>
@@ -33454,7 +33531,7 @@
         <v>803</v>
       </c>
       <c r="G1016">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1016" s="28">
         <v>1</v>
@@ -33480,7 +33557,7 @@
         <v>804</v>
       </c>
       <c r="G1017">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1017" s="28">
         <v>1</v>
@@ -33506,7 +33583,7 @@
         <v>805</v>
       </c>
       <c r="G1018">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1018" s="28">
         <v>1</v>
@@ -33532,7 +33609,7 @@
         <v>806</v>
       </c>
       <c r="G1019">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1019" s="28">
         <v>1</v>
@@ -33558,7 +33635,7 @@
         <v>807</v>
       </c>
       <c r="G1020">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1020" s="28">
         <v>1</v>
@@ -33584,7 +33661,7 @@
         <v>808</v>
       </c>
       <c r="G1021">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1021" s="28">
         <v>1</v>
@@ -33610,7 +33687,7 @@
         <v>809</v>
       </c>
       <c r="G1022">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1022" s="28">
         <v>1</v>
@@ -33636,7 +33713,7 @@
         <v>810</v>
       </c>
       <c r="G1023">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1023" s="28">
         <v>1</v>
@@ -33662,7 +33739,7 @@
         <v>811</v>
       </c>
       <c r="G1024">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1024" s="28">
         <v>1</v>
@@ -33688,7 +33765,7 @@
         <v>812</v>
       </c>
       <c r="G1025">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1025" s="28">
         <v>1</v>
@@ -33714,7 +33791,7 @@
         <v>813</v>
       </c>
       <c r="G1026">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1026" s="28">
         <v>1</v>
@@ -33740,7 +33817,7 @@
         <v>814</v>
       </c>
       <c r="G1027">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1027" s="28">
         <v>1</v>
@@ -33766,7 +33843,7 @@
         <v>815</v>
       </c>
       <c r="G1028">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1028" s="28">
         <v>1</v>
@@ -33792,7 +33869,7 @@
         <v>816</v>
       </c>
       <c r="G1029">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1029" s="28">
         <v>1</v>
@@ -33818,7 +33895,7 @@
         <v>817</v>
       </c>
       <c r="G1030">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1030" s="28">
         <v>1</v>
@@ -33844,7 +33921,7 @@
         <v>818</v>
       </c>
       <c r="G1031">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1031" s="28">
         <v>1</v>
@@ -33870,7 +33947,7 @@
         <v>819</v>
       </c>
       <c r="G1032">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1032" s="28">
         <v>1</v>
@@ -33896,7 +33973,7 @@
         <v>820</v>
       </c>
       <c r="G1033">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1033" s="28">
         <v>1</v>
@@ -33922,7 +33999,7 @@
         <v>821</v>
       </c>
       <c r="G1034">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1034" s="28">
         <v>1</v>
@@ -33948,7 +34025,7 @@
         <v>822</v>
       </c>
       <c r="G1035">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1035" s="28">
         <v>1</v>
@@ -33974,7 +34051,7 @@
         <v>823</v>
       </c>
       <c r="G1036">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1036" s="28">
         <v>1</v>
@@ -34000,7 +34077,7 @@
         <v>824</v>
       </c>
       <c r="G1037">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1037" s="28">
         <v>1</v>
@@ -34026,7 +34103,7 @@
         <v>825</v>
       </c>
       <c r="G1038">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1038" s="28">
         <v>1</v>
@@ -34052,7 +34129,7 @@
         <v>826</v>
       </c>
       <c r="G1039">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1039" s="28">
         <v>1</v>
@@ -34078,7 +34155,7 @@
         <v>827</v>
       </c>
       <c r="G1040">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1040" s="28">
         <v>1</v>
@@ -34104,7 +34181,7 @@
         <v>828</v>
       </c>
       <c r="G1041">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1041" s="28">
         <v>1</v>
@@ -34130,7 +34207,7 @@
         <v>829</v>
       </c>
       <c r="G1042">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1042" s="28">
         <v>1</v>
@@ -34156,7 +34233,7 @@
         <v>830</v>
       </c>
       <c r="G1043">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1043" s="28">
         <v>1</v>
@@ -34182,7 +34259,7 @@
         <v>831</v>
       </c>
       <c r="G1044">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1044" s="28">
         <v>1</v>
@@ -34208,7 +34285,7 @@
         <v>832</v>
       </c>
       <c r="G1045">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1045" s="28">
         <v>1</v>
@@ -34234,7 +34311,7 @@
         <v>833</v>
       </c>
       <c r="G1046">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1046" s="28">
         <v>1</v>
@@ -34260,7 +34337,7 @@
         <v>834</v>
       </c>
       <c r="G1047">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1047" s="28">
         <v>1</v>
@@ -34286,7 +34363,7 @@
         <v>835</v>
       </c>
       <c r="G1048">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1048" s="28">
         <v>1</v>
@@ -34312,7 +34389,7 @@
         <v>836</v>
       </c>
       <c r="G1049">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1049" s="28">
         <v>1</v>
@@ -34338,7 +34415,7 @@
         <v>837</v>
       </c>
       <c r="G1050">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1050" s="28">
         <v>1</v>
@@ -34364,7 +34441,7 @@
         <v>838</v>
       </c>
       <c r="G1051">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1051" s="28">
         <v>1</v>
@@ -34390,7 +34467,7 @@
         <v>839</v>
       </c>
       <c r="G1052">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1052" s="28">
         <v>2</v>
@@ -34416,7 +34493,7 @@
         <v>840</v>
       </c>
       <c r="G1053">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1053" s="28">
         <v>2</v>
@@ -34442,7 +34519,7 @@
         <v>841</v>
       </c>
       <c r="G1054">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1054" s="28">
         <v>2</v>
@@ -34468,7 +34545,7 @@
         <v>842</v>
       </c>
       <c r="G1055">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1055" s="28">
         <v>2</v>
@@ -34494,7 +34571,7 @@
         <v>843</v>
       </c>
       <c r="G1056">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1056" s="28">
         <v>2</v>
@@ -34520,7 +34597,7 @@
         <v>844</v>
       </c>
       <c r="G1057">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1057" s="28">
         <v>2</v>
@@ -34546,7 +34623,7 @@
         <v>845</v>
       </c>
       <c r="G1058">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1058" s="28">
         <v>2</v>
@@ -34572,7 +34649,7 @@
         <v>846</v>
       </c>
       <c r="G1059">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1059" s="28">
         <v>2</v>
@@ -34598,7 +34675,7 @@
         <v>847</v>
       </c>
       <c r="G1060">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1060" s="28">
         <v>2</v>
@@ -34624,7 +34701,7 @@
         <v>848</v>
       </c>
       <c r="G1061">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1061" s="28">
         <v>1</v>
@@ -34650,7 +34727,7 @@
         <v>849</v>
       </c>
       <c r="G1062">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1062" s="28">
         <v>1</v>
@@ -34676,7 +34753,7 @@
         <v>850</v>
       </c>
       <c r="G1063">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1063" s="28">
         <v>1</v>
@@ -34702,7 +34779,7 @@
         <v>851</v>
       </c>
       <c r="G1064">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1064" s="28">
         <v>1</v>
@@ -34728,7 +34805,7 @@
         <v>852</v>
       </c>
       <c r="G1065">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1065" s="28">
         <v>1</v>
@@ -34754,7 +34831,7 @@
         <v>853</v>
       </c>
       <c r="G1066">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1066" s="28">
         <v>1</v>
@@ -34780,7 +34857,7 @@
         <v>854</v>
       </c>
       <c r="G1067">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1067" s="28">
         <v>1</v>
@@ -34806,7 +34883,7 @@
         <v>855</v>
       </c>
       <c r="G1068">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1068" s="28">
         <v>1</v>
@@ -34832,7 +34909,7 @@
         <v>856</v>
       </c>
       <c r="G1069">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1069" s="28">
         <v>1</v>
@@ -34858,7 +34935,7 @@
         <v>857</v>
       </c>
       <c r="G1070">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1070" s="28">
         <v>2</v>
@@ -34884,7 +34961,7 @@
         <v>858</v>
       </c>
       <c r="G1071">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1071" s="28">
         <v>2</v>
@@ -34910,7 +34987,7 @@
         <v>859</v>
       </c>
       <c r="G1072">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1072" s="28">
         <v>2</v>
@@ -34936,7 +35013,7 @@
         <v>860</v>
       </c>
       <c r="G1073">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1073" s="28">
         <v>2</v>
@@ -34962,7 +35039,7 @@
         <v>861</v>
       </c>
       <c r="G1074">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1074" s="28">
         <v>2</v>
@@ -34988,7 +35065,7 @@
         <v>862</v>
       </c>
       <c r="G1075">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1075" s="28">
         <v>2</v>
@@ -35014,7 +35091,7 @@
         <v>863</v>
       </c>
       <c r="G1076">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1076" s="28">
         <v>2</v>
@@ -35040,7 +35117,7 @@
         <v>864</v>
       </c>
       <c r="G1077">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1077" s="28">
         <v>2</v>
@@ -35066,7 +35143,7 @@
         <v>865</v>
       </c>
       <c r="G1078">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1078" s="28">
         <v>2</v>
@@ -35092,7 +35169,7 @@
         <v>957</v>
       </c>
       <c r="G1079">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1079" s="28">
         <v>1</v>
@@ -35118,7 +35195,7 @@
         <v>958</v>
       </c>
       <c r="G1080">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1080" s="28">
         <v>1</v>
@@ -35144,7 +35221,7 @@
         <v>959</v>
       </c>
       <c r="G1081">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1081" s="28">
         <v>1</v>
@@ -35170,7 +35247,7 @@
         <v>960</v>
       </c>
       <c r="G1082">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1082" s="28">
         <v>1</v>
@@ -35196,7 +35273,7 @@
         <v>961</v>
       </c>
       <c r="G1083">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1083" s="28">
         <v>1</v>
@@ -35222,7 +35299,7 @@
         <v>962</v>
       </c>
       <c r="G1084">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1084" s="28">
         <v>1</v>
@@ -35248,7 +35325,7 @@
         <v>963</v>
       </c>
       <c r="G1085">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1085" s="28">
         <v>1</v>
@@ -35274,7 +35351,7 @@
         <v>964</v>
       </c>
       <c r="G1086">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1086" s="28">
         <v>2</v>
@@ -35300,7 +35377,7 @@
         <v>965</v>
       </c>
       <c r="G1087">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1087" s="28">
         <v>1</v>
@@ -35326,7 +35403,7 @@
         <v>966</v>
       </c>
       <c r="G1088">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1088" s="28">
         <v>2</v>
@@ -35349,7 +35426,7 @@
         <v>967</v>
       </c>
       <c r="G1089">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1089" s="28">
         <v>1</v>
@@ -35372,7 +35449,7 @@
         <v>968</v>
       </c>
       <c r="G1090">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1090" s="28">
         <v>2</v>
@@ -35395,7 +35472,7 @@
         <v>969</v>
       </c>
       <c r="G1091">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1091" s="28">
         <v>1</v>
@@ -35418,7 +35495,7 @@
         <v>970</v>
       </c>
       <c r="G1092">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1092" s="28">
         <v>1</v>
@@ -35441,7 +35518,7 @@
         <v>971</v>
       </c>
       <c r="G1093">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1093" s="28">
         <v>1</v>
@@ -35464,7 +35541,7 @@
         <v>972</v>
       </c>
       <c r="G1094">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1094" s="28">
         <v>1</v>
@@ -35487,7 +35564,7 @@
         <v>973</v>
       </c>
       <c r="G1095">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1095" s="28">
         <v>1</v>
@@ -35510,7 +35587,7 @@
         <v>974</v>
       </c>
       <c r="G1096">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1096" s="28">
         <v>1</v>
@@ -35533,7 +35610,7 @@
         <v>975</v>
       </c>
       <c r="G1097">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1097" s="28">
         <v>1</v>
@@ -35556,7 +35633,7 @@
         <v>976</v>
       </c>
       <c r="G1098">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1098" s="28">
         <v>1</v>
@@ -35579,7 +35656,7 @@
         <v>977</v>
       </c>
       <c r="G1099">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1099" s="28">
         <v>1</v>
@@ -35602,7 +35679,7 @@
         <v>978</v>
       </c>
       <c r="G1100">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1100" s="28">
         <v>1</v>
@@ -35625,7 +35702,7 @@
         <v>979</v>
       </c>
       <c r="G1101">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1101" s="28">
         <v>2</v>
@@ -35648,7 +35725,7 @@
         <v>980</v>
       </c>
       <c r="G1102">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1102" s="28">
         <v>1</v>
@@ -35671,12 +35748,647 @@
         <v>981</v>
       </c>
       <c r="G1103">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1103" s="28">
         <v>2</v>
       </c>
       <c r="I1103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1104">
+        <v>920011</v>
+      </c>
+      <c r="B1104" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1104">
+        <v>0</v>
+      </c>
+      <c r="D1104" s="30" t="s">
+        <v>982</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>982</v>
+      </c>
+      <c r="G1104">
+        <v>10</v>
+      </c>
+      <c r="H1104" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1105">
+        <v>1920011</v>
+      </c>
+      <c r="B1105" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1105">
+        <v>0</v>
+      </c>
+      <c r="D1105" s="30" t="s">
+        <v>983</v>
+      </c>
+      <c r="F1105" t="s">
+        <v>983</v>
+      </c>
+      <c r="G1105">
+        <v>10</v>
+      </c>
+      <c r="H1105" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1105">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1106">
+        <v>2920011</v>
+      </c>
+      <c r="B1106" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1106">
+        <v>0</v>
+      </c>
+      <c r="D1106" s="30" t="s">
+        <v>984</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>984</v>
+      </c>
+      <c r="G1106">
+        <v>10</v>
+      </c>
+      <c r="H1106" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1107">
+        <v>3920011</v>
+      </c>
+      <c r="B1107" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1107">
+        <v>0</v>
+      </c>
+      <c r="D1107" s="30" t="s">
+        <v>985</v>
+      </c>
+      <c r="F1107" t="s">
+        <v>985</v>
+      </c>
+      <c r="G1107">
+        <v>10</v>
+      </c>
+      <c r="H1107" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1108">
+        <v>4920011</v>
+      </c>
+      <c r="B1108" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1108">
+        <v>0</v>
+      </c>
+      <c r="D1108" s="30" t="s">
+        <v>986</v>
+      </c>
+      <c r="F1108" t="s">
+        <v>986</v>
+      </c>
+      <c r="G1108">
+        <v>10</v>
+      </c>
+      <c r="H1108" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1109">
+        <v>5920011</v>
+      </c>
+      <c r="B1109" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1109">
+        <v>0</v>
+      </c>
+      <c r="D1109" s="30" t="s">
+        <v>987</v>
+      </c>
+      <c r="F1109" t="s">
+        <v>987</v>
+      </c>
+      <c r="G1109">
+        <v>10</v>
+      </c>
+      <c r="H1109" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1110">
+        <v>6920011</v>
+      </c>
+      <c r="B1110" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1110">
+        <v>0</v>
+      </c>
+      <c r="D1110" s="30" t="s">
+        <v>988</v>
+      </c>
+      <c r="F1110" t="s">
+        <v>988</v>
+      </c>
+      <c r="G1110">
+        <v>10</v>
+      </c>
+      <c r="H1110" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1111">
+        <v>7920011</v>
+      </c>
+      <c r="B1111" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1111">
+        <v>0</v>
+      </c>
+      <c r="D1111" s="30" t="s">
+        <v>989</v>
+      </c>
+      <c r="F1111" t="s">
+        <v>989</v>
+      </c>
+      <c r="G1111">
+        <v>10</v>
+      </c>
+      <c r="H1111" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1112">
+        <v>8920011</v>
+      </c>
+      <c r="B1112" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1112">
+        <v>0</v>
+      </c>
+      <c r="D1112" s="30" t="s">
+        <v>990</v>
+      </c>
+      <c r="F1112" t="s">
+        <v>990</v>
+      </c>
+      <c r="G1112">
+        <v>10</v>
+      </c>
+      <c r="H1112" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1113">
+        <v>9920011</v>
+      </c>
+      <c r="B1113" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1113">
+        <v>0</v>
+      </c>
+      <c r="D1113" s="30" t="s">
+        <v>991</v>
+      </c>
+      <c r="F1113" t="s">
+        <v>991</v>
+      </c>
+      <c r="G1113">
+        <v>10</v>
+      </c>
+      <c r="H1113" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1114">
+        <v>920012</v>
+      </c>
+      <c r="B1114" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1114">
+        <v>0</v>
+      </c>
+      <c r="D1114" s="30" t="s">
+        <v>992</v>
+      </c>
+      <c r="F1114" t="s">
+        <v>982</v>
+      </c>
+      <c r="G1114">
+        <v>10</v>
+      </c>
+      <c r="H1114" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1115">
+        <v>1920012</v>
+      </c>
+      <c r="B1115" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1115">
+        <v>0</v>
+      </c>
+      <c r="D1115" s="30" t="s">
+        <v>993</v>
+      </c>
+      <c r="F1115" t="s">
+        <v>983</v>
+      </c>
+      <c r="G1115">
+        <v>10</v>
+      </c>
+      <c r="H1115" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1116">
+        <v>2920012</v>
+      </c>
+      <c r="B1116" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1116">
+        <v>0</v>
+      </c>
+      <c r="D1116" s="30" t="s">
+        <v>994</v>
+      </c>
+      <c r="F1116" t="s">
+        <v>984</v>
+      </c>
+      <c r="G1116">
+        <v>10</v>
+      </c>
+      <c r="H1116" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1117">
+        <v>3920012</v>
+      </c>
+      <c r="B1117" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1117">
+        <v>0</v>
+      </c>
+      <c r="D1117" s="30" t="s">
+        <v>995</v>
+      </c>
+      <c r="F1117" t="s">
+        <v>985</v>
+      </c>
+      <c r="G1117">
+        <v>10</v>
+      </c>
+      <c r="H1117" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1118">
+        <v>4920012</v>
+      </c>
+      <c r="B1118" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1118">
+        <v>0</v>
+      </c>
+      <c r="D1118" s="30" t="s">
+        <v>996</v>
+      </c>
+      <c r="F1118" t="s">
+        <v>986</v>
+      </c>
+      <c r="G1118">
+        <v>10</v>
+      </c>
+      <c r="H1118" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1118">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1119">
+        <v>5920012</v>
+      </c>
+      <c r="B1119" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1119">
+        <v>0</v>
+      </c>
+      <c r="D1119" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="F1119" t="s">
+        <v>987</v>
+      </c>
+      <c r="G1119">
+        <v>10</v>
+      </c>
+      <c r="H1119" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1120">
+        <v>6920012</v>
+      </c>
+      <c r="B1120" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1120">
+        <v>0</v>
+      </c>
+      <c r="D1120" s="30" t="s">
+        <v>998</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>988</v>
+      </c>
+      <c r="G1120">
+        <v>10</v>
+      </c>
+      <c r="H1120" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1120">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1121">
+        <v>7920012</v>
+      </c>
+      <c r="B1121" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1121">
+        <v>0</v>
+      </c>
+      <c r="D1121" s="30" t="s">
+        <v>999</v>
+      </c>
+      <c r="F1121" t="s">
+        <v>989</v>
+      </c>
+      <c r="G1121">
+        <v>10</v>
+      </c>
+      <c r="H1121" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1122">
+        <v>8920012</v>
+      </c>
+      <c r="B1122" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1122">
+        <v>0</v>
+      </c>
+      <c r="D1122" s="30" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F1122" t="s">
+        <v>990</v>
+      </c>
+      <c r="G1122">
+        <v>10</v>
+      </c>
+      <c r="H1122" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1122">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1123">
+        <v>9920012</v>
+      </c>
+      <c r="B1123" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1123">
+        <v>0</v>
+      </c>
+      <c r="D1123" s="30" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F1123" t="s">
+        <v>991</v>
+      </c>
+      <c r="G1123">
+        <v>10</v>
+      </c>
+      <c r="H1123" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1124">
+        <v>820011</v>
+      </c>
+      <c r="B1124" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1124">
+        <v>0</v>
+      </c>
+      <c r="D1124" s="30" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G1124">
+        <v>10</v>
+      </c>
+      <c r="H1124" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1125">
+        <v>8200111</v>
+      </c>
+      <c r="B1125" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1125">
+        <v>0</v>
+      </c>
+      <c r="D1125" s="30" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G1125">
+        <v>10</v>
+      </c>
+      <c r="H1125" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1126">
+        <v>8200112</v>
+      </c>
+      <c r="B1126" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1126">
+        <v>0</v>
+      </c>
+      <c r="D1126" s="30" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G1126">
+        <v>10</v>
+      </c>
+      <c r="H1126" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1127">
+        <v>8200115</v>
+      </c>
+      <c r="B1127" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1127">
+        <v>0</v>
+      </c>
+      <c r="D1127" s="30" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G1127">
+        <v>10</v>
+      </c>
+      <c r="H1127" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1128">
+        <v>8200118</v>
+      </c>
+      <c r="B1128" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1128">
+        <v>0</v>
+      </c>
+      <c r="D1128" s="30" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G1128">
+        <v>10</v>
+      </c>
+      <c r="H1128" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1128">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB693128-FE03-4E66-88EC-6F61661066AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F529076-E903-4424-8F58-85AA606136A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3368" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3408" uniqueCount="1028">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3499,6 +3499,70 @@
   <si>
     <t>毒爆-毒元素伤害固定值系数</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺_获得</t>
+  </si>
+  <si>
+    <t>爆炎冲刺_冷却</t>
+  </si>
+  <si>
+    <t>爆炎冲刺_最近释放距离</t>
+  </si>
+  <si>
+    <t>爆炎冲刺_最远释放距离</t>
+  </si>
+  <si>
+    <t>爆炎冲刺_技能效果半径</t>
+  </si>
+  <si>
+    <t>爆炎冲刺_目标数量</t>
+  </si>
+  <si>
+    <t>爆炎冲刺_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>爆炎冲刺_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>爆炎冲刺_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>爆炎冲刺_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒爆_获得</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>升龙击_获得</t>
+  </si>
+  <si>
+    <t>升龙击_冷却</t>
+  </si>
+  <si>
+    <t>升龙击_最近释放距离</t>
+  </si>
+  <si>
+    <t>升龙击_最远释放距离</t>
+  </si>
+  <si>
+    <t>升龙击_技能效果半径</t>
+  </si>
+  <si>
+    <t>升龙击_目标数量</t>
+  </si>
+  <si>
+    <t>升龙击_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>升龙击_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>升龙击_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>升龙击_非主目标直接伤害系数</t>
   </si>
 </sst>
 </file>
@@ -4183,7 +4247,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1128"/>
+  <dimension ref="A1:I1148"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -36030,8 +36094,8 @@
       <c r="D1114" s="30" t="s">
         <v>992</v>
       </c>
-      <c r="F1114" t="s">
-        <v>982</v>
+      <c r="F1114" s="28" t="s">
+        <v>1017</v>
       </c>
       <c r="G1114">
         <v>10</v>
@@ -36057,7 +36121,7 @@
         <v>993</v>
       </c>
       <c r="F1115" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
       <c r="G1115">
         <v>10</v>
@@ -36083,7 +36147,7 @@
         <v>994</v>
       </c>
       <c r="F1116" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="G1116">
         <v>10</v>
@@ -36109,7 +36173,7 @@
         <v>995</v>
       </c>
       <c r="F1117" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="G1117">
         <v>10</v>
@@ -36135,7 +36199,7 @@
         <v>996</v>
       </c>
       <c r="F1118" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="G1118">
         <v>10</v>
@@ -36161,7 +36225,7 @@
         <v>997</v>
       </c>
       <c r="F1119" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="G1119">
         <v>10</v>
@@ -36187,7 +36251,7 @@
         <v>998</v>
       </c>
       <c r="F1120" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="G1120">
         <v>10</v>
@@ -36196,7 +36260,7 @@
         <v>1</v>
       </c>
       <c r="I1120">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1121" spans="1:9" x14ac:dyDescent="0.15">
@@ -36213,7 +36277,7 @@
         <v>999</v>
       </c>
       <c r="F1121" t="s">
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="G1121">
         <v>10</v>
@@ -36222,7 +36286,7 @@
         <v>2</v>
       </c>
       <c r="I1121">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1122" spans="1:9" x14ac:dyDescent="0.15">
@@ -36239,7 +36303,7 @@
         <v>1000</v>
       </c>
       <c r="F1122" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="G1122">
         <v>10</v>
@@ -36248,7 +36312,7 @@
         <v>1</v>
       </c>
       <c r="I1122">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1123" spans="1:9" x14ac:dyDescent="0.15">
@@ -36265,7 +36329,7 @@
         <v>1001</v>
       </c>
       <c r="F1123" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="G1123">
         <v>10</v>
@@ -36274,7 +36338,7 @@
         <v>2</v>
       </c>
       <c r="I1123">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1124" spans="1:9" x14ac:dyDescent="0.15">
@@ -36390,6 +36454,526 @@
       </c>
       <c r="I1128">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1129">
+        <v>920021</v>
+      </c>
+      <c r="B1129" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1129">
+        <v>0</v>
+      </c>
+      <c r="D1129" s="30" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G1129">
+        <v>10</v>
+      </c>
+      <c r="H1129" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1130">
+        <v>1920021</v>
+      </c>
+      <c r="B1130" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1130">
+        <v>0</v>
+      </c>
+      <c r="D1130" s="30" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F1130" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G1130">
+        <v>10</v>
+      </c>
+      <c r="H1130" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1130">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1131">
+        <v>2920021</v>
+      </c>
+      <c r="B1131" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1131">
+        <v>0</v>
+      </c>
+      <c r="D1131" s="30" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F1131" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G1131">
+        <v>10</v>
+      </c>
+      <c r="H1131" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1132">
+        <v>3920021</v>
+      </c>
+      <c r="B1132" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1132">
+        <v>0</v>
+      </c>
+      <c r="D1132" s="30" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F1132" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G1132">
+        <v>10</v>
+      </c>
+      <c r="H1132" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1132">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1133">
+        <v>4920021</v>
+      </c>
+      <c r="B1133" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1133">
+        <v>0</v>
+      </c>
+      <c r="D1133" s="30" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F1133" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G1133">
+        <v>10</v>
+      </c>
+      <c r="H1133" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1134">
+        <v>5920021</v>
+      </c>
+      <c r="B1134" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1134">
+        <v>0</v>
+      </c>
+      <c r="D1134" s="30" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F1134" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G1134">
+        <v>10</v>
+      </c>
+      <c r="H1134" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1135">
+        <v>6920021</v>
+      </c>
+      <c r="B1135" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1135">
+        <v>0</v>
+      </c>
+      <c r="D1135" s="30" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F1135" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G1135">
+        <v>10</v>
+      </c>
+      <c r="H1135" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1136">
+        <v>7920021</v>
+      </c>
+      <c r="B1136" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1136">
+        <v>0</v>
+      </c>
+      <c r="D1136" s="30" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F1136" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G1136">
+        <v>10</v>
+      </c>
+      <c r="H1136" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1136">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1137">
+        <v>8920021</v>
+      </c>
+      <c r="B1137" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1137">
+        <v>0</v>
+      </c>
+      <c r="D1137" s="30" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F1137" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G1137">
+        <v>10</v>
+      </c>
+      <c r="H1137" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1138">
+        <v>9920021</v>
+      </c>
+      <c r="B1138" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1138">
+        <v>0</v>
+      </c>
+      <c r="D1138" s="30" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F1138" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G1138">
+        <v>10</v>
+      </c>
+      <c r="H1138" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1138">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1139">
+        <v>920022</v>
+      </c>
+      <c r="B1139" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1139">
+        <v>0</v>
+      </c>
+      <c r="D1139" s="30" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F1139" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G1139">
+        <v>10</v>
+      </c>
+      <c r="H1139" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1140">
+        <v>1920022</v>
+      </c>
+      <c r="B1140" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1140">
+        <v>0</v>
+      </c>
+      <c r="D1140" s="30" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F1140" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G1140">
+        <v>10</v>
+      </c>
+      <c r="H1140" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1141">
+        <v>2920022</v>
+      </c>
+      <c r="B1141" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1141">
+        <v>0</v>
+      </c>
+      <c r="D1141" s="30" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F1141" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G1141">
+        <v>10</v>
+      </c>
+      <c r="H1141" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1142">
+        <v>3920022</v>
+      </c>
+      <c r="B1142" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1142">
+        <v>0</v>
+      </c>
+      <c r="D1142" s="30" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F1142" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G1142">
+        <v>10</v>
+      </c>
+      <c r="H1142" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1143">
+        <v>4920022</v>
+      </c>
+      <c r="B1143" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1143">
+        <v>0</v>
+      </c>
+      <c r="D1143" s="30" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F1143" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G1143">
+        <v>10</v>
+      </c>
+      <c r="H1143" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1144">
+        <v>5920022</v>
+      </c>
+      <c r="B1144" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1144">
+        <v>0</v>
+      </c>
+      <c r="D1144" s="30" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F1144" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G1144">
+        <v>10</v>
+      </c>
+      <c r="H1144" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1145">
+        <v>6920022</v>
+      </c>
+      <c r="B1145" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1145">
+        <v>0</v>
+      </c>
+      <c r="D1145" s="30" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G1145">
+        <v>10</v>
+      </c>
+      <c r="H1145" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1146">
+        <v>7920022</v>
+      </c>
+      <c r="B1146" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1146">
+        <v>0</v>
+      </c>
+      <c r="D1146" s="30" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F1146" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G1146">
+        <v>10</v>
+      </c>
+      <c r="H1146" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1146">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1147">
+        <v>8920022</v>
+      </c>
+      <c r="B1147" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1147">
+        <v>0</v>
+      </c>
+      <c r="D1147" s="30" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F1147" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G1147">
+        <v>10</v>
+      </c>
+      <c r="H1147" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1148">
+        <v>9920022</v>
+      </c>
+      <c r="B1148" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1148">
+        <v>0</v>
+      </c>
+      <c r="D1148" s="30" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F1148" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G1148">
+        <v>10</v>
+      </c>
+      <c r="H1148" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1148">
+        <v>50000</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F529076-E903-4424-8F58-85AA606136A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443E9C15-2C37-4A6A-A481-5E327199EF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3408" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3409" uniqueCount="1029">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3563,6 +3563,10 @@
   </si>
   <si>
     <t>升龙击_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>追加升龙击-逻辑id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4247,7 +4251,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1148"/>
+  <dimension ref="A1:I1149"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -36974,6 +36978,29 @@
       </c>
       <c r="I1148">
         <v>50000</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1149">
+        <v>820021</v>
+      </c>
+      <c r="B1149" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1149">
+        <v>0</v>
+      </c>
+      <c r="D1149" s="30" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G1149">
+        <v>10</v>
+      </c>
+      <c r="H1149" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1149">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443E9C15-2C37-4A6A-A481-5E327199EF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE56AE4D-9E5F-460A-820C-C7D73B32CF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -36108,7 +36108,7 @@
         <v>1</v>
       </c>
       <c r="I1114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1115" spans="1:9" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE56AE4D-9E5F-460A-820C-C7D73B32CF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F04EBD1-67B0-4B15-8168-7772D79D8198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3409" uniqueCount="1029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3408" uniqueCount="1028">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3563,10 +3563,6 @@
   </si>
   <si>
     <t>升龙击_非主目标直接伤害系数</t>
-  </si>
-  <si>
-    <t>追加升龙击-逻辑id</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4251,7 +4247,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1149"/>
+  <dimension ref="A1:I1148"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -36978,29 +36974,6 @@
       </c>
       <c r="I1148">
         <v>50000</v>
-      </c>
-    </row>
-    <row r="1149" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1149">
-        <v>820021</v>
-      </c>
-      <c r="B1149" s="25">
-        <v>1</v>
-      </c>
-      <c r="C1149">
-        <v>0</v>
-      </c>
-      <c r="D1149" s="30" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G1149">
-        <v>10</v>
-      </c>
-      <c r="H1149" s="28">
-        <v>1</v>
-      </c>
-      <c r="I1149">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F04EBD1-67B0-4B15-8168-7772D79D8198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292C71FF-2E96-4F4C-B684-E602E64D4770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3408" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="1038">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3563,6 +3563,36 @@
   </si>
   <si>
     <t>升龙击_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>爆炎砸地_获得</t>
+  </si>
+  <si>
+    <t>爆炎砸地_冷却</t>
+  </si>
+  <si>
+    <t>爆炎砸地_最近释放距离</t>
+  </si>
+  <si>
+    <t>爆炎砸地_最远释放距离</t>
+  </si>
+  <si>
+    <t>爆炎砸地_技能效果半径</t>
+  </si>
+  <si>
+    <t>爆炎砸地_目标数量</t>
+  </si>
+  <si>
+    <t>爆炎砸地_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>爆炎砸地_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>爆炎砸地_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>爆炎砸地_非主目标直接伤害系数</t>
   </si>
 </sst>
 </file>
@@ -4247,7 +4277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1148"/>
+  <dimension ref="A1:I1158"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -36974,6 +37004,266 @@
       </c>
       <c r="I1148">
         <v>50000</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1149">
+        <v>920023</v>
+      </c>
+      <c r="B1149" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1149">
+        <v>0</v>
+      </c>
+      <c r="D1149" s="30" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F1149" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G1149">
+        <v>10</v>
+      </c>
+      <c r="H1149" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1150">
+        <v>1920023</v>
+      </c>
+      <c r="B1150" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1150">
+        <v>0</v>
+      </c>
+      <c r="D1150" s="30" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F1150" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G1150">
+        <v>10</v>
+      </c>
+      <c r="H1150" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1151">
+        <v>2920023</v>
+      </c>
+      <c r="B1151" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1151">
+        <v>0</v>
+      </c>
+      <c r="D1151" s="30" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G1151">
+        <v>10</v>
+      </c>
+      <c r="H1151" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1152">
+        <v>3920023</v>
+      </c>
+      <c r="B1152" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1152">
+        <v>0</v>
+      </c>
+      <c r="D1152" s="30" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F1152" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G1152">
+        <v>10</v>
+      </c>
+      <c r="H1152" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1153">
+        <v>4920023</v>
+      </c>
+      <c r="B1153" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1153">
+        <v>0</v>
+      </c>
+      <c r="D1153" s="30" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G1153">
+        <v>10</v>
+      </c>
+      <c r="H1153" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1153">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1154">
+        <v>5920023</v>
+      </c>
+      <c r="B1154" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1154">
+        <v>0</v>
+      </c>
+      <c r="D1154" s="30" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G1154">
+        <v>10</v>
+      </c>
+      <c r="H1154" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1155">
+        <v>6920023</v>
+      </c>
+      <c r="B1155" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1155">
+        <v>0</v>
+      </c>
+      <c r="D1155" s="30" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G1155">
+        <v>10</v>
+      </c>
+      <c r="H1155" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1156">
+        <v>7920023</v>
+      </c>
+      <c r="B1156" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1156">
+        <v>0</v>
+      </c>
+      <c r="D1156" s="30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F1156" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G1156">
+        <v>10</v>
+      </c>
+      <c r="H1156" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1156">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1157">
+        <v>8920023</v>
+      </c>
+      <c r="B1157" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1157">
+        <v>0</v>
+      </c>
+      <c r="D1157" s="30" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G1157">
+        <v>10</v>
+      </c>
+      <c r="H1157" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1158">
+        <v>9920023</v>
+      </c>
+      <c r="B1158" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1158">
+        <v>0</v>
+      </c>
+      <c r="D1158" s="30" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F1158" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G1158">
+        <v>10</v>
+      </c>
+      <c r="H1158" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1158">
+        <v>45000</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292C71FF-2E96-4F4C-B684-E602E64D4770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEE8BF3-E646-4E11-99CD-839944A39993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3448" uniqueCount="1048">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3593,6 +3593,36 @@
   </si>
   <si>
     <t>爆炎砸地_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>闪电链_获得</t>
+  </si>
+  <si>
+    <t>闪电链_冷却</t>
+  </si>
+  <si>
+    <t>闪电链_最近释放距离</t>
+  </si>
+  <si>
+    <t>闪电链_最远释放距离</t>
+  </si>
+  <si>
+    <t>闪电链_技能效果半径</t>
+  </si>
+  <si>
+    <t>闪电链_目标数量</t>
+  </si>
+  <si>
+    <t>闪电链_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>闪电链_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>闪电链_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>闪电链_非主目标直接伤害系数</t>
   </si>
 </sst>
 </file>
@@ -4277,7 +4307,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1158"/>
+  <dimension ref="A1:I1168"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -37264,6 +37294,266 @@
       </c>
       <c r="I1158">
         <v>45000</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1159">
+        <v>920031</v>
+      </c>
+      <c r="B1159" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1159">
+        <v>0</v>
+      </c>
+      <c r="D1159" s="30" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G1159">
+        <v>10</v>
+      </c>
+      <c r="H1159" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1160">
+        <v>1920031</v>
+      </c>
+      <c r="B1160" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1160">
+        <v>0</v>
+      </c>
+      <c r="D1160" s="30" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F1160" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G1160">
+        <v>10</v>
+      </c>
+      <c r="H1160" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1160">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1161">
+        <v>2920031</v>
+      </c>
+      <c r="B1161" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1161">
+        <v>0</v>
+      </c>
+      <c r="D1161" s="30" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G1161">
+        <v>10</v>
+      </c>
+      <c r="H1161" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1162">
+        <v>3920031</v>
+      </c>
+      <c r="B1162" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1162">
+        <v>0</v>
+      </c>
+      <c r="D1162" s="30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F1162" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G1162">
+        <v>10</v>
+      </c>
+      <c r="H1162" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1162">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1163">
+        <v>4920031</v>
+      </c>
+      <c r="B1163" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1163">
+        <v>0</v>
+      </c>
+      <c r="D1163" s="30" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F1163" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1163">
+        <v>10</v>
+      </c>
+      <c r="H1163" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1164">
+        <v>5920031</v>
+      </c>
+      <c r="B1164" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1164">
+        <v>0</v>
+      </c>
+      <c r="D1164" s="30" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F1164" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G1164">
+        <v>10</v>
+      </c>
+      <c r="H1164" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1164">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1165">
+        <v>6920031</v>
+      </c>
+      <c r="B1165" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1165">
+        <v>0</v>
+      </c>
+      <c r="D1165" s="30" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F1165" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G1165">
+        <v>10</v>
+      </c>
+      <c r="H1165" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1165">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1166">
+        <v>7920031</v>
+      </c>
+      <c r="B1166" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1166">
+        <v>0</v>
+      </c>
+      <c r="D1166" s="30" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F1166" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G1166">
+        <v>10</v>
+      </c>
+      <c r="H1166" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1166">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1167">
+        <v>8920031</v>
+      </c>
+      <c r="B1167" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1167">
+        <v>0</v>
+      </c>
+      <c r="D1167" s="30" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F1167" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G1167">
+        <v>10</v>
+      </c>
+      <c r="H1167" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1168">
+        <v>9920031</v>
+      </c>
+      <c r="B1168" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1168">
+        <v>0</v>
+      </c>
+      <c r="D1168" s="30" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F1168" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G1168">
+        <v>10</v>
+      </c>
+      <c r="H1168" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1168">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEE8BF3-E646-4E11-99CD-839944A39993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCFCB96-8F02-4AFC-9D6E-0C77D0E6E748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -37423,7 +37423,7 @@
         <v>1</v>
       </c>
       <c r="I1163">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1164" spans="1:9" x14ac:dyDescent="0.15">
@@ -37449,7 +37449,7 @@
         <v>1</v>
       </c>
       <c r="I1164">
-        <v>5000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1165" spans="1:9" x14ac:dyDescent="0.15">
@@ -37475,7 +37475,7 @@
         <v>1</v>
       </c>
       <c r="I1165">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1166" spans="1:9" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCFCB96-8F02-4AFC-9D6E-0C77D0E6E748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7256AA6F-E824-4724-82E6-D32E022C4BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3448" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3468" uniqueCount="1058">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3623,6 +3623,36 @@
   </si>
   <si>
     <t>闪电链_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>召唤守卫_获得</t>
+  </si>
+  <si>
+    <t>召唤守卫_冷却</t>
+  </si>
+  <si>
+    <t>召唤守卫_最近释放距离</t>
+  </si>
+  <si>
+    <t>召唤守卫_最远释放距离</t>
+  </si>
+  <si>
+    <t>召唤守卫_技能效果半径</t>
+  </si>
+  <si>
+    <t>召唤守卫_目标数量</t>
+  </si>
+  <si>
+    <t>召唤守卫_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>召唤守卫_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>召唤守卫_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>召唤守卫_非主目标直接伤害系数</t>
   </si>
 </sst>
 </file>
@@ -4307,7 +4337,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1168"/>
+  <dimension ref="A1:I1178"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -37554,6 +37584,266 @@
       </c>
       <c r="I1168">
         <v>20000</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1169">
+        <v>920041</v>
+      </c>
+      <c r="B1169" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1169">
+        <v>0</v>
+      </c>
+      <c r="D1169" s="30" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F1169" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G1169">
+        <v>10</v>
+      </c>
+      <c r="H1169" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1170">
+        <v>1920041</v>
+      </c>
+      <c r="B1170" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1170">
+        <v>0</v>
+      </c>
+      <c r="D1170" s="30" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F1170" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G1170">
+        <v>10</v>
+      </c>
+      <c r="H1170" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1170">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1171">
+        <v>2920041</v>
+      </c>
+      <c r="B1171" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1171">
+        <v>0</v>
+      </c>
+      <c r="D1171" s="30" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F1171" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G1171">
+        <v>10</v>
+      </c>
+      <c r="H1171" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1172">
+        <v>3920041</v>
+      </c>
+      <c r="B1172" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1172">
+        <v>0</v>
+      </c>
+      <c r="D1172" s="30" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F1172" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G1172">
+        <v>10</v>
+      </c>
+      <c r="H1172" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1172">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1173">
+        <v>4920041</v>
+      </c>
+      <c r="B1173" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1173">
+        <v>0</v>
+      </c>
+      <c r="D1173" s="30" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F1173" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G1173">
+        <v>10</v>
+      </c>
+      <c r="H1173" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1174">
+        <v>5920041</v>
+      </c>
+      <c r="B1174" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1174">
+        <v>0</v>
+      </c>
+      <c r="D1174" s="30" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F1174" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G1174">
+        <v>10</v>
+      </c>
+      <c r="H1174" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1175">
+        <v>6920041</v>
+      </c>
+      <c r="B1175" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1175">
+        <v>0</v>
+      </c>
+      <c r="D1175" s="30" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F1175" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G1175">
+        <v>10</v>
+      </c>
+      <c r="H1175" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1176">
+        <v>7920041</v>
+      </c>
+      <c r="B1176" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1176">
+        <v>0</v>
+      </c>
+      <c r="D1176" s="30" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1176" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G1176">
+        <v>10</v>
+      </c>
+      <c r="H1176" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1177">
+        <v>8920041</v>
+      </c>
+      <c r="B1177" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1177">
+        <v>0</v>
+      </c>
+      <c r="D1177" s="30" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F1177" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G1177">
+        <v>10</v>
+      </c>
+      <c r="H1177" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1178">
+        <v>9920041</v>
+      </c>
+      <c r="B1178" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1178">
+        <v>0</v>
+      </c>
+      <c r="D1178" s="30" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F1178" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G1178">
+        <v>10</v>
+      </c>
+      <c r="H1178" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1178">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7256AA6F-E824-4724-82E6-D32E022C4BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E1715F-DBE5-4179-AF4D-7AB8507CBDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3468" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3472" uniqueCount="1060">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3653,6 +3653,14 @@
   </si>
   <si>
     <t>召唤守卫_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>炎域_技能持续时间</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎域_技能伤害\效果生效间隔</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4337,7 +4345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1178"/>
+  <dimension ref="A1:I1180"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -5083,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.15">
@@ -35568,7 +35576,7 @@
     </row>
     <row r="1089" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1089">
-        <v>820001</v>
+        <v>10920001</v>
       </c>
       <c r="B1089" s="25">
         <v>1</v>
@@ -35577,7 +35585,10 @@
         <v>0</v>
       </c>
       <c r="D1089" s="30" t="s">
-        <v>967</v>
+        <v>1058</v>
+      </c>
+      <c r="F1089" s="30" t="s">
+        <v>1058</v>
       </c>
       <c r="G1089">
         <v>10</v>
@@ -35586,12 +35597,12 @@
         <v>1</v>
       </c>
       <c r="I1089">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1090" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1090">
-        <v>8200011</v>
+        <v>11920001</v>
       </c>
       <c r="B1090" s="25">
         <v>1</v>
@@ -35600,21 +35611,24 @@
         <v>0</v>
       </c>
       <c r="D1090" s="30" t="s">
-        <v>968</v>
+        <v>1059</v>
+      </c>
+      <c r="F1090" s="30" t="s">
+        <v>1059</v>
       </c>
       <c r="G1090">
         <v>10</v>
       </c>
       <c r="H1090" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1090">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1091" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1091">
-        <v>8200012</v>
+        <v>820001</v>
       </c>
       <c r="B1091" s="25">
         <v>1</v>
@@ -35623,7 +35637,7 @@
         <v>0</v>
       </c>
       <c r="D1091" s="30" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="G1091">
         <v>10</v>
@@ -35637,7 +35651,7 @@
     </row>
     <row r="1092" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1092">
-        <v>8200015</v>
+        <v>8200011</v>
       </c>
       <c r="B1092" s="25">
         <v>1</v>
@@ -35646,13 +35660,13 @@
         <v>0</v>
       </c>
       <c r="D1092" s="30" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G1092">
         <v>10</v>
       </c>
       <c r="H1092" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1092">
         <v>0</v>
@@ -35660,7 +35674,7 @@
     </row>
     <row r="1093" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1093">
-        <v>8200018</v>
+        <v>8200012</v>
       </c>
       <c r="B1093" s="25">
         <v>1</v>
@@ -35669,7 +35683,7 @@
         <v>0</v>
       </c>
       <c r="D1093" s="30" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G1093">
         <v>10</v>
@@ -35683,7 +35697,7 @@
     </row>
     <row r="1094" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1094">
-        <v>3592200</v>
+        <v>8200015</v>
       </c>
       <c r="B1094" s="25">
         <v>1</v>
@@ -35692,7 +35706,7 @@
         <v>0</v>
       </c>
       <c r="D1094" s="30" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="G1094">
         <v>10</v>
@@ -35706,7 +35720,7 @@
     </row>
     <row r="1095" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1095">
-        <v>159260001</v>
+        <v>8200018</v>
       </c>
       <c r="B1095" s="25">
         <v>1</v>
@@ -35715,7 +35729,7 @@
         <v>0</v>
       </c>
       <c r="D1095" s="30" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="G1095">
         <v>10</v>
@@ -35729,7 +35743,7 @@
     </row>
     <row r="1096" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1096">
-        <v>259260001</v>
+        <v>3592200</v>
       </c>
       <c r="B1096" s="25">
         <v>1</v>
@@ -35738,7 +35752,7 @@
         <v>0</v>
       </c>
       <c r="D1096" s="30" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G1096">
         <v>10</v>
@@ -35752,7 +35766,7 @@
     </row>
     <row r="1097" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1097">
-        <v>359260001</v>
+        <v>159260001</v>
       </c>
       <c r="B1097" s="25">
         <v>1</v>
@@ -35761,7 +35775,7 @@
         <v>0</v>
       </c>
       <c r="D1097" s="30" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G1097">
         <v>10</v>
@@ -35775,7 +35789,7 @@
     </row>
     <row r="1098" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1098">
-        <v>459260001</v>
+        <v>259260001</v>
       </c>
       <c r="B1098" s="25">
         <v>1</v>
@@ -35784,7 +35798,7 @@
         <v>0</v>
       </c>
       <c r="D1098" s="30" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="G1098">
         <v>10</v>
@@ -35798,7 +35812,7 @@
     </row>
     <row r="1099" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1099">
-        <v>559260001</v>
+        <v>359260001</v>
       </c>
       <c r="B1099" s="25">
         <v>1</v>
@@ -35807,7 +35821,7 @@
         <v>0</v>
       </c>
       <c r="D1099" s="30" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="G1099">
         <v>10</v>
@@ -35821,7 +35835,7 @@
     </row>
     <row r="1100" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1100">
-        <v>659260001</v>
+        <v>459260001</v>
       </c>
       <c r="B1100" s="25">
         <v>1</v>
@@ -35830,7 +35844,7 @@
         <v>0</v>
       </c>
       <c r="D1100" s="30" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="G1100">
         <v>10</v>
@@ -35844,7 +35858,7 @@
     </row>
     <row r="1101" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1101">
-        <v>759260001</v>
+        <v>559260001</v>
       </c>
       <c r="B1101" s="25">
         <v>1</v>
@@ -35853,13 +35867,13 @@
         <v>0</v>
       </c>
       <c r="D1101" s="30" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G1101">
         <v>10</v>
       </c>
       <c r="H1101" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1101">
         <v>0</v>
@@ -35867,7 +35881,7 @@
     </row>
     <row r="1102" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1102">
-        <v>859260001</v>
+        <v>659260001</v>
       </c>
       <c r="B1102" s="25">
         <v>1</v>
@@ -35876,7 +35890,7 @@
         <v>0</v>
       </c>
       <c r="D1102" s="30" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="G1102">
         <v>10</v>
@@ -35890,7 +35904,7 @@
     </row>
     <row r="1103" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1103">
-        <v>959260001</v>
+        <v>759260001</v>
       </c>
       <c r="B1103" s="25">
         <v>1</v>
@@ -35899,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="D1103" s="30" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G1103">
         <v>10</v>
@@ -35913,7 +35927,7 @@
     </row>
     <row r="1104" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1104">
-        <v>920011</v>
+        <v>859260001</v>
       </c>
       <c r="B1104" s="25">
         <v>1</v>
@@ -35922,10 +35936,7 @@
         <v>0</v>
       </c>
       <c r="D1104" s="30" t="s">
-        <v>982</v>
-      </c>
-      <c r="F1104" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="G1104">
         <v>10</v>
@@ -35939,7 +35950,7 @@
     </row>
     <row r="1105" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1105">
-        <v>1920011</v>
+        <v>959260001</v>
       </c>
       <c r="B1105" s="25">
         <v>1</v>
@@ -35948,24 +35959,21 @@
         <v>0</v>
       </c>
       <c r="D1105" s="30" t="s">
-        <v>983</v>
-      </c>
-      <c r="F1105" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G1105">
         <v>10</v>
       </c>
       <c r="H1105" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1105">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1106" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1106">
-        <v>2920011</v>
+        <v>920011</v>
       </c>
       <c r="B1106" s="25">
         <v>1</v>
@@ -35974,10 +35982,10 @@
         <v>0</v>
       </c>
       <c r="D1106" s="30" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F1106" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="G1106">
         <v>10</v>
@@ -35991,7 +35999,7 @@
     </row>
     <row r="1107" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1107">
-        <v>3920011</v>
+        <v>1920011</v>
       </c>
       <c r="B1107" s="25">
         <v>1</v>
@@ -36000,10 +36008,10 @@
         <v>0</v>
       </c>
       <c r="D1107" s="30" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="F1107" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G1107">
         <v>10</v>
@@ -36012,12 +36020,12 @@
         <v>1</v>
       </c>
       <c r="I1107">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1108" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1108">
-        <v>4920011</v>
+        <v>2920011</v>
       </c>
       <c r="B1108" s="25">
         <v>1</v>
@@ -36026,10 +36034,10 @@
         <v>0</v>
       </c>
       <c r="D1108" s="30" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F1108" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="G1108">
         <v>10</v>
@@ -36043,7 +36051,7 @@
     </row>
     <row r="1109" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1109">
-        <v>5920011</v>
+        <v>3920011</v>
       </c>
       <c r="B1109" s="25">
         <v>1</v>
@@ -36052,10 +36060,10 @@
         <v>0</v>
       </c>
       <c r="D1109" s="30" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="F1109" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G1109">
         <v>10</v>
@@ -36069,7 +36077,7 @@
     </row>
     <row r="1110" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1110">
-        <v>6920011</v>
+        <v>4920011</v>
       </c>
       <c r="B1110" s="25">
         <v>1</v>
@@ -36078,10 +36086,10 @@
         <v>0</v>
       </c>
       <c r="D1110" s="30" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F1110" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="G1110">
         <v>10</v>
@@ -36095,7 +36103,7 @@
     </row>
     <row r="1111" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1111">
-        <v>7920011</v>
+        <v>5920011</v>
       </c>
       <c r="B1111" s="25">
         <v>1</v>
@@ -36104,16 +36112,16 @@
         <v>0</v>
       </c>
       <c r="D1111" s="30" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="F1111" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="G1111">
         <v>10</v>
       </c>
       <c r="H1111" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1111">
         <v>0</v>
@@ -36121,7 +36129,7 @@
     </row>
     <row r="1112" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1112">
-        <v>8920011</v>
+        <v>6920011</v>
       </c>
       <c r="B1112" s="25">
         <v>1</v>
@@ -36130,10 +36138,10 @@
         <v>0</v>
       </c>
       <c r="D1112" s="30" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F1112" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G1112">
         <v>10</v>
@@ -36147,7 +36155,7 @@
     </row>
     <row r="1113" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1113">
-        <v>9920011</v>
+        <v>7920011</v>
       </c>
       <c r="B1113" s="25">
         <v>1</v>
@@ -36156,10 +36164,10 @@
         <v>0</v>
       </c>
       <c r="D1113" s="30" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="F1113" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="G1113">
         <v>10</v>
@@ -36173,7 +36181,7 @@
     </row>
     <row r="1114" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1114">
-        <v>920012</v>
+        <v>8920011</v>
       </c>
       <c r="B1114" s="25">
         <v>1</v>
@@ -36182,10 +36190,10 @@
         <v>0</v>
       </c>
       <c r="D1114" s="30" t="s">
-        <v>992</v>
-      </c>
-      <c r="F1114" s="28" t="s">
-        <v>1017</v>
+        <v>990</v>
+      </c>
+      <c r="F1114" t="s">
+        <v>990</v>
       </c>
       <c r="G1114">
         <v>10</v>
@@ -36199,7 +36207,7 @@
     </row>
     <row r="1115" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1115">
-        <v>1920012</v>
+        <v>9920011</v>
       </c>
       <c r="B1115" s="25">
         <v>1</v>
@@ -36208,16 +36216,16 @@
         <v>0</v>
       </c>
       <c r="D1115" s="30" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="F1115" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G1115">
         <v>10</v>
       </c>
       <c r="H1115" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1115">
         <v>0</v>
@@ -36225,7 +36233,7 @@
     </row>
     <row r="1116" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1116">
-        <v>2920012</v>
+        <v>920012</v>
       </c>
       <c r="B1116" s="25">
         <v>1</v>
@@ -36234,10 +36242,10 @@
         <v>0</v>
       </c>
       <c r="D1116" s="30" t="s">
-        <v>994</v>
-      </c>
-      <c r="F1116" t="s">
-        <v>994</v>
+        <v>992</v>
+      </c>
+      <c r="F1116" s="28" t="s">
+        <v>1017</v>
       </c>
       <c r="G1116">
         <v>10</v>
@@ -36251,7 +36259,7 @@
     </row>
     <row r="1117" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1117">
-        <v>3920012</v>
+        <v>1920012</v>
       </c>
       <c r="B1117" s="25">
         <v>1</v>
@@ -36260,10 +36268,10 @@
         <v>0</v>
       </c>
       <c r="D1117" s="30" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="F1117" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="G1117">
         <v>10</v>
@@ -36277,7 +36285,7 @@
     </row>
     <row r="1118" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1118">
-        <v>4920012</v>
+        <v>2920012</v>
       </c>
       <c r="B1118" s="25">
         <v>1</v>
@@ -36286,10 +36294,10 @@
         <v>0</v>
       </c>
       <c r="D1118" s="30" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="F1118" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="G1118">
         <v>10</v>
@@ -36298,12 +36306,12 @@
         <v>1</v>
       </c>
       <c r="I1118">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1119" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1119">
-        <v>5920012</v>
+        <v>3920012</v>
       </c>
       <c r="B1119" s="25">
         <v>1</v>
@@ -36312,10 +36320,10 @@
         <v>0</v>
       </c>
       <c r="D1119" s="30" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="F1119" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G1119">
         <v>10</v>
@@ -36329,7 +36337,7 @@
     </row>
     <row r="1120" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1120">
-        <v>6920012</v>
+        <v>4920012</v>
       </c>
       <c r="B1120" s="25">
         <v>1</v>
@@ -36338,10 +36346,10 @@
         <v>0</v>
       </c>
       <c r="D1120" s="30" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="F1120" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G1120">
         <v>10</v>
@@ -36350,12 +36358,12 @@
         <v>1</v>
       </c>
       <c r="I1120">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1121" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1121">
-        <v>7920012</v>
+        <v>5920012</v>
       </c>
       <c r="B1121" s="25">
         <v>1</v>
@@ -36364,24 +36372,24 @@
         <v>0</v>
       </c>
       <c r="D1121" s="30" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="F1121" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G1121">
         <v>10</v>
       </c>
       <c r="H1121" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1121">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1122" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1122">
-        <v>8920012</v>
+        <v>6920012</v>
       </c>
       <c r="B1122" s="25">
         <v>1</v>
@@ -36390,10 +36398,10 @@
         <v>0</v>
       </c>
       <c r="D1122" s="30" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="F1122" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="G1122">
         <v>10</v>
@@ -36407,7 +36415,7 @@
     </row>
     <row r="1123" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1123">
-        <v>9920012</v>
+        <v>7920012</v>
       </c>
       <c r="B1123" s="25">
         <v>1</v>
@@ -36416,10 +36424,10 @@
         <v>0</v>
       </c>
       <c r="D1123" s="30" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="F1123" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="G1123">
         <v>10</v>
@@ -36433,7 +36441,7 @@
     </row>
     <row r="1124" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1124">
-        <v>820011</v>
+        <v>8920012</v>
       </c>
       <c r="B1124" s="25">
         <v>1</v>
@@ -36442,7 +36450,10 @@
         <v>0</v>
       </c>
       <c r="D1124" s="30" t="s">
-        <v>1002</v>
+        <v>1000</v>
+      </c>
+      <c r="F1124" t="s">
+        <v>1000</v>
       </c>
       <c r="G1124">
         <v>10</v>
@@ -36456,7 +36467,7 @@
     </row>
     <row r="1125" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1125">
-        <v>8200111</v>
+        <v>9920012</v>
       </c>
       <c r="B1125" s="25">
         <v>1</v>
@@ -36465,7 +36476,10 @@
         <v>0</v>
       </c>
       <c r="D1125" s="30" t="s">
-        <v>1005</v>
+        <v>1001</v>
+      </c>
+      <c r="F1125" t="s">
+        <v>1001</v>
       </c>
       <c r="G1125">
         <v>10</v>
@@ -36474,12 +36488,12 @@
         <v>2</v>
       </c>
       <c r="I1125">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1126" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1126">
-        <v>8200112</v>
+        <v>820011</v>
       </c>
       <c r="B1126" s="25">
         <v>1</v>
@@ -36488,7 +36502,7 @@
         <v>0</v>
       </c>
       <c r="D1126" s="30" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="G1126">
         <v>10</v>
@@ -36502,7 +36516,7 @@
     </row>
     <row r="1127" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1127">
-        <v>8200115</v>
+        <v>8200111</v>
       </c>
       <c r="B1127" s="25">
         <v>1</v>
@@ -36511,13 +36525,13 @@
         <v>0</v>
       </c>
       <c r="D1127" s="30" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="G1127">
         <v>10</v>
       </c>
       <c r="H1127" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1127">
         <v>0</v>
@@ -36525,7 +36539,7 @@
     </row>
     <row r="1128" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1128">
-        <v>8200118</v>
+        <v>8200112</v>
       </c>
       <c r="B1128" s="25">
         <v>1</v>
@@ -36534,7 +36548,7 @@
         <v>0</v>
       </c>
       <c r="D1128" s="30" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="G1128">
         <v>10</v>
@@ -36548,7 +36562,7 @@
     </row>
     <row r="1129" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1129">
-        <v>920021</v>
+        <v>8200115</v>
       </c>
       <c r="B1129" s="25">
         <v>1</v>
@@ -36557,10 +36571,7 @@
         <v>0</v>
       </c>
       <c r="D1129" s="30" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F1129" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="G1129">
         <v>10</v>
@@ -36574,7 +36585,7 @@
     </row>
     <row r="1130" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1130">
-        <v>1920021</v>
+        <v>8200118</v>
       </c>
       <c r="B1130" s="25">
         <v>1</v>
@@ -36583,10 +36594,7 @@
         <v>0</v>
       </c>
       <c r="D1130" s="30" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F1130" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="G1130">
         <v>10</v>
@@ -36595,12 +36603,12 @@
         <v>1</v>
       </c>
       <c r="I1130">
-        <v>7000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1131" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1131">
-        <v>2920021</v>
+        <v>920021</v>
       </c>
       <c r="B1131" s="25">
         <v>1</v>
@@ -36609,10 +36617,10 @@
         <v>0</v>
       </c>
       <c r="D1131" s="30" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="F1131" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G1131">
         <v>10</v>
@@ -36626,7 +36634,7 @@
     </row>
     <row r="1132" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1132">
-        <v>3920021</v>
+        <v>1920021</v>
       </c>
       <c r="B1132" s="25">
         <v>1</v>
@@ -36635,10 +36643,10 @@
         <v>0</v>
       </c>
       <c r="D1132" s="30" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F1132" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G1132">
         <v>10</v>
@@ -36647,12 +36655,12 @@
         <v>1</v>
       </c>
       <c r="I1132">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1133" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1133">
-        <v>4920021</v>
+        <v>2920021</v>
       </c>
       <c r="B1133" s="25">
         <v>1</v>
@@ -36661,10 +36669,10 @@
         <v>0</v>
       </c>
       <c r="D1133" s="30" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="F1133" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G1133">
         <v>10</v>
@@ -36678,7 +36686,7 @@
     </row>
     <row r="1134" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1134">
-        <v>5920021</v>
+        <v>3920021</v>
       </c>
       <c r="B1134" s="25">
         <v>1</v>
@@ -36687,10 +36695,10 @@
         <v>0</v>
       </c>
       <c r="D1134" s="30" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="F1134" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="G1134">
         <v>10</v>
@@ -36699,12 +36707,12 @@
         <v>1</v>
       </c>
       <c r="I1134">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1135" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1135">
-        <v>6920021</v>
+        <v>4920021</v>
       </c>
       <c r="B1135" s="25">
         <v>1</v>
@@ -36713,10 +36721,10 @@
         <v>0</v>
       </c>
       <c r="D1135" s="30" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="F1135" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="G1135">
         <v>10</v>
@@ -36730,7 +36738,7 @@
     </row>
     <row r="1136" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1136">
-        <v>7920021</v>
+        <v>5920021</v>
       </c>
       <c r="B1136" s="25">
         <v>1</v>
@@ -36739,24 +36747,24 @@
         <v>0</v>
       </c>
       <c r="D1136" s="30" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F1136" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G1136">
         <v>10</v>
       </c>
       <c r="H1136" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1136">
-        <v>25000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1137" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1137">
-        <v>8920021</v>
+        <v>6920021</v>
       </c>
       <c r="B1137" s="25">
         <v>1</v>
@@ -36765,10 +36773,10 @@
         <v>0</v>
       </c>
       <c r="D1137" s="30" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="F1137" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G1137">
         <v>10</v>
@@ -36782,7 +36790,7 @@
     </row>
     <row r="1138" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1138">
-        <v>9920021</v>
+        <v>7920021</v>
       </c>
       <c r="B1138" s="25">
         <v>1</v>
@@ -36791,10 +36799,10 @@
         <v>0</v>
       </c>
       <c r="D1138" s="30" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="F1138" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G1138">
         <v>10</v>
@@ -36808,7 +36816,7 @@
     </row>
     <row r="1139" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1139">
-        <v>920022</v>
+        <v>8920021</v>
       </c>
       <c r="B1139" s="25">
         <v>1</v>
@@ -36817,10 +36825,10 @@
         <v>0</v>
       </c>
       <c r="D1139" s="30" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="F1139" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="G1139">
         <v>10</v>
@@ -36834,7 +36842,7 @@
     </row>
     <row r="1140" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1140">
-        <v>1920022</v>
+        <v>9920021</v>
       </c>
       <c r="B1140" s="25">
         <v>1</v>
@@ -36843,24 +36851,24 @@
         <v>0</v>
       </c>
       <c r="D1140" s="30" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="F1140" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="G1140">
         <v>10</v>
       </c>
       <c r="H1140" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1140">
-        <v>0</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="1141" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1141">
-        <v>2920022</v>
+        <v>920022</v>
       </c>
       <c r="B1141" s="25">
         <v>1</v>
@@ -36869,10 +36877,10 @@
         <v>0</v>
       </c>
       <c r="D1141" s="30" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F1141" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="G1141">
         <v>10</v>
@@ -36886,7 +36894,7 @@
     </row>
     <row r="1142" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1142">
-        <v>3920022</v>
+        <v>1920022</v>
       </c>
       <c r="B1142" s="25">
         <v>1</v>
@@ -36895,10 +36903,10 @@
         <v>0</v>
       </c>
       <c r="D1142" s="30" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="F1142" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G1142">
         <v>10</v>
@@ -36912,7 +36920,7 @@
     </row>
     <row r="1143" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1143">
-        <v>4920022</v>
+        <v>2920022</v>
       </c>
       <c r="B1143" s="25">
         <v>1</v>
@@ -36921,10 +36929,10 @@
         <v>0</v>
       </c>
       <c r="D1143" s="30" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="F1143" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G1143">
         <v>10</v>
@@ -36938,7 +36946,7 @@
     </row>
     <row r="1144" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1144">
-        <v>5920022</v>
+        <v>3920022</v>
       </c>
       <c r="B1144" s="25">
         <v>1</v>
@@ -36947,10 +36955,10 @@
         <v>0</v>
       </c>
       <c r="D1144" s="30" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="F1144" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G1144">
         <v>10</v>
@@ -36964,7 +36972,7 @@
     </row>
     <row r="1145" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1145">
-        <v>6920022</v>
+        <v>4920022</v>
       </c>
       <c r="B1145" s="25">
         <v>1</v>
@@ -36973,10 +36981,10 @@
         <v>0</v>
       </c>
       <c r="D1145" s="30" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F1145" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="G1145">
         <v>10</v>
@@ -36990,7 +36998,7 @@
     </row>
     <row r="1146" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1146">
-        <v>7920022</v>
+        <v>5920022</v>
       </c>
       <c r="B1146" s="25">
         <v>1</v>
@@ -36999,24 +37007,24 @@
         <v>0</v>
       </c>
       <c r="D1146" s="30" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="F1146" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G1146">
         <v>10</v>
       </c>
       <c r="H1146" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1146">
-        <v>50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1147" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1147">
-        <v>8920022</v>
+        <v>6920022</v>
       </c>
       <c r="B1147" s="25">
         <v>1</v>
@@ -37025,10 +37033,10 @@
         <v>0</v>
       </c>
       <c r="D1147" s="30" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="F1147" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G1147">
         <v>10</v>
@@ -37042,7 +37050,7 @@
     </row>
     <row r="1148" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1148">
-        <v>9920022</v>
+        <v>7920022</v>
       </c>
       <c r="B1148" s="25">
         <v>1</v>
@@ -37051,10 +37059,10 @@
         <v>0</v>
       </c>
       <c r="D1148" s="30" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="F1148" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G1148">
         <v>10</v>
@@ -37068,7 +37076,7 @@
     </row>
     <row r="1149" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1149">
-        <v>920023</v>
+        <v>8920022</v>
       </c>
       <c r="B1149" s="25">
         <v>1</v>
@@ -37077,10 +37085,10 @@
         <v>0</v>
       </c>
       <c r="D1149" s="30" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="F1149" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="G1149">
         <v>10</v>
@@ -37094,7 +37102,7 @@
     </row>
     <row r="1150" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1150">
-        <v>1920023</v>
+        <v>9920022</v>
       </c>
       <c r="B1150" s="25">
         <v>1</v>
@@ -37103,24 +37111,24 @@
         <v>0</v>
       </c>
       <c r="D1150" s="30" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="F1150" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="G1150">
         <v>10</v>
       </c>
       <c r="H1150" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1150">
-        <v>0</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="1151" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1151">
-        <v>2920023</v>
+        <v>920023</v>
       </c>
       <c r="B1151" s="25">
         <v>1</v>
@@ -37129,10 +37137,10 @@
         <v>0</v>
       </c>
       <c r="D1151" s="30" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="F1151" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G1151">
         <v>10</v>
@@ -37146,7 +37154,7 @@
     </row>
     <row r="1152" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1152">
-        <v>3920023</v>
+        <v>1920023</v>
       </c>
       <c r="B1152" s="25">
         <v>1</v>
@@ -37155,10 +37163,10 @@
         <v>0</v>
       </c>
       <c r="D1152" s="30" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="F1152" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G1152">
         <v>10</v>
@@ -37172,7 +37180,7 @@
     </row>
     <row r="1153" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1153">
-        <v>4920023</v>
+        <v>2920023</v>
       </c>
       <c r="B1153" s="25">
         <v>1</v>
@@ -37181,10 +37189,10 @@
         <v>0</v>
       </c>
       <c r="D1153" s="30" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="F1153" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G1153">
         <v>10</v>
@@ -37193,12 +37201,12 @@
         <v>1</v>
       </c>
       <c r="I1153">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1154" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1154">
-        <v>5920023</v>
+        <v>3920023</v>
       </c>
       <c r="B1154" s="25">
         <v>1</v>
@@ -37207,10 +37215,10 @@
         <v>0</v>
       </c>
       <c r="D1154" s="30" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="F1154" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="G1154">
         <v>10</v>
@@ -37224,7 +37232,7 @@
     </row>
     <row r="1155" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1155">
-        <v>6920023</v>
+        <v>4920023</v>
       </c>
       <c r="B1155" s="25">
         <v>1</v>
@@ -37233,10 +37241,10 @@
         <v>0</v>
       </c>
       <c r="D1155" s="30" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="F1155" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="G1155">
         <v>10</v>
@@ -37245,12 +37253,12 @@
         <v>1</v>
       </c>
       <c r="I1155">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1156" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1156">
-        <v>7920023</v>
+        <v>5920023</v>
       </c>
       <c r="B1156" s="25">
         <v>1</v>
@@ -37259,24 +37267,24 @@
         <v>0</v>
       </c>
       <c r="D1156" s="30" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="F1156" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="G1156">
         <v>10</v>
       </c>
       <c r="H1156" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1156">
-        <v>45000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1157" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1157">
-        <v>8920023</v>
+        <v>6920023</v>
       </c>
       <c r="B1157" s="25">
         <v>1</v>
@@ -37285,10 +37293,10 @@
         <v>0</v>
       </c>
       <c r="D1157" s="30" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F1157" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G1157">
         <v>10</v>
@@ -37302,7 +37310,7 @@
     </row>
     <row r="1158" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1158">
-        <v>9920023</v>
+        <v>7920023</v>
       </c>
       <c r="B1158" s="25">
         <v>1</v>
@@ -37311,10 +37319,10 @@
         <v>0</v>
       </c>
       <c r="D1158" s="30" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="F1158" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G1158">
         <v>10</v>
@@ -37328,7 +37336,7 @@
     </row>
     <row r="1159" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1159">
-        <v>920031</v>
+        <v>8920023</v>
       </c>
       <c r="B1159" s="25">
         <v>1</v>
@@ -37337,10 +37345,10 @@
         <v>0</v>
       </c>
       <c r="D1159" s="30" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="F1159" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="G1159">
         <v>10</v>
@@ -37354,7 +37362,7 @@
     </row>
     <row r="1160" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1160">
-        <v>1920031</v>
+        <v>9920023</v>
       </c>
       <c r="B1160" s="25">
         <v>1</v>
@@ -37363,24 +37371,24 @@
         <v>0</v>
       </c>
       <c r="D1160" s="30" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="F1160" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G1160">
         <v>10</v>
       </c>
       <c r="H1160" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1160">
-        <v>6000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="1161" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1161">
-        <v>2920031</v>
+        <v>920031</v>
       </c>
       <c r="B1161" s="25">
         <v>1</v>
@@ -37389,10 +37397,10 @@
         <v>0</v>
       </c>
       <c r="D1161" s="30" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="F1161" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G1161">
         <v>10</v>
@@ -37406,7 +37414,7 @@
     </row>
     <row r="1162" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1162">
-        <v>3920031</v>
+        <v>1920031</v>
       </c>
       <c r="B1162" s="25">
         <v>1</v>
@@ -37415,10 +37423,10 @@
         <v>0</v>
       </c>
       <c r="D1162" s="30" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="F1162" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="G1162">
         <v>10</v>
@@ -37427,12 +37435,12 @@
         <v>1</v>
       </c>
       <c r="I1162">
-        <v>10000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1163" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1163">
-        <v>4920031</v>
+        <v>2920031</v>
       </c>
       <c r="B1163" s="25">
         <v>1</v>
@@ -37441,10 +37449,10 @@
         <v>0</v>
       </c>
       <c r="D1163" s="30" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="F1163" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G1163">
         <v>10</v>
@@ -37453,12 +37461,12 @@
         <v>1</v>
       </c>
       <c r="I1163">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1164" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1164">
-        <v>5920031</v>
+        <v>3920031</v>
       </c>
       <c r="B1164" s="25">
         <v>1</v>
@@ -37467,10 +37475,10 @@
         <v>0</v>
       </c>
       <c r="D1164" s="30" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="F1164" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G1164">
         <v>10</v>
@@ -37479,12 +37487,12 @@
         <v>1</v>
       </c>
       <c r="I1164">
-        <v>4</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1165" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1165">
-        <v>6920031</v>
+        <v>4920031</v>
       </c>
       <c r="B1165" s="25">
         <v>1</v>
@@ -37493,10 +37501,10 @@
         <v>0</v>
       </c>
       <c r="D1165" s="30" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="F1165" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G1165">
         <v>10</v>
@@ -37505,12 +37513,12 @@
         <v>1</v>
       </c>
       <c r="I1165">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1166" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1166">
-        <v>7920031</v>
+        <v>5920031</v>
       </c>
       <c r="B1166" s="25">
         <v>1</v>
@@ -37519,24 +37527,24 @@
         <v>0</v>
       </c>
       <c r="D1166" s="30" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="F1166" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="G1166">
         <v>10</v>
       </c>
       <c r="H1166" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1166">
-        <v>20000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1167" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1167">
-        <v>8920031</v>
+        <v>6920031</v>
       </c>
       <c r="B1167" s="25">
         <v>1</v>
@@ -37545,10 +37553,10 @@
         <v>0</v>
       </c>
       <c r="D1167" s="30" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="F1167" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="G1167">
         <v>10</v>
@@ -37562,7 +37570,7 @@
     </row>
     <row r="1168" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1168">
-        <v>9920031</v>
+        <v>7920031</v>
       </c>
       <c r="B1168" s="25">
         <v>1</v>
@@ -37571,10 +37579,10 @@
         <v>0</v>
       </c>
       <c r="D1168" s="30" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="F1168" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G1168">
         <v>10</v>
@@ -37588,7 +37596,7 @@
     </row>
     <row r="1169" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1169">
-        <v>920041</v>
+        <v>8920031</v>
       </c>
       <c r="B1169" s="25">
         <v>1</v>
@@ -37597,10 +37605,10 @@
         <v>0</v>
       </c>
       <c r="D1169" s="30" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F1169" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G1169">
         <v>10</v>
@@ -37614,7 +37622,7 @@
     </row>
     <row r="1170" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1170">
-        <v>1920041</v>
+        <v>9920031</v>
       </c>
       <c r="B1170" s="25">
         <v>1</v>
@@ -37623,24 +37631,24 @@
         <v>0</v>
       </c>
       <c r="D1170" s="30" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F1170" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G1170">
         <v>10</v>
       </c>
       <c r="H1170" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1170">
-        <v>8000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1171" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1171">
-        <v>2920041</v>
+        <v>920041</v>
       </c>
       <c r="B1171" s="25">
         <v>1</v>
@@ -37649,10 +37657,10 @@
         <v>0</v>
       </c>
       <c r="D1171" s="30" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="F1171" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="G1171">
         <v>10</v>
@@ -37666,7 +37674,7 @@
     </row>
     <row r="1172" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1172">
-        <v>3920041</v>
+        <v>1920041</v>
       </c>
       <c r="B1172" s="25">
         <v>1</v>
@@ -37675,10 +37683,10 @@
         <v>0</v>
       </c>
       <c r="D1172" s="30" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F1172" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G1172">
         <v>10</v>
@@ -37687,12 +37695,12 @@
         <v>1</v>
       </c>
       <c r="I1172">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1173" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1173">
-        <v>4920041</v>
+        <v>2920041</v>
       </c>
       <c r="B1173" s="25">
         <v>1</v>
@@ -37701,10 +37709,10 @@
         <v>0</v>
       </c>
       <c r="D1173" s="30" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="F1173" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G1173">
         <v>10</v>
@@ -37718,7 +37726,7 @@
     </row>
     <row r="1174" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1174">
-        <v>5920041</v>
+        <v>3920041</v>
       </c>
       <c r="B1174" s="25">
         <v>1</v>
@@ -37727,10 +37735,10 @@
         <v>0</v>
       </c>
       <c r="D1174" s="30" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="F1174" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G1174">
         <v>10</v>
@@ -37739,12 +37747,12 @@
         <v>1</v>
       </c>
       <c r="I1174">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1175" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1175">
-        <v>6920041</v>
+        <v>4920041</v>
       </c>
       <c r="B1175" s="25">
         <v>1</v>
@@ -37753,10 +37761,10 @@
         <v>0</v>
       </c>
       <c r="D1175" s="30" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F1175" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="G1175">
         <v>10</v>
@@ -37770,7 +37778,7 @@
     </row>
     <row r="1176" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1176">
-        <v>7920041</v>
+        <v>5920041</v>
       </c>
       <c r="B1176" s="25">
         <v>1</v>
@@ -37779,16 +37787,16 @@
         <v>0</v>
       </c>
       <c r="D1176" s="30" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="F1176" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G1176">
         <v>10</v>
       </c>
       <c r="H1176" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1176">
         <v>0</v>
@@ -37796,7 +37804,7 @@
     </row>
     <row r="1177" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1177">
-        <v>8920041</v>
+        <v>6920041</v>
       </c>
       <c r="B1177" s="25">
         <v>1</v>
@@ -37805,10 +37813,10 @@
         <v>0</v>
       </c>
       <c r="D1177" s="30" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F1177" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G1177">
         <v>10</v>
@@ -37822,7 +37830,7 @@
     </row>
     <row r="1178" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1178">
-        <v>9920041</v>
+        <v>7920041</v>
       </c>
       <c r="B1178" s="25">
         <v>1</v>
@@ -37831,10 +37839,10 @@
         <v>0</v>
       </c>
       <c r="D1178" s="30" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F1178" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G1178">
         <v>10</v>
@@ -37843,6 +37851,58 @@
         <v>2</v>
       </c>
       <c r="I1178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1179">
+        <v>8920041</v>
+      </c>
+      <c r="B1179" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1179">
+        <v>0</v>
+      </c>
+      <c r="D1179" s="30" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F1179" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G1179">
+        <v>10</v>
+      </c>
+      <c r="H1179" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1180">
+        <v>9920041</v>
+      </c>
+      <c r="B1180" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1180">
+        <v>0</v>
+      </c>
+      <c r="D1180" s="30" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F1180" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G1180">
+        <v>10</v>
+      </c>
+      <c r="H1180" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1180">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E1715F-DBE5-4179-AF4D-7AB8507CBDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3588C34D-CC33-4A6B-AF27-9991B9D2F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3472" uniqueCount="1060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="1085">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3659,7 +3659,85 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>炎域_技能伤害\效果生效间隔</t>
+    <t>正式技能</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>电环_获得</t>
+  </si>
+  <si>
+    <t>电环_冷却</t>
+  </si>
+  <si>
+    <t>电环_最近释放距离</t>
+  </si>
+  <si>
+    <t>电环_最远释放距离</t>
+  </si>
+  <si>
+    <t>电环_技能效果半径</t>
+  </si>
+  <si>
+    <t>电环_目标数量</t>
+  </si>
+  <si>
+    <t>电环_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>电环_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>电环_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>电环_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>雷暴云_获得</t>
+  </si>
+  <si>
+    <t>雷暴云_冷却</t>
+  </si>
+  <si>
+    <t>雷暴云_最近释放距离</t>
+  </si>
+  <si>
+    <t>雷暴云_最远释放距离</t>
+  </si>
+  <si>
+    <t>雷暴云_技能效果半径</t>
+  </si>
+  <si>
+    <t>雷暴云_目标数量</t>
+  </si>
+  <si>
+    <t>雷暴云_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>雷暴云_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>雷暴云_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>雷暴云_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>炎域_技能伤害或效果生效间隔</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷暴云_技能持续时间</t>
+  </si>
+  <si>
+    <t>雷暴云_技能伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>闪电链_每次造成伤害后的伤害调整系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>连环闪电-逻辑id</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3667,7 +3745,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3814,6 +3892,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFEE0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -3959,7 +4052,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4035,6 +4128,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="差 2" xfId="5" xr:uid="{2DD3A33C-F8AA-458E-BFA0-D16932B5BC9D}"/>
@@ -4345,7 +4442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1180"/>
+  <dimension ref="A1:I1204"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -4353,7 +4450,7 @@
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="21.875" customWidth="1"/>
     <col min="5" max="5" width="32.25" customWidth="1"/>
-    <col min="6" max="6" width="11.125" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -35611,10 +35708,10 @@
         <v>0</v>
       </c>
       <c r="D1090" s="30" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="F1090" s="30" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="G1090">
         <v>10</v>
@@ -37399,6 +37496,9 @@
       <c r="D1161" s="30" t="s">
         <v>1038</v>
       </c>
+      <c r="E1161" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1161" t="s">
         <v>1038</v>
       </c>
@@ -37425,6 +37525,9 @@
       <c r="D1162" s="30" t="s">
         <v>1039</v>
       </c>
+      <c r="E1162" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1162" t="s">
         <v>1039</v>
       </c>
@@ -37451,6 +37554,9 @@
       <c r="D1163" s="30" t="s">
         <v>1040</v>
       </c>
+      <c r="E1163" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1163" t="s">
         <v>1040</v>
       </c>
@@ -37477,6 +37583,9 @@
       <c r="D1164" s="30" t="s">
         <v>1041</v>
       </c>
+      <c r="E1164" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1164" t="s">
         <v>1041</v>
       </c>
@@ -37503,6 +37612,9 @@
       <c r="D1165" s="30" t="s">
         <v>1042</v>
       </c>
+      <c r="E1165" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1165" t="s">
         <v>1042</v>
       </c>
@@ -37529,6 +37641,9 @@
       <c r="D1166" s="30" t="s">
         <v>1043</v>
       </c>
+      <c r="E1166" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1166" t="s">
         <v>1043</v>
       </c>
@@ -37555,6 +37670,9 @@
       <c r="D1167" s="30" t="s">
         <v>1044</v>
       </c>
+      <c r="E1167" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1167" t="s">
         <v>1044</v>
       </c>
@@ -37581,6 +37699,9 @@
       <c r="D1168" s="30" t="s">
         <v>1045</v>
       </c>
+      <c r="E1168" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1168" t="s">
         <v>1045</v>
       </c>
@@ -37607,6 +37728,9 @@
       <c r="D1169" s="30" t="s">
         <v>1046</v>
       </c>
+      <c r="E1169" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1169" t="s">
         <v>1046</v>
       </c>
@@ -37633,6 +37757,9 @@
       <c r="D1170" s="30" t="s">
         <v>1047</v>
       </c>
+      <c r="E1170" s="31" t="s">
+        <v>1059</v>
+      </c>
       <c r="F1170" t="s">
         <v>1047</v>
       </c>
@@ -37648,7 +37775,7 @@
     </row>
     <row r="1171" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1171">
-        <v>920041</v>
+        <v>12920031</v>
       </c>
       <c r="B1171" s="25">
         <v>1</v>
@@ -37657,16 +37784,19 @@
         <v>0</v>
       </c>
       <c r="D1171" s="30" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F1171" t="s">
-        <v>1048</v>
+        <v>1083</v>
+      </c>
+      <c r="E1171" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1171" s="30" t="s">
+        <v>1083</v>
       </c>
       <c r="G1171">
         <v>10</v>
       </c>
       <c r="H1171" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1171">
         <v>0</v>
@@ -37674,7 +37804,7 @@
     </row>
     <row r="1172" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1172">
-        <v>1920041</v>
+        <v>920032</v>
       </c>
       <c r="B1172" s="25">
         <v>1</v>
@@ -37683,10 +37813,13 @@
         <v>0</v>
       </c>
       <c r="D1172" s="30" t="s">
-        <v>1049</v>
+        <v>1060</v>
+      </c>
+      <c r="E1172" s="31" t="s">
+        <v>1059</v>
       </c>
       <c r="F1172" t="s">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="G1172">
         <v>10</v>
@@ -37695,12 +37828,12 @@
         <v>1</v>
       </c>
       <c r="I1172">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1173" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1173">
-        <v>2920041</v>
+        <v>1920032</v>
       </c>
       <c r="B1173" s="25">
         <v>1</v>
@@ -37709,10 +37842,13 @@
         <v>0</v>
       </c>
       <c r="D1173" s="30" t="s">
-        <v>1050</v>
+        <v>1061</v>
+      </c>
+      <c r="E1173" s="31" t="s">
+        <v>1059</v>
       </c>
       <c r="F1173" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="G1173">
         <v>10</v>
@@ -37721,12 +37857,12 @@
         <v>1</v>
       </c>
       <c r="I1173">
-        <v>0</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="1174" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1174">
-        <v>3920041</v>
+        <v>2920032</v>
       </c>
       <c r="B1174" s="25">
         <v>1</v>
@@ -37735,10 +37871,13 @@
         <v>0</v>
       </c>
       <c r="D1174" s="30" t="s">
-        <v>1051</v>
+        <v>1062</v>
+      </c>
+      <c r="E1174" s="31" t="s">
+        <v>1059</v>
       </c>
       <c r="F1174" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="G1174">
         <v>10</v>
@@ -37747,12 +37886,12 @@
         <v>1</v>
       </c>
       <c r="I1174">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1175" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1175">
-        <v>4920041</v>
+        <v>3920032</v>
       </c>
       <c r="B1175" s="25">
         <v>1</v>
@@ -37761,10 +37900,13 @@
         <v>0</v>
       </c>
       <c r="D1175" s="30" t="s">
-        <v>1052</v>
+        <v>1063</v>
+      </c>
+      <c r="E1175" s="31" t="s">
+        <v>1059</v>
       </c>
       <c r="F1175" t="s">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="G1175">
         <v>10</v>
@@ -37773,12 +37915,12 @@
         <v>1</v>
       </c>
       <c r="I1175">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1176" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1176">
-        <v>5920041</v>
+        <v>4920032</v>
       </c>
       <c r="B1176" s="25">
         <v>1</v>
@@ -37787,10 +37929,13 @@
         <v>0</v>
       </c>
       <c r="D1176" s="30" t="s">
-        <v>1053</v>
+        <v>1064</v>
+      </c>
+      <c r="E1176" s="31" t="s">
+        <v>1059</v>
       </c>
       <c r="F1176" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="G1176">
         <v>10</v>
@@ -37799,12 +37944,12 @@
         <v>1</v>
       </c>
       <c r="I1176">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1177" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1177">
-        <v>6920041</v>
+        <v>5920032</v>
       </c>
       <c r="B1177" s="25">
         <v>1</v>
@@ -37813,10 +37958,13 @@
         <v>0</v>
       </c>
       <c r="D1177" s="30" t="s">
-        <v>1054</v>
+        <v>1065</v>
+      </c>
+      <c r="E1177" s="31" t="s">
+        <v>1059</v>
       </c>
       <c r="F1177" t="s">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="G1177">
         <v>10</v>
@@ -37830,7 +37978,7 @@
     </row>
     <row r="1178" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1178">
-        <v>7920041</v>
+        <v>6920032</v>
       </c>
       <c r="B1178" s="25">
         <v>1</v>
@@ -37839,16 +37987,19 @@
         <v>0</v>
       </c>
       <c r="D1178" s="30" t="s">
-        <v>1055</v>
+        <v>1066</v>
+      </c>
+      <c r="E1178" s="31" t="s">
+        <v>1059</v>
       </c>
       <c r="F1178" t="s">
-        <v>1055</v>
+        <v>1066</v>
       </c>
       <c r="G1178">
         <v>10</v>
       </c>
       <c r="H1178" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1178">
         <v>0</v>
@@ -37856,7 +38007,7 @@
     </row>
     <row r="1179" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1179">
-        <v>8920041</v>
+        <v>7920032</v>
       </c>
       <c r="B1179" s="25">
         <v>1</v>
@@ -37865,44 +38016,710 @@
         <v>0</v>
       </c>
       <c r="D1179" s="30" t="s">
-        <v>1056</v>
+        <v>1067</v>
+      </c>
+      <c r="E1179" s="31" t="s">
+        <v>1059</v>
       </c>
       <c r="F1179" t="s">
-        <v>1056</v>
+        <v>1067</v>
       </c>
       <c r="G1179">
         <v>10</v>
       </c>
       <c r="H1179" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1179">
-        <v>0</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="1180" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1180">
+        <v>8920032</v>
+      </c>
+      <c r="B1180" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1180">
+        <v>0</v>
+      </c>
+      <c r="D1180" s="30" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E1180" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1180" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G1180">
+        <v>10</v>
+      </c>
+      <c r="H1180" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1181">
+        <v>9920032</v>
+      </c>
+      <c r="B1181" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1181">
+        <v>0</v>
+      </c>
+      <c r="D1181" s="30" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E1181" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1181" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G1181">
+        <v>10</v>
+      </c>
+      <c r="H1181" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1181">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1182">
+        <v>920033</v>
+      </c>
+      <c r="B1182" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1182">
+        <v>0</v>
+      </c>
+      <c r="D1182" s="30" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E1182" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1182" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G1182">
+        <v>10</v>
+      </c>
+      <c r="H1182" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1183">
+        <v>1920033</v>
+      </c>
+      <c r="B1183" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1183">
+        <v>0</v>
+      </c>
+      <c r="D1183" s="30" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E1183" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1183" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G1183">
+        <v>10</v>
+      </c>
+      <c r="H1183" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1183">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1184">
+        <v>2920033</v>
+      </c>
+      <c r="B1184" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1184">
+        <v>0</v>
+      </c>
+      <c r="D1184" s="30" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E1184" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1184" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G1184">
+        <v>10</v>
+      </c>
+      <c r="H1184" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1185">
+        <v>3920033</v>
+      </c>
+      <c r="B1185" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1185">
+        <v>0</v>
+      </c>
+      <c r="D1185" s="30" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E1185" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1185" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G1185">
+        <v>10</v>
+      </c>
+      <c r="H1185" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1185">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1186">
+        <v>4920033</v>
+      </c>
+      <c r="B1186" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1186">
+        <v>0</v>
+      </c>
+      <c r="D1186" s="30" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E1186" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1186" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G1186">
+        <v>10</v>
+      </c>
+      <c r="H1186" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1186">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1187">
+        <v>5920033</v>
+      </c>
+      <c r="B1187" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1187">
+        <v>0</v>
+      </c>
+      <c r="D1187" s="30" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1187" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1187" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G1187">
+        <v>10</v>
+      </c>
+      <c r="H1187" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1188">
+        <v>6920033</v>
+      </c>
+      <c r="B1188" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1188">
+        <v>0</v>
+      </c>
+      <c r="D1188" s="30" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E1188" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1188" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G1188">
+        <v>10</v>
+      </c>
+      <c r="H1188" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1189">
+        <v>7920033</v>
+      </c>
+      <c r="B1189" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1189">
+        <v>0</v>
+      </c>
+      <c r="D1189" s="30" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E1189" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1189" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G1189">
+        <v>10</v>
+      </c>
+      <c r="H1189" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1189">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1190">
+        <v>8920033</v>
+      </c>
+      <c r="B1190" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1190">
+        <v>0</v>
+      </c>
+      <c r="D1190" s="30" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E1190" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1190" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G1190">
+        <v>10</v>
+      </c>
+      <c r="H1190" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1191">
+        <v>9920033</v>
+      </c>
+      <c r="B1191" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1191">
+        <v>0</v>
+      </c>
+      <c r="D1191" s="30" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E1191" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1191" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G1191">
+        <v>10</v>
+      </c>
+      <c r="H1191" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1191">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1192">
+        <v>10920033</v>
+      </c>
+      <c r="B1192" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1192">
+        <v>0</v>
+      </c>
+      <c r="D1192" s="30" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1192" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1192" s="30" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G1192">
+        <v>10</v>
+      </c>
+      <c r="H1192" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1192">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1193">
+        <v>11920033</v>
+      </c>
+      <c r="B1193" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1193">
+        <v>0</v>
+      </c>
+      <c r="D1193" s="30" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E1193" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1193" s="30" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G1193">
+        <v>10</v>
+      </c>
+      <c r="H1193" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1193">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1194" s="32">
+        <v>820034</v>
+      </c>
+      <c r="B1194" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1194">
+        <v>0</v>
+      </c>
+      <c r="D1194" s="32" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1194">
+        <v>10</v>
+      </c>
+      <c r="H1194" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1195">
+        <v>920041</v>
+      </c>
+      <c r="B1195" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1195">
+        <v>0</v>
+      </c>
+      <c r="D1195" s="30" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F1195" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G1195">
+        <v>10</v>
+      </c>
+      <c r="H1195" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1196">
+        <v>1920041</v>
+      </c>
+      <c r="B1196" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1196">
+        <v>0</v>
+      </c>
+      <c r="D1196" s="30" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F1196" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G1196">
+        <v>10</v>
+      </c>
+      <c r="H1196" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1196">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1197">
+        <v>2920041</v>
+      </c>
+      <c r="B1197" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1197">
+        <v>0</v>
+      </c>
+      <c r="D1197" s="30" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F1197" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G1197">
+        <v>10</v>
+      </c>
+      <c r="H1197" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1198">
+        <v>3920041</v>
+      </c>
+      <c r="B1198" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1198">
+        <v>0</v>
+      </c>
+      <c r="D1198" s="30" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F1198" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G1198">
+        <v>10</v>
+      </c>
+      <c r="H1198" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1198">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1199">
+        <v>4920041</v>
+      </c>
+      <c r="B1199" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1199">
+        <v>0</v>
+      </c>
+      <c r="D1199" s="30" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F1199" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G1199">
+        <v>10</v>
+      </c>
+      <c r="H1199" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1200">
+        <v>5920041</v>
+      </c>
+      <c r="B1200" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1200">
+        <v>0</v>
+      </c>
+      <c r="D1200" s="30" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F1200" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G1200">
+        <v>10</v>
+      </c>
+      <c r="H1200" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1201">
+        <v>6920041</v>
+      </c>
+      <c r="B1201" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1201">
+        <v>0</v>
+      </c>
+      <c r="D1201" s="30" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F1201" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G1201">
+        <v>10</v>
+      </c>
+      <c r="H1201" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1202">
+        <v>7920041</v>
+      </c>
+      <c r="B1202" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1202">
+        <v>0</v>
+      </c>
+      <c r="D1202" s="30" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G1202">
+        <v>10</v>
+      </c>
+      <c r="H1202" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1203">
+        <v>8920041</v>
+      </c>
+      <c r="B1203" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1203">
+        <v>0</v>
+      </c>
+      <c r="D1203" s="30" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G1203">
+        <v>10</v>
+      </c>
+      <c r="H1203" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1204">
         <v>9920041</v>
       </c>
-      <c r="B1180" s="25">
-        <v>1</v>
-      </c>
-      <c r="C1180">
-        <v>0</v>
-      </c>
-      <c r="D1180" s="30" t="s">
+      <c r="B1204" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1204">
+        <v>0</v>
+      </c>
+      <c r="D1204" s="30" t="s">
         <v>1057</v>
       </c>
-      <c r="F1180" t="s">
+      <c r="F1204" t="s">
         <v>1057</v>
       </c>
-      <c r="G1180">
-        <v>10</v>
-      </c>
-      <c r="H1180" s="28">
+      <c r="G1204">
+        <v>10</v>
+      </c>
+      <c r="H1204" s="28">
         <v>2</v>
       </c>
-      <c r="I1180">
+      <c r="I1204">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3588C34D-CC33-4A6B-AF27-9991B9D2F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCDC5EE-87FA-4567-B560-45BE5306FB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="1086">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3738,6 +3738,10 @@
   </si>
   <si>
     <t>连环闪电-逻辑id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>连环闪电_获得</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4442,7 +4446,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1204"/>
+  <dimension ref="A1:I1205"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -38441,43 +38445,46 @@
       </c>
     </row>
     <row r="1194" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1194" s="32">
+      <c r="A1194">
+        <v>920034</v>
+      </c>
+      <c r="B1194" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1194">
+        <v>0</v>
+      </c>
+      <c r="D1194" s="30" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E1194" s="31" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F1194" s="30" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G1194">
+        <v>10</v>
+      </c>
+      <c r="H1194" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1195" s="32">
         <v>820034</v>
       </c>
-      <c r="B1194" s="25">
-        <v>1</v>
-      </c>
-      <c r="C1194">
-        <v>0</v>
-      </c>
-      <c r="D1194" s="32" t="s">
+      <c r="B1195" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1195">
+        <v>0</v>
+      </c>
+      <c r="D1195" s="32" t="s">
         <v>1084</v>
-      </c>
-      <c r="G1194">
-        <v>10</v>
-      </c>
-      <c r="H1194" s="28">
-        <v>1</v>
-      </c>
-      <c r="I1194">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1195" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1195">
-        <v>920041</v>
-      </c>
-      <c r="B1195" s="25">
-        <v>1</v>
-      </c>
-      <c r="C1195">
-        <v>0</v>
-      </c>
-      <c r="D1195" s="30" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F1195" t="s">
-        <v>1048</v>
       </c>
       <c r="G1195">
         <v>10</v>
@@ -38491,7 +38498,7 @@
     </row>
     <row r="1196" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1196">
-        <v>1920041</v>
+        <v>920041</v>
       </c>
       <c r="B1196" s="25">
         <v>1</v>
@@ -38500,10 +38507,10 @@
         <v>0</v>
       </c>
       <c r="D1196" s="30" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F1196" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G1196">
         <v>10</v>
@@ -38512,12 +38519,12 @@
         <v>1</v>
       </c>
       <c r="I1196">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1197" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1197">
-        <v>2920041</v>
+        <v>1920041</v>
       </c>
       <c r="B1197" s="25">
         <v>1</v>
@@ -38526,10 +38533,10 @@
         <v>0</v>
       </c>
       <c r="D1197" s="30" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F1197" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G1197">
         <v>10</v>
@@ -38538,12 +38545,12 @@
         <v>1</v>
       </c>
       <c r="I1197">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1198" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1198">
-        <v>3920041</v>
+        <v>2920041</v>
       </c>
       <c r="B1198" s="25">
         <v>1</v>
@@ -38552,10 +38559,10 @@
         <v>0</v>
       </c>
       <c r="D1198" s="30" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F1198" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G1198">
         <v>10</v>
@@ -38564,12 +38571,12 @@
         <v>1</v>
       </c>
       <c r="I1198">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1199" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1199">
-        <v>4920041</v>
+        <v>3920041</v>
       </c>
       <c r="B1199" s="25">
         <v>1</v>
@@ -38578,10 +38585,10 @@
         <v>0</v>
       </c>
       <c r="D1199" s="30" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F1199" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G1199">
         <v>10</v>
@@ -38590,12 +38597,12 @@
         <v>1</v>
       </c>
       <c r="I1199">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1200" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1200">
-        <v>5920041</v>
+        <v>4920041</v>
       </c>
       <c r="B1200" s="25">
         <v>1</v>
@@ -38604,10 +38611,10 @@
         <v>0</v>
       </c>
       <c r="D1200" s="30" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F1200" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G1200">
         <v>10</v>
@@ -38621,7 +38628,7 @@
     </row>
     <row r="1201" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1201">
-        <v>6920041</v>
+        <v>5920041</v>
       </c>
       <c r="B1201" s="25">
         <v>1</v>
@@ -38630,10 +38637,10 @@
         <v>0</v>
       </c>
       <c r="D1201" s="30" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F1201" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G1201">
         <v>10</v>
@@ -38647,7 +38654,7 @@
     </row>
     <row r="1202" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1202">
-        <v>7920041</v>
+        <v>6920041</v>
       </c>
       <c r="B1202" s="25">
         <v>1</v>
@@ -38656,16 +38663,16 @@
         <v>0</v>
       </c>
       <c r="D1202" s="30" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F1202" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G1202">
         <v>10</v>
       </c>
       <c r="H1202" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1202">
         <v>0</v>
@@ -38673,7 +38680,7 @@
     </row>
     <row r="1203" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1203">
-        <v>8920041</v>
+        <v>7920041</v>
       </c>
       <c r="B1203" s="25">
         <v>1</v>
@@ -38682,16 +38689,16 @@
         <v>0</v>
       </c>
       <c r="D1203" s="30" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F1203" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G1203">
         <v>10</v>
       </c>
       <c r="H1203" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1203">
         <v>0</v>
@@ -38699,27 +38706,53 @@
     </row>
     <row r="1204" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1204">
+        <v>8920041</v>
+      </c>
+      <c r="B1204" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1204">
+        <v>0</v>
+      </c>
+      <c r="D1204" s="30" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G1204">
+        <v>10</v>
+      </c>
+      <c r="H1204" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1205">
         <v>9920041</v>
       </c>
-      <c r="B1204" s="25">
-        <v>1</v>
-      </c>
-      <c r="C1204">
-        <v>0</v>
-      </c>
-      <c r="D1204" s="30" t="s">
+      <c r="B1205" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1205">
+        <v>0</v>
+      </c>
+      <c r="D1205" s="30" t="s">
         <v>1057</v>
       </c>
-      <c r="F1204" t="s">
+      <c r="F1205" t="s">
         <v>1057</v>
       </c>
-      <c r="G1204">
-        <v>10</v>
-      </c>
-      <c r="H1204" s="28">
+      <c r="G1205">
+        <v>10</v>
+      </c>
+      <c r="H1205" s="28">
         <v>2</v>
       </c>
-      <c r="I1204">
+      <c r="I1205">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A73D85-4B4C-4DE2-B7B4-D5AF5778278B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1DE945-C09B-4A23-9B89-468D362033B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="maze_attribute_formula_v8" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1223</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3596" uniqueCount="1105">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3799,6 +3799,14 @@
   </si>
   <si>
     <t>电环_技能等级</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>天罚_获得</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>超强电刃_弹道数量</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4503,7 +4511,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1222"/>
+  <dimension ref="A1:I1223"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -38960,71 +38968,71 @@
     </row>
     <row r="1211" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1211">
+        <v>14920053</v>
+      </c>
+      <c r="B1211" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1211">
+        <v>0</v>
+      </c>
+      <c r="D1211" s="30" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F1211" s="30" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G1211">
+        <v>10</v>
+      </c>
+      <c r="H1211" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1212">
         <v>920054</v>
       </c>
-      <c r="B1211" s="25">
-        <v>1</v>
-      </c>
-      <c r="C1211">
-        <v>0</v>
-      </c>
-      <c r="D1211" s="30" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E1211" s="31" t="s">
+      <c r="B1212" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1212">
+        <v>0</v>
+      </c>
+      <c r="D1212" s="30" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E1212" s="31" t="s">
         <v>1057</v>
       </c>
-      <c r="F1211" s="30" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G1211">
-        <v>10</v>
-      </c>
-      <c r="H1211" s="28">
-        <v>1</v>
-      </c>
-      <c r="I1211">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1212" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1212" s="32">
+      <c r="F1212" s="30" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G1212">
+        <v>10</v>
+      </c>
+      <c r="H1212" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1213" s="32">
         <v>820054</v>
       </c>
-      <c r="B1212" s="25">
-        <v>1</v>
-      </c>
-      <c r="C1212">
-        <v>0</v>
-      </c>
-      <c r="D1212" s="32" t="s">
+      <c r="B1213" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1213">
+        <v>0</v>
+      </c>
+      <c r="D1213" s="32" t="s">
         <v>1100</v>
-      </c>
-      <c r="G1212">
-        <v>10</v>
-      </c>
-      <c r="H1212" s="28">
-        <v>1</v>
-      </c>
-      <c r="I1212">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1213" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1213">
-        <v>920041</v>
-      </c>
-      <c r="B1213" s="25">
-        <v>1</v>
-      </c>
-      <c r="C1213">
-        <v>0</v>
-      </c>
-      <c r="D1213" s="30" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F1213" t="s">
-        <v>1046</v>
       </c>
       <c r="G1213">
         <v>10</v>
@@ -39038,7 +39046,7 @@
     </row>
     <row r="1214" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1214">
-        <v>1920041</v>
+        <v>920041</v>
       </c>
       <c r="B1214" s="25">
         <v>1</v>
@@ -39047,10 +39055,10 @@
         <v>0</v>
       </c>
       <c r="D1214" s="30" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F1214" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G1214">
         <v>10</v>
@@ -39059,12 +39067,12 @@
         <v>1</v>
       </c>
       <c r="I1214">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1215" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1215">
-        <v>2920041</v>
+        <v>1920041</v>
       </c>
       <c r="B1215" s="25">
         <v>1</v>
@@ -39073,10 +39081,10 @@
         <v>0</v>
       </c>
       <c r="D1215" s="30" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F1215" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="G1215">
         <v>10</v>
@@ -39085,12 +39093,12 @@
         <v>1</v>
       </c>
       <c r="I1215">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1216" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1216">
-        <v>3920041</v>
+        <v>2920041</v>
       </c>
       <c r="B1216" s="25">
         <v>1</v>
@@ -39099,10 +39107,10 @@
         <v>0</v>
       </c>
       <c r="D1216" s="30" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F1216" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G1216">
         <v>10</v>
@@ -39111,12 +39119,12 @@
         <v>1</v>
       </c>
       <c r="I1216">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1217" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1217">
-        <v>4920041</v>
+        <v>3920041</v>
       </c>
       <c r="B1217" s="25">
         <v>1</v>
@@ -39125,10 +39133,10 @@
         <v>0</v>
       </c>
       <c r="D1217" s="30" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F1217" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G1217">
         <v>10</v>
@@ -39137,12 +39145,12 @@
         <v>1</v>
       </c>
       <c r="I1217">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1218" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1218">
-        <v>5920041</v>
+        <v>4920041</v>
       </c>
       <c r="B1218" s="25">
         <v>1</v>
@@ -39151,10 +39159,10 @@
         <v>0</v>
       </c>
       <c r="D1218" s="30" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F1218" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G1218">
         <v>10</v>
@@ -39168,7 +39176,7 @@
     </row>
     <row r="1219" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1219">
-        <v>6920041</v>
+        <v>5920041</v>
       </c>
       <c r="B1219" s="25">
         <v>1</v>
@@ -39177,10 +39185,10 @@
         <v>0</v>
       </c>
       <c r="D1219" s="30" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F1219" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G1219">
         <v>10</v>
@@ -39194,7 +39202,7 @@
     </row>
     <row r="1220" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1220">
-        <v>7920041</v>
+        <v>6920041</v>
       </c>
       <c r="B1220" s="25">
         <v>1</v>
@@ -39203,16 +39211,16 @@
         <v>0</v>
       </c>
       <c r="D1220" s="30" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F1220" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G1220">
         <v>10</v>
       </c>
       <c r="H1220" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1220">
         <v>0</v>
@@ -39220,7 +39228,7 @@
     </row>
     <row r="1221" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1221">
-        <v>8920041</v>
+        <v>7920041</v>
       </c>
       <c r="B1221" s="25">
         <v>1</v>
@@ -39229,16 +39237,16 @@
         <v>0</v>
       </c>
       <c r="D1221" s="30" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F1221" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G1221">
         <v>10</v>
       </c>
       <c r="H1221" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1221">
         <v>0</v>
@@ -39246,27 +39254,53 @@
     </row>
     <row r="1222" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1222">
+        <v>8920041</v>
+      </c>
+      <c r="B1222" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1222">
+        <v>0</v>
+      </c>
+      <c r="D1222" s="30" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F1222" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G1222">
+        <v>10</v>
+      </c>
+      <c r="H1222" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1223">
         <v>9920041</v>
       </c>
-      <c r="B1222" s="25">
-        <v>1</v>
-      </c>
-      <c r="C1222">
-        <v>0</v>
-      </c>
-      <c r="D1222" s="30" t="s">
+      <c r="B1223" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1223">
+        <v>0</v>
+      </c>
+      <c r="D1223" s="30" t="s">
         <v>1055</v>
       </c>
-      <c r="F1222" t="s">
+      <c r="F1223" t="s">
         <v>1055</v>
       </c>
-      <c r="G1222">
-        <v>10</v>
-      </c>
-      <c r="H1222" s="28">
+      <c r="G1223">
+        <v>10</v>
+      </c>
+      <c r="H1223" s="28">
         <v>2</v>
       </c>
-      <c r="I1222">
+      <c r="I1223">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1DE945-C09B-4A23-9B89-468D362033B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A3209A-60F7-4292-822C-579A9E11BF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="maze_attribute_formula_v8" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1222</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3596" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3625" uniqueCount="1120">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3757,10 +3757,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>电刃_获得</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>超强电刃_获得</t>
   </si>
   <si>
@@ -3789,9 +3785,6 @@
   </si>
   <si>
     <t>超强电刃_非主目标直接伤害系数</t>
-  </si>
-  <si>
-    <t>超强电刃-逻辑id</t>
   </si>
   <si>
     <t>闪电链_技能等级</t>
@@ -3808,6 +3801,59 @@
   <si>
     <t>超强电刃_弹道数量</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>天罚-逻辑id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>电波_获得</t>
+  </si>
+  <si>
+    <t>电波_冷却</t>
+  </si>
+  <si>
+    <t>电波_最近释放距离</t>
+  </si>
+  <si>
+    <t>电波_最远释放距离</t>
+  </si>
+  <si>
+    <t>电波_技能效果半径</t>
+  </si>
+  <si>
+    <t>电波_目标数量</t>
+  </si>
+  <si>
+    <t>电波_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>电波_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>电波_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>电波_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>电波_弹道数量</t>
+  </si>
+  <si>
+    <t>雷神降世_获得</t>
+  </si>
+  <si>
+    <t>雷神附体-逻辑id</t>
+  </si>
+  <si>
+    <t>雷神附体-逻辑id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷神附体_获得</t>
+  </si>
+  <si>
+    <t>雷神附体-参数6-触发概率</t>
   </si>
 </sst>
 </file>
@@ -4511,7 +4557,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1223"/>
+  <dimension ref="A1:I1236"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -37795,13 +37841,13 @@
         <v>0</v>
       </c>
       <c r="D1169" s="28" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="E1169" s="31" t="s">
         <v>1057</v>
       </c>
       <c r="F1169" s="28" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G1169">
         <v>10</v>
@@ -38114,13 +38160,13 @@
         <v>0</v>
       </c>
       <c r="D1180" s="28" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="E1180" s="31" t="s">
         <v>1057</v>
       </c>
       <c r="F1180" s="28" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="G1180">
         <v>10</v>
@@ -38667,6 +38713,9 @@
       <c r="D1199" s="32" t="s">
         <v>1082</v>
       </c>
+      <c r="E1199" s="32" t="s">
+        <v>1082</v>
+      </c>
       <c r="G1199">
         <v>10</v>
       </c>
@@ -38679,7 +38728,7 @@
     </row>
     <row r="1200" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1200">
-        <v>920051</v>
+        <v>920053</v>
       </c>
       <c r="B1200" s="25">
         <v>1</v>
@@ -38690,10 +38739,7 @@
       <c r="D1200" s="30" t="s">
         <v>1089</v>
       </c>
-      <c r="E1200" s="31" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F1200" s="30" t="s">
+      <c r="F1200" t="s">
         <v>1089</v>
       </c>
       <c r="G1200">
@@ -38708,7 +38754,7 @@
     </row>
     <row r="1201" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1201">
-        <v>920053</v>
+        <v>1920053</v>
       </c>
       <c r="B1201" s="25">
         <v>1</v>
@@ -38734,7 +38780,7 @@
     </row>
     <row r="1202" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1202">
-        <v>1920053</v>
+        <v>2920053</v>
       </c>
       <c r="B1202" s="25">
         <v>1</v>
@@ -38760,7 +38806,7 @@
     </row>
     <row r="1203" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1203">
-        <v>2920053</v>
+        <v>3920053</v>
       </c>
       <c r="B1203" s="25">
         <v>1</v>
@@ -38786,7 +38832,7 @@
     </row>
     <row r="1204" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1204">
-        <v>3920053</v>
+        <v>4920053</v>
       </c>
       <c r="B1204" s="25">
         <v>1</v>
@@ -38807,12 +38853,12 @@
         <v>1</v>
       </c>
       <c r="I1204">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1205" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1205">
-        <v>4920053</v>
+        <v>5920053</v>
       </c>
       <c r="B1205" s="25">
         <v>1</v>
@@ -38833,12 +38879,12 @@
         <v>1</v>
       </c>
       <c r="I1205">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1206" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1206">
-        <v>5920053</v>
+        <v>6920053</v>
       </c>
       <c r="B1206" s="25">
         <v>1</v>
@@ -38864,7 +38910,7 @@
     </row>
     <row r="1207" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1207">
-        <v>6920053</v>
+        <v>7920053</v>
       </c>
       <c r="B1207" s="25">
         <v>1</v>
@@ -38882,15 +38928,15 @@
         <v>10</v>
       </c>
       <c r="H1207" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1207">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1208" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1208">
-        <v>7920053</v>
+        <v>8920053</v>
       </c>
       <c r="B1208" s="25">
         <v>1</v>
@@ -38908,15 +38954,15 @@
         <v>10</v>
       </c>
       <c r="H1208" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1208">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1209" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1209">
-        <v>8920053</v>
+        <v>9920053</v>
       </c>
       <c r="B1209" s="25">
         <v>1</v>
@@ -38934,15 +38980,15 @@
         <v>10</v>
       </c>
       <c r="H1209" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1209">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1210" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1210">
-        <v>9920053</v>
+        <v>14920053</v>
       </c>
       <c r="B1210" s="25">
         <v>1</v>
@@ -38951,24 +38997,24 @@
         <v>0</v>
       </c>
       <c r="D1210" s="30" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F1210" t="s">
-        <v>1099</v>
+        <v>1102</v>
+      </c>
+      <c r="F1210" s="30" t="s">
+        <v>1102</v>
       </c>
       <c r="G1210">
         <v>10</v>
       </c>
       <c r="H1210" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1210">
-        <v>15000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1211" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1211">
-        <v>14920053</v>
+        <v>920054</v>
       </c>
       <c r="B1211" s="25">
         <v>1</v>
@@ -38977,10 +39023,13 @@
         <v>0</v>
       </c>
       <c r="D1211" s="30" t="s">
-        <v>1104</v>
+        <v>1101</v>
+      </c>
+      <c r="E1211" s="31" t="s">
+        <v>1057</v>
       </c>
       <c r="F1211" s="30" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="G1211">
         <v>10</v>
@@ -38989,12 +39038,12 @@
         <v>1</v>
       </c>
       <c r="I1211">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1212" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1212">
-        <v>920054</v>
+      <c r="A1212" s="32">
+        <v>820054</v>
       </c>
       <c r="B1212" s="25">
         <v>1</v>
@@ -39002,13 +39051,10 @@
       <c r="C1212">
         <v>0</v>
       </c>
-      <c r="D1212" s="30" t="s">
+      <c r="D1212" s="32" t="s">
         <v>1103</v>
       </c>
-      <c r="E1212" s="31" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F1212" s="30" t="s">
+      <c r="E1212" s="32" t="s">
         <v>1103</v>
       </c>
       <c r="G1212">
@@ -39022,8 +39068,8 @@
       </c>
     </row>
     <row r="1213" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1213" s="32">
-        <v>820054</v>
+      <c r="A1213">
+        <v>920041</v>
       </c>
       <c r="B1213" s="25">
         <v>1</v>
@@ -39031,8 +39077,11 @@
       <c r="C1213">
         <v>0</v>
       </c>
-      <c r="D1213" s="32" t="s">
-        <v>1100</v>
+      <c r="D1213" s="30" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>1046</v>
       </c>
       <c r="G1213">
         <v>10</v>
@@ -39046,7 +39095,7 @@
     </row>
     <row r="1214" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1214">
-        <v>920041</v>
+        <v>1920041</v>
       </c>
       <c r="B1214" s="25">
         <v>1</v>
@@ -39055,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="D1214" s="30" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F1214" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G1214">
         <v>10</v>
@@ -39067,12 +39116,12 @@
         <v>1</v>
       </c>
       <c r="I1214">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1215" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1215">
-        <v>1920041</v>
+        <v>2920041</v>
       </c>
       <c r="B1215" s="25">
         <v>1</v>
@@ -39081,10 +39130,10 @@
         <v>0</v>
       </c>
       <c r="D1215" s="30" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F1215" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="G1215">
         <v>10</v>
@@ -39093,12 +39142,12 @@
         <v>1</v>
       </c>
       <c r="I1215">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1216" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1216">
-        <v>2920041</v>
+        <v>3920041</v>
       </c>
       <c r="B1216" s="25">
         <v>1</v>
@@ -39107,10 +39156,10 @@
         <v>0</v>
       </c>
       <c r="D1216" s="30" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F1216" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="G1216">
         <v>10</v>
@@ -39119,12 +39168,12 @@
         <v>1</v>
       </c>
       <c r="I1216">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1217" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1217">
-        <v>3920041</v>
+        <v>4920041</v>
       </c>
       <c r="B1217" s="25">
         <v>1</v>
@@ -39133,10 +39182,10 @@
         <v>0</v>
       </c>
       <c r="D1217" s="30" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F1217" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="G1217">
         <v>10</v>
@@ -39145,12 +39194,12 @@
         <v>1</v>
       </c>
       <c r="I1217">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1218" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1218">
-        <v>4920041</v>
+        <v>5920041</v>
       </c>
       <c r="B1218" s="25">
         <v>1</v>
@@ -39159,10 +39208,10 @@
         <v>0</v>
       </c>
       <c r="D1218" s="30" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F1218" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G1218">
         <v>10</v>
@@ -39176,7 +39225,7 @@
     </row>
     <row r="1219" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1219">
-        <v>5920041</v>
+        <v>6920041</v>
       </c>
       <c r="B1219" s="25">
         <v>1</v>
@@ -39185,10 +39234,10 @@
         <v>0</v>
       </c>
       <c r="D1219" s="30" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F1219" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G1219">
         <v>10</v>
@@ -39202,7 +39251,7 @@
     </row>
     <row r="1220" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1220">
-        <v>6920041</v>
+        <v>7920041</v>
       </c>
       <c r="B1220" s="25">
         <v>1</v>
@@ -39211,16 +39260,16 @@
         <v>0</v>
       </c>
       <c r="D1220" s="30" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F1220" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G1220">
         <v>10</v>
       </c>
       <c r="H1220" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1220">
         <v>0</v>
@@ -39228,7 +39277,7 @@
     </row>
     <row r="1221" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1221">
-        <v>7920041</v>
+        <v>8920041</v>
       </c>
       <c r="B1221" s="25">
         <v>1</v>
@@ -39237,16 +39286,16 @@
         <v>0</v>
       </c>
       <c r="D1221" s="30" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F1221" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G1221">
         <v>10</v>
       </c>
       <c r="H1221" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1221">
         <v>0</v>
@@ -39254,7 +39303,7 @@
     </row>
     <row r="1222" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1222">
-        <v>8920041</v>
+        <v>9920041</v>
       </c>
       <c r="B1222" s="25">
         <v>1</v>
@@ -39263,16 +39312,16 @@
         <v>0</v>
       </c>
       <c r="D1222" s="30" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F1222" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="G1222">
         <v>10</v>
       </c>
       <c r="H1222" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1222">
         <v>0</v>
@@ -39280,7 +39329,7 @@
     </row>
     <row r="1223" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1223">
-        <v>9920041</v>
+        <v>920052</v>
       </c>
       <c r="B1223" s="25">
         <v>1</v>
@@ -39289,18 +39338,362 @@
         <v>0</v>
       </c>
       <c r="D1223" s="30" t="s">
-        <v>1055</v>
+        <v>1104</v>
+      </c>
+      <c r="E1223" s="31" t="s">
+        <v>1057</v>
       </c>
       <c r="F1223" t="s">
-        <v>1055</v>
+        <v>1104</v>
       </c>
       <c r="G1223">
         <v>10</v>
       </c>
       <c r="H1223" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1224">
+        <v>1920052</v>
+      </c>
+      <c r="B1224" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1224">
+        <v>0</v>
+      </c>
+      <c r="D1224" s="30" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G1224">
+        <v>10</v>
+      </c>
+      <c r="H1224" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1224">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1225">
+        <v>2920052</v>
+      </c>
+      <c r="B1225" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1225">
+        <v>0</v>
+      </c>
+      <c r="D1225" s="30" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G1225">
+        <v>10</v>
+      </c>
+      <c r="H1225" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1226">
+        <v>3920052</v>
+      </c>
+      <c r="B1226" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1226">
+        <v>0</v>
+      </c>
+      <c r="D1226" s="30" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G1226">
+        <v>10</v>
+      </c>
+      <c r="H1226" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1227">
+        <v>4920052</v>
+      </c>
+      <c r="B1227" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1227">
+        <v>0</v>
+      </c>
+      <c r="D1227" s="30" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F1227" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G1227">
+        <v>10</v>
+      </c>
+      <c r="H1227" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1228">
+        <v>5920052</v>
+      </c>
+      <c r="B1228" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1228">
+        <v>0</v>
+      </c>
+      <c r="D1228" s="30" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G1228">
+        <v>10</v>
+      </c>
+      <c r="H1228" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1229">
+        <v>6920052</v>
+      </c>
+      <c r="B1229" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1229">
+        <v>0</v>
+      </c>
+      <c r="D1229" s="30" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G1229">
+        <v>10</v>
+      </c>
+      <c r="H1229" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1230">
+        <v>7920052</v>
+      </c>
+      <c r="B1230" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1230">
+        <v>0</v>
+      </c>
+      <c r="D1230" s="30" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G1230">
+        <v>10</v>
+      </c>
+      <c r="H1230" s="28">
         <v>2</v>
       </c>
-      <c r="I1223">
+      <c r="I1230">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1231">
+        <v>8920052</v>
+      </c>
+      <c r="B1231" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1231">
+        <v>0</v>
+      </c>
+      <c r="D1231" s="30" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G1231">
+        <v>10</v>
+      </c>
+      <c r="H1231" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1232">
+        <v>9920052</v>
+      </c>
+      <c r="B1232" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1232">
+        <v>0</v>
+      </c>
+      <c r="D1232" s="30" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G1232">
+        <v>10</v>
+      </c>
+      <c r="H1232" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1232">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1233">
+        <v>14920052</v>
+      </c>
+      <c r="B1233" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1233">
+        <v>0</v>
+      </c>
+      <c r="D1233" s="30" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F1233" s="30" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1233">
+        <v>10</v>
+      </c>
+      <c r="H1233" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1233">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1234">
+        <v>920055</v>
+      </c>
+      <c r="B1234" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1234">
+        <v>0</v>
+      </c>
+      <c r="D1234" s="30" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E1234" s="31" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F1234" s="30" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G1234">
+        <v>10</v>
+      </c>
+      <c r="H1234" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1235" s="32">
+        <v>820055</v>
+      </c>
+      <c r="B1235" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1235">
+        <v>0</v>
+      </c>
+      <c r="D1235" s="32" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E1235" s="32" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G1235">
+        <v>10</v>
+      </c>
+      <c r="H1235" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1236" s="32">
+        <v>8200556</v>
+      </c>
+      <c r="B1236" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1236">
+        <v>0</v>
+      </c>
+      <c r="D1236" s="32" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E1236" s="32" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G1236">
+        <v>10</v>
+      </c>
+      <c r="H1236" s="28">
+        <v>1</v>
+      </c>
+      <c r="I1236">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A3209A-60F7-4292-822C-579A9E11BF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7CEC85-8F0B-4439-A3BB-93DEBCED8852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3625" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3622" uniqueCount="1119">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2716,34 +2716,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>参数-调整伤害系数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻附带冰元素伤害系数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻附带火元素伤害系数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻附带毒元素伤害系数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻附带电元素伤害系数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>被动技能-整体提高普攻伤害，含附加的元素属性伤害</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>普攻附带物理伤害系数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>普攻概率附加冰冻</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -3854,6 +3830,23 @@
   </si>
   <si>
     <t>雷神附体-参数6-触发概率</t>
+  </si>
+  <si>
+    <t>普攻附带冰元素伤害标记</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数-元素类型标记</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻附带火元素伤害标记</t>
+  </si>
+  <si>
+    <t>普攻附带毒元素伤害标记</t>
+  </si>
+  <si>
+    <t>普攻附带电元素伤害标记</t>
   </si>
 </sst>
 </file>
@@ -4557,7 +4550,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1236"/>
+  <dimension ref="A1:I1240"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -4607,7 +4600,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -4636,7 +4629,7 @@
         <v>13</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -4665,7 +4658,7 @@
         <v>21</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
@@ -5581,7 +5574,7 @@
         <v>29</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>27</v>
@@ -5607,13 +5600,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G37" s="29">
         <v>6</v>
@@ -5636,13 +5629,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G38" s="29">
         <v>6</v>
@@ -5665,13 +5658,13 @@
         <v>0</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G39" s="29">
         <v>6</v>
@@ -5694,13 +5687,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G40" s="29">
         <v>6</v>
@@ -5723,13 +5716,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G41" s="29">
         <v>6</v>
@@ -5752,13 +5745,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G42" s="29">
         <v>6</v>
@@ -20274,7 +20267,7 @@
         <v>742</v>
       </c>
       <c r="E543" s="25" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="F543" s="14" t="s">
         <v>262</v>
@@ -20347,151 +20340,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A546" s="25">
-        <v>7000301</v>
-      </c>
-      <c r="B546" s="25">
-        <v>1</v>
-      </c>
-      <c r="C546" s="25">
-        <v>0</v>
-      </c>
-      <c r="D546" s="27" t="s">
-        <v>758</v>
-      </c>
-      <c r="E546" s="25" t="s">
-        <v>757</v>
-      </c>
-      <c r="F546" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="G546" s="25">
-        <v>10</v>
-      </c>
-      <c r="H546" s="25">
-        <v>2</v>
-      </c>
-      <c r="I546">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A547" s="25">
-        <v>7000302</v>
-      </c>
-      <c r="B547" s="25">
-        <v>1</v>
-      </c>
-      <c r="C547" s="25">
-        <v>0</v>
-      </c>
-      <c r="D547" s="27" t="s">
-        <v>759</v>
-      </c>
-      <c r="E547" s="25" t="s">
-        <v>757</v>
-      </c>
-      <c r="F547" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="G547" s="25">
-        <v>10</v>
-      </c>
-      <c r="H547" s="25">
-        <v>2</v>
-      </c>
-      <c r="I547">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A548" s="25">
-        <v>7000303</v>
-      </c>
-      <c r="B548" s="25">
-        <v>1</v>
-      </c>
-      <c r="C548" s="25">
-        <v>0</v>
-      </c>
-      <c r="D548" s="27" t="s">
-        <v>760</v>
-      </c>
-      <c r="E548" s="25" t="s">
-        <v>757</v>
-      </c>
-      <c r="F548" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="G548" s="25">
-        <v>10</v>
-      </c>
-      <c r="H548" s="25">
-        <v>2</v>
-      </c>
-      <c r="I548">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A549" s="25">
-        <v>7000304</v>
-      </c>
-      <c r="B549" s="25">
-        <v>1</v>
-      </c>
-      <c r="C549" s="25">
-        <v>0</v>
-      </c>
-      <c r="D549" s="27" t="s">
-        <v>761</v>
-      </c>
-      <c r="E549" s="25" t="s">
-        <v>757</v>
-      </c>
-      <c r="F549" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="G549" s="25">
-        <v>10</v>
-      </c>
-      <c r="H549" s="25">
-        <v>2</v>
-      </c>
-      <c r="I549">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A550" s="25">
-        <v>7000305</v>
-      </c>
-      <c r="B550" s="25">
-        <v>1</v>
-      </c>
-      <c r="C550" s="25">
-        <v>0</v>
-      </c>
-      <c r="D550" s="27" t="s">
-        <v>763</v>
-      </c>
-      <c r="E550" s="25" t="s">
-        <v>757</v>
-      </c>
-      <c r="F550" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="G550" s="25">
-        <v>10</v>
-      </c>
-      <c r="H550" s="25">
-        <v>2</v>
-      </c>
-      <c r="I550">
-        <v>10000</v>
-      </c>
-    </row>
     <row r="551" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A551" s="25">
         <v>7000501</v>
@@ -20503,10 +20351,10 @@
         <v>0</v>
       </c>
       <c r="D551" s="27" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="E551" s="25" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="F551" s="14" t="s">
         <v>262</v>
@@ -20532,10 +20380,10 @@
         <v>0</v>
       </c>
       <c r="D552" s="27" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="E552" s="25" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="F552" s="14" t="s">
         <v>262</v>
@@ -20561,10 +20409,10 @@
         <v>0</v>
       </c>
       <c r="D553" s="27" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="E553" s="25" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="F553" s="14" t="s">
         <v>262</v>
@@ -33110,10 +32958,10 @@
         <v>0</v>
       </c>
       <c r="D986" s="30" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="F986" s="14" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="G986">
         <v>10</v>
@@ -33136,10 +32984,10 @@
         <v>0</v>
       </c>
       <c r="D987" s="30" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="F987" s="14" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="G987">
         <v>10</v>
@@ -33162,10 +33010,10 @@
         <v>0</v>
       </c>
       <c r="D988" s="30" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="F988" s="14" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="G988">
         <v>10</v>
@@ -33188,10 +33036,10 @@
         <v>0</v>
       </c>
       <c r="D989" s="30" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="F989" s="14" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="G989">
         <v>10</v>
@@ -33214,10 +33062,10 @@
         <v>0</v>
       </c>
       <c r="D990" s="30" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="F990" s="14" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="G990">
         <v>10</v>
@@ -33240,10 +33088,10 @@
         <v>0</v>
       </c>
       <c r="D991" s="30" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="F991" s="14" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="G991">
         <v>10</v>
@@ -33266,10 +33114,10 @@
         <v>0</v>
       </c>
       <c r="D992" s="30" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="F992" s="14" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="G992">
         <v>10</v>
@@ -33292,10 +33140,10 @@
         <v>0</v>
       </c>
       <c r="D993" s="30" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="F993" s="14" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="G993">
         <v>10</v>
@@ -33318,10 +33166,10 @@
         <v>0</v>
       </c>
       <c r="D994" s="30" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="F994" s="14" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="G994">
         <v>10</v>
@@ -33335,7 +33183,7 @@
     </row>
     <row r="995" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A995" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="B995" s="25">
         <v>1</v>
@@ -33344,10 +33192,10 @@
         <v>0</v>
       </c>
       <c r="D995" s="30" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="F995" s="14" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="G995">
         <v>10</v>
@@ -33361,7 +33209,7 @@
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A996" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="B996" s="25">
         <v>1</v>
@@ -33370,10 +33218,10 @@
         <v>0</v>
       </c>
       <c r="D996" s="30" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="F996" s="14" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="G996">
         <v>10</v>
@@ -33387,7 +33235,7 @@
     </row>
     <row r="997" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A997" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="B997" s="25">
         <v>1</v>
@@ -33396,10 +33244,10 @@
         <v>0</v>
       </c>
       <c r="D997" s="30" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="F997" s="14" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="G997">
         <v>10</v>
@@ -33413,7 +33261,7 @@
     </row>
     <row r="998" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A998" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B998" s="25">
         <v>1</v>
@@ -33422,10 +33270,10 @@
         <v>0</v>
       </c>
       <c r="D998" s="30" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="F998" s="14" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="G998">
         <v>10</v>
@@ -33439,7 +33287,7 @@
     </row>
     <row r="999" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A999" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="B999" s="25">
         <v>1</v>
@@ -33448,10 +33296,10 @@
         <v>0</v>
       </c>
       <c r="D999" s="30" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="F999" s="14" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="G999">
         <v>10</v>
@@ -33465,7 +33313,7 @@
     </row>
     <row r="1000" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1000" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="B1000" s="25">
         <v>1</v>
@@ -33474,10 +33322,10 @@
         <v>0</v>
       </c>
       <c r="D1000" s="30" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F1000" s="14" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="G1000">
         <v>10</v>
@@ -33491,7 +33339,7 @@
     </row>
     <row r="1001" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1001" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="B1001" s="25">
         <v>1</v>
@@ -33500,10 +33348,10 @@
         <v>0</v>
       </c>
       <c r="D1001" s="30" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="F1001" s="14" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="G1001">
         <v>10</v>
@@ -33517,7 +33365,7 @@
     </row>
     <row r="1002" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1002" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="B1002" s="25">
         <v>1</v>
@@ -33526,10 +33374,10 @@
         <v>0</v>
       </c>
       <c r="D1002" s="30" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="F1002" s="14" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="G1002">
         <v>10</v>
@@ -33543,7 +33391,7 @@
     </row>
     <row r="1003" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1003" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="B1003" s="25">
         <v>1</v>
@@ -33552,10 +33400,10 @@
         <v>0</v>
       </c>
       <c r="D1003" s="30" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="F1003" s="14" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="G1003">
         <v>10</v>
@@ -33569,7 +33417,7 @@
     </row>
     <row r="1004" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1004" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="B1004" s="25">
         <v>1</v>
@@ -33578,10 +33426,10 @@
         <v>0</v>
       </c>
       <c r="D1004" s="30" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="F1004" s="14" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="G1004">
         <v>10</v>
@@ -33595,7 +33443,7 @@
     </row>
     <row r="1005" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1005" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="B1005" s="25">
         <v>1</v>
@@ -33604,10 +33452,10 @@
         <v>0</v>
       </c>
       <c r="D1005" s="30" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="F1005" s="14" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="G1005">
         <v>10</v>
@@ -33621,7 +33469,7 @@
     </row>
     <row r="1006" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1006" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="B1006" s="25">
         <v>1</v>
@@ -33630,10 +33478,10 @@
         <v>0</v>
       </c>
       <c r="D1006" s="30" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="F1006" s="14" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="G1006">
         <v>10</v>
@@ -33647,7 +33495,7 @@
     </row>
     <row r="1007" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1007" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="B1007" s="25">
         <v>1</v>
@@ -33656,10 +33504,10 @@
         <v>0</v>
       </c>
       <c r="D1007" s="30" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="F1007" s="14" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="G1007">
         <v>10</v>
@@ -33673,7 +33521,7 @@
     </row>
     <row r="1008" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1008" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="B1008" s="25">
         <v>1</v>
@@ -33682,10 +33530,10 @@
         <v>0</v>
       </c>
       <c r="D1008" s="30" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="F1008" s="14" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="G1008">
         <v>10</v>
@@ -33699,7 +33547,7 @@
     </row>
     <row r="1009" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1009" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="B1009" s="25">
         <v>1</v>
@@ -33708,10 +33556,10 @@
         <v>0</v>
       </c>
       <c r="D1009" s="30" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="F1009" s="14" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="G1009">
         <v>10</v>
@@ -33725,7 +33573,7 @@
     </row>
     <row r="1010" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1010" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="B1010" s="25">
         <v>1</v>
@@ -33734,10 +33582,10 @@
         <v>0</v>
       </c>
       <c r="D1010" s="30" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="F1010" s="14" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="G1010">
         <v>10</v>
@@ -33751,7 +33599,7 @@
     </row>
     <row r="1011" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1011" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="B1011" s="25">
         <v>1</v>
@@ -33760,10 +33608,10 @@
         <v>0</v>
       </c>
       <c r="D1011" s="30" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="F1011" s="14" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="G1011">
         <v>10</v>
@@ -33777,7 +33625,7 @@
     </row>
     <row r="1012" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1012" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="B1012" s="25">
         <v>1</v>
@@ -33786,10 +33634,10 @@
         <v>0</v>
       </c>
       <c r="D1012" s="30" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="F1012" s="14" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="G1012">
         <v>10</v>
@@ -33803,7 +33651,7 @@
     </row>
     <row r="1013" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1013" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="B1013" s="25">
         <v>1</v>
@@ -33812,10 +33660,10 @@
         <v>0</v>
       </c>
       <c r="D1013" s="30" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="F1013" s="14" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="G1013">
         <v>10</v>
@@ -33829,7 +33677,7 @@
     </row>
     <row r="1014" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1014" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="B1014" s="25">
         <v>1</v>
@@ -33838,10 +33686,10 @@
         <v>0</v>
       </c>
       <c r="D1014" s="30" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="F1014" s="14" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="G1014">
         <v>10</v>
@@ -33855,7 +33703,7 @@
     </row>
     <row r="1015" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1015" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="B1015" s="25">
         <v>1</v>
@@ -33864,10 +33712,10 @@
         <v>0</v>
       </c>
       <c r="D1015" s="30" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="F1015" s="14" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="G1015">
         <v>10</v>
@@ -33881,7 +33729,7 @@
     </row>
     <row r="1016" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1016" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="B1016" s="25">
         <v>1</v>
@@ -33890,10 +33738,10 @@
         <v>0</v>
       </c>
       <c r="D1016" s="30" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="F1016" s="14" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="G1016">
         <v>10</v>
@@ -33907,7 +33755,7 @@
     </row>
     <row r="1017" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1017" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="B1017" s="25">
         <v>1</v>
@@ -33916,10 +33764,10 @@
         <v>0</v>
       </c>
       <c r="D1017" s="30" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="F1017" s="14" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="G1017">
         <v>10</v>
@@ -33933,7 +33781,7 @@
     </row>
     <row r="1018" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1018" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="B1018" s="25">
         <v>1</v>
@@ -33942,10 +33790,10 @@
         <v>0</v>
       </c>
       <c r="D1018" s="30" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="F1018" s="14" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="G1018">
         <v>10</v>
@@ -33959,7 +33807,7 @@
     </row>
     <row r="1019" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1019" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="B1019" s="25">
         <v>1</v>
@@ -33968,10 +33816,10 @@
         <v>0</v>
       </c>
       <c r="D1019" s="30" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="F1019" s="14" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="G1019">
         <v>10</v>
@@ -33985,7 +33833,7 @@
     </row>
     <row r="1020" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1020" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="B1020" s="25">
         <v>1</v>
@@ -33994,10 +33842,10 @@
         <v>0</v>
       </c>
       <c r="D1020" s="30" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="F1020" s="14" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G1020">
         <v>10</v>
@@ -34011,7 +33859,7 @@
     </row>
     <row r="1021" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1021" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="B1021" s="25">
         <v>1</v>
@@ -34020,10 +33868,10 @@
         <v>0</v>
       </c>
       <c r="D1021" s="30" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="F1021" s="14" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="G1021">
         <v>10</v>
@@ -34037,7 +33885,7 @@
     </row>
     <row r="1022" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1022" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="B1022" s="25">
         <v>1</v>
@@ -34046,10 +33894,10 @@
         <v>0</v>
       </c>
       <c r="D1022" s="30" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="F1022" s="14" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="G1022">
         <v>10</v>
@@ -34063,7 +33911,7 @@
     </row>
     <row r="1023" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1023" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="B1023" s="25">
         <v>1</v>
@@ -34072,10 +33920,10 @@
         <v>0</v>
       </c>
       <c r="D1023" s="30" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="F1023" s="14" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="G1023">
         <v>10</v>
@@ -34089,7 +33937,7 @@
     </row>
     <row r="1024" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1024" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="B1024" s="25">
         <v>1</v>
@@ -34098,10 +33946,10 @@
         <v>0</v>
       </c>
       <c r="D1024" s="30" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="F1024" s="14" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="G1024">
         <v>10</v>
@@ -34115,7 +33963,7 @@
     </row>
     <row r="1025" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1025" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="B1025" s="25">
         <v>1</v>
@@ -34124,10 +33972,10 @@
         <v>0</v>
       </c>
       <c r="D1025" s="30" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="F1025" s="14" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="G1025">
         <v>10</v>
@@ -34141,7 +33989,7 @@
     </row>
     <row r="1026" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1026" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="B1026" s="25">
         <v>1</v>
@@ -34150,10 +33998,10 @@
         <v>0</v>
       </c>
       <c r="D1026" s="30" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="F1026" s="14" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="G1026">
         <v>10</v>
@@ -34167,7 +34015,7 @@
     </row>
     <row r="1027" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1027" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="B1027" s="25">
         <v>1</v>
@@ -34176,10 +34024,10 @@
         <v>0</v>
       </c>
       <c r="D1027" s="30" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="F1027" s="14" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="G1027">
         <v>10</v>
@@ -34193,7 +34041,7 @@
     </row>
     <row r="1028" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1028" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="B1028" s="25">
         <v>1</v>
@@ -34202,10 +34050,10 @@
         <v>0</v>
       </c>
       <c r="D1028" s="30" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F1028" s="14" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="G1028">
         <v>10</v>
@@ -34219,7 +34067,7 @@
     </row>
     <row r="1029" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1029" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="B1029" s="25">
         <v>1</v>
@@ -34228,10 +34076,10 @@
         <v>0</v>
       </c>
       <c r="D1029" s="30" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="F1029" s="14" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="G1029">
         <v>10</v>
@@ -34245,7 +34093,7 @@
     </row>
     <row r="1030" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1030" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="B1030" s="25">
         <v>1</v>
@@ -34254,10 +34102,10 @@
         <v>0</v>
       </c>
       <c r="D1030" s="30" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="F1030" s="14" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="G1030">
         <v>10</v>
@@ -34271,7 +34119,7 @@
     </row>
     <row r="1031" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1031" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="B1031" s="25">
         <v>1</v>
@@ -34280,10 +34128,10 @@
         <v>0</v>
       </c>
       <c r="D1031" s="30" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="F1031" s="14" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="G1031">
         <v>10</v>
@@ -34297,7 +34145,7 @@
     </row>
     <row r="1032" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1032" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="B1032" s="25">
         <v>1</v>
@@ -34306,10 +34154,10 @@
         <v>0</v>
       </c>
       <c r="D1032" s="30" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="F1032" s="14" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="G1032">
         <v>10</v>
@@ -34323,7 +34171,7 @@
     </row>
     <row r="1033" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1033" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="B1033" s="25">
         <v>1</v>
@@ -34332,10 +34180,10 @@
         <v>0</v>
       </c>
       <c r="D1033" s="30" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="F1033" s="14" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="G1033">
         <v>10</v>
@@ -34349,7 +34197,7 @@
     </row>
     <row r="1034" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1034" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="B1034" s="25">
         <v>1</v>
@@ -34358,10 +34206,10 @@
         <v>0</v>
       </c>
       <c r="D1034" s="30" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="F1034" s="14" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="G1034">
         <v>10</v>
@@ -34375,7 +34223,7 @@
     </row>
     <row r="1035" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1035" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="B1035" s="25">
         <v>1</v>
@@ -34384,10 +34232,10 @@
         <v>0</v>
       </c>
       <c r="D1035" s="30" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="F1035" s="14" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="G1035">
         <v>10</v>
@@ -34401,7 +34249,7 @@
     </row>
     <row r="1036" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1036" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B1036" s="25">
         <v>1</v>
@@ -34410,10 +34258,10 @@
         <v>0</v>
       </c>
       <c r="D1036" s="30" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="F1036" s="14" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="G1036">
         <v>10</v>
@@ -34427,7 +34275,7 @@
     </row>
     <row r="1037" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1037" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="B1037" s="25">
         <v>1</v>
@@ -34436,10 +34284,10 @@
         <v>0</v>
       </c>
       <c r="D1037" s="30" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="F1037" s="14" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="G1037">
         <v>10</v>
@@ -34453,7 +34301,7 @@
     </row>
     <row r="1038" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1038" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="B1038" s="25">
         <v>1</v>
@@ -34462,10 +34310,10 @@
         <v>0</v>
       </c>
       <c r="D1038" s="30" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="F1038" s="14" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="G1038">
         <v>10</v>
@@ -34479,7 +34327,7 @@
     </row>
     <row r="1039" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1039" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="B1039" s="25">
         <v>1</v>
@@ -34488,10 +34336,10 @@
         <v>0</v>
       </c>
       <c r="D1039" s="30" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="F1039" s="14" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="G1039">
         <v>10</v>
@@ -34505,7 +34353,7 @@
     </row>
     <row r="1040" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1040" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="B1040" s="25">
         <v>1</v>
@@ -34514,10 +34362,10 @@
         <v>0</v>
       </c>
       <c r="D1040" s="30" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="F1040" s="14" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="G1040">
         <v>10</v>
@@ -34531,7 +34379,7 @@
     </row>
     <row r="1041" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1041" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="B1041" s="25">
         <v>1</v>
@@ -34540,10 +34388,10 @@
         <v>0</v>
       </c>
       <c r="D1041" s="30" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="F1041" s="14" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="G1041">
         <v>10</v>
@@ -34557,7 +34405,7 @@
     </row>
     <row r="1042" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1042" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="B1042" s="25">
         <v>1</v>
@@ -34566,10 +34414,10 @@
         <v>0</v>
       </c>
       <c r="D1042" s="30" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="F1042" s="14" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="G1042">
         <v>10</v>
@@ -34583,7 +34431,7 @@
     </row>
     <row r="1043" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1043" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="B1043" s="25">
         <v>1</v>
@@ -34592,10 +34440,10 @@
         <v>0</v>
       </c>
       <c r="D1043" s="30" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="F1043" s="14" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="G1043">
         <v>10</v>
@@ -34609,7 +34457,7 @@
     </row>
     <row r="1044" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1044" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="B1044" s="25">
         <v>1</v>
@@ -34618,10 +34466,10 @@
         <v>0</v>
       </c>
       <c r="D1044" s="30" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="F1044" s="14" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="G1044">
         <v>10</v>
@@ -34635,7 +34483,7 @@
     </row>
     <row r="1045" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1045" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="B1045" s="25">
         <v>1</v>
@@ -34644,10 +34492,10 @@
         <v>0</v>
       </c>
       <c r="D1045" s="30" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="F1045" s="14" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="G1045">
         <v>10</v>
@@ -34661,7 +34509,7 @@
     </row>
     <row r="1046" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1046" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="B1046" s="25">
         <v>1</v>
@@ -34670,10 +34518,10 @@
         <v>0</v>
       </c>
       <c r="D1046" s="30" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="F1046" s="14" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="G1046">
         <v>10</v>
@@ -34687,7 +34535,7 @@
     </row>
     <row r="1047" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1047" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B1047" s="25">
         <v>1</v>
@@ -34696,10 +34544,10 @@
         <v>0</v>
       </c>
       <c r="D1047" s="30" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="F1047" s="14" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="G1047">
         <v>10</v>
@@ -34713,7 +34561,7 @@
     </row>
     <row r="1048" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1048" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="B1048" s="25">
         <v>1</v>
@@ -34722,10 +34570,10 @@
         <v>0</v>
       </c>
       <c r="D1048" s="30" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="F1048" s="14" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="G1048">
         <v>10</v>
@@ -34739,7 +34587,7 @@
     </row>
     <row r="1049" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1049" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="B1049" s="25">
         <v>1</v>
@@ -34748,10 +34596,10 @@
         <v>0</v>
       </c>
       <c r="D1049" s="30" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="F1049" s="14" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="G1049">
         <v>10</v>
@@ -34765,7 +34613,7 @@
     </row>
     <row r="1050" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1050" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="B1050" s="25">
         <v>1</v>
@@ -34774,10 +34622,10 @@
         <v>0</v>
       </c>
       <c r="D1050" s="30" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="F1050" s="14" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="G1050">
         <v>10</v>
@@ -34791,7 +34639,7 @@
     </row>
     <row r="1051" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1051" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="B1051" s="25">
         <v>1</v>
@@ -34800,10 +34648,10 @@
         <v>0</v>
       </c>
       <c r="D1051" s="30" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="F1051" s="14" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="G1051">
         <v>10</v>
@@ -34817,7 +34665,7 @@
     </row>
     <row r="1052" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1052" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="B1052" s="25">
         <v>1</v>
@@ -34826,10 +34674,10 @@
         <v>0</v>
       </c>
       <c r="D1052" s="30" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="F1052" s="14" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="G1052">
         <v>10</v>
@@ -34843,7 +34691,7 @@
     </row>
     <row r="1053" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1053" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="B1053" s="25">
         <v>1</v>
@@ -34852,10 +34700,10 @@
         <v>0</v>
       </c>
       <c r="D1053" s="30" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="F1053" s="14" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="G1053">
         <v>10</v>
@@ -34869,7 +34717,7 @@
     </row>
     <row r="1054" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1054" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="B1054" s="25">
         <v>1</v>
@@ -34878,10 +34726,10 @@
         <v>0</v>
       </c>
       <c r="D1054" s="30" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="F1054" s="14" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="G1054">
         <v>10</v>
@@ -34895,7 +34743,7 @@
     </row>
     <row r="1055" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1055" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="B1055" s="25">
         <v>1</v>
@@ -34904,10 +34752,10 @@
         <v>0</v>
       </c>
       <c r="D1055" s="30" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="F1055" s="14" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="G1055">
         <v>10</v>
@@ -34921,7 +34769,7 @@
     </row>
     <row r="1056" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1056" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="B1056" s="25">
         <v>1</v>
@@ -34930,10 +34778,10 @@
         <v>0</v>
       </c>
       <c r="D1056" s="30" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="F1056" s="14" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="G1056">
         <v>10</v>
@@ -34947,7 +34795,7 @@
     </row>
     <row r="1057" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1057" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="B1057" s="25">
         <v>1</v>
@@ -34956,10 +34804,10 @@
         <v>0</v>
       </c>
       <c r="D1057" s="30" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="F1057" s="14" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="G1057">
         <v>10</v>
@@ -34973,7 +34821,7 @@
     </row>
     <row r="1058" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1058" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="B1058" s="25">
         <v>1</v>
@@ -34982,10 +34830,10 @@
         <v>0</v>
       </c>
       <c r="D1058" s="30" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="F1058" s="14" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="G1058">
         <v>10</v>
@@ -34999,7 +34847,7 @@
     </row>
     <row r="1059" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1059" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="B1059" s="25">
         <v>1</v>
@@ -35008,10 +34856,10 @@
         <v>0</v>
       </c>
       <c r="D1059" s="30" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="F1059" s="14" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="G1059">
         <v>10</v>
@@ -35025,7 +34873,7 @@
     </row>
     <row r="1060" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1060" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="B1060" s="25">
         <v>1</v>
@@ -35034,10 +34882,10 @@
         <v>0</v>
       </c>
       <c r="D1060" s="30" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="F1060" s="14" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="G1060">
         <v>10</v>
@@ -35051,7 +34899,7 @@
     </row>
     <row r="1061" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1061" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="B1061" s="25">
         <v>1</v>
@@ -35060,10 +34908,10 @@
         <v>0</v>
       </c>
       <c r="D1061" s="30" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="F1061" s="14" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="G1061">
         <v>10</v>
@@ -35077,7 +34925,7 @@
     </row>
     <row r="1062" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1062" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="B1062" s="25">
         <v>1</v>
@@ -35086,10 +34934,10 @@
         <v>0</v>
       </c>
       <c r="D1062" s="30" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="F1062" s="14" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="G1062">
         <v>10</v>
@@ -35103,7 +34951,7 @@
     </row>
     <row r="1063" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1063" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="B1063" s="25">
         <v>1</v>
@@ -35112,10 +34960,10 @@
         <v>0</v>
       </c>
       <c r="D1063" s="30" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="F1063" s="14" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="G1063">
         <v>10</v>
@@ -35129,7 +34977,7 @@
     </row>
     <row r="1064" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1064" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="B1064" s="25">
         <v>1</v>
@@ -35138,10 +34986,10 @@
         <v>0</v>
       </c>
       <c r="D1064" s="30" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="F1064" s="14" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="G1064">
         <v>10</v>
@@ -35155,7 +35003,7 @@
     </row>
     <row r="1065" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1065" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B1065" s="25">
         <v>1</v>
@@ -35164,10 +35012,10 @@
         <v>0</v>
       </c>
       <c r="D1065" s="30" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="F1065" s="14" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="G1065">
         <v>10</v>
@@ -35181,7 +35029,7 @@
     </row>
     <row r="1066" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1066" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="B1066" s="25">
         <v>1</v>
@@ -35190,10 +35038,10 @@
         <v>0</v>
       </c>
       <c r="D1066" s="30" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="F1066" s="14" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="G1066">
         <v>10</v>
@@ -35207,7 +35055,7 @@
     </row>
     <row r="1067" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1067" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="B1067" s="25">
         <v>1</v>
@@ -35216,10 +35064,10 @@
         <v>0</v>
       </c>
       <c r="D1067" s="30" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="F1067" s="14" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="G1067">
         <v>10</v>
@@ -35233,7 +35081,7 @@
     </row>
     <row r="1068" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1068" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="B1068" s="25">
         <v>1</v>
@@ -35242,10 +35090,10 @@
         <v>0</v>
       </c>
       <c r="D1068" s="30" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="F1068" s="14" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="G1068">
         <v>10</v>
@@ -35259,7 +35107,7 @@
     </row>
     <row r="1069" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1069" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="B1069" s="25">
         <v>1</v>
@@ -35268,10 +35116,10 @@
         <v>0</v>
       </c>
       <c r="D1069" s="30" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="F1069" s="14" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="G1069">
         <v>10</v>
@@ -35285,7 +35133,7 @@
     </row>
     <row r="1070" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1070" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="B1070" s="25">
         <v>1</v>
@@ -35294,10 +35142,10 @@
         <v>0</v>
       </c>
       <c r="D1070" s="30" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="F1070" s="14" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="G1070">
         <v>10</v>
@@ -35311,7 +35159,7 @@
     </row>
     <row r="1071" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1071" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="B1071" s="25">
         <v>1</v>
@@ -35320,10 +35168,10 @@
         <v>0</v>
       </c>
       <c r="D1071" s="30" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="F1071" s="14" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="G1071">
         <v>10</v>
@@ -35337,7 +35185,7 @@
     </row>
     <row r="1072" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1072" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="B1072" s="25">
         <v>1</v>
@@ -35346,10 +35194,10 @@
         <v>0</v>
       </c>
       <c r="D1072" s="30" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="F1072" s="14" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="G1072">
         <v>10</v>
@@ -35363,7 +35211,7 @@
     </row>
     <row r="1073" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1073" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B1073" s="25">
         <v>1</v>
@@ -35372,10 +35220,10 @@
         <v>0</v>
       </c>
       <c r="D1073" s="30" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="F1073" s="14" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="G1073">
         <v>10</v>
@@ -35389,7 +35237,7 @@
     </row>
     <row r="1074" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1074" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="B1074" s="25">
         <v>1</v>
@@ -35398,10 +35246,10 @@
         <v>0</v>
       </c>
       <c r="D1074" s="30" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="F1074" s="14" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="G1074">
         <v>10</v>
@@ -35415,7 +35263,7 @@
     </row>
     <row r="1075" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1075" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B1075" s="25">
         <v>1</v>
@@ -35424,10 +35272,10 @@
         <v>0</v>
       </c>
       <c r="D1075" s="30" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="F1075" s="14" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="G1075">
         <v>10</v>
@@ -35450,10 +35298,10 @@
         <v>0</v>
       </c>
       <c r="D1076" s="30" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="F1076" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="G1076">
         <v>10</v>
@@ -35476,10 +35324,10 @@
         <v>0</v>
       </c>
       <c r="D1077" s="30" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="F1077" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="G1077">
         <v>10</v>
@@ -35502,10 +35350,10 @@
         <v>0</v>
       </c>
       <c r="D1078" s="30" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="F1078" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="G1078">
         <v>10</v>
@@ -35528,10 +35376,10 @@
         <v>0</v>
       </c>
       <c r="D1079" s="30" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="F1079" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="G1079">
         <v>10</v>
@@ -35554,10 +35402,10 @@
         <v>0</v>
       </c>
       <c r="D1080" s="30" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="F1080" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="G1080">
         <v>10</v>
@@ -35580,10 +35428,10 @@
         <v>0</v>
       </c>
       <c r="D1081" s="30" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="F1081" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="G1081">
         <v>10</v>
@@ -35606,10 +35454,10 @@
         <v>0</v>
       </c>
       <c r="D1082" s="30" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="F1082" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="G1082">
         <v>10</v>
@@ -35632,10 +35480,10 @@
         <v>0</v>
       </c>
       <c r="D1083" s="30" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="F1083" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="G1083">
         <v>10</v>
@@ -35658,10 +35506,10 @@
         <v>0</v>
       </c>
       <c r="D1084" s="30" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="F1084" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="G1084">
         <v>10</v>
@@ -35684,10 +35532,10 @@
         <v>0</v>
       </c>
       <c r="D1085" s="30" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="F1085" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G1085">
         <v>10</v>
@@ -35710,10 +35558,10 @@
         <v>0</v>
       </c>
       <c r="D1086" s="30" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="F1086" s="30" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="G1086">
         <v>10</v>
@@ -35736,10 +35584,10 @@
         <v>0</v>
       </c>
       <c r="D1087" s="30" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="F1087" s="30" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="G1087">
         <v>10</v>
@@ -35762,7 +35610,7 @@
         <v>0</v>
       </c>
       <c r="D1088" s="30" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="G1088">
         <v>10</v>
@@ -35785,7 +35633,7 @@
         <v>0</v>
       </c>
       <c r="D1089" s="30" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="G1089">
         <v>10</v>
@@ -35808,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="D1090" s="30" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="G1090">
         <v>10</v>
@@ -35831,7 +35679,7 @@
         <v>0</v>
       </c>
       <c r="D1091" s="30" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="G1091">
         <v>10</v>
@@ -35854,7 +35702,7 @@
         <v>0</v>
       </c>
       <c r="D1092" s="30" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="G1092">
         <v>10</v>
@@ -35877,7 +35725,7 @@
         <v>0</v>
       </c>
       <c r="D1093" s="30" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="G1093">
         <v>10</v>
@@ -35900,7 +35748,7 @@
         <v>0</v>
       </c>
       <c r="D1094" s="30" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="G1094">
         <v>10</v>
@@ -35923,7 +35771,7 @@
         <v>0</v>
       </c>
       <c r="D1095" s="30" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="G1095">
         <v>10</v>
@@ -35946,7 +35794,7 @@
         <v>0</v>
       </c>
       <c r="D1096" s="30" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="G1096">
         <v>10</v>
@@ -35969,7 +35817,7 @@
         <v>0</v>
       </c>
       <c r="D1097" s="30" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="G1097">
         <v>10</v>
@@ -35992,7 +35840,7 @@
         <v>0</v>
       </c>
       <c r="D1098" s="30" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="G1098">
         <v>10</v>
@@ -36015,7 +35863,7 @@
         <v>0</v>
       </c>
       <c r="D1099" s="30" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="G1099">
         <v>10</v>
@@ -36038,7 +35886,7 @@
         <v>0</v>
       </c>
       <c r="D1100" s="30" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="G1100">
         <v>10</v>
@@ -36061,7 +35909,7 @@
         <v>0</v>
       </c>
       <c r="D1101" s="30" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="G1101">
         <v>10</v>
@@ -36084,7 +35932,7 @@
         <v>0</v>
       </c>
       <c r="D1102" s="30" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="G1102">
         <v>10</v>
@@ -36107,10 +35955,10 @@
         <v>0</v>
       </c>
       <c r="D1103" s="30" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="F1103" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="G1103">
         <v>10</v>
@@ -36133,10 +35981,10 @@
         <v>0</v>
       </c>
       <c r="D1104" s="30" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="F1104" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="G1104">
         <v>10</v>
@@ -36159,10 +36007,10 @@
         <v>0</v>
       </c>
       <c r="D1105" s="30" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="F1105" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="G1105">
         <v>10</v>
@@ -36185,10 +36033,10 @@
         <v>0</v>
       </c>
       <c r="D1106" s="30" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="F1106" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="G1106">
         <v>10</v>
@@ -36211,10 +36059,10 @@
         <v>0</v>
       </c>
       <c r="D1107" s="30" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="F1107" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="G1107">
         <v>10</v>
@@ -36237,10 +36085,10 @@
         <v>0</v>
       </c>
       <c r="D1108" s="30" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="F1108" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="G1108">
         <v>10</v>
@@ -36263,10 +36111,10 @@
         <v>0</v>
       </c>
       <c r="D1109" s="30" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="F1109" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="G1109">
         <v>10</v>
@@ -36289,10 +36137,10 @@
         <v>0</v>
       </c>
       <c r="D1110" s="30" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="F1110" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="G1110">
         <v>10</v>
@@ -36315,10 +36163,10 @@
         <v>0</v>
       </c>
       <c r="D1111" s="30" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="F1111" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="G1111">
         <v>10</v>
@@ -36341,10 +36189,10 @@
         <v>0</v>
       </c>
       <c r="D1112" s="30" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="F1112" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="G1112">
         <v>10</v>
@@ -36367,10 +36215,10 @@
         <v>0</v>
       </c>
       <c r="D1113" s="30" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="F1113" s="28" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G1113">
         <v>10</v>
@@ -36393,10 +36241,10 @@
         <v>0</v>
       </c>
       <c r="D1114" s="30" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="F1114" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="G1114">
         <v>10</v>
@@ -36419,10 +36267,10 @@
         <v>0</v>
       </c>
       <c r="D1115" s="30" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="F1115" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="G1115">
         <v>10</v>
@@ -36445,10 +36293,10 @@
         <v>0</v>
       </c>
       <c r="D1116" s="30" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="F1116" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="G1116">
         <v>10</v>
@@ -36471,10 +36319,10 @@
         <v>0</v>
       </c>
       <c r="D1117" s="30" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="F1117" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="G1117">
         <v>10</v>
@@ -36497,10 +36345,10 @@
         <v>0</v>
       </c>
       <c r="D1118" s="30" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="F1118" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="G1118">
         <v>10</v>
@@ -36523,10 +36371,10 @@
         <v>0</v>
       </c>
       <c r="D1119" s="30" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="F1119" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="G1119">
         <v>10</v>
@@ -36549,10 +36397,10 @@
         <v>0</v>
       </c>
       <c r="D1120" s="30" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="F1120" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="G1120">
         <v>10</v>
@@ -36575,10 +36423,10 @@
         <v>0</v>
       </c>
       <c r="D1121" s="30" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="F1121" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="G1121">
         <v>10</v>
@@ -36601,10 +36449,10 @@
         <v>0</v>
       </c>
       <c r="D1122" s="30" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="F1122" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="G1122">
         <v>10</v>
@@ -36627,7 +36475,7 @@
         <v>0</v>
       </c>
       <c r="D1123" s="30" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="G1123">
         <v>10</v>
@@ -36650,7 +36498,7 @@
         <v>0</v>
       </c>
       <c r="D1124" s="30" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="G1124">
         <v>10</v>
@@ -36673,7 +36521,7 @@
         <v>0</v>
       </c>
       <c r="D1125" s="30" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="G1125">
         <v>10</v>
@@ -36696,7 +36544,7 @@
         <v>0</v>
       </c>
       <c r="D1126" s="30" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="G1126">
         <v>10</v>
@@ -36719,7 +36567,7 @@
         <v>0</v>
       </c>
       <c r="D1127" s="30" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="G1127">
         <v>10</v>
@@ -36742,10 +36590,10 @@
         <v>0</v>
       </c>
       <c r="D1128" s="30" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="F1128" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="G1128">
         <v>10</v>
@@ -36768,10 +36616,10 @@
         <v>0</v>
       </c>
       <c r="D1129" s="30" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="F1129" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="G1129">
         <v>10</v>
@@ -36794,10 +36642,10 @@
         <v>0</v>
       </c>
       <c r="D1130" s="30" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="F1130" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="G1130">
         <v>10</v>
@@ -36820,10 +36668,10 @@
         <v>0</v>
       </c>
       <c r="D1131" s="30" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="F1131" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="G1131">
         <v>10</v>
@@ -36846,10 +36694,10 @@
         <v>0</v>
       </c>
       <c r="D1132" s="30" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="F1132" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="G1132">
         <v>10</v>
@@ -36872,10 +36720,10 @@
         <v>0</v>
       </c>
       <c r="D1133" s="30" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="F1133" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="G1133">
         <v>10</v>
@@ -36898,10 +36746,10 @@
         <v>0</v>
       </c>
       <c r="D1134" s="30" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="F1134" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="G1134">
         <v>10</v>
@@ -36924,10 +36772,10 @@
         <v>0</v>
       </c>
       <c r="D1135" s="30" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="F1135" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="G1135">
         <v>10</v>
@@ -36950,10 +36798,10 @@
         <v>0</v>
       </c>
       <c r="D1136" s="30" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="F1136" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="G1136">
         <v>10</v>
@@ -36976,10 +36824,10 @@
         <v>0</v>
       </c>
       <c r="D1137" s="30" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="F1137" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="G1137">
         <v>10</v>
@@ -37002,10 +36850,10 @@
         <v>0</v>
       </c>
       <c r="D1138" s="30" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="F1138" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="G1138">
         <v>10</v>
@@ -37028,10 +36876,10 @@
         <v>0</v>
       </c>
       <c r="D1139" s="30" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="F1139" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="G1139">
         <v>10</v>
@@ -37054,10 +36902,10 @@
         <v>0</v>
       </c>
       <c r="D1140" s="30" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="F1140" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="G1140">
         <v>10</v>
@@ -37080,10 +36928,10 @@
         <v>0</v>
       </c>
       <c r="D1141" s="30" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="F1141" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="G1141">
         <v>10</v>
@@ -37106,10 +36954,10 @@
         <v>0</v>
       </c>
       <c r="D1142" s="30" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="F1142" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="G1142">
         <v>10</v>
@@ -37132,10 +36980,10 @@
         <v>0</v>
       </c>
       <c r="D1143" s="30" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="F1143" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="G1143">
         <v>10</v>
@@ -37158,10 +37006,10 @@
         <v>0</v>
       </c>
       <c r="D1144" s="30" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="F1144" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="G1144">
         <v>10</v>
@@ -37184,10 +37032,10 @@
         <v>0</v>
       </c>
       <c r="D1145" s="30" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="F1145" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="G1145">
         <v>10</v>
@@ -37210,10 +37058,10 @@
         <v>0</v>
       </c>
       <c r="D1146" s="30" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="F1146" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="G1146">
         <v>10</v>
@@ -37236,10 +37084,10 @@
         <v>0</v>
       </c>
       <c r="D1147" s="30" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="F1147" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="G1147">
         <v>10</v>
@@ -37262,10 +37110,10 @@
         <v>0</v>
       </c>
       <c r="D1148" s="30" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="F1148" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="G1148">
         <v>10</v>
@@ -37288,10 +37136,10 @@
         <v>0</v>
       </c>
       <c r="D1149" s="30" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="F1149" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="G1149">
         <v>10</v>
@@ -37314,10 +37162,10 @@
         <v>0</v>
       </c>
       <c r="D1150" s="30" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="F1150" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="G1150">
         <v>10</v>
@@ -37340,10 +37188,10 @@
         <v>0</v>
       </c>
       <c r="D1151" s="30" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="F1151" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="G1151">
         <v>10</v>
@@ -37366,10 +37214,10 @@
         <v>0</v>
       </c>
       <c r="D1152" s="30" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="F1152" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G1152">
         <v>10</v>
@@ -37392,10 +37240,10 @@
         <v>0</v>
       </c>
       <c r="D1153" s="30" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="F1153" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="G1153">
         <v>10</v>
@@ -37418,10 +37266,10 @@
         <v>0</v>
       </c>
       <c r="D1154" s="30" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="F1154" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="G1154">
         <v>10</v>
@@ -37444,10 +37292,10 @@
         <v>0</v>
       </c>
       <c r="D1155" s="30" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="F1155" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="G1155">
         <v>10</v>
@@ -37470,10 +37318,10 @@
         <v>0</v>
       </c>
       <c r="D1156" s="30" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="F1156" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="G1156">
         <v>10</v>
@@ -37496,10 +37344,10 @@
         <v>0</v>
       </c>
       <c r="D1157" s="30" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="F1157" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="G1157">
         <v>10</v>
@@ -37522,13 +37370,13 @@
         <v>0</v>
       </c>
       <c r="D1158" s="30" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="E1158" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1158" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="G1158">
         <v>10</v>
@@ -37551,13 +37399,13 @@
         <v>0</v>
       </c>
       <c r="D1159" s="30" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="E1159" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1159" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="G1159">
         <v>10</v>
@@ -37580,13 +37428,13 @@
         <v>0</v>
       </c>
       <c r="D1160" s="30" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="E1160" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1160" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="G1160">
         <v>10</v>
@@ -37609,13 +37457,13 @@
         <v>0</v>
       </c>
       <c r="D1161" s="30" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="E1161" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1161" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="G1161">
         <v>10</v>
@@ -37638,13 +37486,13 @@
         <v>0</v>
       </c>
       <c r="D1162" s="30" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="E1162" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1162" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="G1162">
         <v>10</v>
@@ -37667,13 +37515,13 @@
         <v>0</v>
       </c>
       <c r="D1163" s="30" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="E1163" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1163" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="G1163">
         <v>10</v>
@@ -37696,13 +37544,13 @@
         <v>0</v>
       </c>
       <c r="D1164" s="30" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="E1164" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1164" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="G1164">
         <v>10</v>
@@ -37725,13 +37573,13 @@
         <v>0</v>
       </c>
       <c r="D1165" s="30" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="E1165" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1165" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="G1165">
         <v>10</v>
@@ -37754,13 +37602,13 @@
         <v>0</v>
       </c>
       <c r="D1166" s="30" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="E1166" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1166" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="G1166">
         <v>10</v>
@@ -37783,13 +37631,13 @@
         <v>0</v>
       </c>
       <c r="D1167" s="30" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="E1167" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1167" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="G1167">
         <v>10</v>
@@ -37812,13 +37660,13 @@
         <v>0</v>
       </c>
       <c r="D1168" s="30" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="E1168" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1168" s="30" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="G1168">
         <v>10</v>
@@ -37841,13 +37689,13 @@
         <v>0</v>
       </c>
       <c r="D1169" s="28" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="E1169" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1169" s="28" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="G1169">
         <v>10</v>
@@ -37870,13 +37718,13 @@
         <v>0</v>
       </c>
       <c r="D1170" s="30" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="E1170" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1170" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="G1170">
         <v>10</v>
@@ -37899,13 +37747,13 @@
         <v>0</v>
       </c>
       <c r="D1171" s="30" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="E1171" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1171" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="G1171">
         <v>10</v>
@@ -37928,13 +37776,13 @@
         <v>0</v>
       </c>
       <c r="D1172" s="30" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="E1172" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1172" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="G1172">
         <v>10</v>
@@ -37957,13 +37805,13 @@
         <v>0</v>
       </c>
       <c r="D1173" s="30" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="E1173" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1173" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="G1173">
         <v>10</v>
@@ -37986,13 +37834,13 @@
         <v>0</v>
       </c>
       <c r="D1174" s="30" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="E1174" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1174" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="G1174">
         <v>10</v>
@@ -38015,13 +37863,13 @@
         <v>0</v>
       </c>
       <c r="D1175" s="30" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="E1175" s="31" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F1175" t="s">
         <v>1057</v>
-      </c>
-      <c r="F1175" t="s">
-        <v>1063</v>
       </c>
       <c r="G1175">
         <v>10</v>
@@ -38044,13 +37892,13 @@
         <v>0</v>
       </c>
       <c r="D1176" s="30" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="E1176" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1176" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="G1176">
         <v>10</v>
@@ -38073,13 +37921,13 @@
         <v>0</v>
       </c>
       <c r="D1177" s="30" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="E1177" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1177" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="G1177">
         <v>10</v>
@@ -38102,13 +37950,13 @@
         <v>0</v>
       </c>
       <c r="D1178" s="30" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="E1178" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1178" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="G1178">
         <v>10</v>
@@ -38131,13 +37979,13 @@
         <v>0</v>
       </c>
       <c r="D1179" s="30" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="E1179" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1179" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="G1179">
         <v>10</v>
@@ -38160,13 +38008,13 @@
         <v>0</v>
       </c>
       <c r="D1180" s="28" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="E1180" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1180" s="28" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="G1180">
         <v>10</v>
@@ -38189,13 +38037,13 @@
         <v>0</v>
       </c>
       <c r="D1181" s="30" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="E1181" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1181" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="G1181">
         <v>10</v>
@@ -38218,13 +38066,13 @@
         <v>0</v>
       </c>
       <c r="D1182" s="30" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="E1182" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1182" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="G1182">
         <v>10</v>
@@ -38247,13 +38095,13 @@
         <v>0</v>
       </c>
       <c r="D1183" s="30" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="E1183" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1183" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="G1183">
         <v>10</v>
@@ -38276,13 +38124,13 @@
         <v>0</v>
       </c>
       <c r="D1184" s="30" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="E1184" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1184" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="G1184">
         <v>10</v>
@@ -38305,13 +38153,13 @@
         <v>0</v>
       </c>
       <c r="D1185" s="30" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="E1185" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1185" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G1185">
         <v>10</v>
@@ -38334,13 +38182,13 @@
         <v>0</v>
       </c>
       <c r="D1186" s="30" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="E1186" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1186" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="G1186">
         <v>10</v>
@@ -38363,13 +38211,13 @@
         <v>0</v>
       </c>
       <c r="D1187" s="30" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="E1187" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1187" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="G1187">
         <v>10</v>
@@ -38392,13 +38240,13 @@
         <v>0</v>
       </c>
       <c r="D1188" s="30" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="E1188" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1188" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="G1188">
         <v>10</v>
@@ -38421,13 +38269,13 @@
         <v>0</v>
       </c>
       <c r="D1189" s="30" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="E1189" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1189" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G1189">
         <v>10</v>
@@ -38450,13 +38298,13 @@
         <v>0</v>
       </c>
       <c r="D1190" s="30" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="E1190" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1190" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="G1190">
         <v>10</v>
@@ -38479,13 +38327,13 @@
         <v>0</v>
       </c>
       <c r="D1191" s="30" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="E1191" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1191" s="30" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="G1191">
         <v>10</v>
@@ -38508,13 +38356,13 @@
         <v>0</v>
       </c>
       <c r="D1192" s="30" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="E1192" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1192" s="30" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="G1192">
         <v>10</v>
@@ -38537,7 +38385,7 @@
         <v>0</v>
       </c>
       <c r="D1193" s="25" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="E1193" s="25" t="s">
         <v>126</v>
@@ -38566,7 +38414,7 @@
         <v>0</v>
       </c>
       <c r="D1194" s="25" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="E1194" s="24" t="s">
         <v>754</v>
@@ -38595,7 +38443,7 @@
         <v>0</v>
       </c>
       <c r="D1195" s="25" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="E1195" s="24" t="s">
         <v>755</v>
@@ -38624,7 +38472,7 @@
         <v>0</v>
       </c>
       <c r="D1196" s="25" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="E1196" s="24" t="s">
         <v>754</v>
@@ -38653,7 +38501,7 @@
         <v>0</v>
       </c>
       <c r="D1197" s="25" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="E1197" s="24" t="s">
         <v>755</v>
@@ -38682,13 +38530,13 @@
         <v>0</v>
       </c>
       <c r="D1198" s="30" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="E1198" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1198" s="30" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="G1198">
         <v>10</v>
@@ -38711,10 +38559,10 @@
         <v>0</v>
       </c>
       <c r="D1199" s="32" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="E1199" s="32" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="G1199">
         <v>10</v>
@@ -38737,10 +38585,10 @@
         <v>0</v>
       </c>
       <c r="D1200" s="30" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="F1200" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="G1200">
         <v>10</v>
@@ -38763,10 +38611,10 @@
         <v>0</v>
       </c>
       <c r="D1201" s="30" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="F1201" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="G1201">
         <v>10</v>
@@ -38789,10 +38637,10 @@
         <v>0</v>
       </c>
       <c r="D1202" s="30" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="F1202" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="G1202">
         <v>10</v>
@@ -38815,10 +38663,10 @@
         <v>0</v>
       </c>
       <c r="D1203" s="30" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="F1203" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="G1203">
         <v>10</v>
@@ -38841,10 +38689,10 @@
         <v>0</v>
       </c>
       <c r="D1204" s="30" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F1204" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="G1204">
         <v>10</v>
@@ -38867,10 +38715,10 @@
         <v>0</v>
       </c>
       <c r="D1205" s="30" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="F1205" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="G1205">
         <v>10</v>
@@ -38893,10 +38741,10 @@
         <v>0</v>
       </c>
       <c r="D1206" s="30" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="F1206" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="G1206">
         <v>10</v>
@@ -38919,10 +38767,10 @@
         <v>0</v>
       </c>
       <c r="D1207" s="30" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="F1207" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="G1207">
         <v>10</v>
@@ -38945,10 +38793,10 @@
         <v>0</v>
       </c>
       <c r="D1208" s="30" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="F1208" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="G1208">
         <v>10</v>
@@ -38971,10 +38819,10 @@
         <v>0</v>
       </c>
       <c r="D1209" s="30" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="F1209" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="G1209">
         <v>10</v>
@@ -38997,10 +38845,10 @@
         <v>0</v>
       </c>
       <c r="D1210" s="30" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="F1210" s="30" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="G1210">
         <v>10</v>
@@ -39023,13 +38871,13 @@
         <v>0</v>
       </c>
       <c r="D1211" s="30" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="E1211" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1211" s="30" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="G1211">
         <v>10</v>
@@ -39052,10 +38900,10 @@
         <v>0</v>
       </c>
       <c r="D1212" s="32" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="E1212" s="32" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="G1212">
         <v>10</v>
@@ -39078,10 +38926,10 @@
         <v>0</v>
       </c>
       <c r="D1213" s="30" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="F1213" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="G1213">
         <v>10</v>
@@ -39104,10 +38952,10 @@
         <v>0</v>
       </c>
       <c r="D1214" s="30" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="F1214" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="G1214">
         <v>10</v>
@@ -39130,10 +38978,10 @@
         <v>0</v>
       </c>
       <c r="D1215" s="30" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="F1215" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="G1215">
         <v>10</v>
@@ -39156,10 +39004,10 @@
         <v>0</v>
       </c>
       <c r="D1216" s="30" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="F1216" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G1216">
         <v>10</v>
@@ -39182,10 +39030,10 @@
         <v>0</v>
       </c>
       <c r="D1217" s="30" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="F1217" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="G1217">
         <v>10</v>
@@ -39208,10 +39056,10 @@
         <v>0</v>
       </c>
       <c r="D1218" s="30" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="F1218" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="G1218">
         <v>10</v>
@@ -39234,10 +39082,10 @@
         <v>0</v>
       </c>
       <c r="D1219" s="30" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="F1219" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G1219">
         <v>10</v>
@@ -39260,10 +39108,10 @@
         <v>0</v>
       </c>
       <c r="D1220" s="30" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="F1220" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="G1220">
         <v>10</v>
@@ -39286,10 +39134,10 @@
         <v>0</v>
       </c>
       <c r="D1221" s="30" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="F1221" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="G1221">
         <v>10</v>
@@ -39312,10 +39160,10 @@
         <v>0</v>
       </c>
       <c r="D1222" s="30" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="F1222" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="G1222">
         <v>10</v>
@@ -39338,13 +39186,13 @@
         <v>0</v>
       </c>
       <c r="D1223" s="30" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="E1223" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1223" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="G1223">
         <v>10</v>
@@ -39367,10 +39215,10 @@
         <v>0</v>
       </c>
       <c r="D1224" s="30" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="F1224" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="G1224">
         <v>10</v>
@@ -39393,10 +39241,10 @@
         <v>0</v>
       </c>
       <c r="D1225" s="30" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="F1225" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="G1225">
         <v>10</v>
@@ -39419,10 +39267,10 @@
         <v>0</v>
       </c>
       <c r="D1226" s="30" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="F1226" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="G1226">
         <v>10</v>
@@ -39445,10 +39293,10 @@
         <v>0</v>
       </c>
       <c r="D1227" s="30" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="F1227" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="G1227">
         <v>10</v>
@@ -39471,10 +39319,10 @@
         <v>0</v>
       </c>
       <c r="D1228" s="30" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="F1228" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="G1228">
         <v>10</v>
@@ -39497,10 +39345,10 @@
         <v>0</v>
       </c>
       <c r="D1229" s="30" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="F1229" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="G1229">
         <v>10</v>
@@ -39523,10 +39371,10 @@
         <v>0</v>
       </c>
       <c r="D1230" s="30" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="F1230" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="G1230">
         <v>10</v>
@@ -39549,10 +39397,10 @@
         <v>0</v>
       </c>
       <c r="D1231" s="30" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="F1231" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="G1231">
         <v>10</v>
@@ -39575,10 +39423,10 @@
         <v>0</v>
       </c>
       <c r="D1232" s="30" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="F1232" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="G1232">
         <v>10</v>
@@ -39601,10 +39449,10 @@
         <v>0</v>
       </c>
       <c r="D1233" s="30" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="F1233" s="30" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="G1233">
         <v>10</v>
@@ -39627,13 +39475,13 @@
         <v>0</v>
       </c>
       <c r="D1234" s="30" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="E1234" s="31" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="F1234" s="30" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="G1234">
         <v>10</v>
@@ -39656,10 +39504,10 @@
         <v>0</v>
       </c>
       <c r="D1235" s="32" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="E1235" s="32" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="G1235">
         <v>10</v>
@@ -39682,10 +39530,10 @@
         <v>0</v>
       </c>
       <c r="D1236" s="32" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="E1236" s="32" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="G1236">
         <v>10</v>
@@ -39694,6 +39542,122 @@
         <v>1</v>
       </c>
       <c r="I1236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1237" s="32">
+        <v>7000311</v>
+      </c>
+      <c r="B1237" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1237" s="25">
+        <v>0</v>
+      </c>
+      <c r="D1237" s="27" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E1237" s="25" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1237" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1237" s="25">
+        <v>10</v>
+      </c>
+      <c r="H1237" s="25">
+        <v>1</v>
+      </c>
+      <c r="I1237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1238" s="32">
+        <v>7000312</v>
+      </c>
+      <c r="B1238" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1238" s="25">
+        <v>0</v>
+      </c>
+      <c r="D1238" s="27" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E1238" s="25" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1238" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1238" s="25">
+        <v>10</v>
+      </c>
+      <c r="H1238" s="25">
+        <v>1</v>
+      </c>
+      <c r="I1238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1239" s="32">
+        <v>7000313</v>
+      </c>
+      <c r="B1239" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1239" s="25">
+        <v>0</v>
+      </c>
+      <c r="D1239" s="27" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E1239" s="25" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1239" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1239" s="25">
+        <v>10</v>
+      </c>
+      <c r="H1239" s="25">
+        <v>1</v>
+      </c>
+      <c r="I1239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1240" s="32">
+        <v>7000314</v>
+      </c>
+      <c r="B1240" s="25">
+        <v>1</v>
+      </c>
+      <c r="C1240" s="25">
+        <v>0</v>
+      </c>
+      <c r="D1240" s="27" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E1240" s="25" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F1240" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1240" s="25">
+        <v>10</v>
+      </c>
+      <c r="H1240" s="25">
+        <v>1</v>
+      </c>
+      <c r="I1240">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -2826,14 +2826,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3088,18 +3081,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="41">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3192,19 +3185,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3217,12 +3198,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3319,12 +3294,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3478,13 +3447,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3493,124 +3465,121 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3618,80 +3587,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -36908,7 +36877,7 @@
         <v>1</v>
       </c>
       <c r="I1154">
-        <v>6000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1155" spans="1:9">
@@ -36966,7 +36935,7 @@
         <v>1</v>
       </c>
       <c r="I1156">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1157" spans="1:9">
@@ -37256,7 +37225,7 @@
         <v>1</v>
       </c>
       <c r="I1166">
-        <v>7500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="1167" spans="1:9">
@@ -37575,7 +37544,7 @@
         <v>1</v>
       </c>
       <c r="I1177">
-        <v>8500</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="1178" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3081,12 +3081,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -37544,7 +37544,7 @@
         <v>1</v>
       </c>
       <c r="I1177">
-        <v>6500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1178" spans="1:9">
@@ -37631,7 +37631,7 @@
         <v>1</v>
       </c>
       <c r="I1180">
-        <v>4000</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1181" spans="1:9">
@@ -37660,7 +37660,7 @@
         <v>1</v>
       </c>
       <c r="I1181">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1182" spans="1:9">
@@ -37718,7 +37718,7 @@
         <v>2</v>
       </c>
       <c r="I1183">
-        <v>13500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1184" spans="1:9">
@@ -37776,7 +37776,7 @@
         <v>2</v>
       </c>
       <c r="I1185">
-        <v>13500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1186" spans="1:9">
@@ -37805,7 +37805,7 @@
         <v>1</v>
       </c>
       <c r="I1186">
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1187" spans="1:9">
@@ -38190,7 +38190,7 @@
         <v>1</v>
       </c>
       <c r="I1200">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1201" spans="1:9">
@@ -38794,7 +38794,7 @@
         <v>1</v>
       </c>
       <c r="I1223">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1224" spans="1:9">
@@ -38846,7 +38846,7 @@
         <v>2</v>
       </c>
       <c r="I1225">
-        <v>18000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1226" spans="1:9">
@@ -38898,7 +38898,7 @@
         <v>2</v>
       </c>
       <c r="I1227">
-        <v>18000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1228" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -2961,14 +2961,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3234,7 +3227,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3327,12 +3320,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3352,12 +3339,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3613,13 +3594,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3628,55 +3612,58 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3685,10 +3672,10 @@
     <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3697,10 +3684,10 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3709,10 +3696,10 @@
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3721,10 +3708,10 @@
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3733,19 +3720,13 @@
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3753,77 +3734,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -36865,7 +36846,7 @@
         <v>1</v>
       </c>
       <c r="I1163">
-        <v>3000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="1164" spans="1:9">
@@ -36891,7 +36872,7 @@
         <v>1</v>
       </c>
       <c r="I1164">
-        <v>6000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1165" spans="1:9">
@@ -37516,7 +37497,7 @@
         <v>1</v>
       </c>
       <c r="I1188">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1189" spans="1:9">
@@ -37568,7 +37549,7 @@
         <v>2</v>
       </c>
       <c r="I1190">
-        <v>11500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1191" spans="1:9">
@@ -37620,7 +37601,7 @@
         <v>2</v>
       </c>
       <c r="I1192">
-        <v>11500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1193" spans="1:9">
@@ -37647,7 +37628,7 @@
         <v>1</v>
       </c>
       <c r="I1193">
-        <v>6000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1194" spans="1:9">
@@ -38281,7 +38262,7 @@
         <v>1</v>
       </c>
       <c r="I1217">
-        <v>500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1218" spans="1:9">
@@ -38437,7 +38418,7 @@
         <v>2</v>
       </c>
       <c r="I1223">
-        <v>2500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1224" spans="1:9">
@@ -38489,7 +38470,7 @@
         <v>2</v>
       </c>
       <c r="I1225">
-        <v>2500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1226" spans="1:9">
@@ -38724,7 +38705,7 @@
         <v>2</v>
       </c>
       <c r="I1234">
-        <v>5000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="1235" spans="1:9">
@@ -38776,7 +38757,7 @@
         <v>2</v>
       </c>
       <c r="I1236">
-        <v>5000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="1237" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -36846,7 +36846,7 @@
         <v>1</v>
       </c>
       <c r="I1163">
-        <v>7500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1164" spans="1:9">
@@ -36872,7 +36872,7 @@
         <v>1</v>
       </c>
       <c r="I1164">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1165" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3216,12 +3216,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -38838,7 +38838,7 @@
         <v>1</v>
       </c>
       <c r="I1239">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1240" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3216,12 +3216,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -37549,7 +37549,7 @@
         <v>2</v>
       </c>
       <c r="I1190">
-        <v>8000</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="1191" spans="1:9">
@@ -37601,7 +37601,7 @@
         <v>2</v>
       </c>
       <c r="I1192">
-        <v>8000</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="1193" spans="1:9">
@@ -37628,7 +37628,7 @@
         <v>1</v>
       </c>
       <c r="I1193">
-        <v>4000</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="1194" spans="1:9">
@@ -38705,7 +38705,7 @@
         <v>2</v>
       </c>
       <c r="I1234">
-        <v>4500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="1235" spans="1:9">
@@ -38757,7 +38757,7 @@
         <v>2</v>
       </c>
       <c r="I1236">
-        <v>4500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="1237" spans="1:9">
@@ -38865,7 +38865,7 @@
         <v>2</v>
       </c>
       <c r="I1240">
-        <v>3500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1241" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -38653,7 +38653,7 @@
         <v>1</v>
       </c>
       <c r="I1232">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1233" spans="1:9">
@@ -38705,7 +38705,7 @@
         <v>2</v>
       </c>
       <c r="I1234">
-        <v>5500</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="1235" spans="1:9">
@@ -38757,7 +38757,7 @@
         <v>2</v>
       </c>
       <c r="I1236">
-        <v>5500</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="1237" spans="1:9">
@@ -38784,7 +38784,7 @@
         <v>1</v>
       </c>
       <c r="I1237">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1238" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -7097,7 +7097,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -38051,7 +38051,7 @@
         <v>2</v>
       </c>
       <c r="I1209">
-        <v>5500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1210" spans="1:9">
@@ -38103,7 +38103,7 @@
         <v>2</v>
       </c>
       <c r="I1211">
-        <v>5500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1212" spans="1:9">
@@ -38314,7 +38314,7 @@
         <v>1</v>
       </c>
       <c r="I1219">
-        <v>2000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="1220" spans="1:9">
@@ -38340,7 +38340,7 @@
         <v>1</v>
       </c>
       <c r="I1220">
-        <v>2000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="1221" spans="1:9">
@@ -38418,7 +38418,7 @@
         <v>2</v>
       </c>
       <c r="I1223">
-        <v>6000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="1224" spans="1:9">
@@ -38470,7 +38470,7 @@
         <v>2</v>
       </c>
       <c r="I1225">
-        <v>6000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="1226" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -38705,7 +38705,7 @@
         <v>2</v>
       </c>
       <c r="I1234">
-        <v>3600</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1235" spans="1:9">
@@ -38757,7 +38757,7 @@
         <v>2</v>
       </c>
       <c r="I1236">
-        <v>3600</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1237" spans="1:9">
@@ -38811,7 +38811,7 @@
         <v>1</v>
       </c>
       <c r="I1238">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1239" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -38705,7 +38705,7 @@
         <v>2</v>
       </c>
       <c r="I1234">
-        <v>3000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="1235" spans="1:9">
@@ -38757,7 +38757,7 @@
         <v>2</v>
       </c>
       <c r="I1236">
-        <v>3000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="1237" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -38418,7 +38418,7 @@
         <v>2</v>
       </c>
       <c r="I1223">
-        <v>5500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1224" spans="1:9">
@@ -38470,7 +38470,7 @@
         <v>2</v>
       </c>
       <c r="I1225">
-        <v>5500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1226" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -37159,7 +37159,7 @@
         <v>1</v>
       </c>
       <c r="I1175">
-        <v>3500</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="1176" spans="1:9">
@@ -37185,7 +37185,7 @@
         <v>1</v>
       </c>
       <c r="I1176">
-        <v>3500</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="1177" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -38314,7 +38314,7 @@
         <v>1</v>
       </c>
       <c r="I1219">
-        <v>2400</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1220" spans="1:9">
@@ -38340,7 +38340,7 @@
         <v>1</v>
       </c>
       <c r="I1220">
-        <v>2400</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1221" spans="1:9">
@@ -38497,7 +38497,7 @@
         <v>1</v>
       </c>
       <c r="I1226">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1227" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AB97A4-6186-4212-A223-F81C4ECD8FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8A9185-A24C-4ED7-B812-3ECE97468E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3509" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3539" uniqueCount="947">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2963,6 +2963,49 @@
   </si>
   <si>
     <t>暴风雪_弹道数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰球_获得</t>
+  </si>
+  <si>
+    <t>冰球_冷却</t>
+  </si>
+  <si>
+    <t>冰球_最近释放距离</t>
+  </si>
+  <si>
+    <t>冰球_最远释放距离</t>
+  </si>
+  <si>
+    <t>冰球_技能效果半径</t>
+  </si>
+  <si>
+    <t>冰球_目标数量</t>
+  </si>
+  <si>
+    <t>冰球_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>冰球_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>冰球_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>冰球_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>冰球_技能持续时间</t>
+  </si>
+  <si>
+    <t>冰球_技能伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>冰球_弹道数量</t>
+  </si>
+  <si>
+    <t>冰球概率附加冰冻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3664,7 +3707,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1286"/>
+  <dimension ref="A1:I1301"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -39150,7 +39193,7 @@
     </row>
     <row r="1270" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1270" s="26">
-        <v>5001800</v>
+        <v>5001511</v>
       </c>
       <c r="B1270" s="26">
         <v>1</v>
@@ -39159,16 +39202,17 @@
         <v>0</v>
       </c>
       <c r="D1270" s="26" t="s">
-        <v>877</v>
-      </c>
-      <c r="E1270" s="26" t="s">
-        <v>242</v>
-      </c>
+        <v>946</v>
+      </c>
+      <c r="E1270" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="F1270" s="9"/>
       <c r="G1270" s="26">
         <v>10</v>
       </c>
       <c r="H1270" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1270">
         <v>0</v>
@@ -39176,7 +39220,7 @@
     </row>
     <row r="1271" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1271" s="26">
-        <v>5001701</v>
+        <v>5001512</v>
       </c>
       <c r="B1271" s="26">
         <v>1</v>
@@ -39185,16 +39229,17 @@
         <v>0</v>
       </c>
       <c r="D1271" s="26" t="s">
-        <v>877</v>
+        <v>946</v>
       </c>
       <c r="E1271" s="19" t="s">
-        <v>878</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="F1271" s="9"/>
       <c r="G1271" s="26">
         <v>10</v>
       </c>
       <c r="H1271" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1271">
         <v>0</v>
@@ -39202,7 +39247,7 @@
     </row>
     <row r="1272" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1272" s="26">
-        <v>5001702</v>
+        <v>5001800</v>
       </c>
       <c r="B1272" s="26">
         <v>1</v>
@@ -39213,14 +39258,14 @@
       <c r="D1272" s="26" t="s">
         <v>877</v>
       </c>
-      <c r="E1272" s="19" t="s">
-        <v>879</v>
+      <c r="E1272" s="26" t="s">
+        <v>242</v>
       </c>
       <c r="G1272" s="26">
         <v>10</v>
       </c>
       <c r="H1272" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1272">
         <v>0</v>
@@ -39228,7 +39273,7 @@
     </row>
     <row r="1273" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1273" s="26">
-        <v>5001705</v>
+        <v>5001701</v>
       </c>
       <c r="B1273" s="26">
         <v>1</v>
@@ -39240,13 +39285,13 @@
         <v>877</v>
       </c>
       <c r="E1273" s="19" t="s">
-        <v>326</v>
+        <v>878</v>
       </c>
       <c r="G1273" s="26">
         <v>10</v>
       </c>
       <c r="H1273" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1273">
         <v>0</v>
@@ -39254,7 +39299,7 @@
     </row>
     <row r="1274" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1274" s="26">
-        <v>5001706</v>
+        <v>5001702</v>
       </c>
       <c r="B1274" s="26">
         <v>1</v>
@@ -39266,65 +39311,65 @@
         <v>877</v>
       </c>
       <c r="E1274" s="19" t="s">
+        <v>879</v>
+      </c>
+      <c r="G1274" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1274" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1275" s="26">
+        <v>5001705</v>
+      </c>
+      <c r="B1275" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1275" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1275" s="26" t="s">
+        <v>877</v>
+      </c>
+      <c r="E1275" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="G1275" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1275" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1276" s="26">
+        <v>5001706</v>
+      </c>
+      <c r="B1276" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1276" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1276" s="26" t="s">
+        <v>877</v>
+      </c>
+      <c r="E1276" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="G1274" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1274" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1274">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1275" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1275">
-        <v>920071</v>
-      </c>
-      <c r="B1275" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1275">
-        <v>0</v>
-      </c>
-      <c r="D1275" s="28" t="s">
-        <v>880</v>
-      </c>
-      <c r="E1275" s="29" t="s">
-        <v>766</v>
-      </c>
-      <c r="G1275">
-        <v>10</v>
-      </c>
-      <c r="H1275">
-        <v>1</v>
-      </c>
-      <c r="I1275">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1276" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1276">
-        <v>1920071</v>
-      </c>
-      <c r="B1276" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1276">
-        <v>0</v>
-      </c>
-      <c r="D1276" s="28" t="s">
-        <v>881</v>
-      </c>
-      <c r="E1276" s="29" t="s">
-        <v>768</v>
-      </c>
-      <c r="G1276">
-        <v>10</v>
-      </c>
-      <c r="H1276">
-        <v>1</v>
+      <c r="G1276" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1276" s="26">
+        <v>2</v>
       </c>
       <c r="I1276">
         <v>0</v>
@@ -39332,7 +39377,7 @@
     </row>
     <row r="1277" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1277">
-        <v>2920071</v>
+        <v>920071</v>
       </c>
       <c r="B1277" s="26">
         <v>1</v>
@@ -39341,10 +39386,10 @@
         <v>0</v>
       </c>
       <c r="D1277" s="28" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="E1277" s="29" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="G1277">
         <v>10</v>
@@ -39353,12 +39398,12 @@
         <v>1</v>
       </c>
       <c r="I1277">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1278" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1278">
-        <v>3920071</v>
+        <v>1920071</v>
       </c>
       <c r="B1278" s="26">
         <v>1</v>
@@ -39367,7 +39412,7 @@
         <v>0</v>
       </c>
       <c r="D1278" s="28" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E1278" s="29" t="s">
         <v>768</v>
@@ -39379,12 +39424,12 @@
         <v>1</v>
       </c>
       <c r="I1278">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1279" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1279">
-        <v>4920071</v>
+        <v>2920071</v>
       </c>
       <c r="B1279" s="26">
         <v>1</v>
@@ -39393,7 +39438,7 @@
         <v>0</v>
       </c>
       <c r="D1279" s="28" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="E1279" s="29" t="s">
         <v>768</v>
@@ -39405,12 +39450,12 @@
         <v>1</v>
       </c>
       <c r="I1279">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1280" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1280">
-        <v>5920071</v>
+        <v>3920071</v>
       </c>
       <c r="B1280" s="26">
         <v>1</v>
@@ -39419,7 +39464,7 @@
         <v>0</v>
       </c>
       <c r="D1280" s="28" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E1280" s="29" t="s">
         <v>768</v>
@@ -39431,12 +39476,12 @@
         <v>1</v>
       </c>
       <c r="I1280">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1281" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1281">
-        <v>6920071</v>
+        <v>4920071</v>
       </c>
       <c r="B1281" s="26">
         <v>1</v>
@@ -39445,7 +39490,7 @@
         <v>0</v>
       </c>
       <c r="D1281" s="28" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E1281" s="29" t="s">
         <v>768</v>
@@ -39457,12 +39502,12 @@
         <v>1</v>
       </c>
       <c r="I1281">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1282" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1282">
-        <v>7920071</v>
+        <v>5920071</v>
       </c>
       <c r="B1282" s="26">
         <v>1</v>
@@ -39471,7 +39516,7 @@
         <v>0</v>
       </c>
       <c r="D1282" s="28" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E1282" s="29" t="s">
         <v>768</v>
@@ -39480,15 +39525,15 @@
         <v>10</v>
       </c>
       <c r="H1282">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1282">
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1283" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1283">
-        <v>8920071</v>
+        <v>6920071</v>
       </c>
       <c r="B1283" s="26">
         <v>1</v>
@@ -39497,7 +39542,7 @@
         <v>0</v>
       </c>
       <c r="D1283" s="28" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="E1283" s="29" t="s">
         <v>768</v>
@@ -39514,7 +39559,7 @@
     </row>
     <row r="1284" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1284">
-        <v>9920071</v>
+        <v>7920071</v>
       </c>
       <c r="B1284" s="26">
         <v>1</v>
@@ -39523,7 +39568,7 @@
         <v>0</v>
       </c>
       <c r="D1284" s="28" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="E1284" s="29" t="s">
         <v>768</v>
@@ -39540,7 +39585,7 @@
     </row>
     <row r="1285" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1285">
-        <v>920072</v>
+        <v>8920071</v>
       </c>
       <c r="B1285" s="26">
         <v>1</v>
@@ -39549,12 +39594,11 @@
         <v>0</v>
       </c>
       <c r="D1285" s="28" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E1285" s="29" t="s">
-        <v>766</v>
-      </c>
-      <c r="F1285" s="28"/>
+        <v>768</v>
+      </c>
       <c r="G1285">
         <v>10</v>
       </c>
@@ -39567,28 +39611,422 @@
     </row>
     <row r="1286" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1286">
+        <v>9920071</v>
+      </c>
+      <c r="B1286" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1286">
+        <v>0</v>
+      </c>
+      <c r="D1286" s="28" t="s">
+        <v>889</v>
+      </c>
+      <c r="E1286" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1286">
+        <v>10</v>
+      </c>
+      <c r="H1286">
+        <v>2</v>
+      </c>
+      <c r="I1286">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1287">
+        <v>920072</v>
+      </c>
+      <c r="B1287" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1287">
+        <v>0</v>
+      </c>
+      <c r="D1287" s="28" t="s">
+        <v>890</v>
+      </c>
+      <c r="E1287" s="29" t="s">
+        <v>766</v>
+      </c>
+      <c r="F1287" s="28"/>
+      <c r="G1287">
+        <v>10</v>
+      </c>
+      <c r="H1287">
+        <v>1</v>
+      </c>
+      <c r="I1287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1288">
         <v>820072</v>
       </c>
-      <c r="B1286" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1286">
-        <v>0</v>
-      </c>
-      <c r="D1286" s="30" t="s">
+      <c r="B1288" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1288">
+        <v>0</v>
+      </c>
+      <c r="D1288" s="30" t="s">
         <v>891</v>
       </c>
-      <c r="E1286" s="30" t="s">
+      <c r="E1288" s="30" t="s">
         <v>891</v>
       </c>
-      <c r="G1286">
-        <v>10</v>
-      </c>
-      <c r="H1286">
-        <v>1</v>
-      </c>
-      <c r="I1286">
-        <v>0</v>
+      <c r="G1288">
+        <v>10</v>
+      </c>
+      <c r="H1288">
+        <v>1</v>
+      </c>
+      <c r="I1288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1289">
+        <v>920081</v>
+      </c>
+      <c r="B1289" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1289">
+        <v>0</v>
+      </c>
+      <c r="D1289" s="28" t="s">
+        <v>933</v>
+      </c>
+      <c r="E1289" s="29" t="s">
+        <v>766</v>
+      </c>
+      <c r="G1289">
+        <v>10</v>
+      </c>
+      <c r="H1289">
+        <v>1</v>
+      </c>
+      <c r="I1289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1290">
+        <v>1920081</v>
+      </c>
+      <c r="B1290" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1290">
+        <v>0</v>
+      </c>
+      <c r="D1290" s="28" t="s">
+        <v>934</v>
+      </c>
+      <c r="E1290" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1290">
+        <v>10</v>
+      </c>
+      <c r="H1290">
+        <v>1</v>
+      </c>
+      <c r="I1290">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1291">
+        <v>2920081</v>
+      </c>
+      <c r="B1291" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1291">
+        <v>0</v>
+      </c>
+      <c r="D1291" s="28" t="s">
+        <v>935</v>
+      </c>
+      <c r="E1291" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1291">
+        <v>10</v>
+      </c>
+      <c r="H1291">
+        <v>1</v>
+      </c>
+      <c r="I1291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1292">
+        <v>3920081</v>
+      </c>
+      <c r="B1292" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1292">
+        <v>0</v>
+      </c>
+      <c r="D1292" s="28" t="s">
+        <v>936</v>
+      </c>
+      <c r="E1292" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1292">
+        <v>10</v>
+      </c>
+      <c r="H1292">
+        <v>1</v>
+      </c>
+      <c r="I1292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1293">
+        <v>4920081</v>
+      </c>
+      <c r="B1293" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1293">
+        <v>0</v>
+      </c>
+      <c r="D1293" s="28" t="s">
+        <v>937</v>
+      </c>
+      <c r="E1293" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1293">
+        <v>10</v>
+      </c>
+      <c r="H1293">
+        <v>1</v>
+      </c>
+      <c r="I1293">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1294">
+        <v>5920081</v>
+      </c>
+      <c r="B1294" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1294">
+        <v>0</v>
+      </c>
+      <c r="D1294" s="28" t="s">
+        <v>938</v>
+      </c>
+      <c r="E1294" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1294">
+        <v>10</v>
+      </c>
+      <c r="H1294">
+        <v>1</v>
+      </c>
+      <c r="I1294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1295">
+        <v>6920081</v>
+      </c>
+      <c r="B1295" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1295">
+        <v>0</v>
+      </c>
+      <c r="D1295" s="28" t="s">
+        <v>939</v>
+      </c>
+      <c r="E1295" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1295">
+        <v>10</v>
+      </c>
+      <c r="H1295">
+        <v>1</v>
+      </c>
+      <c r="I1295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1296">
+        <v>7920081</v>
+      </c>
+      <c r="B1296" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1296">
+        <v>0</v>
+      </c>
+      <c r="D1296" s="28" t="s">
+        <v>940</v>
+      </c>
+      <c r="E1296" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1296">
+        <v>10</v>
+      </c>
+      <c r="H1296">
+        <v>2</v>
+      </c>
+      <c r="I1296">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1297">
+        <v>8920081</v>
+      </c>
+      <c r="B1297" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1297">
+        <v>0</v>
+      </c>
+      <c r="D1297" s="28" t="s">
+        <v>941</v>
+      </c>
+      <c r="E1297" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1297">
+        <v>10</v>
+      </c>
+      <c r="H1297">
+        <v>1</v>
+      </c>
+      <c r="I1297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1298">
+        <v>9920081</v>
+      </c>
+      <c r="B1298" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1298">
+        <v>0</v>
+      </c>
+      <c r="D1298" s="28" t="s">
+        <v>942</v>
+      </c>
+      <c r="E1298" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1298">
+        <v>10</v>
+      </c>
+      <c r="H1298">
+        <v>2</v>
+      </c>
+      <c r="I1298">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1299">
+        <v>10920081</v>
+      </c>
+      <c r="B1299" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1299">
+        <v>0</v>
+      </c>
+      <c r="D1299" s="28" t="s">
+        <v>943</v>
+      </c>
+      <c r="E1299" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="F1299" s="28"/>
+      <c r="G1299">
+        <v>10</v>
+      </c>
+      <c r="H1299">
+        <v>1</v>
+      </c>
+      <c r="I1299">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1300">
+        <v>11920081</v>
+      </c>
+      <c r="B1300" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1300">
+        <v>0</v>
+      </c>
+      <c r="D1300" s="28" t="s">
+        <v>944</v>
+      </c>
+      <c r="E1300" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="F1300" s="28"/>
+      <c r="G1300">
+        <v>10</v>
+      </c>
+      <c r="H1300">
+        <v>1</v>
+      </c>
+      <c r="I1300">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1301">
+        <v>14920081</v>
+      </c>
+      <c r="B1301" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1301">
+        <v>0</v>
+      </c>
+      <c r="D1301" s="28" t="s">
+        <v>945</v>
+      </c>
+      <c r="E1301" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="F1301" s="28"/>
+      <c r="G1301">
+        <v>10</v>
+      </c>
+      <c r="H1301">
+        <v>1</v>
+      </c>
+      <c r="I1301">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C741E0C-FD15-47D4-8BBF-C97F7DCA5860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D926BBE8-ECF5-45CD-AD4D-89F5F5E1666D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3550" uniqueCount="954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3624" uniqueCount="989">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2975,9 +2975,6 @@
     <t>冰球_最远释放距离</t>
   </si>
   <si>
-    <t>冰球_技能效果半径</t>
-  </si>
-  <si>
     <t>冰球_目标数量</t>
   </si>
   <si>
@@ -2991,9 +2988,6 @@
   </si>
   <si>
     <t>冰球_非主目标直接伤害系数</t>
-  </si>
-  <si>
-    <t>冰球_技能持续时间</t>
   </si>
   <si>
     <t>冰球_技能伤害或效果生效间隔</t>
@@ -3035,6 +3029,133 @@
   </si>
   <si>
     <t>极寒领域被动-唤冰球-逻辑id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级暴风雪_获得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级暴风雪_弹道数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰风暴被动_获得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰风暴被动-逻辑id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰球_技能效果半径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级暴风雪_技能效果半径倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰球_技能持续时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级暴风雪_技能持续时间倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级暴风雪_伤害倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雪概率附加减速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰刃概率附加减速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碎冰_获得</t>
+  </si>
+  <si>
+    <t>碎冰_冷却</t>
+  </si>
+  <si>
+    <t>碎冰_最近释放距离</t>
+  </si>
+  <si>
+    <t>碎冰_最远释放距离</t>
+  </si>
+  <si>
+    <t>碎冰_技能效果半径</t>
+  </si>
+  <si>
+    <t>碎冰_目标数量</t>
+  </si>
+  <si>
+    <t>碎冰_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>碎冰_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>碎冰_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>碎冰_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>碎冰_释放角度</t>
+  </si>
+  <si>
+    <t>冰雪领域_获得</t>
+  </si>
+  <si>
+    <t>冰雪领域_冷却</t>
+  </si>
+  <si>
+    <t>冰雪领域_最近释放距离</t>
+  </si>
+  <si>
+    <t>冰雪领域_最远释放距离</t>
+  </si>
+  <si>
+    <t>冰雪领域_技能效果半径</t>
+  </si>
+  <si>
+    <t>冰雪领域_目标数量</t>
+  </si>
+  <si>
+    <t>冰雪领域_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>冰雪领域_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>冰雪领域_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>冰雪领域_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>冰雪领域概率附加冰冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰雪领域被动_获得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰雪领域被动-逻辑id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰雪领域被动-参数1-释放技能概率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰雪领域被动-概率释放技能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3739,7 +3860,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1306"/>
+  <dimension ref="A1:I1343"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -6144,10 +6265,10 @@
         <v>0</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>62</v>
@@ -37898,7 +38019,7 @@
         <v>1</v>
       </c>
       <c r="I1219">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1220" spans="1:9" x14ac:dyDescent="0.15">
@@ -39236,7 +39357,7 @@
         <v>0</v>
       </c>
       <c r="D1270" s="26" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="E1270" s="19" t="s">
         <v>327</v>
@@ -39263,7 +39384,7 @@
         <v>0</v>
       </c>
       <c r="D1271" s="26" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="E1271" s="19" t="s">
         <v>325</v>
@@ -39281,7 +39402,7 @@
     </row>
     <row r="1272" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1272" s="26">
-        <v>5001800</v>
+        <v>5001521</v>
       </c>
       <c r="B1272" s="26">
         <v>1</v>
@@ -39290,16 +39411,17 @@
         <v>0</v>
       </c>
       <c r="D1272" s="26" t="s">
-        <v>876</v>
-      </c>
-      <c r="E1272" s="26" t="s">
-        <v>241</v>
-      </c>
+        <v>984</v>
+      </c>
+      <c r="E1272" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1272" s="9"/>
       <c r="G1272" s="26">
         <v>10</v>
       </c>
       <c r="H1272" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1272">
         <v>0</v>
@@ -39307,7 +39429,7 @@
     </row>
     <row r="1273" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1273" s="26">
-        <v>5001701</v>
+        <v>5001522</v>
       </c>
       <c r="B1273" s="26">
         <v>1</v>
@@ -39316,16 +39438,17 @@
         <v>0</v>
       </c>
       <c r="D1273" s="26" t="s">
-        <v>876</v>
+        <v>984</v>
       </c>
       <c r="E1273" s="19" t="s">
-        <v>877</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="F1273" s="9"/>
       <c r="G1273" s="26">
         <v>10</v>
       </c>
       <c r="H1273" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1273">
         <v>0</v>
@@ -39333,7 +39456,7 @@
     </row>
     <row r="1274" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1274" s="26">
-        <v>5001702</v>
+        <v>5001800</v>
       </c>
       <c r="B1274" s="26">
         <v>1</v>
@@ -39344,14 +39467,14 @@
       <c r="D1274" s="26" t="s">
         <v>876</v>
       </c>
-      <c r="E1274" s="19" t="s">
-        <v>878</v>
+      <c r="E1274" s="26" t="s">
+        <v>241</v>
       </c>
       <c r="G1274" s="26">
         <v>10</v>
       </c>
       <c r="H1274" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1274">
         <v>0</v>
@@ -39359,7 +39482,7 @@
     </row>
     <row r="1275" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1275" s="26">
-        <v>5001705</v>
+        <v>5001701</v>
       </c>
       <c r="B1275" s="26">
         <v>1</v>
@@ -39368,16 +39491,16 @@
         <v>0</v>
       </c>
       <c r="D1275" s="26" t="s">
-        <v>876</v>
+        <v>961</v>
       </c>
       <c r="E1275" s="19" t="s">
-        <v>325</v>
+        <v>877</v>
       </c>
       <c r="G1275" s="26">
         <v>10</v>
       </c>
       <c r="H1275" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1275">
         <v>0</v>
@@ -39385,7 +39508,7 @@
     </row>
     <row r="1276" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1276" s="26">
-        <v>5001706</v>
+        <v>5001702</v>
       </c>
       <c r="B1276" s="26">
         <v>1</v>
@@ -39394,10 +39517,10 @@
         <v>0</v>
       </c>
       <c r="D1276" s="26" t="s">
-        <v>876</v>
+        <v>961</v>
       </c>
       <c r="E1276" s="19" t="s">
-        <v>327</v>
+        <v>878</v>
       </c>
       <c r="G1276" s="26">
         <v>10</v>
@@ -39410,156 +39533,156 @@
       </c>
     </row>
     <row r="1277" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1277">
-        <v>920071</v>
+      <c r="A1277" s="26">
+        <v>5001705</v>
       </c>
       <c r="B1277" s="26">
         <v>1</v>
       </c>
-      <c r="C1277">
-        <v>0</v>
-      </c>
-      <c r="D1277" s="28" t="s">
-        <v>879</v>
-      </c>
-      <c r="E1277" s="29" t="s">
-        <v>765</v>
-      </c>
-      <c r="G1277">
-        <v>10</v>
-      </c>
-      <c r="H1277">
+      <c r="C1277" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1277" s="26" t="s">
+        <v>961</v>
+      </c>
+      <c r="E1277" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1277" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1277" s="26">
         <v>1</v>
       </c>
       <c r="I1277">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1278" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1278">
-        <v>1920071</v>
+      <c r="A1278" s="26">
+        <v>5001706</v>
       </c>
       <c r="B1278" s="26">
         <v>1</v>
       </c>
-      <c r="C1278">
-        <v>0</v>
-      </c>
-      <c r="D1278" s="28" t="s">
-        <v>880</v>
-      </c>
-      <c r="E1278" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1278">
-        <v>10</v>
-      </c>
-      <c r="H1278">
-        <v>1</v>
+      <c r="C1278" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1278" s="26" t="s">
+        <v>961</v>
+      </c>
+      <c r="E1278" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1278" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1278" s="26">
+        <v>2</v>
       </c>
       <c r="I1278">
         <v>0</v>
       </c>
     </row>
     <row r="1279" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1279">
-        <v>2920071</v>
+      <c r="A1279" s="26">
+        <v>5001711</v>
       </c>
       <c r="B1279" s="26">
         <v>1</v>
       </c>
-      <c r="C1279">
-        <v>0</v>
-      </c>
-      <c r="D1279" s="28" t="s">
-        <v>881</v>
-      </c>
-      <c r="E1279" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1279">
-        <v>10</v>
-      </c>
-      <c r="H1279">
-        <v>1</v>
+      <c r="C1279" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1279" s="26" t="s">
+        <v>962</v>
+      </c>
+      <c r="E1279" s="19" t="s">
+        <v>877</v>
+      </c>
+      <c r="G1279" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1279" s="26">
+        <v>2</v>
       </c>
       <c r="I1279">
         <v>0</v>
       </c>
     </row>
     <row r="1280" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1280">
-        <v>3920071</v>
+      <c r="A1280" s="26">
+        <v>5001712</v>
       </c>
       <c r="B1280" s="26">
         <v>1</v>
       </c>
-      <c r="C1280">
-        <v>0</v>
-      </c>
-      <c r="D1280" s="28" t="s">
-        <v>882</v>
-      </c>
-      <c r="E1280" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1280">
-        <v>10</v>
-      </c>
-      <c r="H1280">
-        <v>1</v>
+      <c r="C1280" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1280" s="26" t="s">
+        <v>962</v>
+      </c>
+      <c r="E1280" s="19" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1280" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1280" s="26">
+        <v>2</v>
       </c>
       <c r="I1280">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1281" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1281">
-        <v>4920071</v>
+      <c r="A1281" s="26">
+        <v>5001715</v>
       </c>
       <c r="B1281" s="26">
         <v>1</v>
       </c>
-      <c r="C1281">
-        <v>0</v>
-      </c>
-      <c r="D1281" s="28" t="s">
-        <v>883</v>
-      </c>
-      <c r="E1281" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1281">
-        <v>10</v>
-      </c>
-      <c r="H1281">
+      <c r="C1281" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1281" s="26" t="s">
+        <v>962</v>
+      </c>
+      <c r="E1281" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1281" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1281" s="26">
         <v>1</v>
       </c>
       <c r="I1281">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1282" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1282">
-        <v>5920071</v>
+      <c r="A1282" s="26">
+        <v>5001716</v>
       </c>
       <c r="B1282" s="26">
         <v>1</v>
       </c>
-      <c r="C1282">
-        <v>0</v>
-      </c>
-      <c r="D1282" s="28" t="s">
-        <v>884</v>
-      </c>
-      <c r="E1282" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1282">
-        <v>10</v>
-      </c>
-      <c r="H1282">
-        <v>1</v>
+      <c r="C1282" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1282" s="26" t="s">
+        <v>962</v>
+      </c>
+      <c r="E1282" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1282" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1282" s="26">
+        <v>2</v>
       </c>
       <c r="I1282">
         <v>0</v>
@@ -39567,7 +39690,7 @@
     </row>
     <row r="1283" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1283">
-        <v>6920071</v>
+        <v>920071</v>
       </c>
       <c r="B1283" s="26">
         <v>1</v>
@@ -39576,10 +39699,10 @@
         <v>0</v>
       </c>
       <c r="D1283" s="28" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="E1283" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G1283">
         <v>10</v>
@@ -39588,12 +39711,12 @@
         <v>1</v>
       </c>
       <c r="I1283">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1284" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1284">
-        <v>7920071</v>
+        <v>1920071</v>
       </c>
       <c r="B1284" s="26">
         <v>1</v>
@@ -39602,7 +39725,7 @@
         <v>0</v>
       </c>
       <c r="D1284" s="28" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="E1284" s="29" t="s">
         <v>767</v>
@@ -39611,15 +39734,15 @@
         <v>10</v>
       </c>
       <c r="H1284">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1284">
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1285" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1285">
-        <v>8920071</v>
+        <v>2920071</v>
       </c>
       <c r="B1285" s="26">
         <v>1</v>
@@ -39628,7 +39751,7 @@
         <v>0</v>
       </c>
       <c r="D1285" s="28" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="E1285" s="29" t="s">
         <v>767</v>
@@ -39645,7 +39768,7 @@
     </row>
     <row r="1286" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1286">
-        <v>9920071</v>
+        <v>3920071</v>
       </c>
       <c r="B1286" s="26">
         <v>1</v>
@@ -39654,7 +39777,7 @@
         <v>0</v>
       </c>
       <c r="D1286" s="28" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="E1286" s="29" t="s">
         <v>767</v>
@@ -39663,15 +39786,15 @@
         <v>10</v>
       </c>
       <c r="H1286">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1286">
-        <v>12000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1287" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1287">
-        <v>920072</v>
+        <v>4920071</v>
       </c>
       <c r="B1287" s="26">
         <v>1</v>
@@ -39680,12 +39803,11 @@
         <v>0</v>
       </c>
       <c r="D1287" s="28" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="E1287" s="29" t="s">
-        <v>765</v>
-      </c>
-      <c r="F1287" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1287">
         <v>10</v>
       </c>
@@ -39693,12 +39815,12 @@
         <v>1</v>
       </c>
       <c r="I1287">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1288" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1288">
-        <v>820072</v>
+        <v>5920071</v>
       </c>
       <c r="B1288" s="26">
         <v>1</v>
@@ -39706,11 +39828,11 @@
       <c r="C1288">
         <v>0</v>
       </c>
-      <c r="D1288" s="30" t="s">
-        <v>890</v>
-      </c>
-      <c r="E1288" s="30" t="s">
-        <v>890</v>
+      <c r="D1288" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="E1288" s="29" t="s">
+        <v>767</v>
       </c>
       <c r="G1288">
         <v>10</v>
@@ -39724,7 +39846,7 @@
     </row>
     <row r="1289" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1289">
-        <v>920081</v>
+        <v>6920071</v>
       </c>
       <c r="B1289" s="26">
         <v>1</v>
@@ -39733,10 +39855,10 @@
         <v>0</v>
       </c>
       <c r="D1289" s="28" t="s">
-        <v>932</v>
+        <v>885</v>
       </c>
       <c r="E1289" s="29" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="G1289">
         <v>10</v>
@@ -39750,7 +39872,7 @@
     </row>
     <row r="1290" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1290">
-        <v>1920081</v>
+        <v>7920071</v>
       </c>
       <c r="B1290" s="26">
         <v>1</v>
@@ -39759,7 +39881,7 @@
         <v>0</v>
       </c>
       <c r="D1290" s="28" t="s">
-        <v>933</v>
+        <v>886</v>
       </c>
       <c r="E1290" s="29" t="s">
         <v>767</v>
@@ -39768,15 +39890,15 @@
         <v>10</v>
       </c>
       <c r="H1290">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1290">
-        <v>8000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1291" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1291">
-        <v>2920081</v>
+        <v>8920071</v>
       </c>
       <c r="B1291" s="26">
         <v>1</v>
@@ -39785,7 +39907,7 @@
         <v>0</v>
       </c>
       <c r="D1291" s="28" t="s">
-        <v>934</v>
+        <v>887</v>
       </c>
       <c r="E1291" s="29" t="s">
         <v>767</v>
@@ -39802,7 +39924,7 @@
     </row>
     <row r="1292" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1292">
-        <v>3920081</v>
+        <v>9920071</v>
       </c>
       <c r="B1292" s="26">
         <v>1</v>
@@ -39811,7 +39933,7 @@
         <v>0</v>
       </c>
       <c r="D1292" s="28" t="s">
-        <v>935</v>
+        <v>888</v>
       </c>
       <c r="E1292" s="29" t="s">
         <v>767</v>
@@ -39820,15 +39942,15 @@
         <v>10</v>
       </c>
       <c r="H1292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1292">
-        <v>0</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1293" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1293">
-        <v>4920081</v>
+        <v>920072</v>
       </c>
       <c r="B1293" s="26">
         <v>1</v>
@@ -39837,11 +39959,12 @@
         <v>0</v>
       </c>
       <c r="D1293" s="28" t="s">
-        <v>936</v>
+        <v>889</v>
       </c>
       <c r="E1293" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>765</v>
+      </c>
+      <c r="F1293" s="28"/>
       <c r="G1293">
         <v>10</v>
       </c>
@@ -39849,12 +39972,12 @@
         <v>1</v>
       </c>
       <c r="I1293">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1294" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1294">
-        <v>5920081</v>
+        <v>820072</v>
       </c>
       <c r="B1294" s="26">
         <v>1</v>
@@ -39862,11 +39985,11 @@
       <c r="C1294">
         <v>0</v>
       </c>
-      <c r="D1294" s="28" t="s">
-        <v>937</v>
-      </c>
-      <c r="E1294" s="29" t="s">
-        <v>767</v>
+      <c r="D1294" s="30" t="s">
+        <v>890</v>
+      </c>
+      <c r="E1294" s="30" t="s">
+        <v>890</v>
       </c>
       <c r="G1294">
         <v>10</v>
@@ -39880,7 +40003,7 @@
     </row>
     <row r="1295" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1295">
-        <v>6920081</v>
+        <v>920081</v>
       </c>
       <c r="B1295" s="26">
         <v>1</v>
@@ -39889,10 +40012,10 @@
         <v>0</v>
       </c>
       <c r="D1295" s="28" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="E1295" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G1295">
         <v>10</v>
@@ -39906,7 +40029,7 @@
     </row>
     <row r="1296" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1296">
-        <v>7920081</v>
+        <v>1920081</v>
       </c>
       <c r="B1296" s="26">
         <v>1</v>
@@ -39915,7 +40038,7 @@
         <v>0</v>
       </c>
       <c r="D1296" s="28" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="E1296" s="29" t="s">
         <v>767</v>
@@ -39924,15 +40047,15 @@
         <v>10</v>
       </c>
       <c r="H1296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1296">
-        <v>12000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1297" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1297">
-        <v>8920081</v>
+        <v>2920081</v>
       </c>
       <c r="B1297" s="26">
         <v>1</v>
@@ -39941,7 +40064,7 @@
         <v>0</v>
       </c>
       <c r="D1297" s="28" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="E1297" s="29" t="s">
         <v>767</v>
@@ -39958,7 +40081,7 @@
     </row>
     <row r="1298" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1298">
-        <v>9920081</v>
+        <v>3920081</v>
       </c>
       <c r="B1298" s="26">
         <v>1</v>
@@ -39967,7 +40090,7 @@
         <v>0</v>
       </c>
       <c r="D1298" s="28" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="E1298" s="29" t="s">
         <v>767</v>
@@ -39976,15 +40099,15 @@
         <v>10</v>
       </c>
       <c r="H1298">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1298">
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1299" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1299">
-        <v>10920081</v>
+        <v>4920081</v>
       </c>
       <c r="B1299" s="26">
         <v>1</v>
@@ -39993,12 +40116,11 @@
         <v>0</v>
       </c>
       <c r="D1299" s="28" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
       <c r="E1299" s="29" t="s">
         <v>767</v>
       </c>
-      <c r="F1299" s="28"/>
       <c r="G1299">
         <v>10</v>
       </c>
@@ -40006,12 +40128,12 @@
         <v>1</v>
       </c>
       <c r="I1299">
-        <v>5000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1300" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1300">
-        <v>11920081</v>
+        <v>5920081</v>
       </c>
       <c r="B1300" s="26">
         <v>1</v>
@@ -40020,12 +40142,11 @@
         <v>0</v>
       </c>
       <c r="D1300" s="28" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="E1300" s="29" t="s">
         <v>767</v>
       </c>
-      <c r="F1300" s="28"/>
       <c r="G1300">
         <v>10</v>
       </c>
@@ -40033,12 +40154,12 @@
         <v>1</v>
       </c>
       <c r="I1300">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1301" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1301">
-        <v>14920081</v>
+        <v>6920081</v>
       </c>
       <c r="B1301" s="26">
         <v>1</v>
@@ -40047,12 +40168,11 @@
         <v>0</v>
       </c>
       <c r="D1301" s="28" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="E1301" s="29" t="s">
         <v>767</v>
       </c>
-      <c r="F1301" s="28"/>
       <c r="G1301">
         <v>10</v>
       </c>
@@ -40060,12 +40180,12 @@
         <v>1</v>
       </c>
       <c r="I1301">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1302" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1302">
-        <v>920083</v>
+        <v>7920081</v>
       </c>
       <c r="B1302" s="26">
         <v>1</v>
@@ -40074,24 +40194,24 @@
         <v>0</v>
       </c>
       <c r="D1302" s="28" t="s">
-        <v>948</v>
+        <v>938</v>
       </c>
       <c r="E1302" s="29" t="s">
-        <v>951</v>
+        <v>767</v>
       </c>
       <c r="G1302">
         <v>10</v>
       </c>
       <c r="H1302">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1302">
-        <v>1</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1303" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1303">
-        <v>14920083</v>
+        <v>8920081</v>
       </c>
       <c r="B1303" s="26">
         <v>1</v>
@@ -40100,12 +40220,11 @@
         <v>0</v>
       </c>
       <c r="D1303" s="28" t="s">
-        <v>950</v>
+        <v>939</v>
       </c>
       <c r="E1303" s="29" t="s">
         <v>767</v>
       </c>
-      <c r="F1303" s="28"/>
       <c r="G1303">
         <v>10</v>
       </c>
@@ -40113,85 +40232,1058 @@
         <v>1</v>
       </c>
       <c r="I1303">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1304" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1304" s="32">
+      <c r="A1304">
+        <v>9920081</v>
+      </c>
+      <c r="B1304" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1304">
+        <v>0</v>
+      </c>
+      <c r="D1304" s="28" t="s">
+        <v>940</v>
+      </c>
+      <c r="E1304" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1304">
+        <v>10</v>
+      </c>
+      <c r="H1304">
+        <v>2</v>
+      </c>
+      <c r="I1304">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1305">
+        <v>10920081</v>
+      </c>
+      <c r="B1305" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1305">
+        <v>0</v>
+      </c>
+      <c r="D1305" s="28" t="s">
+        <v>958</v>
+      </c>
+      <c r="E1305" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1305" s="28"/>
+      <c r="G1305">
+        <v>10</v>
+      </c>
+      <c r="H1305">
+        <v>1</v>
+      </c>
+      <c r="I1305">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1306">
+        <v>11920081</v>
+      </c>
+      <c r="B1306" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1306">
+        <v>0</v>
+      </c>
+      <c r="D1306" s="28" t="s">
+        <v>941</v>
+      </c>
+      <c r="E1306" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1306" s="28"/>
+      <c r="G1306">
+        <v>10</v>
+      </c>
+      <c r="H1306">
+        <v>1</v>
+      </c>
+      <c r="I1306">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1307">
+        <v>14920081</v>
+      </c>
+      <c r="B1307" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1307">
+        <v>0</v>
+      </c>
+      <c r="D1307" s="28" t="s">
+        <v>942</v>
+      </c>
+      <c r="E1307" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1307" s="28"/>
+      <c r="G1307">
+        <v>10</v>
+      </c>
+      <c r="H1307">
+        <v>1</v>
+      </c>
+      <c r="I1307">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1308">
+        <v>920083</v>
+      </c>
+      <c r="B1308" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1308">
+        <v>0</v>
+      </c>
+      <c r="D1308" s="28" t="s">
+        <v>946</v>
+      </c>
+      <c r="E1308" s="29" t="s">
+        <v>949</v>
+      </c>
+      <c r="G1308">
+        <v>10</v>
+      </c>
+      <c r="H1308">
+        <v>1</v>
+      </c>
+      <c r="I1308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1309">
+        <v>14920083</v>
+      </c>
+      <c r="B1309" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1309">
+        <v>0</v>
+      </c>
+      <c r="D1309" s="28" t="s">
+        <v>948</v>
+      </c>
+      <c r="E1309" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1309" s="28"/>
+      <c r="G1309">
+        <v>10</v>
+      </c>
+      <c r="H1309">
+        <v>1</v>
+      </c>
+      <c r="I1309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1310" s="32">
         <v>920082</v>
       </c>
-      <c r="B1304" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1304">
-        <v>0</v>
-      </c>
-      <c r="D1304" s="28" t="s">
-        <v>949</v>
-      </c>
-      <c r="E1304" s="29" t="s">
+      <c r="B1310" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1310">
+        <v>0</v>
+      </c>
+      <c r="D1310" s="28" t="s">
+        <v>947</v>
+      </c>
+      <c r="E1310" s="29" t="s">
         <v>765</v>
       </c>
-      <c r="F1304" s="28"/>
-      <c r="G1304">
-        <v>10</v>
-      </c>
-      <c r="H1304">
-        <v>1</v>
-      </c>
-      <c r="I1304">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1305" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1305" s="30">
+      <c r="F1310" s="28"/>
+      <c r="G1310">
+        <v>10</v>
+      </c>
+      <c r="H1310">
+        <v>1</v>
+      </c>
+      <c r="I1310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1311" s="30">
         <v>820082</v>
       </c>
-      <c r="B1305" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1305">
-        <v>0</v>
-      </c>
-      <c r="D1305" s="30" t="s">
+      <c r="B1311" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1311">
+        <v>0</v>
+      </c>
+      <c r="D1311" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="E1311" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="G1311">
+        <v>10</v>
+      </c>
+      <c r="H1311">
+        <v>1</v>
+      </c>
+      <c r="I1311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1312" s="30">
+        <v>820083</v>
+      </c>
+      <c r="B1312" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1312">
+        <v>0</v>
+      </c>
+      <c r="D1312" s="30" t="s">
+        <v>951</v>
+      </c>
+      <c r="E1312" s="30" t="s">
+        <v>951</v>
+      </c>
+      <c r="G1312">
+        <v>10</v>
+      </c>
+      <c r="H1312">
+        <v>1</v>
+      </c>
+      <c r="I1312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1313">
+        <v>920074</v>
+      </c>
+      <c r="B1313" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1313">
+        <v>0</v>
+      </c>
+      <c r="D1313" s="28" t="s">
         <v>952</v>
       </c>
-      <c r="E1305" s="30" t="s">
-        <v>952</v>
-      </c>
-      <c r="G1305">
-        <v>10</v>
-      </c>
-      <c r="H1305">
-        <v>1</v>
-      </c>
-      <c r="I1305">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1306" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1306" s="30">
-        <v>820083</v>
-      </c>
-      <c r="B1306" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1306">
-        <v>0</v>
-      </c>
-      <c r="D1306" s="30" t="s">
+      <c r="E1313" s="29" t="s">
+        <v>765</v>
+      </c>
+      <c r="G1313">
+        <v>10</v>
+      </c>
+      <c r="H1313">
+        <v>1</v>
+      </c>
+      <c r="I1313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1314">
+        <v>14920074</v>
+      </c>
+      <c r="B1314" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1314">
+        <v>0</v>
+      </c>
+      <c r="D1314" s="28" t="s">
         <v>953</v>
       </c>
-      <c r="E1306" s="30" t="s">
-        <v>953</v>
-      </c>
-      <c r="G1306">
-        <v>10</v>
-      </c>
-      <c r="H1306">
-        <v>1</v>
-      </c>
-      <c r="I1306">
+      <c r="E1314" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1314" s="28"/>
+      <c r="G1314">
+        <v>10</v>
+      </c>
+      <c r="H1314">
+        <v>1</v>
+      </c>
+      <c r="I1314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1315">
+        <v>16920074</v>
+      </c>
+      <c r="B1315" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1315">
+        <v>0</v>
+      </c>
+      <c r="D1315" s="28" t="s">
+        <v>957</v>
+      </c>
+      <c r="E1315" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1315" s="28"/>
+      <c r="G1315">
+        <v>10</v>
+      </c>
+      <c r="H1315">
+        <v>2</v>
+      </c>
+      <c r="I1315">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1316">
+        <v>17920074</v>
+      </c>
+      <c r="B1316" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1316">
+        <v>0</v>
+      </c>
+      <c r="D1316" s="28" t="s">
+        <v>959</v>
+      </c>
+      <c r="E1316" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1316" s="28"/>
+      <c r="G1316">
+        <v>10</v>
+      </c>
+      <c r="H1316">
+        <v>2</v>
+      </c>
+      <c r="I1316">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1317">
+        <v>18920074</v>
+      </c>
+      <c r="B1317" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1317">
+        <v>0</v>
+      </c>
+      <c r="D1317" s="28" t="s">
+        <v>960</v>
+      </c>
+      <c r="E1317" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1317" s="28"/>
+      <c r="G1317">
+        <v>10</v>
+      </c>
+      <c r="H1317">
+        <v>2</v>
+      </c>
+      <c r="I1317">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1318">
+        <v>920073</v>
+      </c>
+      <c r="B1318" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1318">
+        <v>0</v>
+      </c>
+      <c r="D1318" s="28" t="s">
+        <v>954</v>
+      </c>
+      <c r="E1318" s="29" t="s">
+        <v>765</v>
+      </c>
+      <c r="F1318" s="28"/>
+      <c r="G1318">
+        <v>10</v>
+      </c>
+      <c r="H1318">
+        <v>1</v>
+      </c>
+      <c r="I1318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1319">
+        <v>820073</v>
+      </c>
+      <c r="B1319" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1319">
+        <v>0</v>
+      </c>
+      <c r="D1319" s="30" t="s">
+        <v>955</v>
+      </c>
+      <c r="E1319" s="30" t="s">
+        <v>955</v>
+      </c>
+      <c r="G1319">
+        <v>10</v>
+      </c>
+      <c r="H1319">
+        <v>1</v>
+      </c>
+      <c r="I1319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1320">
+        <v>920084</v>
+      </c>
+      <c r="B1320" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1320">
+        <v>0</v>
+      </c>
+      <c r="D1320" s="28" t="s">
+        <v>963</v>
+      </c>
+      <c r="E1320" s="29" t="s">
+        <v>765</v>
+      </c>
+      <c r="G1320">
+        <v>10</v>
+      </c>
+      <c r="H1320">
+        <v>1</v>
+      </c>
+      <c r="I1320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1321">
+        <v>1920084</v>
+      </c>
+      <c r="B1321" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1321">
+        <v>0</v>
+      </c>
+      <c r="D1321" s="28" t="s">
+        <v>964</v>
+      </c>
+      <c r="E1321" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1321">
+        <v>10</v>
+      </c>
+      <c r="H1321">
+        <v>1</v>
+      </c>
+      <c r="I1321">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1322">
+        <v>2920084</v>
+      </c>
+      <c r="B1322" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1322">
+        <v>0</v>
+      </c>
+      <c r="D1322" s="28" t="s">
+        <v>965</v>
+      </c>
+      <c r="E1322" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1322">
+        <v>10</v>
+      </c>
+      <c r="H1322">
+        <v>1</v>
+      </c>
+      <c r="I1322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1323">
+        <v>3920084</v>
+      </c>
+      <c r="B1323" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1323">
+        <v>0</v>
+      </c>
+      <c r="D1323" s="28" t="s">
+        <v>966</v>
+      </c>
+      <c r="E1323" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1323">
+        <v>10</v>
+      </c>
+      <c r="H1323">
+        <v>1</v>
+      </c>
+      <c r="I1323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1324">
+        <v>4920084</v>
+      </c>
+      <c r="B1324" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1324">
+        <v>0</v>
+      </c>
+      <c r="D1324" s="28" t="s">
+        <v>967</v>
+      </c>
+      <c r="E1324" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1324">
+        <v>10</v>
+      </c>
+      <c r="H1324">
+        <v>1</v>
+      </c>
+      <c r="I1324">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1325">
+        <v>5920084</v>
+      </c>
+      <c r="B1325" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1325">
+        <v>0</v>
+      </c>
+      <c r="D1325" s="28" t="s">
+        <v>968</v>
+      </c>
+      <c r="E1325" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1325">
+        <v>10</v>
+      </c>
+      <c r="H1325">
+        <v>1</v>
+      </c>
+      <c r="I1325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1326">
+        <v>6920084</v>
+      </c>
+      <c r="B1326" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1326">
+        <v>0</v>
+      </c>
+      <c r="D1326" s="28" t="s">
+        <v>969</v>
+      </c>
+      <c r="E1326" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1326">
+        <v>10</v>
+      </c>
+      <c r="H1326">
+        <v>1</v>
+      </c>
+      <c r="I1326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1327">
+        <v>7920084</v>
+      </c>
+      <c r="B1327" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1327">
+        <v>0</v>
+      </c>
+      <c r="D1327" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="E1327" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1327">
+        <v>10</v>
+      </c>
+      <c r="H1327">
+        <v>2</v>
+      </c>
+      <c r="I1327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1328">
+        <v>8920084</v>
+      </c>
+      <c r="B1328" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1328">
+        <v>0</v>
+      </c>
+      <c r="D1328" s="28" t="s">
+        <v>971</v>
+      </c>
+      <c r="E1328" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1328">
+        <v>10</v>
+      </c>
+      <c r="H1328">
+        <v>1</v>
+      </c>
+      <c r="I1328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1329">
+        <v>9920084</v>
+      </c>
+      <c r="B1329" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1329">
+        <v>0</v>
+      </c>
+      <c r="D1329" s="28" t="s">
+        <v>972</v>
+      </c>
+      <c r="E1329" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1329">
+        <v>10</v>
+      </c>
+      <c r="H1329">
+        <v>2</v>
+      </c>
+      <c r="I1329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1330">
+        <v>16920084</v>
+      </c>
+      <c r="B1330" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1330">
+        <v>0</v>
+      </c>
+      <c r="D1330" s="28" t="s">
+        <v>973</v>
+      </c>
+      <c r="E1330" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1330" s="28"/>
+      <c r="G1330">
+        <v>10</v>
+      </c>
+      <c r="H1330">
+        <v>1</v>
+      </c>
+      <c r="I1330">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1331">
+        <v>920085</v>
+      </c>
+      <c r="B1331" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1331">
+        <v>0</v>
+      </c>
+      <c r="D1331" s="28" t="s">
+        <v>974</v>
+      </c>
+      <c r="E1331" s="29" t="s">
+        <v>765</v>
+      </c>
+      <c r="G1331">
+        <v>10</v>
+      </c>
+      <c r="H1331">
+        <v>1</v>
+      </c>
+      <c r="I1331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1332">
+        <v>1920085</v>
+      </c>
+      <c r="B1332" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1332">
+        <v>0</v>
+      </c>
+      <c r="D1332" s="28" t="s">
+        <v>975</v>
+      </c>
+      <c r="E1332" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1332">
+        <v>10</v>
+      </c>
+      <c r="H1332">
+        <v>1</v>
+      </c>
+      <c r="I1332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1333">
+        <v>2920085</v>
+      </c>
+      <c r="B1333" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1333">
+        <v>0</v>
+      </c>
+      <c r="D1333" s="28" t="s">
+        <v>976</v>
+      </c>
+      <c r="E1333" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1333">
+        <v>10</v>
+      </c>
+      <c r="H1333">
+        <v>1</v>
+      </c>
+      <c r="I1333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1334">
+        <v>3920085</v>
+      </c>
+      <c r="B1334" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1334">
+        <v>0</v>
+      </c>
+      <c r="D1334" s="28" t="s">
+        <v>977</v>
+      </c>
+      <c r="E1334" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1334">
+        <v>10</v>
+      </c>
+      <c r="H1334">
+        <v>1</v>
+      </c>
+      <c r="I1334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1335">
+        <v>4920085</v>
+      </c>
+      <c r="B1335" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1335">
+        <v>0</v>
+      </c>
+      <c r="D1335" s="28" t="s">
+        <v>978</v>
+      </c>
+      <c r="E1335" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1335">
+        <v>10</v>
+      </c>
+      <c r="H1335">
+        <v>1</v>
+      </c>
+      <c r="I1335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1336">
+        <v>5920085</v>
+      </c>
+      <c r="B1336" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1336">
+        <v>0</v>
+      </c>
+      <c r="D1336" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="E1336" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1336">
+        <v>10</v>
+      </c>
+      <c r="H1336">
+        <v>1</v>
+      </c>
+      <c r="I1336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1337">
+        <v>6920085</v>
+      </c>
+      <c r="B1337" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1337">
+        <v>0</v>
+      </c>
+      <c r="D1337" s="28" t="s">
+        <v>980</v>
+      </c>
+      <c r="E1337" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1337">
+        <v>10</v>
+      </c>
+      <c r="H1337">
+        <v>1</v>
+      </c>
+      <c r="I1337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1338">
+        <v>7920085</v>
+      </c>
+      <c r="B1338" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1338">
+        <v>0</v>
+      </c>
+      <c r="D1338" s="28" t="s">
+        <v>981</v>
+      </c>
+      <c r="E1338" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1338">
+        <v>10</v>
+      </c>
+      <c r="H1338">
+        <v>2</v>
+      </c>
+      <c r="I1338">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1339">
+        <v>8920085</v>
+      </c>
+      <c r="B1339" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1339">
+        <v>0</v>
+      </c>
+      <c r="D1339" s="28" t="s">
+        <v>982</v>
+      </c>
+      <c r="E1339" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1339">
+        <v>10</v>
+      </c>
+      <c r="H1339">
+        <v>1</v>
+      </c>
+      <c r="I1339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1340">
+        <v>9920085</v>
+      </c>
+      <c r="B1340" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1340">
+        <v>0</v>
+      </c>
+      <c r="D1340" s="28" t="s">
+        <v>983</v>
+      </c>
+      <c r="E1340" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1340">
+        <v>10</v>
+      </c>
+      <c r="H1340">
+        <v>2</v>
+      </c>
+      <c r="I1340">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1341">
+        <v>920086</v>
+      </c>
+      <c r="B1341" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1341">
+        <v>0</v>
+      </c>
+      <c r="D1341" s="28" t="s">
+        <v>985</v>
+      </c>
+      <c r="E1341" s="29" t="s">
+        <v>765</v>
+      </c>
+      <c r="F1341" s="28"/>
+      <c r="G1341">
+        <v>10</v>
+      </c>
+      <c r="H1341">
+        <v>1</v>
+      </c>
+      <c r="I1341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1342">
+        <v>820086</v>
+      </c>
+      <c r="B1342" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1342">
+        <v>0</v>
+      </c>
+      <c r="D1342" s="30" t="s">
+        <v>986</v>
+      </c>
+      <c r="E1342" s="30" t="s">
+        <v>986</v>
+      </c>
+      <c r="G1342">
+        <v>10</v>
+      </c>
+      <c r="H1342">
+        <v>1</v>
+      </c>
+      <c r="I1342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1343">
+        <v>8200861</v>
+      </c>
+      <c r="B1343" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1343">
+        <v>0</v>
+      </c>
+      <c r="D1343" s="30" t="s">
+        <v>988</v>
+      </c>
+      <c r="E1343" s="30" t="s">
+        <v>987</v>
+      </c>
+      <c r="G1343">
+        <v>10</v>
+      </c>
+      <c r="H1343">
+        <v>2</v>
+      </c>
+      <c r="I1343">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3141,14 +3141,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3414,7 +3407,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3507,12 +3500,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3532,12 +3519,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3793,13 +3774,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3808,55 +3792,58 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3865,10 +3852,10 @@
     <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3877,10 +3864,10 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3889,10 +3876,10 @@
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3901,10 +3888,10 @@
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3913,19 +3900,13 @@
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3933,80 +3914,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -40656,7 +40637,7 @@
         <v>1</v>
       </c>
       <c r="I1300">
-        <v>7000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1301" spans="1:9">
@@ -40812,7 +40793,7 @@
         <v>2</v>
       </c>
       <c r="I1306">
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1307" spans="1:9">
@@ -40864,7 +40845,7 @@
         <v>2</v>
       </c>
       <c r="I1308">
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
@@ -40891,7 +40872,7 @@
         <v>1</v>
       </c>
       <c r="I1309">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1310" spans="1:9">
@@ -40918,7 +40899,7 @@
         <v>1</v>
       </c>
       <c r="I1310">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1311" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3632" uniqueCount="992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3634" uniqueCount="993">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2895,6 +2895,9 @@
   </si>
   <si>
     <t>冰球_技能伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>冰球_技能等级</t>
   </si>
   <si>
     <t>冰球_弹道数量</t>
@@ -4340,7 +4343,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1347"/>
+  <dimension ref="A1:I1348"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -40904,7 +40907,7 @@
     </row>
     <row r="1311" spans="1:9">
       <c r="A1311">
-        <v>14920081</v>
+        <v>13920081</v>
       </c>
       <c r="B1311" s="26">
         <v>1</v>
@@ -40926,12 +40929,12 @@
         <v>1</v>
       </c>
       <c r="I1311">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1312" spans="1:9">
       <c r="A1312">
-        <v>920083</v>
+        <v>14920081</v>
       </c>
       <c r="B1312" s="26">
         <v>1</v>
@@ -40943,8 +40946,9 @@
         <v>915</v>
       </c>
       <c r="E1312" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1312" s="28"/>
       <c r="G1312">
         <v>10</v>
       </c>
@@ -40952,12 +40956,12 @@
         <v>1</v>
       </c>
       <c r="I1312">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1313" spans="1:9">
       <c r="A1313">
-        <v>14920083</v>
+        <v>920083</v>
       </c>
       <c r="B1313" s="26">
         <v>1</v>
@@ -40969,9 +40973,8 @@
         <v>916</v>
       </c>
       <c r="E1313" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1313" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1313">
         <v>10</v>
       </c>
@@ -40983,8 +40986,8 @@
       </c>
     </row>
     <row r="1314" spans="1:9">
-      <c r="A1314" s="31">
-        <v>920082</v>
+      <c r="A1314">
+        <v>14920083</v>
       </c>
       <c r="B1314" s="26">
         <v>1</v>
@@ -40996,7 +40999,7 @@
         <v>917</v>
       </c>
       <c r="E1314" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1314" s="28"/>
       <c r="G1314">
@@ -41006,12 +41009,12 @@
         <v>1</v>
       </c>
       <c r="I1314">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1315" spans="1:9">
-      <c r="A1315" s="30">
-        <v>820082</v>
+      <c r="A1315" s="31">
+        <v>920082</v>
       </c>
       <c r="B1315" s="26">
         <v>1</v>
@@ -41019,12 +41022,13 @@
       <c r="C1315">
         <v>0</v>
       </c>
-      <c r="D1315" s="30" t="s">
+      <c r="D1315" s="28" t="s">
         <v>918</v>
       </c>
-      <c r="E1315" s="30" t="s">
-        <v>918</v>
-      </c>
+      <c r="E1315" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1315" s="28"/>
       <c r="G1315">
         <v>10</v>
       </c>
@@ -41037,7 +41041,7 @@
     </row>
     <row r="1316" spans="1:9">
       <c r="A1316" s="30">
-        <v>820083</v>
+        <v>820082</v>
       </c>
       <c r="B1316" s="26">
         <v>1</v>
@@ -41062,8 +41066,8 @@
       </c>
     </row>
     <row r="1317" spans="1:9">
-      <c r="A1317">
-        <v>920074</v>
+      <c r="A1317" s="30">
+        <v>820083</v>
       </c>
       <c r="B1317" s="26">
         <v>1</v>
@@ -41071,11 +41075,11 @@
       <c r="C1317">
         <v>0</v>
       </c>
-      <c r="D1317" s="28" t="s">
+      <c r="D1317" s="30" t="s">
         <v>920</v>
       </c>
-      <c r="E1317" s="29" t="s">
-        <v>767</v>
+      <c r="E1317" s="30" t="s">
+        <v>920</v>
       </c>
       <c r="G1317">
         <v>10</v>
@@ -41089,7 +41093,7 @@
     </row>
     <row r="1318" spans="1:9">
       <c r="A1318">
-        <v>14920074</v>
+        <v>920074</v>
       </c>
       <c r="B1318" s="26">
         <v>1</v>
@@ -41101,9 +41105,8 @@
         <v>921</v>
       </c>
       <c r="E1318" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1318" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1318">
         <v>10</v>
       </c>
@@ -41111,12 +41114,12 @@
         <v>1</v>
       </c>
       <c r="I1318">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1319" spans="1:9">
       <c r="A1319">
-        <v>16920074</v>
+        <v>14920074</v>
       </c>
       <c r="B1319" s="26">
         <v>1</v>
@@ -41135,15 +41138,15 @@
         <v>10</v>
       </c>
       <c r="H1319">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1319">
-        <v>10000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1320" spans="1:9">
       <c r="A1320">
-        <v>17920074</v>
+        <v>16920074</v>
       </c>
       <c r="B1320" s="26">
         <v>1</v>
@@ -41165,12 +41168,12 @@
         <v>2</v>
       </c>
       <c r="I1320">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1321" spans="1:9">
       <c r="A1321">
-        <v>18920074</v>
+        <v>17920074</v>
       </c>
       <c r="B1321" s="26">
         <v>1</v>
@@ -41192,12 +41195,12 @@
         <v>2</v>
       </c>
       <c r="I1321">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1322" spans="1:9">
       <c r="A1322">
-        <v>920073</v>
+        <v>18920074</v>
       </c>
       <c r="B1322" s="26">
         <v>1</v>
@@ -41209,22 +41212,22 @@
         <v>925</v>
       </c>
       <c r="E1322" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1322" s="28"/>
       <c r="G1322">
         <v>10</v>
       </c>
       <c r="H1322">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1322">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1323" spans="1:9">
       <c r="A1323">
-        <v>820073</v>
+        <v>920073</v>
       </c>
       <c r="B1323" s="26">
         <v>1</v>
@@ -41232,12 +41235,13 @@
       <c r="C1323">
         <v>0</v>
       </c>
-      <c r="D1323" s="30" t="s">
+      <c r="D1323" s="28" t="s">
         <v>926</v>
       </c>
-      <c r="E1323" s="30" t="s">
-        <v>926</v>
-      </c>
+      <c r="E1323" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1323" s="28"/>
       <c r="G1323">
         <v>10</v>
       </c>
@@ -41250,7 +41254,7 @@
     </row>
     <row r="1324" spans="1:9">
       <c r="A1324">
-        <v>920084</v>
+        <v>820073</v>
       </c>
       <c r="B1324" s="26">
         <v>1</v>
@@ -41258,11 +41262,11 @@
       <c r="C1324">
         <v>0</v>
       </c>
-      <c r="D1324" s="28" t="s">
+      <c r="D1324" s="30" t="s">
         <v>927</v>
       </c>
-      <c r="E1324" s="29" t="s">
-        <v>767</v>
+      <c r="E1324" s="30" t="s">
+        <v>927</v>
       </c>
       <c r="G1324">
         <v>10</v>
@@ -41276,7 +41280,7 @@
     </row>
     <row r="1325" spans="1:9">
       <c r="A1325">
-        <v>1920084</v>
+        <v>920084</v>
       </c>
       <c r="B1325" s="26">
         <v>1</v>
@@ -41288,7 +41292,7 @@
         <v>928</v>
       </c>
       <c r="E1325" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1325">
         <v>10</v>
@@ -41297,12 +41301,12 @@
         <v>1</v>
       </c>
       <c r="I1325">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1326" spans="1:9">
       <c r="A1326">
-        <v>2920084</v>
+        <v>1920084</v>
       </c>
       <c r="B1326" s="26">
         <v>1</v>
@@ -41323,12 +41327,12 @@
         <v>1</v>
       </c>
       <c r="I1326">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1327" spans="1:9">
       <c r="A1327">
-        <v>3920084</v>
+        <v>2920084</v>
       </c>
       <c r="B1327" s="26">
         <v>1</v>
@@ -41354,7 +41358,7 @@
     </row>
     <row r="1328" spans="1:9">
       <c r="A1328">
-        <v>4920084</v>
+        <v>3920084</v>
       </c>
       <c r="B1328" s="26">
         <v>1</v>
@@ -41375,12 +41379,12 @@
         <v>1</v>
       </c>
       <c r="I1328">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1329" spans="1:9">
       <c r="A1329">
-        <v>5920084</v>
+        <v>4920084</v>
       </c>
       <c r="B1329" s="26">
         <v>1</v>
@@ -41401,12 +41405,12 @@
         <v>1</v>
       </c>
       <c r="I1329">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1330" spans="1:9">
       <c r="A1330">
-        <v>6920084</v>
+        <v>5920084</v>
       </c>
       <c r="B1330" s="26">
         <v>1</v>
@@ -41432,7 +41436,7 @@
     </row>
     <row r="1331" spans="1:9">
       <c r="A1331">
-        <v>7920084</v>
+        <v>6920084</v>
       </c>
       <c r="B1331" s="26">
         <v>1</v>
@@ -41450,7 +41454,7 @@
         <v>10</v>
       </c>
       <c r="H1331">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1331">
         <v>0</v>
@@ -41458,7 +41462,7 @@
     </row>
     <row r="1332" spans="1:9">
       <c r="A1332">
-        <v>8920084</v>
+        <v>7920084</v>
       </c>
       <c r="B1332" s="26">
         <v>1</v>
@@ -41476,7 +41480,7 @@
         <v>10</v>
       </c>
       <c r="H1332">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1332">
         <v>0</v>
@@ -41484,7 +41488,7 @@
     </row>
     <row r="1333" spans="1:9">
       <c r="A1333">
-        <v>9920084</v>
+        <v>8920084</v>
       </c>
       <c r="B1333" s="26">
         <v>1</v>
@@ -41502,7 +41506,7 @@
         <v>10</v>
       </c>
       <c r="H1333">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1333">
         <v>0</v>
@@ -41510,7 +41514,7 @@
     </row>
     <row r="1334" spans="1:9">
       <c r="A1334">
-        <v>16920084</v>
+        <v>9920084</v>
       </c>
       <c r="B1334" s="26">
         <v>1</v>
@@ -41524,20 +41528,19 @@
       <c r="E1334" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1334" s="28"/>
       <c r="G1334">
         <v>10</v>
       </c>
       <c r="H1334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1334">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1335" spans="1:9">
       <c r="A1335">
-        <v>920085</v>
+        <v>16920084</v>
       </c>
       <c r="B1335" s="26">
         <v>1</v>
@@ -41549,8 +41552,9 @@
         <v>938</v>
       </c>
       <c r="E1335" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1335" s="28"/>
       <c r="G1335">
         <v>10</v>
       </c>
@@ -41558,12 +41562,12 @@
         <v>1</v>
       </c>
       <c r="I1335">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1336" spans="1:9">
       <c r="A1336">
-        <v>1920085</v>
+        <v>920085</v>
       </c>
       <c r="B1336" s="26">
         <v>1</v>
@@ -41575,7 +41579,7 @@
         <v>939</v>
       </c>
       <c r="E1336" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1336">
         <v>10</v>
@@ -41589,7 +41593,7 @@
     </row>
     <row r="1337" spans="1:9">
       <c r="A1337">
-        <v>2920085</v>
+        <v>1920085</v>
       </c>
       <c r="B1337" s="26">
         <v>1</v>
@@ -41615,7 +41619,7 @@
     </row>
     <row r="1338" spans="1:9">
       <c r="A1338">
-        <v>3920085</v>
+        <v>2920085</v>
       </c>
       <c r="B1338" s="26">
         <v>1</v>
@@ -41641,7 +41645,7 @@
     </row>
     <row r="1339" spans="1:9">
       <c r="A1339">
-        <v>4920085</v>
+        <v>3920085</v>
       </c>
       <c r="B1339" s="26">
         <v>1</v>
@@ -41667,7 +41671,7 @@
     </row>
     <row r="1340" spans="1:9">
       <c r="A1340">
-        <v>5920085</v>
+        <v>4920085</v>
       </c>
       <c r="B1340" s="26">
         <v>1</v>
@@ -41688,12 +41692,12 @@
         <v>1</v>
       </c>
       <c r="I1340">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1341" spans="1:9">
       <c r="A1341">
-        <v>6920085</v>
+        <v>5920085</v>
       </c>
       <c r="B1341" s="26">
         <v>1</v>
@@ -41714,12 +41718,12 @@
         <v>1</v>
       </c>
       <c r="I1341">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1342" spans="1:9">
       <c r="A1342">
-        <v>7920085</v>
+        <v>6920085</v>
       </c>
       <c r="B1342" s="26">
         <v>1</v>
@@ -41737,15 +41741,15 @@
         <v>10</v>
       </c>
       <c r="H1342">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1342">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1343" spans="1:9">
       <c r="A1343">
-        <v>8920085</v>
+        <v>7920085</v>
       </c>
       <c r="B1343" s="26">
         <v>1</v>
@@ -41763,15 +41767,15 @@
         <v>10</v>
       </c>
       <c r="H1343">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1343">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1344" spans="1:9">
       <c r="A1344">
-        <v>9920085</v>
+        <v>8920085</v>
       </c>
       <c r="B1344" s="26">
         <v>1</v>
@@ -41789,15 +41793,15 @@
         <v>10</v>
       </c>
       <c r="H1344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1344">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1345" spans="1:9">
       <c r="A1345">
-        <v>920086</v>
+        <v>9920085</v>
       </c>
       <c r="B1345" s="26">
         <v>1</v>
@@ -41809,22 +41813,21 @@
         <v>948</v>
       </c>
       <c r="E1345" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1345" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1345">
         <v>10</v>
       </c>
       <c r="H1345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1345">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1346" spans="1:9">
       <c r="A1346">
-        <v>820086</v>
+        <v>920086</v>
       </c>
       <c r="B1346" s="26">
         <v>1</v>
@@ -41832,12 +41835,13 @@
       <c r="C1346">
         <v>0</v>
       </c>
-      <c r="D1346" s="30" t="s">
+      <c r="D1346" s="28" t="s">
         <v>949</v>
       </c>
-      <c r="E1346" s="30" t="s">
-        <v>949</v>
-      </c>
+      <c r="E1346" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1346" s="28"/>
       <c r="G1346">
         <v>10</v>
       </c>
@@ -41850,7 +41854,7 @@
     </row>
     <row r="1347" spans="1:9">
       <c r="A1347">
-        <v>8200861</v>
+        <v>820086</v>
       </c>
       <c r="B1347" s="26">
         <v>1</v>
@@ -41862,15 +41866,41 @@
         <v>950</v>
       </c>
       <c r="E1347" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="G1347">
+        <v>10</v>
+      </c>
+      <c r="H1347">
+        <v>1</v>
+      </c>
+      <c r="I1347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:9">
+      <c r="A1348">
+        <v>8200861</v>
+      </c>
+      <c r="B1348" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1348">
+        <v>0</v>
+      </c>
+      <c r="D1348" s="30" t="s">
         <v>951</v>
       </c>
-      <c r="G1347">
-        <v>10</v>
-      </c>
-      <c r="H1347">
+      <c r="E1348" s="30" t="s">
+        <v>952</v>
+      </c>
+      <c r="G1348">
+        <v>10</v>
+      </c>
+      <c r="H1348">
         <v>2</v>
       </c>
-      <c r="I1347">
+      <c r="I1348">
         <v>0</v>
       </c>
     </row>
@@ -41936,7 +41966,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -41948,10 +41978,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -41965,90 +41995,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>969</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>970</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>971</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>972</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>973</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>974</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>976</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>977</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>978</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -42059,7 +42089,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -42080,7 +42110,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -42092,7 +42122,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42103,7 +42133,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -42144,7 +42174,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -42185,7 +42215,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -42206,7 +42236,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -42218,7 +42248,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -42229,7 +42259,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -42250,7 +42280,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -42262,7 +42292,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -42273,7 +42303,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -42294,7 +42324,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3634" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3636" uniqueCount="994">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3012,6 +3012,9 @@
   </si>
   <si>
     <t>冰雪领域被动-参数1-释放技能概率</t>
+  </si>
+  <si>
+    <t>生命药剂技能_获得</t>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S</t>
@@ -3144,7 +3147,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3399,18 +3409,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3425,7 +3435,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799798577837458"/>
+        <fgColor theme="9" tint="0.799768059327982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3461,7 +3471,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799798577837458"/>
+        <fgColor theme="4" tint="0.799768059327982"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3503,6 +3513,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3522,6 +3538,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3777,16 +3799,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3795,58 +3814,55 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3855,10 +3871,10 @@
     <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3867,10 +3883,10 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3879,10 +3895,10 @@
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3891,10 +3907,10 @@
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3903,13 +3919,19 @@
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3917,80 +3939,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4343,7 +4365,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1348"/>
+  <dimension ref="A1:I1349"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -39400,7 +39422,7 @@
         <v>1</v>
       </c>
       <c r="I1253">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1254" spans="1:9">
@@ -41902,6 +41924,33 @@
       </c>
       <c r="I1348">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:9">
+      <c r="A1349">
+        <v>990001</v>
+      </c>
+      <c r="B1349" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1349">
+        <v>0</v>
+      </c>
+      <c r="D1349" s="28" t="s">
+        <v>953</v>
+      </c>
+      <c r="E1349" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1349" s="28"/>
+      <c r="G1349">
+        <v>10</v>
+      </c>
+      <c r="H1349">
+        <v>1</v>
+      </c>
+      <c r="I1349">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -41966,7 +42015,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -41978,10 +42027,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -41995,90 +42044,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>970</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>971</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>972</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>973</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>974</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>976</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>977</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>978</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -42089,7 +42138,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -42110,7 +42159,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -42122,7 +42171,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42133,7 +42182,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -42174,7 +42223,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -42215,7 +42264,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -42236,7 +42285,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -42248,7 +42297,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -42259,7 +42308,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -42280,7 +42329,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -42292,7 +42341,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -42303,7 +42352,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -42324,7 +42373,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3168,14 +3168,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3441,7 +3434,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3534,12 +3527,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3559,12 +3546,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3820,13 +3801,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3835,55 +3819,58 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3892,10 +3879,10 @@
     <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3904,10 +3891,10 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3916,10 +3903,10 @@
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3928,10 +3915,10 @@
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3940,19 +3927,13 @@
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3960,80 +3941,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -40839,7 +40820,7 @@
         <v>2</v>
       </c>
       <c r="I1306">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1307" spans="1:9">
@@ -40891,7 +40872,7 @@
         <v>2</v>
       </c>
       <c r="I1308">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
@@ -40945,7 +40926,7 @@
         <v>1</v>
       </c>
       <c r="I1310">
-        <v>1500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1311" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -39715,7 +39715,7 @@
         <v>1</v>
       </c>
       <c r="I1264">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1265" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -41192,7 +41192,7 @@
         <v>2</v>
       </c>
       <c r="I1320">
-        <v>10000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1321" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -39450,7 +39450,7 @@
         <v>1</v>
       </c>
       <c r="I1254">
-        <v>3500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1255" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -39528,7 +39528,7 @@
         <v>2</v>
       </c>
       <c r="I1257">
-        <v>3600</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="1258" spans="1:9">
@@ -39580,7 +39580,7 @@
         <v>2</v>
       </c>
       <c r="I1259">
-        <v>3600</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="1260" spans="1:9">
@@ -39769,7 +39769,7 @@
         <v>1</v>
       </c>
       <c r="I1266">
-        <v>4000</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="1267" spans="1:9">
@@ -39823,7 +39823,7 @@
         <v>2</v>
       </c>
       <c r="I1268">
-        <v>4500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="1269" spans="1:9">
@@ -40403,7 +40403,7 @@
         <v>1</v>
       </c>
       <c r="I1290">
-        <v>1600</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1291" spans="1:9">
@@ -40481,7 +40481,7 @@
         <v>2</v>
       </c>
       <c r="I1293">
-        <v>13500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1294" spans="1:9">
@@ -40533,7 +40533,7 @@
         <v>2</v>
       </c>
       <c r="I1295">
-        <v>13500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1296" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -11,7 +11,7 @@
     <sheet name="maze_attribute_formula_v8" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1351</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4367,7 +4367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1354"/>
+  <dimension ref="A1:I1355"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -39745,36 +39745,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1266" spans="1:9">
-      <c r="A1266">
-        <v>17920061</v>
-      </c>
-      <c r="B1266" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1266">
-        <v>0</v>
-      </c>
-      <c r="D1266" s="28" t="s">
-        <v>876</v>
-      </c>
-      <c r="E1266" s="29" t="s">
-        <v>769</v>
-      </c>
+    <row r="1266" spans="2:6">
+      <c r="B1266" s="26"/>
+      <c r="D1266" s="28"/>
+      <c r="E1266" s="29"/>
       <c r="F1266" s="28"/>
-      <c r="G1266">
-        <v>10</v>
-      </c>
-      <c r="H1266">
-        <v>1</v>
-      </c>
-      <c r="I1266">
-        <v>10500</v>
-      </c>
     </row>
     <row r="1267" spans="1:9">
       <c r="A1267">
-        <v>18920061</v>
+        <v>17920061</v>
       </c>
       <c r="B1267" s="26">
         <v>1</v>
@@ -39783,7 +39762,7 @@
         <v>0</v>
       </c>
       <c r="D1267" s="28" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E1267" s="29" t="s">
         <v>769</v>
@@ -39796,12 +39775,12 @@
         <v>1</v>
       </c>
       <c r="I1267">
-        <v>500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="1268" spans="1:9">
       <c r="A1268">
-        <v>19920061</v>
+        <v>18920061</v>
       </c>
       <c r="B1268" s="26">
         <v>1</v>
@@ -39810,7 +39789,7 @@
         <v>0</v>
       </c>
       <c r="D1268" s="28" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E1268" s="29" t="s">
         <v>769</v>
@@ -39820,15 +39799,15 @@
         <v>10</v>
       </c>
       <c r="H1268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1268">
-        <v>10500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1269" spans="1:9">
       <c r="A1269">
-        <v>20920061</v>
+        <v>19920061</v>
       </c>
       <c r="B1269" s="26">
         <v>1</v>
@@ -39837,7 +39816,7 @@
         <v>0</v>
       </c>
       <c r="D1269" s="28" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E1269" s="29" t="s">
         <v>769</v>
@@ -39847,42 +39826,42 @@
         <v>10</v>
       </c>
       <c r="H1269">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1269">
-        <v>1</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="1270" spans="1:9">
-      <c r="A1270" s="26">
-        <v>5001600</v>
+      <c r="A1270">
+        <v>20920061</v>
       </c>
       <c r="B1270" s="26">
         <v>1</v>
       </c>
-      <c r="C1270" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1270" s="26" t="s">
-        <v>880</v>
-      </c>
-      <c r="E1270" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="F1270" s="9"/>
-      <c r="G1270" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1270" s="26">
+      <c r="C1270">
+        <v>0</v>
+      </c>
+      <c r="D1270" s="28" t="s">
+        <v>879</v>
+      </c>
+      <c r="E1270" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1270" s="28"/>
+      <c r="G1270">
+        <v>10</v>
+      </c>
+      <c r="H1270">
         <v>1</v>
       </c>
       <c r="I1270">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1271" spans="1:9">
       <c r="A1271" s="26">
-        <v>5001501</v>
+        <v>5001600</v>
       </c>
       <c r="B1271" s="26">
         <v>1</v>
@@ -39891,17 +39870,17 @@
         <v>0</v>
       </c>
       <c r="D1271" s="26" t="s">
-        <v>881</v>
-      </c>
-      <c r="E1271" s="19" t="s">
-        <v>329</v>
+        <v>880</v>
+      </c>
+      <c r="E1271" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="F1271" s="9"/>
       <c r="G1271" s="26">
         <v>10</v>
       </c>
       <c r="H1271" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1271">
         <v>0</v>
@@ -39909,7 +39888,7 @@
     </row>
     <row r="1272" spans="1:9">
       <c r="A1272" s="26">
-        <v>5001502</v>
+        <v>5001501</v>
       </c>
       <c r="B1272" s="26">
         <v>1</v>
@@ -39921,14 +39900,14 @@
         <v>881</v>
       </c>
       <c r="E1272" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1272" s="9"/>
       <c r="G1272" s="26">
         <v>10</v>
       </c>
       <c r="H1272" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1272">
         <v>0</v>
@@ -39936,7 +39915,7 @@
     </row>
     <row r="1273" spans="1:9">
       <c r="A1273" s="26">
-        <v>5001511</v>
+        <v>5001502</v>
       </c>
       <c r="B1273" s="26">
         <v>1</v>
@@ -39945,17 +39924,17 @@
         <v>0</v>
       </c>
       <c r="D1273" s="26" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E1273" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1273" s="9"/>
       <c r="G1273" s="26">
         <v>10</v>
       </c>
       <c r="H1273" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1273">
         <v>0</v>
@@ -39963,7 +39942,7 @@
     </row>
     <row r="1274" spans="1:9">
       <c r="A1274" s="26">
-        <v>5001512</v>
+        <v>5001511</v>
       </c>
       <c r="B1274" s="26">
         <v>1</v>
@@ -39975,14 +39954,14 @@
         <v>882</v>
       </c>
       <c r="E1274" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1274" s="9"/>
       <c r="G1274" s="26">
         <v>10</v>
       </c>
       <c r="H1274" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1274">
         <v>0</v>
@@ -39990,7 +39969,7 @@
     </row>
     <row r="1275" spans="1:9">
       <c r="A1275" s="26">
-        <v>5001521</v>
+        <v>5001512</v>
       </c>
       <c r="B1275" s="26">
         <v>1</v>
@@ -39999,17 +39978,17 @@
         <v>0</v>
       </c>
       <c r="D1275" s="26" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E1275" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1275" s="9"/>
       <c r="G1275" s="26">
         <v>10</v>
       </c>
       <c r="H1275" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1275">
         <v>0</v>
@@ -40017,7 +39996,7 @@
     </row>
     <row r="1276" spans="1:9">
       <c r="A1276" s="26">
-        <v>5001522</v>
+        <v>5001521</v>
       </c>
       <c r="B1276" s="26">
         <v>1</v>
@@ -40029,14 +40008,14 @@
         <v>883</v>
       </c>
       <c r="E1276" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1276" s="9"/>
       <c r="G1276" s="26">
         <v>10</v>
       </c>
       <c r="H1276" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1276">
         <v>0</v>
@@ -40044,7 +40023,7 @@
     </row>
     <row r="1277" spans="1:9">
       <c r="A1277" s="26">
-        <v>5001800</v>
+        <v>5001522</v>
       </c>
       <c r="B1277" s="26">
         <v>1</v>
@@ -40053,11 +40032,12 @@
         <v>0</v>
       </c>
       <c r="D1277" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="E1277" s="26" t="s">
-        <v>243</v>
-      </c>
+        <v>883</v>
+      </c>
+      <c r="E1277" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1277" s="9"/>
       <c r="G1277" s="26">
         <v>10</v>
       </c>
@@ -40070,7 +40050,7 @@
     </row>
     <row r="1278" spans="1:9">
       <c r="A1278" s="26">
-        <v>5001701</v>
+        <v>5001800</v>
       </c>
       <c r="B1278" s="26">
         <v>1</v>
@@ -40079,16 +40059,16 @@
         <v>0</v>
       </c>
       <c r="D1278" s="26" t="s">
-        <v>885</v>
-      </c>
-      <c r="E1278" s="19" t="s">
-        <v>886</v>
+        <v>884</v>
+      </c>
+      <c r="E1278" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="G1278" s="26">
         <v>10</v>
       </c>
       <c r="H1278" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1278">
         <v>0</v>
@@ -40096,7 +40076,7 @@
     </row>
     <row r="1279" spans="1:9">
       <c r="A1279" s="26">
-        <v>5001702</v>
+        <v>5001701</v>
       </c>
       <c r="B1279" s="26">
         <v>1</v>
@@ -40108,7 +40088,7 @@
         <v>885</v>
       </c>
       <c r="E1279" s="19" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G1279" s="26">
         <v>10</v>
@@ -40122,7 +40102,7 @@
     </row>
     <row r="1280" spans="1:9">
       <c r="A1280" s="26">
-        <v>5001705</v>
+        <v>5001702</v>
       </c>
       <c r="B1280" s="26">
         <v>1</v>
@@ -40134,13 +40114,13 @@
         <v>885</v>
       </c>
       <c r="E1280" s="19" t="s">
-        <v>327</v>
+        <v>887</v>
       </c>
       <c r="G1280" s="26">
         <v>10</v>
       </c>
       <c r="H1280" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1280">
         <v>0</v>
@@ -40148,7 +40128,7 @@
     </row>
     <row r="1281" spans="1:9">
       <c r="A1281" s="26">
-        <v>5001706</v>
+        <v>5001705</v>
       </c>
       <c r="B1281" s="26">
         <v>1</v>
@@ -40160,13 +40140,13 @@
         <v>885</v>
       </c>
       <c r="E1281" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G1281" s="26">
         <v>10</v>
       </c>
       <c r="H1281" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1281">
         <v>0</v>
@@ -40174,7 +40154,7 @@
     </row>
     <row r="1282" spans="1:9">
       <c r="A1282" s="26">
-        <v>5001711</v>
+        <v>5001706</v>
       </c>
       <c r="B1282" s="26">
         <v>1</v>
@@ -40183,10 +40163,10 @@
         <v>0</v>
       </c>
       <c r="D1282" s="26" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="E1282" s="19" t="s">
-        <v>886</v>
+        <v>329</v>
       </c>
       <c r="G1282" s="26">
         <v>10</v>
@@ -40200,7 +40180,7 @@
     </row>
     <row r="1283" spans="1:9">
       <c r="A1283" s="26">
-        <v>5001712</v>
+        <v>5001711</v>
       </c>
       <c r="B1283" s="26">
         <v>1</v>
@@ -40212,7 +40192,7 @@
         <v>888</v>
       </c>
       <c r="E1283" s="19" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G1283" s="26">
         <v>10</v>
@@ -40226,7 +40206,7 @@
     </row>
     <row r="1284" spans="1:9">
       <c r="A1284" s="26">
-        <v>5001715</v>
+        <v>5001712</v>
       </c>
       <c r="B1284" s="26">
         <v>1</v>
@@ -40238,13 +40218,13 @@
         <v>888</v>
       </c>
       <c r="E1284" s="19" t="s">
-        <v>327</v>
+        <v>887</v>
       </c>
       <c r="G1284" s="26">
         <v>10</v>
       </c>
       <c r="H1284" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1284">
         <v>0</v>
@@ -40252,7 +40232,7 @@
     </row>
     <row r="1285" spans="1:9">
       <c r="A1285" s="26">
-        <v>5001716</v>
+        <v>5001715</v>
       </c>
       <c r="B1285" s="26">
         <v>1</v>
@@ -40264,39 +40244,39 @@
         <v>888</v>
       </c>
       <c r="E1285" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1285" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1285" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:9">
+      <c r="A1286" s="26">
+        <v>5001716</v>
+      </c>
+      <c r="B1286" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1286" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1286" s="26" t="s">
+        <v>888</v>
+      </c>
+      <c r="E1286" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="G1285" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1285" s="26">
+      <c r="G1286" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1286" s="26">
         <v>2</v>
-      </c>
-      <c r="I1285">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1286" spans="1:9">
-      <c r="A1286">
-        <v>920071</v>
-      </c>
-      <c r="B1286" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1286">
-        <v>0</v>
-      </c>
-      <c r="D1286" s="28" t="s">
-        <v>889</v>
-      </c>
-      <c r="E1286" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1286">
-        <v>10</v>
-      </c>
-      <c r="H1286">
-        <v>1</v>
       </c>
       <c r="I1286">
         <v>0</v>
@@ -40304,7 +40284,7 @@
     </row>
     <row r="1287" spans="1:9">
       <c r="A1287">
-        <v>1920071</v>
+        <v>920071</v>
       </c>
       <c r="B1287" s="26">
         <v>1</v>
@@ -40313,10 +40293,10 @@
         <v>0</v>
       </c>
       <c r="D1287" s="28" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E1287" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1287">
         <v>10</v>
@@ -40330,7 +40310,7 @@
     </row>
     <row r="1288" spans="1:9">
       <c r="A1288">
-        <v>2920071</v>
+        <v>1920071</v>
       </c>
       <c r="B1288" s="26">
         <v>1</v>
@@ -40339,7 +40319,7 @@
         <v>0</v>
       </c>
       <c r="D1288" s="28" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E1288" s="29" t="s">
         <v>769</v>
@@ -40356,7 +40336,7 @@
     </row>
     <row r="1289" spans="1:9">
       <c r="A1289">
-        <v>3920071</v>
+        <v>2920071</v>
       </c>
       <c r="B1289" s="26">
         <v>1</v>
@@ -40365,7 +40345,7 @@
         <v>0</v>
       </c>
       <c r="D1289" s="28" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E1289" s="29" t="s">
         <v>769</v>
@@ -40382,7 +40362,7 @@
     </row>
     <row r="1290" spans="1:9">
       <c r="A1290">
-        <v>4920071</v>
+        <v>3920071</v>
       </c>
       <c r="B1290" s="26">
         <v>1</v>
@@ -40391,7 +40371,7 @@
         <v>0</v>
       </c>
       <c r="D1290" s="28" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E1290" s="29" t="s">
         <v>769</v>
@@ -40403,12 +40383,12 @@
         <v>1</v>
       </c>
       <c r="I1290">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1291" spans="1:9">
       <c r="A1291">
-        <v>5920071</v>
+        <v>4920071</v>
       </c>
       <c r="B1291" s="26">
         <v>1</v>
@@ -40417,7 +40397,7 @@
         <v>0</v>
       </c>
       <c r="D1291" s="28" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E1291" s="29" t="s">
         <v>769</v>
@@ -40429,12 +40409,12 @@
         <v>1</v>
       </c>
       <c r="I1291">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1292" spans="1:9">
       <c r="A1292">
-        <v>6920071</v>
+        <v>5920071</v>
       </c>
       <c r="B1292" s="26">
         <v>1</v>
@@ -40443,7 +40423,7 @@
         <v>0</v>
       </c>
       <c r="D1292" s="28" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E1292" s="29" t="s">
         <v>769</v>
@@ -40460,7 +40440,7 @@
     </row>
     <row r="1293" spans="1:9">
       <c r="A1293">
-        <v>7920071</v>
+        <v>6920071</v>
       </c>
       <c r="B1293" s="26">
         <v>1</v>
@@ -40469,7 +40449,7 @@
         <v>0</v>
       </c>
       <c r="D1293" s="28" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E1293" s="29" t="s">
         <v>769</v>
@@ -40478,15 +40458,15 @@
         <v>10</v>
       </c>
       <c r="H1293">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1293">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1294" spans="1:9">
       <c r="A1294">
-        <v>8920071</v>
+        <v>7920071</v>
       </c>
       <c r="B1294" s="26">
         <v>1</v>
@@ -40495,7 +40475,7 @@
         <v>0</v>
       </c>
       <c r="D1294" s="28" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E1294" s="29" t="s">
         <v>769</v>
@@ -40504,15 +40484,15 @@
         <v>10</v>
       </c>
       <c r="H1294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1294">
-        <v>0</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="1295" spans="1:9">
       <c r="A1295">
-        <v>9920071</v>
+        <v>8920071</v>
       </c>
       <c r="B1295" s="26">
         <v>1</v>
@@ -40521,7 +40501,7 @@
         <v>0</v>
       </c>
       <c r="D1295" s="28" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E1295" s="29" t="s">
         <v>769</v>
@@ -40530,15 +40510,15 @@
         <v>10</v>
       </c>
       <c r="H1295">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1295">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1296" spans="1:9">
       <c r="A1296">
-        <v>13920071</v>
+        <v>9920071</v>
       </c>
       <c r="B1296" s="26">
         <v>1</v>
@@ -40547,7 +40527,7 @@
         <v>0</v>
       </c>
       <c r="D1296" s="28" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E1296" s="29" t="s">
         <v>769</v>
@@ -40556,15 +40536,15 @@
         <v>10</v>
       </c>
       <c r="H1296">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1296">
-        <v>1</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="1297" spans="1:9">
       <c r="A1297">
-        <v>920072</v>
+        <v>13920071</v>
       </c>
       <c r="B1297" s="26">
         <v>1</v>
@@ -40573,12 +40553,11 @@
         <v>0</v>
       </c>
       <c r="D1297" s="28" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E1297" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1297" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1297">
         <v>10</v>
       </c>
@@ -40586,12 +40565,12 @@
         <v>1</v>
       </c>
       <c r="I1297">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1298" spans="1:9">
       <c r="A1298">
-        <v>820072</v>
+        <v>920072</v>
       </c>
       <c r="B1298" s="26">
         <v>1</v>
@@ -40599,12 +40578,13 @@
       <c r="C1298">
         <v>0</v>
       </c>
-      <c r="D1298" s="30" t="s">
-        <v>901</v>
-      </c>
-      <c r="E1298" s="30" t="s">
-        <v>901</v>
-      </c>
+      <c r="D1298" s="28" t="s">
+        <v>900</v>
+      </c>
+      <c r="E1298" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1298" s="28"/>
       <c r="G1298">
         <v>10</v>
       </c>
@@ -40617,7 +40597,7 @@
     </row>
     <row r="1299" spans="1:9">
       <c r="A1299">
-        <v>920081</v>
+        <v>820072</v>
       </c>
       <c r="B1299" s="26">
         <v>1</v>
@@ -40625,11 +40605,11 @@
       <c r="C1299">
         <v>0</v>
       </c>
-      <c r="D1299" s="28" t="s">
-        <v>902</v>
-      </c>
-      <c r="E1299" s="29" t="s">
-        <v>767</v>
+      <c r="D1299" s="30" t="s">
+        <v>901</v>
+      </c>
+      <c r="E1299" s="30" t="s">
+        <v>901</v>
       </c>
       <c r="G1299">
         <v>10</v>
@@ -40643,7 +40623,7 @@
     </row>
     <row r="1300" spans="1:9">
       <c r="A1300">
-        <v>1920081</v>
+        <v>920081</v>
       </c>
       <c r="B1300" s="26">
         <v>1</v>
@@ -40652,10 +40632,10 @@
         <v>0</v>
       </c>
       <c r="D1300" s="28" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E1300" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1300">
         <v>10</v>
@@ -40664,12 +40644,12 @@
         <v>1</v>
       </c>
       <c r="I1300">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1301" spans="1:9">
       <c r="A1301">
-        <v>2920081</v>
+        <v>1920081</v>
       </c>
       <c r="B1301" s="26">
         <v>1</v>
@@ -40678,7 +40658,7 @@
         <v>0</v>
       </c>
       <c r="D1301" s="28" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E1301" s="29" t="s">
         <v>769</v>
@@ -40690,12 +40670,12 @@
         <v>1</v>
       </c>
       <c r="I1301">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1302" spans="1:9">
       <c r="A1302">
-        <v>3920081</v>
+        <v>2920081</v>
       </c>
       <c r="B1302" s="26">
         <v>1</v>
@@ -40704,7 +40684,7 @@
         <v>0</v>
       </c>
       <c r="D1302" s="28" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E1302" s="29" t="s">
         <v>769</v>
@@ -40721,7 +40701,7 @@
     </row>
     <row r="1303" spans="1:9">
       <c r="A1303">
-        <v>4920081</v>
+        <v>3920081</v>
       </c>
       <c r="B1303" s="26">
         <v>1</v>
@@ -40730,7 +40710,7 @@
         <v>0</v>
       </c>
       <c r="D1303" s="28" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1303" s="29" t="s">
         <v>769</v>
@@ -40742,12 +40722,12 @@
         <v>1</v>
       </c>
       <c r="I1303">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1304" spans="1:9">
       <c r="A1304">
-        <v>5920081</v>
+        <v>4920081</v>
       </c>
       <c r="B1304" s="26">
         <v>1</v>
@@ -40756,7 +40736,7 @@
         <v>0</v>
       </c>
       <c r="D1304" s="28" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E1304" s="29" t="s">
         <v>769</v>
@@ -40768,12 +40748,12 @@
         <v>1</v>
       </c>
       <c r="I1304">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1305" spans="1:9">
       <c r="A1305">
-        <v>6920081</v>
+        <v>5920081</v>
       </c>
       <c r="B1305" s="26">
         <v>1</v>
@@ -40782,7 +40762,7 @@
         <v>0</v>
       </c>
       <c r="D1305" s="28" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E1305" s="29" t="s">
         <v>769</v>
@@ -40799,7 +40779,7 @@
     </row>
     <row r="1306" spans="1:9">
       <c r="A1306">
-        <v>7920081</v>
+        <v>6920081</v>
       </c>
       <c r="B1306" s="26">
         <v>1</v>
@@ -40808,7 +40788,7 @@
         <v>0</v>
       </c>
       <c r="D1306" s="28" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E1306" s="29" t="s">
         <v>769</v>
@@ -40817,15 +40797,15 @@
         <v>10</v>
       </c>
       <c r="H1306">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1306">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1307" spans="1:9">
       <c r="A1307">
-        <v>8920081</v>
+        <v>7920081</v>
       </c>
       <c r="B1307" s="26">
         <v>1</v>
@@ -40834,7 +40814,7 @@
         <v>0</v>
       </c>
       <c r="D1307" s="28" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1307" s="29" t="s">
         <v>769</v>
@@ -40843,15 +40823,15 @@
         <v>10</v>
       </c>
       <c r="H1307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1307">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1308" spans="1:9">
       <c r="A1308">
-        <v>9920081</v>
+        <v>8920081</v>
       </c>
       <c r="B1308" s="26">
         <v>1</v>
@@ -40860,7 +40840,7 @@
         <v>0</v>
       </c>
       <c r="D1308" s="28" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E1308" s="29" t="s">
         <v>769</v>
@@ -40869,15 +40849,15 @@
         <v>10</v>
       </c>
       <c r="H1308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1308">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
       <c r="A1309">
-        <v>10920081</v>
+        <v>9920081</v>
       </c>
       <c r="B1309" s="26">
         <v>1</v>
@@ -40886,25 +40866,24 @@
         <v>0</v>
       </c>
       <c r="D1309" s="28" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E1309" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1309" s="28"/>
       <c r="G1309">
         <v>10</v>
       </c>
       <c r="H1309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1309">
-        <v>6000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1310" spans="1:9">
       <c r="A1310">
-        <v>11920081</v>
+        <v>10920081</v>
       </c>
       <c r="B1310" s="26">
         <v>1</v>
@@ -40913,7 +40892,7 @@
         <v>0</v>
       </c>
       <c r="D1310" s="28" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1310" s="29" t="s">
         <v>769</v>
@@ -40926,12 +40905,12 @@
         <v>1</v>
       </c>
       <c r="I1310">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1311" spans="1:9">
       <c r="A1311">
-        <v>13920081</v>
+        <v>11920081</v>
       </c>
       <c r="B1311" s="26">
         <v>1</v>
@@ -40940,7 +40919,7 @@
         <v>0</v>
       </c>
       <c r="D1311" s="28" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E1311" s="29" t="s">
         <v>769</v>
@@ -40953,12 +40932,12 @@
         <v>1</v>
       </c>
       <c r="I1311">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1312" spans="1:9">
       <c r="A1312">
-        <v>14920081</v>
+        <v>13920081</v>
       </c>
       <c r="B1312" s="26">
         <v>1</v>
@@ -40967,7 +40946,7 @@
         <v>0</v>
       </c>
       <c r="D1312" s="28" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E1312" s="29" t="s">
         <v>769</v>
@@ -40980,12 +40959,12 @@
         <v>1</v>
       </c>
       <c r="I1312">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1313" spans="1:9">
       <c r="A1313">
-        <v>920083</v>
+        <v>14920081</v>
       </c>
       <c r="B1313" s="26">
         <v>1</v>
@@ -40994,11 +40973,12 @@
         <v>0</v>
       </c>
       <c r="D1313" s="28" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E1313" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1313" s="28"/>
       <c r="G1313">
         <v>10</v>
       </c>
@@ -41006,51 +40986,50 @@
         <v>1</v>
       </c>
       <c r="I1313">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1314" spans="1:9">
       <c r="A1314">
+        <v>920083</v>
+      </c>
+      <c r="B1314" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1314">
+        <v>0</v>
+      </c>
+      <c r="D1314" s="28" t="s">
+        <v>916</v>
+      </c>
+      <c r="E1314" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1314">
+        <v>10</v>
+      </c>
+      <c r="H1314">
+        <v>1</v>
+      </c>
+      <c r="I1314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:9">
+      <c r="A1315">
         <v>14920083</v>
       </c>
-      <c r="B1314" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1314">
-        <v>0</v>
-      </c>
-      <c r="D1314" s="28" t="s">
+      <c r="B1315" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1315">
+        <v>0</v>
+      </c>
+      <c r="D1315" s="28" t="s">
         <v>917</v>
       </c>
-      <c r="E1314" s="29" t="s">
+      <c r="E1315" s="29" t="s">
         <v>769</v>
-      </c>
-      <c r="F1314" s="28"/>
-      <c r="G1314">
-        <v>10</v>
-      </c>
-      <c r="H1314">
-        <v>1</v>
-      </c>
-      <c r="I1314">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1315" spans="1:9">
-      <c r="A1315" s="31">
-        <v>920082</v>
-      </c>
-      <c r="B1315" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1315">
-        <v>0</v>
-      </c>
-      <c r="D1315" s="28" t="s">
-        <v>918</v>
-      </c>
-      <c r="E1315" s="29" t="s">
-        <v>767</v>
       </c>
       <c r="F1315" s="28"/>
       <c r="G1315">
@@ -41060,12 +41039,12 @@
         <v>1</v>
       </c>
       <c r="I1315">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1316" spans="1:9">
-      <c r="A1316" s="30">
-        <v>820082</v>
+      <c r="A1316" s="31">
+        <v>920082</v>
       </c>
       <c r="B1316" s="26">
         <v>1</v>
@@ -41073,12 +41052,13 @@
       <c r="C1316">
         <v>0</v>
       </c>
-      <c r="D1316" s="30" t="s">
-        <v>919</v>
-      </c>
-      <c r="E1316" s="30" t="s">
-        <v>919</v>
-      </c>
+      <c r="D1316" s="28" t="s">
+        <v>918</v>
+      </c>
+      <c r="E1316" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1316" s="28"/>
       <c r="G1316">
         <v>10</v>
       </c>
@@ -41091,45 +41071,45 @@
     </row>
     <row r="1317" spans="1:9">
       <c r="A1317" s="30">
+        <v>820082</v>
+      </c>
+      <c r="B1317" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1317">
+        <v>0</v>
+      </c>
+      <c r="D1317" s="30" t="s">
+        <v>919</v>
+      </c>
+      <c r="E1317" s="30" t="s">
+        <v>919</v>
+      </c>
+      <c r="G1317">
+        <v>10</v>
+      </c>
+      <c r="H1317">
+        <v>1</v>
+      </c>
+      <c r="I1317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:9">
+      <c r="A1318" s="30">
         <v>820083</v>
       </c>
-      <c r="B1317" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1317">
-        <v>0</v>
-      </c>
-      <c r="D1317" s="30" t="s">
+      <c r="B1318" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1318">
+        <v>0</v>
+      </c>
+      <c r="D1318" s="30" t="s">
         <v>920</v>
       </c>
-      <c r="E1317" s="30" t="s">
+      <c r="E1318" s="30" t="s">
         <v>920</v>
-      </c>
-      <c r="G1317">
-        <v>10</v>
-      </c>
-      <c r="H1317">
-        <v>1</v>
-      </c>
-      <c r="I1317">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1318" spans="1:9">
-      <c r="A1318">
-        <v>920074</v>
-      </c>
-      <c r="B1318" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1318">
-        <v>0</v>
-      </c>
-      <c r="D1318" s="28" t="s">
-        <v>921</v>
-      </c>
-      <c r="E1318" s="29" t="s">
-        <v>767</v>
       </c>
       <c r="G1318">
         <v>10</v>
@@ -41143,7 +41123,7 @@
     </row>
     <row r="1319" spans="1:9">
       <c r="A1319">
-        <v>14920074</v>
+        <v>920074</v>
       </c>
       <c r="B1319" s="26">
         <v>1</v>
@@ -41152,12 +41132,11 @@
         <v>0</v>
       </c>
       <c r="D1319" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E1319" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1319" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1319">
         <v>10</v>
       </c>
@@ -41165,12 +41144,12 @@
         <v>1</v>
       </c>
       <c r="I1319">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1320" spans="1:9">
       <c r="A1320">
-        <v>16920074</v>
+        <v>14920074</v>
       </c>
       <c r="B1320" s="26">
         <v>1</v>
@@ -41179,7 +41158,7 @@
         <v>0</v>
       </c>
       <c r="D1320" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E1320" s="29" t="s">
         <v>769</v>
@@ -41189,15 +41168,15 @@
         <v>10</v>
       </c>
       <c r="H1320">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1320">
-        <v>12000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1321" spans="1:9">
       <c r="A1321">
-        <v>17920074</v>
+        <v>16920074</v>
       </c>
       <c r="B1321" s="26">
         <v>1</v>
@@ -41206,7 +41185,7 @@
         <v>0</v>
       </c>
       <c r="D1321" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E1321" s="29" t="s">
         <v>769</v>
@@ -41219,12 +41198,12 @@
         <v>2</v>
       </c>
       <c r="I1321">
-        <v>8000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1322" spans="1:9">
       <c r="A1322">
-        <v>18920074</v>
+        <v>17920074</v>
       </c>
       <c r="B1322" s="26">
         <v>1</v>
@@ -41233,7 +41212,7 @@
         <v>0</v>
       </c>
       <c r="D1322" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E1322" s="29" t="s">
         <v>769</v>
@@ -41246,12 +41225,12 @@
         <v>2</v>
       </c>
       <c r="I1322">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1323" spans="1:9">
       <c r="A1323">
-        <v>920073</v>
+        <v>18920074</v>
       </c>
       <c r="B1323" s="26">
         <v>1</v>
@@ -41260,25 +41239,25 @@
         <v>0</v>
       </c>
       <c r="D1323" s="28" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E1323" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1323" s="28"/>
       <c r="G1323">
         <v>10</v>
       </c>
       <c r="H1323">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1323">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1324" spans="1:9">
       <c r="A1324">
-        <v>820073</v>
+        <v>920073</v>
       </c>
       <c r="B1324" s="26">
         <v>1</v>
@@ -41286,12 +41265,13 @@
       <c r="C1324">
         <v>0</v>
       </c>
-      <c r="D1324" s="30" t="s">
-        <v>927</v>
-      </c>
-      <c r="E1324" s="30" t="s">
-        <v>927</v>
-      </c>
+      <c r="D1324" s="28" t="s">
+        <v>926</v>
+      </c>
+      <c r="E1324" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1324" s="28"/>
       <c r="G1324">
         <v>10</v>
       </c>
@@ -41304,7 +41284,7 @@
     </row>
     <row r="1325" spans="1:9">
       <c r="A1325">
-        <v>920084</v>
+        <v>820073</v>
       </c>
       <c r="B1325" s="26">
         <v>1</v>
@@ -41312,11 +41292,11 @@
       <c r="C1325">
         <v>0</v>
       </c>
-      <c r="D1325" s="28" t="s">
-        <v>928</v>
-      </c>
-      <c r="E1325" s="29" t="s">
-        <v>767</v>
+      <c r="D1325" s="30" t="s">
+        <v>927</v>
+      </c>
+      <c r="E1325" s="30" t="s">
+        <v>927</v>
       </c>
       <c r="G1325">
         <v>10</v>
@@ -41330,7 +41310,7 @@
     </row>
     <row r="1326" spans="1:9">
       <c r="A1326">
-        <v>1920084</v>
+        <v>920084</v>
       </c>
       <c r="B1326" s="26">
         <v>1</v>
@@ -41339,10 +41319,10 @@
         <v>0</v>
       </c>
       <c r="D1326" s="28" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E1326" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1326">
         <v>10</v>
@@ -41351,12 +41331,12 @@
         <v>1</v>
       </c>
       <c r="I1326">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1327" spans="1:9">
       <c r="A1327">
-        <v>2920084</v>
+        <v>1920084</v>
       </c>
       <c r="B1327" s="26">
         <v>1</v>
@@ -41365,7 +41345,7 @@
         <v>0</v>
       </c>
       <c r="D1327" s="28" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E1327" s="29" t="s">
         <v>769</v>
@@ -41377,12 +41357,12 @@
         <v>1</v>
       </c>
       <c r="I1327">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1328" spans="1:9">
       <c r="A1328">
-        <v>3920084</v>
+        <v>2920084</v>
       </c>
       <c r="B1328" s="26">
         <v>1</v>
@@ -41391,7 +41371,7 @@
         <v>0</v>
       </c>
       <c r="D1328" s="28" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E1328" s="29" t="s">
         <v>769</v>
@@ -41408,7 +41388,7 @@
     </row>
     <row r="1329" spans="1:9">
       <c r="A1329">
-        <v>4920084</v>
+        <v>3920084</v>
       </c>
       <c r="B1329" s="26">
         <v>1</v>
@@ -41417,7 +41397,7 @@
         <v>0</v>
       </c>
       <c r="D1329" s="28" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E1329" s="29" t="s">
         <v>769</v>
@@ -41429,12 +41409,12 @@
         <v>1</v>
       </c>
       <c r="I1329">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1330" spans="1:9">
       <c r="A1330">
-        <v>5920084</v>
+        <v>4920084</v>
       </c>
       <c r="B1330" s="26">
         <v>1</v>
@@ -41443,7 +41423,7 @@
         <v>0</v>
       </c>
       <c r="D1330" s="28" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E1330" s="29" t="s">
         <v>769</v>
@@ -41455,12 +41435,12 @@
         <v>1</v>
       </c>
       <c r="I1330">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1331" spans="1:9">
       <c r="A1331">
-        <v>6920084</v>
+        <v>5920084</v>
       </c>
       <c r="B1331" s="26">
         <v>1</v>
@@ -41469,7 +41449,7 @@
         <v>0</v>
       </c>
       <c r="D1331" s="28" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E1331" s="29" t="s">
         <v>769</v>
@@ -41486,7 +41466,7 @@
     </row>
     <row r="1332" spans="1:9">
       <c r="A1332">
-        <v>7920084</v>
+        <v>6920084</v>
       </c>
       <c r="B1332" s="26">
         <v>1</v>
@@ -41495,7 +41475,7 @@
         <v>0</v>
       </c>
       <c r="D1332" s="28" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E1332" s="29" t="s">
         <v>769</v>
@@ -41504,7 +41484,7 @@
         <v>10</v>
       </c>
       <c r="H1332">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1332">
         <v>0</v>
@@ -41512,7 +41492,7 @@
     </row>
     <row r="1333" spans="1:9">
       <c r="A1333">
-        <v>8920084</v>
+        <v>7920084</v>
       </c>
       <c r="B1333" s="26">
         <v>1</v>
@@ -41521,7 +41501,7 @@
         <v>0</v>
       </c>
       <c r="D1333" s="28" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E1333" s="29" t="s">
         <v>769</v>
@@ -41530,7 +41510,7 @@
         <v>10</v>
       </c>
       <c r="H1333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1333">
         <v>0</v>
@@ -41538,7 +41518,7 @@
     </row>
     <row r="1334" spans="1:9">
       <c r="A1334">
-        <v>9920084</v>
+        <v>8920084</v>
       </c>
       <c r="B1334" s="26">
         <v>1</v>
@@ -41547,7 +41527,7 @@
         <v>0</v>
       </c>
       <c r="D1334" s="28" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E1334" s="29" t="s">
         <v>769</v>
@@ -41556,7 +41536,7 @@
         <v>10</v>
       </c>
       <c r="H1334">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1334">
         <v>0</v>
@@ -41564,7 +41544,7 @@
     </row>
     <row r="1335" spans="1:9">
       <c r="A1335">
-        <v>13920084</v>
+        <v>9920084</v>
       </c>
       <c r="B1335" s="26">
         <v>1</v>
@@ -41573,7 +41553,7 @@
         <v>0</v>
       </c>
       <c r="D1335" s="28" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E1335" s="29" t="s">
         <v>769</v>
@@ -41582,15 +41562,15 @@
         <v>10</v>
       </c>
       <c r="H1335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1335">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1336" spans="1:9">
       <c r="A1336">
-        <v>16920084</v>
+        <v>13920084</v>
       </c>
       <c r="B1336" s="26">
         <v>1</v>
@@ -41599,12 +41579,11 @@
         <v>0</v>
       </c>
       <c r="D1336" s="28" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E1336" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1336" s="28"/>
       <c r="G1336">
         <v>10</v>
       </c>
@@ -41612,12 +41591,12 @@
         <v>1</v>
       </c>
       <c r="I1336">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1337" spans="1:9">
       <c r="A1337">
-        <v>920085</v>
+        <v>16920084</v>
       </c>
       <c r="B1337" s="26">
         <v>1</v>
@@ -41626,11 +41605,12 @@
         <v>0</v>
       </c>
       <c r="D1337" s="28" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E1337" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1337" s="28"/>
       <c r="G1337">
         <v>10</v>
       </c>
@@ -41638,12 +41618,12 @@
         <v>1</v>
       </c>
       <c r="I1337">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1338" spans="1:9">
       <c r="A1338">
-        <v>1920085</v>
+        <v>920085</v>
       </c>
       <c r="B1338" s="26">
         <v>1</v>
@@ -41652,10 +41632,10 @@
         <v>0</v>
       </c>
       <c r="D1338" s="28" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E1338" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1338">
         <v>10</v>
@@ -41669,7 +41649,7 @@
     </row>
     <row r="1339" spans="1:9">
       <c r="A1339">
-        <v>2920085</v>
+        <v>1920085</v>
       </c>
       <c r="B1339" s="26">
         <v>1</v>
@@ -41678,7 +41658,7 @@
         <v>0</v>
       </c>
       <c r="D1339" s="28" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E1339" s="29" t="s">
         <v>769</v>
@@ -41695,7 +41675,7 @@
     </row>
     <row r="1340" spans="1:9">
       <c r="A1340">
-        <v>3920085</v>
+        <v>2920085</v>
       </c>
       <c r="B1340" s="26">
         <v>1</v>
@@ -41704,7 +41684,7 @@
         <v>0</v>
       </c>
       <c r="D1340" s="28" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E1340" s="29" t="s">
         <v>769</v>
@@ -41721,7 +41701,7 @@
     </row>
     <row r="1341" spans="1:9">
       <c r="A1341">
-        <v>4920085</v>
+        <v>3920085</v>
       </c>
       <c r="B1341" s="26">
         <v>1</v>
@@ -41730,7 +41710,7 @@
         <v>0</v>
       </c>
       <c r="D1341" s="28" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E1341" s="29" t="s">
         <v>769</v>
@@ -41747,7 +41727,7 @@
     </row>
     <row r="1342" spans="1:9">
       <c r="A1342">
-        <v>5920085</v>
+        <v>4920085</v>
       </c>
       <c r="B1342" s="26">
         <v>1</v>
@@ -41756,7 +41736,7 @@
         <v>0</v>
       </c>
       <c r="D1342" s="28" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E1342" s="29" t="s">
         <v>769</v>
@@ -41768,12 +41748,12 @@
         <v>1</v>
       </c>
       <c r="I1342">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1343" spans="1:9">
       <c r="A1343">
-        <v>6920085</v>
+        <v>5920085</v>
       </c>
       <c r="B1343" s="26">
         <v>1</v>
@@ -41782,7 +41762,7 @@
         <v>0</v>
       </c>
       <c r="D1343" s="28" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E1343" s="29" t="s">
         <v>769</v>
@@ -41794,12 +41774,12 @@
         <v>1</v>
       </c>
       <c r="I1343">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1344" spans="1:9">
       <c r="A1344">
-        <v>7920085</v>
+        <v>6920085</v>
       </c>
       <c r="B1344" s="26">
         <v>1</v>
@@ -41808,7 +41788,7 @@
         <v>0</v>
       </c>
       <c r="D1344" s="28" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E1344" s="29" t="s">
         <v>769</v>
@@ -41817,15 +41797,15 @@
         <v>10</v>
       </c>
       <c r="H1344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1344">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1345" spans="1:9">
       <c r="A1345">
-        <v>8920085</v>
+        <v>7920085</v>
       </c>
       <c r="B1345" s="26">
         <v>1</v>
@@ -41834,7 +41814,7 @@
         <v>0</v>
       </c>
       <c r="D1345" s="28" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E1345" s="29" t="s">
         <v>769</v>
@@ -41843,15 +41823,15 @@
         <v>10</v>
       </c>
       <c r="H1345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1345">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1346" spans="1:9">
       <c r="A1346">
-        <v>9920085</v>
+        <v>8920085</v>
       </c>
       <c r="B1346" s="26">
         <v>1</v>
@@ -41860,7 +41840,7 @@
         <v>0</v>
       </c>
       <c r="D1346" s="28" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E1346" s="29" t="s">
         <v>769</v>
@@ -41869,15 +41849,15 @@
         <v>10</v>
       </c>
       <c r="H1346">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1346">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1347" spans="1:9">
       <c r="A1347">
-        <v>920086</v>
+        <v>9920085</v>
       </c>
       <c r="B1347" s="26">
         <v>1</v>
@@ -41886,25 +41866,24 @@
         <v>0</v>
       </c>
       <c r="D1347" s="28" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E1347" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1347" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1347">
         <v>10</v>
       </c>
       <c r="H1347">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1347">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1348" spans="1:9">
       <c r="A1348">
-        <v>820086</v>
+        <v>920086</v>
       </c>
       <c r="B1348" s="26">
         <v>1</v>
@@ -41912,12 +41891,13 @@
       <c r="C1348">
         <v>0</v>
       </c>
-      <c r="D1348" s="30" t="s">
-        <v>951</v>
-      </c>
-      <c r="E1348" s="30" t="s">
-        <v>951</v>
-      </c>
+      <c r="D1348" s="28" t="s">
+        <v>950</v>
+      </c>
+      <c r="E1348" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1348" s="28"/>
       <c r="G1348">
         <v>10</v>
       </c>
@@ -41930,7 +41910,7 @@
     </row>
     <row r="1349" spans="1:9">
       <c r="A1349">
-        <v>8200861</v>
+        <v>820086</v>
       </c>
       <c r="B1349" s="26">
         <v>1</v>
@@ -41939,16 +41919,16 @@
         <v>0</v>
       </c>
       <c r="D1349" s="30" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E1349" s="30" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="G1349">
         <v>10</v>
       </c>
       <c r="H1349">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1349">
         <v>0</v>
@@ -41956,7 +41936,7 @@
     </row>
     <row r="1350" spans="1:9">
       <c r="A1350">
-        <v>990001</v>
+        <v>8200861</v>
       </c>
       <c r="B1350" s="26">
         <v>1</v>
@@ -41964,26 +41944,25 @@
       <c r="C1350">
         <v>0</v>
       </c>
-      <c r="D1350" s="28" t="s">
-        <v>954</v>
-      </c>
-      <c r="E1350" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1350" s="28"/>
+      <c r="D1350" s="30" t="s">
+        <v>952</v>
+      </c>
+      <c r="E1350" s="30" t="s">
+        <v>953</v>
+      </c>
       <c r="G1350">
         <v>10</v>
       </c>
       <c r="H1350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1350">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1351" spans="1:9">
       <c r="A1351">
-        <v>890001</v>
+        <v>990001</v>
       </c>
       <c r="B1351" s="26">
         <v>1</v>
@@ -41992,11 +41971,12 @@
         <v>0</v>
       </c>
       <c r="D1351" s="28" t="s">
-        <v>955</v>
-      </c>
-      <c r="E1351" s="28" t="s">
-        <v>955</v>
-      </c>
+        <v>954</v>
+      </c>
+      <c r="E1351" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1351" s="28"/>
       <c r="G1351">
         <v>10</v>
       </c>
@@ -42004,12 +41984,12 @@
         <v>1</v>
       </c>
       <c r="I1351">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1352" spans="1:9">
       <c r="A1352">
-        <v>890011</v>
+        <v>890001</v>
       </c>
       <c r="B1352" s="26">
         <v>1</v>
@@ -42018,16 +41998,16 @@
         <v>0</v>
       </c>
       <c r="D1352" s="28" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E1352" s="28" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G1352">
         <v>10</v>
       </c>
       <c r="H1352">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1352">
         <v>0</v>
@@ -42035,7 +42015,7 @@
     </row>
     <row r="1353" spans="1:9">
       <c r="A1353">
-        <v>890021</v>
+        <v>890011</v>
       </c>
       <c r="B1353" s="26">
         <v>1</v>
@@ -42044,16 +42024,16 @@
         <v>0</v>
       </c>
       <c r="D1353" s="28" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E1353" s="28" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="G1353">
         <v>10</v>
       </c>
       <c r="H1353">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1353">
         <v>0</v>
@@ -42061,27 +42041,53 @@
     </row>
     <row r="1354" spans="1:9">
       <c r="A1354">
+        <v>890021</v>
+      </c>
+      <c r="B1354" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1354">
+        <v>0</v>
+      </c>
+      <c r="D1354" s="28" t="s">
+        <v>957</v>
+      </c>
+      <c r="E1354" s="28" t="s">
+        <v>958</v>
+      </c>
+      <c r="G1354">
+        <v>10</v>
+      </c>
+      <c r="H1354">
+        <v>1</v>
+      </c>
+      <c r="I1354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:9">
+      <c r="A1355">
         <v>890022</v>
       </c>
-      <c r="B1354" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1354">
-        <v>0</v>
-      </c>
-      <c r="D1354" s="28" t="s">
+      <c r="B1355" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1355">
+        <v>0</v>
+      </c>
+      <c r="D1355" s="28" t="s">
         <v>959</v>
       </c>
-      <c r="E1354" s="28" t="s">
+      <c r="E1355" s="28" t="s">
         <v>960</v>
       </c>
-      <c r="G1354">
-        <v>10</v>
-      </c>
-      <c r="H1354">
+      <c r="G1355">
+        <v>10</v>
+      </c>
+      <c r="H1355">
         <v>2</v>
       </c>
-      <c r="I1354">
+      <c r="I1355">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -11,7 +11,7 @@
     <sheet name="maze_attribute_formula_v8" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1351</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1356</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3646" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="1002">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2781,6 +2781,9 @@
   </si>
   <si>
     <t>暴风雪_极寒领域获得</t>
+  </si>
+  <si>
+    <t>暴风雪_极寒领域冷却</t>
   </si>
   <si>
     <t>暴风雪_极寒领域技能持续时间</t>
@@ -4367,7 +4370,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1355"/>
+  <dimension ref="A1:I1360"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -39450,7 +39453,7 @@
         <v>1</v>
       </c>
       <c r="I1254">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1255" spans="1:9">
@@ -39745,258 +39748,186 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1266" spans="2:6">
-      <c r="B1266" s="26"/>
-      <c r="D1266" s="28"/>
-      <c r="E1266" s="29"/>
+    <row r="1266" spans="1:9">
+      <c r="A1266">
+        <v>1920062</v>
+      </c>
+      <c r="B1266" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1266">
+        <v>0</v>
+      </c>
+      <c r="D1266" s="28" t="s">
+        <v>876</v>
+      </c>
+      <c r="E1266" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="F1266" s="28"/>
-    </row>
-    <row r="1267" spans="1:9">
+      <c r="G1266">
+        <v>10</v>
+      </c>
+      <c r="H1266">
+        <v>1</v>
+      </c>
+      <c r="I1266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:6">
       <c r="A1267">
+        <v>2920062</v>
+      </c>
+      <c r="B1267" s="26"/>
+      <c r="D1267" s="28"/>
+      <c r="E1267" s="29"/>
+      <c r="F1267" s="28"/>
+    </row>
+    <row r="1268" spans="1:6">
+      <c r="A1268">
+        <v>3920062</v>
+      </c>
+      <c r="B1268" s="26"/>
+      <c r="D1268" s="28"/>
+      <c r="E1268" s="29"/>
+      <c r="F1268" s="28"/>
+    </row>
+    <row r="1269" spans="1:6">
+      <c r="A1269">
+        <v>4920062</v>
+      </c>
+      <c r="B1269" s="26"/>
+      <c r="D1269" s="28"/>
+      <c r="E1269" s="29"/>
+      <c r="F1269" s="28"/>
+    </row>
+    <row r="1270" spans="1:6">
+      <c r="A1270">
+        <v>5920062</v>
+      </c>
+      <c r="B1270" s="26"/>
+      <c r="D1270" s="28"/>
+      <c r="E1270" s="29"/>
+      <c r="F1270" s="28"/>
+    </row>
+    <row r="1271" spans="2:6">
+      <c r="B1271" s="26"/>
+      <c r="D1271" s="28"/>
+      <c r="E1271" s="29"/>
+      <c r="F1271" s="28"/>
+    </row>
+    <row r="1272" spans="1:9">
+      <c r="A1272">
         <v>17920061</v>
       </c>
-      <c r="B1267" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1267">
-        <v>0</v>
-      </c>
-      <c r="D1267" s="28" t="s">
-        <v>876</v>
-      </c>
-      <c r="E1267" s="29" t="s">
+      <c r="B1272" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1272">
+        <v>0</v>
+      </c>
+      <c r="D1272" s="28" t="s">
+        <v>877</v>
+      </c>
+      <c r="E1272" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1267" s="28"/>
-      <c r="G1267">
-        <v>10</v>
-      </c>
-      <c r="H1267">
-        <v>1</v>
-      </c>
-      <c r="I1267">
+      <c r="F1272" s="28"/>
+      <c r="G1272">
+        <v>10</v>
+      </c>
+      <c r="H1272">
+        <v>1</v>
+      </c>
+      <c r="I1272">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:9">
+      <c r="A1273">
+        <v>18920061</v>
+      </c>
+      <c r="B1273" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1273">
+        <v>0</v>
+      </c>
+      <c r="D1273" s="28" t="s">
+        <v>878</v>
+      </c>
+      <c r="E1273" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1273" s="28"/>
+      <c r="G1273">
+        <v>10</v>
+      </c>
+      <c r="H1273">
+        <v>1</v>
+      </c>
+      <c r="I1273">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:9">
+      <c r="A1274">
+        <v>19920061</v>
+      </c>
+      <c r="B1274" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1274">
+        <v>0</v>
+      </c>
+      <c r="D1274" s="28" t="s">
+        <v>879</v>
+      </c>
+      <c r="E1274" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1274" s="28"/>
+      <c r="G1274">
+        <v>10</v>
+      </c>
+      <c r="H1274">
+        <v>2</v>
+      </c>
+      <c r="I1274">
         <v>10500</v>
       </c>
     </row>
-    <row r="1268" spans="1:9">
-      <c r="A1268">
-        <v>18920061</v>
-      </c>
-      <c r="B1268" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1268">
-        <v>0</v>
-      </c>
-      <c r="D1268" s="28" t="s">
-        <v>877</v>
-      </c>
-      <c r="E1268" s="29" t="s">
+    <row r="1275" spans="1:9">
+      <c r="A1275">
+        <v>20920061</v>
+      </c>
+      <c r="B1275" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1275">
+        <v>0</v>
+      </c>
+      <c r="D1275" s="28" t="s">
+        <v>880</v>
+      </c>
+      <c r="E1275" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1268" s="28"/>
-      <c r="G1268">
-        <v>10</v>
-      </c>
-      <c r="H1268">
-        <v>1</v>
-      </c>
-      <c r="I1268">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="1269" spans="1:9">
-      <c r="A1269">
-        <v>19920061</v>
-      </c>
-      <c r="B1269" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1269">
-        <v>0</v>
-      </c>
-      <c r="D1269" s="28" t="s">
-        <v>878</v>
-      </c>
-      <c r="E1269" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1269" s="28"/>
-      <c r="G1269">
-        <v>10</v>
-      </c>
-      <c r="H1269">
-        <v>2</v>
-      </c>
-      <c r="I1269">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="1270" spans="1:9">
-      <c r="A1270">
-        <v>20920061</v>
-      </c>
-      <c r="B1270" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1270">
-        <v>0</v>
-      </c>
-      <c r="D1270" s="28" t="s">
-        <v>879</v>
-      </c>
-      <c r="E1270" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1270" s="28"/>
-      <c r="G1270">
-        <v>10</v>
-      </c>
-      <c r="H1270">
-        <v>1</v>
-      </c>
-      <c r="I1270">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1271" spans="1:9">
-      <c r="A1271" s="26">
-        <v>5001600</v>
-      </c>
-      <c r="B1271" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1271" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1271" s="26" t="s">
-        <v>880</v>
-      </c>
-      <c r="E1271" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="F1271" s="9"/>
-      <c r="G1271" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1271" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1271">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1272" spans="1:9">
-      <c r="A1272" s="26">
-        <v>5001501</v>
-      </c>
-      <c r="B1272" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1272" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1272" s="26" t="s">
-        <v>881</v>
-      </c>
-      <c r="E1272" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1272" s="9"/>
-      <c r="G1272" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1272" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1272">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1273" spans="1:9">
-      <c r="A1273" s="26">
-        <v>5001502</v>
-      </c>
-      <c r="B1273" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1273" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1273" s="26" t="s">
-        <v>881</v>
-      </c>
-      <c r="E1273" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1273" s="9"/>
-      <c r="G1273" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1273" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1273">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1274" spans="1:9">
-      <c r="A1274" s="26">
-        <v>5001511</v>
-      </c>
-      <c r="B1274" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1274" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1274" s="26" t="s">
-        <v>882</v>
-      </c>
-      <c r="E1274" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1274" s="9"/>
-      <c r="G1274" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1274" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1274">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1275" spans="1:9">
-      <c r="A1275" s="26">
-        <v>5001512</v>
-      </c>
-      <c r="B1275" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1275" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1275" s="26" t="s">
-        <v>882</v>
-      </c>
-      <c r="E1275" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1275" s="9"/>
-      <c r="G1275" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1275" s="26">
+      <c r="F1275" s="28"/>
+      <c r="G1275">
+        <v>10</v>
+      </c>
+      <c r="H1275">
         <v>1</v>
       </c>
       <c r="I1275">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1276" spans="1:9">
       <c r="A1276" s="26">
-        <v>5001521</v>
+        <v>5001600</v>
       </c>
       <c r="B1276" s="26">
         <v>1</v>
@@ -40005,17 +39936,17 @@
         <v>0</v>
       </c>
       <c r="D1276" s="26" t="s">
-        <v>883</v>
-      </c>
-      <c r="E1276" s="19" t="s">
-        <v>329</v>
+        <v>881</v>
+      </c>
+      <c r="E1276" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="F1276" s="9"/>
       <c r="G1276" s="26">
         <v>10</v>
       </c>
       <c r="H1276" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1276">
         <v>0</v>
@@ -40023,7 +39954,7 @@
     </row>
     <row r="1277" spans="1:9">
       <c r="A1277" s="26">
-        <v>5001522</v>
+        <v>5001501</v>
       </c>
       <c r="B1277" s="26">
         <v>1</v>
@@ -40032,17 +39963,17 @@
         <v>0</v>
       </c>
       <c r="D1277" s="26" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E1277" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1277" s="9"/>
       <c r="G1277" s="26">
         <v>10</v>
       </c>
       <c r="H1277" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1277">
         <v>0</v>
@@ -40050,7 +39981,7 @@
     </row>
     <row r="1278" spans="1:9">
       <c r="A1278" s="26">
-        <v>5001800</v>
+        <v>5001502</v>
       </c>
       <c r="B1278" s="26">
         <v>1</v>
@@ -40059,11 +39990,12 @@
         <v>0</v>
       </c>
       <c r="D1278" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="E1278" s="26" t="s">
-        <v>243</v>
-      </c>
+        <v>882</v>
+      </c>
+      <c r="E1278" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1278" s="9"/>
       <c r="G1278" s="26">
         <v>10</v>
       </c>
@@ -40076,7 +40008,7 @@
     </row>
     <row r="1279" spans="1:9">
       <c r="A1279" s="26">
-        <v>5001701</v>
+        <v>5001511</v>
       </c>
       <c r="B1279" s="26">
         <v>1</v>
@@ -40085,11 +40017,12 @@
         <v>0</v>
       </c>
       <c r="D1279" s="26" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E1279" s="19" t="s">
-        <v>886</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="F1279" s="9"/>
       <c r="G1279" s="26">
         <v>10</v>
       </c>
@@ -40102,7 +40035,7 @@
     </row>
     <row r="1280" spans="1:9">
       <c r="A1280" s="26">
-        <v>5001702</v>
+        <v>5001512</v>
       </c>
       <c r="B1280" s="26">
         <v>1</v>
@@ -40111,16 +40044,17 @@
         <v>0</v>
       </c>
       <c r="D1280" s="26" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E1280" s="19" t="s">
-        <v>887</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="F1280" s="9"/>
       <c r="G1280" s="26">
         <v>10</v>
       </c>
       <c r="H1280" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1280">
         <v>0</v>
@@ -40128,7 +40062,7 @@
     </row>
     <row r="1281" spans="1:9">
       <c r="A1281" s="26">
-        <v>5001705</v>
+        <v>5001521</v>
       </c>
       <c r="B1281" s="26">
         <v>1</v>
@@ -40137,16 +40071,17 @@
         <v>0</v>
       </c>
       <c r="D1281" s="26" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E1281" s="19" t="s">
-        <v>327</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="F1281" s="9"/>
       <c r="G1281" s="26">
         <v>10</v>
       </c>
       <c r="H1281" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1281">
         <v>0</v>
@@ -40154,7 +40089,7 @@
     </row>
     <row r="1282" spans="1:9">
       <c r="A1282" s="26">
-        <v>5001706</v>
+        <v>5001522</v>
       </c>
       <c r="B1282" s="26">
         <v>1</v>
@@ -40163,16 +40098,17 @@
         <v>0</v>
       </c>
       <c r="D1282" s="26" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E1282" s="19" t="s">
-        <v>329</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="F1282" s="9"/>
       <c r="G1282" s="26">
         <v>10</v>
       </c>
       <c r="H1282" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1282">
         <v>0</v>
@@ -40180,7 +40116,7 @@
     </row>
     <row r="1283" spans="1:9">
       <c r="A1283" s="26">
-        <v>5001711</v>
+        <v>5001800</v>
       </c>
       <c r="B1283" s="26">
         <v>1</v>
@@ -40189,16 +40125,16 @@
         <v>0</v>
       </c>
       <c r="D1283" s="26" t="s">
-        <v>888</v>
-      </c>
-      <c r="E1283" s="19" t="s">
-        <v>886</v>
+        <v>885</v>
+      </c>
+      <c r="E1283" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="G1283" s="26">
         <v>10</v>
       </c>
       <c r="H1283" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1283">
         <v>0</v>
@@ -40206,7 +40142,7 @@
     </row>
     <row r="1284" spans="1:9">
       <c r="A1284" s="26">
-        <v>5001712</v>
+        <v>5001701</v>
       </c>
       <c r="B1284" s="26">
         <v>1</v>
@@ -40215,7 +40151,7 @@
         <v>0</v>
       </c>
       <c r="D1284" s="26" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="E1284" s="19" t="s">
         <v>887</v>
@@ -40232,7 +40168,7 @@
     </row>
     <row r="1285" spans="1:9">
       <c r="A1285" s="26">
-        <v>5001715</v>
+        <v>5001702</v>
       </c>
       <c r="B1285" s="26">
         <v>1</v>
@@ -40241,16 +40177,16 @@
         <v>0</v>
       </c>
       <c r="D1285" s="26" t="s">
+        <v>886</v>
+      </c>
+      <c r="E1285" s="19" t="s">
         <v>888</v>
       </c>
-      <c r="E1285" s="19" t="s">
-        <v>327</v>
-      </c>
       <c r="G1285" s="26">
         <v>10</v>
       </c>
       <c r="H1285" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1285">
         <v>0</v>
@@ -40258,163 +40194,163 @@
     </row>
     <row r="1286" spans="1:9">
       <c r="A1286" s="26">
+        <v>5001705</v>
+      </c>
+      <c r="B1286" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1286" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1286" s="26" t="s">
+        <v>886</v>
+      </c>
+      <c r="E1286" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1286" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1286" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:9">
+      <c r="A1287" s="26">
+        <v>5001706</v>
+      </c>
+      <c r="B1287" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1287" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1287" s="26" t="s">
+        <v>886</v>
+      </c>
+      <c r="E1287" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="G1287" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1287" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:9">
+      <c r="A1288" s="26">
+        <v>5001711</v>
+      </c>
+      <c r="B1288" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1288" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1288" s="26" t="s">
+        <v>889</v>
+      </c>
+      <c r="E1288" s="19" t="s">
+        <v>887</v>
+      </c>
+      <c r="G1288" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1288" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:9">
+      <c r="A1289" s="26">
+        <v>5001712</v>
+      </c>
+      <c r="B1289" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1289" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1289" s="26" t="s">
+        <v>889</v>
+      </c>
+      <c r="E1289" s="19" t="s">
+        <v>888</v>
+      </c>
+      <c r="G1289" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1289" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:9">
+      <c r="A1290" s="26">
+        <v>5001715</v>
+      </c>
+      <c r="B1290" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1290" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1290" s="26" t="s">
+        <v>889</v>
+      </c>
+      <c r="E1290" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1290" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1290" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:9">
+      <c r="A1291" s="26">
         <v>5001716</v>
       </c>
-      <c r="B1286" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1286" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1286" s="26" t="s">
-        <v>888</v>
-      </c>
-      <c r="E1286" s="19" t="s">
+      <c r="B1291" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1291" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1291" s="26" t="s">
+        <v>889</v>
+      </c>
+      <c r="E1291" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="G1286" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1286" s="26">
+      <c r="G1291" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1291" s="26">
         <v>2</v>
       </c>
-      <c r="I1286">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1287" spans="1:9">
-      <c r="A1287">
-        <v>920071</v>
-      </c>
-      <c r="B1287" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1287">
-        <v>0</v>
-      </c>
-      <c r="D1287" s="28" t="s">
-        <v>889</v>
-      </c>
-      <c r="E1287" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1287">
-        <v>10</v>
-      </c>
-      <c r="H1287">
-        <v>1</v>
-      </c>
-      <c r="I1287">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1288" spans="1:9">
-      <c r="A1288">
-        <v>1920071</v>
-      </c>
-      <c r="B1288" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1288">
-        <v>0</v>
-      </c>
-      <c r="D1288" s="28" t="s">
-        <v>890</v>
-      </c>
-      <c r="E1288" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1288">
-        <v>10</v>
-      </c>
-      <c r="H1288">
-        <v>1</v>
-      </c>
-      <c r="I1288">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1289" spans="1:9">
-      <c r="A1289">
-        <v>2920071</v>
-      </c>
-      <c r="B1289" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1289">
-        <v>0</v>
-      </c>
-      <c r="D1289" s="28" t="s">
-        <v>891</v>
-      </c>
-      <c r="E1289" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1289">
-        <v>10</v>
-      </c>
-      <c r="H1289">
-        <v>1</v>
-      </c>
-      <c r="I1289">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1290" spans="1:9">
-      <c r="A1290">
-        <v>3920071</v>
-      </c>
-      <c r="B1290" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1290">
-        <v>0</v>
-      </c>
-      <c r="D1290" s="28" t="s">
-        <v>892</v>
-      </c>
-      <c r="E1290" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1290">
-        <v>10</v>
-      </c>
-      <c r="H1290">
-        <v>1</v>
-      </c>
-      <c r="I1290">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1291" spans="1:9">
-      <c r="A1291">
-        <v>4920071</v>
-      </c>
-      <c r="B1291" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1291">
-        <v>0</v>
-      </c>
-      <c r="D1291" s="28" t="s">
-        <v>893</v>
-      </c>
-      <c r="E1291" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1291">
-        <v>10</v>
-      </c>
-      <c r="H1291">
-        <v>1</v>
-      </c>
       <c r="I1291">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1292" spans="1:9">
       <c r="A1292">
-        <v>5920071</v>
+        <v>920071</v>
       </c>
       <c r="B1292" s="26">
         <v>1</v>
@@ -40423,10 +40359,10 @@
         <v>0</v>
       </c>
       <c r="D1292" s="28" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="E1292" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1292">
         <v>10</v>
@@ -40440,7 +40376,7 @@
     </row>
     <row r="1293" spans="1:9">
       <c r="A1293">
-        <v>6920071</v>
+        <v>1920071</v>
       </c>
       <c r="B1293" s="26">
         <v>1</v>
@@ -40449,7 +40385,7 @@
         <v>0</v>
       </c>
       <c r="D1293" s="28" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="E1293" s="29" t="s">
         <v>769</v>
@@ -40466,7 +40402,7 @@
     </row>
     <row r="1294" spans="1:9">
       <c r="A1294">
-        <v>7920071</v>
+        <v>2920071</v>
       </c>
       <c r="B1294" s="26">
         <v>1</v>
@@ -40475,7 +40411,7 @@
         <v>0</v>
       </c>
       <c r="D1294" s="28" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="E1294" s="29" t="s">
         <v>769</v>
@@ -40484,15 +40420,15 @@
         <v>10</v>
       </c>
       <c r="H1294">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1294">
-        <v>11500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1295" spans="1:9">
       <c r="A1295">
-        <v>8920071</v>
+        <v>3920071</v>
       </c>
       <c r="B1295" s="26">
         <v>1</v>
@@ -40501,7 +40437,7 @@
         <v>0</v>
       </c>
       <c r="D1295" s="28" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="E1295" s="29" t="s">
         <v>769</v>
@@ -40518,7 +40454,7 @@
     </row>
     <row r="1296" spans="1:9">
       <c r="A1296">
-        <v>9920071</v>
+        <v>4920071</v>
       </c>
       <c r="B1296" s="26">
         <v>1</v>
@@ -40527,7 +40463,7 @@
         <v>0</v>
       </c>
       <c r="D1296" s="28" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="E1296" s="29" t="s">
         <v>769</v>
@@ -40536,15 +40472,15 @@
         <v>10</v>
       </c>
       <c r="H1296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1296">
-        <v>11500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1297" spans="1:9">
       <c r="A1297">
-        <v>13920071</v>
+        <v>5920071</v>
       </c>
       <c r="B1297" s="26">
         <v>1</v>
@@ -40553,7 +40489,7 @@
         <v>0</v>
       </c>
       <c r="D1297" s="28" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="E1297" s="29" t="s">
         <v>769</v>
@@ -40565,12 +40501,12 @@
         <v>1</v>
       </c>
       <c r="I1297">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1298" spans="1:9">
       <c r="A1298">
-        <v>920072</v>
+        <v>6920071</v>
       </c>
       <c r="B1298" s="26">
         <v>1</v>
@@ -40579,12 +40515,11 @@
         <v>0</v>
       </c>
       <c r="D1298" s="28" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="E1298" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1298" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1298">
         <v>10</v>
       </c>
@@ -40597,7 +40532,7 @@
     </row>
     <row r="1299" spans="1:9">
       <c r="A1299">
-        <v>820072</v>
+        <v>7920071</v>
       </c>
       <c r="B1299" s="26">
         <v>1</v>
@@ -40605,25 +40540,25 @@
       <c r="C1299">
         <v>0</v>
       </c>
-      <c r="D1299" s="30" t="s">
-        <v>901</v>
-      </c>
-      <c r="E1299" s="30" t="s">
-        <v>901</v>
+      <c r="D1299" s="28" t="s">
+        <v>897</v>
+      </c>
+      <c r="E1299" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1299">
         <v>10</v>
       </c>
       <c r="H1299">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1299">
-        <v>0</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="1300" spans="1:9">
       <c r="A1300">
-        <v>920081</v>
+        <v>8920071</v>
       </c>
       <c r="B1300" s="26">
         <v>1</v>
@@ -40632,10 +40567,10 @@
         <v>0</v>
       </c>
       <c r="D1300" s="28" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="E1300" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1300">
         <v>10</v>
@@ -40649,7 +40584,7 @@
     </row>
     <row r="1301" spans="1:9">
       <c r="A1301">
-        <v>1920081</v>
+        <v>9920071</v>
       </c>
       <c r="B1301" s="26">
         <v>1</v>
@@ -40658,7 +40593,7 @@
         <v>0</v>
       </c>
       <c r="D1301" s="28" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="E1301" s="29" t="s">
         <v>769</v>
@@ -40667,15 +40602,15 @@
         <v>10</v>
       </c>
       <c r="H1301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1301">
-        <v>8000</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="1302" spans="1:9">
       <c r="A1302">
-        <v>2920081</v>
+        <v>13920071</v>
       </c>
       <c r="B1302" s="26">
         <v>1</v>
@@ -40684,7 +40619,7 @@
         <v>0</v>
       </c>
       <c r="D1302" s="28" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="E1302" s="29" t="s">
         <v>769</v>
@@ -40696,12 +40631,12 @@
         <v>1</v>
       </c>
       <c r="I1302">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1303" spans="1:9">
       <c r="A1303">
-        <v>3920081</v>
+        <v>920072</v>
       </c>
       <c r="B1303" s="26">
         <v>1</v>
@@ -40710,11 +40645,12 @@
         <v>0</v>
       </c>
       <c r="D1303" s="28" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="E1303" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1303" s="28"/>
       <c r="G1303">
         <v>10</v>
       </c>
@@ -40727,7 +40663,7 @@
     </row>
     <row r="1304" spans="1:9">
       <c r="A1304">
-        <v>4920081</v>
+        <v>820072</v>
       </c>
       <c r="B1304" s="26">
         <v>1</v>
@@ -40735,11 +40671,11 @@
       <c r="C1304">
         <v>0</v>
       </c>
-      <c r="D1304" s="28" t="s">
-        <v>906</v>
-      </c>
-      <c r="E1304" s="29" t="s">
-        <v>769</v>
+      <c r="D1304" s="30" t="s">
+        <v>902</v>
+      </c>
+      <c r="E1304" s="30" t="s">
+        <v>902</v>
       </c>
       <c r="G1304">
         <v>10</v>
@@ -40748,12 +40684,12 @@
         <v>1</v>
       </c>
       <c r="I1304">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1305" spans="1:9">
       <c r="A1305">
-        <v>5920081</v>
+        <v>920081</v>
       </c>
       <c r="B1305" s="26">
         <v>1</v>
@@ -40762,10 +40698,10 @@
         <v>0</v>
       </c>
       <c r="D1305" s="28" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="E1305" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1305">
         <v>10</v>
@@ -40779,7 +40715,7 @@
     </row>
     <row r="1306" spans="1:9">
       <c r="A1306">
-        <v>6920081</v>
+        <v>1920081</v>
       </c>
       <c r="B1306" s="26">
         <v>1</v>
@@ -40788,7 +40724,7 @@
         <v>0</v>
       </c>
       <c r="D1306" s="28" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="E1306" s="29" t="s">
         <v>769</v>
@@ -40800,12 +40736,12 @@
         <v>1</v>
       </c>
       <c r="I1306">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1307" spans="1:9">
       <c r="A1307">
-        <v>7920081</v>
+        <v>2920081</v>
       </c>
       <c r="B1307" s="26">
         <v>1</v>
@@ -40814,7 +40750,7 @@
         <v>0</v>
       </c>
       <c r="D1307" s="28" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="E1307" s="29" t="s">
         <v>769</v>
@@ -40823,15 +40759,15 @@
         <v>10</v>
       </c>
       <c r="H1307">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1307">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1308" spans="1:9">
       <c r="A1308">
-        <v>8920081</v>
+        <v>3920081</v>
       </c>
       <c r="B1308" s="26">
         <v>1</v>
@@ -40840,7 +40776,7 @@
         <v>0</v>
       </c>
       <c r="D1308" s="28" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="E1308" s="29" t="s">
         <v>769</v>
@@ -40857,7 +40793,7 @@
     </row>
     <row r="1309" spans="1:9">
       <c r="A1309">
-        <v>9920081</v>
+        <v>4920081</v>
       </c>
       <c r="B1309" s="26">
         <v>1</v>
@@ -40866,7 +40802,7 @@
         <v>0</v>
       </c>
       <c r="D1309" s="28" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="E1309" s="29" t="s">
         <v>769</v>
@@ -40875,15 +40811,15 @@
         <v>10</v>
       </c>
       <c r="H1309">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1309">
-        <v>8000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1310" spans="1:9">
       <c r="A1310">
-        <v>10920081</v>
+        <v>5920081</v>
       </c>
       <c r="B1310" s="26">
         <v>1</v>
@@ -40892,12 +40828,11 @@
         <v>0</v>
       </c>
       <c r="D1310" s="28" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="E1310" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1310" s="28"/>
       <c r="G1310">
         <v>10</v>
       </c>
@@ -40905,12 +40840,12 @@
         <v>1</v>
       </c>
       <c r="I1310">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1311" spans="1:9">
       <c r="A1311">
-        <v>11920081</v>
+        <v>6920081</v>
       </c>
       <c r="B1311" s="26">
         <v>1</v>
@@ -40919,12 +40854,11 @@
         <v>0</v>
       </c>
       <c r="D1311" s="28" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E1311" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1311" s="28"/>
       <c r="G1311">
         <v>10</v>
       </c>
@@ -40932,12 +40866,12 @@
         <v>1</v>
       </c>
       <c r="I1311">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1312" spans="1:9">
       <c r="A1312">
-        <v>13920081</v>
+        <v>7920081</v>
       </c>
       <c r="B1312" s="26">
         <v>1</v>
@@ -40946,25 +40880,24 @@
         <v>0</v>
       </c>
       <c r="D1312" s="28" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="E1312" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1312" s="28"/>
       <c r="G1312">
         <v>10</v>
       </c>
       <c r="H1312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1312">
-        <v>1</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1313" spans="1:9">
       <c r="A1313">
-        <v>14920081</v>
+        <v>8920081</v>
       </c>
       <c r="B1313" s="26">
         <v>1</v>
@@ -40973,12 +40906,11 @@
         <v>0</v>
       </c>
       <c r="D1313" s="28" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="E1313" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1313" s="28"/>
       <c r="G1313">
         <v>10</v>
       </c>
@@ -40986,12 +40918,12 @@
         <v>1</v>
       </c>
       <c r="I1313">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1314" spans="1:9">
       <c r="A1314">
-        <v>920083</v>
+        <v>9920081</v>
       </c>
       <c r="B1314" s="26">
         <v>1</v>
@@ -41000,24 +40932,24 @@
         <v>0</v>
       </c>
       <c r="D1314" s="28" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="E1314" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1314">
         <v>10</v>
       </c>
       <c r="H1314">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1314">
-        <v>1</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1315" spans="1:9">
       <c r="A1315">
-        <v>14920083</v>
+        <v>10920081</v>
       </c>
       <c r="B1315" s="26">
         <v>1</v>
@@ -41026,7 +40958,7 @@
         <v>0</v>
       </c>
       <c r="D1315" s="28" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="E1315" s="29" t="s">
         <v>769</v>
@@ -41039,12 +40971,12 @@
         <v>1</v>
       </c>
       <c r="I1315">
-        <v>1</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1316" spans="1:9">
-      <c r="A1316" s="31">
-        <v>920082</v>
+      <c r="A1316">
+        <v>11920081</v>
       </c>
       <c r="B1316" s="26">
         <v>1</v>
@@ -41053,10 +40985,10 @@
         <v>0</v>
       </c>
       <c r="D1316" s="28" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E1316" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1316" s="28"/>
       <c r="G1316">
@@ -41066,12 +40998,12 @@
         <v>1</v>
       </c>
       <c r="I1316">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1317" spans="1:9">
-      <c r="A1317" s="30">
-        <v>820082</v>
+      <c r="A1317">
+        <v>13920081</v>
       </c>
       <c r="B1317" s="26">
         <v>1</v>
@@ -41079,12 +41011,13 @@
       <c r="C1317">
         <v>0</v>
       </c>
-      <c r="D1317" s="30" t="s">
-        <v>919</v>
-      </c>
-      <c r="E1317" s="30" t="s">
-        <v>919</v>
-      </c>
+      <c r="D1317" s="28" t="s">
+        <v>915</v>
+      </c>
+      <c r="E1317" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1317" s="28"/>
       <c r="G1317">
         <v>10</v>
       </c>
@@ -41092,12 +41025,12 @@
         <v>1</v>
       </c>
       <c r="I1317">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1318" spans="1:9">
-      <c r="A1318" s="30">
-        <v>820083</v>
+      <c r="A1318">
+        <v>14920081</v>
       </c>
       <c r="B1318" s="26">
         <v>1</v>
@@ -41105,12 +41038,13 @@
       <c r="C1318">
         <v>0</v>
       </c>
-      <c r="D1318" s="30" t="s">
-        <v>920</v>
-      </c>
-      <c r="E1318" s="30" t="s">
-        <v>920</v>
-      </c>
+      <c r="D1318" s="28" t="s">
+        <v>916</v>
+      </c>
+      <c r="E1318" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1318" s="28"/>
       <c r="G1318">
         <v>10</v>
       </c>
@@ -41118,12 +41052,12 @@
         <v>1</v>
       </c>
       <c r="I1318">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1319" spans="1:9">
       <c r="A1319">
-        <v>920074</v>
+        <v>920083</v>
       </c>
       <c r="B1319" s="26">
         <v>1</v>
@@ -41132,7 +41066,7 @@
         <v>0</v>
       </c>
       <c r="D1319" s="28" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="E1319" s="29" t="s">
         <v>767</v>
@@ -41144,12 +41078,12 @@
         <v>1</v>
       </c>
       <c r="I1319">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1320" spans="1:9">
       <c r="A1320">
-        <v>14920074</v>
+        <v>14920083</v>
       </c>
       <c r="B1320" s="26">
         <v>1</v>
@@ -41158,7 +41092,7 @@
         <v>0</v>
       </c>
       <c r="D1320" s="28" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E1320" s="29" t="s">
         <v>769</v>
@@ -41175,8 +41109,8 @@
       </c>
     </row>
     <row r="1321" spans="1:9">
-      <c r="A1321">
-        <v>16920074</v>
+      <c r="A1321" s="31">
+        <v>920082</v>
       </c>
       <c r="B1321" s="26">
         <v>1</v>
@@ -41185,25 +41119,25 @@
         <v>0</v>
       </c>
       <c r="D1321" s="28" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="E1321" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F1321" s="28"/>
       <c r="G1321">
         <v>10</v>
       </c>
       <c r="H1321">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1321">
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1322" spans="1:9">
-      <c r="A1322">
-        <v>17920074</v>
+      <c r="A1322" s="30">
+        <v>820082</v>
       </c>
       <c r="B1322" s="26">
         <v>1</v>
@@ -41211,26 +41145,25 @@
       <c r="C1322">
         <v>0</v>
       </c>
-      <c r="D1322" s="28" t="s">
-        <v>924</v>
-      </c>
-      <c r="E1322" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1322" s="28"/>
+      <c r="D1322" s="30" t="s">
+        <v>920</v>
+      </c>
+      <c r="E1322" s="30" t="s">
+        <v>920</v>
+      </c>
       <c r="G1322">
         <v>10</v>
       </c>
       <c r="H1322">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1322">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1323" spans="1:9">
-      <c r="A1323">
-        <v>18920074</v>
+      <c r="A1323" s="30">
+        <v>820083</v>
       </c>
       <c r="B1323" s="26">
         <v>1</v>
@@ -41238,26 +41171,25 @@
       <c r="C1323">
         <v>0</v>
       </c>
-      <c r="D1323" s="28" t="s">
-        <v>925</v>
-      </c>
-      <c r="E1323" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1323" s="28"/>
+      <c r="D1323" s="30" t="s">
+        <v>921</v>
+      </c>
+      <c r="E1323" s="30" t="s">
+        <v>921</v>
+      </c>
       <c r="G1323">
         <v>10</v>
       </c>
       <c r="H1323">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1323">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1324" spans="1:9">
       <c r="A1324">
-        <v>920073</v>
+        <v>920074</v>
       </c>
       <c r="B1324" s="26">
         <v>1</v>
@@ -41266,12 +41198,11 @@
         <v>0</v>
       </c>
       <c r="D1324" s="28" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="E1324" s="29" t="s">
         <v>767</v>
       </c>
-      <c r="F1324" s="28"/>
       <c r="G1324">
         <v>10</v>
       </c>
@@ -41284,7 +41215,7 @@
     </row>
     <row r="1325" spans="1:9">
       <c r="A1325">
-        <v>820073</v>
+        <v>14920074</v>
       </c>
       <c r="B1325" s="26">
         <v>1</v>
@@ -41292,12 +41223,13 @@
       <c r="C1325">
         <v>0</v>
       </c>
-      <c r="D1325" s="30" t="s">
-        <v>927</v>
-      </c>
-      <c r="E1325" s="30" t="s">
-        <v>927</v>
-      </c>
+      <c r="D1325" s="28" t="s">
+        <v>923</v>
+      </c>
+      <c r="E1325" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1325" s="28"/>
       <c r="G1325">
         <v>10</v>
       </c>
@@ -41305,12 +41237,12 @@
         <v>1</v>
       </c>
       <c r="I1325">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1326" spans="1:9">
       <c r="A1326">
-        <v>920084</v>
+        <v>16920074</v>
       </c>
       <c r="B1326" s="26">
         <v>1</v>
@@ -41319,24 +41251,25 @@
         <v>0</v>
       </c>
       <c r="D1326" s="28" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="E1326" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1326" s="28"/>
       <c r="G1326">
         <v>10</v>
       </c>
       <c r="H1326">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1326">
-        <v>0</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="1327" spans="1:9">
       <c r="A1327">
-        <v>1920084</v>
+        <v>17920074</v>
       </c>
       <c r="B1327" s="26">
         <v>1</v>
@@ -41345,24 +41278,25 @@
         <v>0</v>
       </c>
       <c r="D1327" s="28" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="E1327" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1327" s="28"/>
       <c r="G1327">
         <v>10</v>
       </c>
       <c r="H1327">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1327">
-        <v>100</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1328" spans="1:9">
       <c r="A1328">
-        <v>2920084</v>
+        <v>18920074</v>
       </c>
       <c r="B1328" s="26">
         <v>1</v>
@@ -41371,24 +41305,25 @@
         <v>0</v>
       </c>
       <c r="D1328" s="28" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="E1328" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1328" s="28"/>
       <c r="G1328">
         <v>10</v>
       </c>
       <c r="H1328">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1328">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1329" spans="1:9">
       <c r="A1329">
-        <v>3920084</v>
+        <v>920073</v>
       </c>
       <c r="B1329" s="26">
         <v>1</v>
@@ -41397,11 +41332,12 @@
         <v>0</v>
       </c>
       <c r="D1329" s="28" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="E1329" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1329" s="28"/>
       <c r="G1329">
         <v>10</v>
       </c>
@@ -41414,7 +41350,7 @@
     </row>
     <row r="1330" spans="1:9">
       <c r="A1330">
-        <v>4920084</v>
+        <v>820073</v>
       </c>
       <c r="B1330" s="26">
         <v>1</v>
@@ -41422,11 +41358,11 @@
       <c r="C1330">
         <v>0</v>
       </c>
-      <c r="D1330" s="28" t="s">
-        <v>932</v>
-      </c>
-      <c r="E1330" s="29" t="s">
-        <v>769</v>
+      <c r="D1330" s="30" t="s">
+        <v>928</v>
+      </c>
+      <c r="E1330" s="30" t="s">
+        <v>928</v>
       </c>
       <c r="G1330">
         <v>10</v>
@@ -41435,12 +41371,12 @@
         <v>1</v>
       </c>
       <c r="I1330">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1331" spans="1:9">
       <c r="A1331">
-        <v>5920084</v>
+        <v>920084</v>
       </c>
       <c r="B1331" s="26">
         <v>1</v>
@@ -41449,10 +41385,10 @@
         <v>0</v>
       </c>
       <c r="D1331" s="28" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="E1331" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1331">
         <v>10</v>
@@ -41466,7 +41402,7 @@
     </row>
     <row r="1332" spans="1:9">
       <c r="A1332">
-        <v>6920084</v>
+        <v>1920084</v>
       </c>
       <c r="B1332" s="26">
         <v>1</v>
@@ -41475,7 +41411,7 @@
         <v>0</v>
       </c>
       <c r="D1332" s="28" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E1332" s="29" t="s">
         <v>769</v>
@@ -41487,12 +41423,12 @@
         <v>1</v>
       </c>
       <c r="I1332">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1333" spans="1:9">
       <c r="A1333">
-        <v>7920084</v>
+        <v>2920084</v>
       </c>
       <c r="B1333" s="26">
         <v>1</v>
@@ -41501,7 +41437,7 @@
         <v>0</v>
       </c>
       <c r="D1333" s="28" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="E1333" s="29" t="s">
         <v>769</v>
@@ -41510,7 +41446,7 @@
         <v>10</v>
       </c>
       <c r="H1333">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1333">
         <v>0</v>
@@ -41518,7 +41454,7 @@
     </row>
     <row r="1334" spans="1:9">
       <c r="A1334">
-        <v>8920084</v>
+        <v>3920084</v>
       </c>
       <c r="B1334" s="26">
         <v>1</v>
@@ -41527,7 +41463,7 @@
         <v>0</v>
       </c>
       <c r="D1334" s="28" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="E1334" s="29" t="s">
         <v>769</v>
@@ -41544,7 +41480,7 @@
     </row>
     <row r="1335" spans="1:9">
       <c r="A1335">
-        <v>9920084</v>
+        <v>4920084</v>
       </c>
       <c r="B1335" s="26">
         <v>1</v>
@@ -41553,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="D1335" s="28" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="E1335" s="29" t="s">
         <v>769</v>
@@ -41562,15 +41498,15 @@
         <v>10</v>
       </c>
       <c r="H1335">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1335">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1336" spans="1:9">
       <c r="A1336">
-        <v>13920084</v>
+        <v>5920084</v>
       </c>
       <c r="B1336" s="26">
         <v>1</v>
@@ -41579,7 +41515,7 @@
         <v>0</v>
       </c>
       <c r="D1336" s="28" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="E1336" s="29" t="s">
         <v>769</v>
@@ -41591,12 +41527,12 @@
         <v>1</v>
       </c>
       <c r="I1336">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1337" spans="1:9">
       <c r="A1337">
-        <v>16920084</v>
+        <v>6920084</v>
       </c>
       <c r="B1337" s="26">
         <v>1</v>
@@ -41605,12 +41541,11 @@
         <v>0</v>
       </c>
       <c r="D1337" s="28" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="E1337" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1337" s="28"/>
       <c r="G1337">
         <v>10</v>
       </c>
@@ -41618,12 +41553,12 @@
         <v>1</v>
       </c>
       <c r="I1337">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1338" spans="1:9">
       <c r="A1338">
-        <v>920085</v>
+        <v>7920084</v>
       </c>
       <c r="B1338" s="26">
         <v>1</v>
@@ -41632,16 +41567,16 @@
         <v>0</v>
       </c>
       <c r="D1338" s="28" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="E1338" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1338">
         <v>10</v>
       </c>
       <c r="H1338">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1338">
         <v>0</v>
@@ -41649,7 +41584,7 @@
     </row>
     <row r="1339" spans="1:9">
       <c r="A1339">
-        <v>1920085</v>
+        <v>8920084</v>
       </c>
       <c r="B1339" s="26">
         <v>1</v>
@@ -41658,7 +41593,7 @@
         <v>0</v>
       </c>
       <c r="D1339" s="28" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="E1339" s="29" t="s">
         <v>769</v>
@@ -41675,7 +41610,7 @@
     </row>
     <row r="1340" spans="1:9">
       <c r="A1340">
-        <v>2920085</v>
+        <v>9920084</v>
       </c>
       <c r="B1340" s="26">
         <v>1</v>
@@ -41684,7 +41619,7 @@
         <v>0</v>
       </c>
       <c r="D1340" s="28" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="E1340" s="29" t="s">
         <v>769</v>
@@ -41693,7 +41628,7 @@
         <v>10</v>
       </c>
       <c r="H1340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1340">
         <v>0</v>
@@ -41701,7 +41636,7 @@
     </row>
     <row r="1341" spans="1:9">
       <c r="A1341">
-        <v>3920085</v>
+        <v>13920084</v>
       </c>
       <c r="B1341" s="26">
         <v>1</v>
@@ -41710,7 +41645,7 @@
         <v>0</v>
       </c>
       <c r="D1341" s="28" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="E1341" s="29" t="s">
         <v>769</v>
@@ -41722,12 +41657,12 @@
         <v>1</v>
       </c>
       <c r="I1341">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1342" spans="1:9">
       <c r="A1342">
-        <v>4920085</v>
+        <v>16920084</v>
       </c>
       <c r="B1342" s="26">
         <v>1</v>
@@ -41736,11 +41671,12 @@
         <v>0</v>
       </c>
       <c r="D1342" s="28" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="E1342" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1342" s="28"/>
       <c r="G1342">
         <v>10</v>
       </c>
@@ -41748,12 +41684,12 @@
         <v>1</v>
       </c>
       <c r="I1342">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1343" spans="1:9">
       <c r="A1343">
-        <v>5920085</v>
+        <v>920085</v>
       </c>
       <c r="B1343" s="26">
         <v>1</v>
@@ -41762,10 +41698,10 @@
         <v>0</v>
       </c>
       <c r="D1343" s="28" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="E1343" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1343">
         <v>10</v>
@@ -41774,12 +41710,12 @@
         <v>1</v>
       </c>
       <c r="I1343">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1344" spans="1:9">
       <c r="A1344">
-        <v>6920085</v>
+        <v>1920085</v>
       </c>
       <c r="B1344" s="26">
         <v>1</v>
@@ -41788,7 +41724,7 @@
         <v>0</v>
       </c>
       <c r="D1344" s="28" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="E1344" s="29" t="s">
         <v>769</v>
@@ -41805,7 +41741,7 @@
     </row>
     <row r="1345" spans="1:9">
       <c r="A1345">
-        <v>7920085</v>
+        <v>2920085</v>
       </c>
       <c r="B1345" s="26">
         <v>1</v>
@@ -41814,7 +41750,7 @@
         <v>0</v>
       </c>
       <c r="D1345" s="28" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="E1345" s="29" t="s">
         <v>769</v>
@@ -41823,15 +41759,15 @@
         <v>10</v>
       </c>
       <c r="H1345">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1345">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1346" spans="1:9">
       <c r="A1346">
-        <v>8920085</v>
+        <v>3920085</v>
       </c>
       <c r="B1346" s="26">
         <v>1</v>
@@ -41840,7 +41776,7 @@
         <v>0</v>
       </c>
       <c r="D1346" s="28" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="E1346" s="29" t="s">
         <v>769</v>
@@ -41857,7 +41793,7 @@
     </row>
     <row r="1347" spans="1:9">
       <c r="A1347">
-        <v>9920085</v>
+        <v>4920085</v>
       </c>
       <c r="B1347" s="26">
         <v>1</v>
@@ -41866,7 +41802,7 @@
         <v>0</v>
       </c>
       <c r="D1347" s="28" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="E1347" s="29" t="s">
         <v>769</v>
@@ -41875,15 +41811,15 @@
         <v>10</v>
       </c>
       <c r="H1347">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1347">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1348" spans="1:9">
       <c r="A1348">
-        <v>920086</v>
+        <v>5920085</v>
       </c>
       <c r="B1348" s="26">
         <v>1</v>
@@ -41892,12 +41828,11 @@
         <v>0</v>
       </c>
       <c r="D1348" s="28" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="E1348" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1348" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1348">
         <v>10</v>
       </c>
@@ -41905,12 +41840,12 @@
         <v>1</v>
       </c>
       <c r="I1348">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1349" spans="1:9">
       <c r="A1349">
-        <v>820086</v>
+        <v>6920085</v>
       </c>
       <c r="B1349" s="26">
         <v>1</v>
@@ -41918,11 +41853,11 @@
       <c r="C1349">
         <v>0</v>
       </c>
-      <c r="D1349" s="30" t="s">
-        <v>951</v>
-      </c>
-      <c r="E1349" s="30" t="s">
-        <v>951</v>
+      <c r="D1349" s="28" t="s">
+        <v>947</v>
+      </c>
+      <c r="E1349" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1349">
         <v>10</v>
@@ -41936,7 +41871,7 @@
     </row>
     <row r="1350" spans="1:9">
       <c r="A1350">
-        <v>8200861</v>
+        <v>7920085</v>
       </c>
       <c r="B1350" s="26">
         <v>1</v>
@@ -41944,11 +41879,11 @@
       <c r="C1350">
         <v>0</v>
       </c>
-      <c r="D1350" s="30" t="s">
-        <v>952</v>
-      </c>
-      <c r="E1350" s="30" t="s">
-        <v>953</v>
+      <c r="D1350" s="28" t="s">
+        <v>948</v>
+      </c>
+      <c r="E1350" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1350">
         <v>10</v>
@@ -41957,12 +41892,12 @@
         <v>2</v>
       </c>
       <c r="I1350">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1351" spans="1:9">
       <c r="A1351">
-        <v>990001</v>
+        <v>8920085</v>
       </c>
       <c r="B1351" s="26">
         <v>1</v>
@@ -41971,12 +41906,11 @@
         <v>0</v>
       </c>
       <c r="D1351" s="28" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="E1351" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1351" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1351">
         <v>10</v>
       </c>
@@ -41984,12 +41918,12 @@
         <v>1</v>
       </c>
       <c r="I1351">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1352" spans="1:9">
       <c r="A1352">
-        <v>890001</v>
+        <v>9920085</v>
       </c>
       <c r="B1352" s="26">
         <v>1</v>
@@ -41998,24 +41932,24 @@
         <v>0</v>
       </c>
       <c r="D1352" s="28" t="s">
-        <v>955</v>
-      </c>
-      <c r="E1352" s="28" t="s">
-        <v>955</v>
+        <v>950</v>
+      </c>
+      <c r="E1352" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1352">
         <v>10</v>
       </c>
       <c r="H1352">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1352">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1353" spans="1:9">
       <c r="A1353">
-        <v>890011</v>
+        <v>920086</v>
       </c>
       <c r="B1353" s="26">
         <v>1</v>
@@ -42024,16 +41958,17 @@
         <v>0</v>
       </c>
       <c r="D1353" s="28" t="s">
-        <v>956</v>
-      </c>
-      <c r="E1353" s="28" t="s">
-        <v>956</v>
-      </c>
+        <v>951</v>
+      </c>
+      <c r="E1353" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1353" s="28"/>
       <c r="G1353">
         <v>10</v>
       </c>
       <c r="H1353">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1353">
         <v>0</v>
@@ -42041,7 +41976,7 @@
     </row>
     <row r="1354" spans="1:9">
       <c r="A1354">
-        <v>890021</v>
+        <v>820086</v>
       </c>
       <c r="B1354" s="26">
         <v>1</v>
@@ -42049,11 +41984,11 @@
       <c r="C1354">
         <v>0</v>
       </c>
-      <c r="D1354" s="28" t="s">
-        <v>957</v>
-      </c>
-      <c r="E1354" s="28" t="s">
-        <v>958</v>
+      <c r="D1354" s="30" t="s">
+        <v>952</v>
+      </c>
+      <c r="E1354" s="30" t="s">
+        <v>952</v>
       </c>
       <c r="G1354">
         <v>10</v>
@@ -42067,7 +42002,7 @@
     </row>
     <row r="1355" spans="1:9">
       <c r="A1355">
-        <v>890022</v>
+        <v>8200861</v>
       </c>
       <c r="B1355" s="26">
         <v>1</v>
@@ -42075,11 +42010,11 @@
       <c r="C1355">
         <v>0</v>
       </c>
-      <c r="D1355" s="28" t="s">
-        <v>959</v>
-      </c>
-      <c r="E1355" s="28" t="s">
-        <v>960</v>
+      <c r="D1355" s="30" t="s">
+        <v>953</v>
+      </c>
+      <c r="E1355" s="30" t="s">
+        <v>954</v>
       </c>
       <c r="G1355">
         <v>10</v>
@@ -42088,6 +42023,137 @@
         <v>2</v>
       </c>
       <c r="I1355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:9">
+      <c r="A1356">
+        <v>990001</v>
+      </c>
+      <c r="B1356" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1356">
+        <v>0</v>
+      </c>
+      <c r="D1356" s="28" t="s">
+        <v>955</v>
+      </c>
+      <c r="E1356" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1356" s="28"/>
+      <c r="G1356">
+        <v>10</v>
+      </c>
+      <c r="H1356">
+        <v>1</v>
+      </c>
+      <c r="I1356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:9">
+      <c r="A1357">
+        <v>890001</v>
+      </c>
+      <c r="B1357" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1357">
+        <v>0</v>
+      </c>
+      <c r="D1357" s="28" t="s">
+        <v>956</v>
+      </c>
+      <c r="E1357" s="28" t="s">
+        <v>956</v>
+      </c>
+      <c r="G1357">
+        <v>10</v>
+      </c>
+      <c r="H1357">
+        <v>1</v>
+      </c>
+      <c r="I1357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:9">
+      <c r="A1358">
+        <v>890011</v>
+      </c>
+      <c r="B1358" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1358">
+        <v>0</v>
+      </c>
+      <c r="D1358" s="28" t="s">
+        <v>957</v>
+      </c>
+      <c r="E1358" s="28" t="s">
+        <v>957</v>
+      </c>
+      <c r="G1358">
+        <v>10</v>
+      </c>
+      <c r="H1358">
+        <v>3</v>
+      </c>
+      <c r="I1358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:9">
+      <c r="A1359">
+        <v>890021</v>
+      </c>
+      <c r="B1359" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1359">
+        <v>0</v>
+      </c>
+      <c r="D1359" s="28" t="s">
+        <v>958</v>
+      </c>
+      <c r="E1359" s="28" t="s">
+        <v>959</v>
+      </c>
+      <c r="G1359">
+        <v>10</v>
+      </c>
+      <c r="H1359">
+        <v>1</v>
+      </c>
+      <c r="I1359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:9">
+      <c r="A1360">
+        <v>890022</v>
+      </c>
+      <c r="B1360" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1360">
+        <v>0</v>
+      </c>
+      <c r="D1360" s="28" t="s">
+        <v>960</v>
+      </c>
+      <c r="E1360" s="28" t="s">
+        <v>961</v>
+      </c>
+      <c r="G1360">
+        <v>10</v>
+      </c>
+      <c r="H1360">
+        <v>2</v>
+      </c>
+      <c r="I1360">
         <v>0</v>
       </c>
     </row>
@@ -42153,7 +42219,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -42165,10 +42231,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -42182,90 +42248,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>978</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>981</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>984</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -42276,7 +42342,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -42297,7 +42363,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -42309,7 +42375,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42320,7 +42386,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -42361,7 +42427,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -42402,7 +42468,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -42423,7 +42489,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -42435,7 +42501,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -42446,7 +42512,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -42467,7 +42533,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -42479,7 +42545,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -42490,7 +42556,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -42511,7 +42577,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -11,7 +11,7 @@
     <sheet name="maze_attribute_formula_v8" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1359</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="1010">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2786,6 +2786,9 @@
     <t>暴风雪_极寒领域冷却</t>
   </si>
   <si>
+    <t>暴风雪_极寒领域技能效果半径</t>
+  </si>
+  <si>
     <t>暴风雪_极寒领域技能持续时间</t>
   </si>
   <si>
@@ -2934,6 +2937,27 @@
   </si>
   <si>
     <t>超级暴风雪_伤害倍率</t>
+  </si>
+  <si>
+    <t>超级暴风雪_极寒领域获取</t>
+  </si>
+  <si>
+    <t>超级暴风雪_极寒领域冷却</t>
+  </si>
+  <si>
+    <t>超级暴风雪_极寒领域技能效果半径</t>
+  </si>
+  <si>
+    <t>超级暴风雪_极寒领域技能持续时间</t>
+  </si>
+  <si>
+    <t>超级暴风雪_极寒领域伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>超级暴风雪_极寒领域伤害系数</t>
+  </si>
+  <si>
+    <t>超级暴风雪_极寒领域技能等级</t>
   </si>
   <si>
     <t>冰风暴被动_获得</t>
@@ -3426,12 +3450,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4370,7 +4394,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1360"/>
+  <dimension ref="A1:I1363"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -39453,7 +39477,7 @@
         <v>1</v>
       </c>
       <c r="I1254">
-        <v>1500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1255" spans="1:9">
@@ -39775,159 +39799,252 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1267" spans="1:6">
+    <row r="1267" spans="1:9">
       <c r="A1267">
-        <v>2920062</v>
-      </c>
-      <c r="B1267" s="26"/>
-      <c r="D1267" s="28"/>
-      <c r="E1267" s="29"/>
+        <v>4920062</v>
+      </c>
+      <c r="B1267" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1267">
+        <v>0</v>
+      </c>
+      <c r="D1267" s="28" t="s">
+        <v>877</v>
+      </c>
+      <c r="E1267" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="F1267" s="28"/>
-    </row>
-    <row r="1268" spans="1:6">
+      <c r="G1267">
+        <v>10</v>
+      </c>
+      <c r="H1267">
+        <v>1</v>
+      </c>
+      <c r="I1267">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:9">
       <c r="A1268">
-        <v>3920062</v>
-      </c>
-      <c r="B1268" s="26"/>
-      <c r="D1268" s="28"/>
-      <c r="E1268" s="29"/>
+        <v>17920061</v>
+      </c>
+      <c r="B1268" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1268">
+        <v>0</v>
+      </c>
+      <c r="D1268" s="28" t="s">
+        <v>878</v>
+      </c>
+      <c r="E1268" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="F1268" s="28"/>
-    </row>
-    <row r="1269" spans="1:6">
+      <c r="G1268">
+        <v>10</v>
+      </c>
+      <c r="H1268">
+        <v>1</v>
+      </c>
+      <c r="I1268">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:9">
       <c r="A1269">
-        <v>4920062</v>
-      </c>
-      <c r="B1269" s="26"/>
-      <c r="D1269" s="28"/>
-      <c r="E1269" s="29"/>
+        <v>18920061</v>
+      </c>
+      <c r="B1269" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1269">
+        <v>0</v>
+      </c>
+      <c r="D1269" s="28" t="s">
+        <v>879</v>
+      </c>
+      <c r="E1269" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="F1269" s="28"/>
-    </row>
-    <row r="1270" spans="1:6">
+      <c r="G1269">
+        <v>10</v>
+      </c>
+      <c r="H1269">
+        <v>1</v>
+      </c>
+      <c r="I1269">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:9">
       <c r="A1270">
-        <v>5920062</v>
-      </c>
-      <c r="B1270" s="26"/>
-      <c r="D1270" s="28"/>
-      <c r="E1270" s="29"/>
+        <v>19920061</v>
+      </c>
+      <c r="B1270" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1270">
+        <v>0</v>
+      </c>
+      <c r="D1270" s="28" t="s">
+        <v>880</v>
+      </c>
+      <c r="E1270" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="F1270" s="28"/>
-    </row>
-    <row r="1271" spans="2:6">
-      <c r="B1271" s="26"/>
-      <c r="D1271" s="28"/>
-      <c r="E1271" s="29"/>
+      <c r="G1270">
+        <v>10</v>
+      </c>
+      <c r="H1270">
+        <v>2</v>
+      </c>
+      <c r="I1270">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:9">
+      <c r="A1271">
+        <v>20920061</v>
+      </c>
+      <c r="B1271" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1271">
+        <v>0</v>
+      </c>
+      <c r="D1271" s="28" t="s">
+        <v>881</v>
+      </c>
+      <c r="E1271" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="F1271" s="28"/>
+      <c r="G1271">
+        <v>10</v>
+      </c>
+      <c r="H1271">
+        <v>1</v>
+      </c>
+      <c r="I1271">
+        <v>1</v>
+      </c>
     </row>
     <row r="1272" spans="1:9">
-      <c r="A1272">
-        <v>17920061</v>
+      <c r="A1272" s="26">
+        <v>5001600</v>
       </c>
       <c r="B1272" s="26">
         <v>1</v>
       </c>
-      <c r="C1272">
-        <v>0</v>
-      </c>
-      <c r="D1272" s="28" t="s">
-        <v>877</v>
-      </c>
-      <c r="E1272" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1272" s="28"/>
-      <c r="G1272">
-        <v>10</v>
-      </c>
-      <c r="H1272">
+      <c r="C1272" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1272" s="26" t="s">
+        <v>882</v>
+      </c>
+      <c r="E1272" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="F1272" s="9"/>
+      <c r="G1272" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1272" s="26">
         <v>1</v>
       </c>
       <c r="I1272">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1273" spans="1:9">
-      <c r="A1273">
-        <v>18920061</v>
+      <c r="A1273" s="26">
+        <v>5001501</v>
       </c>
       <c r="B1273" s="26">
         <v>1</v>
       </c>
-      <c r="C1273">
-        <v>0</v>
-      </c>
-      <c r="D1273" s="28" t="s">
-        <v>878</v>
-      </c>
-      <c r="E1273" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1273" s="28"/>
-      <c r="G1273">
-        <v>10</v>
-      </c>
-      <c r="H1273">
-        <v>1</v>
+      <c r="C1273" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1273" s="26" t="s">
+        <v>883</v>
+      </c>
+      <c r="E1273" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1273" s="9"/>
+      <c r="G1273" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1273" s="26">
+        <v>2</v>
       </c>
       <c r="I1273">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1274" spans="1:9">
-      <c r="A1274">
-        <v>19920061</v>
+      <c r="A1274" s="26">
+        <v>5001502</v>
       </c>
       <c r="B1274" s="26">
         <v>1</v>
       </c>
-      <c r="C1274">
-        <v>0</v>
-      </c>
-      <c r="D1274" s="28" t="s">
-        <v>879</v>
-      </c>
-      <c r="E1274" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1274" s="28"/>
-      <c r="G1274">
-        <v>10</v>
-      </c>
-      <c r="H1274">
+      <c r="C1274" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1274" s="26" t="s">
+        <v>883</v>
+      </c>
+      <c r="E1274" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1274" s="9"/>
+      <c r="G1274" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1274" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:9">
+      <c r="A1275" s="26">
+        <v>5001511</v>
+      </c>
+      <c r="B1275" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1275" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1275" s="26" t="s">
+        <v>884</v>
+      </c>
+      <c r="E1275" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1275" s="9"/>
+      <c r="G1275" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1275" s="26">
         <v>2</v>
       </c>
-      <c r="I1274">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="1275" spans="1:9">
-      <c r="A1275">
-        <v>20920061</v>
-      </c>
-      <c r="B1275" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1275">
-        <v>0</v>
-      </c>
-      <c r="D1275" s="28" t="s">
-        <v>880</v>
-      </c>
-      <c r="E1275" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1275" s="28"/>
-      <c r="G1275">
-        <v>10</v>
-      </c>
-      <c r="H1275">
-        <v>1</v>
-      </c>
       <c r="I1275">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1276" spans="1:9">
       <c r="A1276" s="26">
-        <v>5001600</v>
+        <v>5001512</v>
       </c>
       <c r="B1276" s="26">
         <v>1</v>
@@ -39936,10 +40053,10 @@
         <v>0</v>
       </c>
       <c r="D1276" s="26" t="s">
-        <v>881</v>
-      </c>
-      <c r="E1276" s="26" t="s">
-        <v>243</v>
+        <v>884</v>
+      </c>
+      <c r="E1276" s="19" t="s">
+        <v>327</v>
       </c>
       <c r="F1276" s="9"/>
       <c r="G1276" s="26">
@@ -39954,7 +40071,7 @@
     </row>
     <row r="1277" spans="1:9">
       <c r="A1277" s="26">
-        <v>5001501</v>
+        <v>5001521</v>
       </c>
       <c r="B1277" s="26">
         <v>1</v>
@@ -39963,7 +40080,7 @@
         <v>0</v>
       </c>
       <c r="D1277" s="26" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E1277" s="19" t="s">
         <v>329</v>
@@ -39981,7 +40098,7 @@
     </row>
     <row r="1278" spans="1:9">
       <c r="A1278" s="26">
-        <v>5001502</v>
+        <v>5001522</v>
       </c>
       <c r="B1278" s="26">
         <v>1</v>
@@ -39990,7 +40107,7 @@
         <v>0</v>
       </c>
       <c r="D1278" s="26" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E1278" s="19" t="s">
         <v>327</v>
@@ -40008,7 +40125,7 @@
     </row>
     <row r="1279" spans="1:9">
       <c r="A1279" s="26">
-        <v>5001511</v>
+        <v>5001800</v>
       </c>
       <c r="B1279" s="26">
         <v>1</v>
@@ -40017,17 +40134,16 @@
         <v>0</v>
       </c>
       <c r="D1279" s="26" t="s">
-        <v>883</v>
-      </c>
-      <c r="E1279" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1279" s="9"/>
+        <v>886</v>
+      </c>
+      <c r="E1279" s="26" t="s">
+        <v>243</v>
+      </c>
       <c r="G1279" s="26">
         <v>10</v>
       </c>
       <c r="H1279" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1279">
         <v>0</v>
@@ -40035,7 +40151,7 @@
     </row>
     <row r="1280" spans="1:9">
       <c r="A1280" s="26">
-        <v>5001512</v>
+        <v>5001701</v>
       </c>
       <c r="B1280" s="26">
         <v>1</v>
@@ -40044,17 +40160,16 @@
         <v>0</v>
       </c>
       <c r="D1280" s="26" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E1280" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1280" s="9"/>
+        <v>888</v>
+      </c>
       <c r="G1280" s="26">
         <v>10</v>
       </c>
       <c r="H1280" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1280">
         <v>0</v>
@@ -40062,7 +40177,7 @@
     </row>
     <row r="1281" spans="1:9">
       <c r="A1281" s="26">
-        <v>5001521</v>
+        <v>5001702</v>
       </c>
       <c r="B1281" s="26">
         <v>1</v>
@@ -40071,12 +40186,11 @@
         <v>0</v>
       </c>
       <c r="D1281" s="26" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E1281" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1281" s="9"/>
+        <v>889</v>
+      </c>
       <c r="G1281" s="26">
         <v>10</v>
       </c>
@@ -40089,7 +40203,7 @@
     </row>
     <row r="1282" spans="1:9">
       <c r="A1282" s="26">
-        <v>5001522</v>
+        <v>5001705</v>
       </c>
       <c r="B1282" s="26">
         <v>1</v>
@@ -40098,12 +40212,11 @@
         <v>0</v>
       </c>
       <c r="D1282" s="26" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E1282" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="F1282" s="9"/>
       <c r="G1282" s="26">
         <v>10</v>
       </c>
@@ -40116,7 +40229,7 @@
     </row>
     <row r="1283" spans="1:9">
       <c r="A1283" s="26">
-        <v>5001800</v>
+        <v>5001706</v>
       </c>
       <c r="B1283" s="26">
         <v>1</v>
@@ -40125,16 +40238,16 @@
         <v>0</v>
       </c>
       <c r="D1283" s="26" t="s">
-        <v>885</v>
-      </c>
-      <c r="E1283" s="26" t="s">
-        <v>243</v>
+        <v>887</v>
+      </c>
+      <c r="E1283" s="19" t="s">
+        <v>329</v>
       </c>
       <c r="G1283" s="26">
         <v>10</v>
       </c>
       <c r="H1283" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1283">
         <v>0</v>
@@ -40142,7 +40255,7 @@
     </row>
     <row r="1284" spans="1:9">
       <c r="A1284" s="26">
-        <v>5001701</v>
+        <v>5001711</v>
       </c>
       <c r="B1284" s="26">
         <v>1</v>
@@ -40151,10 +40264,10 @@
         <v>0</v>
       </c>
       <c r="D1284" s="26" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E1284" s="19" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="G1284" s="26">
         <v>10</v>
@@ -40168,7 +40281,7 @@
     </row>
     <row r="1285" spans="1:9">
       <c r="A1285" s="26">
-        <v>5001702</v>
+        <v>5001712</v>
       </c>
       <c r="B1285" s="26">
         <v>1</v>
@@ -40177,10 +40290,10 @@
         <v>0</v>
       </c>
       <c r="D1285" s="26" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E1285" s="19" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G1285" s="26">
         <v>10</v>
@@ -40194,7 +40307,7 @@
     </row>
     <row r="1286" spans="1:9">
       <c r="A1286" s="26">
-        <v>5001705</v>
+        <v>5001715</v>
       </c>
       <c r="B1286" s="26">
         <v>1</v>
@@ -40203,7 +40316,7 @@
         <v>0</v>
       </c>
       <c r="D1286" s="26" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E1286" s="19" t="s">
         <v>327</v>
@@ -40220,7 +40333,7 @@
     </row>
     <row r="1287" spans="1:9">
       <c r="A1287" s="26">
-        <v>5001706</v>
+        <v>5001716</v>
       </c>
       <c r="B1287" s="26">
         <v>1</v>
@@ -40229,7 +40342,7 @@
         <v>0</v>
       </c>
       <c r="D1287" s="26" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E1287" s="19" t="s">
         <v>329</v>
@@ -40245,77 +40358,77 @@
       </c>
     </row>
     <row r="1288" spans="1:9">
-      <c r="A1288" s="26">
-        <v>5001711</v>
+      <c r="A1288">
+        <v>920071</v>
       </c>
       <c r="B1288" s="26">
         <v>1</v>
       </c>
-      <c r="C1288" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1288" s="26" t="s">
-        <v>889</v>
-      </c>
-      <c r="E1288" s="19" t="s">
-        <v>887</v>
-      </c>
-      <c r="G1288" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1288" s="26">
-        <v>2</v>
+      <c r="C1288">
+        <v>0</v>
+      </c>
+      <c r="D1288" s="28" t="s">
+        <v>891</v>
+      </c>
+      <c r="E1288" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1288">
+        <v>10</v>
+      </c>
+      <c r="H1288">
+        <v>1</v>
       </c>
       <c r="I1288">
         <v>0</v>
       </c>
     </row>
     <row r="1289" spans="1:9">
-      <c r="A1289" s="26">
-        <v>5001712</v>
+      <c r="A1289">
+        <v>1920071</v>
       </c>
       <c r="B1289" s="26">
         <v>1</v>
       </c>
-      <c r="C1289" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1289" s="26" t="s">
-        <v>889</v>
-      </c>
-      <c r="E1289" s="19" t="s">
-        <v>888</v>
-      </c>
-      <c r="G1289" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1289" s="26">
-        <v>2</v>
+      <c r="C1289">
+        <v>0</v>
+      </c>
+      <c r="D1289" s="28" t="s">
+        <v>892</v>
+      </c>
+      <c r="E1289" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1289">
+        <v>10</v>
+      </c>
+      <c r="H1289">
+        <v>1</v>
       </c>
       <c r="I1289">
         <v>0</v>
       </c>
     </row>
     <row r="1290" spans="1:9">
-      <c r="A1290" s="26">
-        <v>5001715</v>
+      <c r="A1290">
+        <v>2920071</v>
       </c>
       <c r="B1290" s="26">
         <v>1</v>
       </c>
-      <c r="C1290" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1290" s="26" t="s">
-        <v>889</v>
-      </c>
-      <c r="E1290" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="G1290" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1290" s="26">
+      <c r="C1290">
+        <v>0</v>
+      </c>
+      <c r="D1290" s="28" t="s">
+        <v>893</v>
+      </c>
+      <c r="E1290" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1290">
+        <v>10</v>
+      </c>
+      <c r="H1290">
         <v>1</v>
       </c>
       <c r="I1290">
@@ -40323,26 +40436,26 @@
       </c>
     </row>
     <row r="1291" spans="1:9">
-      <c r="A1291" s="26">
-        <v>5001716</v>
+      <c r="A1291">
+        <v>3920071</v>
       </c>
       <c r="B1291" s="26">
         <v>1</v>
       </c>
-      <c r="C1291" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1291" s="26" t="s">
-        <v>889</v>
-      </c>
-      <c r="E1291" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="G1291" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1291" s="26">
-        <v>2</v>
+      <c r="C1291">
+        <v>0</v>
+      </c>
+      <c r="D1291" s="28" t="s">
+        <v>894</v>
+      </c>
+      <c r="E1291" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1291">
+        <v>10</v>
+      </c>
+      <c r="H1291">
+        <v>1</v>
       </c>
       <c r="I1291">
         <v>0</v>
@@ -40350,7 +40463,7 @@
     </row>
     <row r="1292" spans="1:9">
       <c r="A1292">
-        <v>920071</v>
+        <v>4920071</v>
       </c>
       <c r="B1292" s="26">
         <v>1</v>
@@ -40359,10 +40472,10 @@
         <v>0</v>
       </c>
       <c r="D1292" s="28" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="E1292" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1292">
         <v>10</v>
@@ -40371,12 +40484,12 @@
         <v>1</v>
       </c>
       <c r="I1292">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1293" spans="1:9">
       <c r="A1293">
-        <v>1920071</v>
+        <v>5920071</v>
       </c>
       <c r="B1293" s="26">
         <v>1</v>
@@ -40385,7 +40498,7 @@
         <v>0</v>
       </c>
       <c r="D1293" s="28" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="E1293" s="29" t="s">
         <v>769</v>
@@ -40402,7 +40515,7 @@
     </row>
     <row r="1294" spans="1:9">
       <c r="A1294">
-        <v>2920071</v>
+        <v>6920071</v>
       </c>
       <c r="B1294" s="26">
         <v>1</v>
@@ -40411,7 +40524,7 @@
         <v>0</v>
       </c>
       <c r="D1294" s="28" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="E1294" s="29" t="s">
         <v>769</v>
@@ -40428,7 +40541,7 @@
     </row>
     <row r="1295" spans="1:9">
       <c r="A1295">
-        <v>3920071</v>
+        <v>7920071</v>
       </c>
       <c r="B1295" s="26">
         <v>1</v>
@@ -40437,7 +40550,7 @@
         <v>0</v>
       </c>
       <c r="D1295" s="28" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="E1295" s="29" t="s">
         <v>769</v>
@@ -40446,15 +40559,15 @@
         <v>10</v>
       </c>
       <c r="H1295">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1295">
-        <v>0</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="1296" spans="1:9">
       <c r="A1296">
-        <v>4920071</v>
+        <v>8920071</v>
       </c>
       <c r="B1296" s="26">
         <v>1</v>
@@ -40463,7 +40576,7 @@
         <v>0</v>
       </c>
       <c r="D1296" s="28" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="E1296" s="29" t="s">
         <v>769</v>
@@ -40475,12 +40588,12 @@
         <v>1</v>
       </c>
       <c r="I1296">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1297" spans="1:9">
       <c r="A1297">
-        <v>5920071</v>
+        <v>9920071</v>
       </c>
       <c r="B1297" s="26">
         <v>1</v>
@@ -40489,7 +40602,7 @@
         <v>0</v>
       </c>
       <c r="D1297" s="28" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="E1297" s="29" t="s">
         <v>769</v>
@@ -40498,15 +40611,15 @@
         <v>10</v>
       </c>
       <c r="H1297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1297">
-        <v>0</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="1298" spans="1:9">
       <c r="A1298">
-        <v>6920071</v>
+        <v>13920071</v>
       </c>
       <c r="B1298" s="26">
         <v>1</v>
@@ -40515,7 +40628,7 @@
         <v>0</v>
       </c>
       <c r="D1298" s="28" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="E1298" s="29" t="s">
         <v>769</v>
@@ -40527,12 +40640,12 @@
         <v>1</v>
       </c>
       <c r="I1298">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1299" spans="1:9">
       <c r="A1299">
-        <v>7920071</v>
+        <v>920072</v>
       </c>
       <c r="B1299" s="26">
         <v>1</v>
@@ -40541,24 +40654,25 @@
         <v>0</v>
       </c>
       <c r="D1299" s="28" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="E1299" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1299" s="28"/>
       <c r="G1299">
         <v>10</v>
       </c>
       <c r="H1299">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1299">
-        <v>11500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1300" spans="1:9">
       <c r="A1300">
-        <v>8920071</v>
+        <v>820072</v>
       </c>
       <c r="B1300" s="26">
         <v>1</v>
@@ -40566,11 +40680,11 @@
       <c r="C1300">
         <v>0</v>
       </c>
-      <c r="D1300" s="28" t="s">
-        <v>898</v>
-      </c>
-      <c r="E1300" s="29" t="s">
-        <v>769</v>
+      <c r="D1300" s="30" t="s">
+        <v>903</v>
+      </c>
+      <c r="E1300" s="30" t="s">
+        <v>903</v>
       </c>
       <c r="G1300">
         <v>10</v>
@@ -40584,7 +40698,7 @@
     </row>
     <row r="1301" spans="1:9">
       <c r="A1301">
-        <v>9920071</v>
+        <v>920081</v>
       </c>
       <c r="B1301" s="26">
         <v>1</v>
@@ -40593,24 +40707,24 @@
         <v>0</v>
       </c>
       <c r="D1301" s="28" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="E1301" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1301">
         <v>10</v>
       </c>
       <c r="H1301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1301">
-        <v>11500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1302" spans="1:9">
       <c r="A1302">
-        <v>13920071</v>
+        <v>1920081</v>
       </c>
       <c r="B1302" s="26">
         <v>1</v>
@@ -40619,7 +40733,7 @@
         <v>0</v>
       </c>
       <c r="D1302" s="28" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="E1302" s="29" t="s">
         <v>769</v>
@@ -40631,12 +40745,12 @@
         <v>1</v>
       </c>
       <c r="I1302">
-        <v>1</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1303" spans="1:9">
       <c r="A1303">
-        <v>920072</v>
+        <v>2920081</v>
       </c>
       <c r="B1303" s="26">
         <v>1</v>
@@ -40645,12 +40759,11 @@
         <v>0</v>
       </c>
       <c r="D1303" s="28" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="E1303" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1303" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1303">
         <v>10</v>
       </c>
@@ -40663,7 +40776,7 @@
     </row>
     <row r="1304" spans="1:9">
       <c r="A1304">
-        <v>820072</v>
+        <v>3920081</v>
       </c>
       <c r="B1304" s="26">
         <v>1</v>
@@ -40671,11 +40784,11 @@
       <c r="C1304">
         <v>0</v>
       </c>
-      <c r="D1304" s="30" t="s">
-        <v>902</v>
-      </c>
-      <c r="E1304" s="30" t="s">
-        <v>902</v>
+      <c r="D1304" s="28" t="s">
+        <v>907</v>
+      </c>
+      <c r="E1304" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1304">
         <v>10</v>
@@ -40689,7 +40802,7 @@
     </row>
     <row r="1305" spans="1:9">
       <c r="A1305">
-        <v>920081</v>
+        <v>4920081</v>
       </c>
       <c r="B1305" s="26">
         <v>1</v>
@@ -40698,10 +40811,10 @@
         <v>0</v>
       </c>
       <c r="D1305" s="28" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="E1305" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1305">
         <v>10</v>
@@ -40710,12 +40823,12 @@
         <v>1</v>
       </c>
       <c r="I1305">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1306" spans="1:9">
       <c r="A1306">
-        <v>1920081</v>
+        <v>5920081</v>
       </c>
       <c r="B1306" s="26">
         <v>1</v>
@@ -40724,7 +40837,7 @@
         <v>0</v>
       </c>
       <c r="D1306" s="28" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="E1306" s="29" t="s">
         <v>769</v>
@@ -40736,12 +40849,12 @@
         <v>1</v>
       </c>
       <c r="I1306">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1307" spans="1:9">
       <c r="A1307">
-        <v>2920081</v>
+        <v>6920081</v>
       </c>
       <c r="B1307" s="26">
         <v>1</v>
@@ -40750,7 +40863,7 @@
         <v>0</v>
       </c>
       <c r="D1307" s="28" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="E1307" s="29" t="s">
         <v>769</v>
@@ -40767,7 +40880,7 @@
     </row>
     <row r="1308" spans="1:9">
       <c r="A1308">
-        <v>3920081</v>
+        <v>7920081</v>
       </c>
       <c r="B1308" s="26">
         <v>1</v>
@@ -40776,7 +40889,7 @@
         <v>0</v>
       </c>
       <c r="D1308" s="28" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="E1308" s="29" t="s">
         <v>769</v>
@@ -40785,15 +40898,15 @@
         <v>10</v>
       </c>
       <c r="H1308">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1308">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
       <c r="A1309">
-        <v>4920081</v>
+        <v>8920081</v>
       </c>
       <c r="B1309" s="26">
         <v>1</v>
@@ -40802,7 +40915,7 @@
         <v>0</v>
       </c>
       <c r="D1309" s="28" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="E1309" s="29" t="s">
         <v>769</v>
@@ -40814,12 +40927,12 @@
         <v>1</v>
       </c>
       <c r="I1309">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1310" spans="1:9">
       <c r="A1310">
-        <v>5920081</v>
+        <v>9920081</v>
       </c>
       <c r="B1310" s="26">
         <v>1</v>
@@ -40828,7 +40941,7 @@
         <v>0</v>
       </c>
       <c r="D1310" s="28" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="E1310" s="29" t="s">
         <v>769</v>
@@ -40837,15 +40950,15 @@
         <v>10</v>
       </c>
       <c r="H1310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1310">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1311" spans="1:9">
       <c r="A1311">
-        <v>6920081</v>
+        <v>10920081</v>
       </c>
       <c r="B1311" s="26">
         <v>1</v>
@@ -40854,11 +40967,12 @@
         <v>0</v>
       </c>
       <c r="D1311" s="28" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="E1311" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1311" s="28"/>
       <c r="G1311">
         <v>10</v>
       </c>
@@ -40866,12 +40980,12 @@
         <v>1</v>
       </c>
       <c r="I1311">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1312" spans="1:9">
       <c r="A1312">
-        <v>7920081</v>
+        <v>11920081</v>
       </c>
       <c r="B1312" s="26">
         <v>1</v>
@@ -40880,24 +40994,25 @@
         <v>0</v>
       </c>
       <c r="D1312" s="28" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="E1312" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1312" s="28"/>
       <c r="G1312">
         <v>10</v>
       </c>
       <c r="H1312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1312">
-        <v>8000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1313" spans="1:9">
       <c r="A1313">
-        <v>8920081</v>
+        <v>13920081</v>
       </c>
       <c r="B1313" s="26">
         <v>1</v>
@@ -40906,11 +41021,12 @@
         <v>0</v>
       </c>
       <c r="D1313" s="28" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="E1313" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1313" s="28"/>
       <c r="G1313">
         <v>10</v>
       </c>
@@ -40918,12 +41034,12 @@
         <v>1</v>
       </c>
       <c r="I1313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1314" spans="1:9">
       <c r="A1314">
-        <v>9920081</v>
+        <v>14920081</v>
       </c>
       <c r="B1314" s="26">
         <v>1</v>
@@ -40932,24 +41048,25 @@
         <v>0</v>
       </c>
       <c r="D1314" s="28" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="E1314" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1314" s="28"/>
       <c r="G1314">
         <v>10</v>
       </c>
       <c r="H1314">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1314">
-        <v>8000</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1315" spans="1:9">
       <c r="A1315">
-        <v>10920081</v>
+        <v>920083</v>
       </c>
       <c r="B1315" s="26">
         <v>1</v>
@@ -40958,12 +41075,11 @@
         <v>0</v>
       </c>
       <c r="D1315" s="28" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="E1315" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1315" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1315">
         <v>10</v>
       </c>
@@ -40971,12 +41087,12 @@
         <v>1</v>
       </c>
       <c r="I1315">
-        <v>6000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1316" spans="1:9">
       <c r="A1316">
-        <v>11920081</v>
+        <v>14920083</v>
       </c>
       <c r="B1316" s="26">
         <v>1</v>
@@ -40985,7 +41101,7 @@
         <v>0</v>
       </c>
       <c r="D1316" s="28" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="E1316" s="29" t="s">
         <v>769</v>
@@ -40998,12 +41114,12 @@
         <v>1</v>
       </c>
       <c r="I1316">
-        <v>3000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1317" spans="1:9">
-      <c r="A1317">
-        <v>13920081</v>
+      <c r="A1317" s="31">
+        <v>920082</v>
       </c>
       <c r="B1317" s="26">
         <v>1</v>
@@ -41012,10 +41128,10 @@
         <v>0</v>
       </c>
       <c r="D1317" s="28" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="E1317" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F1317" s="28"/>
       <c r="G1317">
@@ -41025,12 +41141,12 @@
         <v>1</v>
       </c>
       <c r="I1317">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1318" spans="1:9">
-      <c r="A1318">
-        <v>14920081</v>
+      <c r="A1318" s="30">
+        <v>820082</v>
       </c>
       <c r="B1318" s="26">
         <v>1</v>
@@ -41038,13 +41154,12 @@
       <c r="C1318">
         <v>0</v>
       </c>
-      <c r="D1318" s="28" t="s">
-        <v>916</v>
-      </c>
-      <c r="E1318" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1318" s="28"/>
+      <c r="D1318" s="30" t="s">
+        <v>921</v>
+      </c>
+      <c r="E1318" s="30" t="s">
+        <v>921</v>
+      </c>
       <c r="G1318">
         <v>10</v>
       </c>
@@ -41052,12 +41167,12 @@
         <v>1</v>
       </c>
       <c r="I1318">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1319" spans="1:9">
-      <c r="A1319">
-        <v>920083</v>
+      <c r="A1319" s="30">
+        <v>820083</v>
       </c>
       <c r="B1319" s="26">
         <v>1</v>
@@ -41065,11 +41180,11 @@
       <c r="C1319">
         <v>0</v>
       </c>
-      <c r="D1319" s="28" t="s">
-        <v>917</v>
-      </c>
-      <c r="E1319" s="29" t="s">
-        <v>767</v>
+      <c r="D1319" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="E1319" s="30" t="s">
+        <v>922</v>
       </c>
       <c r="G1319">
         <v>10</v>
@@ -41078,12 +41193,12 @@
         <v>1</v>
       </c>
       <c r="I1319">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1320" spans="1:9">
       <c r="A1320">
-        <v>14920083</v>
+        <v>920074</v>
       </c>
       <c r="B1320" s="26">
         <v>1</v>
@@ -41092,37 +41207,36 @@
         <v>0</v>
       </c>
       <c r="D1320" s="28" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="E1320" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1320">
+        <v>10</v>
+      </c>
+      <c r="H1320">
+        <v>1</v>
+      </c>
+      <c r="I1320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:9">
+      <c r="A1321">
+        <v>14920074</v>
+      </c>
+      <c r="B1321" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1321">
+        <v>0</v>
+      </c>
+      <c r="D1321" s="28" t="s">
+        <v>924</v>
+      </c>
+      <c r="E1321" s="29" t="s">
         <v>769</v>
-      </c>
-      <c r="F1320" s="28"/>
-      <c r="G1320">
-        <v>10</v>
-      </c>
-      <c r="H1320">
-        <v>1</v>
-      </c>
-      <c r="I1320">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1321" spans="1:9">
-      <c r="A1321" s="31">
-        <v>920082</v>
-      </c>
-      <c r="B1321" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1321">
-        <v>0</v>
-      </c>
-      <c r="D1321" s="28" t="s">
-        <v>919</v>
-      </c>
-      <c r="E1321" s="29" t="s">
-        <v>767</v>
       </c>
       <c r="F1321" s="28"/>
       <c r="G1321">
@@ -41132,12 +41246,12 @@
         <v>1</v>
       </c>
       <c r="I1321">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1322" spans="1:9">
-      <c r="A1322" s="30">
-        <v>820082</v>
+      <c r="A1322">
+        <v>16920074</v>
       </c>
       <c r="B1322" s="26">
         <v>1</v>
@@ -41145,25 +41259,26 @@
       <c r="C1322">
         <v>0</v>
       </c>
-      <c r="D1322" s="30" t="s">
-        <v>920</v>
-      </c>
-      <c r="E1322" s="30" t="s">
-        <v>920</v>
-      </c>
+      <c r="D1322" s="28" t="s">
+        <v>925</v>
+      </c>
+      <c r="E1322" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1322" s="28"/>
       <c r="G1322">
         <v>10</v>
       </c>
       <c r="H1322">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1322">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1323" spans="1:9">
-      <c r="A1323" s="30">
-        <v>820083</v>
+      <c r="A1323">
+        <v>17920074</v>
       </c>
       <c r="B1323" s="26">
         <v>1</v>
@@ -41171,25 +41286,26 @@
       <c r="C1323">
         <v>0</v>
       </c>
-      <c r="D1323" s="30" t="s">
-        <v>921</v>
-      </c>
-      <c r="E1323" s="30" t="s">
-        <v>921</v>
-      </c>
+      <c r="D1323" s="28" t="s">
+        <v>926</v>
+      </c>
+      <c r="E1323" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1323" s="28"/>
       <c r="G1323">
         <v>10</v>
       </c>
       <c r="H1323">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1323">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1324" spans="1:9">
       <c r="A1324">
-        <v>920074</v>
+        <v>18920074</v>
       </c>
       <c r="B1324" s="26">
         <v>1</v>
@@ -41198,24 +41314,25 @@
         <v>0</v>
       </c>
       <c r="D1324" s="28" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="E1324" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1324" s="28"/>
       <c r="G1324">
         <v>10</v>
       </c>
       <c r="H1324">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1324">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1325" spans="1:9">
       <c r="A1325">
-        <v>14920074</v>
+        <v>920075</v>
       </c>
       <c r="B1325" s="26">
         <v>1</v>
@@ -41224,7 +41341,7 @@
         <v>0</v>
       </c>
       <c r="D1325" s="28" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="E1325" s="29" t="s">
         <v>769</v>
@@ -41237,12 +41354,12 @@
         <v>1</v>
       </c>
       <c r="I1325">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1326" spans="1:9">
       <c r="A1326">
-        <v>16920074</v>
+        <v>1920075</v>
       </c>
       <c r="B1326" s="26">
         <v>1</v>
@@ -41251,7 +41368,7 @@
         <v>0</v>
       </c>
       <c r="D1326" s="28" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="E1326" s="29" t="s">
         <v>769</v>
@@ -41261,15 +41378,15 @@
         <v>10</v>
       </c>
       <c r="H1326">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1326">
-        <v>11500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1327" spans="1:9">
       <c r="A1327">
-        <v>17920074</v>
+        <v>4920075</v>
       </c>
       <c r="B1327" s="26">
         <v>1</v>
@@ -41278,7 +41395,7 @@
         <v>0</v>
       </c>
       <c r="D1327" s="28" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="E1327" s="29" t="s">
         <v>769</v>
@@ -41288,7 +41405,7 @@
         <v>10</v>
       </c>
       <c r="H1327">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1327">
         <v>1500</v>
@@ -41296,7 +41413,7 @@
     </row>
     <row r="1328" spans="1:9">
       <c r="A1328">
-        <v>18920074</v>
+        <v>10920075</v>
       </c>
       <c r="B1328" s="26">
         <v>1</v>
@@ -41305,7 +41422,7 @@
         <v>0</v>
       </c>
       <c r="D1328" s="28" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="E1328" s="29" t="s">
         <v>769</v>
@@ -41315,15 +41432,15 @@
         <v>10</v>
       </c>
       <c r="H1328">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1328">
-        <v>10000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1329" spans="1:9">
       <c r="A1329">
-        <v>920073</v>
+        <v>18920075</v>
       </c>
       <c r="B1329" s="26">
         <v>1</v>
@@ -41332,10 +41449,10 @@
         <v>0</v>
       </c>
       <c r="D1329" s="28" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="E1329" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1329" s="28"/>
       <c r="G1329">
@@ -41345,12 +41462,12 @@
         <v>1</v>
       </c>
       <c r="I1329">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1330" spans="1:9">
       <c r="A1330">
-        <v>820073</v>
+        <v>11920075</v>
       </c>
       <c r="B1330" s="26">
         <v>1</v>
@@ -41358,12 +41475,13 @@
       <c r="C1330">
         <v>0</v>
       </c>
-      <c r="D1330" s="30" t="s">
-        <v>928</v>
-      </c>
-      <c r="E1330" s="30" t="s">
-        <v>928</v>
-      </c>
+      <c r="D1330" s="28" t="s">
+        <v>933</v>
+      </c>
+      <c r="E1330" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1330" s="28"/>
       <c r="G1330">
         <v>10</v>
       </c>
@@ -41371,12 +41489,12 @@
         <v>1</v>
       </c>
       <c r="I1330">
-        <v>0</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="1331" spans="1:9">
       <c r="A1331">
-        <v>920084</v>
+        <v>13920075</v>
       </c>
       <c r="B1331" s="26">
         <v>1</v>
@@ -41385,11 +41503,12 @@
         <v>0</v>
       </c>
       <c r="D1331" s="28" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="E1331" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1331" s="28"/>
       <c r="G1331">
         <v>10</v>
       </c>
@@ -41397,12 +41516,12 @@
         <v>1</v>
       </c>
       <c r="I1331">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1332" spans="1:9">
       <c r="A1332">
-        <v>1920084</v>
+        <v>920073</v>
       </c>
       <c r="B1332" s="26">
         <v>1</v>
@@ -41411,11 +41530,12 @@
         <v>0</v>
       </c>
       <c r="D1332" s="28" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="E1332" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1332" s="28"/>
       <c r="G1332">
         <v>10</v>
       </c>
@@ -41423,12 +41543,12 @@
         <v>1</v>
       </c>
       <c r="I1332">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1333" spans="1:9">
       <c r="A1333">
-        <v>2920084</v>
+        <v>820073</v>
       </c>
       <c r="B1333" s="26">
         <v>1</v>
@@ -41436,11 +41556,11 @@
       <c r="C1333">
         <v>0</v>
       </c>
-      <c r="D1333" s="28" t="s">
-        <v>931</v>
-      </c>
-      <c r="E1333" s="29" t="s">
-        <v>769</v>
+      <c r="D1333" s="30" t="s">
+        <v>936</v>
+      </c>
+      <c r="E1333" s="30" t="s">
+        <v>936</v>
       </c>
       <c r="G1333">
         <v>10</v>
@@ -41454,7 +41574,7 @@
     </row>
     <row r="1334" spans="1:9">
       <c r="A1334">
-        <v>3920084</v>
+        <v>920084</v>
       </c>
       <c r="B1334" s="26">
         <v>1</v>
@@ -41463,10 +41583,10 @@
         <v>0</v>
       </c>
       <c r="D1334" s="28" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="E1334" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1334">
         <v>10</v>
@@ -41480,7 +41600,7 @@
     </row>
     <row r="1335" spans="1:9">
       <c r="A1335">
-        <v>4920084</v>
+        <v>1920084</v>
       </c>
       <c r="B1335" s="26">
         <v>1</v>
@@ -41489,7 +41609,7 @@
         <v>0</v>
       </c>
       <c r="D1335" s="28" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="E1335" s="29" t="s">
         <v>769</v>
@@ -41501,12 +41621,12 @@
         <v>1</v>
       </c>
       <c r="I1335">
-        <v>3500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1336" spans="1:9">
       <c r="A1336">
-        <v>5920084</v>
+        <v>2920084</v>
       </c>
       <c r="B1336" s="26">
         <v>1</v>
@@ -41515,7 +41635,7 @@
         <v>0</v>
       </c>
       <c r="D1336" s="28" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="E1336" s="29" t="s">
         <v>769</v>
@@ -41532,7 +41652,7 @@
     </row>
     <row r="1337" spans="1:9">
       <c r="A1337">
-        <v>6920084</v>
+        <v>3920084</v>
       </c>
       <c r="B1337" s="26">
         <v>1</v>
@@ -41541,7 +41661,7 @@
         <v>0</v>
       </c>
       <c r="D1337" s="28" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="E1337" s="29" t="s">
         <v>769</v>
@@ -41558,7 +41678,7 @@
     </row>
     <row r="1338" spans="1:9">
       <c r="A1338">
-        <v>7920084</v>
+        <v>4920084</v>
       </c>
       <c r="B1338" s="26">
         <v>1</v>
@@ -41567,7 +41687,7 @@
         <v>0</v>
       </c>
       <c r="D1338" s="28" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="E1338" s="29" t="s">
         <v>769</v>
@@ -41576,15 +41696,15 @@
         <v>10</v>
       </c>
       <c r="H1338">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1338">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1339" spans="1:9">
       <c r="A1339">
-        <v>8920084</v>
+        <v>5920084</v>
       </c>
       <c r="B1339" s="26">
         <v>1</v>
@@ -41593,7 +41713,7 @@
         <v>0</v>
       </c>
       <c r="D1339" s="28" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="E1339" s="29" t="s">
         <v>769</v>
@@ -41610,7 +41730,7 @@
     </row>
     <row r="1340" spans="1:9">
       <c r="A1340">
-        <v>9920084</v>
+        <v>6920084</v>
       </c>
       <c r="B1340" s="26">
         <v>1</v>
@@ -41619,7 +41739,7 @@
         <v>0</v>
       </c>
       <c r="D1340" s="28" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="E1340" s="29" t="s">
         <v>769</v>
@@ -41628,7 +41748,7 @@
         <v>10</v>
       </c>
       <c r="H1340">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1340">
         <v>0</v>
@@ -41636,7 +41756,7 @@
     </row>
     <row r="1341" spans="1:9">
       <c r="A1341">
-        <v>13920084</v>
+        <v>7920084</v>
       </c>
       <c r="B1341" s="26">
         <v>1</v>
@@ -41645,7 +41765,7 @@
         <v>0</v>
       </c>
       <c r="D1341" s="28" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="E1341" s="29" t="s">
         <v>769</v>
@@ -41654,15 +41774,15 @@
         <v>10</v>
       </c>
       <c r="H1341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1341">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1342" spans="1:9">
       <c r="A1342">
-        <v>16920084</v>
+        <v>8920084</v>
       </c>
       <c r="B1342" s="26">
         <v>1</v>
@@ -41671,12 +41791,11 @@
         <v>0</v>
       </c>
       <c r="D1342" s="28" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="E1342" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1342" s="28"/>
       <c r="G1342">
         <v>10</v>
       </c>
@@ -41684,12 +41803,12 @@
         <v>1</v>
       </c>
       <c r="I1342">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1343" spans="1:9">
       <c r="A1343">
-        <v>920085</v>
+        <v>9920084</v>
       </c>
       <c r="B1343" s="26">
         <v>1</v>
@@ -41698,16 +41817,16 @@
         <v>0</v>
       </c>
       <c r="D1343" s="28" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="E1343" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1343">
         <v>10</v>
       </c>
       <c r="H1343">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1343">
         <v>0</v>
@@ -41715,7 +41834,7 @@
     </row>
     <row r="1344" spans="1:9">
       <c r="A1344">
-        <v>1920085</v>
+        <v>13920084</v>
       </c>
       <c r="B1344" s="26">
         <v>1</v>
@@ -41724,7 +41843,7 @@
         <v>0</v>
       </c>
       <c r="D1344" s="28" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="E1344" s="29" t="s">
         <v>769</v>
@@ -41736,12 +41855,12 @@
         <v>1</v>
       </c>
       <c r="I1344">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1345" spans="1:9">
       <c r="A1345">
-        <v>2920085</v>
+        <v>16920084</v>
       </c>
       <c r="B1345" s="26">
         <v>1</v>
@@ -41750,11 +41869,12 @@
         <v>0</v>
       </c>
       <c r="D1345" s="28" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="E1345" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1345" s="28"/>
       <c r="G1345">
         <v>10</v>
       </c>
@@ -41762,12 +41882,12 @@
         <v>1</v>
       </c>
       <c r="I1345">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1346" spans="1:9">
       <c r="A1346">
-        <v>3920085</v>
+        <v>920085</v>
       </c>
       <c r="B1346" s="26">
         <v>1</v>
@@ -41776,10 +41896,10 @@
         <v>0</v>
       </c>
       <c r="D1346" s="28" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="E1346" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1346">
         <v>10</v>
@@ -41793,7 +41913,7 @@
     </row>
     <row r="1347" spans="1:9">
       <c r="A1347">
-        <v>4920085</v>
+        <v>1920085</v>
       </c>
       <c r="B1347" s="26">
         <v>1</v>
@@ -41802,7 +41922,7 @@
         <v>0</v>
       </c>
       <c r="D1347" s="28" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="E1347" s="29" t="s">
         <v>769</v>
@@ -41819,7 +41939,7 @@
     </row>
     <row r="1348" spans="1:9">
       <c r="A1348">
-        <v>5920085</v>
+        <v>2920085</v>
       </c>
       <c r="B1348" s="26">
         <v>1</v>
@@ -41828,7 +41948,7 @@
         <v>0</v>
       </c>
       <c r="D1348" s="28" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="E1348" s="29" t="s">
         <v>769</v>
@@ -41840,12 +41960,12 @@
         <v>1</v>
       </c>
       <c r="I1348">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1349" spans="1:9">
       <c r="A1349">
-        <v>6920085</v>
+        <v>3920085</v>
       </c>
       <c r="B1349" s="26">
         <v>1</v>
@@ -41854,7 +41974,7 @@
         <v>0</v>
       </c>
       <c r="D1349" s="28" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="E1349" s="29" t="s">
         <v>769</v>
@@ -41871,7 +41991,7 @@
     </row>
     <row r="1350" spans="1:9">
       <c r="A1350">
-        <v>7920085</v>
+        <v>4920085</v>
       </c>
       <c r="B1350" s="26">
         <v>1</v>
@@ -41880,7 +42000,7 @@
         <v>0</v>
       </c>
       <c r="D1350" s="28" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="E1350" s="29" t="s">
         <v>769</v>
@@ -41889,15 +42009,15 @@
         <v>10</v>
       </c>
       <c r="H1350">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1350">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1351" spans="1:9">
       <c r="A1351">
-        <v>8920085</v>
+        <v>5920085</v>
       </c>
       <c r="B1351" s="26">
         <v>1</v>
@@ -41906,7 +42026,7 @@
         <v>0</v>
       </c>
       <c r="D1351" s="28" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="E1351" s="29" t="s">
         <v>769</v>
@@ -41918,12 +42038,12 @@
         <v>1</v>
       </c>
       <c r="I1351">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1352" spans="1:9">
       <c r="A1352">
-        <v>9920085</v>
+        <v>6920085</v>
       </c>
       <c r="B1352" s="26">
         <v>1</v>
@@ -41932,7 +42052,7 @@
         <v>0</v>
       </c>
       <c r="D1352" s="28" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="E1352" s="29" t="s">
         <v>769</v>
@@ -41941,15 +42061,15 @@
         <v>10</v>
       </c>
       <c r="H1352">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1352">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1353" spans="1:9">
       <c r="A1353">
-        <v>920086</v>
+        <v>7920085</v>
       </c>
       <c r="B1353" s="26">
         <v>1</v>
@@ -41958,25 +42078,24 @@
         <v>0</v>
       </c>
       <c r="D1353" s="28" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="E1353" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1353" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1353">
         <v>10</v>
       </c>
       <c r="H1353">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1353">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1354" spans="1:9">
       <c r="A1354">
-        <v>820086</v>
+        <v>8920085</v>
       </c>
       <c r="B1354" s="26">
         <v>1</v>
@@ -41984,11 +42103,11 @@
       <c r="C1354">
         <v>0</v>
       </c>
-      <c r="D1354" s="30" t="s">
-        <v>952</v>
-      </c>
-      <c r="E1354" s="30" t="s">
-        <v>952</v>
+      <c r="D1354" s="28" t="s">
+        <v>957</v>
+      </c>
+      <c r="E1354" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1354">
         <v>10</v>
@@ -42002,7 +42121,7 @@
     </row>
     <row r="1355" spans="1:9">
       <c r="A1355">
-        <v>8200861</v>
+        <v>9920085</v>
       </c>
       <c r="B1355" s="26">
         <v>1</v>
@@ -42010,11 +42129,11 @@
       <c r="C1355">
         <v>0</v>
       </c>
-      <c r="D1355" s="30" t="s">
-        <v>953</v>
-      </c>
-      <c r="E1355" s="30" t="s">
-        <v>954</v>
+      <c r="D1355" s="28" t="s">
+        <v>958</v>
+      </c>
+      <c r="E1355" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1355">
         <v>10</v>
@@ -42023,12 +42142,12 @@
         <v>2</v>
       </c>
       <c r="I1355">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1356" spans="1:9">
       <c r="A1356">
-        <v>990001</v>
+        <v>920086</v>
       </c>
       <c r="B1356" s="26">
         <v>1</v>
@@ -42037,7 +42156,7 @@
         <v>0</v>
       </c>
       <c r="D1356" s="28" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="E1356" s="29" t="s">
         <v>767</v>
@@ -42050,12 +42169,12 @@
         <v>1</v>
       </c>
       <c r="I1356">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1357" spans="1:9">
       <c r="A1357">
-        <v>890001</v>
+        <v>820086</v>
       </c>
       <c r="B1357" s="26">
         <v>1</v>
@@ -42063,11 +42182,11 @@
       <c r="C1357">
         <v>0</v>
       </c>
-      <c r="D1357" s="28" t="s">
-        <v>956</v>
-      </c>
-      <c r="E1357" s="28" t="s">
-        <v>956</v>
+      <c r="D1357" s="30" t="s">
+        <v>960</v>
+      </c>
+      <c r="E1357" s="30" t="s">
+        <v>960</v>
       </c>
       <c r="G1357">
         <v>10</v>
@@ -42081,7 +42200,7 @@
     </row>
     <row r="1358" spans="1:9">
       <c r="A1358">
-        <v>890011</v>
+        <v>8200861</v>
       </c>
       <c r="B1358" s="26">
         <v>1</v>
@@ -42089,17 +42208,17 @@
       <c r="C1358">
         <v>0</v>
       </c>
-      <c r="D1358" s="28" t="s">
-        <v>957</v>
-      </c>
-      <c r="E1358" s="28" t="s">
-        <v>957</v>
+      <c r="D1358" s="30" t="s">
+        <v>961</v>
+      </c>
+      <c r="E1358" s="30" t="s">
+        <v>962</v>
       </c>
       <c r="G1358">
         <v>10</v>
       </c>
       <c r="H1358">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1358">
         <v>0</v>
@@ -42107,7 +42226,7 @@
     </row>
     <row r="1359" spans="1:9">
       <c r="A1359">
-        <v>890021</v>
+        <v>990001</v>
       </c>
       <c r="B1359" s="26">
         <v>1</v>
@@ -42116,11 +42235,12 @@
         <v>0</v>
       </c>
       <c r="D1359" s="28" t="s">
-        <v>958</v>
-      </c>
-      <c r="E1359" s="28" t="s">
-        <v>959</v>
-      </c>
+        <v>963</v>
+      </c>
+      <c r="E1359" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1359" s="28"/>
       <c r="G1359">
         <v>10</v>
       </c>
@@ -42128,32 +42248,110 @@
         <v>1</v>
       </c>
       <c r="I1359">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1360" spans="1:9">
       <c r="A1360">
+        <v>890001</v>
+      </c>
+      <c r="B1360" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1360">
+        <v>0</v>
+      </c>
+      <c r="D1360" s="28" t="s">
+        <v>964</v>
+      </c>
+      <c r="E1360" s="28" t="s">
+        <v>964</v>
+      </c>
+      <c r="G1360">
+        <v>10</v>
+      </c>
+      <c r="H1360">
+        <v>1</v>
+      </c>
+      <c r="I1360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:9">
+      <c r="A1361">
+        <v>890011</v>
+      </c>
+      <c r="B1361" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1361">
+        <v>0</v>
+      </c>
+      <c r="D1361" s="28" t="s">
+        <v>965</v>
+      </c>
+      <c r="E1361" s="28" t="s">
+        <v>965</v>
+      </c>
+      <c r="G1361">
+        <v>10</v>
+      </c>
+      <c r="H1361">
+        <v>3</v>
+      </c>
+      <c r="I1361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:9">
+      <c r="A1362">
+        <v>890021</v>
+      </c>
+      <c r="B1362" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1362">
+        <v>0</v>
+      </c>
+      <c r="D1362" s="28" t="s">
+        <v>966</v>
+      </c>
+      <c r="E1362" s="28" t="s">
+        <v>967</v>
+      </c>
+      <c r="G1362">
+        <v>10</v>
+      </c>
+      <c r="H1362">
+        <v>1</v>
+      </c>
+      <c r="I1362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:9">
+      <c r="A1363">
         <v>890022</v>
       </c>
-      <c r="B1360" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1360">
-        <v>0</v>
-      </c>
-      <c r="D1360" s="28" t="s">
-        <v>960</v>
-      </c>
-      <c r="E1360" s="28" t="s">
-        <v>961</v>
-      </c>
-      <c r="G1360">
-        <v>10</v>
-      </c>
-      <c r="H1360">
+      <c r="B1363" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1363">
+        <v>0</v>
+      </c>
+      <c r="D1363" s="28" t="s">
+        <v>968</v>
+      </c>
+      <c r="E1363" s="28" t="s">
+        <v>969</v>
+      </c>
+      <c r="G1363">
+        <v>10</v>
+      </c>
+      <c r="H1363">
         <v>2</v>
       </c>
-      <c r="I1360">
+      <c r="I1363">
         <v>0</v>
       </c>
     </row>
@@ -42219,7 +42417,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -42231,10 +42429,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -42248,90 +42446,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="K4" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>986</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>988</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -42342,7 +42540,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -42363,7 +42561,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -42375,7 +42573,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42386,7 +42584,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -42427,7 +42625,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -42468,7 +42666,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -42489,7 +42687,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -42501,7 +42699,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -42512,7 +42710,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -42533,7 +42731,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -42545,7 +42743,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -42556,7 +42754,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -42577,7 +42775,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -11,7 +11,7 @@
     <sheet name="maze_attribute_formula_v8" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1360</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="1010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3666" uniqueCount="1011">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2925,6 +2925,9 @@
   </si>
   <si>
     <t>超级暴风雪_获得</t>
+  </si>
+  <si>
+    <t>超级暴风雪_最远释放距离</t>
   </si>
   <si>
     <t>超级暴风雪_弹道数量</t>
@@ -4394,7 +4397,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1363"/>
+  <dimension ref="A1:I1364"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -41224,7 +41227,7 @@
     </row>
     <row r="1321" spans="1:9">
       <c r="A1321">
-        <v>14920074</v>
+        <v>3920074</v>
       </c>
       <c r="B1321" s="26">
         <v>1</v>
@@ -41246,12 +41249,12 @@
         <v>1</v>
       </c>
       <c r="I1321">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1322" spans="1:9">
       <c r="A1322">
-        <v>16920074</v>
+        <v>14920074</v>
       </c>
       <c r="B1322" s="26">
         <v>1</v>
@@ -41270,15 +41273,15 @@
         <v>10</v>
       </c>
       <c r="H1322">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1322">
-        <v>10000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1323" spans="1:9">
       <c r="A1323">
-        <v>17920074</v>
+        <v>16920074</v>
       </c>
       <c r="B1323" s="26">
         <v>1</v>
@@ -41300,12 +41303,12 @@
         <v>2</v>
       </c>
       <c r="I1323">
-        <v>2000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1324" spans="1:9">
       <c r="A1324">
-        <v>18920074</v>
+        <v>17920074</v>
       </c>
       <c r="B1324" s="26">
         <v>1</v>
@@ -41327,12 +41330,12 @@
         <v>2</v>
       </c>
       <c r="I1324">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1325" spans="1:9">
       <c r="A1325">
-        <v>920075</v>
+        <v>18920074</v>
       </c>
       <c r="B1325" s="26">
         <v>1</v>
@@ -41351,15 +41354,15 @@
         <v>10</v>
       </c>
       <c r="H1325">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1325">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1326" spans="1:9">
       <c r="A1326">
-        <v>1920075</v>
+        <v>920075</v>
       </c>
       <c r="B1326" s="26">
         <v>1</v>
@@ -41386,7 +41389,7 @@
     </row>
     <row r="1327" spans="1:9">
       <c r="A1327">
-        <v>4920075</v>
+        <v>1920075</v>
       </c>
       <c r="B1327" s="26">
         <v>1</v>
@@ -41408,12 +41411,12 @@
         <v>1</v>
       </c>
       <c r="I1327">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1328" spans="1:9">
       <c r="A1328">
-        <v>10920075</v>
+        <v>4920075</v>
       </c>
       <c r="B1328" s="26">
         <v>1</v>
@@ -41435,12 +41438,12 @@
         <v>1</v>
       </c>
       <c r="I1328">
-        <v>4000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1329" spans="1:9">
       <c r="A1329">
-        <v>18920075</v>
+        <v>10920075</v>
       </c>
       <c r="B1329" s="26">
         <v>1</v>
@@ -41462,12 +41465,12 @@
         <v>1</v>
       </c>
       <c r="I1329">
-        <v>500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1330" spans="1:9">
       <c r="A1330">
-        <v>11920075</v>
+        <v>18920075</v>
       </c>
       <c r="B1330" s="26">
         <v>1</v>
@@ -41489,12 +41492,12 @@
         <v>1</v>
       </c>
       <c r="I1330">
-        <v>10500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1331" spans="1:9">
       <c r="A1331">
-        <v>13920075</v>
+        <v>11920075</v>
       </c>
       <c r="B1331" s="26">
         <v>1</v>
@@ -41516,12 +41519,12 @@
         <v>1</v>
       </c>
       <c r="I1331">
-        <v>1</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="1332" spans="1:9">
       <c r="A1332">
-        <v>920073</v>
+        <v>13920075</v>
       </c>
       <c r="B1332" s="26">
         <v>1</v>
@@ -41533,7 +41536,7 @@
         <v>935</v>
       </c>
       <c r="E1332" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1332" s="28"/>
       <c r="G1332">
@@ -41543,12 +41546,12 @@
         <v>1</v>
       </c>
       <c r="I1332">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1333" spans="1:9">
       <c r="A1333">
-        <v>820073</v>
+        <v>920073</v>
       </c>
       <c r="B1333" s="26">
         <v>1</v>
@@ -41556,12 +41559,13 @@
       <c r="C1333">
         <v>0</v>
       </c>
-      <c r="D1333" s="30" t="s">
+      <c r="D1333" s="28" t="s">
         <v>936</v>
       </c>
-      <c r="E1333" s="30" t="s">
-        <v>936</v>
-      </c>
+      <c r="E1333" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1333" s="28"/>
       <c r="G1333">
         <v>10</v>
       </c>
@@ -41574,7 +41578,7 @@
     </row>
     <row r="1334" spans="1:9">
       <c r="A1334">
-        <v>920084</v>
+        <v>820073</v>
       </c>
       <c r="B1334" s="26">
         <v>1</v>
@@ -41582,11 +41586,11 @@
       <c r="C1334">
         <v>0</v>
       </c>
-      <c r="D1334" s="28" t="s">
+      <c r="D1334" s="30" t="s">
         <v>937</v>
       </c>
-      <c r="E1334" s="29" t="s">
-        <v>767</v>
+      <c r="E1334" s="30" t="s">
+        <v>937</v>
       </c>
       <c r="G1334">
         <v>10</v>
@@ -41600,7 +41604,7 @@
     </row>
     <row r="1335" spans="1:9">
       <c r="A1335">
-        <v>1920084</v>
+        <v>920084</v>
       </c>
       <c r="B1335" s="26">
         <v>1</v>
@@ -41612,7 +41616,7 @@
         <v>938</v>
       </c>
       <c r="E1335" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1335">
         <v>10</v>
@@ -41621,12 +41625,12 @@
         <v>1</v>
       </c>
       <c r="I1335">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1336" spans="1:9">
       <c r="A1336">
-        <v>2920084</v>
+        <v>1920084</v>
       </c>
       <c r="B1336" s="26">
         <v>1</v>
@@ -41647,12 +41651,12 @@
         <v>1</v>
       </c>
       <c r="I1336">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1337" spans="1:9">
       <c r="A1337">
-        <v>3920084</v>
+        <v>2920084</v>
       </c>
       <c r="B1337" s="26">
         <v>1</v>
@@ -41678,7 +41682,7 @@
     </row>
     <row r="1338" spans="1:9">
       <c r="A1338">
-        <v>4920084</v>
+        <v>3920084</v>
       </c>
       <c r="B1338" s="26">
         <v>1</v>
@@ -41699,12 +41703,12 @@
         <v>1</v>
       </c>
       <c r="I1338">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1339" spans="1:9">
       <c r="A1339">
-        <v>5920084</v>
+        <v>4920084</v>
       </c>
       <c r="B1339" s="26">
         <v>1</v>
@@ -41725,12 +41729,12 @@
         <v>1</v>
       </c>
       <c r="I1339">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1340" spans="1:9">
       <c r="A1340">
-        <v>6920084</v>
+        <v>5920084</v>
       </c>
       <c r="B1340" s="26">
         <v>1</v>
@@ -41756,7 +41760,7 @@
     </row>
     <row r="1341" spans="1:9">
       <c r="A1341">
-        <v>7920084</v>
+        <v>6920084</v>
       </c>
       <c r="B1341" s="26">
         <v>1</v>
@@ -41774,7 +41778,7 @@
         <v>10</v>
       </c>
       <c r="H1341">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1341">
         <v>0</v>
@@ -41782,7 +41786,7 @@
     </row>
     <row r="1342" spans="1:9">
       <c r="A1342">
-        <v>8920084</v>
+        <v>7920084</v>
       </c>
       <c r="B1342" s="26">
         <v>1</v>
@@ -41800,7 +41804,7 @@
         <v>10</v>
       </c>
       <c r="H1342">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1342">
         <v>0</v>
@@ -41808,7 +41812,7 @@
     </row>
     <row r="1343" spans="1:9">
       <c r="A1343">
-        <v>9920084</v>
+        <v>8920084</v>
       </c>
       <c r="B1343" s="26">
         <v>1</v>
@@ -41826,7 +41830,7 @@
         <v>10</v>
       </c>
       <c r="H1343">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1343">
         <v>0</v>
@@ -41834,7 +41838,7 @@
     </row>
     <row r="1344" spans="1:9">
       <c r="A1344">
-        <v>13920084</v>
+        <v>9920084</v>
       </c>
       <c r="B1344" s="26">
         <v>1</v>
@@ -41852,15 +41856,15 @@
         <v>10</v>
       </c>
       <c r="H1344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1344">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1345" spans="1:9">
       <c r="A1345">
-        <v>16920084</v>
+        <v>13920084</v>
       </c>
       <c r="B1345" s="26">
         <v>1</v>
@@ -41874,7 +41878,6 @@
       <c r="E1345" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1345" s="28"/>
       <c r="G1345">
         <v>10</v>
       </c>
@@ -41882,12 +41885,12 @@
         <v>1</v>
       </c>
       <c r="I1345">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1346" spans="1:9">
       <c r="A1346">
-        <v>920085</v>
+        <v>16920084</v>
       </c>
       <c r="B1346" s="26">
         <v>1</v>
@@ -41899,8 +41902,9 @@
         <v>949</v>
       </c>
       <c r="E1346" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1346" s="28"/>
       <c r="G1346">
         <v>10</v>
       </c>
@@ -41908,12 +41912,12 @@
         <v>1</v>
       </c>
       <c r="I1346">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1347" spans="1:9">
       <c r="A1347">
-        <v>1920085</v>
+        <v>920085</v>
       </c>
       <c r="B1347" s="26">
         <v>1</v>
@@ -41925,7 +41929,7 @@
         <v>950</v>
       </c>
       <c r="E1347" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1347">
         <v>10</v>
@@ -41939,7 +41943,7 @@
     </row>
     <row r="1348" spans="1:9">
       <c r="A1348">
-        <v>2920085</v>
+        <v>1920085</v>
       </c>
       <c r="B1348" s="26">
         <v>1</v>
@@ -41965,7 +41969,7 @@
     </row>
     <row r="1349" spans="1:9">
       <c r="A1349">
-        <v>3920085</v>
+        <v>2920085</v>
       </c>
       <c r="B1349" s="26">
         <v>1</v>
@@ -41991,7 +41995,7 @@
     </row>
     <row r="1350" spans="1:9">
       <c r="A1350">
-        <v>4920085</v>
+        <v>3920085</v>
       </c>
       <c r="B1350" s="26">
         <v>1</v>
@@ -42017,7 +42021,7 @@
     </row>
     <row r="1351" spans="1:9">
       <c r="A1351">
-        <v>5920085</v>
+        <v>4920085</v>
       </c>
       <c r="B1351" s="26">
         <v>1</v>
@@ -42038,12 +42042,12 @@
         <v>1</v>
       </c>
       <c r="I1351">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1352" spans="1:9">
       <c r="A1352">
-        <v>6920085</v>
+        <v>5920085</v>
       </c>
       <c r="B1352" s="26">
         <v>1</v>
@@ -42064,12 +42068,12 @@
         <v>1</v>
       </c>
       <c r="I1352">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1353" spans="1:9">
       <c r="A1353">
-        <v>7920085</v>
+        <v>6920085</v>
       </c>
       <c r="B1353" s="26">
         <v>1</v>
@@ -42087,15 +42091,15 @@
         <v>10</v>
       </c>
       <c r="H1353">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1353">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1354" spans="1:9">
       <c r="A1354">
-        <v>8920085</v>
+        <v>7920085</v>
       </c>
       <c r="B1354" s="26">
         <v>1</v>
@@ -42113,15 +42117,15 @@
         <v>10</v>
       </c>
       <c r="H1354">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1354">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1355" spans="1:9">
       <c r="A1355">
-        <v>9920085</v>
+        <v>8920085</v>
       </c>
       <c r="B1355" s="26">
         <v>1</v>
@@ -42139,15 +42143,15 @@
         <v>10</v>
       </c>
       <c r="H1355">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1355">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1356" spans="1:9">
       <c r="A1356">
-        <v>920086</v>
+        <v>9920085</v>
       </c>
       <c r="B1356" s="26">
         <v>1</v>
@@ -42159,22 +42163,21 @@
         <v>959</v>
       </c>
       <c r="E1356" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1356" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1356">
         <v>10</v>
       </c>
       <c r="H1356">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1356">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1357" spans="1:9">
       <c r="A1357">
-        <v>820086</v>
+        <v>920086</v>
       </c>
       <c r="B1357" s="26">
         <v>1</v>
@@ -42182,12 +42185,13 @@
       <c r="C1357">
         <v>0</v>
       </c>
-      <c r="D1357" s="30" t="s">
+      <c r="D1357" s="28" t="s">
         <v>960</v>
       </c>
-      <c r="E1357" s="30" t="s">
-        <v>960</v>
-      </c>
+      <c r="E1357" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1357" s="28"/>
       <c r="G1357">
         <v>10</v>
       </c>
@@ -42200,7 +42204,7 @@
     </row>
     <row r="1358" spans="1:9">
       <c r="A1358">
-        <v>8200861</v>
+        <v>820086</v>
       </c>
       <c r="B1358" s="26">
         <v>1</v>
@@ -42212,13 +42216,13 @@
         <v>961</v>
       </c>
       <c r="E1358" s="30" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G1358">
         <v>10</v>
       </c>
       <c r="H1358">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1358">
         <v>0</v>
@@ -42226,7 +42230,7 @@
     </row>
     <row r="1359" spans="1:9">
       <c r="A1359">
-        <v>990001</v>
+        <v>8200861</v>
       </c>
       <c r="B1359" s="26">
         <v>1</v>
@@ -42234,26 +42238,25 @@
       <c r="C1359">
         <v>0</v>
       </c>
-      <c r="D1359" s="28" t="s">
+      <c r="D1359" s="30" t="s">
+        <v>962</v>
+      </c>
+      <c r="E1359" s="30" t="s">
         <v>963</v>
       </c>
-      <c r="E1359" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1359" s="28"/>
       <c r="G1359">
         <v>10</v>
       </c>
       <c r="H1359">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1359">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1360" spans="1:9">
       <c r="A1360">
-        <v>890001</v>
+        <v>990001</v>
       </c>
       <c r="B1360" s="26">
         <v>1</v>
@@ -42264,9 +42267,10 @@
       <c r="D1360" s="28" t="s">
         <v>964</v>
       </c>
-      <c r="E1360" s="28" t="s">
-        <v>964</v>
-      </c>
+      <c r="E1360" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1360" s="28"/>
       <c r="G1360">
         <v>10</v>
       </c>
@@ -42274,12 +42278,12 @@
         <v>1</v>
       </c>
       <c r="I1360">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1361" spans="1:9">
       <c r="A1361">
-        <v>890011</v>
+        <v>890001</v>
       </c>
       <c r="B1361" s="26">
         <v>1</v>
@@ -42297,7 +42301,7 @@
         <v>10</v>
       </c>
       <c r="H1361">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1361">
         <v>0</v>
@@ -42305,7 +42309,7 @@
     </row>
     <row r="1362" spans="1:9">
       <c r="A1362">
-        <v>890021</v>
+        <v>890011</v>
       </c>
       <c r="B1362" s="26">
         <v>1</v>
@@ -42317,13 +42321,13 @@
         <v>966</v>
       </c>
       <c r="E1362" s="28" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G1362">
         <v>10</v>
       </c>
       <c r="H1362">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1362">
         <v>0</v>
@@ -42331,27 +42335,53 @@
     </row>
     <row r="1363" spans="1:9">
       <c r="A1363">
+        <v>890021</v>
+      </c>
+      <c r="B1363" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1363">
+        <v>0</v>
+      </c>
+      <c r="D1363" s="28" t="s">
+        <v>967</v>
+      </c>
+      <c r="E1363" s="28" t="s">
+        <v>968</v>
+      </c>
+      <c r="G1363">
+        <v>10</v>
+      </c>
+      <c r="H1363">
+        <v>1</v>
+      </c>
+      <c r="I1363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:9">
+      <c r="A1364">
         <v>890022</v>
       </c>
-      <c r="B1363" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1363">
-        <v>0</v>
-      </c>
-      <c r="D1363" s="28" t="s">
-        <v>968</v>
-      </c>
-      <c r="E1363" s="28" t="s">
+      <c r="B1364" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1364">
+        <v>0</v>
+      </c>
+      <c r="D1364" s="28" t="s">
         <v>969</v>
       </c>
-      <c r="G1363">
-        <v>10</v>
-      </c>
-      <c r="H1363">
+      <c r="E1364" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="G1364">
+        <v>10</v>
+      </c>
+      <c r="H1364">
         <v>2</v>
       </c>
-      <c r="I1363">
+      <c r="I1364">
         <v>0</v>
       </c>
     </row>
@@ -42417,7 +42447,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -42429,10 +42459,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -42446,90 +42476,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>987</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>988</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>990</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>991</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>992</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>993</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>994</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>996</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -42540,7 +42570,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -42561,7 +42591,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -42573,7 +42603,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42584,7 +42614,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -42625,7 +42655,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -42666,7 +42696,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -42687,7 +42717,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -42699,7 +42729,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -42710,7 +42740,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -42731,7 +42761,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -42743,7 +42773,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -42754,7 +42784,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -42775,7 +42805,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3453,12 +3453,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -37192,7 +37192,7 @@
         <v>2</v>
       </c>
       <c r="I1167">
-        <v>18000</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="1168" spans="1:9">
@@ -37244,7 +37244,7 @@
         <v>2</v>
       </c>
       <c r="I1169">
-        <v>18000</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="1170" spans="1:9">
@@ -37505,7 +37505,7 @@
         <v>2</v>
       </c>
       <c r="I1179">
-        <v>15500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="1180" spans="1:9">
@@ -37557,7 +37557,7 @@
         <v>2</v>
       </c>
       <c r="I1181">
-        <v>15500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="1182" spans="1:9">
@@ -37791,7 +37791,7 @@
         <v>2</v>
       </c>
       <c r="I1190">
-        <v>12500</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="1191" spans="1:9">
@@ -37843,7 +37843,7 @@
         <v>2</v>
       </c>
       <c r="I1192">
-        <v>12500</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="1193" spans="1:9">
@@ -38293,7 +38293,7 @@
         <v>2</v>
       </c>
       <c r="I1209">
-        <v>15000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1210" spans="1:9">
@@ -38345,7 +38345,7 @@
         <v>2</v>
       </c>
       <c r="I1211">
-        <v>15000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1212" spans="1:9">
@@ -38947,7 +38947,7 @@
         <v>2</v>
       </c>
       <c r="I1234">
-        <v>4500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1235" spans="1:9">
@@ -38999,7 +38999,7 @@
         <v>2</v>
       </c>
       <c r="I1236">
-        <v>4500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1237" spans="1:9">
@@ -39745,7 +39745,7 @@
         <v>1</v>
       </c>
       <c r="I1264">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1265" spans="1:9">
@@ -40904,7 +40904,7 @@
         <v>2</v>
       </c>
       <c r="I1308">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
@@ -40956,7 +40956,7 @@
         <v>2</v>
       </c>
       <c r="I1310">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1311" spans="1:9">
@@ -40983,7 +40983,7 @@
         <v>1</v>
       </c>
       <c r="I1311">
-        <v>6000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1312" spans="1:9">
@@ -41064,7 +41064,7 @@
         <v>1</v>
       </c>
       <c r="I1314">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1315" spans="1:9">
@@ -42120,7 +42120,7 @@
         <v>2</v>
       </c>
       <c r="I1354">
-        <v>30000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="1355" spans="1:9">
@@ -42172,7 +42172,7 @@
         <v>2</v>
       </c>
       <c r="I1356">
-        <v>30000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="1357" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -11,7 +11,7 @@
     <sheet name="maze_attribute_formula_v8" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1360</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1353</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3666" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3652" uniqueCount="1004">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2940,27 +2940,6 @@
   </si>
   <si>
     <t>超级暴风雪_伤害倍率</t>
-  </si>
-  <si>
-    <t>超级暴风雪_极寒领域获取</t>
-  </si>
-  <si>
-    <t>超级暴风雪_极寒领域冷却</t>
-  </si>
-  <si>
-    <t>超级暴风雪_极寒领域技能效果半径</t>
-  </si>
-  <si>
-    <t>超级暴风雪_极寒领域技能持续时间</t>
-  </si>
-  <si>
-    <t>超级暴风雪_极寒领域伤害或效果生效间隔</t>
-  </si>
-  <si>
-    <t>超级暴风雪_极寒领域伤害系数</t>
-  </si>
-  <si>
-    <t>超级暴风雪_极寒领域技能等级</t>
   </si>
   <si>
     <t>冰风暴被动_获得</t>
@@ -4397,7 +4376,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1364"/>
+  <dimension ref="A1:I1357"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -41362,7 +41341,7 @@
     </row>
     <row r="1326" spans="1:9">
       <c r="A1326">
-        <v>920075</v>
+        <v>920073</v>
       </c>
       <c r="B1326" s="26">
         <v>1</v>
@@ -41374,7 +41353,7 @@
         <v>929</v>
       </c>
       <c r="E1326" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F1326" s="28"/>
       <c r="G1326">
@@ -41389,7 +41368,7 @@
     </row>
     <row r="1327" spans="1:9">
       <c r="A1327">
-        <v>1920075</v>
+        <v>820073</v>
       </c>
       <c r="B1327" s="26">
         <v>1</v>
@@ -41397,13 +41376,12 @@
       <c r="C1327">
         <v>0</v>
       </c>
-      <c r="D1327" s="28" t="s">
+      <c r="D1327" s="30" t="s">
         <v>930</v>
       </c>
-      <c r="E1327" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1327" s="28"/>
+      <c r="E1327" s="30" t="s">
+        <v>930</v>
+      </c>
       <c r="G1327">
         <v>10</v>
       </c>
@@ -41416,7 +41394,7 @@
     </row>
     <row r="1328" spans="1:9">
       <c r="A1328">
-        <v>4920075</v>
+        <v>920084</v>
       </c>
       <c r="B1328" s="26">
         <v>1</v>
@@ -41428,9 +41406,8 @@
         <v>931</v>
       </c>
       <c r="E1328" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1328" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1328">
         <v>10</v>
       </c>
@@ -41438,12 +41415,12 @@
         <v>1</v>
       </c>
       <c r="I1328">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1329" spans="1:9">
       <c r="A1329">
-        <v>10920075</v>
+        <v>1920084</v>
       </c>
       <c r="B1329" s="26">
         <v>1</v>
@@ -41457,7 +41434,6 @@
       <c r="E1329" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1329" s="28"/>
       <c r="G1329">
         <v>10</v>
       </c>
@@ -41465,12 +41441,12 @@
         <v>1</v>
       </c>
       <c r="I1329">
-        <v>4000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1330" spans="1:9">
       <c r="A1330">
-        <v>18920075</v>
+        <v>2920084</v>
       </c>
       <c r="B1330" s="26">
         <v>1</v>
@@ -41484,7 +41460,6 @@
       <c r="E1330" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1330" s="28"/>
       <c r="G1330">
         <v>10</v>
       </c>
@@ -41492,12 +41467,12 @@
         <v>1</v>
       </c>
       <c r="I1330">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1331" spans="1:9">
       <c r="A1331">
-        <v>11920075</v>
+        <v>3920084</v>
       </c>
       <c r="B1331" s="26">
         <v>1</v>
@@ -41511,7 +41486,6 @@
       <c r="E1331" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1331" s="28"/>
       <c r="G1331">
         <v>10</v>
       </c>
@@ -41519,12 +41493,12 @@
         <v>1</v>
       </c>
       <c r="I1331">
-        <v>10500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1332" spans="1:9">
       <c r="A1332">
-        <v>13920075</v>
+        <v>4920084</v>
       </c>
       <c r="B1332" s="26">
         <v>1</v>
@@ -41538,7 +41512,6 @@
       <c r="E1332" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1332" s="28"/>
       <c r="G1332">
         <v>10</v>
       </c>
@@ -41546,12 +41519,12 @@
         <v>1</v>
       </c>
       <c r="I1332">
-        <v>1</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1333" spans="1:9">
       <c r="A1333">
-        <v>920073</v>
+        <v>5920084</v>
       </c>
       <c r="B1333" s="26">
         <v>1</v>
@@ -41563,9 +41536,8 @@
         <v>936</v>
       </c>
       <c r="E1333" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1333" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1333">
         <v>10</v>
       </c>
@@ -41578,7 +41550,7 @@
     </row>
     <row r="1334" spans="1:9">
       <c r="A1334">
-        <v>820073</v>
+        <v>6920084</v>
       </c>
       <c r="B1334" s="26">
         <v>1</v>
@@ -41586,11 +41558,11 @@
       <c r="C1334">
         <v>0</v>
       </c>
-      <c r="D1334" s="30" t="s">
+      <c r="D1334" s="28" t="s">
         <v>937</v>
       </c>
-      <c r="E1334" s="30" t="s">
-        <v>937</v>
+      <c r="E1334" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1334">
         <v>10</v>
@@ -41604,7 +41576,7 @@
     </row>
     <row r="1335" spans="1:9">
       <c r="A1335">
-        <v>920084</v>
+        <v>7920084</v>
       </c>
       <c r="B1335" s="26">
         <v>1</v>
@@ -41616,13 +41588,13 @@
         <v>938</v>
       </c>
       <c r="E1335" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1335">
         <v>10</v>
       </c>
       <c r="H1335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1335">
         <v>0</v>
@@ -41630,7 +41602,7 @@
     </row>
     <row r="1336" spans="1:9">
       <c r="A1336">
-        <v>1920084</v>
+        <v>8920084</v>
       </c>
       <c r="B1336" s="26">
         <v>1</v>
@@ -41651,12 +41623,12 @@
         <v>1</v>
       </c>
       <c r="I1336">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1337" spans="1:9">
       <c r="A1337">
-        <v>2920084</v>
+        <v>9920084</v>
       </c>
       <c r="B1337" s="26">
         <v>1</v>
@@ -41674,7 +41646,7 @@
         <v>10</v>
       </c>
       <c r="H1337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1337">
         <v>0</v>
@@ -41682,7 +41654,7 @@
     </row>
     <row r="1338" spans="1:9">
       <c r="A1338">
-        <v>3920084</v>
+        <v>13920084</v>
       </c>
       <c r="B1338" s="26">
         <v>1</v>
@@ -41703,12 +41675,12 @@
         <v>1</v>
       </c>
       <c r="I1338">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1339" spans="1:9">
       <c r="A1339">
-        <v>4920084</v>
+        <v>16920084</v>
       </c>
       <c r="B1339" s="26">
         <v>1</v>
@@ -41722,6 +41694,7 @@
       <c r="E1339" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1339" s="28"/>
       <c r="G1339">
         <v>10</v>
       </c>
@@ -41729,12 +41702,12 @@
         <v>1</v>
       </c>
       <c r="I1339">
-        <v>3500</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1340" spans="1:9">
       <c r="A1340">
-        <v>5920084</v>
+        <v>920085</v>
       </c>
       <c r="B1340" s="26">
         <v>1</v>
@@ -41746,7 +41719,7 @@
         <v>943</v>
       </c>
       <c r="E1340" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1340">
         <v>10</v>
@@ -41760,7 +41733,7 @@
     </row>
     <row r="1341" spans="1:9">
       <c r="A1341">
-        <v>6920084</v>
+        <v>1920085</v>
       </c>
       <c r="B1341" s="26">
         <v>1</v>
@@ -41786,7 +41759,7 @@
     </row>
     <row r="1342" spans="1:9">
       <c r="A1342">
-        <v>7920084</v>
+        <v>2920085</v>
       </c>
       <c r="B1342" s="26">
         <v>1</v>
@@ -41804,7 +41777,7 @@
         <v>10</v>
       </c>
       <c r="H1342">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1342">
         <v>0</v>
@@ -41812,7 +41785,7 @@
     </row>
     <row r="1343" spans="1:9">
       <c r="A1343">
-        <v>8920084</v>
+        <v>3920085</v>
       </c>
       <c r="B1343" s="26">
         <v>1</v>
@@ -41838,7 +41811,7 @@
     </row>
     <row r="1344" spans="1:9">
       <c r="A1344">
-        <v>9920084</v>
+        <v>4920085</v>
       </c>
       <c r="B1344" s="26">
         <v>1</v>
@@ -41856,7 +41829,7 @@
         <v>10</v>
       </c>
       <c r="H1344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1344">
         <v>0</v>
@@ -41864,7 +41837,7 @@
     </row>
     <row r="1345" spans="1:9">
       <c r="A1345">
-        <v>13920084</v>
+        <v>5920085</v>
       </c>
       <c r="B1345" s="26">
         <v>1</v>
@@ -41885,12 +41858,12 @@
         <v>1</v>
       </c>
       <c r="I1345">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1346" spans="1:9">
       <c r="A1346">
-        <v>16920084</v>
+        <v>6920085</v>
       </c>
       <c r="B1346" s="26">
         <v>1</v>
@@ -41904,7 +41877,6 @@
       <c r="E1346" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1346" s="28"/>
       <c r="G1346">
         <v>10</v>
       </c>
@@ -41912,12 +41884,12 @@
         <v>1</v>
       </c>
       <c r="I1346">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1347" spans="1:9">
       <c r="A1347">
-        <v>920085</v>
+        <v>7920085</v>
       </c>
       <c r="B1347" s="26">
         <v>1</v>
@@ -41929,21 +41901,21 @@
         <v>950</v>
       </c>
       <c r="E1347" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1347">
         <v>10</v>
       </c>
       <c r="H1347">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1347">
-        <v>0</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="1348" spans="1:9">
       <c r="A1348">
-        <v>1920085</v>
+        <v>8920085</v>
       </c>
       <c r="B1348" s="26">
         <v>1</v>
@@ -41969,7 +41941,7 @@
     </row>
     <row r="1349" spans="1:9">
       <c r="A1349">
-        <v>2920085</v>
+        <v>9920085</v>
       </c>
       <c r="B1349" s="26">
         <v>1</v>
@@ -41987,15 +41959,15 @@
         <v>10</v>
       </c>
       <c r="H1349">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1349">
-        <v>0</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="1350" spans="1:9">
       <c r="A1350">
-        <v>3920085</v>
+        <v>920086</v>
       </c>
       <c r="B1350" s="26">
         <v>1</v>
@@ -42007,8 +41979,9 @@
         <v>953</v>
       </c>
       <c r="E1350" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1350" s="28"/>
       <c r="G1350">
         <v>10</v>
       </c>
@@ -42021,7 +41994,7 @@
     </row>
     <row r="1351" spans="1:9">
       <c r="A1351">
-        <v>4920085</v>
+        <v>820086</v>
       </c>
       <c r="B1351" s="26">
         <v>1</v>
@@ -42029,11 +42002,11 @@
       <c r="C1351">
         <v>0</v>
       </c>
-      <c r="D1351" s="28" t="s">
+      <c r="D1351" s="30" t="s">
         <v>954</v>
       </c>
-      <c r="E1351" s="29" t="s">
-        <v>769</v>
+      <c r="E1351" s="30" t="s">
+        <v>954</v>
       </c>
       <c r="G1351">
         <v>10</v>
@@ -42047,7 +42020,7 @@
     </row>
     <row r="1352" spans="1:9">
       <c r="A1352">
-        <v>5920085</v>
+        <v>8200861</v>
       </c>
       <c r="B1352" s="26">
         <v>1</v>
@@ -42055,25 +42028,25 @@
       <c r="C1352">
         <v>0</v>
       </c>
-      <c r="D1352" s="28" t="s">
+      <c r="D1352" s="30" t="s">
         <v>955</v>
       </c>
-      <c r="E1352" s="29" t="s">
-        <v>769</v>
+      <c r="E1352" s="30" t="s">
+        <v>956</v>
       </c>
       <c r="G1352">
         <v>10</v>
       </c>
       <c r="H1352">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1352">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1353" spans="1:9">
       <c r="A1353">
-        <v>6920085</v>
+        <v>990001</v>
       </c>
       <c r="B1353" s="26">
         <v>1</v>
@@ -42082,11 +42055,12 @@
         <v>0</v>
       </c>
       <c r="D1353" s="28" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E1353" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1353" s="28"/>
       <c r="G1353">
         <v>10</v>
       </c>
@@ -42094,12 +42068,12 @@
         <v>1</v>
       </c>
       <c r="I1353">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1354" spans="1:9">
       <c r="A1354">
-        <v>7920085</v>
+        <v>890001</v>
       </c>
       <c r="B1354" s="26">
         <v>1</v>
@@ -42108,24 +42082,24 @@
         <v>0</v>
       </c>
       <c r="D1354" s="28" t="s">
-        <v>957</v>
-      </c>
-      <c r="E1354" s="29" t="s">
-        <v>769</v>
+        <v>958</v>
+      </c>
+      <c r="E1354" s="28" t="s">
+        <v>958</v>
       </c>
       <c r="G1354">
         <v>10</v>
       </c>
       <c r="H1354">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1354">
-        <v>35000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1355" spans="1:9">
       <c r="A1355">
-        <v>8920085</v>
+        <v>890011</v>
       </c>
       <c r="B1355" s="26">
         <v>1</v>
@@ -42134,16 +42108,16 @@
         <v>0</v>
       </c>
       <c r="D1355" s="28" t="s">
-        <v>958</v>
-      </c>
-      <c r="E1355" s="29" t="s">
-        <v>769</v>
+        <v>959</v>
+      </c>
+      <c r="E1355" s="28" t="s">
+        <v>959</v>
       </c>
       <c r="G1355">
         <v>10</v>
       </c>
       <c r="H1355">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1355">
         <v>0</v>
@@ -42151,7 +42125,7 @@
     </row>
     <row r="1356" spans="1:9">
       <c r="A1356">
-        <v>9920085</v>
+        <v>890021</v>
       </c>
       <c r="B1356" s="26">
         <v>1</v>
@@ -42160,24 +42134,24 @@
         <v>0</v>
       </c>
       <c r="D1356" s="28" t="s">
-        <v>959</v>
-      </c>
-      <c r="E1356" s="29" t="s">
-        <v>769</v>
+        <v>960</v>
+      </c>
+      <c r="E1356" s="28" t="s">
+        <v>961</v>
       </c>
       <c r="G1356">
         <v>10</v>
       </c>
       <c r="H1356">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1356">
-        <v>35000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1357" spans="1:9">
       <c r="A1357">
-        <v>920086</v>
+        <v>890022</v>
       </c>
       <c r="B1357" s="26">
         <v>1</v>
@@ -42186,202 +42160,18 @@
         <v>0</v>
       </c>
       <c r="D1357" s="28" t="s">
-        <v>960</v>
-      </c>
-      <c r="E1357" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1357" s="28"/>
+        <v>962</v>
+      </c>
+      <c r="E1357" s="28" t="s">
+        <v>963</v>
+      </c>
       <c r="G1357">
         <v>10</v>
       </c>
       <c r="H1357">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1357">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1358" spans="1:9">
-      <c r="A1358">
-        <v>820086</v>
-      </c>
-      <c r="B1358" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1358">
-        <v>0</v>
-      </c>
-      <c r="D1358" s="30" t="s">
-        <v>961</v>
-      </c>
-      <c r="E1358" s="30" t="s">
-        <v>961</v>
-      </c>
-      <c r="G1358">
-        <v>10</v>
-      </c>
-      <c r="H1358">
-        <v>1</v>
-      </c>
-      <c r="I1358">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1359" spans="1:9">
-      <c r="A1359">
-        <v>8200861</v>
-      </c>
-      <c r="B1359" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1359">
-        <v>0</v>
-      </c>
-      <c r="D1359" s="30" t="s">
-        <v>962</v>
-      </c>
-      <c r="E1359" s="30" t="s">
-        <v>963</v>
-      </c>
-      <c r="G1359">
-        <v>10</v>
-      </c>
-      <c r="H1359">
-        <v>2</v>
-      </c>
-      <c r="I1359">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1360" spans="1:9">
-      <c r="A1360">
-        <v>990001</v>
-      </c>
-      <c r="B1360" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1360">
-        <v>0</v>
-      </c>
-      <c r="D1360" s="28" t="s">
-        <v>964</v>
-      </c>
-      <c r="E1360" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1360" s="28"/>
-      <c r="G1360">
-        <v>10</v>
-      </c>
-      <c r="H1360">
-        <v>1</v>
-      </c>
-      <c r="I1360">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1361" spans="1:9">
-      <c r="A1361">
-        <v>890001</v>
-      </c>
-      <c r="B1361" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1361">
-        <v>0</v>
-      </c>
-      <c r="D1361" s="28" t="s">
-        <v>965</v>
-      </c>
-      <c r="E1361" s="28" t="s">
-        <v>965</v>
-      </c>
-      <c r="G1361">
-        <v>10</v>
-      </c>
-      <c r="H1361">
-        <v>1</v>
-      </c>
-      <c r="I1361">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1362" spans="1:9">
-      <c r="A1362">
-        <v>890011</v>
-      </c>
-      <c r="B1362" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1362">
-        <v>0</v>
-      </c>
-      <c r="D1362" s="28" t="s">
-        <v>966</v>
-      </c>
-      <c r="E1362" s="28" t="s">
-        <v>966</v>
-      </c>
-      <c r="G1362">
-        <v>10</v>
-      </c>
-      <c r="H1362">
-        <v>3</v>
-      </c>
-      <c r="I1362">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1363" spans="1:9">
-      <c r="A1363">
-        <v>890021</v>
-      </c>
-      <c r="B1363" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1363">
-        <v>0</v>
-      </c>
-      <c r="D1363" s="28" t="s">
-        <v>967</v>
-      </c>
-      <c r="E1363" s="28" t="s">
-        <v>968</v>
-      </c>
-      <c r="G1363">
-        <v>10</v>
-      </c>
-      <c r="H1363">
-        <v>1</v>
-      </c>
-      <c r="I1363">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1364" spans="1:9">
-      <c r="A1364">
-        <v>890022</v>
-      </c>
-      <c r="B1364" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1364">
-        <v>0</v>
-      </c>
-      <c r="D1364" s="28" t="s">
-        <v>969</v>
-      </c>
-      <c r="E1364" s="28" t="s">
-        <v>970</v>
-      </c>
-      <c r="G1364">
-        <v>10</v>
-      </c>
-      <c r="H1364">
-        <v>2</v>
-      </c>
-      <c r="I1364">
         <v>0</v>
       </c>
     </row>
@@ -42447,7 +42237,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -42459,10 +42249,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -42476,90 +42266,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>974</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>975</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>976</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>977</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>978</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>981</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>985</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>986</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>988</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>991</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>992</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>993</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>994</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>996</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>997</v>
-      </c>
       <c r="N4" s="4" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -42570,7 +42360,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -42591,7 +42381,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -42603,7 +42393,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -42614,7 +42404,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -42655,7 +42445,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -42696,7 +42486,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -42717,7 +42507,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -42729,7 +42519,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -42740,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -42761,7 +42551,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -42773,7 +42563,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -42784,7 +42574,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -42805,7 +42595,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3177,7 +3177,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3432,18 +3439,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3458,7 +3465,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79970702230903"/>
+        <fgColor theme="9" tint="0.799676503799554"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3494,7 +3501,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79970702230903"/>
+        <fgColor theme="4" tint="0.799676503799554"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3536,6 +3543,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3555,6 +3568,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3810,16 +3829,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3828,58 +3844,55 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3888,10 +3901,10 @@
     <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3900,10 +3913,10 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3912,10 +3925,10 @@
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3924,10 +3937,10 @@
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3936,13 +3949,19 @@
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3950,80 +3969,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5122,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -39381,7 +39400,7 @@
         <v>1</v>
       </c>
       <c r="I1251">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1252" spans="1:9">
@@ -39537,7 +39556,7 @@
         <v>2</v>
       </c>
       <c r="I1257">
-        <v>11500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1258" spans="1:9">
@@ -39589,7 +39608,7 @@
         <v>2</v>
       </c>
       <c r="I1259">
-        <v>11500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1260" spans="1:9">
@@ -39832,7 +39851,7 @@
         <v>1</v>
       </c>
       <c r="I1268">
-        <v>4000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1269" spans="1:9">
@@ -39886,7 +39905,7 @@
         <v>2</v>
       </c>
       <c r="I1270">
-        <v>10500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1271" spans="1:9">
@@ -40466,7 +40485,7 @@
         <v>1</v>
       </c>
       <c r="I1292">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1293" spans="1:9">
@@ -40544,7 +40563,7 @@
         <v>2</v>
       </c>
       <c r="I1295">
-        <v>11500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1296" spans="1:9">
@@ -40596,7 +40615,7 @@
         <v>2</v>
       </c>
       <c r="I1297">
-        <v>11500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1298" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3177,14 +3177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3439,18 +3432,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3543,12 +3536,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3568,12 +3555,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3829,13 +3810,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3844,55 +3828,58 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3901,10 +3888,10 @@
     <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3913,10 +3900,10 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3925,10 +3912,10 @@
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3937,10 +3924,10 @@
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3949,19 +3936,13 @@
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3969,80 +3950,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -38945,7 +38926,7 @@
         <v>2</v>
       </c>
       <c r="I1234">
-        <v>8000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1235" spans="1:9">
@@ -38997,7 +38978,7 @@
         <v>2</v>
       </c>
       <c r="I1236">
-        <v>8000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1237" spans="1:9">
@@ -39105,7 +39086,7 @@
         <v>2</v>
       </c>
       <c r="I1240">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1241" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -40883,7 +40883,7 @@
         <v>2</v>
       </c>
       <c r="I1308">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
@@ -40935,7 +40935,7 @@
         <v>2</v>
       </c>
       <c r="I1310">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1311" spans="1:9">
@@ -41043,7 +41043,7 @@
         <v>1</v>
       </c>
       <c r="I1314">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1315" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -39832,7 +39832,7 @@
         <v>1</v>
       </c>
       <c r="I1268">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1269" spans="1:9">
@@ -39859,7 +39859,7 @@
         <v>1</v>
       </c>
       <c r="I1269">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="1270" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -39537,7 +39537,7 @@
         <v>2</v>
       </c>
       <c r="I1257">
-        <v>14000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1258" spans="1:9">
@@ -39589,7 +39589,7 @@
         <v>2</v>
       </c>
       <c r="I1259">
-        <v>14000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1260" spans="1:9">
@@ -39832,7 +39832,7 @@
         <v>1</v>
       </c>
       <c r="I1268">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1269" spans="1:9">
@@ -39859,7 +39859,7 @@
         <v>1</v>
       </c>
       <c r="I1269">
-        <v>250</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1270" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -39459,7 +39459,7 @@
         <v>1</v>
       </c>
       <c r="I1254">
-        <v>1800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1255" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -39537,7 +39537,7 @@
         <v>2</v>
       </c>
       <c r="I1257">
-        <v>16000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1258" spans="1:9">
@@ -39589,7 +39589,7 @@
         <v>2</v>
       </c>
       <c r="I1259">
-        <v>16000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1260" spans="1:9">
@@ -39616,7 +39616,7 @@
         <v>1</v>
       </c>
       <c r="I1260">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1261" spans="1:9">
@@ -39643,7 +39643,7 @@
         <v>1</v>
       </c>
       <c r="I1261">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1262" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -39616,7 +39616,7 @@
         <v>1</v>
       </c>
       <c r="I1260">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1261" spans="1:9">
@@ -39643,7 +39643,7 @@
         <v>1</v>
       </c>
       <c r="I1261">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1262" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3432,12 +3432,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -37171,7 +37171,7 @@
         <v>2</v>
       </c>
       <c r="I1167">
-        <v>19500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1168" spans="1:9">
@@ -37223,7 +37223,7 @@
         <v>2</v>
       </c>
       <c r="I1169">
-        <v>19500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1170" spans="1:9">
@@ -37484,7 +37484,7 @@
         <v>2</v>
       </c>
       <c r="I1179">
-        <v>16500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1180" spans="1:9">
@@ -37536,7 +37536,7 @@
         <v>2</v>
       </c>
       <c r="I1181">
-        <v>16500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1182" spans="1:9">
@@ -37718,7 +37718,7 @@
         <v>1</v>
       </c>
       <c r="I1188">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1189" spans="1:9">
@@ -37770,7 +37770,7 @@
         <v>2</v>
       </c>
       <c r="I1190">
-        <v>15500</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1191" spans="1:9">
@@ -37822,7 +37822,7 @@
         <v>2</v>
       </c>
       <c r="I1192">
-        <v>15500</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1193" spans="1:9">
@@ -37876,7 +37876,7 @@
         <v>1</v>
       </c>
       <c r="I1194">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1195" spans="1:9">
@@ -38272,7 +38272,7 @@
         <v>2</v>
       </c>
       <c r="I1209">
-        <v>16000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1210" spans="1:9">
@@ -38324,7 +38324,7 @@
         <v>2</v>
       </c>
       <c r="I1211">
-        <v>16000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1212" spans="1:9">
@@ -40883,7 +40883,7 @@
         <v>2</v>
       </c>
       <c r="I1308">
-        <v>18000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
@@ -40935,7 +40935,7 @@
         <v>2</v>
       </c>
       <c r="I1310">
-        <v>18000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1311" spans="1:9">
@@ -41910,7 +41910,7 @@
         <v>2</v>
       </c>
       <c r="I1347">
-        <v>35000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1348" spans="1:9">
@@ -41962,7 +41962,7 @@
         <v>2</v>
       </c>
       <c r="I1349">
-        <v>35000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1350" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -3432,12 +3432,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -37171,7 +37171,7 @@
         <v>2</v>
       </c>
       <c r="I1167">
-        <v>18000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1168" spans="1:9">
@@ -37223,7 +37223,7 @@
         <v>2</v>
       </c>
       <c r="I1169">
-        <v>18000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1170" spans="1:9">
@@ -37484,7 +37484,7 @@
         <v>2</v>
       </c>
       <c r="I1179">
-        <v>20000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1180" spans="1:9">
@@ -37536,7 +37536,7 @@
         <v>2</v>
       </c>
       <c r="I1181">
-        <v>20000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1182" spans="1:9">
@@ -37770,7 +37770,7 @@
         <v>2</v>
       </c>
       <c r="I1190">
-        <v>16000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1191" spans="1:9">
@@ -37822,7 +37822,7 @@
         <v>2</v>
       </c>
       <c r="I1192">
-        <v>16000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1193" spans="1:9">
@@ -38272,7 +38272,7 @@
         <v>2</v>
       </c>
       <c r="I1209">
-        <v>14000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1210" spans="1:9">
@@ -38324,7 +38324,7 @@
         <v>2</v>
       </c>
       <c r="I1211">
-        <v>14000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1212" spans="1:9">
@@ -38561,7 +38561,7 @@
         <v>1</v>
       </c>
       <c r="I1220">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1221" spans="1:9">
@@ -40883,7 +40883,7 @@
         <v>2</v>
       </c>
       <c r="I1308">
-        <v>14000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
@@ -40935,7 +40935,7 @@
         <v>2</v>
       </c>
       <c r="I1310">
-        <v>14000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1311" spans="1:9">
@@ -41519,7 +41519,7 @@
         <v>1</v>
       </c>
       <c r="I1332">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1333" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -37119,7 +37119,7 @@
         <v>1</v>
       </c>
       <c r="I1165">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1166" spans="1:9">
@@ -37171,7 +37171,7 @@
         <v>2</v>
       </c>
       <c r="I1167">
-        <v>24000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1168" spans="1:9">
@@ -37223,7 +37223,7 @@
         <v>2</v>
       </c>
       <c r="I1169">
-        <v>24000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1170" spans="1:9">
@@ -37380,7 +37380,7 @@
         <v>1</v>
       </c>
       <c r="I1175">
-        <v>4200</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1176" spans="1:9">
@@ -37406,7 +37406,7 @@
         <v>1</v>
       </c>
       <c r="I1176">
-        <v>4200</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1177" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5901B813-2D65-4E79-AA4E-98DFE28BFC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6644ABE6-75E2-4B4E-BFC3-B5EA7627D004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3708" uniqueCount="1022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3799" uniqueCount="1071">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3235,6 +3235,160 @@
   <si>
     <t>天火被动-逻辑id</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石-燃烧伤害系数万分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石-燃烧伤害系数固定值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石-燃烧持续时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石-燃烧的命中率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石-伤害结算间隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火刃-燃烧伤害系数万分比</t>
+  </si>
+  <si>
+    <t>火刃-燃烧伤害系数固定值</t>
+  </si>
+  <si>
+    <t>火刃-燃烧持续时间</t>
+  </si>
+  <si>
+    <t>火刃-燃烧的命中率</t>
+  </si>
+  <si>
+    <t>火刃-伤害结算间隔</t>
+  </si>
+  <si>
+    <t>参数-参数8-伤害结算间隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰溅射_获得</t>
+  </si>
+  <si>
+    <t>火焰溅射_冷却</t>
+  </si>
+  <si>
+    <t>火焰溅射_最近释放距离</t>
+  </si>
+  <si>
+    <t>火焰溅射_最远释放距离</t>
+  </si>
+  <si>
+    <t>火焰溅射_技能效果半径</t>
+  </si>
+  <si>
+    <t>火焰溅射_目标数量</t>
+  </si>
+  <si>
+    <t>火焰溅射_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>火焰溅射_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>火焰溅射_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>火焰溅射_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>火焰溅射_技能等级</t>
+  </si>
+  <si>
+    <t>火焰溅射_释放角度</t>
+  </si>
+  <si>
+    <t>火焰冲击_获得</t>
+  </si>
+  <si>
+    <t>火焰冲击_冷却</t>
+  </si>
+  <si>
+    <t>火焰冲击_最近释放距离</t>
+  </si>
+  <si>
+    <t>火焰冲击_最远释放距离</t>
+  </si>
+  <si>
+    <t>火焰冲击_技能效果半径</t>
+  </si>
+  <si>
+    <t>火焰冲击_目标数量</t>
+  </si>
+  <si>
+    <t>火焰冲击_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>火焰冲击_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>火焰冲击_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>火焰冲击_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>火焰冲击_技能等级</t>
+  </si>
+  <si>
+    <t>火焰冲击_弹道数量</t>
+  </si>
+  <si>
+    <t>火焰冲击_弹道飞行速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引燃_获得</t>
+  </si>
+  <si>
+    <t>引燃_冷却</t>
+  </si>
+  <si>
+    <t>引燃_最近释放距离</t>
+  </si>
+  <si>
+    <t>引燃_最远释放距离</t>
+  </si>
+  <si>
+    <t>引燃_技能效果半径</t>
+  </si>
+  <si>
+    <t>引燃_目标数量</t>
+  </si>
+  <si>
+    <t>引燃_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>引燃_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>引燃_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>引燃_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>引燃_技能持续时间</t>
+  </si>
+  <si>
+    <t>引燃_技能伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>引燃技能等级</t>
   </si>
 </sst>
 </file>
@@ -3938,7 +4092,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1385"/>
+  <dimension ref="A1:I1428"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -37608,7 +37762,7 @@
         <v>1</v>
       </c>
       <c r="I1201">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1202" spans="1:9" x14ac:dyDescent="0.15">
@@ -41603,7 +41757,7 @@
         <v>0</v>
       </c>
       <c r="D1353" s="27" t="s">
-        <v>324</v>
+        <v>1022</v>
       </c>
       <c r="E1353" s="26" t="s">
         <v>245</v>
@@ -41632,7 +41786,7 @@
         <v>0</v>
       </c>
       <c r="D1354" s="27" t="s">
-        <v>325</v>
+        <v>1023</v>
       </c>
       <c r="E1354" s="26" t="s">
         <v>253</v>
@@ -41661,7 +41815,7 @@
         <v>0</v>
       </c>
       <c r="D1355" s="27" t="s">
-        <v>326</v>
+        <v>1024</v>
       </c>
       <c r="E1355" s="26" t="s">
         <v>327</v>
@@ -41690,7 +41844,7 @@
         <v>0</v>
       </c>
       <c r="D1356" s="27" t="s">
-        <v>328</v>
+        <v>1025</v>
       </c>
       <c r="E1356" s="26" t="s">
         <v>329</v>
@@ -41719,10 +41873,10 @@
         <v>0</v>
       </c>
       <c r="D1357" s="27" t="s">
-        <v>330</v>
+        <v>1026</v>
       </c>
       <c r="E1357" s="26" t="s">
-        <v>305</v>
+        <v>1032</v>
       </c>
       <c r="F1357" s="9" t="s">
         <v>100</v>
@@ -41738,51 +41892,57 @@
       </c>
     </row>
     <row r="1358" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1358">
-        <v>920091</v>
+      <c r="A1358" s="26">
+        <v>5101211</v>
       </c>
       <c r="B1358" s="26">
         <v>1</v>
       </c>
-      <c r="C1358">
-        <v>0</v>
-      </c>
-      <c r="D1358" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="E1358" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1358">
-        <v>10</v>
-      </c>
-      <c r="H1358">
-        <v>1</v>
+      <c r="C1358" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1358" s="27" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E1358" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1358" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1358" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1358" s="26">
+        <v>2</v>
       </c>
       <c r="I1358">
         <v>0</v>
       </c>
     </row>
     <row r="1359" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1359">
-        <v>1920091</v>
+      <c r="A1359" s="26">
+        <v>5101212</v>
       </c>
       <c r="B1359" s="26">
         <v>1</v>
       </c>
-      <c r="C1359">
-        <v>0</v>
-      </c>
-      <c r="D1359" s="28" t="s">
-        <v>529</v>
-      </c>
-      <c r="E1359" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1359">
-        <v>10</v>
-      </c>
-      <c r="H1359">
+      <c r="C1359" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1359" s="27" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E1359" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1359" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1359" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1359" s="26">
         <v>1</v>
       </c>
       <c r="I1359">
@@ -41790,25 +41950,28 @@
       </c>
     </row>
     <row r="1360" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1360">
-        <v>2920091</v>
+      <c r="A1360" s="26">
+        <v>5101215</v>
       </c>
       <c r="B1360" s="26">
         <v>1</v>
       </c>
-      <c r="C1360">
-        <v>0</v>
-      </c>
-      <c r="D1360" s="28" t="s">
-        <v>547</v>
-      </c>
-      <c r="E1360" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1360">
-        <v>10</v>
-      </c>
-      <c r="H1360">
+      <c r="C1360" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1360" s="27" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E1360" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1360" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1360" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1360" s="26">
         <v>1</v>
       </c>
       <c r="I1360">
@@ -41816,60 +41979,66 @@
       </c>
     </row>
     <row r="1361" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1361">
-        <v>3920091</v>
+      <c r="A1361" s="26">
+        <v>5101216</v>
       </c>
       <c r="B1361" s="26">
         <v>1</v>
       </c>
-      <c r="C1361">
-        <v>0</v>
-      </c>
-      <c r="D1361" s="28" t="s">
-        <v>565</v>
-      </c>
-      <c r="E1361" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1361">
-        <v>10</v>
-      </c>
-      <c r="H1361">
-        <v>1</v>
+      <c r="C1361" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1361" s="27" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E1361" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1361" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1361" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1361" s="26">
+        <v>2</v>
       </c>
       <c r="I1361">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1362" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1362">
-        <v>4920091</v>
+      <c r="A1362" s="26">
+        <v>5101218</v>
       </c>
       <c r="B1362" s="26">
         <v>1</v>
       </c>
-      <c r="C1362">
-        <v>0</v>
-      </c>
-      <c r="D1362" s="28" t="s">
-        <v>583</v>
-      </c>
-      <c r="E1362" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1362">
-        <v>10</v>
-      </c>
-      <c r="H1362">
+      <c r="C1362" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1362" s="27" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E1362" s="26" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1362" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1362" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1362" s="26">
         <v>1</v>
       </c>
       <c r="I1362">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1363" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1363">
-        <v>5920091</v>
+        <v>920091</v>
       </c>
       <c r="B1363" s="26">
         <v>1</v>
@@ -41878,10 +42047,10 @@
         <v>0</v>
       </c>
       <c r="D1363" s="28" t="s">
-        <v>601</v>
+        <v>512</v>
       </c>
       <c r="E1363" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1363">
         <v>10</v>
@@ -41890,12 +42059,12 @@
         <v>1</v>
       </c>
       <c r="I1363">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1364" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1364">
-        <v>6920091</v>
+        <v>1920091</v>
       </c>
       <c r="B1364" s="26">
         <v>1</v>
@@ -41904,7 +42073,7 @@
         <v>0</v>
       </c>
       <c r="D1364" s="28" t="s">
-        <v>619</v>
+        <v>529</v>
       </c>
       <c r="E1364" s="29" t="s">
         <v>769</v>
@@ -41921,7 +42090,7 @@
     </row>
     <row r="1365" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1365">
-        <v>7920091</v>
+        <v>2920091</v>
       </c>
       <c r="B1365" s="26">
         <v>1</v>
@@ -41930,7 +42099,7 @@
         <v>0</v>
       </c>
       <c r="D1365" s="28" t="s">
-        <v>637</v>
+        <v>547</v>
       </c>
       <c r="E1365" s="29" t="s">
         <v>769</v>
@@ -41939,15 +42108,15 @@
         <v>10</v>
       </c>
       <c r="H1365">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1365">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1366" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1366">
-        <v>8920091</v>
+        <v>3920091</v>
       </c>
       <c r="B1366" s="26">
         <v>1</v>
@@ -41956,7 +42125,7 @@
         <v>0</v>
       </c>
       <c r="D1366" s="28" t="s">
-        <v>653</v>
+        <v>565</v>
       </c>
       <c r="E1366" s="29" t="s">
         <v>769</v>
@@ -41968,12 +42137,12 @@
         <v>1</v>
       </c>
       <c r="I1366">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1367" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1367">
-        <v>9920091</v>
+        <v>4920091</v>
       </c>
       <c r="B1367" s="26">
         <v>1</v>
@@ -41982,7 +42151,7 @@
         <v>0</v>
       </c>
       <c r="D1367" s="28" t="s">
-        <v>671</v>
+        <v>583</v>
       </c>
       <c r="E1367" s="29" t="s">
         <v>769</v>
@@ -41991,21 +42160,24 @@
         <v>10</v>
       </c>
       <c r="H1367">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1367">
-        <v>20000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1368" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1368">
-        <v>13920091</v>
+        <v>5920091</v>
       </c>
       <c r="B1368" s="26">
         <v>1</v>
       </c>
+      <c r="C1368">
+        <v>0</v>
+      </c>
       <c r="D1368" s="28" t="s">
-        <v>964</v>
+        <v>601</v>
       </c>
       <c r="E1368" s="29" t="s">
         <v>769</v>
@@ -42017,18 +42189,21 @@
         <v>1</v>
       </c>
       <c r="I1368">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1369" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1369">
-        <v>14920091</v>
+        <v>6920091</v>
       </c>
       <c r="B1369" s="26">
         <v>1</v>
       </c>
+      <c r="C1369">
+        <v>0</v>
+      </c>
       <c r="D1369" s="28" t="s">
-        <v>965</v>
+        <v>619</v>
       </c>
       <c r="E1369" s="29" t="s">
         <v>769</v>
@@ -42040,18 +42215,21 @@
         <v>1</v>
       </c>
       <c r="I1369">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1370" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1370">
-        <v>15920091</v>
+        <v>7920091</v>
       </c>
       <c r="B1370" s="26">
         <v>1</v>
       </c>
+      <c r="C1370">
+        <v>0</v>
+      </c>
       <c r="D1370" s="28" t="s">
-        <v>966</v>
+        <v>637</v>
       </c>
       <c r="E1370" s="29" t="s">
         <v>769</v>
@@ -42060,15 +42238,15 @@
         <v>10</v>
       </c>
       <c r="H1370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1370">
-        <v>200</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1371" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1371">
-        <v>920092</v>
+        <v>8920091</v>
       </c>
       <c r="B1371" s="26">
         <v>1</v>
@@ -42077,10 +42255,10 @@
         <v>0</v>
       </c>
       <c r="D1371" s="28" t="s">
-        <v>1007</v>
+        <v>653</v>
       </c>
       <c r="E1371" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1371">
         <v>10</v>
@@ -42094,7 +42272,7 @@
     </row>
     <row r="1372" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1372">
-        <v>1920092</v>
+        <v>9920091</v>
       </c>
       <c r="B1372" s="26">
         <v>1</v>
@@ -42103,7 +42281,7 @@
         <v>0</v>
       </c>
       <c r="D1372" s="28" t="s">
-        <v>1008</v>
+        <v>671</v>
       </c>
       <c r="E1372" s="29" t="s">
         <v>769</v>
@@ -42112,24 +42290,21 @@
         <v>10</v>
       </c>
       <c r="H1372">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1372">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1373" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1373">
-        <v>2920092</v>
+        <v>13920091</v>
       </c>
       <c r="B1373" s="26">
         <v>1</v>
       </c>
-      <c r="C1373">
-        <v>0</v>
-      </c>
       <c r="D1373" s="28" t="s">
-        <v>1009</v>
+        <v>964</v>
       </c>
       <c r="E1373" s="29" t="s">
         <v>769</v>
@@ -42141,21 +42316,18 @@
         <v>1</v>
       </c>
       <c r="I1373">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1374" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1374">
-        <v>3920092</v>
+        <v>14920091</v>
       </c>
       <c r="B1374" s="26">
         <v>1</v>
       </c>
-      <c r="C1374">
-        <v>0</v>
-      </c>
       <c r="D1374" s="28" t="s">
-        <v>1010</v>
+        <v>965</v>
       </c>
       <c r="E1374" s="29" t="s">
         <v>769</v>
@@ -42167,21 +42339,18 @@
         <v>1</v>
       </c>
       <c r="I1374">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1375" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1375">
-        <v>4920092</v>
+        <v>15920091</v>
       </c>
       <c r="B1375" s="26">
         <v>1</v>
       </c>
-      <c r="C1375">
-        <v>0</v>
-      </c>
       <c r="D1375" s="28" t="s">
-        <v>1011</v>
+        <v>966</v>
       </c>
       <c r="E1375" s="29" t="s">
         <v>769</v>
@@ -42193,12 +42362,12 @@
         <v>1</v>
       </c>
       <c r="I1375">
-        <v>2000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1376" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1376">
-        <v>5920092</v>
+        <v>920092</v>
       </c>
       <c r="B1376" s="26">
         <v>1</v>
@@ -42207,10 +42376,10 @@
         <v>0</v>
       </c>
       <c r="D1376" s="28" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="E1376" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1376">
         <v>10</v>
@@ -42224,7 +42393,7 @@
     </row>
     <row r="1377" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1377">
-        <v>6920092</v>
+        <v>1920092</v>
       </c>
       <c r="B1377" s="26">
         <v>1</v>
@@ -42233,7 +42402,7 @@
         <v>0</v>
       </c>
       <c r="D1377" s="28" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="E1377" s="29" t="s">
         <v>769</v>
@@ -42250,7 +42419,7 @@
     </row>
     <row r="1378" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1378">
-        <v>7920092</v>
+        <v>2920092</v>
       </c>
       <c r="B1378" s="26">
         <v>1</v>
@@ -42259,7 +42428,7 @@
         <v>0</v>
       </c>
       <c r="D1378" s="28" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="E1378" s="29" t="s">
         <v>769</v>
@@ -42268,15 +42437,15 @@
         <v>10</v>
       </c>
       <c r="H1378">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1378">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1379" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1379">
-        <v>8920092</v>
+        <v>3920092</v>
       </c>
       <c r="B1379" s="26">
         <v>1</v>
@@ -42285,7 +42454,7 @@
         <v>0</v>
       </c>
       <c r="D1379" s="28" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="E1379" s="29" t="s">
         <v>769</v>
@@ -42302,7 +42471,7 @@
     </row>
     <row r="1380" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1380">
-        <v>9920092</v>
+        <v>4920092</v>
       </c>
       <c r="B1380" s="26">
         <v>1</v>
@@ -42311,7 +42480,7 @@
         <v>0</v>
       </c>
       <c r="D1380" s="28" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="E1380" s="29" t="s">
         <v>769</v>
@@ -42320,15 +42489,15 @@
         <v>10</v>
       </c>
       <c r="H1380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1380">
-        <v>6000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1381" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1381">
-        <v>10920092</v>
+        <v>5920092</v>
       </c>
       <c r="B1381" s="26">
         <v>1</v>
@@ -42337,7 +42506,7 @@
         <v>0</v>
       </c>
       <c r="D1381" s="28" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="E1381" s="29" t="s">
         <v>769</v>
@@ -42349,12 +42518,12 @@
         <v>1</v>
       </c>
       <c r="I1381">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1382" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1382">
-        <v>11920092</v>
+        <v>6920092</v>
       </c>
       <c r="B1382" s="26">
         <v>1</v>
@@ -42363,7 +42532,7 @@
         <v>0</v>
       </c>
       <c r="D1382" s="28" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="E1382" s="29" t="s">
         <v>769</v>
@@ -42375,12 +42544,12 @@
         <v>1</v>
       </c>
       <c r="I1382">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1383" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1383">
-        <v>13920092</v>
+        <v>7920092</v>
       </c>
       <c r="B1383" s="26">
         <v>1</v>
@@ -42389,7 +42558,7 @@
         <v>0</v>
       </c>
       <c r="D1383" s="28" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="E1383" s="29" t="s">
         <v>769</v>
@@ -42398,15 +42567,15 @@
         <v>10</v>
       </c>
       <c r="H1383">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1383">
-        <v>1</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1384" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1384">
-        <v>920093</v>
+        <v>8920092</v>
       </c>
       <c r="B1384" s="26">
         <v>1</v>
@@ -42415,10 +42584,10 @@
         <v>0</v>
       </c>
       <c r="D1384" s="28" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="E1384" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1384">
         <v>10</v>
@@ -42432,28 +42601,1150 @@
     </row>
     <row r="1385" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1385">
+        <v>9920092</v>
+      </c>
+      <c r="B1385" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1385">
+        <v>0</v>
+      </c>
+      <c r="D1385" s="28" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E1385" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1385">
+        <v>10</v>
+      </c>
+      <c r="H1385">
+        <v>2</v>
+      </c>
+      <c r="I1385">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1386">
+        <v>10920092</v>
+      </c>
+      <c r="B1386" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1386">
+        <v>0</v>
+      </c>
+      <c r="D1386" s="28" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E1386" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1386">
+        <v>10</v>
+      </c>
+      <c r="H1386">
+        <v>1</v>
+      </c>
+      <c r="I1386">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1387">
+        <v>11920092</v>
+      </c>
+      <c r="B1387" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1387">
+        <v>0</v>
+      </c>
+      <c r="D1387" s="28" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E1387" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1387">
+        <v>10</v>
+      </c>
+      <c r="H1387">
+        <v>1</v>
+      </c>
+      <c r="I1387">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1388">
+        <v>13920092</v>
+      </c>
+      <c r="B1388" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1388">
+        <v>0</v>
+      </c>
+      <c r="D1388" s="28" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E1388" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1388">
+        <v>10</v>
+      </c>
+      <c r="H1388">
+        <v>1</v>
+      </c>
+      <c r="I1388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1389">
+        <v>920093</v>
+      </c>
+      <c r="B1389" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1389">
+        <v>0</v>
+      </c>
+      <c r="D1389" s="28" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E1389" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1389">
+        <v>10</v>
+      </c>
+      <c r="H1389">
+        <v>1</v>
+      </c>
+      <c r="I1389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1390">
         <v>820093</v>
       </c>
-      <c r="B1385" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1385">
-        <v>0</v>
-      </c>
-      <c r="D1385" s="30" t="s">
+      <c r="B1390" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1390">
+        <v>0</v>
+      </c>
+      <c r="D1390" s="30" t="s">
         <v>1021</v>
       </c>
-      <c r="E1385" s="30" t="s">
+      <c r="E1390" s="30" t="s">
         <v>1021</v>
       </c>
-      <c r="G1385">
-        <v>10</v>
-      </c>
-      <c r="H1385">
-        <v>1</v>
-      </c>
-      <c r="I1385">
-        <v>0</v>
+      <c r="G1390">
+        <v>10</v>
+      </c>
+      <c r="H1390">
+        <v>1</v>
+      </c>
+      <c r="I1390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1391">
+        <v>920101</v>
+      </c>
+      <c r="B1391" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1391">
+        <v>0</v>
+      </c>
+      <c r="D1391" s="28" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E1391" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1391">
+        <v>10</v>
+      </c>
+      <c r="H1391">
+        <v>1</v>
+      </c>
+      <c r="I1391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1392">
+        <v>1920101</v>
+      </c>
+      <c r="B1392" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1392">
+        <v>0</v>
+      </c>
+      <c r="D1392" s="28" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E1392" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1392">
+        <v>10</v>
+      </c>
+      <c r="H1392">
+        <v>1</v>
+      </c>
+      <c r="I1392">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1393">
+        <v>2920101</v>
+      </c>
+      <c r="B1393" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1393">
+        <v>0</v>
+      </c>
+      <c r="D1393" s="28" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E1393" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1393">
+        <v>10</v>
+      </c>
+      <c r="H1393">
+        <v>1</v>
+      </c>
+      <c r="I1393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1394">
+        <v>3920101</v>
+      </c>
+      <c r="B1394" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1394">
+        <v>0</v>
+      </c>
+      <c r="D1394" s="28" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E1394" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1394">
+        <v>10</v>
+      </c>
+      <c r="H1394">
+        <v>1</v>
+      </c>
+      <c r="I1394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1395">
+        <v>4920101</v>
+      </c>
+      <c r="B1395" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1395">
+        <v>0</v>
+      </c>
+      <c r="D1395" s="28" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E1395" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1395">
+        <v>10</v>
+      </c>
+      <c r="H1395">
+        <v>1</v>
+      </c>
+      <c r="I1395">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1396">
+        <v>5920101</v>
+      </c>
+      <c r="B1396" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1396">
+        <v>0</v>
+      </c>
+      <c r="D1396" s="28" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E1396" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1396">
+        <v>10</v>
+      </c>
+      <c r="H1396">
+        <v>1</v>
+      </c>
+      <c r="I1396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1397">
+        <v>6920101</v>
+      </c>
+      <c r="B1397" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1397">
+        <v>0</v>
+      </c>
+      <c r="D1397" s="28" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E1397" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1397">
+        <v>10</v>
+      </c>
+      <c r="H1397">
+        <v>1</v>
+      </c>
+      <c r="I1397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1398">
+        <v>7920101</v>
+      </c>
+      <c r="B1398" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1398">
+        <v>0</v>
+      </c>
+      <c r="D1398" s="28" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E1398" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1398">
+        <v>10</v>
+      </c>
+      <c r="H1398">
+        <v>2</v>
+      </c>
+      <c r="I1398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1399">
+        <v>8920101</v>
+      </c>
+      <c r="B1399" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1399">
+        <v>0</v>
+      </c>
+      <c r="D1399" s="28" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E1399" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1399">
+        <v>10</v>
+      </c>
+      <c r="H1399">
+        <v>1</v>
+      </c>
+      <c r="I1399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1400">
+        <v>9920101</v>
+      </c>
+      <c r="B1400" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1400">
+        <v>0</v>
+      </c>
+      <c r="D1400" s="28" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E1400" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1400">
+        <v>10</v>
+      </c>
+      <c r="H1400">
+        <v>2</v>
+      </c>
+      <c r="I1400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1401">
+        <v>13920101</v>
+      </c>
+      <c r="B1401" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1401">
+        <v>0</v>
+      </c>
+      <c r="D1401" s="28" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E1401" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1401">
+        <v>10</v>
+      </c>
+      <c r="H1401">
+        <v>1</v>
+      </c>
+      <c r="I1401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1402">
+        <v>16920101</v>
+      </c>
+      <c r="B1402" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1402">
+        <v>0</v>
+      </c>
+      <c r="D1402" s="28" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E1402" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1402" s="28"/>
+      <c r="G1402">
+        <v>10</v>
+      </c>
+      <c r="H1402">
+        <v>1</v>
+      </c>
+      <c r="I1402">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1403">
+        <v>920102</v>
+      </c>
+      <c r="B1403" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1403">
+        <v>0</v>
+      </c>
+      <c r="D1403" s="28" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E1403" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1403">
+        <v>10</v>
+      </c>
+      <c r="H1403">
+        <v>1</v>
+      </c>
+      <c r="I1403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1404">
+        <v>1920102</v>
+      </c>
+      <c r="B1404" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1404">
+        <v>0</v>
+      </c>
+      <c r="D1404" s="28" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E1404" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1404">
+        <v>10</v>
+      </c>
+      <c r="H1404">
+        <v>1</v>
+      </c>
+      <c r="I1404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1405">
+        <v>2920102</v>
+      </c>
+      <c r="B1405" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1405">
+        <v>0</v>
+      </c>
+      <c r="D1405" s="28" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E1405" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1405">
+        <v>10</v>
+      </c>
+      <c r="H1405">
+        <v>1</v>
+      </c>
+      <c r="I1405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1406">
+        <v>3920102</v>
+      </c>
+      <c r="B1406" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1406">
+        <v>0</v>
+      </c>
+      <c r="D1406" s="28" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E1406" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1406">
+        <v>10</v>
+      </c>
+      <c r="H1406">
+        <v>1</v>
+      </c>
+      <c r="I1406">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1407">
+        <v>4920102</v>
+      </c>
+      <c r="B1407" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1407">
+        <v>0</v>
+      </c>
+      <c r="D1407" s="28" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E1407" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1407">
+        <v>10</v>
+      </c>
+      <c r="H1407">
+        <v>1</v>
+      </c>
+      <c r="I1407">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1408">
+        <v>5920102</v>
+      </c>
+      <c r="B1408" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1408">
+        <v>0</v>
+      </c>
+      <c r="D1408" s="28" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E1408" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1408">
+        <v>10</v>
+      </c>
+      <c r="H1408">
+        <v>1</v>
+      </c>
+      <c r="I1408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1409">
+        <v>6920102</v>
+      </c>
+      <c r="B1409" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1409">
+        <v>0</v>
+      </c>
+      <c r="D1409" s="28" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E1409" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1409">
+        <v>10</v>
+      </c>
+      <c r="H1409">
+        <v>1</v>
+      </c>
+      <c r="I1409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1410">
+        <v>7920102</v>
+      </c>
+      <c r="B1410" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1410">
+        <v>0</v>
+      </c>
+      <c r="D1410" s="28" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E1410" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1410">
+        <v>10</v>
+      </c>
+      <c r="H1410">
+        <v>2</v>
+      </c>
+      <c r="I1410">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1411">
+        <v>8920102</v>
+      </c>
+      <c r="B1411" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1411">
+        <v>0</v>
+      </c>
+      <c r="D1411" s="28" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E1411" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1411">
+        <v>10</v>
+      </c>
+      <c r="H1411">
+        <v>1</v>
+      </c>
+      <c r="I1411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1412">
+        <v>9920102</v>
+      </c>
+      <c r="B1412" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1412">
+        <v>0</v>
+      </c>
+      <c r="D1412" s="28" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1412" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1412">
+        <v>10</v>
+      </c>
+      <c r="H1412">
+        <v>2</v>
+      </c>
+      <c r="I1412">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1413">
+        <v>13920102</v>
+      </c>
+      <c r="B1413" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1413">
+        <v>0</v>
+      </c>
+      <c r="D1413" s="28" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E1413" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1413" s="28"/>
+      <c r="G1413">
+        <v>10</v>
+      </c>
+      <c r="H1413">
+        <v>1</v>
+      </c>
+      <c r="I1413">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1414">
+        <v>14920102</v>
+      </c>
+      <c r="B1414" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1414">
+        <v>0</v>
+      </c>
+      <c r="D1414" s="28" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E1414" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1414" s="28"/>
+      <c r="G1414">
+        <v>10</v>
+      </c>
+      <c r="H1414">
+        <v>1</v>
+      </c>
+      <c r="I1414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1415">
+        <v>15920102</v>
+      </c>
+      <c r="B1415" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1415">
+        <v>0</v>
+      </c>
+      <c r="D1415" s="28" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E1415" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1415" s="28"/>
+      <c r="G1415">
+        <v>10</v>
+      </c>
+      <c r="H1415">
+        <v>1</v>
+      </c>
+      <c r="I1415">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1416">
+        <v>920103</v>
+      </c>
+      <c r="B1416" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1416">
+        <v>0</v>
+      </c>
+      <c r="D1416" s="28" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E1416" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1416">
+        <v>10</v>
+      </c>
+      <c r="H1416">
+        <v>1</v>
+      </c>
+      <c r="I1416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1417">
+        <v>1920103</v>
+      </c>
+      <c r="B1417" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1417">
+        <v>0</v>
+      </c>
+      <c r="D1417" s="28" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E1417" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1417">
+        <v>10</v>
+      </c>
+      <c r="H1417">
+        <v>1</v>
+      </c>
+      <c r="I1417">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1418">
+        <v>2920103</v>
+      </c>
+      <c r="B1418" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1418">
+        <v>0</v>
+      </c>
+      <c r="D1418" s="28" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E1418" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1418">
+        <v>10</v>
+      </c>
+      <c r="H1418">
+        <v>1</v>
+      </c>
+      <c r="I1418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1419">
+        <v>3920103</v>
+      </c>
+      <c r="B1419" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1419">
+        <v>0</v>
+      </c>
+      <c r="D1419" s="28" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E1419" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1419">
+        <v>10</v>
+      </c>
+      <c r="H1419">
+        <v>1</v>
+      </c>
+      <c r="I1419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1420">
+        <v>4920103</v>
+      </c>
+      <c r="B1420" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1420">
+        <v>0</v>
+      </c>
+      <c r="D1420" s="28" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E1420" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1420">
+        <v>10</v>
+      </c>
+      <c r="H1420">
+        <v>1</v>
+      </c>
+      <c r="I1420">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1421">
+        <v>5920103</v>
+      </c>
+      <c r="B1421" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1421">
+        <v>0</v>
+      </c>
+      <c r="D1421" s="28" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E1421" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1421">
+        <v>10</v>
+      </c>
+      <c r="H1421">
+        <v>1</v>
+      </c>
+      <c r="I1421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1422">
+        <v>6920103</v>
+      </c>
+      <c r="B1422" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1422">
+        <v>0</v>
+      </c>
+      <c r="D1422" s="28" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E1422" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1422">
+        <v>10</v>
+      </c>
+      <c r="H1422">
+        <v>1</v>
+      </c>
+      <c r="I1422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1423">
+        <v>7920103</v>
+      </c>
+      <c r="B1423" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1423">
+        <v>0</v>
+      </c>
+      <c r="D1423" s="28" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E1423" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1423">
+        <v>10</v>
+      </c>
+      <c r="H1423">
+        <v>2</v>
+      </c>
+      <c r="I1423">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1424">
+        <v>8920103</v>
+      </c>
+      <c r="B1424" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1424">
+        <v>0</v>
+      </c>
+      <c r="D1424" s="28" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E1424" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1424">
+        <v>10</v>
+      </c>
+      <c r="H1424">
+        <v>1</v>
+      </c>
+      <c r="I1424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1425">
+        <v>9920103</v>
+      </c>
+      <c r="B1425" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1425">
+        <v>0</v>
+      </c>
+      <c r="D1425" s="28" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E1425" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1425">
+        <v>10</v>
+      </c>
+      <c r="H1425">
+        <v>2</v>
+      </c>
+      <c r="I1425">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1426">
+        <v>11030103</v>
+      </c>
+      <c r="B1426" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1426">
+        <v>0</v>
+      </c>
+      <c r="D1426" s="28" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E1426" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1426">
+        <v>10</v>
+      </c>
+      <c r="H1426">
+        <v>1</v>
+      </c>
+      <c r="I1426">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1427">
+        <v>11920103</v>
+      </c>
+      <c r="B1427" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1427">
+        <v>0</v>
+      </c>
+      <c r="D1427" s="28" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E1427" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1427">
+        <v>10</v>
+      </c>
+      <c r="H1427">
+        <v>1</v>
+      </c>
+      <c r="I1427">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1428">
+        <v>13920103</v>
+      </c>
+      <c r="B1428" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1428">
+        <v>0</v>
+      </c>
+      <c r="D1428" s="28" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E1428" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1428">
+        <v>10</v>
+      </c>
+      <c r="H1428">
+        <v>1</v>
+      </c>
+      <c r="I1428">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6644ABE6-75E2-4B4E-BFC3-B5EA7627D004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDC3222-F148-4198-A32B-1FF0C5AF10C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
     <sheet name="maze_attribute_formula_v8" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1348</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3799" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="1092">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3229,14 +3229,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>天火被动_获得</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天火被动-逻辑id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>陨石-燃烧伤害系数万分比</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3306,9 +3298,6 @@
     <t>火焰溅射_非主目标直接伤害系数</t>
   </si>
   <si>
-    <t>火焰溅射_技能等级</t>
-  </si>
-  <si>
     <t>火焰溅射_释放角度</t>
   </si>
   <si>
@@ -3389,6 +3378,82 @@
   </si>
   <si>
     <t>引燃技能等级</t>
+  </si>
+  <si>
+    <t>暴风雪_自动寻敌范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>散射_获得</t>
+  </si>
+  <si>
+    <t>散射_冷却</t>
+  </si>
+  <si>
+    <t>散射_最近释放距离</t>
+  </si>
+  <si>
+    <t>散射_最远释放距离</t>
+  </si>
+  <si>
+    <t>散射_技能效果半径</t>
+  </si>
+  <si>
+    <t>散射_目标数量</t>
+  </si>
+  <si>
+    <t>散射_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>散射_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>散射_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>散射_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>散射_弹道数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毁天灭地被动_获得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毁天灭地被动-逻辑id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炸火球_获得</t>
+  </si>
+  <si>
+    <t>爆炸火球_冷却</t>
+  </si>
+  <si>
+    <t>爆炸火球_最近释放距离</t>
+  </si>
+  <si>
+    <t>爆炸火球_最远释放距离</t>
+  </si>
+  <si>
+    <t>爆炸火球_技能效果半径</t>
+  </si>
+  <si>
+    <t>爆炸火球_目标数量</t>
+  </si>
+  <si>
+    <t>爆炸火球_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>爆炸火球_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>爆炸火球_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>爆炸火球_非主目标直接伤害系数</t>
   </si>
 </sst>
 </file>
@@ -4092,7 +4157,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1428"/>
+  <dimension ref="A1:I1449"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -39459,35 +39524,35 @@
       </c>
     </row>
     <row r="1266" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1266" s="26">
-        <v>5001600</v>
+      <c r="A1266">
+        <v>21920061</v>
       </c>
       <c r="B1266" s="26">
         <v>1</v>
       </c>
-      <c r="C1266" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1266" s="26" t="s">
-        <v>882</v>
-      </c>
-      <c r="E1266" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="F1266" s="9"/>
-      <c r="G1266" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1266" s="26">
+      <c r="C1266">
+        <v>0</v>
+      </c>
+      <c r="D1266" s="28" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E1266" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1266" s="28"/>
+      <c r="G1266">
+        <v>10</v>
+      </c>
+      <c r="H1266">
         <v>1</v>
       </c>
       <c r="I1266">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1267" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1267" s="26">
-        <v>5001501</v>
+        <v>5001600</v>
       </c>
       <c r="B1267" s="26">
         <v>1</v>
@@ -39496,17 +39561,17 @@
         <v>0</v>
       </c>
       <c r="D1267" s="26" t="s">
-        <v>883</v>
-      </c>
-      <c r="E1267" s="19" t="s">
-        <v>329</v>
+        <v>882</v>
+      </c>
+      <c r="E1267" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="F1267" s="9"/>
       <c r="G1267" s="26">
         <v>10</v>
       </c>
       <c r="H1267" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1267">
         <v>0</v>
@@ -39514,7 +39579,7 @@
     </row>
     <row r="1268" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1268" s="26">
-        <v>5001502</v>
+        <v>5001501</v>
       </c>
       <c r="B1268" s="26">
         <v>1</v>
@@ -39526,14 +39591,14 @@
         <v>883</v>
       </c>
       <c r="E1268" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1268" s="9"/>
       <c r="G1268" s="26">
         <v>10</v>
       </c>
       <c r="H1268" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1268">
         <v>0</v>
@@ -39541,7 +39606,7 @@
     </row>
     <row r="1269" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1269" s="26">
-        <v>5001511</v>
+        <v>5001502</v>
       </c>
       <c r="B1269" s="26">
         <v>1</v>
@@ -39550,17 +39615,17 @@
         <v>0</v>
       </c>
       <c r="D1269" s="26" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E1269" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1269" s="9"/>
       <c r="G1269" s="26">
         <v>10</v>
       </c>
       <c r="H1269" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1269">
         <v>0</v>
@@ -39568,7 +39633,7 @@
     </row>
     <row r="1270" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1270" s="26">
-        <v>5001512</v>
+        <v>5001511</v>
       </c>
       <c r="B1270" s="26">
         <v>1</v>
@@ -39580,14 +39645,14 @@
         <v>884</v>
       </c>
       <c r="E1270" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1270" s="9"/>
       <c r="G1270" s="26">
         <v>10</v>
       </c>
       <c r="H1270" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1270">
         <v>0</v>
@@ -39595,7 +39660,7 @@
     </row>
     <row r="1271" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1271" s="26">
-        <v>5001521</v>
+        <v>5001512</v>
       </c>
       <c r="B1271" s="26">
         <v>1</v>
@@ -39604,17 +39669,17 @@
         <v>0</v>
       </c>
       <c r="D1271" s="26" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E1271" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1271" s="9"/>
       <c r="G1271" s="26">
         <v>10</v>
       </c>
       <c r="H1271" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1271">
         <v>0</v>
@@ -39622,7 +39687,7 @@
     </row>
     <row r="1272" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1272" s="26">
-        <v>5001522</v>
+        <v>5001521</v>
       </c>
       <c r="B1272" s="26">
         <v>1</v>
@@ -39634,14 +39699,14 @@
         <v>885</v>
       </c>
       <c r="E1272" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1272" s="9"/>
       <c r="G1272" s="26">
         <v>10</v>
       </c>
       <c r="H1272" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1272">
         <v>0</v>
@@ -39649,7 +39714,7 @@
     </row>
     <row r="1273" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1273" s="26">
-        <v>5001800</v>
+        <v>5001522</v>
       </c>
       <c r="B1273" s="26">
         <v>1</v>
@@ -39658,11 +39723,12 @@
         <v>0</v>
       </c>
       <c r="D1273" s="26" t="s">
-        <v>886</v>
-      </c>
-      <c r="E1273" s="26" t="s">
-        <v>243</v>
-      </c>
+        <v>885</v>
+      </c>
+      <c r="E1273" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1273" s="9"/>
       <c r="G1273" s="26">
         <v>10</v>
       </c>
@@ -39675,7 +39741,7 @@
     </row>
     <row r="1274" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1274" s="26">
-        <v>5001701</v>
+        <v>5001800</v>
       </c>
       <c r="B1274" s="26">
         <v>1</v>
@@ -39684,16 +39750,16 @@
         <v>0</v>
       </c>
       <c r="D1274" s="26" t="s">
-        <v>887</v>
-      </c>
-      <c r="E1274" s="19" t="s">
-        <v>888</v>
+        <v>886</v>
+      </c>
+      <c r="E1274" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="G1274" s="26">
         <v>10</v>
       </c>
       <c r="H1274" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1274">
         <v>0</v>
@@ -39701,7 +39767,7 @@
     </row>
     <row r="1275" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1275" s="26">
-        <v>5001702</v>
+        <v>5001701</v>
       </c>
       <c r="B1275" s="26">
         <v>1</v>
@@ -39713,7 +39779,7 @@
         <v>887</v>
       </c>
       <c r="E1275" s="19" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G1275" s="26">
         <v>10</v>
@@ -39727,7 +39793,7 @@
     </row>
     <row r="1276" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1276" s="26">
-        <v>5001705</v>
+        <v>5001702</v>
       </c>
       <c r="B1276" s="26">
         <v>1</v>
@@ -39739,13 +39805,13 @@
         <v>887</v>
       </c>
       <c r="E1276" s="19" t="s">
-        <v>327</v>
+        <v>889</v>
       </c>
       <c r="G1276" s="26">
         <v>10</v>
       </c>
       <c r="H1276" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1276">
         <v>0</v>
@@ -39753,7 +39819,7 @@
     </row>
     <row r="1277" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1277" s="26">
-        <v>5001706</v>
+        <v>5001705</v>
       </c>
       <c r="B1277" s="26">
         <v>1</v>
@@ -39765,13 +39831,13 @@
         <v>887</v>
       </c>
       <c r="E1277" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G1277" s="26">
         <v>10</v>
       </c>
       <c r="H1277" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1277">
         <v>0</v>
@@ -39779,7 +39845,7 @@
     </row>
     <row r="1278" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1278" s="26">
-        <v>5001711</v>
+        <v>5001706</v>
       </c>
       <c r="B1278" s="26">
         <v>1</v>
@@ -39788,10 +39854,10 @@
         <v>0</v>
       </c>
       <c r="D1278" s="26" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="E1278" s="19" t="s">
-        <v>888</v>
+        <v>329</v>
       </c>
       <c r="G1278" s="26">
         <v>10</v>
@@ -39805,7 +39871,7 @@
     </row>
     <row r="1279" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1279" s="26">
-        <v>5001712</v>
+        <v>5001711</v>
       </c>
       <c r="B1279" s="26">
         <v>1</v>
@@ -39817,7 +39883,7 @@
         <v>890</v>
       </c>
       <c r="E1279" s="19" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G1279" s="26">
         <v>10</v>
@@ -39831,7 +39897,7 @@
     </row>
     <row r="1280" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1280" s="26">
-        <v>5001715</v>
+        <v>5001712</v>
       </c>
       <c r="B1280" s="26">
         <v>1</v>
@@ -39843,13 +39909,13 @@
         <v>890</v>
       </c>
       <c r="E1280" s="19" t="s">
-        <v>327</v>
+        <v>889</v>
       </c>
       <c r="G1280" s="26">
         <v>10</v>
       </c>
       <c r="H1280" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1280">
         <v>0</v>
@@ -39857,7 +39923,7 @@
     </row>
     <row r="1281" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1281" s="26">
-        <v>5001716</v>
+        <v>5001715</v>
       </c>
       <c r="B1281" s="26">
         <v>1</v>
@@ -39869,39 +39935,39 @@
         <v>890</v>
       </c>
       <c r="E1281" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1281" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1281" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1282" s="26">
+        <v>5001716</v>
+      </c>
+      <c r="B1282" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1282" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1282" s="26" t="s">
+        <v>890</v>
+      </c>
+      <c r="E1282" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="G1281" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1281" s="26">
+      <c r="G1282" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1282" s="26">
         <v>2</v>
-      </c>
-      <c r="I1281">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1282" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1282">
-        <v>920071</v>
-      </c>
-      <c r="B1282" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1282">
-        <v>0</v>
-      </c>
-      <c r="D1282" s="28" t="s">
-        <v>891</v>
-      </c>
-      <c r="E1282" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1282">
-        <v>10</v>
-      </c>
-      <c r="H1282">
-        <v>1</v>
       </c>
       <c r="I1282">
         <v>0</v>
@@ -39909,7 +39975,7 @@
     </row>
     <row r="1283" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1283">
-        <v>1920071</v>
+        <v>920071</v>
       </c>
       <c r="B1283" s="26">
         <v>1</v>
@@ -39918,10 +39984,10 @@
         <v>0</v>
       </c>
       <c r="D1283" s="28" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E1283" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1283">
         <v>10</v>
@@ -39935,7 +40001,7 @@
     </row>
     <row r="1284" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1284">
-        <v>2920071</v>
+        <v>1920071</v>
       </c>
       <c r="B1284" s="26">
         <v>1</v>
@@ -39944,7 +40010,7 @@
         <v>0</v>
       </c>
       <c r="D1284" s="28" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E1284" s="29" t="s">
         <v>769</v>
@@ -39961,7 +40027,7 @@
     </row>
     <row r="1285" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1285">
-        <v>3920071</v>
+        <v>2920071</v>
       </c>
       <c r="B1285" s="26">
         <v>1</v>
@@ -39970,7 +40036,7 @@
         <v>0</v>
       </c>
       <c r="D1285" s="28" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E1285" s="29" t="s">
         <v>769</v>
@@ -39987,7 +40053,7 @@
     </row>
     <row r="1286" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1286">
-        <v>4920071</v>
+        <v>3920071</v>
       </c>
       <c r="B1286" s="26">
         <v>1</v>
@@ -39996,7 +40062,7 @@
         <v>0</v>
       </c>
       <c r="D1286" s="28" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E1286" s="29" t="s">
         <v>769</v>
@@ -40008,12 +40074,12 @@
         <v>1</v>
       </c>
       <c r="I1286">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1287" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1287">
-        <v>5920071</v>
+        <v>4920071</v>
       </c>
       <c r="B1287" s="26">
         <v>1</v>
@@ -40022,7 +40088,7 @@
         <v>0</v>
       </c>
       <c r="D1287" s="28" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E1287" s="29" t="s">
         <v>769</v>
@@ -40034,12 +40100,12 @@
         <v>1</v>
       </c>
       <c r="I1287">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1288" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1288">
-        <v>6920071</v>
+        <v>5920071</v>
       </c>
       <c r="B1288" s="26">
         <v>1</v>
@@ -40048,7 +40114,7 @@
         <v>0</v>
       </c>
       <c r="D1288" s="28" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E1288" s="29" t="s">
         <v>769</v>
@@ -40065,7 +40131,7 @@
     </row>
     <row r="1289" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1289">
-        <v>7920071</v>
+        <v>6920071</v>
       </c>
       <c r="B1289" s="26">
         <v>1</v>
@@ -40074,7 +40140,7 @@
         <v>0</v>
       </c>
       <c r="D1289" s="28" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E1289" s="29" t="s">
         <v>769</v>
@@ -40083,15 +40149,15 @@
         <v>10</v>
       </c>
       <c r="H1289">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1289">
-        <v>18000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1290" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1290">
-        <v>8920071</v>
+        <v>7920071</v>
       </c>
       <c r="B1290" s="26">
         <v>1</v>
@@ -40100,7 +40166,7 @@
         <v>0</v>
       </c>
       <c r="D1290" s="28" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E1290" s="29" t="s">
         <v>769</v>
@@ -40109,15 +40175,15 @@
         <v>10</v>
       </c>
       <c r="H1290">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1290">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1291" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1291">
-        <v>9920071</v>
+        <v>8920071</v>
       </c>
       <c r="B1291" s="26">
         <v>1</v>
@@ -40126,7 +40192,7 @@
         <v>0</v>
       </c>
       <c r="D1291" s="28" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E1291" s="29" t="s">
         <v>769</v>
@@ -40135,15 +40201,15 @@
         <v>10</v>
       </c>
       <c r="H1291">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1291">
-        <v>18000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1292" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1292">
-        <v>13920071</v>
+        <v>9920071</v>
       </c>
       <c r="B1292" s="26">
         <v>1</v>
@@ -40152,7 +40218,7 @@
         <v>0</v>
       </c>
       <c r="D1292" s="28" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E1292" s="29" t="s">
         <v>769</v>
@@ -40161,15 +40227,15 @@
         <v>10</v>
       </c>
       <c r="H1292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1292">
-        <v>1</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1293" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1293">
-        <v>920072</v>
+        <v>13920071</v>
       </c>
       <c r="B1293" s="26">
         <v>1</v>
@@ -40178,12 +40244,11 @@
         <v>0</v>
       </c>
       <c r="D1293" s="28" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E1293" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1293" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1293">
         <v>10</v>
       </c>
@@ -40191,12 +40256,12 @@
         <v>1</v>
       </c>
       <c r="I1293">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1294" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1294">
-        <v>820072</v>
+        <v>920072</v>
       </c>
       <c r="B1294" s="26">
         <v>1</v>
@@ -40204,12 +40269,13 @@
       <c r="C1294">
         <v>0</v>
       </c>
-      <c r="D1294" s="30" t="s">
-        <v>903</v>
-      </c>
-      <c r="E1294" s="30" t="s">
-        <v>903</v>
-      </c>
+      <c r="D1294" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="E1294" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1294" s="28"/>
       <c r="G1294">
         <v>10</v>
       </c>
@@ -40222,7 +40288,7 @@
     </row>
     <row r="1295" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1295">
-        <v>920081</v>
+        <v>820072</v>
       </c>
       <c r="B1295" s="26">
         <v>1</v>
@@ -40230,11 +40296,11 @@
       <c r="C1295">
         <v>0</v>
       </c>
-      <c r="D1295" s="28" t="s">
-        <v>904</v>
-      </c>
-      <c r="E1295" s="29" t="s">
-        <v>767</v>
+      <c r="D1295" s="30" t="s">
+        <v>903</v>
+      </c>
+      <c r="E1295" s="30" t="s">
+        <v>903</v>
       </c>
       <c r="G1295">
         <v>10</v>
@@ -40248,7 +40314,7 @@
     </row>
     <row r="1296" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1296">
-        <v>1920081</v>
+        <v>920081</v>
       </c>
       <c r="B1296" s="26">
         <v>1</v>
@@ -40257,10 +40323,10 @@
         <v>0</v>
       </c>
       <c r="D1296" s="28" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E1296" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1296">
         <v>10</v>
@@ -40269,12 +40335,12 @@
         <v>1</v>
       </c>
       <c r="I1296">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1297" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1297">
-        <v>2920081</v>
+        <v>1920081</v>
       </c>
       <c r="B1297" s="26">
         <v>1</v>
@@ -40283,7 +40349,7 @@
         <v>0</v>
       </c>
       <c r="D1297" s="28" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E1297" s="29" t="s">
         <v>769</v>
@@ -40295,12 +40361,12 @@
         <v>1</v>
       </c>
       <c r="I1297">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1298" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1298">
-        <v>3920081</v>
+        <v>2920081</v>
       </c>
       <c r="B1298" s="26">
         <v>1</v>
@@ -40309,7 +40375,7 @@
         <v>0</v>
       </c>
       <c r="D1298" s="28" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E1298" s="29" t="s">
         <v>769</v>
@@ -40326,7 +40392,7 @@
     </row>
     <row r="1299" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1299">
-        <v>4920081</v>
+        <v>3920081</v>
       </c>
       <c r="B1299" s="26">
         <v>1</v>
@@ -40335,7 +40401,7 @@
         <v>0</v>
       </c>
       <c r="D1299" s="28" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E1299" s="29" t="s">
         <v>769</v>
@@ -40347,12 +40413,12 @@
         <v>1</v>
       </c>
       <c r="I1299">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1300" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1300">
-        <v>5920081</v>
+        <v>4920081</v>
       </c>
       <c r="B1300" s="26">
         <v>1</v>
@@ -40361,7 +40427,7 @@
         <v>0</v>
       </c>
       <c r="D1300" s="28" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E1300" s="29" t="s">
         <v>769</v>
@@ -40373,12 +40439,12 @@
         <v>1</v>
       </c>
       <c r="I1300">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1301" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1301">
-        <v>6920081</v>
+        <v>5920081</v>
       </c>
       <c r="B1301" s="26">
         <v>1</v>
@@ -40387,7 +40453,7 @@
         <v>0</v>
       </c>
       <c r="D1301" s="28" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1301" s="29" t="s">
         <v>769</v>
@@ -40404,7 +40470,7 @@
     </row>
     <row r="1302" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1302">
-        <v>7920081</v>
+        <v>6920081</v>
       </c>
       <c r="B1302" s="26">
         <v>1</v>
@@ -40413,7 +40479,7 @@
         <v>0</v>
       </c>
       <c r="D1302" s="28" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E1302" s="29" t="s">
         <v>769</v>
@@ -40422,15 +40488,15 @@
         <v>10</v>
       </c>
       <c r="H1302">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1302">
-        <v>16000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1303" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1303">
-        <v>8920081</v>
+        <v>7920081</v>
       </c>
       <c r="B1303" s="26">
         <v>1</v>
@@ -40439,7 +40505,7 @@
         <v>0</v>
       </c>
       <c r="D1303" s="28" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E1303" s="29" t="s">
         <v>769</v>
@@ -40448,15 +40514,15 @@
         <v>10</v>
       </c>
       <c r="H1303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1303">
-        <v>0</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1304" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1304">
-        <v>9920081</v>
+        <v>8920081</v>
       </c>
       <c r="B1304" s="26">
         <v>1</v>
@@ -40465,7 +40531,7 @@
         <v>0</v>
       </c>
       <c r="D1304" s="28" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1304" s="29" t="s">
         <v>769</v>
@@ -40474,15 +40540,15 @@
         <v>10</v>
       </c>
       <c r="H1304">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1304">
-        <v>16000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1305" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1305">
-        <v>10920081</v>
+        <v>9920081</v>
       </c>
       <c r="B1305" s="26">
         <v>1</v>
@@ -40491,25 +40557,24 @@
         <v>0</v>
       </c>
       <c r="D1305" s="28" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E1305" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1305" s="28"/>
       <c r="G1305">
         <v>10</v>
       </c>
       <c r="H1305">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1305">
-        <v>3000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1306" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1306">
-        <v>11920081</v>
+        <v>10920081</v>
       </c>
       <c r="B1306" s="26">
         <v>1</v>
@@ -40518,7 +40583,7 @@
         <v>0</v>
       </c>
       <c r="D1306" s="28" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E1306" s="29" t="s">
         <v>769</v>
@@ -40536,7 +40601,7 @@
     </row>
     <row r="1307" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1307">
-        <v>13920081</v>
+        <v>11920081</v>
       </c>
       <c r="B1307" s="26">
         <v>1</v>
@@ -40545,7 +40610,7 @@
         <v>0</v>
       </c>
       <c r="D1307" s="28" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E1307" s="29" t="s">
         <v>769</v>
@@ -40558,12 +40623,12 @@
         <v>1</v>
       </c>
       <c r="I1307">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1308" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1308">
-        <v>14920081</v>
+        <v>13920081</v>
       </c>
       <c r="B1308" s="26">
         <v>1</v>
@@ -40572,7 +40637,7 @@
         <v>0</v>
       </c>
       <c r="D1308" s="28" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E1308" s="29" t="s">
         <v>769</v>
@@ -40590,7 +40655,7 @@
     </row>
     <row r="1309" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1309">
-        <v>920083</v>
+        <v>14920081</v>
       </c>
       <c r="B1309" s="26">
         <v>1</v>
@@ -40599,11 +40664,12 @@
         <v>0</v>
       </c>
       <c r="D1309" s="28" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E1309" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1309" s="28"/>
       <c r="G1309">
         <v>10</v>
       </c>
@@ -40616,46 +40682,45 @@
     </row>
     <row r="1310" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1310">
+        <v>920083</v>
+      </c>
+      <c r="B1310" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1310">
+        <v>0</v>
+      </c>
+      <c r="D1310" s="28" t="s">
+        <v>918</v>
+      </c>
+      <c r="E1310" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1310">
+        <v>10</v>
+      </c>
+      <c r="H1310">
+        <v>1</v>
+      </c>
+      <c r="I1310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1311">
         <v>14920083</v>
       </c>
-      <c r="B1310" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1310">
-        <v>0</v>
-      </c>
-      <c r="D1310" s="28" t="s">
+      <c r="B1311" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1311">
+        <v>0</v>
+      </c>
+      <c r="D1311" s="28" t="s">
         <v>919</v>
       </c>
-      <c r="E1310" s="29" t="s">
+      <c r="E1311" s="29" t="s">
         <v>769</v>
-      </c>
-      <c r="F1310" s="28"/>
-      <c r="G1310">
-        <v>10</v>
-      </c>
-      <c r="H1310">
-        <v>1</v>
-      </c>
-      <c r="I1310">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1311" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1311" s="31">
-        <v>920082</v>
-      </c>
-      <c r="B1311" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1311">
-        <v>0</v>
-      </c>
-      <c r="D1311" s="28" t="s">
-        <v>920</v>
-      </c>
-      <c r="E1311" s="29" t="s">
-        <v>767</v>
       </c>
       <c r="F1311" s="28"/>
       <c r="G1311">
@@ -40665,12 +40730,12 @@
         <v>1</v>
       </c>
       <c r="I1311">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1312" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1312" s="30">
-        <v>820082</v>
+      <c r="A1312" s="31">
+        <v>920082</v>
       </c>
       <c r="B1312" s="26">
         <v>1</v>
@@ -40678,12 +40743,13 @@
       <c r="C1312">
         <v>0</v>
       </c>
-      <c r="D1312" s="30" t="s">
-        <v>921</v>
-      </c>
-      <c r="E1312" s="30" t="s">
-        <v>921</v>
-      </c>
+      <c r="D1312" s="28" t="s">
+        <v>920</v>
+      </c>
+      <c r="E1312" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1312" s="28"/>
       <c r="G1312">
         <v>10</v>
       </c>
@@ -40696,45 +40762,45 @@
     </row>
     <row r="1313" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1313" s="30">
+        <v>820082</v>
+      </c>
+      <c r="B1313" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1313">
+        <v>0</v>
+      </c>
+      <c r="D1313" s="30" t="s">
+        <v>921</v>
+      </c>
+      <c r="E1313" s="30" t="s">
+        <v>921</v>
+      </c>
+      <c r="G1313">
+        <v>10</v>
+      </c>
+      <c r="H1313">
+        <v>1</v>
+      </c>
+      <c r="I1313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1314" s="30">
         <v>820083</v>
       </c>
-      <c r="B1313" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1313">
-        <v>0</v>
-      </c>
-      <c r="D1313" s="30" t="s">
+      <c r="B1314" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1314">
+        <v>0</v>
+      </c>
+      <c r="D1314" s="30" t="s">
         <v>922</v>
       </c>
-      <c r="E1313" s="30" t="s">
+      <c r="E1314" s="30" t="s">
         <v>922</v>
-      </c>
-      <c r="G1313">
-        <v>10</v>
-      </c>
-      <c r="H1313">
-        <v>1</v>
-      </c>
-      <c r="I1313">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1314" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1314">
-        <v>920074</v>
-      </c>
-      <c r="B1314" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1314">
-        <v>0</v>
-      </c>
-      <c r="D1314" s="28" t="s">
-        <v>923</v>
-      </c>
-      <c r="E1314" s="29" t="s">
-        <v>767</v>
       </c>
       <c r="G1314">
         <v>10</v>
@@ -40748,7 +40814,7 @@
     </row>
     <row r="1315" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1315">
-        <v>3920074</v>
+        <v>920074</v>
       </c>
       <c r="B1315" s="26">
         <v>1</v>
@@ -40757,12 +40823,11 @@
         <v>0</v>
       </c>
       <c r="D1315" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E1315" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1315" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1315">
         <v>10</v>
       </c>
@@ -40770,12 +40835,12 @@
         <v>1</v>
       </c>
       <c r="I1315">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1316" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1316">
-        <v>14920074</v>
+        <v>3920074</v>
       </c>
       <c r="B1316" s="26">
         <v>1</v>
@@ -40784,7 +40849,7 @@
         <v>0</v>
       </c>
       <c r="D1316" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E1316" s="29" t="s">
         <v>769</v>
@@ -40797,12 +40862,12 @@
         <v>1</v>
       </c>
       <c r="I1316">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1317" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1317">
-        <v>16920074</v>
+        <v>14920074</v>
       </c>
       <c r="B1317" s="26">
         <v>1</v>
@@ -40811,7 +40876,7 @@
         <v>0</v>
       </c>
       <c r="D1317" s="28" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E1317" s="29" t="s">
         <v>769</v>
@@ -40821,15 +40886,15 @@
         <v>10</v>
       </c>
       <c r="H1317">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1317">
-        <v>10000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1318" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1318">
-        <v>17920074</v>
+        <v>16920074</v>
       </c>
       <c r="B1318" s="26">
         <v>1</v>
@@ -40838,7 +40903,7 @@
         <v>0</v>
       </c>
       <c r="D1318" s="28" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E1318" s="29" t="s">
         <v>769</v>
@@ -40851,12 +40916,12 @@
         <v>2</v>
       </c>
       <c r="I1318">
-        <v>2000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1319" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1319">
-        <v>18920074</v>
+        <v>17920074</v>
       </c>
       <c r="B1319" s="26">
         <v>1</v>
@@ -40865,7 +40930,7 @@
         <v>0</v>
       </c>
       <c r="D1319" s="28" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E1319" s="29" t="s">
         <v>769</v>
@@ -40878,12 +40943,12 @@
         <v>2</v>
       </c>
       <c r="I1319">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1320" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1320">
-        <v>920073</v>
+        <v>18920074</v>
       </c>
       <c r="B1320" s="26">
         <v>1</v>
@@ -40892,25 +40957,25 @@
         <v>0</v>
       </c>
       <c r="D1320" s="28" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E1320" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1320" s="28"/>
       <c r="G1320">
         <v>10</v>
       </c>
       <c r="H1320">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1320">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1321" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1321">
-        <v>820073</v>
+        <v>920073</v>
       </c>
       <c r="B1321" s="26">
         <v>1</v>
@@ -40918,12 +40983,13 @@
       <c r="C1321">
         <v>0</v>
       </c>
-      <c r="D1321" s="30" t="s">
-        <v>930</v>
-      </c>
-      <c r="E1321" s="30" t="s">
-        <v>930</v>
-      </c>
+      <c r="D1321" s="28" t="s">
+        <v>929</v>
+      </c>
+      <c r="E1321" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1321" s="28"/>
       <c r="G1321">
         <v>10</v>
       </c>
@@ -40936,7 +41002,7 @@
     </row>
     <row r="1322" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1322">
-        <v>920084</v>
+        <v>820073</v>
       </c>
       <c r="B1322" s="26">
         <v>1</v>
@@ -40944,11 +41010,11 @@
       <c r="C1322">
         <v>0</v>
       </c>
-      <c r="D1322" s="28" t="s">
-        <v>931</v>
-      </c>
-      <c r="E1322" s="29" t="s">
-        <v>767</v>
+      <c r="D1322" s="30" t="s">
+        <v>930</v>
+      </c>
+      <c r="E1322" s="30" t="s">
+        <v>930</v>
       </c>
       <c r="G1322">
         <v>10</v>
@@ -40962,7 +41028,7 @@
     </row>
     <row r="1323" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1323">
-        <v>1920084</v>
+        <v>920084</v>
       </c>
       <c r="B1323" s="26">
         <v>1</v>
@@ -40971,10 +41037,10 @@
         <v>0</v>
       </c>
       <c r="D1323" s="28" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E1323" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1323">
         <v>10</v>
@@ -40983,12 +41049,12 @@
         <v>1</v>
       </c>
       <c r="I1323">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1324" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1324">
-        <v>2920084</v>
+        <v>1920084</v>
       </c>
       <c r="B1324" s="26">
         <v>1</v>
@@ -40997,7 +41063,7 @@
         <v>0</v>
       </c>
       <c r="D1324" s="28" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E1324" s="29" t="s">
         <v>769</v>
@@ -41009,12 +41075,12 @@
         <v>1</v>
       </c>
       <c r="I1324">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1325" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1325">
-        <v>3920084</v>
+        <v>2920084</v>
       </c>
       <c r="B1325" s="26">
         <v>1</v>
@@ -41023,7 +41089,7 @@
         <v>0</v>
       </c>
       <c r="D1325" s="28" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E1325" s="29" t="s">
         <v>769</v>
@@ -41040,7 +41106,7 @@
     </row>
     <row r="1326" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1326">
-        <v>4920084</v>
+        <v>3920084</v>
       </c>
       <c r="B1326" s="26">
         <v>1</v>
@@ -41049,7 +41115,7 @@
         <v>0</v>
       </c>
       <c r="D1326" s="28" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E1326" s="29" t="s">
         <v>769</v>
@@ -41061,12 +41127,12 @@
         <v>1</v>
       </c>
       <c r="I1326">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1327" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1327">
-        <v>5920084</v>
+        <v>4920084</v>
       </c>
       <c r="B1327" s="26">
         <v>1</v>
@@ -41075,7 +41141,7 @@
         <v>0</v>
       </c>
       <c r="D1327" s="28" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E1327" s="29" t="s">
         <v>769</v>
@@ -41087,12 +41153,12 @@
         <v>1</v>
       </c>
       <c r="I1327">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1328" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1328">
-        <v>6920084</v>
+        <v>5920084</v>
       </c>
       <c r="B1328" s="26">
         <v>1</v>
@@ -41101,7 +41167,7 @@
         <v>0</v>
       </c>
       <c r="D1328" s="28" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E1328" s="29" t="s">
         <v>769</v>
@@ -41118,7 +41184,7 @@
     </row>
     <row r="1329" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1329">
-        <v>7920084</v>
+        <v>6920084</v>
       </c>
       <c r="B1329" s="26">
         <v>1</v>
@@ -41127,7 +41193,7 @@
         <v>0</v>
       </c>
       <c r="D1329" s="28" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E1329" s="29" t="s">
         <v>769</v>
@@ -41136,7 +41202,7 @@
         <v>10</v>
       </c>
       <c r="H1329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1329">
         <v>0</v>
@@ -41144,7 +41210,7 @@
     </row>
     <row r="1330" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1330">
-        <v>8920084</v>
+        <v>7920084</v>
       </c>
       <c r="B1330" s="26">
         <v>1</v>
@@ -41153,7 +41219,7 @@
         <v>0</v>
       </c>
       <c r="D1330" s="28" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E1330" s="29" t="s">
         <v>769</v>
@@ -41162,7 +41228,7 @@
         <v>10</v>
       </c>
       <c r="H1330">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1330">
         <v>0</v>
@@ -41170,7 +41236,7 @@
     </row>
     <row r="1331" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1331">
-        <v>9920084</v>
+        <v>8920084</v>
       </c>
       <c r="B1331" s="26">
         <v>1</v>
@@ -41179,7 +41245,7 @@
         <v>0</v>
       </c>
       <c r="D1331" s="28" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E1331" s="29" t="s">
         <v>769</v>
@@ -41188,7 +41254,7 @@
         <v>10</v>
       </c>
       <c r="H1331">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1331">
         <v>0</v>
@@ -41196,7 +41262,7 @@
     </row>
     <row r="1332" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1332">
-        <v>13920084</v>
+        <v>9920084</v>
       </c>
       <c r="B1332" s="26">
         <v>1</v>
@@ -41205,7 +41271,7 @@
         <v>0</v>
       </c>
       <c r="D1332" s="28" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E1332" s="29" t="s">
         <v>769</v>
@@ -41214,15 +41280,15 @@
         <v>10</v>
       </c>
       <c r="H1332">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1332">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1333" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1333">
-        <v>16920084</v>
+        <v>13920084</v>
       </c>
       <c r="B1333" s="26">
         <v>1</v>
@@ -41231,12 +41297,11 @@
         <v>0</v>
       </c>
       <c r="D1333" s="28" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E1333" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1333" s="28"/>
       <c r="G1333">
         <v>10</v>
       </c>
@@ -41244,12 +41309,12 @@
         <v>1</v>
       </c>
       <c r="I1333">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1334" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1334">
-        <v>920085</v>
+        <v>16920084</v>
       </c>
       <c r="B1334" s="26">
         <v>1</v>
@@ -41258,11 +41323,12 @@
         <v>0</v>
       </c>
       <c r="D1334" s="28" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E1334" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1334" s="28"/>
       <c r="G1334">
         <v>10</v>
       </c>
@@ -41270,12 +41336,12 @@
         <v>1</v>
       </c>
       <c r="I1334">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1335" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1335">
-        <v>1920085</v>
+        <v>920085</v>
       </c>
       <c r="B1335" s="26">
         <v>1</v>
@@ -41284,10 +41350,10 @@
         <v>0</v>
       </c>
       <c r="D1335" s="28" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E1335" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1335">
         <v>10</v>
@@ -41301,7 +41367,7 @@
     </row>
     <row r="1336" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1336">
-        <v>2920085</v>
+        <v>1920085</v>
       </c>
       <c r="B1336" s="26">
         <v>1</v>
@@ -41310,7 +41376,7 @@
         <v>0</v>
       </c>
       <c r="D1336" s="28" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E1336" s="29" t="s">
         <v>769</v>
@@ -41327,7 +41393,7 @@
     </row>
     <row r="1337" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1337">
-        <v>3920085</v>
+        <v>2920085</v>
       </c>
       <c r="B1337" s="26">
         <v>1</v>
@@ -41336,7 +41402,7 @@
         <v>0</v>
       </c>
       <c r="D1337" s="28" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E1337" s="29" t="s">
         <v>769</v>
@@ -41353,7 +41419,7 @@
     </row>
     <row r="1338" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1338">
-        <v>4920085</v>
+        <v>3920085</v>
       </c>
       <c r="B1338" s="26">
         <v>1</v>
@@ -41362,7 +41428,7 @@
         <v>0</v>
       </c>
       <c r="D1338" s="28" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E1338" s="29" t="s">
         <v>769</v>
@@ -41374,12 +41440,12 @@
         <v>1</v>
       </c>
       <c r="I1338">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1339" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1339">
-        <v>5920085</v>
+        <v>4920085</v>
       </c>
       <c r="B1339" s="26">
         <v>1</v>
@@ -41388,7 +41454,7 @@
         <v>0</v>
       </c>
       <c r="D1339" s="28" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E1339" s="29" t="s">
         <v>769</v>
@@ -41400,12 +41466,12 @@
         <v>1</v>
       </c>
       <c r="I1339">
-        <v>6</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1340" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1340">
-        <v>6920085</v>
+        <v>5920085</v>
       </c>
       <c r="B1340" s="26">
         <v>1</v>
@@ -41414,7 +41480,7 @@
         <v>0</v>
       </c>
       <c r="D1340" s="28" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E1340" s="29" t="s">
         <v>769</v>
@@ -41426,12 +41492,12 @@
         <v>1</v>
       </c>
       <c r="I1340">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1341" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1341">
-        <v>7920085</v>
+        <v>6920085</v>
       </c>
       <c r="B1341" s="26">
         <v>1</v>
@@ -41440,7 +41506,7 @@
         <v>0</v>
       </c>
       <c r="D1341" s="28" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E1341" s="29" t="s">
         <v>769</v>
@@ -41449,15 +41515,15 @@
         <v>10</v>
       </c>
       <c r="H1341">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1341">
-        <v>18000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1342" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1342">
-        <v>8920085</v>
+        <v>7920085</v>
       </c>
       <c r="B1342" s="26">
         <v>1</v>
@@ -41466,7 +41532,7 @@
         <v>0</v>
       </c>
       <c r="D1342" s="28" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E1342" s="29" t="s">
         <v>769</v>
@@ -41475,15 +41541,15 @@
         <v>10</v>
       </c>
       <c r="H1342">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1342">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1343" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1343">
-        <v>9920085</v>
+        <v>8920085</v>
       </c>
       <c r="B1343" s="26">
         <v>1</v>
@@ -41492,7 +41558,7 @@
         <v>0</v>
       </c>
       <c r="D1343" s="28" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E1343" s="29" t="s">
         <v>769</v>
@@ -41501,15 +41567,15 @@
         <v>10</v>
       </c>
       <c r="H1343">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1343">
-        <v>18000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1344" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1344">
-        <v>920086</v>
+        <v>9920085</v>
       </c>
       <c r="B1344" s="26">
         <v>1</v>
@@ -41518,25 +41584,24 @@
         <v>0</v>
       </c>
       <c r="D1344" s="28" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E1344" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1344" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1344">
         <v>10</v>
       </c>
       <c r="H1344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1344">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1345" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1345">
-        <v>820086</v>
+        <v>920086</v>
       </c>
       <c r="B1345" s="26">
         <v>1</v>
@@ -41544,12 +41609,13 @@
       <c r="C1345">
         <v>0</v>
       </c>
-      <c r="D1345" s="30" t="s">
-        <v>954</v>
-      </c>
-      <c r="E1345" s="30" t="s">
-        <v>954</v>
-      </c>
+      <c r="D1345" s="28" t="s">
+        <v>953</v>
+      </c>
+      <c r="E1345" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1345" s="28"/>
       <c r="G1345">
         <v>10</v>
       </c>
@@ -41562,7 +41628,7 @@
     </row>
     <row r="1346" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1346">
-        <v>8200861</v>
+        <v>820086</v>
       </c>
       <c r="B1346" s="26">
         <v>1</v>
@@ -41571,16 +41637,16 @@
         <v>0</v>
       </c>
       <c r="D1346" s="30" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E1346" s="30" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G1346">
         <v>10</v>
       </c>
       <c r="H1346">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1346">
         <v>0</v>
@@ -41588,7 +41654,7 @@
     </row>
     <row r="1347" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1347">
-        <v>990001</v>
+        <v>8200861</v>
       </c>
       <c r="B1347" s="26">
         <v>1</v>
@@ -41596,26 +41662,25 @@
       <c r="C1347">
         <v>0</v>
       </c>
-      <c r="D1347" s="28" t="s">
-        <v>957</v>
-      </c>
-      <c r="E1347" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1347" s="28"/>
+      <c r="D1347" s="30" t="s">
+        <v>955</v>
+      </c>
+      <c r="E1347" s="30" t="s">
+        <v>956</v>
+      </c>
       <c r="G1347">
         <v>10</v>
       </c>
       <c r="H1347">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1347">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1348" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1348">
-        <v>890001</v>
+        <v>990001</v>
       </c>
       <c r="B1348" s="26">
         <v>1</v>
@@ -41624,11 +41689,12 @@
         <v>0</v>
       </c>
       <c r="D1348" s="28" t="s">
-        <v>958</v>
-      </c>
-      <c r="E1348" s="28" t="s">
-        <v>958</v>
-      </c>
+        <v>957</v>
+      </c>
+      <c r="E1348" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1348" s="28"/>
       <c r="G1348">
         <v>10</v>
       </c>
@@ -41636,12 +41702,12 @@
         <v>1</v>
       </c>
       <c r="I1348">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1349" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1349">
-        <v>890011</v>
+        <v>890001</v>
       </c>
       <c r="B1349" s="26">
         <v>1</v>
@@ -41650,16 +41716,16 @@
         <v>0</v>
       </c>
       <c r="D1349" s="28" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E1349" s="28" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G1349">
         <v>10</v>
       </c>
       <c r="H1349">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1349">
         <v>0</v>
@@ -41667,7 +41733,7 @@
     </row>
     <row r="1350" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1350">
-        <v>890021</v>
+        <v>890011</v>
       </c>
       <c r="B1350" s="26">
         <v>1</v>
@@ -41676,16 +41742,16 @@
         <v>0</v>
       </c>
       <c r="D1350" s="28" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1350" s="28" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="G1350">
         <v>10</v>
       </c>
       <c r="H1350">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1350">
         <v>0</v>
@@ -41693,54 +41759,51 @@
     </row>
     <row r="1351" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1351">
+        <v>890021</v>
+      </c>
+      <c r="B1351" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1351">
+        <v>0</v>
+      </c>
+      <c r="D1351" s="28" t="s">
+        <v>960</v>
+      </c>
+      <c r="E1351" s="28" t="s">
+        <v>961</v>
+      </c>
+      <c r="G1351">
+        <v>10</v>
+      </c>
+      <c r="H1351">
+        <v>1</v>
+      </c>
+      <c r="I1351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1352">
         <v>890022</v>
       </c>
-      <c r="B1351" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1351">
-        <v>0</v>
-      </c>
-      <c r="D1351" s="28" t="s">
+      <c r="B1352" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1352">
+        <v>0</v>
+      </c>
+      <c r="D1352" s="28" t="s">
         <v>962</v>
       </c>
-      <c r="E1351" s="28" t="s">
+      <c r="E1352" s="28" t="s">
         <v>963</v>
       </c>
-      <c r="G1351">
-        <v>10</v>
-      </c>
-      <c r="H1351">
+      <c r="G1352">
+        <v>10</v>
+      </c>
+      <c r="H1352">
         <v>2</v>
-      </c>
-      <c r="I1351">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1352" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1352" s="26">
-        <v>5101200</v>
-      </c>
-      <c r="B1352" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1352" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1352" s="27" t="s">
-        <v>323</v>
-      </c>
-      <c r="E1352" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="F1352" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1352" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1352" s="26">
-        <v>1</v>
       </c>
       <c r="I1352">
         <v>0</v>
@@ -41748,7 +41811,7 @@
     </row>
     <row r="1353" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1353" s="26">
-        <v>5101201</v>
+        <v>5101200</v>
       </c>
       <c r="B1353" s="26">
         <v>1</v>
@@ -41757,10 +41820,10 @@
         <v>0</v>
       </c>
       <c r="D1353" s="27" t="s">
-        <v>1022</v>
+        <v>323</v>
       </c>
       <c r="E1353" s="26" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F1353" s="9" t="s">
         <v>100</v>
@@ -41769,7 +41832,7 @@
         <v>10</v>
       </c>
       <c r="H1353" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1353">
         <v>0</v>
@@ -41777,7 +41840,7 @@
     </row>
     <row r="1354" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1354" s="26">
-        <v>5101202</v>
+        <v>5101201</v>
       </c>
       <c r="B1354" s="26">
         <v>1</v>
@@ -41786,10 +41849,10 @@
         <v>0</v>
       </c>
       <c r="D1354" s="27" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E1354" s="26" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1354" s="9" t="s">
         <v>100</v>
@@ -41798,7 +41861,7 @@
         <v>10</v>
       </c>
       <c r="H1354" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1354">
         <v>0</v>
@@ -41806,7 +41869,7 @@
     </row>
     <row r="1355" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1355" s="26">
-        <v>5101205</v>
+        <v>5101202</v>
       </c>
       <c r="B1355" s="26">
         <v>1</v>
@@ -41815,10 +41878,10 @@
         <v>0</v>
       </c>
       <c r="D1355" s="27" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="E1355" s="26" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="F1355" s="9" t="s">
         <v>100</v>
@@ -41835,7 +41898,7 @@
     </row>
     <row r="1356" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1356" s="26">
-        <v>5101206</v>
+        <v>5101205</v>
       </c>
       <c r="B1356" s="26">
         <v>1</v>
@@ -41844,10 +41907,10 @@
         <v>0</v>
       </c>
       <c r="D1356" s="27" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="E1356" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1356" s="9" t="s">
         <v>100</v>
@@ -41856,7 +41919,7 @@
         <v>10</v>
       </c>
       <c r="H1356" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1356">
         <v>0</v>
@@ -41864,7 +41927,7 @@
     </row>
     <row r="1357" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1357" s="26">
-        <v>5101208</v>
+        <v>5101206</v>
       </c>
       <c r="B1357" s="26">
         <v>1</v>
@@ -41873,10 +41936,10 @@
         <v>0</v>
       </c>
       <c r="D1357" s="27" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="E1357" s="26" t="s">
-        <v>1032</v>
+        <v>329</v>
       </c>
       <c r="F1357" s="9" t="s">
         <v>100</v>
@@ -41885,7 +41948,7 @@
         <v>10</v>
       </c>
       <c r="H1357" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1357">
         <v>0</v>
@@ -41893,7 +41956,7 @@
     </row>
     <row r="1358" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1358" s="26">
-        <v>5101211</v>
+        <v>5101208</v>
       </c>
       <c r="B1358" s="26">
         <v>1</v>
@@ -41902,10 +41965,10 @@
         <v>0</v>
       </c>
       <c r="D1358" s="27" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E1358" s="26" t="s">
-        <v>245</v>
+        <v>1030</v>
       </c>
       <c r="F1358" s="9" t="s">
         <v>100</v>
@@ -41914,7 +41977,7 @@
         <v>10</v>
       </c>
       <c r="H1358" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1358">
         <v>0</v>
@@ -41922,7 +41985,7 @@
     </row>
     <row r="1359" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1359" s="26">
-        <v>5101212</v>
+        <v>5101211</v>
       </c>
       <c r="B1359" s="26">
         <v>1</v>
@@ -41931,10 +41994,10 @@
         <v>0</v>
       </c>
       <c r="D1359" s="27" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="E1359" s="26" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1359" s="9" t="s">
         <v>100</v>
@@ -41943,7 +42006,7 @@
         <v>10</v>
       </c>
       <c r="H1359" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1359">
         <v>0</v>
@@ -41951,7 +42014,7 @@
     </row>
     <row r="1360" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1360" s="26">
-        <v>5101215</v>
+        <v>5101212</v>
       </c>
       <c r="B1360" s="26">
         <v>1</v>
@@ -41960,10 +42023,10 @@
         <v>0</v>
       </c>
       <c r="D1360" s="27" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="E1360" s="26" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="F1360" s="9" t="s">
         <v>100</v>
@@ -41980,7 +42043,7 @@
     </row>
     <row r="1361" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1361" s="26">
-        <v>5101216</v>
+        <v>5101215</v>
       </c>
       <c r="B1361" s="26">
         <v>1</v>
@@ -41989,10 +42052,10 @@
         <v>0</v>
       </c>
       <c r="D1361" s="27" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="E1361" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1361" s="9" t="s">
         <v>100</v>
@@ -42001,7 +42064,7 @@
         <v>10</v>
       </c>
       <c r="H1361" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1361">
         <v>0</v>
@@ -42009,53 +42072,56 @@
     </row>
     <row r="1362" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1362" s="26">
+        <v>5101216</v>
+      </c>
+      <c r="B1362" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1362" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1362" s="27" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E1362" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1362" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1362" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1362" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1363" s="26">
         <v>5101218</v>
       </c>
-      <c r="B1362" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1362" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1362" s="27" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E1362" s="26" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F1362" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1362" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1362" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1362">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1363" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1363">
-        <v>920091</v>
-      </c>
       <c r="B1363" s="26">
         <v>1</v>
       </c>
-      <c r="C1363">
-        <v>0</v>
-      </c>
-      <c r="D1363" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="E1363" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1363">
-        <v>10</v>
-      </c>
-      <c r="H1363">
+      <c r="C1363" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1363" s="27" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E1363" s="26" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F1363" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1363" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1363" s="26">
         <v>1</v>
       </c>
       <c r="I1363">
@@ -42064,7 +42130,7 @@
     </row>
     <row r="1364" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1364">
-        <v>1920091</v>
+        <v>920091</v>
       </c>
       <c r="B1364" s="26">
         <v>1</v>
@@ -42073,10 +42139,10 @@
         <v>0</v>
       </c>
       <c r="D1364" s="28" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="E1364" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1364">
         <v>10</v>
@@ -42090,7 +42156,7 @@
     </row>
     <row r="1365" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1365">
-        <v>2920091</v>
+        <v>1920091</v>
       </c>
       <c r="B1365" s="26">
         <v>1</v>
@@ -42099,7 +42165,7 @@
         <v>0</v>
       </c>
       <c r="D1365" s="28" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="E1365" s="29" t="s">
         <v>769</v>
@@ -42116,7 +42182,7 @@
     </row>
     <row r="1366" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1366">
-        <v>3920091</v>
+        <v>2920091</v>
       </c>
       <c r="B1366" s="26">
         <v>1</v>
@@ -42125,7 +42191,7 @@
         <v>0</v>
       </c>
       <c r="D1366" s="28" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="E1366" s="29" t="s">
         <v>769</v>
@@ -42137,12 +42203,12 @@
         <v>1</v>
       </c>
       <c r="I1366">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1367" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1367">
-        <v>4920091</v>
+        <v>3920091</v>
       </c>
       <c r="B1367" s="26">
         <v>1</v>
@@ -42151,7 +42217,7 @@
         <v>0</v>
       </c>
       <c r="D1367" s="28" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="E1367" s="29" t="s">
         <v>769</v>
@@ -42163,12 +42229,12 @@
         <v>1</v>
       </c>
       <c r="I1367">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1368" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1368">
-        <v>5920091</v>
+        <v>4920091</v>
       </c>
       <c r="B1368" s="26">
         <v>1</v>
@@ -42177,7 +42243,7 @@
         <v>0</v>
       </c>
       <c r="D1368" s="28" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="E1368" s="29" t="s">
         <v>769</v>
@@ -42189,12 +42255,12 @@
         <v>1</v>
       </c>
       <c r="I1368">
-        <v>6</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1369" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1369">
-        <v>6920091</v>
+        <v>5920091</v>
       </c>
       <c r="B1369" s="26">
         <v>1</v>
@@ -42203,7 +42269,7 @@
         <v>0</v>
       </c>
       <c r="D1369" s="28" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="E1369" s="29" t="s">
         <v>769</v>
@@ -42220,7 +42286,7 @@
     </row>
     <row r="1370" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1370">
-        <v>7920091</v>
+        <v>6920091</v>
       </c>
       <c r="B1370" s="26">
         <v>1</v>
@@ -42229,7 +42295,7 @@
         <v>0</v>
       </c>
       <c r="D1370" s="28" t="s">
-        <v>637</v>
+        <v>619</v>
       </c>
       <c r="E1370" s="29" t="s">
         <v>769</v>
@@ -42238,15 +42304,15 @@
         <v>10</v>
       </c>
       <c r="H1370">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1370">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1371" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1371">
-        <v>8920091</v>
+        <v>7920091</v>
       </c>
       <c r="B1371" s="26">
         <v>1</v>
@@ -42255,7 +42321,7 @@
         <v>0</v>
       </c>
       <c r="D1371" s="28" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="E1371" s="29" t="s">
         <v>769</v>
@@ -42264,15 +42330,15 @@
         <v>10</v>
       </c>
       <c r="H1371">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1371">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1372" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1372">
-        <v>9920091</v>
+        <v>8920091</v>
       </c>
       <c r="B1372" s="26">
         <v>1</v>
@@ -42281,7 +42347,7 @@
         <v>0</v>
       </c>
       <c r="D1372" s="28" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="E1372" s="29" t="s">
         <v>769</v>
@@ -42290,21 +42356,24 @@
         <v>10</v>
       </c>
       <c r="H1372">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1372">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1373" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1373">
-        <v>13920091</v>
+        <v>9920091</v>
       </c>
       <c r="B1373" s="26">
         <v>1</v>
       </c>
+      <c r="C1373">
+        <v>0</v>
+      </c>
       <c r="D1373" s="28" t="s">
-        <v>964</v>
+        <v>671</v>
       </c>
       <c r="E1373" s="29" t="s">
         <v>769</v>
@@ -42313,21 +42382,21 @@
         <v>10</v>
       </c>
       <c r="H1373">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1373">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1374" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1374">
-        <v>14920091</v>
+        <v>13920091</v>
       </c>
       <c r="B1374" s="26">
         <v>1</v>
       </c>
       <c r="D1374" s="28" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E1374" s="29" t="s">
         <v>769</v>
@@ -42344,13 +42413,13 @@
     </row>
     <row r="1375" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1375">
-        <v>15920091</v>
+        <v>14920091</v>
       </c>
       <c r="B1375" s="26">
         <v>1</v>
       </c>
       <c r="D1375" s="28" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E1375" s="29" t="s">
         <v>769</v>
@@ -42362,24 +42431,21 @@
         <v>1</v>
       </c>
       <c r="I1375">
-        <v>200</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1376" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1376">
-        <v>920092</v>
+        <v>15920091</v>
       </c>
       <c r="B1376" s="26">
         <v>1</v>
       </c>
-      <c r="C1376">
-        <v>0</v>
-      </c>
       <c r="D1376" s="28" t="s">
-        <v>1007</v>
+        <v>966</v>
       </c>
       <c r="E1376" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1376">
         <v>10</v>
@@ -42388,12 +42454,12 @@
         <v>1</v>
       </c>
       <c r="I1376">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1377" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1377">
-        <v>1920092</v>
+        <v>920092</v>
       </c>
       <c r="B1377" s="26">
         <v>1</v>
@@ -42402,10 +42468,10 @@
         <v>0</v>
       </c>
       <c r="D1377" s="28" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E1377" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1377">
         <v>10</v>
@@ -42419,7 +42485,7 @@
     </row>
     <row r="1378" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1378">
-        <v>2920092</v>
+        <v>1920092</v>
       </c>
       <c r="B1378" s="26">
         <v>1</v>
@@ -42428,7 +42494,7 @@
         <v>0</v>
       </c>
       <c r="D1378" s="28" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E1378" s="29" t="s">
         <v>769</v>
@@ -42445,7 +42511,7 @@
     </row>
     <row r="1379" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1379">
-        <v>3920092</v>
+        <v>2920092</v>
       </c>
       <c r="B1379" s="26">
         <v>1</v>
@@ -42454,7 +42520,7 @@
         <v>0</v>
       </c>
       <c r="D1379" s="28" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E1379" s="29" t="s">
         <v>769</v>
@@ -42471,7 +42537,7 @@
     </row>
     <row r="1380" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1380">
-        <v>4920092</v>
+        <v>3920092</v>
       </c>
       <c r="B1380" s="26">
         <v>1</v>
@@ -42480,7 +42546,7 @@
         <v>0</v>
       </c>
       <c r="D1380" s="28" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E1380" s="29" t="s">
         <v>769</v>
@@ -42492,12 +42558,12 @@
         <v>1</v>
       </c>
       <c r="I1380">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1381" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1381">
-        <v>5920092</v>
+        <v>4920092</v>
       </c>
       <c r="B1381" s="26">
         <v>1</v>
@@ -42506,7 +42572,7 @@
         <v>0</v>
       </c>
       <c r="D1381" s="28" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E1381" s="29" t="s">
         <v>769</v>
@@ -42518,12 +42584,12 @@
         <v>1</v>
       </c>
       <c r="I1381">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1382" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1382">
-        <v>6920092</v>
+        <v>5920092</v>
       </c>
       <c r="B1382" s="26">
         <v>1</v>
@@ -42532,7 +42598,7 @@
         <v>0</v>
       </c>
       <c r="D1382" s="28" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E1382" s="29" t="s">
         <v>769</v>
@@ -42549,7 +42615,7 @@
     </row>
     <row r="1383" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1383">
-        <v>7920092</v>
+        <v>6920092</v>
       </c>
       <c r="B1383" s="26">
         <v>1</v>
@@ -42558,7 +42624,7 @@
         <v>0</v>
       </c>
       <c r="D1383" s="28" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E1383" s="29" t="s">
         <v>769</v>
@@ -42567,15 +42633,15 @@
         <v>10</v>
       </c>
       <c r="H1383">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1383">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1384" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1384">
-        <v>8920092</v>
+        <v>7920092</v>
       </c>
       <c r="B1384" s="26">
         <v>1</v>
@@ -42584,7 +42650,7 @@
         <v>0</v>
       </c>
       <c r="D1384" s="28" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E1384" s="29" t="s">
         <v>769</v>
@@ -42593,15 +42659,15 @@
         <v>10</v>
       </c>
       <c r="H1384">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1384">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1385" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1385">
-        <v>9920092</v>
+        <v>8920092</v>
       </c>
       <c r="B1385" s="26">
         <v>1</v>
@@ -42610,7 +42676,7 @@
         <v>0</v>
       </c>
       <c r="D1385" s="28" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E1385" s="29" t="s">
         <v>769</v>
@@ -42619,15 +42685,15 @@
         <v>10</v>
       </c>
       <c r="H1385">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1385">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1386" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1386">
-        <v>10920092</v>
+        <v>9920092</v>
       </c>
       <c r="B1386" s="26">
         <v>1</v>
@@ -42636,7 +42702,7 @@
         <v>0</v>
       </c>
       <c r="D1386" s="28" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E1386" s="29" t="s">
         <v>769</v>
@@ -42645,15 +42711,15 @@
         <v>10</v>
       </c>
       <c r="H1386">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1386">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1387" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1387">
-        <v>11920092</v>
+        <v>10920092</v>
       </c>
       <c r="B1387" s="26">
         <v>1</v>
@@ -42662,7 +42728,7 @@
         <v>0</v>
       </c>
       <c r="D1387" s="28" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E1387" s="29" t="s">
         <v>769</v>
@@ -42674,12 +42740,12 @@
         <v>1</v>
       </c>
       <c r="I1387">
-        <v>1000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1388" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1388">
-        <v>13920092</v>
+        <v>11920092</v>
       </c>
       <c r="B1388" s="26">
         <v>1</v>
@@ -42688,7 +42754,7 @@
         <v>0</v>
       </c>
       <c r="D1388" s="28" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E1388" s="29" t="s">
         <v>769</v>
@@ -42700,12 +42766,12 @@
         <v>1</v>
       </c>
       <c r="I1388">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1389" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1389">
-        <v>920093</v>
+        <v>13920092</v>
       </c>
       <c r="B1389" s="26">
         <v>1</v>
@@ -42714,10 +42780,10 @@
         <v>0</v>
       </c>
       <c r="D1389" s="28" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E1389" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1389">
         <v>10</v>
@@ -42726,12 +42792,12 @@
         <v>1</v>
       </c>
       <c r="I1389">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1390" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1390">
-        <v>820093</v>
+        <v>920101</v>
       </c>
       <c r="B1390" s="26">
         <v>1</v>
@@ -42739,11 +42805,11 @@
       <c r="C1390">
         <v>0</v>
       </c>
-      <c r="D1390" s="30" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E1390" s="30" t="s">
-        <v>1021</v>
+      <c r="D1390" s="28" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E1390" s="29" t="s">
+        <v>767</v>
       </c>
       <c r="G1390">
         <v>10</v>
@@ -42757,7 +42823,7 @@
     </row>
     <row r="1391" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1391">
-        <v>920101</v>
+        <v>1920101</v>
       </c>
       <c r="B1391" s="26">
         <v>1</v>
@@ -42766,10 +42832,10 @@
         <v>0</v>
       </c>
       <c r="D1391" s="28" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E1391" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1391">
         <v>10</v>
@@ -42778,12 +42844,12 @@
         <v>1</v>
       </c>
       <c r="I1391">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1392" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1392">
-        <v>1920101</v>
+        <v>2920101</v>
       </c>
       <c r="B1392" s="26">
         <v>1</v>
@@ -42792,7 +42858,7 @@
         <v>0</v>
       </c>
       <c r="D1392" s="28" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E1392" s="29" t="s">
         <v>769</v>
@@ -42804,12 +42870,12 @@
         <v>1</v>
       </c>
       <c r="I1392">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1393" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1393">
-        <v>2920101</v>
+        <v>3920101</v>
       </c>
       <c r="B1393" s="26">
         <v>1</v>
@@ -42818,7 +42884,7 @@
         <v>0</v>
       </c>
       <c r="D1393" s="28" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E1393" s="29" t="s">
         <v>769</v>
@@ -42835,7 +42901,7 @@
     </row>
     <row r="1394" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1394">
-        <v>3920101</v>
+        <v>4920101</v>
       </c>
       <c r="B1394" s="26">
         <v>1</v>
@@ -42844,7 +42910,7 @@
         <v>0</v>
       </c>
       <c r="D1394" s="28" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E1394" s="29" t="s">
         <v>769</v>
@@ -42856,12 +42922,12 @@
         <v>1</v>
       </c>
       <c r="I1394">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1395" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1395">
-        <v>4920101</v>
+        <v>5920101</v>
       </c>
       <c r="B1395" s="26">
         <v>1</v>
@@ -42870,7 +42936,7 @@
         <v>0</v>
       </c>
       <c r="D1395" s="28" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E1395" s="29" t="s">
         <v>769</v>
@@ -42882,12 +42948,12 @@
         <v>1</v>
       </c>
       <c r="I1395">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1396" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1396">
-        <v>5920101</v>
+        <v>6920101</v>
       </c>
       <c r="B1396" s="26">
         <v>1</v>
@@ -42896,7 +42962,7 @@
         <v>0</v>
       </c>
       <c r="D1396" s="28" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E1396" s="29" t="s">
         <v>769</v>
@@ -42913,7 +42979,7 @@
     </row>
     <row r="1397" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1397">
-        <v>6920101</v>
+        <v>7920101</v>
       </c>
       <c r="B1397" s="26">
         <v>1</v>
@@ -42922,7 +42988,7 @@
         <v>0</v>
       </c>
       <c r="D1397" s="28" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E1397" s="29" t="s">
         <v>769</v>
@@ -42931,7 +42997,7 @@
         <v>10</v>
       </c>
       <c r="H1397">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1397">
         <v>0</v>
@@ -42939,7 +43005,7 @@
     </row>
     <row r="1398" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1398">
-        <v>7920101</v>
+        <v>8920101</v>
       </c>
       <c r="B1398" s="26">
         <v>1</v>
@@ -42948,7 +43014,7 @@
         <v>0</v>
       </c>
       <c r="D1398" s="28" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E1398" s="29" t="s">
         <v>769</v>
@@ -42957,7 +43023,7 @@
         <v>10</v>
       </c>
       <c r="H1398">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1398">
         <v>0</v>
@@ -42965,7 +43031,7 @@
     </row>
     <row r="1399" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1399">
-        <v>8920101</v>
+        <v>9920101</v>
       </c>
       <c r="B1399" s="26">
         <v>1</v>
@@ -42974,7 +43040,7 @@
         <v>0</v>
       </c>
       <c r="D1399" s="28" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E1399" s="29" t="s">
         <v>769</v>
@@ -42983,7 +43049,7 @@
         <v>10</v>
       </c>
       <c r="H1399">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1399">
         <v>0</v>
@@ -42991,7 +43057,7 @@
     </row>
     <row r="1400" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1400">
-        <v>9920101</v>
+        <v>16920101</v>
       </c>
       <c r="B1400" s="26">
         <v>1</v>
@@ -43000,24 +43066,25 @@
         <v>0</v>
       </c>
       <c r="D1400" s="28" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E1400" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1400" s="28"/>
       <c r="G1400">
         <v>10</v>
       </c>
       <c r="H1400">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1400">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1401" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1401">
-        <v>13920101</v>
+        <v>920102</v>
       </c>
       <c r="B1401" s="26">
         <v>1</v>
@@ -43026,10 +43093,10 @@
         <v>0</v>
       </c>
       <c r="D1401" s="28" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E1401" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1401">
         <v>10</v>
@@ -43038,12 +43105,12 @@
         <v>1</v>
       </c>
       <c r="I1401">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1402" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1402">
-        <v>16920101</v>
+        <v>1920102</v>
       </c>
       <c r="B1402" s="26">
         <v>1</v>
@@ -43052,12 +43119,11 @@
         <v>0</v>
       </c>
       <c r="D1402" s="28" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E1402" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1402" s="28"/>
       <c r="G1402">
         <v>10</v>
       </c>
@@ -43065,12 +43131,12 @@
         <v>1</v>
       </c>
       <c r="I1402">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1403" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1403">
-        <v>920102</v>
+        <v>2920102</v>
       </c>
       <c r="B1403" s="26">
         <v>1</v>
@@ -43079,10 +43145,10 @@
         <v>0</v>
       </c>
       <c r="D1403" s="28" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E1403" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1403">
         <v>10</v>
@@ -43096,7 +43162,7 @@
     </row>
     <row r="1404" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1404">
-        <v>1920102</v>
+        <v>3920102</v>
       </c>
       <c r="B1404" s="26">
         <v>1</v>
@@ -43105,7 +43171,7 @@
         <v>0</v>
       </c>
       <c r="D1404" s="28" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E1404" s="29" t="s">
         <v>769</v>
@@ -43117,12 +43183,12 @@
         <v>1</v>
       </c>
       <c r="I1404">
-        <v>0</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="1405" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1405">
-        <v>2920102</v>
+        <v>4920102</v>
       </c>
       <c r="B1405" s="26">
         <v>1</v>
@@ -43131,7 +43197,7 @@
         <v>0</v>
       </c>
       <c r="D1405" s="28" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E1405" s="29" t="s">
         <v>769</v>
@@ -43143,12 +43209,12 @@
         <v>1</v>
       </c>
       <c r="I1405">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1406" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1406">
-        <v>3920102</v>
+        <v>5920102</v>
       </c>
       <c r="B1406" s="26">
         <v>1</v>
@@ -43157,7 +43223,7 @@
         <v>0</v>
       </c>
       <c r="D1406" s="28" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E1406" s="29" t="s">
         <v>769</v>
@@ -43169,12 +43235,12 @@
         <v>1</v>
       </c>
       <c r="I1406">
-        <v>7500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1407" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1407">
-        <v>4920102</v>
+        <v>6920102</v>
       </c>
       <c r="B1407" s="26">
         <v>1</v>
@@ -43183,7 +43249,7 @@
         <v>0</v>
       </c>
       <c r="D1407" s="28" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E1407" s="29" t="s">
         <v>769</v>
@@ -43195,12 +43261,12 @@
         <v>1</v>
       </c>
       <c r="I1407">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1408" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1408">
-        <v>5920102</v>
+        <v>7920102</v>
       </c>
       <c r="B1408" s="26">
         <v>1</v>
@@ -43209,7 +43275,7 @@
         <v>0</v>
       </c>
       <c r="D1408" s="28" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E1408" s="29" t="s">
         <v>769</v>
@@ -43218,15 +43284,15 @@
         <v>10</v>
       </c>
       <c r="H1408">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1408">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1409" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1409">
-        <v>6920102</v>
+        <v>8920102</v>
       </c>
       <c r="B1409" s="26">
         <v>1</v>
@@ -43235,7 +43301,7 @@
         <v>0</v>
       </c>
       <c r="D1409" s="28" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E1409" s="29" t="s">
         <v>769</v>
@@ -43252,7 +43318,7 @@
     </row>
     <row r="1410" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1410">
-        <v>7920102</v>
+        <v>9920102</v>
       </c>
       <c r="B1410" s="26">
         <v>1</v>
@@ -43261,7 +43327,7 @@
         <v>0</v>
       </c>
       <c r="D1410" s="28" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E1410" s="29" t="s">
         <v>769</v>
@@ -43278,7 +43344,7 @@
     </row>
     <row r="1411" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1411">
-        <v>8920102</v>
+        <v>13920102</v>
       </c>
       <c r="B1411" s="26">
         <v>1</v>
@@ -43287,11 +43353,12 @@
         <v>0</v>
       </c>
       <c r="D1411" s="28" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E1411" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1411" s="28"/>
       <c r="G1411">
         <v>10</v>
       </c>
@@ -43299,12 +43366,12 @@
         <v>1</v>
       </c>
       <c r="I1411">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1412" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1412">
-        <v>9920102</v>
+        <v>14920102</v>
       </c>
       <c r="B1412" s="26">
         <v>1</v>
@@ -43313,24 +43380,25 @@
         <v>0</v>
       </c>
       <c r="D1412" s="28" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E1412" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1412" s="28"/>
       <c r="G1412">
         <v>10</v>
       </c>
       <c r="H1412">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1412">
-        <v>18000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1413" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1413">
-        <v>13920102</v>
+        <v>15920102</v>
       </c>
       <c r="B1413" s="26">
         <v>1</v>
@@ -43339,7 +43407,7 @@
         <v>0</v>
       </c>
       <c r="D1413" s="28" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E1413" s="29" t="s">
         <v>769</v>
@@ -43352,12 +43420,12 @@
         <v>1</v>
       </c>
       <c r="I1413">
-        <v>1</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1414" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1414">
-        <v>14920102</v>
+        <v>920103</v>
       </c>
       <c r="B1414" s="26">
         <v>1</v>
@@ -43366,12 +43434,11 @@
         <v>0</v>
       </c>
       <c r="D1414" s="28" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E1414" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1414" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1414">
         <v>10</v>
       </c>
@@ -43379,12 +43446,12 @@
         <v>1</v>
       </c>
       <c r="I1414">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1415" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1415">
-        <v>15920102</v>
+        <v>1920103</v>
       </c>
       <c r="B1415" s="26">
         <v>1</v>
@@ -43393,12 +43460,11 @@
         <v>0</v>
       </c>
       <c r="D1415" s="28" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E1415" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1415" s="28"/>
       <c r="G1415">
         <v>10</v>
       </c>
@@ -43406,12 +43472,12 @@
         <v>1</v>
       </c>
       <c r="I1415">
-        <v>3500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1416" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1416">
-        <v>920103</v>
+        <v>2920103</v>
       </c>
       <c r="B1416" s="26">
         <v>1</v>
@@ -43420,10 +43486,10 @@
         <v>0</v>
       </c>
       <c r="D1416" s="28" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E1416" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1416">
         <v>10</v>
@@ -43437,7 +43503,7 @@
     </row>
     <row r="1417" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1417">
-        <v>1920103</v>
+        <v>3920103</v>
       </c>
       <c r="B1417" s="26">
         <v>1</v>
@@ -43446,7 +43512,7 @@
         <v>0</v>
       </c>
       <c r="D1417" s="28" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E1417" s="29" t="s">
         <v>769</v>
@@ -43458,12 +43524,12 @@
         <v>1</v>
       </c>
       <c r="I1417">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1418" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1418">
-        <v>2920103</v>
+        <v>4920103</v>
       </c>
       <c r="B1418" s="26">
         <v>1</v>
@@ -43472,7 +43538,7 @@
         <v>0</v>
       </c>
       <c r="D1418" s="28" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E1418" s="29" t="s">
         <v>769</v>
@@ -43484,12 +43550,12 @@
         <v>1</v>
       </c>
       <c r="I1418">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1419" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1419">
-        <v>3920103</v>
+        <v>5920103</v>
       </c>
       <c r="B1419" s="26">
         <v>1</v>
@@ -43498,7 +43564,7 @@
         <v>0</v>
       </c>
       <c r="D1419" s="28" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E1419" s="29" t="s">
         <v>769</v>
@@ -43515,7 +43581,7 @@
     </row>
     <row r="1420" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1420">
-        <v>4920103</v>
+        <v>6920103</v>
       </c>
       <c r="B1420" s="26">
         <v>1</v>
@@ -43524,7 +43590,7 @@
         <v>0</v>
       </c>
       <c r="D1420" s="28" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E1420" s="29" t="s">
         <v>769</v>
@@ -43536,12 +43602,12 @@
         <v>1</v>
       </c>
       <c r="I1420">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1421" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1421">
-        <v>5920103</v>
+        <v>7920103</v>
       </c>
       <c r="B1421" s="26">
         <v>1</v>
@@ -43550,7 +43616,7 @@
         <v>0</v>
       </c>
       <c r="D1421" s="28" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E1421" s="29" t="s">
         <v>769</v>
@@ -43559,15 +43625,15 @@
         <v>10</v>
       </c>
       <c r="H1421">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1421">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1422" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1422">
-        <v>6920103</v>
+        <v>8920103</v>
       </c>
       <c r="B1422" s="26">
         <v>1</v>
@@ -43576,7 +43642,7 @@
         <v>0</v>
       </c>
       <c r="D1422" s="28" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E1422" s="29" t="s">
         <v>769</v>
@@ -43593,7 +43659,7 @@
     </row>
     <row r="1423" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1423">
-        <v>7920103</v>
+        <v>9920103</v>
       </c>
       <c r="B1423" s="26">
         <v>1</v>
@@ -43602,7 +43668,7 @@
         <v>0</v>
       </c>
       <c r="D1423" s="28" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E1423" s="29" t="s">
         <v>769</v>
@@ -43619,7 +43685,7 @@
     </row>
     <row r="1424" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1424">
-        <v>8920103</v>
+        <v>11030103</v>
       </c>
       <c r="B1424" s="26">
         <v>1</v>
@@ -43628,7 +43694,7 @@
         <v>0</v>
       </c>
       <c r="D1424" s="28" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E1424" s="29" t="s">
         <v>769</v>
@@ -43640,12 +43706,12 @@
         <v>1</v>
       </c>
       <c r="I1424">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1425" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1425">
-        <v>9920103</v>
+        <v>11920103</v>
       </c>
       <c r="B1425" s="26">
         <v>1</v>
@@ -43654,7 +43720,7 @@
         <v>0</v>
       </c>
       <c r="D1425" s="28" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E1425" s="29" t="s">
         <v>769</v>
@@ -43663,15 +43729,15 @@
         <v>10</v>
       </c>
       <c r="H1425">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1425">
-        <v>6000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1426" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1426">
-        <v>11030103</v>
+        <v>13920103</v>
       </c>
       <c r="B1426" s="26">
         <v>1</v>
@@ -43680,7 +43746,7 @@
         <v>0</v>
       </c>
       <c r="D1426" s="28" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E1426" s="29" t="s">
         <v>769</v>
@@ -43692,12 +43758,12 @@
         <v>1</v>
       </c>
       <c r="I1426">
-        <v>4000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1427" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1427">
-        <v>11920103</v>
+        <v>920093</v>
       </c>
       <c r="B1427" s="26">
         <v>1</v>
@@ -43709,7 +43775,7 @@
         <v>1069</v>
       </c>
       <c r="E1427" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1427">
         <v>10</v>
@@ -43718,12 +43784,12 @@
         <v>1</v>
       </c>
       <c r="I1427">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1428" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1428">
-        <v>13920103</v>
+        <v>1920093</v>
       </c>
       <c r="B1428" s="26">
         <v>1</v>
@@ -43744,7 +43810,554 @@
         <v>1</v>
       </c>
       <c r="I1428">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1429">
+        <v>2920093</v>
+      </c>
+      <c r="B1429" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1429">
+        <v>0</v>
+      </c>
+      <c r="D1429" s="28" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E1429" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1429">
+        <v>10</v>
+      </c>
+      <c r="H1429">
+        <v>1</v>
+      </c>
+      <c r="I1429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1430">
+        <v>3920093</v>
+      </c>
+      <c r="B1430" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1430">
+        <v>0</v>
+      </c>
+      <c r="D1430" s="28" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E1430" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1430">
+        <v>10</v>
+      </c>
+      <c r="H1430">
+        <v>1</v>
+      </c>
+      <c r="I1430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1431">
+        <v>4920093</v>
+      </c>
+      <c r="B1431" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1431">
+        <v>0</v>
+      </c>
+      <c r="D1431" s="28" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E1431" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1431">
+        <v>10</v>
+      </c>
+      <c r="H1431">
+        <v>1</v>
+      </c>
+      <c r="I1431">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1432">
+        <v>5920093</v>
+      </c>
+      <c r="B1432" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1432">
+        <v>0</v>
+      </c>
+      <c r="D1432" s="28" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E1432" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1432">
+        <v>10</v>
+      </c>
+      <c r="H1432">
+        <v>1</v>
+      </c>
+      <c r="I1432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1433">
+        <v>6920093</v>
+      </c>
+      <c r="B1433" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1433">
+        <v>0</v>
+      </c>
+      <c r="D1433" s="28" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1433" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1433">
+        <v>10</v>
+      </c>
+      <c r="H1433">
+        <v>1</v>
+      </c>
+      <c r="I1433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1434">
+        <v>7920093</v>
+      </c>
+      <c r="B1434" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1434">
+        <v>0</v>
+      </c>
+      <c r="D1434" s="28" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E1434" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1434">
+        <v>10</v>
+      </c>
+      <c r="H1434">
+        <v>2</v>
+      </c>
+      <c r="I1434">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1435">
+        <v>8920093</v>
+      </c>
+      <c r="B1435" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1435">
+        <v>0</v>
+      </c>
+      <c r="D1435" s="28" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E1435" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1435">
+        <v>10</v>
+      </c>
+      <c r="H1435">
+        <v>1</v>
+      </c>
+      <c r="I1435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1436">
+        <v>9920093</v>
+      </c>
+      <c r="B1436" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1436">
+        <v>0</v>
+      </c>
+      <c r="D1436" s="28" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E1436" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1436">
+        <v>10</v>
+      </c>
+      <c r="H1436">
+        <v>2</v>
+      </c>
+      <c r="I1436">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1437">
+        <v>14920093</v>
+      </c>
+      <c r="B1437" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1437">
+        <v>0</v>
+      </c>
+      <c r="D1437" s="28" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E1437" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1437">
+        <v>10</v>
+      </c>
+      <c r="H1437">
+        <v>1</v>
+      </c>
+      <c r="I1437">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1438">
+        <v>920094</v>
+      </c>
+      <c r="B1438" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1438">
+        <v>0</v>
+      </c>
+      <c r="D1438" s="28" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1438" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1438" s="28"/>
+      <c r="G1438">
+        <v>10</v>
+      </c>
+      <c r="H1438">
+        <v>1</v>
+      </c>
+      <c r="I1438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1439">
+        <v>820094</v>
+      </c>
+      <c r="B1439" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1439">
+        <v>0</v>
+      </c>
+      <c r="D1439" s="30" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1439" s="30" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G1439">
+        <v>10</v>
+      </c>
+      <c r="H1439">
+        <v>1</v>
+      </c>
+      <c r="I1439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1440">
+        <v>920095</v>
+      </c>
+      <c r="B1440" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1440">
+        <v>0</v>
+      </c>
+      <c r="D1440" s="28" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E1440" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1440">
+        <v>10</v>
+      </c>
+      <c r="H1440">
+        <v>1</v>
+      </c>
+      <c r="I1440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1441">
+        <v>1920095</v>
+      </c>
+      <c r="B1441" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1441">
+        <v>0</v>
+      </c>
+      <c r="D1441" s="28" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E1441" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1441">
+        <v>10</v>
+      </c>
+      <c r="H1441">
+        <v>1</v>
+      </c>
+      <c r="I1441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1442">
+        <v>2920095</v>
+      </c>
+      <c r="B1442" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1442">
+        <v>0</v>
+      </c>
+      <c r="D1442" s="28" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E1442" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1442">
+        <v>10</v>
+      </c>
+      <c r="H1442">
+        <v>1</v>
+      </c>
+      <c r="I1442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1443">
+        <v>3920095</v>
+      </c>
+      <c r="B1443" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1443">
+        <v>0</v>
+      </c>
+      <c r="D1443" s="28" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E1443" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1443">
+        <v>10</v>
+      </c>
+      <c r="H1443">
+        <v>1</v>
+      </c>
+      <c r="I1443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1444">
+        <v>4920095</v>
+      </c>
+      <c r="B1444" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1444">
+        <v>0</v>
+      </c>
+      <c r="D1444" s="28" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E1444" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1444">
+        <v>10</v>
+      </c>
+      <c r="H1444">
+        <v>1</v>
+      </c>
+      <c r="I1444">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1445">
+        <v>5920095</v>
+      </c>
+      <c r="B1445" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1445">
+        <v>0</v>
+      </c>
+      <c r="D1445" s="28" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E1445" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1445">
+        <v>10</v>
+      </c>
+      <c r="H1445">
+        <v>1</v>
+      </c>
+      <c r="I1445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1446">
+        <v>6920095</v>
+      </c>
+      <c r="B1446" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1446">
+        <v>0</v>
+      </c>
+      <c r="D1446" s="28" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E1446" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1446">
+        <v>10</v>
+      </c>
+      <c r="H1446">
+        <v>1</v>
+      </c>
+      <c r="I1446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1447">
+        <v>7920095</v>
+      </c>
+      <c r="B1447" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1447">
+        <v>0</v>
+      </c>
+      <c r="D1447" s="28" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E1447" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1447">
+        <v>10</v>
+      </c>
+      <c r="H1447">
+        <v>2</v>
+      </c>
+      <c r="I1447">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1448">
+        <v>8920095</v>
+      </c>
+      <c r="B1448" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1448">
+        <v>0</v>
+      </c>
+      <c r="D1448" s="28" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E1448" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1448">
+        <v>10</v>
+      </c>
+      <c r="H1448">
+        <v>1</v>
+      </c>
+      <c r="I1448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1449">
+        <v>9920095</v>
+      </c>
+      <c r="B1449" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1449">
+        <v>0</v>
+      </c>
+      <c r="D1449" s="28" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E1449" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1449">
+        <v>10</v>
+      </c>
+      <c r="H1449">
+        <v>2</v>
+      </c>
+      <c r="I1449">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDC3222-F148-4198-A32B-1FF0C5AF10C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B935DDD-49C7-463B-99EE-782670B693FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="1112">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3454,6 +3454,66 @@
   </si>
   <si>
     <t>爆炸火球_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>召唤火龙_获得</t>
+  </si>
+  <si>
+    <t>召唤火龙_冷却</t>
+  </si>
+  <si>
+    <t>召唤火龙_最近释放距离</t>
+  </si>
+  <si>
+    <t>召唤火龙_最远释放距离</t>
+  </si>
+  <si>
+    <t>召唤火龙_技能效果半径</t>
+  </si>
+  <si>
+    <t>召唤火龙_目标数量</t>
+  </si>
+  <si>
+    <t>召唤火龙_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>召唤火龙_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>召唤火龙_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>召唤火龙_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毁灭风暴_获得</t>
+  </si>
+  <si>
+    <t>毁灭风暴_冷却</t>
+  </si>
+  <si>
+    <t>毁灭风暴_最近释放距离</t>
+  </si>
+  <si>
+    <t>毁灭风暴_最远释放距离</t>
+  </si>
+  <si>
+    <t>毁灭风暴_技能效果半径</t>
+  </si>
+  <si>
+    <t>毁灭风暴_目标数量</t>
+  </si>
+  <si>
+    <t>毁灭风暴_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毁灭风暴_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毁灭风暴_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毁灭风暴_非主目标直接伤害系数</t>
   </si>
 </sst>
 </file>
@@ -4157,7 +4217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1449"/>
+  <dimension ref="A1:I1469"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -44358,6 +44418,466 @@
       </c>
       <c r="I1449">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1450">
+        <v>920096</v>
+      </c>
+      <c r="B1450" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1450">
+        <v>0</v>
+      </c>
+      <c r="D1450" s="28" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G1450">
+        <v>10</v>
+      </c>
+      <c r="H1450">
+        <v>1</v>
+      </c>
+      <c r="I1450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1451">
+        <v>1920096</v>
+      </c>
+      <c r="B1451" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1451">
+        <v>0</v>
+      </c>
+      <c r="D1451" s="28" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G1451">
+        <v>10</v>
+      </c>
+      <c r="H1451">
+        <v>1</v>
+      </c>
+      <c r="I1451">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1452">
+        <v>2920096</v>
+      </c>
+      <c r="B1452" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1452">
+        <v>0</v>
+      </c>
+      <c r="D1452" s="28" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G1452">
+        <v>10</v>
+      </c>
+      <c r="H1452">
+        <v>1</v>
+      </c>
+      <c r="I1452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1453">
+        <v>3920096</v>
+      </c>
+      <c r="B1453" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1453">
+        <v>0</v>
+      </c>
+      <c r="D1453" s="28" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G1453">
+        <v>10</v>
+      </c>
+      <c r="H1453">
+        <v>1</v>
+      </c>
+      <c r="I1453">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1454">
+        <v>4920096</v>
+      </c>
+      <c r="B1454" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1454">
+        <v>0</v>
+      </c>
+      <c r="D1454" s="28" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G1454">
+        <v>10</v>
+      </c>
+      <c r="H1454">
+        <v>1</v>
+      </c>
+      <c r="I1454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1455">
+        <v>5920096</v>
+      </c>
+      <c r="B1455" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1455">
+        <v>0</v>
+      </c>
+      <c r="D1455" s="28" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G1455">
+        <v>10</v>
+      </c>
+      <c r="H1455">
+        <v>1</v>
+      </c>
+      <c r="I1455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1456">
+        <v>6920096</v>
+      </c>
+      <c r="B1456" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1456">
+        <v>0</v>
+      </c>
+      <c r="D1456" s="28" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G1456">
+        <v>10</v>
+      </c>
+      <c r="H1456">
+        <v>1</v>
+      </c>
+      <c r="I1456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1457">
+        <v>7920096</v>
+      </c>
+      <c r="B1457" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1457">
+        <v>0</v>
+      </c>
+      <c r="D1457" s="28" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G1457">
+        <v>10</v>
+      </c>
+      <c r="H1457">
+        <v>2</v>
+      </c>
+      <c r="I1457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1458">
+        <v>8920096</v>
+      </c>
+      <c r="B1458" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1458">
+        <v>0</v>
+      </c>
+      <c r="D1458" s="28" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G1458">
+        <v>10</v>
+      </c>
+      <c r="H1458">
+        <v>1</v>
+      </c>
+      <c r="I1458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1459">
+        <v>9920096</v>
+      </c>
+      <c r="B1459" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1459">
+        <v>0</v>
+      </c>
+      <c r="D1459" s="28" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G1459">
+        <v>10</v>
+      </c>
+      <c r="H1459">
+        <v>2</v>
+      </c>
+      <c r="I1459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1460">
+        <v>920104</v>
+      </c>
+      <c r="B1460" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1460">
+        <v>0</v>
+      </c>
+      <c r="D1460" s="28" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G1460">
+        <v>10</v>
+      </c>
+      <c r="H1460">
+        <v>1</v>
+      </c>
+      <c r="I1460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1461">
+        <v>1920104</v>
+      </c>
+      <c r="B1461" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1461">
+        <v>0</v>
+      </c>
+      <c r="D1461" s="28" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G1461">
+        <v>10</v>
+      </c>
+      <c r="H1461">
+        <v>1</v>
+      </c>
+      <c r="I1461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1462">
+        <v>2920104</v>
+      </c>
+      <c r="B1462" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1462">
+        <v>0</v>
+      </c>
+      <c r="D1462" s="28" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G1462">
+        <v>10</v>
+      </c>
+      <c r="H1462">
+        <v>1</v>
+      </c>
+      <c r="I1462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1463">
+        <v>3920104</v>
+      </c>
+      <c r="B1463" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1463">
+        <v>0</v>
+      </c>
+      <c r="D1463" s="28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G1463">
+        <v>10</v>
+      </c>
+      <c r="H1463">
+        <v>1</v>
+      </c>
+      <c r="I1463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1464">
+        <v>4920104</v>
+      </c>
+      <c r="B1464" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1464">
+        <v>0</v>
+      </c>
+      <c r="D1464" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G1464">
+        <v>10</v>
+      </c>
+      <c r="H1464">
+        <v>1</v>
+      </c>
+      <c r="I1464">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1465">
+        <v>5920104</v>
+      </c>
+      <c r="B1465" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1465">
+        <v>0</v>
+      </c>
+      <c r="D1465" s="28" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G1465">
+        <v>10</v>
+      </c>
+      <c r="H1465">
+        <v>1</v>
+      </c>
+      <c r="I1465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1466">
+        <v>6920104</v>
+      </c>
+      <c r="B1466" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1466">
+        <v>0</v>
+      </c>
+      <c r="D1466" s="28" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G1466">
+        <v>10</v>
+      </c>
+      <c r="H1466">
+        <v>1</v>
+      </c>
+      <c r="I1466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1467">
+        <v>7920104</v>
+      </c>
+      <c r="B1467" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1467">
+        <v>0</v>
+      </c>
+      <c r="D1467" s="28" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G1467">
+        <v>10</v>
+      </c>
+      <c r="H1467">
+        <v>2</v>
+      </c>
+      <c r="I1467">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1468">
+        <v>8920104</v>
+      </c>
+      <c r="B1468" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1468">
+        <v>0</v>
+      </c>
+      <c r="D1468" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G1468">
+        <v>10</v>
+      </c>
+      <c r="H1468">
+        <v>1</v>
+      </c>
+      <c r="I1468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A1469">
+        <v>9920104</v>
+      </c>
+      <c r="B1469" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1469">
+        <v>0</v>
+      </c>
+      <c r="D1469" s="28" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G1469">
+        <v>10</v>
+      </c>
+      <c r="H1469">
+        <v>2</v>
+      </c>
+      <c r="I1469">
+        <v>12000</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="12345"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3885" uniqueCount="1114">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3369,6 +3369,12 @@
   </si>
   <si>
     <t>毁灭风暴_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毁灭风暴_技能持续时间</t>
+  </si>
+  <si>
+    <t>毁灭风暴_技能伤害或效果生效间隔</t>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S</t>
@@ -3501,14 +3507,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3774,7 +3773,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3867,12 +3866,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3892,12 +3885,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4153,13 +4140,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4168,55 +4158,58 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4225,10 +4218,10 @@
     <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4237,10 +4230,10 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4249,10 +4242,10 @@
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4261,10 +4254,10 @@
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4273,19 +4266,13 @@
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4293,80 +4280,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4719,7 +4706,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1469"/>
+  <dimension ref="A1:I1471"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -42739,7 +42726,7 @@
         <v>1</v>
       </c>
       <c r="I1365">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1366" spans="1:9">
@@ -42817,7 +42804,7 @@
         <v>1</v>
       </c>
       <c r="I1368">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1369" spans="1:9">
@@ -42895,7 +42882,7 @@
         <v>2</v>
       </c>
       <c r="I1371">
-        <v>20000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1372" spans="1:9">
@@ -42947,7 +42934,7 @@
         <v>2</v>
       </c>
       <c r="I1373">
-        <v>20000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1374" spans="1:9">
@@ -42957,6 +42944,9 @@
       <c r="B1374" s="26">
         <v>1</v>
       </c>
+      <c r="C1374">
+        <v>0</v>
+      </c>
       <c r="D1374" s="28" t="s">
         <v>976</v>
       </c>
@@ -42980,6 +42970,9 @@
       <c r="B1375" s="26">
         <v>1</v>
       </c>
+      <c r="C1375">
+        <v>0</v>
+      </c>
       <c r="D1375" s="28" t="s">
         <v>977</v>
       </c>
@@ -43003,6 +42996,9 @@
       <c r="B1376" s="26">
         <v>1</v>
       </c>
+      <c r="C1376">
+        <v>0</v>
+      </c>
       <c r="D1376" s="28" t="s">
         <v>978</v>
       </c>
@@ -43146,7 +43142,7 @@
         <v>1</v>
       </c>
       <c r="I1381">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1382" spans="1:9">
@@ -43224,7 +43220,7 @@
         <v>2</v>
       </c>
       <c r="I1384">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1385" spans="1:9">
@@ -43276,7 +43272,7 @@
         <v>2</v>
       </c>
       <c r="I1386">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1387" spans="1:9">
@@ -43302,7 +43298,7 @@
         <v>1</v>
       </c>
       <c r="I1387">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1388" spans="1:9">
@@ -43328,7 +43324,7 @@
         <v>1</v>
       </c>
       <c r="I1388">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1389" spans="1:9">
@@ -43409,7 +43405,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="1392" spans="1:9">
+    <row r="1392" ht="14" customHeight="1" spans="1:9">
       <c r="A1392">
         <v>2920101</v>
       </c>
@@ -43693,7 +43689,7 @@
         <v>1</v>
       </c>
       <c r="I1402">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1403" spans="1:9">
@@ -43745,7 +43741,7 @@
         <v>1</v>
       </c>
       <c r="I1404">
-        <v>7500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1405" spans="1:9">
@@ -43771,7 +43767,7 @@
         <v>1</v>
       </c>
       <c r="I1405">
-        <v>3000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1406" spans="1:9">
@@ -43849,7 +43845,7 @@
         <v>2</v>
       </c>
       <c r="I1408">
-        <v>18000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1409" spans="1:9">
@@ -43901,7 +43897,7 @@
         <v>2</v>
       </c>
       <c r="I1410">
-        <v>18000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1411" spans="1:9">
@@ -44112,7 +44108,7 @@
         <v>1</v>
       </c>
       <c r="I1418">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1419" spans="1:9">
@@ -44190,7 +44186,7 @@
         <v>2</v>
       </c>
       <c r="I1421">
-        <v>6000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1422" spans="1:9">
@@ -44242,7 +44238,7 @@
         <v>2</v>
       </c>
       <c r="I1423">
-        <v>6000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1424" spans="1:9">
@@ -44268,7 +44264,7 @@
         <v>1</v>
       </c>
       <c r="I1424">
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1425" spans="1:9">
@@ -44450,7 +44446,7 @@
         <v>1</v>
       </c>
       <c r="I1431">
-        <v>1350</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1432" spans="1:9">
@@ -44528,7 +44524,7 @@
         <v>2</v>
       </c>
       <c r="I1434">
-        <v>12000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1435" spans="1:9">
@@ -44580,7 +44576,7 @@
         <v>2</v>
       </c>
       <c r="I1436">
-        <v>12000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1437" spans="1:9">
@@ -44606,7 +44602,7 @@
         <v>1</v>
       </c>
       <c r="I1437">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1438" spans="1:9">
@@ -44789,7 +44785,7 @@
         <v>1</v>
       </c>
       <c r="I1444">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1445" spans="1:9">
@@ -44867,7 +44863,7 @@
         <v>2</v>
       </c>
       <c r="I1447">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1448" spans="1:9">
@@ -44919,7 +44915,7 @@
         <v>2</v>
       </c>
       <c r="I1449">
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1450" spans="1:9">
@@ -44935,6 +44931,9 @@
       <c r="D1450" s="28" t="s">
         <v>1052</v>
       </c>
+      <c r="E1450" s="29" t="s">
+        <v>767</v>
+      </c>
       <c r="G1450">
         <v>10</v>
       </c>
@@ -44958,6 +44957,9 @@
       <c r="D1451" s="28" t="s">
         <v>1053</v>
       </c>
+      <c r="E1451" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1451">
         <v>10</v>
       </c>
@@ -44965,7 +44967,7 @@
         <v>1</v>
       </c>
       <c r="I1451">
-        <v>8000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1452" spans="1:9">
@@ -44981,6 +44983,9 @@
       <c r="D1452" s="28" t="s">
         <v>1054</v>
       </c>
+      <c r="E1452" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1452">
         <v>10</v>
       </c>
@@ -45004,6 +45009,9 @@
       <c r="D1453" s="28" t="s">
         <v>1055</v>
       </c>
+      <c r="E1453" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1453">
         <v>10</v>
       </c>
@@ -45027,6 +45035,9 @@
       <c r="D1454" s="28" t="s">
         <v>1056</v>
       </c>
+      <c r="E1454" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1454">
         <v>10</v>
       </c>
@@ -45034,7 +45045,7 @@
         <v>1</v>
       </c>
       <c r="I1454">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1455" spans="1:9">
@@ -45050,6 +45061,9 @@
       <c r="D1455" s="28" t="s">
         <v>1057</v>
       </c>
+      <c r="E1455" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1455">
         <v>10</v>
       </c>
@@ -45073,6 +45087,9 @@
       <c r="D1456" s="28" t="s">
         <v>1058</v>
       </c>
+      <c r="E1456" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1456">
         <v>10</v>
       </c>
@@ -45096,6 +45113,9 @@
       <c r="D1457" s="28" t="s">
         <v>1059</v>
       </c>
+      <c r="E1457" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1457">
         <v>10</v>
       </c>
@@ -45103,7 +45123,7 @@
         <v>2</v>
       </c>
       <c r="I1457">
-        <v>0</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1458" spans="1:9">
@@ -45119,6 +45139,9 @@
       <c r="D1458" s="28" t="s">
         <v>1060</v>
       </c>
+      <c r="E1458" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1458">
         <v>10</v>
       </c>
@@ -45142,6 +45165,9 @@
       <c r="D1459" s="28" t="s">
         <v>1061</v>
       </c>
+      <c r="E1459" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1459">
         <v>10</v>
       </c>
@@ -45149,7 +45175,7 @@
         <v>2</v>
       </c>
       <c r="I1459">
-        <v>0</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1460" spans="1:9">
@@ -45165,6 +45191,9 @@
       <c r="D1460" s="28" t="s">
         <v>1062</v>
       </c>
+      <c r="E1460" s="29" t="s">
+        <v>767</v>
+      </c>
       <c r="G1460">
         <v>10</v>
       </c>
@@ -45188,6 +45217,9 @@
       <c r="D1461" s="28" t="s">
         <v>1063</v>
       </c>
+      <c r="E1461" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1461">
         <v>10</v>
       </c>
@@ -45211,6 +45243,9 @@
       <c r="D1462" s="28" t="s">
         <v>1064</v>
       </c>
+      <c r="E1462" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1462">
         <v>10</v>
       </c>
@@ -45234,6 +45269,9 @@
       <c r="D1463" s="28" t="s">
         <v>1065</v>
       </c>
+      <c r="E1463" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1463">
         <v>10</v>
       </c>
@@ -45257,6 +45295,9 @@
       <c r="D1464" s="28" t="s">
         <v>1066</v>
       </c>
+      <c r="E1464" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1464">
         <v>10</v>
       </c>
@@ -45280,6 +45321,9 @@
       <c r="D1465" s="28" t="s">
         <v>1067</v>
       </c>
+      <c r="E1465" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1465">
         <v>10</v>
       </c>
@@ -45303,6 +45347,9 @@
       <c r="D1466" s="28" t="s">
         <v>1068</v>
       </c>
+      <c r="E1466" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1466">
         <v>10</v>
       </c>
@@ -45326,6 +45373,9 @@
       <c r="D1467" s="28" t="s">
         <v>1069</v>
       </c>
+      <c r="E1467" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1467">
         <v>10</v>
       </c>
@@ -45333,7 +45383,7 @@
         <v>2</v>
       </c>
       <c r="I1467">
-        <v>12000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1468" spans="1:9">
@@ -45349,6 +45399,9 @@
       <c r="D1468" s="28" t="s">
         <v>1070</v>
       </c>
+      <c r="E1468" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1468">
         <v>10</v>
       </c>
@@ -45372,6 +45425,9 @@
       <c r="D1469" s="28" t="s">
         <v>1071</v>
       </c>
+      <c r="E1469" s="29" t="s">
+        <v>769</v>
+      </c>
       <c r="G1469">
         <v>10</v>
       </c>
@@ -45379,7 +45435,59 @@
         <v>2</v>
       </c>
       <c r="I1469">
-        <v>12000</v>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:9">
+      <c r="A1470">
+        <v>11030104</v>
+      </c>
+      <c r="B1470" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1470">
+        <v>0</v>
+      </c>
+      <c r="D1470" s="28" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E1470" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1470">
+        <v>10</v>
+      </c>
+      <c r="H1470">
+        <v>1</v>
+      </c>
+      <c r="I1470">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:9">
+      <c r="A1471">
+        <v>11920104</v>
+      </c>
+      <c r="B1471" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1471">
+        <v>0</v>
+      </c>
+      <c r="D1471" s="28" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E1471" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1471">
+        <v>10</v>
+      </c>
+      <c r="H1471">
+        <v>1</v>
+      </c>
+      <c r="I1471">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -45444,7 +45552,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -45456,10 +45564,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -45473,90 +45581,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1090</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1092</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1093</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1096</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1097</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -45567,7 +45675,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -45588,7 +45696,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -45600,7 +45708,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45611,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -45652,7 +45760,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -45693,7 +45801,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -45714,7 +45822,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -45726,7 +45834,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -45737,7 +45845,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -45758,7 +45866,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -45770,7 +45878,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -45781,7 +45889,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -45802,7 +45910,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -3762,12 +3762,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -45071,7 +45071,7 @@
         <v>1</v>
       </c>
       <c r="I1455">
-        <v>0</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="1456" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3885" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3887" uniqueCount="1115">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3273,6 +3273,9 @@
   </si>
   <si>
     <t>散射_弹道数量</t>
+  </si>
+  <si>
+    <t>散射_技能等级</t>
   </si>
   <si>
     <t>毁天灭地被动_获得</t>
@@ -3762,12 +3765,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4706,7 +4709,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1471"/>
+  <dimension ref="A1:I1472"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -44607,7 +44610,7 @@
     </row>
     <row r="1438" spans="1:9">
       <c r="A1438">
-        <v>920094</v>
+        <v>13920093</v>
       </c>
       <c r="B1438" s="26">
         <v>1</v>
@@ -44619,7 +44622,7 @@
         <v>1040</v>
       </c>
       <c r="E1438" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1438" s="28"/>
       <c r="G1438">
@@ -44629,12 +44632,12 @@
         <v>1</v>
       </c>
       <c r="I1438">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1439" spans="1:9">
       <c r="A1439">
-        <v>820094</v>
+        <v>920094</v>
       </c>
       <c r="B1439" s="26">
         <v>1</v>
@@ -44642,12 +44645,13 @@
       <c r="C1439">
         <v>0</v>
       </c>
-      <c r="D1439" s="30" t="s">
+      <c r="D1439" s="28" t="s">
         <v>1041</v>
       </c>
-      <c r="E1439" s="30" t="s">
-        <v>1041</v>
-      </c>
+      <c r="E1439" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1439" s="28"/>
       <c r="G1439">
         <v>10</v>
       </c>
@@ -44660,7 +44664,7 @@
     </row>
     <row r="1440" spans="1:9">
       <c r="A1440">
-        <v>920095</v>
+        <v>820094</v>
       </c>
       <c r="B1440" s="26">
         <v>1</v>
@@ -44668,11 +44672,11 @@
       <c r="C1440">
         <v>0</v>
       </c>
-      <c r="D1440" s="28" t="s">
+      <c r="D1440" s="30" t="s">
         <v>1042</v>
       </c>
-      <c r="E1440" s="29" t="s">
-        <v>767</v>
+      <c r="E1440" s="30" t="s">
+        <v>1042</v>
       </c>
       <c r="G1440">
         <v>10</v>
@@ -44686,7 +44690,7 @@
     </row>
     <row r="1441" spans="1:9">
       <c r="A1441">
-        <v>1920095</v>
+        <v>920095</v>
       </c>
       <c r="B1441" s="26">
         <v>1</v>
@@ -44698,7 +44702,7 @@
         <v>1043</v>
       </c>
       <c r="E1441" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1441">
         <v>10</v>
@@ -44712,7 +44716,7 @@
     </row>
     <row r="1442" spans="1:9">
       <c r="A1442">
-        <v>2920095</v>
+        <v>1920095</v>
       </c>
       <c r="B1442" s="26">
         <v>1</v>
@@ -44738,7 +44742,7 @@
     </row>
     <row r="1443" spans="1:9">
       <c r="A1443">
-        <v>3920095</v>
+        <v>2920095</v>
       </c>
       <c r="B1443" s="26">
         <v>1</v>
@@ -44764,7 +44768,7 @@
     </row>
     <row r="1444" spans="1:9">
       <c r="A1444">
-        <v>4920095</v>
+        <v>3920095</v>
       </c>
       <c r="B1444" s="26">
         <v>1</v>
@@ -44785,12 +44789,12 @@
         <v>1</v>
       </c>
       <c r="I1444">
-        <v>1600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1445" spans="1:9">
       <c r="A1445">
-        <v>5920095</v>
+        <v>4920095</v>
       </c>
       <c r="B1445" s="26">
         <v>1</v>
@@ -44811,12 +44815,12 @@
         <v>1</v>
       </c>
       <c r="I1445">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1446" spans="1:9">
       <c r="A1446">
-        <v>6920095</v>
+        <v>5920095</v>
       </c>
       <c r="B1446" s="26">
         <v>1</v>
@@ -44842,7 +44846,7 @@
     </row>
     <row r="1447" spans="1:9">
       <c r="A1447">
-        <v>7920095</v>
+        <v>6920095</v>
       </c>
       <c r="B1447" s="26">
         <v>1</v>
@@ -44860,15 +44864,15 @@
         <v>10</v>
       </c>
       <c r="H1447">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1447">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1448" spans="1:9">
       <c r="A1448">
-        <v>8920095</v>
+        <v>7920095</v>
       </c>
       <c r="B1448" s="26">
         <v>1</v>
@@ -44886,15 +44890,15 @@
         <v>10</v>
       </c>
       <c r="H1448">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1448">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1449" spans="1:9">
       <c r="A1449">
-        <v>9920095</v>
+        <v>8920095</v>
       </c>
       <c r="B1449" s="26">
         <v>1</v>
@@ -44912,15 +44916,15 @@
         <v>10</v>
       </c>
       <c r="H1449">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1449">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1450" spans="1:9">
       <c r="A1450">
-        <v>920096</v>
+        <v>9920095</v>
       </c>
       <c r="B1450" s="26">
         <v>1</v>
@@ -44932,21 +44936,21 @@
         <v>1052</v>
       </c>
       <c r="E1450" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1450">
         <v>10</v>
       </c>
       <c r="H1450">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1450">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1451" spans="1:9">
       <c r="A1451">
-        <v>1920096</v>
+        <v>920096</v>
       </c>
       <c r="B1451" s="26">
         <v>1</v>
@@ -44958,7 +44962,7 @@
         <v>1053</v>
       </c>
       <c r="E1451" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1451">
         <v>10</v>
@@ -44967,12 +44971,12 @@
         <v>1</v>
       </c>
       <c r="I1451">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1452" spans="1:9">
       <c r="A1452">
-        <v>2920096</v>
+        <v>1920096</v>
       </c>
       <c r="B1452" s="26">
         <v>1</v>
@@ -44993,12 +44997,12 @@
         <v>1</v>
       </c>
       <c r="I1452">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1453" spans="1:9">
       <c r="A1453">
-        <v>3920096</v>
+        <v>2920096</v>
       </c>
       <c r="B1453" s="26">
         <v>1</v>
@@ -45019,12 +45023,12 @@
         <v>1</v>
       </c>
       <c r="I1453">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1454" spans="1:9">
       <c r="A1454">
-        <v>4920096</v>
+        <v>3920096</v>
       </c>
       <c r="B1454" s="26">
         <v>1</v>
@@ -45045,12 +45049,12 @@
         <v>1</v>
       </c>
       <c r="I1454">
-        <v>3500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1455" spans="1:9">
       <c r="A1455">
-        <v>5920096</v>
+        <v>4920096</v>
       </c>
       <c r="B1455" s="26">
         <v>1</v>
@@ -45071,12 +45075,12 @@
         <v>1</v>
       </c>
       <c r="I1455">
-        <v>9999</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1456" spans="1:9">
       <c r="A1456">
-        <v>6920096</v>
+        <v>5920096</v>
       </c>
       <c r="B1456" s="26">
         <v>1</v>
@@ -45097,12 +45101,12 @@
         <v>1</v>
       </c>
       <c r="I1456">
-        <v>0</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="1457" spans="1:9">
       <c r="A1457">
-        <v>7920096</v>
+        <v>6920096</v>
       </c>
       <c r="B1457" s="26">
         <v>1</v>
@@ -45120,15 +45124,15 @@
         <v>10</v>
       </c>
       <c r="H1457">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1457">
-        <v>24000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1458" spans="1:9">
       <c r="A1458">
-        <v>8920096</v>
+        <v>7920096</v>
       </c>
       <c r="B1458" s="26">
         <v>1</v>
@@ -45146,15 +45150,15 @@
         <v>10</v>
       </c>
       <c r="H1458">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1458">
-        <v>0</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1459" spans="1:9">
       <c r="A1459">
-        <v>9920096</v>
+        <v>8920096</v>
       </c>
       <c r="B1459" s="26">
         <v>1</v>
@@ -45172,15 +45176,15 @@
         <v>10</v>
       </c>
       <c r="H1459">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1459">
-        <v>24000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1460" spans="1:9">
       <c r="A1460">
-        <v>920104</v>
+        <v>9920096</v>
       </c>
       <c r="B1460" s="26">
         <v>1</v>
@@ -45192,21 +45196,21 @@
         <v>1062</v>
       </c>
       <c r="E1460" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1460">
         <v>10</v>
       </c>
       <c r="H1460">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1460">
-        <v>0</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1461" spans="1:9">
       <c r="A1461">
-        <v>1920104</v>
+        <v>920104</v>
       </c>
       <c r="B1461" s="26">
         <v>1</v>
@@ -45218,7 +45222,7 @@
         <v>1063</v>
       </c>
       <c r="E1461" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1461">
         <v>10</v>
@@ -45232,7 +45236,7 @@
     </row>
     <row r="1462" spans="1:9">
       <c r="A1462">
-        <v>2920104</v>
+        <v>1920104</v>
       </c>
       <c r="B1462" s="26">
         <v>1</v>
@@ -45258,7 +45262,7 @@
     </row>
     <row r="1463" spans="1:9">
       <c r="A1463">
-        <v>3920104</v>
+        <v>2920104</v>
       </c>
       <c r="B1463" s="26">
         <v>1</v>
@@ -45284,7 +45288,7 @@
     </row>
     <row r="1464" spans="1:9">
       <c r="A1464">
-        <v>4920104</v>
+        <v>3920104</v>
       </c>
       <c r="B1464" s="26">
         <v>1</v>
@@ -45305,12 +45309,12 @@
         <v>1</v>
       </c>
       <c r="I1464">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1465" spans="1:9">
       <c r="A1465">
-        <v>5920104</v>
+        <v>4920104</v>
       </c>
       <c r="B1465" s="26">
         <v>1</v>
@@ -45331,12 +45335,12 @@
         <v>1</v>
       </c>
       <c r="I1465">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1466" spans="1:9">
       <c r="A1466">
-        <v>6920104</v>
+        <v>5920104</v>
       </c>
       <c r="B1466" s="26">
         <v>1</v>
@@ -45362,7 +45366,7 @@
     </row>
     <row r="1467" spans="1:9">
       <c r="A1467">
-        <v>7920104</v>
+        <v>6920104</v>
       </c>
       <c r="B1467" s="26">
         <v>1</v>
@@ -45380,15 +45384,15 @@
         <v>10</v>
       </c>
       <c r="H1467">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1467">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1468" spans="1:9">
       <c r="A1468">
-        <v>8920104</v>
+        <v>7920104</v>
       </c>
       <c r="B1468" s="26">
         <v>1</v>
@@ -45406,15 +45410,15 @@
         <v>10</v>
       </c>
       <c r="H1468">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1468">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1469" spans="1:9">
       <c r="A1469">
-        <v>9920104</v>
+        <v>8920104</v>
       </c>
       <c r="B1469" s="26">
         <v>1</v>
@@ -45432,15 +45436,15 @@
         <v>10</v>
       </c>
       <c r="H1469">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1469">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1470" spans="1:9">
       <c r="A1470">
-        <v>11030104</v>
+        <v>9920104</v>
       </c>
       <c r="B1470" s="26">
         <v>1</v>
@@ -45458,15 +45462,15 @@
         <v>10</v>
       </c>
       <c r="H1470">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1470">
-        <v>8000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1471" spans="1:9">
       <c r="A1471">
-        <v>11920104</v>
+        <v>11030104</v>
       </c>
       <c r="B1471" s="26">
         <v>1</v>
@@ -45487,6 +45491,32 @@
         <v>1</v>
       </c>
       <c r="I1471">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:9">
+      <c r="A1472">
+        <v>11920104</v>
+      </c>
+      <c r="B1472" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1472">
+        <v>0</v>
+      </c>
+      <c r="D1472" s="28" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E1472" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1472">
+        <v>10</v>
+      </c>
+      <c r="H1472">
+        <v>1</v>
+      </c>
+      <c r="I1472">
         <v>1000</v>
       </c>
     </row>
@@ -45552,7 +45582,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -45564,10 +45594,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -45581,90 +45611,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1091</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1094</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1096</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1097</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1099</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -45675,7 +45705,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -45696,7 +45726,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -45708,7 +45738,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45719,7 +45749,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -45760,7 +45790,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -45801,7 +45831,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -45822,7 +45852,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -45834,7 +45864,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -45845,7 +45875,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -45866,7 +45896,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -45878,7 +45908,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -45889,7 +45919,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -45910,7 +45940,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -42781,7 +42781,7 @@
         <v>1</v>
       </c>
       <c r="I1367">
-        <v>10000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1368" spans="1:9">
@@ -42807,7 +42807,7 @@
         <v>1</v>
       </c>
       <c r="I1368">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1369" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -11,7 +11,7 @@
     <sheet name="maze_attribute_formula_v8" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1348</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_attribute_v8!$A$2:$I$1349</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3887" uniqueCount="1115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3891" uniqueCount="1117">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2657,6 +2657,9 @@
     <t>电弧_非主目标直接伤害系数</t>
   </si>
   <si>
+    <t>电弧_技能等级</t>
+  </si>
+  <si>
     <t>电弧_释放角度</t>
   </si>
   <si>
@@ -3159,6 +3162,9 @@
   </si>
   <si>
     <t>火焰溅射_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>火焰溅射_技能等级</t>
   </si>
   <si>
     <t>火焰溅射_释放角度</t>
@@ -4709,7 +4715,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1472"/>
+  <dimension ref="A1:I1474"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -38855,7 +38861,7 @@
     </row>
     <row r="1220" spans="1:9">
       <c r="A1220">
-        <v>16920051</v>
+        <v>13920051</v>
       </c>
       <c r="B1220" s="26">
         <v>1</v>
@@ -38877,12 +38883,12 @@
         <v>1</v>
       </c>
       <c r="I1220">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1221" spans="1:9">
       <c r="A1221">
-        <v>920052</v>
+        <v>16920051</v>
       </c>
       <c r="B1221" s="26">
         <v>1</v>
@@ -38894,8 +38900,9 @@
         <v>835</v>
       </c>
       <c r="E1221" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1221" s="28"/>
       <c r="G1221">
         <v>10</v>
       </c>
@@ -38903,12 +38910,12 @@
         <v>1</v>
       </c>
       <c r="I1221">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1222" spans="1:9">
       <c r="A1222">
-        <v>1920052</v>
+        <v>920052</v>
       </c>
       <c r="B1222" s="26">
         <v>1</v>
@@ -38920,7 +38927,7 @@
         <v>836</v>
       </c>
       <c r="E1222" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1222">
         <v>10</v>
@@ -38929,12 +38936,12 @@
         <v>1</v>
       </c>
       <c r="I1222">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1223" spans="1:9">
       <c r="A1223">
-        <v>2920052</v>
+        <v>1920052</v>
       </c>
       <c r="B1223" s="26">
         <v>1</v>
@@ -38955,12 +38962,12 @@
         <v>1</v>
       </c>
       <c r="I1223">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1224" spans="1:9">
       <c r="A1224">
-        <v>3920052</v>
+        <v>2920052</v>
       </c>
       <c r="B1224" s="26">
         <v>1</v>
@@ -38986,7 +38993,7 @@
     </row>
     <row r="1225" spans="1:9">
       <c r="A1225">
-        <v>4920052</v>
+        <v>3920052</v>
       </c>
       <c r="B1225" s="26">
         <v>1</v>
@@ -39012,7 +39019,7 @@
     </row>
     <row r="1226" spans="1:9">
       <c r="A1226">
-        <v>5920052</v>
+        <v>4920052</v>
       </c>
       <c r="B1226" s="26">
         <v>1</v>
@@ -39033,12 +39040,12 @@
         <v>1</v>
       </c>
       <c r="I1226">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1227" spans="1:9">
       <c r="A1227">
-        <v>6920052</v>
+        <v>5920052</v>
       </c>
       <c r="B1227" s="26">
         <v>1</v>
@@ -39059,12 +39066,12 @@
         <v>1</v>
       </c>
       <c r="I1227">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1228" spans="1:9">
       <c r="A1228">
-        <v>7920052</v>
+        <v>6920052</v>
       </c>
       <c r="B1228" s="26">
         <v>1</v>
@@ -39082,15 +39089,15 @@
         <v>10</v>
       </c>
       <c r="H1228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1228">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1229" spans="1:9">
       <c r="A1229">
-        <v>8920052</v>
+        <v>7920052</v>
       </c>
       <c r="B1229" s="26">
         <v>1</v>
@@ -39108,15 +39115,15 @@
         <v>10</v>
       </c>
       <c r="H1229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1229">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1230" spans="1:9">
       <c r="A1230">
-        <v>9920052</v>
+        <v>8920052</v>
       </c>
       <c r="B1230" s="26">
         <v>1</v>
@@ -39134,15 +39141,15 @@
         <v>10</v>
       </c>
       <c r="H1230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1230">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1231" spans="1:9">
       <c r="A1231">
-        <v>14920052</v>
+        <v>9920052</v>
       </c>
       <c r="B1231" s="26">
         <v>1</v>
@@ -39156,20 +39163,19 @@
       <c r="E1231" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1231" s="28"/>
       <c r="G1231">
         <v>10</v>
       </c>
       <c r="H1231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1231">
-        <v>12</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1232" spans="1:9">
       <c r="A1232">
-        <v>15920052</v>
+        <v>14920052</v>
       </c>
       <c r="B1232" s="26">
         <v>1</v>
@@ -39191,12 +39197,12 @@
         <v>1</v>
       </c>
       <c r="I1232">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1233" spans="1:9">
       <c r="A1233">
-        <v>16920052</v>
+        <v>15920052</v>
       </c>
       <c r="B1233" s="26">
         <v>1</v>
@@ -39218,12 +39224,12 @@
         <v>1</v>
       </c>
       <c r="I1233">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1234" spans="1:9">
       <c r="A1234">
-        <v>72005201</v>
+        <v>16920052</v>
       </c>
       <c r="B1234" s="26">
         <v>1</v>
@@ -39242,42 +39248,42 @@
         <v>10</v>
       </c>
       <c r="H1234">
+        <v>1</v>
+      </c>
+      <c r="I1234">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:9">
+      <c r="A1235">
+        <v>72005201</v>
+      </c>
+      <c r="B1235" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1235">
+        <v>0</v>
+      </c>
+      <c r="D1235" s="28" t="s">
+        <v>849</v>
+      </c>
+      <c r="E1235" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1235" s="28"/>
+      <c r="G1235">
+        <v>10</v>
+      </c>
+      <c r="H1235">
         <v>2</v>
       </c>
-      <c r="I1234">
+      <c r="I1235">
         <v>2000</v>
-      </c>
-    </row>
-    <row r="1235" spans="1:9">
-      <c r="A1235" s="26">
-        <v>7000301</v>
-      </c>
-      <c r="B1235" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1235" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1235" s="27" t="s">
-        <v>849</v>
-      </c>
-      <c r="E1235" s="26" t="s">
-        <v>850</v>
-      </c>
-      <c r="F1235" s="4"/>
-      <c r="G1235" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1235" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1235" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="1236" spans="1:9">
       <c r="A1236" s="26">
-        <v>7000302</v>
+        <v>7000301</v>
       </c>
       <c r="B1236" s="26">
         <v>1</v>
@@ -39286,10 +39292,10 @@
         <v>0</v>
       </c>
       <c r="D1236" s="27" t="s">
+        <v>850</v>
+      </c>
+      <c r="E1236" s="26" t="s">
         <v>851</v>
-      </c>
-      <c r="E1236" s="26" t="s">
-        <v>850</v>
       </c>
       <c r="F1236" s="4"/>
       <c r="G1236" s="26">
@@ -39304,7 +39310,7 @@
     </row>
     <row r="1237" spans="1:9">
       <c r="A1237" s="26">
-        <v>7000303</v>
+        <v>7000302</v>
       </c>
       <c r="B1237" s="26">
         <v>1</v>
@@ -39316,7 +39322,7 @@
         <v>852</v>
       </c>
       <c r="E1237" s="26" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F1237" s="4"/>
       <c r="G1237" s="26">
@@ -39331,7 +39337,7 @@
     </row>
     <row r="1238" spans="1:9">
       <c r="A1238" s="26">
-        <v>7000304</v>
+        <v>7000303</v>
       </c>
       <c r="B1238" s="26">
         <v>1</v>
@@ -39343,7 +39349,7 @@
         <v>853</v>
       </c>
       <c r="E1238" s="26" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F1238" s="4"/>
       <c r="G1238" s="26">
@@ -39358,7 +39364,7 @@
     </row>
     <row r="1239" spans="1:9">
       <c r="A1239" s="26">
-        <v>7000305</v>
+        <v>7000304</v>
       </c>
       <c r="B1239" s="26">
         <v>1</v>
@@ -39370,7 +39376,7 @@
         <v>854</v>
       </c>
       <c r="E1239" s="26" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F1239" s="4"/>
       <c r="G1239" s="26">
@@ -39380,12 +39386,12 @@
         <v>2</v>
       </c>
       <c r="I1239" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1240" spans="1:9">
-      <c r="A1240" s="30">
-        <v>7000311</v>
+      <c r="A1240" s="26">
+        <v>7000305</v>
       </c>
       <c r="B1240" s="26">
         <v>1</v>
@@ -39397,22 +39403,22 @@
         <v>855</v>
       </c>
       <c r="E1240" s="26" t="s">
-        <v>856</v>
-      </c>
-      <c r="F1240" s="9"/>
+        <v>851</v>
+      </c>
+      <c r="F1240" s="4"/>
       <c r="G1240" s="26">
         <v>10</v>
       </c>
       <c r="H1240" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1240">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I1240" s="1">
+        <v>10000</v>
       </c>
     </row>
     <row r="1241" spans="1:9">
       <c r="A1241" s="30">
-        <v>7000312</v>
+        <v>7000311</v>
       </c>
       <c r="B1241" s="26">
         <v>1</v>
@@ -39421,10 +39427,10 @@
         <v>0</v>
       </c>
       <c r="D1241" s="27" t="s">
+        <v>856</v>
+      </c>
+      <c r="E1241" s="26" t="s">
         <v>857</v>
-      </c>
-      <c r="E1241" s="26" t="s">
-        <v>856</v>
       </c>
       <c r="F1241" s="9"/>
       <c r="G1241" s="26">
@@ -39439,7 +39445,7 @@
     </row>
     <row r="1242" spans="1:9">
       <c r="A1242" s="30">
-        <v>7000313</v>
+        <v>7000312</v>
       </c>
       <c r="B1242" s="26">
         <v>1</v>
@@ -39451,7 +39457,7 @@
         <v>858</v>
       </c>
       <c r="E1242" s="26" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F1242" s="9"/>
       <c r="G1242" s="26">
@@ -39466,7 +39472,7 @@
     </row>
     <row r="1243" spans="1:9">
       <c r="A1243" s="30">
-        <v>7000314</v>
+        <v>7000313</v>
       </c>
       <c r="B1243" s="26">
         <v>1</v>
@@ -39478,7 +39484,7 @@
         <v>859</v>
       </c>
       <c r="E1243" s="26" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F1243" s="9"/>
       <c r="G1243" s="26">
@@ -39492,25 +39498,26 @@
       </c>
     </row>
     <row r="1244" spans="1:9">
-      <c r="A1244">
-        <v>920061</v>
+      <c r="A1244" s="30">
+        <v>7000314</v>
       </c>
       <c r="B1244" s="26">
         <v>1</v>
       </c>
-      <c r="C1244">
-        <v>0</v>
-      </c>
-      <c r="D1244" s="28" t="s">
+      <c r="C1244" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1244" s="27" t="s">
         <v>860</v>
       </c>
-      <c r="E1244" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1244">
-        <v>10</v>
-      </c>
-      <c r="H1244">
+      <c r="E1244" s="26" t="s">
+        <v>857</v>
+      </c>
+      <c r="F1244" s="9"/>
+      <c r="G1244" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1244" s="26">
         <v>1</v>
       </c>
       <c r="I1244">
@@ -39519,7 +39526,7 @@
     </row>
     <row r="1245" spans="1:9">
       <c r="A1245">
-        <v>1920061</v>
+        <v>920061</v>
       </c>
       <c r="B1245" s="26">
         <v>1</v>
@@ -39531,7 +39538,7 @@
         <v>861</v>
       </c>
       <c r="E1245" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1245">
         <v>10</v>
@@ -39540,12 +39547,12 @@
         <v>1</v>
       </c>
       <c r="I1245">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1246" spans="1:9">
       <c r="A1246">
-        <v>2920061</v>
+        <v>1920061</v>
       </c>
       <c r="B1246" s="26">
         <v>1</v>
@@ -39566,12 +39573,12 @@
         <v>1</v>
       </c>
       <c r="I1246">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1247" spans="1:9">
       <c r="A1247">
-        <v>3920061</v>
+        <v>2920061</v>
       </c>
       <c r="B1247" s="26">
         <v>1</v>
@@ -39592,12 +39599,12 @@
         <v>1</v>
       </c>
       <c r="I1247">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1248" spans="1:9">
       <c r="A1248">
-        <v>4920061</v>
+        <v>3920061</v>
       </c>
       <c r="B1248" s="26">
         <v>1</v>
@@ -39618,12 +39625,12 @@
         <v>1</v>
       </c>
       <c r="I1248">
-        <v>1700</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1249" spans="1:9">
       <c r="A1249">
-        <v>5920061</v>
+        <v>4920061</v>
       </c>
       <c r="B1249" s="26">
         <v>1</v>
@@ -39644,12 +39651,12 @@
         <v>1</v>
       </c>
       <c r="I1249">
-        <v>0</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1250" spans="1:9">
       <c r="A1250">
-        <v>6920061</v>
+        <v>5920061</v>
       </c>
       <c r="B1250" s="26">
         <v>1</v>
@@ -39675,7 +39682,7 @@
     </row>
     <row r="1251" spans="1:9">
       <c r="A1251">
-        <v>7920061</v>
+        <v>6920061</v>
       </c>
       <c r="B1251" s="26">
         <v>1</v>
@@ -39693,15 +39700,15 @@
         <v>10</v>
       </c>
       <c r="H1251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1251">
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1252" spans="1:9">
       <c r="A1252">
-        <v>8920061</v>
+        <v>7920061</v>
       </c>
       <c r="B1252" s="26">
         <v>1</v>
@@ -39719,15 +39726,15 @@
         <v>10</v>
       </c>
       <c r="H1252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1252">
-        <v>0</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1253" spans="1:9">
       <c r="A1253">
-        <v>9920061</v>
+        <v>8920061</v>
       </c>
       <c r="B1253" s="26">
         <v>1</v>
@@ -39745,15 +39752,15 @@
         <v>10</v>
       </c>
       <c r="H1253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1253">
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1254" spans="1:9">
       <c r="A1254">
-        <v>10920061</v>
+        <v>9920061</v>
       </c>
       <c r="B1254" s="26">
         <v>1</v>
@@ -39767,20 +39774,19 @@
       <c r="E1254" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1254" s="28"/>
       <c r="G1254">
         <v>10</v>
       </c>
       <c r="H1254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1254">
-        <v>3000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1255" spans="1:9">
       <c r="A1255">
-        <v>11920061</v>
+        <v>10920061</v>
       </c>
       <c r="B1255" s="26">
         <v>1</v>
@@ -39802,12 +39808,12 @@
         <v>1</v>
       </c>
       <c r="I1255">
-        <v>700</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1256" spans="1:9">
       <c r="A1256">
-        <v>13920061</v>
+        <v>11920061</v>
       </c>
       <c r="B1256" s="26">
         <v>1</v>
@@ -39829,12 +39835,12 @@
         <v>1</v>
       </c>
       <c r="I1256">
-        <v>1</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1257" spans="1:9">
       <c r="A1257">
-        <v>14920061</v>
+        <v>13920061</v>
       </c>
       <c r="B1257" s="26">
         <v>1</v>
@@ -39861,7 +39867,7 @@
     </row>
     <row r="1258" spans="1:9">
       <c r="A1258">
-        <v>15920061</v>
+        <v>14920061</v>
       </c>
       <c r="B1258" s="26">
         <v>1</v>
@@ -39883,12 +39889,12 @@
         <v>1</v>
       </c>
       <c r="I1258">
-        <v>3000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1259" spans="1:9">
       <c r="A1259">
-        <v>16920061</v>
+        <v>15920061</v>
       </c>
       <c r="B1259" s="26">
         <v>1</v>
@@ -39910,12 +39916,12 @@
         <v>1</v>
       </c>
       <c r="I1259">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1260" spans="1:9">
       <c r="A1260">
-        <v>1920062</v>
+        <v>16920061</v>
       </c>
       <c r="B1260" s="26">
         <v>1</v>
@@ -39942,7 +39948,7 @@
     </row>
     <row r="1261" spans="1:9">
       <c r="A1261">
-        <v>4920062</v>
+        <v>1920062</v>
       </c>
       <c r="B1261" s="26">
         <v>1</v>
@@ -39964,12 +39970,12 @@
         <v>1</v>
       </c>
       <c r="I1261">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1262" spans="1:9">
       <c r="A1262">
-        <v>17920061</v>
+        <v>4920062</v>
       </c>
       <c r="B1262" s="26">
         <v>1</v>
@@ -39991,12 +39997,12 @@
         <v>1</v>
       </c>
       <c r="I1262">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1263" spans="1:9">
       <c r="A1263">
-        <v>18920061</v>
+        <v>17920061</v>
       </c>
       <c r="B1263" s="26">
         <v>1</v>
@@ -40018,12 +40024,12 @@
         <v>1</v>
       </c>
       <c r="I1263">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1264" spans="1:9">
       <c r="A1264">
-        <v>19920061</v>
+        <v>18920061</v>
       </c>
       <c r="B1264" s="26">
         <v>1</v>
@@ -40042,15 +40048,15 @@
         <v>10</v>
       </c>
       <c r="H1264">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1264">
-        <v>20000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1265" spans="1:9">
       <c r="A1265">
-        <v>20920061</v>
+        <v>19920061</v>
       </c>
       <c r="B1265" s="26">
         <v>1</v>
@@ -40069,15 +40075,15 @@
         <v>10</v>
       </c>
       <c r="H1265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1265">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1266" spans="1:9">
       <c r="A1266">
-        <v>21920061</v>
+        <v>20920061</v>
       </c>
       <c r="B1266" s="26">
         <v>1</v>
@@ -40099,39 +40105,39 @@
         <v>1</v>
       </c>
       <c r="I1266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:9">
+      <c r="A1267">
+        <v>21920061</v>
+      </c>
+      <c r="B1267" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1267">
+        <v>0</v>
+      </c>
+      <c r="D1267" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E1267" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1267" s="28"/>
+      <c r="G1267">
+        <v>10</v>
+      </c>
+      <c r="H1267">
+        <v>1</v>
+      </c>
+      <c r="I1267">
         <v>4000</v>
-      </c>
-    </row>
-    <row r="1267" spans="1:9">
-      <c r="A1267" s="26">
-        <v>5001600</v>
-      </c>
-      <c r="B1267" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1267" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1267" s="26" t="s">
-        <v>883</v>
-      </c>
-      <c r="E1267" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="F1267" s="9"/>
-      <c r="G1267" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1267" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1267">
-        <v>0</v>
       </c>
     </row>
     <row r="1268" spans="1:9">
       <c r="A1268" s="26">
-        <v>5001501</v>
+        <v>5001600</v>
       </c>
       <c r="B1268" s="26">
         <v>1</v>
@@ -40142,15 +40148,15 @@
       <c r="D1268" s="26" t="s">
         <v>884</v>
       </c>
-      <c r="E1268" s="19" t="s">
-        <v>329</v>
+      <c r="E1268" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="F1268" s="9"/>
       <c r="G1268" s="26">
         <v>10</v>
       </c>
       <c r="H1268" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1268">
         <v>0</v>
@@ -40158,7 +40164,7 @@
     </row>
     <row r="1269" spans="1:9">
       <c r="A1269" s="26">
-        <v>5001502</v>
+        <v>5001501</v>
       </c>
       <c r="B1269" s="26">
         <v>1</v>
@@ -40167,17 +40173,17 @@
         <v>0</v>
       </c>
       <c r="D1269" s="26" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E1269" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1269" s="9"/>
       <c r="G1269" s="26">
         <v>10</v>
       </c>
       <c r="H1269" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1269">
         <v>0</v>
@@ -40185,7 +40191,7 @@
     </row>
     <row r="1270" spans="1:9">
       <c r="A1270" s="26">
-        <v>5001511</v>
+        <v>5001502</v>
       </c>
       <c r="B1270" s="26">
         <v>1</v>
@@ -40197,14 +40203,14 @@
         <v>885</v>
       </c>
       <c r="E1270" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1270" s="9"/>
       <c r="G1270" s="26">
         <v>10</v>
       </c>
       <c r="H1270" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1270">
         <v>0</v>
@@ -40212,7 +40218,7 @@
     </row>
     <row r="1271" spans="1:9">
       <c r="A1271" s="26">
-        <v>5001512</v>
+        <v>5001511</v>
       </c>
       <c r="B1271" s="26">
         <v>1</v>
@@ -40221,17 +40227,17 @@
         <v>0</v>
       </c>
       <c r="D1271" s="26" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E1271" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1271" s="9"/>
       <c r="G1271" s="26">
         <v>10</v>
       </c>
       <c r="H1271" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1271">
         <v>0</v>
@@ -40239,7 +40245,7 @@
     </row>
     <row r="1272" spans="1:9">
       <c r="A1272" s="26">
-        <v>5001521</v>
+        <v>5001512</v>
       </c>
       <c r="B1272" s="26">
         <v>1</v>
@@ -40251,14 +40257,14 @@
         <v>886</v>
       </c>
       <c r="E1272" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1272" s="9"/>
       <c r="G1272" s="26">
         <v>10</v>
       </c>
       <c r="H1272" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1272">
         <v>0</v>
@@ -40266,7 +40272,7 @@
     </row>
     <row r="1273" spans="1:9">
       <c r="A1273" s="26">
-        <v>5001522</v>
+        <v>5001521</v>
       </c>
       <c r="B1273" s="26">
         <v>1</v>
@@ -40275,17 +40281,17 @@
         <v>0</v>
       </c>
       <c r="D1273" s="26" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E1273" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1273" s="9"/>
       <c r="G1273" s="26">
         <v>10</v>
       </c>
       <c r="H1273" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1273">
         <v>0</v>
@@ -40293,7 +40299,7 @@
     </row>
     <row r="1274" spans="1:9">
       <c r="A1274" s="26">
-        <v>5001800</v>
+        <v>5001522</v>
       </c>
       <c r="B1274" s="26">
         <v>1</v>
@@ -40304,9 +40310,10 @@
       <c r="D1274" s="26" t="s">
         <v>887</v>
       </c>
-      <c r="E1274" s="26" t="s">
-        <v>243</v>
-      </c>
+      <c r="E1274" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1274" s="9"/>
       <c r="G1274" s="26">
         <v>10</v>
       </c>
@@ -40319,7 +40326,7 @@
     </row>
     <row r="1275" spans="1:9">
       <c r="A1275" s="26">
-        <v>5001701</v>
+        <v>5001800</v>
       </c>
       <c r="B1275" s="26">
         <v>1</v>
@@ -40330,14 +40337,14 @@
       <c r="D1275" s="26" t="s">
         <v>888</v>
       </c>
-      <c r="E1275" s="19" t="s">
-        <v>889</v>
+      <c r="E1275" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="G1275" s="26">
         <v>10</v>
       </c>
       <c r="H1275" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1275">
         <v>0</v>
@@ -40345,7 +40352,7 @@
     </row>
     <row r="1276" spans="1:9">
       <c r="A1276" s="26">
-        <v>5001702</v>
+        <v>5001701</v>
       </c>
       <c r="B1276" s="26">
         <v>1</v>
@@ -40354,7 +40361,7 @@
         <v>0</v>
       </c>
       <c r="D1276" s="26" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E1276" s="19" t="s">
         <v>890</v>
@@ -40371,7 +40378,7 @@
     </row>
     <row r="1277" spans="1:9">
       <c r="A1277" s="26">
-        <v>5001705</v>
+        <v>5001702</v>
       </c>
       <c r="B1277" s="26">
         <v>1</v>
@@ -40380,16 +40387,16 @@
         <v>0</v>
       </c>
       <c r="D1277" s="26" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E1277" s="19" t="s">
-        <v>327</v>
+        <v>891</v>
       </c>
       <c r="G1277" s="26">
         <v>10</v>
       </c>
       <c r="H1277" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1277">
         <v>0</v>
@@ -40397,7 +40404,7 @@
     </row>
     <row r="1278" spans="1:9">
       <c r="A1278" s="26">
-        <v>5001706</v>
+        <v>5001705</v>
       </c>
       <c r="B1278" s="26">
         <v>1</v>
@@ -40406,16 +40413,16 @@
         <v>0</v>
       </c>
       <c r="D1278" s="26" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E1278" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G1278" s="26">
         <v>10</v>
       </c>
       <c r="H1278" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1278">
         <v>0</v>
@@ -40423,7 +40430,7 @@
     </row>
     <row r="1279" spans="1:9">
       <c r="A1279" s="26">
-        <v>5001711</v>
+        <v>5001706</v>
       </c>
       <c r="B1279" s="26">
         <v>1</v>
@@ -40432,10 +40439,10 @@
         <v>0</v>
       </c>
       <c r="D1279" s="26" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E1279" s="19" t="s">
-        <v>889</v>
+        <v>329</v>
       </c>
       <c r="G1279" s="26">
         <v>10</v>
@@ -40449,7 +40456,7 @@
     </row>
     <row r="1280" spans="1:9">
       <c r="A1280" s="26">
-        <v>5001712</v>
+        <v>5001711</v>
       </c>
       <c r="B1280" s="26">
         <v>1</v>
@@ -40458,7 +40465,7 @@
         <v>0</v>
       </c>
       <c r="D1280" s="26" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E1280" s="19" t="s">
         <v>890</v>
@@ -40475,7 +40482,7 @@
     </row>
     <row r="1281" spans="1:9">
       <c r="A1281" s="26">
-        <v>5001715</v>
+        <v>5001712</v>
       </c>
       <c r="B1281" s="26">
         <v>1</v>
@@ -40484,16 +40491,16 @@
         <v>0</v>
       </c>
       <c r="D1281" s="26" t="s">
+        <v>892</v>
+      </c>
+      <c r="E1281" s="19" t="s">
         <v>891</v>
       </c>
-      <c r="E1281" s="19" t="s">
-        <v>327</v>
-      </c>
       <c r="G1281" s="26">
         <v>10</v>
       </c>
       <c r="H1281" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1281">
         <v>0</v>
@@ -40501,51 +40508,51 @@
     </row>
     <row r="1282" spans="1:9">
       <c r="A1282" s="26">
+        <v>5001715</v>
+      </c>
+      <c r="B1282" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1282" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1282" s="26" t="s">
+        <v>892</v>
+      </c>
+      <c r="E1282" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1282" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1282" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:9">
+      <c r="A1283" s="26">
         <v>5001716</v>
       </c>
-      <c r="B1282" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1282" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1282" s="26" t="s">
-        <v>891</v>
-      </c>
-      <c r="E1282" s="19" t="s">
+      <c r="B1283" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1283" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1283" s="26" t="s">
+        <v>892</v>
+      </c>
+      <c r="E1283" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="G1282" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1282" s="26">
+      <c r="G1283" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1283" s="26">
         <v>2</v>
-      </c>
-      <c r="I1282">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1283" spans="1:9">
-      <c r="A1283">
-        <v>920071</v>
-      </c>
-      <c r="B1283" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1283">
-        <v>0</v>
-      </c>
-      <c r="D1283" s="28" t="s">
-        <v>892</v>
-      </c>
-      <c r="E1283" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1283">
-        <v>10</v>
-      </c>
-      <c r="H1283">
-        <v>1</v>
       </c>
       <c r="I1283">
         <v>0</v>
@@ -40553,7 +40560,7 @@
     </row>
     <row r="1284" spans="1:9">
       <c r="A1284">
-        <v>1920071</v>
+        <v>920071</v>
       </c>
       <c r="B1284" s="26">
         <v>1</v>
@@ -40565,7 +40572,7 @@
         <v>893</v>
       </c>
       <c r="E1284" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1284">
         <v>10</v>
@@ -40579,7 +40586,7 @@
     </row>
     <row r="1285" spans="1:9">
       <c r="A1285">
-        <v>2920071</v>
+        <v>1920071</v>
       </c>
       <c r="B1285" s="26">
         <v>1</v>
@@ -40605,7 +40612,7 @@
     </row>
     <row r="1286" spans="1:9">
       <c r="A1286">
-        <v>3920071</v>
+        <v>2920071</v>
       </c>
       <c r="B1286" s="26">
         <v>1</v>
@@ -40631,7 +40638,7 @@
     </row>
     <row r="1287" spans="1:9">
       <c r="A1287">
-        <v>4920071</v>
+        <v>3920071</v>
       </c>
       <c r="B1287" s="26">
         <v>1</v>
@@ -40652,12 +40659,12 @@
         <v>1</v>
       </c>
       <c r="I1287">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1288" spans="1:9">
       <c r="A1288">
-        <v>5920071</v>
+        <v>4920071</v>
       </c>
       <c r="B1288" s="26">
         <v>1</v>
@@ -40678,12 +40685,12 @@
         <v>1</v>
       </c>
       <c r="I1288">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1289" spans="1:9">
       <c r="A1289">
-        <v>6920071</v>
+        <v>5920071</v>
       </c>
       <c r="B1289" s="26">
         <v>1</v>
@@ -40709,7 +40716,7 @@
     </row>
     <row r="1290" spans="1:9">
       <c r="A1290">
-        <v>7920071</v>
+        <v>6920071</v>
       </c>
       <c r="B1290" s="26">
         <v>1</v>
@@ -40727,15 +40734,15 @@
         <v>10</v>
       </c>
       <c r="H1290">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1290">
-        <v>18000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1291" spans="1:9">
       <c r="A1291">
-        <v>8920071</v>
+        <v>7920071</v>
       </c>
       <c r="B1291" s="26">
         <v>1</v>
@@ -40753,15 +40760,15 @@
         <v>10</v>
       </c>
       <c r="H1291">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1291">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1292" spans="1:9">
       <c r="A1292">
-        <v>9920071</v>
+        <v>8920071</v>
       </c>
       <c r="B1292" s="26">
         <v>1</v>
@@ -40779,15 +40786,15 @@
         <v>10</v>
       </c>
       <c r="H1292">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1292">
-        <v>18000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1293" spans="1:9">
       <c r="A1293">
-        <v>13920071</v>
+        <v>9920071</v>
       </c>
       <c r="B1293" s="26">
         <v>1</v>
@@ -40805,15 +40812,15 @@
         <v>10</v>
       </c>
       <c r="H1293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1293">
-        <v>1</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1294" spans="1:9">
       <c r="A1294">
-        <v>920072</v>
+        <v>13920071</v>
       </c>
       <c r="B1294" s="26">
         <v>1</v>
@@ -40825,9 +40832,8 @@
         <v>903</v>
       </c>
       <c r="E1294" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1294" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1294">
         <v>10</v>
       </c>
@@ -40835,12 +40841,12 @@
         <v>1</v>
       </c>
       <c r="I1294">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1295" spans="1:9">
       <c r="A1295">
-        <v>820072</v>
+        <v>920072</v>
       </c>
       <c r="B1295" s="26">
         <v>1</v>
@@ -40848,12 +40854,13 @@
       <c r="C1295">
         <v>0</v>
       </c>
-      <c r="D1295" s="30" t="s">
+      <c r="D1295" s="28" t="s">
         <v>904</v>
       </c>
-      <c r="E1295" s="30" t="s">
-        <v>904</v>
-      </c>
+      <c r="E1295" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1295" s="28"/>
       <c r="G1295">
         <v>10</v>
       </c>
@@ -40866,7 +40873,7 @@
     </row>
     <row r="1296" spans="1:9">
       <c r="A1296">
-        <v>920081</v>
+        <v>820072</v>
       </c>
       <c r="B1296" s="26">
         <v>1</v>
@@ -40874,11 +40881,11 @@
       <c r="C1296">
         <v>0</v>
       </c>
-      <c r="D1296" s="28" t="s">
+      <c r="D1296" s="30" t="s">
         <v>905</v>
       </c>
-      <c r="E1296" s="29" t="s">
-        <v>767</v>
+      <c r="E1296" s="30" t="s">
+        <v>905</v>
       </c>
       <c r="G1296">
         <v>10</v>
@@ -40892,7 +40899,7 @@
     </row>
     <row r="1297" spans="1:9">
       <c r="A1297">
-        <v>1920081</v>
+        <v>920081</v>
       </c>
       <c r="B1297" s="26">
         <v>1</v>
@@ -40904,7 +40911,7 @@
         <v>906</v>
       </c>
       <c r="E1297" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1297">
         <v>10</v>
@@ -40913,12 +40920,12 @@
         <v>1</v>
       </c>
       <c r="I1297">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1298" spans="1:9">
       <c r="A1298">
-        <v>2920081</v>
+        <v>1920081</v>
       </c>
       <c r="B1298" s="26">
         <v>1</v>
@@ -40939,12 +40946,12 @@
         <v>1</v>
       </c>
       <c r="I1298">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1299" spans="1:9">
       <c r="A1299">
-        <v>3920081</v>
+        <v>2920081</v>
       </c>
       <c r="B1299" s="26">
         <v>1</v>
@@ -40970,7 +40977,7 @@
     </row>
     <row r="1300" spans="1:9">
       <c r="A1300">
-        <v>4920081</v>
+        <v>3920081</v>
       </c>
       <c r="B1300" s="26">
         <v>1</v>
@@ -40991,12 +40998,12 @@
         <v>1</v>
       </c>
       <c r="I1300">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1301" spans="1:9">
       <c r="A1301">
-        <v>5920081</v>
+        <v>4920081</v>
       </c>
       <c r="B1301" s="26">
         <v>1</v>
@@ -41017,12 +41024,12 @@
         <v>1</v>
       </c>
       <c r="I1301">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1302" spans="1:9">
       <c r="A1302">
-        <v>6920081</v>
+        <v>5920081</v>
       </c>
       <c r="B1302" s="26">
         <v>1</v>
@@ -41048,7 +41055,7 @@
     </row>
     <row r="1303" spans="1:9">
       <c r="A1303">
-        <v>7920081</v>
+        <v>6920081</v>
       </c>
       <c r="B1303" s="26">
         <v>1</v>
@@ -41066,15 +41073,15 @@
         <v>10</v>
       </c>
       <c r="H1303">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1303">
-        <v>16000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1304" spans="1:9">
       <c r="A1304">
-        <v>8920081</v>
+        <v>7920081</v>
       </c>
       <c r="B1304" s="26">
         <v>1</v>
@@ -41092,15 +41099,15 @@
         <v>10</v>
       </c>
       <c r="H1304">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1304">
-        <v>0</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1305" spans="1:9">
       <c r="A1305">
-        <v>9920081</v>
+        <v>8920081</v>
       </c>
       <c r="B1305" s="26">
         <v>1</v>
@@ -41118,15 +41125,15 @@
         <v>10</v>
       </c>
       <c r="H1305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1305">
-        <v>16000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1306" spans="1:9">
       <c r="A1306">
-        <v>10920081</v>
+        <v>9920081</v>
       </c>
       <c r="B1306" s="26">
         <v>1</v>
@@ -41140,20 +41147,19 @@
       <c r="E1306" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1306" s="28"/>
       <c r="G1306">
         <v>10</v>
       </c>
       <c r="H1306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1306">
-        <v>3000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1307" spans="1:9">
       <c r="A1307">
-        <v>11920081</v>
+        <v>10920081</v>
       </c>
       <c r="B1307" s="26">
         <v>1</v>
@@ -41180,7 +41186,7 @@
     </row>
     <row r="1308" spans="1:9">
       <c r="A1308">
-        <v>13920081</v>
+        <v>11920081</v>
       </c>
       <c r="B1308" s="26">
         <v>1</v>
@@ -41202,12 +41208,12 @@
         <v>1</v>
       </c>
       <c r="I1308">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
       <c r="A1309">
-        <v>14920081</v>
+        <v>13920081</v>
       </c>
       <c r="B1309" s="26">
         <v>1</v>
@@ -41234,7 +41240,7 @@
     </row>
     <row r="1310" spans="1:9">
       <c r="A1310">
-        <v>920083</v>
+        <v>14920081</v>
       </c>
       <c r="B1310" s="26">
         <v>1</v>
@@ -41246,8 +41252,9 @@
         <v>919</v>
       </c>
       <c r="E1310" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1310" s="28"/>
       <c r="G1310">
         <v>10</v>
       </c>
@@ -41260,7 +41267,7 @@
     </row>
     <row r="1311" spans="1:9">
       <c r="A1311">
-        <v>14920083</v>
+        <v>920083</v>
       </c>
       <c r="B1311" s="26">
         <v>1</v>
@@ -41272,9 +41279,8 @@
         <v>920</v>
       </c>
       <c r="E1311" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1311" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1311">
         <v>10</v>
       </c>
@@ -41286,8 +41292,8 @@
       </c>
     </row>
     <row r="1312" spans="1:9">
-      <c r="A1312" s="31">
-        <v>920082</v>
+      <c r="A1312">
+        <v>14920083</v>
       </c>
       <c r="B1312" s="26">
         <v>1</v>
@@ -41299,7 +41305,7 @@
         <v>921</v>
       </c>
       <c r="E1312" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1312" s="28"/>
       <c r="G1312">
@@ -41309,12 +41315,12 @@
         <v>1</v>
       </c>
       <c r="I1312">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1313" spans="1:9">
-      <c r="A1313" s="30">
-        <v>820082</v>
+      <c r="A1313" s="31">
+        <v>920082</v>
       </c>
       <c r="B1313" s="26">
         <v>1</v>
@@ -41322,12 +41328,13 @@
       <c r="C1313">
         <v>0</v>
       </c>
-      <c r="D1313" s="30" t="s">
+      <c r="D1313" s="28" t="s">
         <v>922</v>
       </c>
-      <c r="E1313" s="30" t="s">
-        <v>922</v>
-      </c>
+      <c r="E1313" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1313" s="28"/>
       <c r="G1313">
         <v>10</v>
       </c>
@@ -41340,7 +41347,7 @@
     </row>
     <row r="1314" spans="1:9">
       <c r="A1314" s="30">
-        <v>820083</v>
+        <v>820082</v>
       </c>
       <c r="B1314" s="26">
         <v>1</v>
@@ -41365,8 +41372,8 @@
       </c>
     </row>
     <row r="1315" spans="1:9">
-      <c r="A1315">
-        <v>920074</v>
+      <c r="A1315" s="30">
+        <v>820083</v>
       </c>
       <c r="B1315" s="26">
         <v>1</v>
@@ -41374,11 +41381,11 @@
       <c r="C1315">
         <v>0</v>
       </c>
-      <c r="D1315" s="28" t="s">
+      <c r="D1315" s="30" t="s">
         <v>924</v>
       </c>
-      <c r="E1315" s="29" t="s">
-        <v>767</v>
+      <c r="E1315" s="30" t="s">
+        <v>924</v>
       </c>
       <c r="G1315">
         <v>10</v>
@@ -41392,7 +41399,7 @@
     </row>
     <row r="1316" spans="1:9">
       <c r="A1316">
-        <v>3920074</v>
+        <v>920074</v>
       </c>
       <c r="B1316" s="26">
         <v>1</v>
@@ -41404,9 +41411,8 @@
         <v>925</v>
       </c>
       <c r="E1316" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1316" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1316">
         <v>10</v>
       </c>
@@ -41414,12 +41420,12 @@
         <v>1</v>
       </c>
       <c r="I1316">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1317" spans="1:9">
       <c r="A1317">
-        <v>14920074</v>
+        <v>3920074</v>
       </c>
       <c r="B1317" s="26">
         <v>1</v>
@@ -41441,12 +41447,12 @@
         <v>1</v>
       </c>
       <c r="I1317">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1318" spans="1:9">
       <c r="A1318">
-        <v>16920074</v>
+        <v>14920074</v>
       </c>
       <c r="B1318" s="26">
         <v>1</v>
@@ -41465,15 +41471,15 @@
         <v>10</v>
       </c>
       <c r="H1318">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1318">
-        <v>10000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1319" spans="1:9">
       <c r="A1319">
-        <v>17920074</v>
+        <v>16920074</v>
       </c>
       <c r="B1319" s="26">
         <v>1</v>
@@ -41495,12 +41501,12 @@
         <v>2</v>
       </c>
       <c r="I1319">
-        <v>2000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1320" spans="1:9">
       <c r="A1320">
-        <v>18920074</v>
+        <v>17920074</v>
       </c>
       <c r="B1320" s="26">
         <v>1</v>
@@ -41522,12 +41528,12 @@
         <v>2</v>
       </c>
       <c r="I1320">
-        <v>10000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1321" spans="1:9">
       <c r="A1321">
-        <v>920073</v>
+        <v>18920074</v>
       </c>
       <c r="B1321" s="26">
         <v>1</v>
@@ -41539,22 +41545,22 @@
         <v>930</v>
       </c>
       <c r="E1321" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="F1321" s="28"/>
       <c r="G1321">
         <v>10</v>
       </c>
       <c r="H1321">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1321">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1322" spans="1:9">
       <c r="A1322">
-        <v>820073</v>
+        <v>920073</v>
       </c>
       <c r="B1322" s="26">
         <v>1</v>
@@ -41562,12 +41568,13 @@
       <c r="C1322">
         <v>0</v>
       </c>
-      <c r="D1322" s="30" t="s">
+      <c r="D1322" s="28" t="s">
         <v>931</v>
       </c>
-      <c r="E1322" s="30" t="s">
-        <v>931</v>
-      </c>
+      <c r="E1322" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1322" s="28"/>
       <c r="G1322">
         <v>10</v>
       </c>
@@ -41580,7 +41587,7 @@
     </row>
     <row r="1323" spans="1:9">
       <c r="A1323">
-        <v>920084</v>
+        <v>820073</v>
       </c>
       <c r="B1323" s="26">
         <v>1</v>
@@ -41588,11 +41595,11 @@
       <c r="C1323">
         <v>0</v>
       </c>
-      <c r="D1323" s="28" t="s">
+      <c r="D1323" s="30" t="s">
         <v>932</v>
       </c>
-      <c r="E1323" s="29" t="s">
-        <v>767</v>
+      <c r="E1323" s="30" t="s">
+        <v>932</v>
       </c>
       <c r="G1323">
         <v>10</v>
@@ -41606,7 +41613,7 @@
     </row>
     <row r="1324" spans="1:9">
       <c r="A1324">
-        <v>1920084</v>
+        <v>920084</v>
       </c>
       <c r="B1324" s="26">
         <v>1</v>
@@ -41618,7 +41625,7 @@
         <v>933</v>
       </c>
       <c r="E1324" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1324">
         <v>10</v>
@@ -41627,12 +41634,12 @@
         <v>1</v>
       </c>
       <c r="I1324">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1325" spans="1:9">
       <c r="A1325">
-        <v>2920084</v>
+        <v>1920084</v>
       </c>
       <c r="B1325" s="26">
         <v>1</v>
@@ -41653,12 +41660,12 @@
         <v>1</v>
       </c>
       <c r="I1325">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1326" spans="1:9">
       <c r="A1326">
-        <v>3920084</v>
+        <v>2920084</v>
       </c>
       <c r="B1326" s="26">
         <v>1</v>
@@ -41684,7 +41691,7 @@
     </row>
     <row r="1327" spans="1:9">
       <c r="A1327">
-        <v>4920084</v>
+        <v>3920084</v>
       </c>
       <c r="B1327" s="26">
         <v>1</v>
@@ -41705,12 +41712,12 @@
         <v>1</v>
       </c>
       <c r="I1327">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1328" spans="1:9">
       <c r="A1328">
-        <v>5920084</v>
+        <v>4920084</v>
       </c>
       <c r="B1328" s="26">
         <v>1</v>
@@ -41731,12 +41738,12 @@
         <v>1</v>
       </c>
       <c r="I1328">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1329" spans="1:9">
       <c r="A1329">
-        <v>6920084</v>
+        <v>5920084</v>
       </c>
       <c r="B1329" s="26">
         <v>1</v>
@@ -41762,7 +41769,7 @@
     </row>
     <row r="1330" spans="1:9">
       <c r="A1330">
-        <v>7920084</v>
+        <v>6920084</v>
       </c>
       <c r="B1330" s="26">
         <v>1</v>
@@ -41780,7 +41787,7 @@
         <v>10</v>
       </c>
       <c r="H1330">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1330">
         <v>0</v>
@@ -41788,7 +41795,7 @@
     </row>
     <row r="1331" spans="1:9">
       <c r="A1331">
-        <v>8920084</v>
+        <v>7920084</v>
       </c>
       <c r="B1331" s="26">
         <v>1</v>
@@ -41806,7 +41813,7 @@
         <v>10</v>
       </c>
       <c r="H1331">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1331">
         <v>0</v>
@@ -41814,7 +41821,7 @@
     </row>
     <row r="1332" spans="1:9">
       <c r="A1332">
-        <v>9920084</v>
+        <v>8920084</v>
       </c>
       <c r="B1332" s="26">
         <v>1</v>
@@ -41832,7 +41839,7 @@
         <v>10</v>
       </c>
       <c r="H1332">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1332">
         <v>0</v>
@@ -41840,7 +41847,7 @@
     </row>
     <row r="1333" spans="1:9">
       <c r="A1333">
-        <v>13920084</v>
+        <v>9920084</v>
       </c>
       <c r="B1333" s="26">
         <v>1</v>
@@ -41858,15 +41865,15 @@
         <v>10</v>
       </c>
       <c r="H1333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1333">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1334" spans="1:9">
       <c r="A1334">
-        <v>16920084</v>
+        <v>13920084</v>
       </c>
       <c r="B1334" s="26">
         <v>1</v>
@@ -41880,7 +41887,6 @@
       <c r="E1334" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1334" s="28"/>
       <c r="G1334">
         <v>10</v>
       </c>
@@ -41888,12 +41894,12 @@
         <v>1</v>
       </c>
       <c r="I1334">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1335" spans="1:9">
       <c r="A1335">
-        <v>920085</v>
+        <v>16920084</v>
       </c>
       <c r="B1335" s="26">
         <v>1</v>
@@ -41905,8 +41911,9 @@
         <v>944</v>
       </c>
       <c r="E1335" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1335" s="28"/>
       <c r="G1335">
         <v>10</v>
       </c>
@@ -41914,12 +41921,12 @@
         <v>1</v>
       </c>
       <c r="I1335">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1336" spans="1:9">
       <c r="A1336">
-        <v>1920085</v>
+        <v>920085</v>
       </c>
       <c r="B1336" s="26">
         <v>1</v>
@@ -41931,7 +41938,7 @@
         <v>945</v>
       </c>
       <c r="E1336" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1336">
         <v>10</v>
@@ -41945,7 +41952,7 @@
     </row>
     <row r="1337" spans="1:9">
       <c r="A1337">
-        <v>2920085</v>
+        <v>1920085</v>
       </c>
       <c r="B1337" s="26">
         <v>1</v>
@@ -41971,7 +41978,7 @@
     </row>
     <row r="1338" spans="1:9">
       <c r="A1338">
-        <v>3920085</v>
+        <v>2920085</v>
       </c>
       <c r="B1338" s="26">
         <v>1</v>
@@ -41997,7 +42004,7 @@
     </row>
     <row r="1339" spans="1:9">
       <c r="A1339">
-        <v>4920085</v>
+        <v>3920085</v>
       </c>
       <c r="B1339" s="26">
         <v>1</v>
@@ -42018,12 +42025,12 @@
         <v>1</v>
       </c>
       <c r="I1339">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1340" spans="1:9">
       <c r="A1340">
-        <v>5920085</v>
+        <v>4920085</v>
       </c>
       <c r="B1340" s="26">
         <v>1</v>
@@ -42044,12 +42051,12 @@
         <v>1</v>
       </c>
       <c r="I1340">
-        <v>6</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1341" spans="1:9">
       <c r="A1341">
-        <v>6920085</v>
+        <v>5920085</v>
       </c>
       <c r="B1341" s="26">
         <v>1</v>
@@ -42070,12 +42077,12 @@
         <v>1</v>
       </c>
       <c r="I1341">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1342" spans="1:9">
       <c r="A1342">
-        <v>7920085</v>
+        <v>6920085</v>
       </c>
       <c r="B1342" s="26">
         <v>1</v>
@@ -42093,15 +42100,15 @@
         <v>10</v>
       </c>
       <c r="H1342">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1342">
-        <v>18000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1343" spans="1:9">
       <c r="A1343">
-        <v>8920085</v>
+        <v>7920085</v>
       </c>
       <c r="B1343" s="26">
         <v>1</v>
@@ -42119,15 +42126,15 @@
         <v>10</v>
       </c>
       <c r="H1343">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1343">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1344" spans="1:9">
       <c r="A1344">
-        <v>9920085</v>
+        <v>8920085</v>
       </c>
       <c r="B1344" s="26">
         <v>1</v>
@@ -42145,15 +42152,15 @@
         <v>10</v>
       </c>
       <c r="H1344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1344">
-        <v>18000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1345" spans="1:9">
       <c r="A1345">
-        <v>920086</v>
+        <v>9920085</v>
       </c>
       <c r="B1345" s="26">
         <v>1</v>
@@ -42165,22 +42172,21 @@
         <v>954</v>
       </c>
       <c r="E1345" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1345" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1345">
         <v>10</v>
       </c>
       <c r="H1345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1345">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1346" spans="1:9">
       <c r="A1346">
-        <v>820086</v>
+        <v>920086</v>
       </c>
       <c r="B1346" s="26">
         <v>1</v>
@@ -42188,12 +42194,13 @@
       <c r="C1346">
         <v>0</v>
       </c>
-      <c r="D1346" s="30" t="s">
+      <c r="D1346" s="28" t="s">
         <v>955</v>
       </c>
-      <c r="E1346" s="30" t="s">
-        <v>955</v>
-      </c>
+      <c r="E1346" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1346" s="28"/>
       <c r="G1346">
         <v>10</v>
       </c>
@@ -42206,7 +42213,7 @@
     </row>
     <row r="1347" spans="1:9">
       <c r="A1347">
-        <v>8200861</v>
+        <v>820086</v>
       </c>
       <c r="B1347" s="26">
         <v>1</v>
@@ -42218,13 +42225,13 @@
         <v>956</v>
       </c>
       <c r="E1347" s="30" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G1347">
         <v>10</v>
       </c>
       <c r="H1347">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1347">
         <v>0</v>
@@ -42232,7 +42239,7 @@
     </row>
     <row r="1348" spans="1:9">
       <c r="A1348">
-        <v>990001</v>
+        <v>8200861</v>
       </c>
       <c r="B1348" s="26">
         <v>1</v>
@@ -42240,26 +42247,25 @@
       <c r="C1348">
         <v>0</v>
       </c>
-      <c r="D1348" s="28" t="s">
+      <c r="D1348" s="30" t="s">
+        <v>957</v>
+      </c>
+      <c r="E1348" s="30" t="s">
         <v>958</v>
       </c>
-      <c r="E1348" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1348" s="28"/>
       <c r="G1348">
         <v>10</v>
       </c>
       <c r="H1348">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1348">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1349" spans="1:9">
       <c r="A1349">
-        <v>890001</v>
+        <v>990001</v>
       </c>
       <c r="B1349" s="26">
         <v>1</v>
@@ -42270,9 +42276,10 @@
       <c r="D1349" s="28" t="s">
         <v>959</v>
       </c>
-      <c r="E1349" s="28" t="s">
-        <v>959</v>
-      </c>
+      <c r="E1349" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1349" s="28"/>
       <c r="G1349">
         <v>10</v>
       </c>
@@ -42280,12 +42287,12 @@
         <v>1</v>
       </c>
       <c r="I1349">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1350" spans="1:9">
       <c r="A1350">
-        <v>890011</v>
+        <v>890001</v>
       </c>
       <c r="B1350" s="26">
         <v>1</v>
@@ -42303,7 +42310,7 @@
         <v>10</v>
       </c>
       <c r="H1350">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1350">
         <v>0</v>
@@ -42311,7 +42318,7 @@
     </row>
     <row r="1351" spans="1:9">
       <c r="A1351">
-        <v>890021</v>
+        <v>890011</v>
       </c>
       <c r="B1351" s="26">
         <v>1</v>
@@ -42323,13 +42330,13 @@
         <v>961</v>
       </c>
       <c r="E1351" s="28" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G1351">
         <v>10</v>
       </c>
       <c r="H1351">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1351">
         <v>0</v>
@@ -42337,54 +42344,51 @@
     </row>
     <row r="1352" spans="1:9">
       <c r="A1352">
+        <v>890021</v>
+      </c>
+      <c r="B1352" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1352">
+        <v>0</v>
+      </c>
+      <c r="D1352" s="28" t="s">
+        <v>962</v>
+      </c>
+      <c r="E1352" s="28" t="s">
+        <v>963</v>
+      </c>
+      <c r="G1352">
+        <v>10</v>
+      </c>
+      <c r="H1352">
+        <v>1</v>
+      </c>
+      <c r="I1352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:9">
+      <c r="A1353">
         <v>890022</v>
       </c>
-      <c r="B1352" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1352">
-        <v>0</v>
-      </c>
-      <c r="D1352" s="28" t="s">
-        <v>963</v>
-      </c>
-      <c r="E1352" s="28" t="s">
+      <c r="B1353" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1353">
+        <v>0</v>
+      </c>
+      <c r="D1353" s="28" t="s">
         <v>964</v>
       </c>
-      <c r="G1352">
-        <v>10</v>
-      </c>
-      <c r="H1352">
+      <c r="E1353" s="28" t="s">
+        <v>965</v>
+      </c>
+      <c r="G1353">
+        <v>10</v>
+      </c>
+      <c r="H1353">
         <v>2</v>
-      </c>
-      <c r="I1352">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1353" spans="1:9">
-      <c r="A1353" s="26">
-        <v>5101200</v>
-      </c>
-      <c r="B1353" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1353" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1353" s="27" t="s">
-        <v>323</v>
-      </c>
-      <c r="E1353" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="F1353" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1353" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1353" s="26">
-        <v>1</v>
       </c>
       <c r="I1353">
         <v>0</v>
@@ -42392,7 +42396,7 @@
     </row>
     <row r="1354" spans="1:9">
       <c r="A1354" s="26">
-        <v>5101201</v>
+        <v>5101200</v>
       </c>
       <c r="B1354" s="26">
         <v>1</v>
@@ -42401,10 +42405,10 @@
         <v>0</v>
       </c>
       <c r="D1354" s="27" t="s">
-        <v>965</v>
+        <v>323</v>
       </c>
       <c r="E1354" s="26" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F1354" s="9" t="s">
         <v>100</v>
@@ -42413,7 +42417,7 @@
         <v>10</v>
       </c>
       <c r="H1354" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1354">
         <v>0</v>
@@ -42421,7 +42425,7 @@
     </row>
     <row r="1355" spans="1:9">
       <c r="A1355" s="26">
-        <v>5101202</v>
+        <v>5101201</v>
       </c>
       <c r="B1355" s="26">
         <v>1</v>
@@ -42433,7 +42437,7 @@
         <v>966</v>
       </c>
       <c r="E1355" s="26" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1355" s="9" t="s">
         <v>100</v>
@@ -42442,7 +42446,7 @@
         <v>10</v>
       </c>
       <c r="H1355" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1355">
         <v>0</v>
@@ -42450,7 +42454,7 @@
     </row>
     <row r="1356" spans="1:9">
       <c r="A1356" s="26">
-        <v>5101205</v>
+        <v>5101202</v>
       </c>
       <c r="B1356" s="26">
         <v>1</v>
@@ -42462,7 +42466,7 @@
         <v>967</v>
       </c>
       <c r="E1356" s="26" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="F1356" s="9" t="s">
         <v>100</v>
@@ -42479,7 +42483,7 @@
     </row>
     <row r="1357" spans="1:9">
       <c r="A1357" s="26">
-        <v>5101206</v>
+        <v>5101205</v>
       </c>
       <c r="B1357" s="26">
         <v>1</v>
@@ -42491,7 +42495,7 @@
         <v>968</v>
       </c>
       <c r="E1357" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1357" s="9" t="s">
         <v>100</v>
@@ -42500,7 +42504,7 @@
         <v>10</v>
       </c>
       <c r="H1357" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1357">
         <v>0</v>
@@ -42508,7 +42512,7 @@
     </row>
     <row r="1358" spans="1:9">
       <c r="A1358" s="26">
-        <v>5101208</v>
+        <v>5101206</v>
       </c>
       <c r="B1358" s="26">
         <v>1</v>
@@ -42520,7 +42524,7 @@
         <v>969</v>
       </c>
       <c r="E1358" s="26" t="s">
-        <v>970</v>
+        <v>329</v>
       </c>
       <c r="F1358" s="9" t="s">
         <v>100</v>
@@ -42529,7 +42533,7 @@
         <v>10</v>
       </c>
       <c r="H1358" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1358">
         <v>0</v>
@@ -42537,7 +42541,7 @@
     </row>
     <row r="1359" spans="1:9">
       <c r="A1359" s="26">
-        <v>5101211</v>
+        <v>5101208</v>
       </c>
       <c r="B1359" s="26">
         <v>1</v>
@@ -42546,11 +42550,11 @@
         <v>0</v>
       </c>
       <c r="D1359" s="27" t="s">
+        <v>970</v>
+      </c>
+      <c r="E1359" s="26" t="s">
         <v>971</v>
       </c>
-      <c r="E1359" s="26" t="s">
-        <v>245</v>
-      </c>
       <c r="F1359" s="9" t="s">
         <v>100</v>
       </c>
@@ -42558,7 +42562,7 @@
         <v>10</v>
       </c>
       <c r="H1359" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1359">
         <v>0</v>
@@ -42566,7 +42570,7 @@
     </row>
     <row r="1360" spans="1:9">
       <c r="A1360" s="26">
-        <v>5101212</v>
+        <v>5101211</v>
       </c>
       <c r="B1360" s="26">
         <v>1</v>
@@ -42578,7 +42582,7 @@
         <v>972</v>
       </c>
       <c r="E1360" s="26" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1360" s="9" t="s">
         <v>100</v>
@@ -42587,7 +42591,7 @@
         <v>10</v>
       </c>
       <c r="H1360" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1360">
         <v>0</v>
@@ -42595,7 +42599,7 @@
     </row>
     <row r="1361" spans="1:9">
       <c r="A1361" s="26">
-        <v>5101215</v>
+        <v>5101212</v>
       </c>
       <c r="B1361" s="26">
         <v>1</v>
@@ -42607,7 +42611,7 @@
         <v>973</v>
       </c>
       <c r="E1361" s="26" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="F1361" s="9" t="s">
         <v>100</v>
@@ -42624,7 +42628,7 @@
     </row>
     <row r="1362" spans="1:9">
       <c r="A1362" s="26">
-        <v>5101216</v>
+        <v>5101215</v>
       </c>
       <c r="B1362" s="26">
         <v>1</v>
@@ -42636,7 +42640,7 @@
         <v>974</v>
       </c>
       <c r="E1362" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1362" s="9" t="s">
         <v>100</v>
@@ -42645,7 +42649,7 @@
         <v>10</v>
       </c>
       <c r="H1362" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1362">
         <v>0</v>
@@ -42653,7 +42657,7 @@
     </row>
     <row r="1363" spans="1:9">
       <c r="A1363" s="26">
-        <v>5101218</v>
+        <v>5101216</v>
       </c>
       <c r="B1363" s="26">
         <v>1</v>
@@ -42665,7 +42669,7 @@
         <v>975</v>
       </c>
       <c r="E1363" s="26" t="s">
-        <v>970</v>
+        <v>329</v>
       </c>
       <c r="F1363" s="9" t="s">
         <v>100</v>
@@ -42674,32 +42678,35 @@
         <v>10</v>
       </c>
       <c r="H1363" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1363">
         <v>0</v>
       </c>
     </row>
     <row r="1364" spans="1:9">
-      <c r="A1364">
-        <v>920091</v>
+      <c r="A1364" s="26">
+        <v>5101218</v>
       </c>
       <c r="B1364" s="26">
         <v>1</v>
       </c>
-      <c r="C1364">
-        <v>0</v>
-      </c>
-      <c r="D1364" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="E1364" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1364">
-        <v>10</v>
-      </c>
-      <c r="H1364">
+      <c r="C1364" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1364" s="27" t="s">
+        <v>976</v>
+      </c>
+      <c r="E1364" s="26" t="s">
+        <v>971</v>
+      </c>
+      <c r="F1364" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1364" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1364" s="26">
         <v>1</v>
       </c>
       <c r="I1364">
@@ -42708,7 +42715,7 @@
     </row>
     <row r="1365" spans="1:9">
       <c r="A1365">
-        <v>1920091</v>
+        <v>920091</v>
       </c>
       <c r="B1365" s="26">
         <v>1</v>
@@ -42717,10 +42724,10 @@
         <v>0</v>
       </c>
       <c r="D1365" s="28" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="E1365" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1365">
         <v>10</v>
@@ -42729,12 +42736,12 @@
         <v>1</v>
       </c>
       <c r="I1365">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1366" spans="1:9">
       <c r="A1366">
-        <v>2920091</v>
+        <v>1920091</v>
       </c>
       <c r="B1366" s="26">
         <v>1</v>
@@ -42743,7 +42750,7 @@
         <v>0</v>
       </c>
       <c r="D1366" s="28" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="E1366" s="29" t="s">
         <v>769</v>
@@ -42755,12 +42762,12 @@
         <v>1</v>
       </c>
       <c r="I1366">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1367" spans="1:9">
       <c r="A1367">
-        <v>3920091</v>
+        <v>2920091</v>
       </c>
       <c r="B1367" s="26">
         <v>1</v>
@@ -42769,7 +42776,7 @@
         <v>0</v>
       </c>
       <c r="D1367" s="28" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="E1367" s="29" t="s">
         <v>769</v>
@@ -42781,12 +42788,12 @@
         <v>1</v>
       </c>
       <c r="I1367">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1368" spans="1:9">
       <c r="A1368">
-        <v>4920091</v>
+        <v>3920091</v>
       </c>
       <c r="B1368" s="26">
         <v>1</v>
@@ -42795,7 +42802,7 @@
         <v>0</v>
       </c>
       <c r="D1368" s="28" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="E1368" s="29" t="s">
         <v>769</v>
@@ -42807,12 +42814,12 @@
         <v>1</v>
       </c>
       <c r="I1368">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1369" spans="1:9">
       <c r="A1369">
-        <v>5920091</v>
+        <v>4920091</v>
       </c>
       <c r="B1369" s="26">
         <v>1</v>
@@ -42821,7 +42828,7 @@
         <v>0</v>
       </c>
       <c r="D1369" s="28" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="E1369" s="29" t="s">
         <v>769</v>
@@ -42833,12 +42840,12 @@
         <v>1</v>
       </c>
       <c r="I1369">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1370" spans="1:9">
       <c r="A1370">
-        <v>6920091</v>
+        <v>5920091</v>
       </c>
       <c r="B1370" s="26">
         <v>1</v>
@@ -42847,7 +42854,7 @@
         <v>0</v>
       </c>
       <c r="D1370" s="28" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="E1370" s="29" t="s">
         <v>769</v>
@@ -42864,7 +42871,7 @@
     </row>
     <row r="1371" spans="1:9">
       <c r="A1371">
-        <v>7920091</v>
+        <v>6920091</v>
       </c>
       <c r="B1371" s="26">
         <v>1</v>
@@ -42873,7 +42880,7 @@
         <v>0</v>
       </c>
       <c r="D1371" s="28" t="s">
-        <v>637</v>
+        <v>619</v>
       </c>
       <c r="E1371" s="29" t="s">
         <v>769</v>
@@ -42882,15 +42889,15 @@
         <v>10</v>
       </c>
       <c r="H1371">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1371">
-        <v>24000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1372" spans="1:9">
       <c r="A1372">
-        <v>8920091</v>
+        <v>7920091</v>
       </c>
       <c r="B1372" s="26">
         <v>1</v>
@@ -42899,7 +42906,7 @@
         <v>0</v>
       </c>
       <c r="D1372" s="28" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="E1372" s="29" t="s">
         <v>769</v>
@@ -42908,15 +42915,15 @@
         <v>10</v>
       </c>
       <c r="H1372">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1372">
-        <v>0</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1373" spans="1:9">
       <c r="A1373">
-        <v>9920091</v>
+        <v>8920091</v>
       </c>
       <c r="B1373" s="26">
         <v>1</v>
@@ -42925,7 +42932,7 @@
         <v>0</v>
       </c>
       <c r="D1373" s="28" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="E1373" s="29" t="s">
         <v>769</v>
@@ -42934,15 +42941,15 @@
         <v>10</v>
       </c>
       <c r="H1373">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1373">
-        <v>24000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1374" spans="1:9">
       <c r="A1374">
-        <v>13920091</v>
+        <v>9920091</v>
       </c>
       <c r="B1374" s="26">
         <v>1</v>
@@ -42951,7 +42958,7 @@
         <v>0</v>
       </c>
       <c r="D1374" s="28" t="s">
-        <v>976</v>
+        <v>671</v>
       </c>
       <c r="E1374" s="29" t="s">
         <v>769</v>
@@ -42960,15 +42967,15 @@
         <v>10</v>
       </c>
       <c r="H1374">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1374">
-        <v>1</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1375" spans="1:9">
       <c r="A1375">
-        <v>14920091</v>
+        <v>13920091</v>
       </c>
       <c r="B1375" s="26">
         <v>1</v>
@@ -42994,7 +43001,7 @@
     </row>
     <row r="1376" spans="1:9">
       <c r="A1376">
-        <v>15920091</v>
+        <v>14920091</v>
       </c>
       <c r="B1376" s="26">
         <v>1</v>
@@ -43015,12 +43022,12 @@
         <v>1</v>
       </c>
       <c r="I1376">
-        <v>200</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1377" spans="1:9">
       <c r="A1377">
-        <v>920092</v>
+        <v>15920091</v>
       </c>
       <c r="B1377" s="26">
         <v>1</v>
@@ -43032,7 +43039,7 @@
         <v>979</v>
       </c>
       <c r="E1377" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1377">
         <v>10</v>
@@ -43041,12 +43048,12 @@
         <v>1</v>
       </c>
       <c r="I1377">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1378" spans="1:9">
       <c r="A1378">
-        <v>1920092</v>
+        <v>920092</v>
       </c>
       <c r="B1378" s="26">
         <v>1</v>
@@ -43058,7 +43065,7 @@
         <v>980</v>
       </c>
       <c r="E1378" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1378">
         <v>10</v>
@@ -43072,7 +43079,7 @@
     </row>
     <row r="1379" spans="1:9">
       <c r="A1379">
-        <v>2920092</v>
+        <v>1920092</v>
       </c>
       <c r="B1379" s="26">
         <v>1</v>
@@ -43098,7 +43105,7 @@
     </row>
     <row r="1380" spans="1:9">
       <c r="A1380">
-        <v>3920092</v>
+        <v>2920092</v>
       </c>
       <c r="B1380" s="26">
         <v>1</v>
@@ -43124,7 +43131,7 @@
     </row>
     <row r="1381" spans="1:9">
       <c r="A1381">
-        <v>4920092</v>
+        <v>3920092</v>
       </c>
       <c r="B1381" s="26">
         <v>1</v>
@@ -43145,12 +43152,12 @@
         <v>1</v>
       </c>
       <c r="I1381">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1382" spans="1:9">
       <c r="A1382">
-        <v>5920092</v>
+        <v>4920092</v>
       </c>
       <c r="B1382" s="26">
         <v>1</v>
@@ -43171,12 +43178,12 @@
         <v>1</v>
       </c>
       <c r="I1382">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1383" spans="1:9">
       <c r="A1383">
-        <v>6920092</v>
+        <v>5920092</v>
       </c>
       <c r="B1383" s="26">
         <v>1</v>
@@ -43202,7 +43209,7 @@
     </row>
     <row r="1384" spans="1:9">
       <c r="A1384">
-        <v>7920092</v>
+        <v>6920092</v>
       </c>
       <c r="B1384" s="26">
         <v>1</v>
@@ -43220,15 +43227,15 @@
         <v>10</v>
       </c>
       <c r="H1384">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1384">
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1385" spans="1:9">
       <c r="A1385">
-        <v>8920092</v>
+        <v>7920092</v>
       </c>
       <c r="B1385" s="26">
         <v>1</v>
@@ -43246,15 +43253,15 @@
         <v>10</v>
       </c>
       <c r="H1385">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1385">
-        <v>0</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1386" spans="1:9">
       <c r="A1386">
-        <v>9920092</v>
+        <v>8920092</v>
       </c>
       <c r="B1386" s="26">
         <v>1</v>
@@ -43272,15 +43279,15 @@
         <v>10</v>
       </c>
       <c r="H1386">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1386">
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1387" spans="1:9">
       <c r="A1387">
-        <v>10920092</v>
+        <v>9920092</v>
       </c>
       <c r="B1387" s="26">
         <v>1</v>
@@ -43298,15 +43305,15 @@
         <v>10</v>
       </c>
       <c r="H1387">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1387">
-        <v>2000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1388" spans="1:9">
       <c r="A1388">
-        <v>11920092</v>
+        <v>10920092</v>
       </c>
       <c r="B1388" s="26">
         <v>1</v>
@@ -43327,12 +43334,12 @@
         <v>1</v>
       </c>
       <c r="I1388">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1389" spans="1:9">
       <c r="A1389">
-        <v>13920092</v>
+        <v>11920092</v>
       </c>
       <c r="B1389" s="26">
         <v>1</v>
@@ -43353,12 +43360,12 @@
         <v>1</v>
       </c>
       <c r="I1389">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1390" spans="1:9">
       <c r="A1390">
-        <v>920101</v>
+        <v>13920092</v>
       </c>
       <c r="B1390" s="26">
         <v>1</v>
@@ -43370,7 +43377,7 @@
         <v>992</v>
       </c>
       <c r="E1390" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1390">
         <v>10</v>
@@ -43379,12 +43386,12 @@
         <v>1</v>
       </c>
       <c r="I1390">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1391" spans="1:9">
       <c r="A1391">
-        <v>1920101</v>
+        <v>920101</v>
       </c>
       <c r="B1391" s="26">
         <v>1</v>
@@ -43396,7 +43403,7 @@
         <v>993</v>
       </c>
       <c r="E1391" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1391">
         <v>10</v>
@@ -43405,12 +43412,12 @@
         <v>1</v>
       </c>
       <c r="I1391">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="1392" ht="14" customHeight="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:9">
       <c r="A1392">
-        <v>2920101</v>
+        <v>1920101</v>
       </c>
       <c r="B1392" s="26">
         <v>1</v>
@@ -43431,12 +43438,12 @@
         <v>1</v>
       </c>
       <c r="I1392">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1393" spans="1:9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1393" ht="14" customHeight="1" spans="1:9">
       <c r="A1393">
-        <v>3920101</v>
+        <v>2920101</v>
       </c>
       <c r="B1393" s="26">
         <v>1</v>
@@ -43462,7 +43469,7 @@
     </row>
     <row r="1394" spans="1:9">
       <c r="A1394">
-        <v>4920101</v>
+        <v>3920101</v>
       </c>
       <c r="B1394" s="26">
         <v>1</v>
@@ -43483,12 +43490,12 @@
         <v>1</v>
       </c>
       <c r="I1394">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1395" spans="1:9">
       <c r="A1395">
-        <v>5920101</v>
+        <v>4920101</v>
       </c>
       <c r="B1395" s="26">
         <v>1</v>
@@ -43509,12 +43516,12 @@
         <v>1</v>
       </c>
       <c r="I1395">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1396" spans="1:9">
       <c r="A1396">
-        <v>6920101</v>
+        <v>5920101</v>
       </c>
       <c r="B1396" s="26">
         <v>1</v>
@@ -43540,7 +43547,7 @@
     </row>
     <row r="1397" spans="1:9">
       <c r="A1397">
-        <v>7920101</v>
+        <v>6920101</v>
       </c>
       <c r="B1397" s="26">
         <v>1</v>
@@ -43558,7 +43565,7 @@
         <v>10</v>
       </c>
       <c r="H1397">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1397">
         <v>0</v>
@@ -43566,7 +43573,7 @@
     </row>
     <row r="1398" spans="1:9">
       <c r="A1398">
-        <v>8920101</v>
+        <v>7920101</v>
       </c>
       <c r="B1398" s="26">
         <v>1</v>
@@ -43584,7 +43591,7 @@
         <v>10</v>
       </c>
       <c r="H1398">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1398">
         <v>0</v>
@@ -43592,7 +43599,7 @@
     </row>
     <row r="1399" spans="1:9">
       <c r="A1399">
-        <v>9920101</v>
+        <v>8920101</v>
       </c>
       <c r="B1399" s="26">
         <v>1</v>
@@ -43610,7 +43617,7 @@
         <v>10</v>
       </c>
       <c r="H1399">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1399">
         <v>0</v>
@@ -43618,7 +43625,7 @@
     </row>
     <row r="1400" spans="1:9">
       <c r="A1400">
-        <v>16920101</v>
+        <v>9920101</v>
       </c>
       <c r="B1400" s="26">
         <v>1</v>
@@ -43632,20 +43639,19 @@
       <c r="E1400" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1400" s="28"/>
       <c r="G1400">
         <v>10</v>
       </c>
       <c r="H1400">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1400">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1401" spans="1:9">
       <c r="A1401">
-        <v>920102</v>
+        <v>13920101</v>
       </c>
       <c r="B1401" s="26">
         <v>1</v>
@@ -43657,8 +43663,9 @@
         <v>1003</v>
       </c>
       <c r="E1401" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1401" s="28"/>
       <c r="G1401">
         <v>10</v>
       </c>
@@ -43666,12 +43673,12 @@
         <v>1</v>
       </c>
       <c r="I1401">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1402" spans="1:9">
       <c r="A1402">
-        <v>1920102</v>
+        <v>16920101</v>
       </c>
       <c r="B1402" s="26">
         <v>1</v>
@@ -43685,6 +43692,7 @@
       <c r="E1402" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1402" s="28"/>
       <c r="G1402">
         <v>10</v>
       </c>
@@ -43692,12 +43700,12 @@
         <v>1</v>
       </c>
       <c r="I1402">
-        <v>3000</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1403" spans="1:9">
       <c r="A1403">
-        <v>2920102</v>
+        <v>920102</v>
       </c>
       <c r="B1403" s="26">
         <v>1</v>
@@ -43709,7 +43717,7 @@
         <v>1005</v>
       </c>
       <c r="E1403" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1403">
         <v>10</v>
@@ -43723,7 +43731,7 @@
     </row>
     <row r="1404" spans="1:9">
       <c r="A1404">
-        <v>3920102</v>
+        <v>1920102</v>
       </c>
       <c r="B1404" s="26">
         <v>1</v>
@@ -43744,12 +43752,12 @@
         <v>1</v>
       </c>
       <c r="I1404">
-        <v>5000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1405" spans="1:9">
       <c r="A1405">
-        <v>4920102</v>
+        <v>2920102</v>
       </c>
       <c r="B1405" s="26">
         <v>1</v>
@@ -43770,12 +43778,12 @@
         <v>1</v>
       </c>
       <c r="I1405">
-        <v>1600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1406" spans="1:9">
       <c r="A1406">
-        <v>5920102</v>
+        <v>3920102</v>
       </c>
       <c r="B1406" s="26">
         <v>1</v>
@@ -43796,12 +43804,12 @@
         <v>1</v>
       </c>
       <c r="I1406">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1407" spans="1:9">
       <c r="A1407">
-        <v>6920102</v>
+        <v>4920102</v>
       </c>
       <c r="B1407" s="26">
         <v>1</v>
@@ -43822,12 +43830,12 @@
         <v>1</v>
       </c>
       <c r="I1407">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1408" spans="1:9">
       <c r="A1408">
-        <v>7920102</v>
+        <v>5920102</v>
       </c>
       <c r="B1408" s="26">
         <v>1</v>
@@ -43845,15 +43853,15 @@
         <v>10</v>
       </c>
       <c r="H1408">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1408">
-        <v>22000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1409" spans="1:9">
       <c r="A1409">
-        <v>8920102</v>
+        <v>6920102</v>
       </c>
       <c r="B1409" s="26">
         <v>1</v>
@@ -43879,7 +43887,7 @@
     </row>
     <row r="1410" spans="1:9">
       <c r="A1410">
-        <v>9920102</v>
+        <v>7920102</v>
       </c>
       <c r="B1410" s="26">
         <v>1</v>
@@ -43905,7 +43913,7 @@
     </row>
     <row r="1411" spans="1:9">
       <c r="A1411">
-        <v>13920102</v>
+        <v>8920102</v>
       </c>
       <c r="B1411" s="26">
         <v>1</v>
@@ -43919,7 +43927,6 @@
       <c r="E1411" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1411" s="28"/>
       <c r="G1411">
         <v>10</v>
       </c>
@@ -43927,12 +43934,12 @@
         <v>1</v>
       </c>
       <c r="I1411">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1412" spans="1:9">
       <c r="A1412">
-        <v>14920102</v>
+        <v>9920102</v>
       </c>
       <c r="B1412" s="26">
         <v>1</v>
@@ -43946,20 +43953,19 @@
       <c r="E1412" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1412" s="28"/>
       <c r="G1412">
         <v>10</v>
       </c>
       <c r="H1412">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1412">
-        <v>1</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1413" spans="1:9">
       <c r="A1413">
-        <v>15920102</v>
+        <v>13920102</v>
       </c>
       <c r="B1413" s="26">
         <v>1</v>
@@ -43981,12 +43987,12 @@
         <v>1</v>
       </c>
       <c r="I1413">
-        <v>3500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1414" spans="1:9">
       <c r="A1414">
-        <v>920103</v>
+        <v>14920102</v>
       </c>
       <c r="B1414" s="26">
         <v>1</v>
@@ -43998,8 +44004,9 @@
         <v>1016</v>
       </c>
       <c r="E1414" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1414" s="28"/>
       <c r="G1414">
         <v>10</v>
       </c>
@@ -44007,12 +44014,12 @@
         <v>1</v>
       </c>
       <c r="I1414">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1415" spans="1:9">
       <c r="A1415">
-        <v>1920103</v>
+        <v>15920102</v>
       </c>
       <c r="B1415" s="26">
         <v>1</v>
@@ -44026,6 +44033,7 @@
       <c r="E1415" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1415" s="28"/>
       <c r="G1415">
         <v>10</v>
       </c>
@@ -44033,12 +44041,12 @@
         <v>1</v>
       </c>
       <c r="I1415">
-        <v>100</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1416" spans="1:9">
       <c r="A1416">
-        <v>2920103</v>
+        <v>920103</v>
       </c>
       <c r="B1416" s="26">
         <v>1</v>
@@ -44050,7 +44058,7 @@
         <v>1018</v>
       </c>
       <c r="E1416" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1416">
         <v>10</v>
@@ -44064,7 +44072,7 @@
     </row>
     <row r="1417" spans="1:9">
       <c r="A1417">
-        <v>3920103</v>
+        <v>1920103</v>
       </c>
       <c r="B1417" s="26">
         <v>1</v>
@@ -44085,12 +44093,12 @@
         <v>1</v>
       </c>
       <c r="I1417">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1418" spans="1:9">
       <c r="A1418">
-        <v>4920103</v>
+        <v>2920103</v>
       </c>
       <c r="B1418" s="26">
         <v>1</v>
@@ -44111,12 +44119,12 @@
         <v>1</v>
       </c>
       <c r="I1418">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1419" spans="1:9">
       <c r="A1419">
-        <v>5920103</v>
+        <v>3920103</v>
       </c>
       <c r="B1419" s="26">
         <v>1</v>
@@ -44142,7 +44150,7 @@
     </row>
     <row r="1420" spans="1:9">
       <c r="A1420">
-        <v>6920103</v>
+        <v>4920103</v>
       </c>
       <c r="B1420" s="26">
         <v>1</v>
@@ -44163,12 +44171,12 @@
         <v>1</v>
       </c>
       <c r="I1420">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1421" spans="1:9">
       <c r="A1421">
-        <v>7920103</v>
+        <v>5920103</v>
       </c>
       <c r="B1421" s="26">
         <v>1</v>
@@ -44186,15 +44194,15 @@
         <v>10</v>
       </c>
       <c r="H1421">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1421">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1422" spans="1:9">
       <c r="A1422">
-        <v>8920103</v>
+        <v>6920103</v>
       </c>
       <c r="B1422" s="26">
         <v>1</v>
@@ -44220,7 +44228,7 @@
     </row>
     <row r="1423" spans="1:9">
       <c r="A1423">
-        <v>9920103</v>
+        <v>7920103</v>
       </c>
       <c r="B1423" s="26">
         <v>1</v>
@@ -44246,7 +44254,7 @@
     </row>
     <row r="1424" spans="1:9">
       <c r="A1424">
-        <v>11030103</v>
+        <v>8920103</v>
       </c>
       <c r="B1424" s="26">
         <v>1</v>
@@ -44267,12 +44275,12 @@
         <v>1</v>
       </c>
       <c r="I1424">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1425" spans="1:9">
       <c r="A1425">
-        <v>11920103</v>
+        <v>9920103</v>
       </c>
       <c r="B1425" s="26">
         <v>1</v>
@@ -44290,15 +44298,15 @@
         <v>10</v>
       </c>
       <c r="H1425">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1425">
-        <v>1000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1426" spans="1:9">
       <c r="A1426">
-        <v>13920103</v>
+        <v>11030103</v>
       </c>
       <c r="B1426" s="26">
         <v>1</v>
@@ -44319,12 +44327,12 @@
         <v>1</v>
       </c>
       <c r="I1426">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1427" spans="1:9">
       <c r="A1427">
-        <v>920093</v>
+        <v>11920103</v>
       </c>
       <c r="B1427" s="26">
         <v>1</v>
@@ -44336,7 +44344,7 @@
         <v>1029</v>
       </c>
       <c r="E1427" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1427">
         <v>10</v>
@@ -44345,12 +44353,12 @@
         <v>1</v>
       </c>
       <c r="I1427">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1428" spans="1:9">
       <c r="A1428">
-        <v>1920093</v>
+        <v>13920103</v>
       </c>
       <c r="B1428" s="26">
         <v>1</v>
@@ -44371,12 +44379,12 @@
         <v>1</v>
       </c>
       <c r="I1428">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1429" spans="1:9">
       <c r="A1429">
-        <v>2920093</v>
+        <v>920093</v>
       </c>
       <c r="B1429" s="26">
         <v>1</v>
@@ -44388,7 +44396,7 @@
         <v>1031</v>
       </c>
       <c r="E1429" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1429">
         <v>10</v>
@@ -44402,7 +44410,7 @@
     </row>
     <row r="1430" spans="1:9">
       <c r="A1430">
-        <v>3920093</v>
+        <v>1920093</v>
       </c>
       <c r="B1430" s="26">
         <v>1</v>
@@ -44428,7 +44436,7 @@
     </row>
     <row r="1431" spans="1:9">
       <c r="A1431">
-        <v>4920093</v>
+        <v>2920093</v>
       </c>
       <c r="B1431" s="26">
         <v>1</v>
@@ -44449,12 +44457,12 @@
         <v>1</v>
       </c>
       <c r="I1431">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1432" spans="1:9">
       <c r="A1432">
-        <v>5920093</v>
+        <v>3920093</v>
       </c>
       <c r="B1432" s="26">
         <v>1</v>
@@ -44480,7 +44488,7 @@
     </row>
     <row r="1433" spans="1:9">
       <c r="A1433">
-        <v>6920093</v>
+        <v>4920093</v>
       </c>
       <c r="B1433" s="26">
         <v>1</v>
@@ -44501,12 +44509,12 @@
         <v>1</v>
       </c>
       <c r="I1433">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1434" spans="1:9">
       <c r="A1434">
-        <v>7920093</v>
+        <v>5920093</v>
       </c>
       <c r="B1434" s="26">
         <v>1</v>
@@ -44524,15 +44532,15 @@
         <v>10</v>
       </c>
       <c r="H1434">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1434">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1435" spans="1:9">
       <c r="A1435">
-        <v>8920093</v>
+        <v>6920093</v>
       </c>
       <c r="B1435" s="26">
         <v>1</v>
@@ -44558,7 +44566,7 @@
     </row>
     <row r="1436" spans="1:9">
       <c r="A1436">
-        <v>9920093</v>
+        <v>7920093</v>
       </c>
       <c r="B1436" s="26">
         <v>1</v>
@@ -44584,7 +44592,7 @@
     </row>
     <row r="1437" spans="1:9">
       <c r="A1437">
-        <v>14920093</v>
+        <v>8920093</v>
       </c>
       <c r="B1437" s="26">
         <v>1</v>
@@ -44605,12 +44613,12 @@
         <v>1</v>
       </c>
       <c r="I1437">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1438" spans="1:9">
       <c r="A1438">
-        <v>13920093</v>
+        <v>9920093</v>
       </c>
       <c r="B1438" s="26">
         <v>1</v>
@@ -44624,20 +44632,19 @@
       <c r="E1438" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1438" s="28"/>
       <c r="G1438">
         <v>10</v>
       </c>
       <c r="H1438">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1438">
-        <v>1</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1439" spans="1:9">
       <c r="A1439">
-        <v>920094</v>
+        <v>14920093</v>
       </c>
       <c r="B1439" s="26">
         <v>1</v>
@@ -44649,9 +44656,8 @@
         <v>1041</v>
       </c>
       <c r="E1439" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1439" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1439">
         <v>10</v>
       </c>
@@ -44659,12 +44665,12 @@
         <v>1</v>
       </c>
       <c r="I1439">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1440" spans="1:9">
       <c r="A1440">
-        <v>820094</v>
+        <v>13920093</v>
       </c>
       <c r="B1440" s="26">
         <v>1</v>
@@ -44672,12 +44678,13 @@
       <c r="C1440">
         <v>0</v>
       </c>
-      <c r="D1440" s="30" t="s">
+      <c r="D1440" s="28" t="s">
         <v>1042</v>
       </c>
-      <c r="E1440" s="30" t="s">
-        <v>1042</v>
-      </c>
+      <c r="E1440" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1440" s="28"/>
       <c r="G1440">
         <v>10</v>
       </c>
@@ -44685,12 +44692,12 @@
         <v>1</v>
       </c>
       <c r="I1440">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1441" spans="1:9">
       <c r="A1441">
-        <v>920095</v>
+        <v>920094</v>
       </c>
       <c r="B1441" s="26">
         <v>1</v>
@@ -44704,6 +44711,7 @@
       <c r="E1441" s="29" t="s">
         <v>767</v>
       </c>
+      <c r="F1441" s="28"/>
       <c r="G1441">
         <v>10</v>
       </c>
@@ -44716,7 +44724,7 @@
     </row>
     <row r="1442" spans="1:9">
       <c r="A1442">
-        <v>1920095</v>
+        <v>820094</v>
       </c>
       <c r="B1442" s="26">
         <v>1</v>
@@ -44724,11 +44732,11 @@
       <c r="C1442">
         <v>0</v>
       </c>
-      <c r="D1442" s="28" t="s">
+      <c r="D1442" s="30" t="s">
         <v>1044</v>
       </c>
-      <c r="E1442" s="29" t="s">
-        <v>769</v>
+      <c r="E1442" s="30" t="s">
+        <v>1044</v>
       </c>
       <c r="G1442">
         <v>10</v>
@@ -44742,7 +44750,7 @@
     </row>
     <row r="1443" spans="1:9">
       <c r="A1443">
-        <v>2920095</v>
+        <v>920095</v>
       </c>
       <c r="B1443" s="26">
         <v>1</v>
@@ -44754,7 +44762,7 @@
         <v>1045</v>
       </c>
       <c r="E1443" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1443">
         <v>10</v>
@@ -44768,7 +44776,7 @@
     </row>
     <row r="1444" spans="1:9">
       <c r="A1444">
-        <v>3920095</v>
+        <v>1920095</v>
       </c>
       <c r="B1444" s="26">
         <v>1</v>
@@ -44794,7 +44802,7 @@
     </row>
     <row r="1445" spans="1:9">
       <c r="A1445">
-        <v>4920095</v>
+        <v>2920095</v>
       </c>
       <c r="B1445" s="26">
         <v>1</v>
@@ -44815,12 +44823,12 @@
         <v>1</v>
       </c>
       <c r="I1445">
-        <v>1600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1446" spans="1:9">
       <c r="A1446">
-        <v>5920095</v>
+        <v>3920095</v>
       </c>
       <c r="B1446" s="26">
         <v>1</v>
@@ -44846,7 +44854,7 @@
     </row>
     <row r="1447" spans="1:9">
       <c r="A1447">
-        <v>6920095</v>
+        <v>4920095</v>
       </c>
       <c r="B1447" s="26">
         <v>1</v>
@@ -44867,12 +44875,12 @@
         <v>1</v>
       </c>
       <c r="I1447">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1448" spans="1:9">
       <c r="A1448">
-        <v>7920095</v>
+        <v>5920095</v>
       </c>
       <c r="B1448" s="26">
         <v>1</v>
@@ -44890,15 +44898,15 @@
         <v>10</v>
       </c>
       <c r="H1448">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1448">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1449" spans="1:9">
       <c r="A1449">
-        <v>8920095</v>
+        <v>6920095</v>
       </c>
       <c r="B1449" s="26">
         <v>1</v>
@@ -44924,7 +44932,7 @@
     </row>
     <row r="1450" spans="1:9">
       <c r="A1450">
-        <v>9920095</v>
+        <v>7920095</v>
       </c>
       <c r="B1450" s="26">
         <v>1</v>
@@ -44950,7 +44958,7 @@
     </row>
     <row r="1451" spans="1:9">
       <c r="A1451">
-        <v>920096</v>
+        <v>8920095</v>
       </c>
       <c r="B1451" s="26">
         <v>1</v>
@@ -44962,7 +44970,7 @@
         <v>1053</v>
       </c>
       <c r="E1451" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1451">
         <v>10</v>
@@ -44976,7 +44984,7 @@
     </row>
     <row r="1452" spans="1:9">
       <c r="A1452">
-        <v>1920096</v>
+        <v>9920095</v>
       </c>
       <c r="B1452" s="26">
         <v>1</v>
@@ -44994,15 +45002,15 @@
         <v>10</v>
       </c>
       <c r="H1452">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1452">
-        <v>6000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1453" spans="1:9">
       <c r="A1453">
-        <v>2920096</v>
+        <v>920096</v>
       </c>
       <c r="B1453" s="26">
         <v>1</v>
@@ -45014,7 +45022,7 @@
         <v>1055</v>
       </c>
       <c r="E1453" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1453">
         <v>10</v>
@@ -45028,7 +45036,7 @@
     </row>
     <row r="1454" spans="1:9">
       <c r="A1454">
-        <v>3920096</v>
+        <v>1920096</v>
       </c>
       <c r="B1454" s="26">
         <v>1</v>
@@ -45049,12 +45057,12 @@
         <v>1</v>
       </c>
       <c r="I1454">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1455" spans="1:9">
       <c r="A1455">
-        <v>4920096</v>
+        <v>2920096</v>
       </c>
       <c r="B1455" s="26">
         <v>1</v>
@@ -45075,12 +45083,12 @@
         <v>1</v>
       </c>
       <c r="I1455">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1456" spans="1:9">
       <c r="A1456">
-        <v>5920096</v>
+        <v>3920096</v>
       </c>
       <c r="B1456" s="26">
         <v>1</v>
@@ -45101,12 +45109,12 @@
         <v>1</v>
       </c>
       <c r="I1456">
-        <v>9999</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1457" spans="1:9">
       <c r="A1457">
-        <v>6920096</v>
+        <v>4920096</v>
       </c>
       <c r="B1457" s="26">
         <v>1</v>
@@ -45127,12 +45135,12 @@
         <v>1</v>
       </c>
       <c r="I1457">
-        <v>0</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1458" spans="1:9">
       <c r="A1458">
-        <v>7920096</v>
+        <v>5920096</v>
       </c>
       <c r="B1458" s="26">
         <v>1</v>
@@ -45150,15 +45158,15 @@
         <v>10</v>
       </c>
       <c r="H1458">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1458">
-        <v>24000</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="1459" spans="1:9">
       <c r="A1459">
-        <v>8920096</v>
+        <v>6920096</v>
       </c>
       <c r="B1459" s="26">
         <v>1</v>
@@ -45184,7 +45192,7 @@
     </row>
     <row r="1460" spans="1:9">
       <c r="A1460">
-        <v>9920096</v>
+        <v>7920096</v>
       </c>
       <c r="B1460" s="26">
         <v>1</v>
@@ -45210,7 +45218,7 @@
     </row>
     <row r="1461" spans="1:9">
       <c r="A1461">
-        <v>920104</v>
+        <v>8920096</v>
       </c>
       <c r="B1461" s="26">
         <v>1</v>
@@ -45222,7 +45230,7 @@
         <v>1063</v>
       </c>
       <c r="E1461" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1461">
         <v>10</v>
@@ -45236,7 +45244,7 @@
     </row>
     <row r="1462" spans="1:9">
       <c r="A1462">
-        <v>1920104</v>
+        <v>9920096</v>
       </c>
       <c r="B1462" s="26">
         <v>1</v>
@@ -45254,15 +45262,15 @@
         <v>10</v>
       </c>
       <c r="H1462">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1462">
-        <v>0</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1463" spans="1:9">
       <c r="A1463">
-        <v>2920104</v>
+        <v>920104</v>
       </c>
       <c r="B1463" s="26">
         <v>1</v>
@@ -45274,7 +45282,7 @@
         <v>1065</v>
       </c>
       <c r="E1463" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1463">
         <v>10</v>
@@ -45288,7 +45296,7 @@
     </row>
     <row r="1464" spans="1:9">
       <c r="A1464">
-        <v>3920104</v>
+        <v>1920104</v>
       </c>
       <c r="B1464" s="26">
         <v>1</v>
@@ -45314,7 +45322,7 @@
     </row>
     <row r="1465" spans="1:9">
       <c r="A1465">
-        <v>4920104</v>
+        <v>2920104</v>
       </c>
       <c r="B1465" s="26">
         <v>1</v>
@@ -45335,12 +45343,12 @@
         <v>1</v>
       </c>
       <c r="I1465">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1466" spans="1:9">
       <c r="A1466">
-        <v>5920104</v>
+        <v>3920104</v>
       </c>
       <c r="B1466" s="26">
         <v>1</v>
@@ -45366,7 +45374,7 @@
     </row>
     <row r="1467" spans="1:9">
       <c r="A1467">
-        <v>6920104</v>
+        <v>4920104</v>
       </c>
       <c r="B1467" s="26">
         <v>1</v>
@@ -45387,12 +45395,12 @@
         <v>1</v>
       </c>
       <c r="I1467">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1468" spans="1:9">
       <c r="A1468">
-        <v>7920104</v>
+        <v>5920104</v>
       </c>
       <c r="B1468" s="26">
         <v>1</v>
@@ -45410,15 +45418,15 @@
         <v>10</v>
       </c>
       <c r="H1468">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1468">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1469" spans="1:9">
       <c r="A1469">
-        <v>8920104</v>
+        <v>6920104</v>
       </c>
       <c r="B1469" s="26">
         <v>1</v>
@@ -45444,7 +45452,7 @@
     </row>
     <row r="1470" spans="1:9">
       <c r="A1470">
-        <v>9920104</v>
+        <v>7920104</v>
       </c>
       <c r="B1470" s="26">
         <v>1</v>
@@ -45470,7 +45478,7 @@
     </row>
     <row r="1471" spans="1:9">
       <c r="A1471">
-        <v>11030104</v>
+        <v>8920104</v>
       </c>
       <c r="B1471" s="26">
         <v>1</v>
@@ -45491,12 +45499,12 @@
         <v>1</v>
       </c>
       <c r="I1471">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1472" spans="1:9">
       <c r="A1472">
-        <v>11920104</v>
+        <v>9920104</v>
       </c>
       <c r="B1472" s="26">
         <v>1</v>
@@ -45514,9 +45522,61 @@
         <v>10</v>
       </c>
       <c r="H1472">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1472">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:9">
+      <c r="A1473">
+        <v>11030104</v>
+      </c>
+      <c r="B1473" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1473">
+        <v>0</v>
+      </c>
+      <c r="D1473" s="28" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E1473" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1473">
+        <v>10</v>
+      </c>
+      <c r="H1473">
+        <v>1</v>
+      </c>
+      <c r="I1473">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:9">
+      <c r="A1474">
+        <v>11920104</v>
+      </c>
+      <c r="B1474" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1474">
+        <v>0</v>
+      </c>
+      <c r="D1474" s="28" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E1474" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1474">
+        <v>10</v>
+      </c>
+      <c r="H1474">
+        <v>1</v>
+      </c>
+      <c r="I1474">
         <v>1000</v>
       </c>
     </row>
@@ -45582,7 +45642,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -45594,10 +45654,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -45611,90 +45671,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1093</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1094</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1097</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1099</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1101</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -45705,7 +45765,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -45726,7 +45786,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -45738,7 +45798,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45749,7 +45809,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -45790,7 +45850,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -45831,7 +45891,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -45852,7 +45912,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -45864,7 +45924,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -45875,7 +45935,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -45896,7 +45956,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -45908,7 +45968,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -45919,7 +45979,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -45940,7 +46000,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="12375"/>
+    <workbookView windowWidth="27870" windowHeight="12225"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3895" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3897" uniqueCount="1120">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3357,6 +3357,9 @@
   </si>
   <si>
     <t>召唤火龙_召唤物数量</t>
+  </si>
+  <si>
+    <t>毁灭风暴_获取</t>
   </si>
   <si>
     <t>毁灭风暴_冷却</t>
@@ -4721,7 +4724,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1476"/>
+  <dimension ref="A1:I1477"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -45354,7 +45357,7 @@
     </row>
     <row r="1466" spans="1:9">
       <c r="A1466">
-        <v>1920104</v>
+        <v>920104</v>
       </c>
       <c r="B1466" s="26">
         <v>1</v>
@@ -45380,7 +45383,7 @@
     </row>
     <row r="1467" spans="1:9">
       <c r="A1467">
-        <v>2920104</v>
+        <v>1920104</v>
       </c>
       <c r="B1467" s="26">
         <v>1</v>
@@ -45406,7 +45409,7 @@
     </row>
     <row r="1468" spans="1:9">
       <c r="A1468">
-        <v>3920104</v>
+        <v>2920104</v>
       </c>
       <c r="B1468" s="26">
         <v>1</v>
@@ -45432,7 +45435,7 @@
     </row>
     <row r="1469" spans="1:9">
       <c r="A1469">
-        <v>4920104</v>
+        <v>3920104</v>
       </c>
       <c r="B1469" s="26">
         <v>1</v>
@@ -45453,12 +45456,12 @@
         <v>1</v>
       </c>
       <c r="I1469">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1470" spans="1:9">
       <c r="A1470">
-        <v>5920104</v>
+        <v>4920104</v>
       </c>
       <c r="B1470" s="26">
         <v>1</v>
@@ -45479,12 +45482,12 @@
         <v>1</v>
       </c>
       <c r="I1470">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1471" spans="1:9">
       <c r="A1471">
-        <v>6920104</v>
+        <v>5920104</v>
       </c>
       <c r="B1471" s="26">
         <v>1</v>
@@ -45510,7 +45513,7 @@
     </row>
     <row r="1472" spans="1:9">
       <c r="A1472">
-        <v>7920104</v>
+        <v>6920104</v>
       </c>
       <c r="B1472" s="26">
         <v>1</v>
@@ -45528,15 +45531,15 @@
         <v>10</v>
       </c>
       <c r="H1472">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1472">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1473" spans="1:9">
       <c r="A1473">
-        <v>8920104</v>
+        <v>7920104</v>
       </c>
       <c r="B1473" s="26">
         <v>1</v>
@@ -45554,15 +45557,15 @@
         <v>10</v>
       </c>
       <c r="H1473">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1473">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1474" spans="1:9">
       <c r="A1474">
-        <v>9920104</v>
+        <v>8920104</v>
       </c>
       <c r="B1474" s="26">
         <v>1</v>
@@ -45580,15 +45583,15 @@
         <v>10</v>
       </c>
       <c r="H1474">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1474">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1475" spans="1:9">
       <c r="A1475">
-        <v>11030104</v>
+        <v>9920104</v>
       </c>
       <c r="B1475" s="26">
         <v>1</v>
@@ -45606,15 +45609,15 @@
         <v>10</v>
       </c>
       <c r="H1475">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1475">
-        <v>8000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1476" spans="1:9">
       <c r="A1476">
-        <v>11920104</v>
+        <v>11030104</v>
       </c>
       <c r="B1476" s="26">
         <v>1</v>
@@ -45635,6 +45638,32 @@
         <v>1</v>
       </c>
       <c r="I1476">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:9">
+      <c r="A1477">
+        <v>11920104</v>
+      </c>
+      <c r="B1477" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1477">
+        <v>0</v>
+      </c>
+      <c r="D1477" s="28" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E1477" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1477">
+        <v>10</v>
+      </c>
+      <c r="H1477">
+        <v>1</v>
+      </c>
+      <c r="I1477">
         <v>1000</v>
       </c>
     </row>
@@ -45700,7 +45729,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -45712,10 +45741,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -45729,90 +45758,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1096</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1099</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1102</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1103</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1104</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1105</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -45823,7 +45852,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -45844,7 +45873,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -45856,7 +45885,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45867,7 +45896,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -45908,7 +45937,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -45949,7 +45978,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -45970,7 +45999,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -45982,7 +46011,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -45993,7 +46022,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -46014,7 +46043,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -46026,7 +46055,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -46037,7 +46066,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -46058,7 +46087,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27870" windowHeight="12225"/>
+    <workbookView windowHeight="12225"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -37345,7 +37345,7 @@
         <v>2</v>
       </c>
       <c r="I1161">
-        <v>14000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1162" spans="1:9">
@@ -37397,7 +37397,7 @@
         <v>2</v>
       </c>
       <c r="I1163">
-        <v>14000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1164" spans="1:9">
@@ -37502,7 +37502,7 @@
         <v>1</v>
       </c>
       <c r="I1167">
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1168" spans="1:9">
@@ -37580,7 +37580,7 @@
         <v>1</v>
       </c>
       <c r="I1170">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1171" spans="1:9">
@@ -37658,7 +37658,7 @@
         <v>2</v>
       </c>
       <c r="I1173">
-        <v>22000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1174" spans="1:9">
@@ -37710,7 +37710,7 @@
         <v>2</v>
       </c>
       <c r="I1175">
-        <v>22000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1176" spans="1:9">
@@ -37788,7 +37788,7 @@
         <v>1</v>
       </c>
       <c r="I1178">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1179" spans="1:9">
@@ -37944,7 +37944,7 @@
         <v>2</v>
       </c>
       <c r="I1184">
-        <v>18000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1185" spans="1:9">
@@ -37996,7 +37996,7 @@
         <v>2</v>
       </c>
       <c r="I1186">
-        <v>18000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1187" spans="1:9">
@@ -38446,7 +38446,7 @@
         <v>2</v>
       </c>
       <c r="I1203">
-        <v>18000</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="1204" spans="1:9">
@@ -38498,7 +38498,7 @@
         <v>2</v>
       </c>
       <c r="I1205">
-        <v>18000</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="1206" spans="1:9">
@@ -39660,7 +39660,7 @@
         <v>1</v>
       </c>
       <c r="I1249">
-        <v>1700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1250" spans="1:9">
@@ -39738,7 +39738,7 @@
         <v>2</v>
       </c>
       <c r="I1252">
-        <v>14000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1253" spans="1:9">
@@ -39790,7 +39790,7 @@
         <v>2</v>
       </c>
       <c r="I1254">
-        <v>14000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1255" spans="1:9">
@@ -40033,7 +40033,7 @@
         <v>1</v>
       </c>
       <c r="I1263">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1264" spans="1:9">
@@ -40772,7 +40772,7 @@
         <v>2</v>
       </c>
       <c r="I1291">
-        <v>18000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1292" spans="1:9">
@@ -40824,7 +40824,7 @@
         <v>2</v>
       </c>
       <c r="I1293">
-        <v>18000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1294" spans="1:9">
@@ -40955,7 +40955,7 @@
         <v>1</v>
       </c>
       <c r="I1298">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1299" spans="1:9">
@@ -41111,7 +41111,7 @@
         <v>2</v>
       </c>
       <c r="I1304">
-        <v>16000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1305" spans="1:9">
@@ -41163,7 +41163,7 @@
         <v>2</v>
       </c>
       <c r="I1306">
-        <v>16000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1307" spans="1:9">
@@ -42060,7 +42060,7 @@
         <v>1</v>
       </c>
       <c r="I1340">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1341" spans="1:9">
@@ -42138,7 +42138,7 @@
         <v>2</v>
       </c>
       <c r="I1343">
-        <v>18000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1344" spans="1:9">
@@ -42190,7 +42190,7 @@
         <v>2</v>
       </c>
       <c r="I1345">
-        <v>18000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1346" spans="1:9">
@@ -42771,7 +42771,7 @@
         <v>1</v>
       </c>
       <c r="I1366">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1367" spans="1:9">
@@ -42849,7 +42849,7 @@
         <v>1</v>
       </c>
       <c r="I1369">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1370" spans="1:9">
@@ -43265,7 +43265,7 @@
         <v>2</v>
       </c>
       <c r="I1385">
-        <v>12000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1386" spans="1:9">
@@ -43317,7 +43317,7 @@
         <v>2</v>
       </c>
       <c r="I1387">
-        <v>12000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1388" spans="1:9">
@@ -43917,7 +43917,7 @@
         <v>2</v>
       </c>
       <c r="I1410">
-        <v>22000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1411" spans="1:9">
@@ -43969,7 +43969,7 @@
         <v>2</v>
       </c>
       <c r="I1412">
-        <v>22000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1413" spans="1:9">
@@ -44180,7 +44180,7 @@
         <v>1</v>
       </c>
       <c r="I1420">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1421" spans="1:9">
@@ -44336,7 +44336,7 @@
         <v>1</v>
       </c>
       <c r="I1426">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1427" spans="1:9">
@@ -44518,7 +44518,7 @@
         <v>1</v>
       </c>
       <c r="I1433">
-        <v>1500</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1434" spans="1:9">
@@ -44596,7 +44596,7 @@
         <v>2</v>
       </c>
       <c r="I1436">
-        <v>10000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1437" spans="1:9">
@@ -44648,7 +44648,7 @@
         <v>2</v>
       </c>
       <c r="I1438">
-        <v>10000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1439" spans="1:9">
@@ -44674,7 +44674,7 @@
         <v>1</v>
       </c>
       <c r="I1439">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1440" spans="1:9">
@@ -45222,7 +45222,7 @@
         <v>2</v>
       </c>
       <c r="I1460">
-        <v>12000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1461" spans="1:9">
@@ -45274,7 +45274,7 @@
         <v>2</v>
       </c>
       <c r="I1462">
-        <v>12000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1463" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -40087,7 +40087,7 @@
         <v>2</v>
       </c>
       <c r="I1265">
-        <v>20000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1266" spans="1:9">
@@ -44596,7 +44596,7 @@
         <v>2</v>
       </c>
       <c r="I1436">
-        <v>7000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1437" spans="1:9">
@@ -44648,7 +44648,7 @@
         <v>2</v>
       </c>
       <c r="I1438">
-        <v>7000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1439" spans="1:9">
@@ -44674,7 +44674,7 @@
         <v>1</v>
       </c>
       <c r="I1439">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1440" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -43839,7 +43839,7 @@
         <v>1</v>
       </c>
       <c r="I1407">
-        <v>1600</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1408" spans="1:9">
@@ -44050,7 +44050,7 @@
         <v>1</v>
       </c>
       <c r="I1415">
-        <v>3500</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1416" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="12225"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3897" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4110" uniqueCount="1220">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3393,6 +3393,306 @@
   </si>
   <si>
     <t>毁灭风暴_技能伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>毒雾-中毒伤害系数万分比</t>
+  </si>
+  <si>
+    <t>毒雾-中毒伤害系数固定值</t>
+  </si>
+  <si>
+    <t>毒雾-中毒持续时间</t>
+  </si>
+  <si>
+    <t>毒雾-中毒的命中率</t>
+  </si>
+  <si>
+    <t>毒雾-中毒伤害结算间隔</t>
+  </si>
+  <si>
+    <t>毒刃-中毒伤害系数万分比</t>
+  </si>
+  <si>
+    <t>毒刃-中毒伤害系数固定值</t>
+  </si>
+  <si>
+    <t>毒刃-中毒持续时间</t>
+  </si>
+  <si>
+    <t>毒刃-中毒的命中率</t>
+  </si>
+  <si>
+    <t>毒刃-中毒伤害结算间隔</t>
+  </si>
+  <si>
+    <t>毒雾_获得</t>
+  </si>
+  <si>
+    <t>毒雾_冷却</t>
+  </si>
+  <si>
+    <t>毒雾_最近释放距离</t>
+  </si>
+  <si>
+    <t>毒雾_最远释放距离</t>
+  </si>
+  <si>
+    <t>毒雾_技能效果半径</t>
+  </si>
+  <si>
+    <t>毒雾_目标数量</t>
+  </si>
+  <si>
+    <t>毒雾_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒雾_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒雾_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒雾_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒雾_技能持续时间</t>
+  </si>
+  <si>
+    <t>毒雾_技能伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>毒雾_技能等级</t>
+  </si>
+  <si>
+    <t>毒雾_弹道数量</t>
+  </si>
+  <si>
+    <t>毒雾_弹道间隔时长（毫秒）</t>
+  </si>
+  <si>
+    <t>毒雾_弹道飞行速度</t>
+  </si>
+  <si>
+    <t>毒沼_获得</t>
+  </si>
+  <si>
+    <t>毒沼_冷却</t>
+  </si>
+  <si>
+    <t>毒沼_最近释放距离</t>
+  </si>
+  <si>
+    <t>毒沼_最远释放距离</t>
+  </si>
+  <si>
+    <t>毒沼_技能效果半径</t>
+  </si>
+  <si>
+    <t>毒沼_目标数量</t>
+  </si>
+  <si>
+    <t>毒沼_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒沼_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒沼_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒沼_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒沼_技能持续时间</t>
+  </si>
+  <si>
+    <t>毒沼_技能伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>毒沼_技能等级</t>
+  </si>
+  <si>
+    <t>毒雨_获得</t>
+  </si>
+  <si>
+    <t>毒雨_最近释放距离</t>
+  </si>
+  <si>
+    <t>毒雨_最远释放距离</t>
+  </si>
+  <si>
+    <t>毒雨_技能效果半径</t>
+  </si>
+  <si>
+    <t>毒雨_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒雨_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒雨_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒雨_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒雨_技能持续时间</t>
+  </si>
+  <si>
+    <t>毒雨_技能伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>毒雨_技能等级</t>
+  </si>
+  <si>
+    <t>毒刃_获得</t>
+  </si>
+  <si>
+    <t>毒刃_最近释放距离</t>
+  </si>
+  <si>
+    <t>毒刃_最远释放距离</t>
+  </si>
+  <si>
+    <t>毒刃_技能效果半径</t>
+  </si>
+  <si>
+    <t>毒刃_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒刃_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒刃_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒刃_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒刃_技能等级</t>
+  </si>
+  <si>
+    <t>淬毒_获得</t>
+  </si>
+  <si>
+    <t>淬毒_最近释放距离</t>
+  </si>
+  <si>
+    <t>淬毒_最远释放距离</t>
+  </si>
+  <si>
+    <t>淬毒_技能效果半径</t>
+  </si>
+  <si>
+    <t>淬毒_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>淬毒_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>淬毒_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>淬毒_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>淬毒_技能等级</t>
+  </si>
+  <si>
+    <t>毒性爆发_获得</t>
+  </si>
+  <si>
+    <t>毒性爆发_冷却</t>
+  </si>
+  <si>
+    <t>毒性爆发_最近释放距离</t>
+  </si>
+  <si>
+    <t>毒性爆发_最远释放距离</t>
+  </si>
+  <si>
+    <t>毒性爆发_技能效果半径</t>
+  </si>
+  <si>
+    <t>毒性爆发_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒性爆发_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒性爆发_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>毒性爆发_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>毒性爆发_技能等级</t>
+  </si>
+  <si>
+    <t>流毒_获得</t>
+  </si>
+  <si>
+    <t>流毒_冷却</t>
+  </si>
+  <si>
+    <t>流毒_最近释放距离</t>
+  </si>
+  <si>
+    <t>流毒_最远释放距离</t>
+  </si>
+  <si>
+    <t>流毒_技能效果半径</t>
+  </si>
+  <si>
+    <t>流毒_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>流毒_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>流毒_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>流毒_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>流毒_技能持续时间</t>
+  </si>
+  <si>
+    <t>流毒_技能伤害或效果生效间隔</t>
+  </si>
+  <si>
+    <t>流毒_技能等级</t>
+  </si>
+  <si>
+    <t>尸爆_获得</t>
+  </si>
+  <si>
+    <t>尸爆_冷却</t>
+  </si>
+  <si>
+    <t>尸爆_最近释放距离</t>
+  </si>
+  <si>
+    <t>尸爆_最远释放距离</t>
+  </si>
+  <si>
+    <t>尸爆_技能效果半径</t>
+  </si>
+  <si>
+    <t>尸爆_主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>尸爆_主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>尸爆_非主目标直接伤害固定值</t>
+  </si>
+  <si>
+    <t>尸爆_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>尸爆_技能等级</t>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S</t>
@@ -4724,7 +5024,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1477"/>
+  <dimension ref="A1:I1578"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -39738,7 +40038,7 @@
         <v>2</v>
       </c>
       <c r="I1252">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1253" spans="1:9">
@@ -39790,7 +40090,7 @@
         <v>2</v>
       </c>
       <c r="I1254">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1255" spans="1:9">
@@ -40772,7 +41072,7 @@
         <v>2</v>
       </c>
       <c r="I1291">
-        <v>15000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1292" spans="1:9">
@@ -40824,7 +41124,7 @@
         <v>2</v>
       </c>
       <c r="I1293">
-        <v>15000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1294" spans="1:9">
@@ -42927,7 +43227,7 @@
         <v>2</v>
       </c>
       <c r="I1372">
-        <v>24000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1373" spans="1:9">
@@ -42979,7 +43279,7 @@
         <v>2</v>
       </c>
       <c r="I1374">
-        <v>24000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1375" spans="1:9">
@@ -43917,7 +44217,7 @@
         <v>2</v>
       </c>
       <c r="I1410">
-        <v>16000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1411" spans="1:9">
@@ -43969,7 +44269,7 @@
         <v>2</v>
       </c>
       <c r="I1412">
-        <v>16000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1413" spans="1:9">
@@ -44180,7 +44480,7 @@
         <v>1</v>
       </c>
       <c r="I1420">
-        <v>2500</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="1421" spans="1:9">
@@ -44336,7 +44636,7 @@
         <v>1</v>
       </c>
       <c r="I1426">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1427" spans="1:9">
@@ -44596,7 +44896,7 @@
         <v>2</v>
       </c>
       <c r="I1436">
-        <v>12000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1437" spans="1:9">
@@ -44648,7 +44948,7 @@
         <v>2</v>
       </c>
       <c r="I1438">
-        <v>12000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1439" spans="1:9">
@@ -45665,6 +45965,2666 @@
       </c>
       <c r="I1477">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:9">
+      <c r="A1478" s="26">
+        <v>5101700</v>
+      </c>
+      <c r="B1478" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1478" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1478" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1478" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="F1478" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1478" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1478" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:9">
+      <c r="A1479" s="26">
+        <v>5101701</v>
+      </c>
+      <c r="B1479" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1479" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1479" s="27" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1479" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1479" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1479" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1479" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:9">
+      <c r="A1480" s="26">
+        <v>5101702</v>
+      </c>
+      <c r="B1480" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1480" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1480" s="27" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1480" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1480" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1480" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1480" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:9">
+      <c r="A1481" s="26">
+        <v>5101705</v>
+      </c>
+      <c r="B1481" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1481" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1481" s="27" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E1481" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1481" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1481" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1481" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:9">
+      <c r="A1482" s="26">
+        <v>5101706</v>
+      </c>
+      <c r="B1482" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1482" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1482" s="27" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E1482" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1482" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1482" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1482" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:9">
+      <c r="A1483" s="26">
+        <v>5101708</v>
+      </c>
+      <c r="B1483" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1483" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1483" s="27" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E1483" s="26" t="s">
+        <v>971</v>
+      </c>
+      <c r="F1483" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1483" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1483" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:9">
+      <c r="A1484" s="26">
+        <v>5101711</v>
+      </c>
+      <c r="B1484" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1484" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1484" s="27" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E1484" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1484" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1484" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1484" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:9">
+      <c r="A1485" s="26">
+        <v>5101712</v>
+      </c>
+      <c r="B1485" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1485" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1485" s="27" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E1485" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1485" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1485" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1485" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:9">
+      <c r="A1486" s="26">
+        <v>5101715</v>
+      </c>
+      <c r="B1486" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1486" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1486" s="27" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E1486" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1486" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1486" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1486" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:9">
+      <c r="A1487" s="26">
+        <v>5101716</v>
+      </c>
+      <c r="B1487" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1487" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1487" s="27" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E1487" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1487" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1487" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1487" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:9">
+      <c r="A1488" s="26">
+        <v>5101718</v>
+      </c>
+      <c r="B1488" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1488" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1488" s="27" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E1488" s="26" t="s">
+        <v>971</v>
+      </c>
+      <c r="F1488" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1488" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1488" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:9">
+      <c r="A1489">
+        <v>920105</v>
+      </c>
+      <c r="B1489" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1489">
+        <v>0</v>
+      </c>
+      <c r="D1489" s="28" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E1489" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1489">
+        <v>10</v>
+      </c>
+      <c r="H1489">
+        <v>1</v>
+      </c>
+      <c r="I1489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:9">
+      <c r="A1490">
+        <v>1920105</v>
+      </c>
+      <c r="B1490" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1490">
+        <v>0</v>
+      </c>
+      <c r="D1490" s="28" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E1490" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1490">
+        <v>10</v>
+      </c>
+      <c r="H1490">
+        <v>1</v>
+      </c>
+      <c r="I1490">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:9">
+      <c r="A1491">
+        <v>2920105</v>
+      </c>
+      <c r="B1491" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1491">
+        <v>0</v>
+      </c>
+      <c r="D1491" s="28" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E1491" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1491">
+        <v>10</v>
+      </c>
+      <c r="H1491">
+        <v>1</v>
+      </c>
+      <c r="I1491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:9">
+      <c r="A1492">
+        <v>3920105</v>
+      </c>
+      <c r="B1492" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1492">
+        <v>0</v>
+      </c>
+      <c r="D1492" s="28" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E1492" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1492">
+        <v>10</v>
+      </c>
+      <c r="H1492">
+        <v>1</v>
+      </c>
+      <c r="I1492">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:9">
+      <c r="A1493">
+        <v>4920105</v>
+      </c>
+      <c r="B1493" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1493">
+        <v>0</v>
+      </c>
+      <c r="D1493" s="28" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E1493" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1493">
+        <v>10</v>
+      </c>
+      <c r="H1493">
+        <v>1</v>
+      </c>
+      <c r="I1493">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:9">
+      <c r="A1494">
+        <v>5920105</v>
+      </c>
+      <c r="B1494" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1494">
+        <v>0</v>
+      </c>
+      <c r="D1494" s="28" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E1494" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1494">
+        <v>10</v>
+      </c>
+      <c r="H1494">
+        <v>1</v>
+      </c>
+      <c r="I1494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:9">
+      <c r="A1495">
+        <v>6920105</v>
+      </c>
+      <c r="B1495" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1495">
+        <v>0</v>
+      </c>
+      <c r="D1495" s="28" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E1495" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1495">
+        <v>10</v>
+      </c>
+      <c r="H1495">
+        <v>1</v>
+      </c>
+      <c r="I1495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:9">
+      <c r="A1496">
+        <v>7920105</v>
+      </c>
+      <c r="B1496" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1496">
+        <v>0</v>
+      </c>
+      <c r="D1496" s="28" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E1496" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1496">
+        <v>10</v>
+      </c>
+      <c r="H1496">
+        <v>2</v>
+      </c>
+      <c r="I1496">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:9">
+      <c r="A1497">
+        <v>8920105</v>
+      </c>
+      <c r="B1497" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1497">
+        <v>0</v>
+      </c>
+      <c r="D1497" s="28" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E1497" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1497">
+        <v>10</v>
+      </c>
+      <c r="H1497">
+        <v>1</v>
+      </c>
+      <c r="I1497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:9">
+      <c r="A1498">
+        <v>9920105</v>
+      </c>
+      <c r="B1498" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1498">
+        <v>0</v>
+      </c>
+      <c r="D1498" s="28" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E1498" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1498">
+        <v>10</v>
+      </c>
+      <c r="H1498">
+        <v>2</v>
+      </c>
+      <c r="I1498">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:9">
+      <c r="A1499">
+        <v>10920105</v>
+      </c>
+      <c r="B1499" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1499">
+        <v>0</v>
+      </c>
+      <c r="D1499" s="28" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E1499" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1499">
+        <v>10</v>
+      </c>
+      <c r="H1499">
+        <v>1</v>
+      </c>
+      <c r="I1499">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:9">
+      <c r="A1500">
+        <v>11920105</v>
+      </c>
+      <c r="B1500" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1500">
+        <v>0</v>
+      </c>
+      <c r="D1500" s="28" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E1500" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1500">
+        <v>10</v>
+      </c>
+      <c r="H1500">
+        <v>1</v>
+      </c>
+      <c r="I1500">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:9">
+      <c r="A1501">
+        <v>13920105</v>
+      </c>
+      <c r="B1501" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1501">
+        <v>0</v>
+      </c>
+      <c r="D1501" s="28" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E1501" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1501">
+        <v>10</v>
+      </c>
+      <c r="H1501">
+        <v>1</v>
+      </c>
+      <c r="I1501">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:9">
+      <c r="A1502">
+        <v>14920105</v>
+      </c>
+      <c r="B1502" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1502">
+        <v>0</v>
+      </c>
+      <c r="D1502" s="28" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E1502" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1502">
+        <v>10</v>
+      </c>
+      <c r="H1502">
+        <v>1</v>
+      </c>
+      <c r="I1502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:9">
+      <c r="A1503">
+        <v>15920105</v>
+      </c>
+      <c r="B1503" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1503">
+        <v>0</v>
+      </c>
+      <c r="D1503" s="28" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E1503" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1503">
+        <v>10</v>
+      </c>
+      <c r="H1503">
+        <v>1</v>
+      </c>
+      <c r="I1503">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:9">
+      <c r="A1504">
+        <v>16920105</v>
+      </c>
+      <c r="B1504" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1504">
+        <v>0</v>
+      </c>
+      <c r="D1504" s="28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E1504" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="F1504" s="28"/>
+      <c r="G1504">
+        <v>10</v>
+      </c>
+      <c r="H1504">
+        <v>1</v>
+      </c>
+      <c r="I1504">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1505" customFormat="1" spans="1:9">
+      <c r="A1505">
+        <v>920106</v>
+      </c>
+      <c r="B1505" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1505">
+        <v>0</v>
+      </c>
+      <c r="D1505" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E1505" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1505">
+        <v>10</v>
+      </c>
+      <c r="H1505">
+        <v>1</v>
+      </c>
+      <c r="I1505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1506" customFormat="1" spans="1:9">
+      <c r="A1506">
+        <v>1920106</v>
+      </c>
+      <c r="B1506" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1506">
+        <v>0</v>
+      </c>
+      <c r="D1506" s="28" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E1506" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1506">
+        <v>10</v>
+      </c>
+      <c r="H1506">
+        <v>1</v>
+      </c>
+      <c r="I1506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1507" customFormat="1" spans="1:9">
+      <c r="A1507">
+        <v>2920106</v>
+      </c>
+      <c r="B1507" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1507">
+        <v>0</v>
+      </c>
+      <c r="D1507" s="28" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E1507" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1507">
+        <v>10</v>
+      </c>
+      <c r="H1507">
+        <v>1</v>
+      </c>
+      <c r="I1507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1508" customFormat="1" spans="1:9">
+      <c r="A1508">
+        <v>3920106</v>
+      </c>
+      <c r="B1508" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1508">
+        <v>0</v>
+      </c>
+      <c r="D1508" s="28" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E1508" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1508">
+        <v>10</v>
+      </c>
+      <c r="H1508">
+        <v>1</v>
+      </c>
+      <c r="I1508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1509" customFormat="1" spans="1:9">
+      <c r="A1509">
+        <v>4920106</v>
+      </c>
+      <c r="B1509" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1509">
+        <v>0</v>
+      </c>
+      <c r="D1509" s="28" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E1509" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1509">
+        <v>10</v>
+      </c>
+      <c r="H1509">
+        <v>1</v>
+      </c>
+      <c r="I1509">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="1510" customFormat="1" spans="1:9">
+      <c r="A1510">
+        <v>5920106</v>
+      </c>
+      <c r="B1510" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1510">
+        <v>0</v>
+      </c>
+      <c r="D1510" s="28" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E1510" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1510">
+        <v>10</v>
+      </c>
+      <c r="H1510">
+        <v>1</v>
+      </c>
+      <c r="I1510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1511" customFormat="1" spans="1:9">
+      <c r="A1511">
+        <v>6920106</v>
+      </c>
+      <c r="B1511" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1511">
+        <v>0</v>
+      </c>
+      <c r="D1511" s="28" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E1511" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1511">
+        <v>10</v>
+      </c>
+      <c r="H1511">
+        <v>1</v>
+      </c>
+      <c r="I1511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1512" customFormat="1" spans="1:9">
+      <c r="A1512">
+        <v>7920106</v>
+      </c>
+      <c r="B1512" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1512">
+        <v>0</v>
+      </c>
+      <c r="D1512" s="28" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E1512" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1512">
+        <v>10</v>
+      </c>
+      <c r="H1512">
+        <v>2</v>
+      </c>
+      <c r="I1512">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="1513" customFormat="1" spans="1:9">
+      <c r="A1513">
+        <v>8920106</v>
+      </c>
+      <c r="B1513" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1513">
+        <v>0</v>
+      </c>
+      <c r="D1513" s="28" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E1513" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1513">
+        <v>10</v>
+      </c>
+      <c r="H1513">
+        <v>1</v>
+      </c>
+      <c r="I1513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1514" customFormat="1" spans="1:9">
+      <c r="A1514">
+        <v>9920106</v>
+      </c>
+      <c r="B1514" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1514">
+        <v>0</v>
+      </c>
+      <c r="D1514" s="28" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E1514" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1514">
+        <v>10</v>
+      </c>
+      <c r="H1514">
+        <v>2</v>
+      </c>
+      <c r="I1514">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="1515" customFormat="1" spans="1:9">
+      <c r="A1515">
+        <v>10920106</v>
+      </c>
+      <c r="B1515" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1515">
+        <v>0</v>
+      </c>
+      <c r="D1515" s="28" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E1515" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1515">
+        <v>10</v>
+      </c>
+      <c r="H1515">
+        <v>1</v>
+      </c>
+      <c r="I1515">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1516" customFormat="1" spans="1:9">
+      <c r="A1516">
+        <v>11920106</v>
+      </c>
+      <c r="B1516" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1516">
+        <v>0</v>
+      </c>
+      <c r="D1516" s="28" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E1516" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1516">
+        <v>10</v>
+      </c>
+      <c r="H1516">
+        <v>1</v>
+      </c>
+      <c r="I1516">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1517" customFormat="1" spans="1:9">
+      <c r="A1517">
+        <v>13920106</v>
+      </c>
+      <c r="B1517" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1517">
+        <v>0</v>
+      </c>
+      <c r="D1517" s="28" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E1517" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1517">
+        <v>10</v>
+      </c>
+      <c r="H1517">
+        <v>1</v>
+      </c>
+      <c r="I1517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1518" customFormat="1" spans="1:9">
+      <c r="A1518">
+        <v>920107</v>
+      </c>
+      <c r="B1518" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1518">
+        <v>0</v>
+      </c>
+      <c r="D1518" s="28" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E1518" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1518">
+        <v>10</v>
+      </c>
+      <c r="H1518">
+        <v>1</v>
+      </c>
+      <c r="I1518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1519" customFormat="1" spans="1:9">
+      <c r="A1519">
+        <v>2920107</v>
+      </c>
+      <c r="B1519" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1519">
+        <v>0</v>
+      </c>
+      <c r="D1519" s="28" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E1519" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1519">
+        <v>10</v>
+      </c>
+      <c r="H1519">
+        <v>1</v>
+      </c>
+      <c r="I1519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1520" customFormat="1" spans="1:9">
+      <c r="A1520">
+        <v>39201057</v>
+      </c>
+      <c r="B1520" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1520">
+        <v>0</v>
+      </c>
+      <c r="D1520" s="28" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E1520" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1520">
+        <v>10</v>
+      </c>
+      <c r="H1520">
+        <v>1</v>
+      </c>
+      <c r="I1520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1521" customFormat="1" spans="1:9">
+      <c r="A1521">
+        <v>4920107</v>
+      </c>
+      <c r="B1521" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1521">
+        <v>0</v>
+      </c>
+      <c r="D1521" s="28" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E1521" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1521">
+        <v>10</v>
+      </c>
+      <c r="H1521">
+        <v>1</v>
+      </c>
+      <c r="I1521">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1522" customFormat="1" spans="1:9">
+      <c r="A1522">
+        <v>6920107</v>
+      </c>
+      <c r="B1522" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1522">
+        <v>0</v>
+      </c>
+      <c r="D1522" s="28" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E1522" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1522">
+        <v>10</v>
+      </c>
+      <c r="H1522">
+        <v>1</v>
+      </c>
+      <c r="I1522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1523" customFormat="1" spans="1:9">
+      <c r="A1523">
+        <v>7920107</v>
+      </c>
+      <c r="B1523" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1523">
+        <v>0</v>
+      </c>
+      <c r="D1523" s="28" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E1523" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1523">
+        <v>10</v>
+      </c>
+      <c r="H1523">
+        <v>2</v>
+      </c>
+      <c r="I1523">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1524" customFormat="1" spans="1:9">
+      <c r="A1524">
+        <v>8920107</v>
+      </c>
+      <c r="B1524" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1524">
+        <v>0</v>
+      </c>
+      <c r="D1524" s="28" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E1524" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1524">
+        <v>10</v>
+      </c>
+      <c r="H1524">
+        <v>1</v>
+      </c>
+      <c r="I1524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1525" customFormat="1" spans="1:9">
+      <c r="A1525">
+        <v>9920107</v>
+      </c>
+      <c r="B1525" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1525">
+        <v>0</v>
+      </c>
+      <c r="D1525" s="28" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E1525" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1525">
+        <v>10</v>
+      </c>
+      <c r="H1525">
+        <v>2</v>
+      </c>
+      <c r="I1525">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1526" customFormat="1" spans="1:9">
+      <c r="A1526">
+        <v>10920107</v>
+      </c>
+      <c r="B1526" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1526">
+        <v>0</v>
+      </c>
+      <c r="D1526" s="28" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1526" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1526">
+        <v>10</v>
+      </c>
+      <c r="H1526">
+        <v>1</v>
+      </c>
+      <c r="I1526">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1527" customFormat="1" spans="1:9">
+      <c r="A1527">
+        <v>11920107</v>
+      </c>
+      <c r="B1527" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1527">
+        <v>0</v>
+      </c>
+      <c r="D1527" s="28" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E1527" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1527">
+        <v>10</v>
+      </c>
+      <c r="H1527">
+        <v>1</v>
+      </c>
+      <c r="I1527">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1528" customFormat="1" spans="1:9">
+      <c r="A1528">
+        <v>13920107</v>
+      </c>
+      <c r="B1528" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1528">
+        <v>0</v>
+      </c>
+      <c r="D1528" s="28" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E1528" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1528">
+        <v>10</v>
+      </c>
+      <c r="H1528">
+        <v>1</v>
+      </c>
+      <c r="I1528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1529" customFormat="1" spans="1:9">
+      <c r="A1529">
+        <v>920108</v>
+      </c>
+      <c r="B1529" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1529">
+        <v>0</v>
+      </c>
+      <c r="D1529" s="28" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E1529" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1529">
+        <v>10</v>
+      </c>
+      <c r="H1529">
+        <v>1</v>
+      </c>
+      <c r="I1529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1530" customFormat="1" spans="1:9">
+      <c r="A1530">
+        <v>2920108</v>
+      </c>
+      <c r="B1530" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1530">
+        <v>0</v>
+      </c>
+      <c r="D1530" s="28" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E1530" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1530">
+        <v>10</v>
+      </c>
+      <c r="H1530">
+        <v>1</v>
+      </c>
+      <c r="I1530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1531" customFormat="1" spans="1:9">
+      <c r="A1531">
+        <v>3920108</v>
+      </c>
+      <c r="B1531" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1531">
+        <v>0</v>
+      </c>
+      <c r="D1531" s="28" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1531" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1531">
+        <v>10</v>
+      </c>
+      <c r="H1531">
+        <v>1</v>
+      </c>
+      <c r="I1531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1532" customFormat="1" spans="1:9">
+      <c r="A1532">
+        <v>4920108</v>
+      </c>
+      <c r="B1532" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1532">
+        <v>0</v>
+      </c>
+      <c r="D1532" s="28" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E1532" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1532">
+        <v>10</v>
+      </c>
+      <c r="H1532">
+        <v>1</v>
+      </c>
+      <c r="I1532">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="1533" customFormat="1" spans="1:9">
+      <c r="A1533">
+        <v>6920108</v>
+      </c>
+      <c r="B1533" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1533">
+        <v>0</v>
+      </c>
+      <c r="D1533" s="28" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E1533" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1533">
+        <v>10</v>
+      </c>
+      <c r="H1533">
+        <v>1</v>
+      </c>
+      <c r="I1533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1534" customFormat="1" spans="1:9">
+      <c r="A1534">
+        <v>7920108</v>
+      </c>
+      <c r="B1534" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1534">
+        <v>0</v>
+      </c>
+      <c r="D1534" s="28" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E1534" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1534">
+        <v>10</v>
+      </c>
+      <c r="H1534">
+        <v>2</v>
+      </c>
+      <c r="I1534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1535" customFormat="1" spans="1:9">
+      <c r="A1535">
+        <v>8920108</v>
+      </c>
+      <c r="B1535" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1535">
+        <v>0</v>
+      </c>
+      <c r="D1535" s="28" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E1535" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1535">
+        <v>10</v>
+      </c>
+      <c r="H1535">
+        <v>1</v>
+      </c>
+      <c r="I1535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1536" customFormat="1" spans="1:9">
+      <c r="A1536">
+        <v>9920108</v>
+      </c>
+      <c r="B1536" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1536">
+        <v>0</v>
+      </c>
+      <c r="D1536" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E1536" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1536">
+        <v>10</v>
+      </c>
+      <c r="H1536">
+        <v>2</v>
+      </c>
+      <c r="I1536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1537" customFormat="1" spans="1:9">
+      <c r="A1537">
+        <v>13920108</v>
+      </c>
+      <c r="B1537" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1537">
+        <v>0</v>
+      </c>
+      <c r="D1537" s="28" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E1537" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1537">
+        <v>10</v>
+      </c>
+      <c r="H1537">
+        <v>1</v>
+      </c>
+      <c r="I1537">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1538" customFormat="1" spans="1:9">
+      <c r="A1538">
+        <v>920109</v>
+      </c>
+      <c r="B1538" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1538">
+        <v>0</v>
+      </c>
+      <c r="D1538" s="28" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E1538" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1538">
+        <v>10</v>
+      </c>
+      <c r="H1538">
+        <v>1</v>
+      </c>
+      <c r="I1538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1539" customFormat="1" spans="1:9">
+      <c r="A1539">
+        <v>2920109</v>
+      </c>
+      <c r="B1539" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1539">
+        <v>0</v>
+      </c>
+      <c r="D1539" s="28" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E1539" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1539">
+        <v>10</v>
+      </c>
+      <c r="H1539">
+        <v>1</v>
+      </c>
+      <c r="I1539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1540" customFormat="1" spans="1:9">
+      <c r="A1540">
+        <v>3920109</v>
+      </c>
+      <c r="B1540" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1540">
+        <v>0</v>
+      </c>
+      <c r="D1540" s="28" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E1540" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1540">
+        <v>10</v>
+      </c>
+      <c r="H1540">
+        <v>1</v>
+      </c>
+      <c r="I1540">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1541" customFormat="1" spans="1:9">
+      <c r="A1541">
+        <v>4920109</v>
+      </c>
+      <c r="B1541" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1541">
+        <v>0</v>
+      </c>
+      <c r="D1541" s="28" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E1541" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1541">
+        <v>10</v>
+      </c>
+      <c r="H1541">
+        <v>1</v>
+      </c>
+      <c r="I1541">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1542" customFormat="1" spans="1:9">
+      <c r="A1542">
+        <v>6920109</v>
+      </c>
+      <c r="B1542" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1542">
+        <v>0</v>
+      </c>
+      <c r="D1542" s="28" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E1542" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1542">
+        <v>10</v>
+      </c>
+      <c r="H1542">
+        <v>1</v>
+      </c>
+      <c r="I1542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1543" customFormat="1" spans="1:9">
+      <c r="A1543">
+        <v>7920109</v>
+      </c>
+      <c r="B1543" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1543">
+        <v>0</v>
+      </c>
+      <c r="D1543" s="28" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E1543" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1543">
+        <v>10</v>
+      </c>
+      <c r="H1543">
+        <v>2</v>
+      </c>
+      <c r="I1543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1544" customFormat="1" spans="1:9">
+      <c r="A1544">
+        <v>8920109</v>
+      </c>
+      <c r="B1544" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1544">
+        <v>0</v>
+      </c>
+      <c r="D1544" s="28" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E1544" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1544">
+        <v>10</v>
+      </c>
+      <c r="H1544">
+        <v>1</v>
+      </c>
+      <c r="I1544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1545" customFormat="1" spans="1:9">
+      <c r="A1545">
+        <v>9920109</v>
+      </c>
+      <c r="B1545" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1545">
+        <v>0</v>
+      </c>
+      <c r="D1545" s="28" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E1545" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1545">
+        <v>10</v>
+      </c>
+      <c r="H1545">
+        <v>2</v>
+      </c>
+      <c r="I1545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1546" customFormat="1" spans="1:9">
+      <c r="A1546">
+        <v>13920109</v>
+      </c>
+      <c r="B1546" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1546">
+        <v>0</v>
+      </c>
+      <c r="D1546" s="28" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E1546" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1546">
+        <v>10</v>
+      </c>
+      <c r="H1546">
+        <v>1</v>
+      </c>
+      <c r="I1546">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1547" customFormat="1" spans="1:9">
+      <c r="A1547">
+        <v>920110</v>
+      </c>
+      <c r="B1547" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1547">
+        <v>0</v>
+      </c>
+      <c r="D1547" s="28" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E1547" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1547">
+        <v>10</v>
+      </c>
+      <c r="H1547">
+        <v>1</v>
+      </c>
+      <c r="I1547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1548" customFormat="1" spans="1:9">
+      <c r="A1548">
+        <v>1920110</v>
+      </c>
+      <c r="B1548" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1548">
+        <v>0</v>
+      </c>
+      <c r="D1548" s="28" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E1548" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1548">
+        <v>10</v>
+      </c>
+      <c r="H1548">
+        <v>1</v>
+      </c>
+      <c r="I1548">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1549" customFormat="1" spans="1:9">
+      <c r="A1549">
+        <v>2920110</v>
+      </c>
+      <c r="B1549" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1549">
+        <v>0</v>
+      </c>
+      <c r="D1549" s="28" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E1549" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1549">
+        <v>10</v>
+      </c>
+      <c r="H1549">
+        <v>1</v>
+      </c>
+      <c r="I1549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1550" customFormat="1" spans="1:9">
+      <c r="A1550">
+        <v>3920110</v>
+      </c>
+      <c r="B1550" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1550">
+        <v>0</v>
+      </c>
+      <c r="D1550" s="28" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E1550" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1550">
+        <v>10</v>
+      </c>
+      <c r="H1550">
+        <v>1</v>
+      </c>
+      <c r="I1550">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1551" customFormat="1" spans="1:9">
+      <c r="A1551">
+        <v>4920110</v>
+      </c>
+      <c r="B1551" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1551">
+        <v>0</v>
+      </c>
+      <c r="D1551" s="28" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E1551" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1551">
+        <v>10</v>
+      </c>
+      <c r="H1551">
+        <v>1</v>
+      </c>
+      <c r="I1551">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1552" customFormat="1" spans="1:9">
+      <c r="A1552">
+        <v>6920110</v>
+      </c>
+      <c r="B1552" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1552">
+        <v>0</v>
+      </c>
+      <c r="D1552" s="28" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E1552" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1552">
+        <v>10</v>
+      </c>
+      <c r="H1552">
+        <v>1</v>
+      </c>
+      <c r="I1552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1553" customFormat="1" spans="1:9">
+      <c r="A1553">
+        <v>7920110</v>
+      </c>
+      <c r="B1553" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1553">
+        <v>0</v>
+      </c>
+      <c r="D1553" s="28" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E1553" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1553">
+        <v>10</v>
+      </c>
+      <c r="H1553">
+        <v>2</v>
+      </c>
+      <c r="I1553">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="1554" customFormat="1" spans="1:9">
+      <c r="A1554">
+        <v>8920110</v>
+      </c>
+      <c r="B1554" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1554">
+        <v>0</v>
+      </c>
+      <c r="D1554" s="28" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E1554" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1554">
+        <v>10</v>
+      </c>
+      <c r="H1554">
+        <v>1</v>
+      </c>
+      <c r="I1554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1555" customFormat="1" spans="1:9">
+      <c r="A1555">
+        <v>9920110</v>
+      </c>
+      <c r="B1555" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1555">
+        <v>0</v>
+      </c>
+      <c r="D1555" s="28" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E1555" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1555">
+        <v>10</v>
+      </c>
+      <c r="H1555">
+        <v>2</v>
+      </c>
+      <c r="I1555">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="1556" customFormat="1" spans="1:9">
+      <c r="A1556">
+        <v>13920110</v>
+      </c>
+      <c r="B1556" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1556">
+        <v>0</v>
+      </c>
+      <c r="D1556" s="28" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E1556" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1556">
+        <v>10</v>
+      </c>
+      <c r="H1556">
+        <v>1</v>
+      </c>
+      <c r="I1556">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1557" customFormat="1" spans="1:9">
+      <c r="A1557">
+        <v>920111</v>
+      </c>
+      <c r="B1557" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1557">
+        <v>0</v>
+      </c>
+      <c r="D1557" s="28" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E1557" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1557">
+        <v>10</v>
+      </c>
+      <c r="H1557">
+        <v>1</v>
+      </c>
+      <c r="I1557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1558" customFormat="1" spans="1:9">
+      <c r="A1558">
+        <v>1920111</v>
+      </c>
+      <c r="B1558" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1558">
+        <v>0</v>
+      </c>
+      <c r="D1558" s="28" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E1558" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1558">
+        <v>10</v>
+      </c>
+      <c r="H1558">
+        <v>1</v>
+      </c>
+      <c r="I1558">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1559" customFormat="1" spans="1:9">
+      <c r="A1559">
+        <v>2920111</v>
+      </c>
+      <c r="B1559" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1559">
+        <v>0</v>
+      </c>
+      <c r="D1559" s="28" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E1559" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1559">
+        <v>10</v>
+      </c>
+      <c r="H1559">
+        <v>1</v>
+      </c>
+      <c r="I1559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1560" customFormat="1" spans="1:9">
+      <c r="A1560">
+        <v>3920111</v>
+      </c>
+      <c r="B1560" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1560">
+        <v>0</v>
+      </c>
+      <c r="D1560" s="28" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E1560" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1560">
+        <v>10</v>
+      </c>
+      <c r="H1560">
+        <v>1</v>
+      </c>
+      <c r="I1560">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1561" customFormat="1" spans="1:9">
+      <c r="A1561">
+        <v>492011</v>
+      </c>
+      <c r="B1561" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1561">
+        <v>0</v>
+      </c>
+      <c r="D1561" s="28" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E1561" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1561">
+        <v>10</v>
+      </c>
+      <c r="H1561">
+        <v>1</v>
+      </c>
+      <c r="I1561">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1562" customFormat="1" spans="1:9">
+      <c r="A1562">
+        <v>6920111</v>
+      </c>
+      <c r="B1562" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1562">
+        <v>0</v>
+      </c>
+      <c r="D1562" s="28" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E1562" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1562">
+        <v>10</v>
+      </c>
+      <c r="H1562">
+        <v>1</v>
+      </c>
+      <c r="I1562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1563" customFormat="1" spans="1:9">
+      <c r="A1563">
+        <v>7920111</v>
+      </c>
+      <c r="B1563" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1563">
+        <v>0</v>
+      </c>
+      <c r="D1563" s="28" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E1563" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1563">
+        <v>10</v>
+      </c>
+      <c r="H1563">
+        <v>2</v>
+      </c>
+      <c r="I1563">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="1564" customFormat="1" spans="1:9">
+      <c r="A1564">
+        <v>8920111</v>
+      </c>
+      <c r="B1564" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1564">
+        <v>0</v>
+      </c>
+      <c r="D1564" s="28" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E1564" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1564">
+        <v>10</v>
+      </c>
+      <c r="H1564">
+        <v>1</v>
+      </c>
+      <c r="I1564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1565" customFormat="1" spans="1:9">
+      <c r="A1565">
+        <v>9920111</v>
+      </c>
+      <c r="B1565" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1565">
+        <v>0</v>
+      </c>
+      <c r="D1565" s="28" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E1565" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1565">
+        <v>10</v>
+      </c>
+      <c r="H1565">
+        <v>2</v>
+      </c>
+      <c r="I1565">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="1566" customFormat="1" spans="1:9">
+      <c r="A1566">
+        <v>10920111</v>
+      </c>
+      <c r="B1566" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1566">
+        <v>0</v>
+      </c>
+      <c r="D1566" s="28" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E1566" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1566">
+        <v>10</v>
+      </c>
+      <c r="H1566">
+        <v>1</v>
+      </c>
+      <c r="I1566">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="1567" customFormat="1" spans="1:9">
+      <c r="A1567">
+        <v>11920111</v>
+      </c>
+      <c r="B1567" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1567">
+        <v>0</v>
+      </c>
+      <c r="D1567" s="28" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E1567" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1567">
+        <v>10</v>
+      </c>
+      <c r="H1567">
+        <v>1</v>
+      </c>
+      <c r="I1567">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1568" customFormat="1" spans="1:9">
+      <c r="A1568">
+        <v>13920111</v>
+      </c>
+      <c r="B1568" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1568">
+        <v>0</v>
+      </c>
+      <c r="D1568" s="28" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E1568" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1568">
+        <v>10</v>
+      </c>
+      <c r="H1568">
+        <v>1</v>
+      </c>
+      <c r="I1568">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1569" customFormat="1" spans="1:9">
+      <c r="A1569">
+        <v>920112</v>
+      </c>
+      <c r="B1569" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1569">
+        <v>0</v>
+      </c>
+      <c r="D1569" s="28" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E1569" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1569">
+        <v>10</v>
+      </c>
+      <c r="H1569">
+        <v>1</v>
+      </c>
+      <c r="I1569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1570" customFormat="1" spans="1:9">
+      <c r="A1570">
+        <v>1920112</v>
+      </c>
+      <c r="B1570" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1570">
+        <v>0</v>
+      </c>
+      <c r="D1570" s="28" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E1570" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1570">
+        <v>10</v>
+      </c>
+      <c r="H1570">
+        <v>1</v>
+      </c>
+      <c r="I1570">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1571" customFormat="1" spans="1:9">
+      <c r="A1571">
+        <v>2920112</v>
+      </c>
+      <c r="B1571" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1571">
+        <v>0</v>
+      </c>
+      <c r="D1571" s="28" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E1571" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1571">
+        <v>10</v>
+      </c>
+      <c r="H1571">
+        <v>1</v>
+      </c>
+      <c r="I1571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1572" customFormat="1" spans="1:9">
+      <c r="A1572">
+        <v>3920112</v>
+      </c>
+      <c r="B1572" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1572">
+        <v>0</v>
+      </c>
+      <c r="D1572" s="28" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E1572" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1572">
+        <v>10</v>
+      </c>
+      <c r="H1572">
+        <v>1</v>
+      </c>
+      <c r="I1572">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1573" customFormat="1" spans="1:9">
+      <c r="A1573">
+        <v>4920112</v>
+      </c>
+      <c r="B1573" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1573">
+        <v>0</v>
+      </c>
+      <c r="D1573" s="28" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E1573" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1573">
+        <v>10</v>
+      </c>
+      <c r="H1573">
+        <v>1</v>
+      </c>
+      <c r="I1573">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1574" customFormat="1" spans="1:9">
+      <c r="A1574">
+        <v>6920112</v>
+      </c>
+      <c r="B1574" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1574">
+        <v>0</v>
+      </c>
+      <c r="D1574" s="28" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E1574" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1574">
+        <v>10</v>
+      </c>
+      <c r="H1574">
+        <v>1</v>
+      </c>
+      <c r="I1574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575" customFormat="1" spans="1:9">
+      <c r="A1575">
+        <v>7920112</v>
+      </c>
+      <c r="B1575" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1575">
+        <v>0</v>
+      </c>
+      <c r="D1575" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E1575" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1575">
+        <v>10</v>
+      </c>
+      <c r="H1575">
+        <v>2</v>
+      </c>
+      <c r="I1575">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="1576" customFormat="1" spans="1:9">
+      <c r="A1576">
+        <v>8920112</v>
+      </c>
+      <c r="B1576" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1576">
+        <v>0</v>
+      </c>
+      <c r="D1576" s="28" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E1576" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1576">
+        <v>10</v>
+      </c>
+      <c r="H1576">
+        <v>1</v>
+      </c>
+      <c r="I1576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577" customFormat="1" spans="1:9">
+      <c r="A1577">
+        <v>9920112</v>
+      </c>
+      <c r="B1577" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1577">
+        <v>0</v>
+      </c>
+      <c r="D1577" s="28" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E1577" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1577">
+        <v>10</v>
+      </c>
+      <c r="H1577">
+        <v>2</v>
+      </c>
+      <c r="I1577">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="1578" customFormat="1" spans="1:9">
+      <c r="A1578">
+        <v>13920112</v>
+      </c>
+      <c r="B1578" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1578">
+        <v>0</v>
+      </c>
+      <c r="D1578" s="28" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E1578" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1578">
+        <v>10</v>
+      </c>
+      <c r="H1578">
+        <v>1</v>
+      </c>
+      <c r="I1578">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -45729,7 +48689,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1080</v>
+        <v>1180</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -45741,10 +48701,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1080</v>
+        <v>1180</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1080</v>
+        <v>1180</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -45758,90 +48718,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1081</v>
+        <v>1181</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1082</v>
+        <v>1182</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1083</v>
+        <v>1183</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1084</v>
+        <v>1184</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1085</v>
+        <v>1185</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1086</v>
+        <v>1186</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1087</v>
+        <v>1187</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1088</v>
+        <v>1188</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1089</v>
+        <v>1189</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1090</v>
+        <v>1190</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1091</v>
+        <v>1191</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1092</v>
+        <v>1192</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1093</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1094</v>
+        <v>1194</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1095</v>
+        <v>1195</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1096</v>
+        <v>1196</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1097</v>
+        <v>1197</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1098</v>
+        <v>1198</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1099</v>
+        <v>1199</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1101</v>
+        <v>1201</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1102</v>
+        <v>1202</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>1103</v>
+        <v>1203</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>1104</v>
+        <v>1204</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>1105</v>
+        <v>1205</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>1106</v>
+        <v>1206</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>1096</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -45852,7 +48812,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1107</v>
+        <v>1207</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -45873,7 +48833,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1108</v>
+        <v>1208</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -45885,7 +48845,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1109</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -45896,7 +48856,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1110</v>
+        <v>1210</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -45937,7 +48897,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1111</v>
+        <v>1211</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -45978,7 +48938,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1112</v>
+        <v>1212</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -45999,7 +48959,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1113</v>
+        <v>1213</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -46011,7 +48971,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1114</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -46022,7 +48982,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1115</v>
+        <v>1215</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -46043,7 +49003,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1116</v>
+        <v>1216</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -46055,7 +49015,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1117</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -46066,7 +49026,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1118</v>
+        <v>1218</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -46087,7 +49047,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1119</v>
+        <v>1219</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4110" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="1237">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3512,6 +3512,12 @@
     <t>毒沼_技能等级</t>
   </si>
   <si>
+    <t>传染被动_获得</t>
+  </si>
+  <si>
+    <t>传染被动-逻辑id</t>
+  </si>
+  <si>
     <t>毒雨_获得</t>
   </si>
   <si>
@@ -3545,6 +3551,9 @@
     <t>毒雨_技能等级</t>
   </si>
   <si>
+    <t>毒雨被动-逻辑id</t>
+  </si>
+  <si>
     <t>毒刃_获得</t>
   </si>
   <si>
@@ -3599,6 +3608,9 @@
     <t>淬毒_技能等级</t>
   </si>
   <si>
+    <t>淬毒_释放角度</t>
+  </si>
+  <si>
     <t>毒性爆发_获得</t>
   </si>
   <si>
@@ -3629,6 +3641,18 @@
     <t>毒性爆发_技能等级</t>
   </si>
   <si>
+    <t>毒性爆发被动_获得</t>
+  </si>
+  <si>
+    <t>毒性爆发被动-逻辑id</t>
+  </si>
+  <si>
+    <t>精神错乱被动_获得</t>
+  </si>
+  <si>
+    <t>精神错乱被动-逻辑id</t>
+  </si>
+  <si>
     <t>流毒_获得</t>
   </si>
   <si>
@@ -3665,6 +3689,12 @@
     <t>流毒_技能等级</t>
   </si>
   <si>
+    <t>流毒被动_获得</t>
+  </si>
+  <si>
+    <t>流毒被动-逻辑id</t>
+  </si>
+  <si>
     <t>尸爆_获得</t>
   </si>
   <si>
@@ -3693,6 +3723,27 @@
   </si>
   <si>
     <t>尸爆_技能等级</t>
+  </si>
+  <si>
+    <t>尸爆被动_获得</t>
+  </si>
+  <si>
+    <t>尸爆被动-逻辑id</t>
+  </si>
+  <si>
+    <t>传染被动-技能持续时间</t>
+  </si>
+  <si>
+    <t>传染被动-传染的命中率</t>
+  </si>
+  <si>
+    <t>毒性爆发被动-传染的命中率</t>
+  </si>
+  <si>
+    <t>精神错乱被动-传染的命中率</t>
+  </si>
+  <si>
+    <t>精神错乱被动-持续时间</t>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S</t>
@@ -5024,7 +5075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1578"/>
+  <dimension ref="A1:I1595"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -38668,7 +38719,7 @@
         <v>1</v>
       </c>
       <c r="I1200">
-        <v>6000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="1201" spans="1:9">
@@ -43227,7 +43278,7 @@
         <v>2</v>
       </c>
       <c r="I1372">
-        <v>18000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1373" spans="1:9">
@@ -43279,7 +43330,7 @@
         <v>2</v>
       </c>
       <c r="I1374">
-        <v>18000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1375" spans="1:9">
@@ -43643,7 +43694,7 @@
         <v>1</v>
       </c>
       <c r="I1388">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1389" spans="1:9">
@@ -44896,7 +44947,7 @@
         <v>2</v>
       </c>
       <c r="I1436">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1437" spans="1:9">
@@ -44948,7 +44999,7 @@
         <v>2</v>
       </c>
       <c r="I1438">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1439" spans="1:9">
@@ -44974,7 +45025,7 @@
         <v>1</v>
       </c>
       <c r="I1439">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1440" spans="1:9">
@@ -45522,7 +45573,7 @@
         <v>2</v>
       </c>
       <c r="I1460">
-        <v>10000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1461" spans="1:9">
@@ -45574,7 +45625,7 @@
         <v>2</v>
       </c>
       <c r="I1462">
-        <v>10000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1463" spans="1:9">
@@ -46413,7 +46464,7 @@
         <v>1</v>
       </c>
       <c r="I1493">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1494" spans="1:9">
@@ -46491,7 +46542,7 @@
         <v>2</v>
       </c>
       <c r="I1496">
-        <v>10000</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="1497" spans="1:9">
@@ -46543,7 +46594,7 @@
         <v>2</v>
       </c>
       <c r="I1498">
-        <v>10000</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="1499" spans="1:9">
@@ -46830,7 +46881,7 @@
         <v>1</v>
       </c>
       <c r="I1509">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1510" customFormat="1" spans="1:9">
@@ -46908,7 +46959,7 @@
         <v>2</v>
       </c>
       <c r="I1512">
-        <v>18000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1513" customFormat="1" spans="1:9">
@@ -46960,7 +47011,7 @@
         <v>2</v>
       </c>
       <c r="I1514">
-        <v>18000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1515" customFormat="1" spans="1:9">
@@ -47043,7 +47094,7 @@
     </row>
     <row r="1518" customFormat="1" spans="1:9">
       <c r="A1518">
-        <v>920107</v>
+        <v>920113</v>
       </c>
       <c r="B1518" s="26">
         <v>1</v>
@@ -47057,6 +47108,7 @@
       <c r="E1518" s="29" t="s">
         <v>767</v>
       </c>
+      <c r="F1518" s="28"/>
       <c r="G1518">
         <v>10</v>
       </c>
@@ -47069,7 +47121,7 @@
     </row>
     <row r="1519" customFormat="1" spans="1:9">
       <c r="A1519">
-        <v>2920107</v>
+        <v>820095</v>
       </c>
       <c r="B1519" s="26">
         <v>1</v>
@@ -47077,11 +47129,11 @@
       <c r="C1519">
         <v>0</v>
       </c>
-      <c r="D1519" s="28" t="s">
+      <c r="D1519" s="30" t="s">
         <v>1120</v>
       </c>
-      <c r="E1519" s="29" t="s">
-        <v>769</v>
+      <c r="E1519" s="30" t="s">
+        <v>1120</v>
       </c>
       <c r="G1519">
         <v>10</v>
@@ -47095,7 +47147,7 @@
     </row>
     <row r="1520" customFormat="1" spans="1:9">
       <c r="A1520">
-        <v>39201057</v>
+        <v>920107</v>
       </c>
       <c r="B1520" s="26">
         <v>1</v>
@@ -47107,7 +47159,7 @@
         <v>1121</v>
       </c>
       <c r="E1520" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1520">
         <v>10</v>
@@ -47121,7 +47173,7 @@
     </row>
     <row r="1521" customFormat="1" spans="1:9">
       <c r="A1521">
-        <v>4920107</v>
+        <v>2920107</v>
       </c>
       <c r="B1521" s="26">
         <v>1</v>
@@ -47142,12 +47194,12 @@
         <v>1</v>
       </c>
       <c r="I1521">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1522" customFormat="1" spans="1:9">
       <c r="A1522">
-        <v>6920107</v>
+        <v>39201057</v>
       </c>
       <c r="B1522" s="26">
         <v>1</v>
@@ -47173,7 +47225,7 @@
     </row>
     <row r="1523" customFormat="1" spans="1:9">
       <c r="A1523">
-        <v>7920107</v>
+        <v>4920107</v>
       </c>
       <c r="B1523" s="26">
         <v>1</v>
@@ -47191,15 +47243,15 @@
         <v>10</v>
       </c>
       <c r="H1523">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1523">
-        <v>8000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1524" customFormat="1" spans="1:9">
       <c r="A1524">
-        <v>8920107</v>
+        <v>6920107</v>
       </c>
       <c r="B1524" s="26">
         <v>1</v>
@@ -47225,7 +47277,7 @@
     </row>
     <row r="1525" customFormat="1" spans="1:9">
       <c r="A1525">
-        <v>9920107</v>
+        <v>7920107</v>
       </c>
       <c r="B1525" s="26">
         <v>1</v>
@@ -47251,7 +47303,7 @@
     </row>
     <row r="1526" customFormat="1" spans="1:9">
       <c r="A1526">
-        <v>10920107</v>
+        <v>8920107</v>
       </c>
       <c r="B1526" s="26">
         <v>1</v>
@@ -47272,12 +47324,12 @@
         <v>1</v>
       </c>
       <c r="I1526">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1527" customFormat="1" spans="1:9">
       <c r="A1527">
-        <v>11920107</v>
+        <v>9920107</v>
       </c>
       <c r="B1527" s="26">
         <v>1</v>
@@ -47295,15 +47347,15 @@
         <v>10</v>
       </c>
       <c r="H1527">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1527">
-        <v>500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1528" customFormat="1" spans="1:9">
       <c r="A1528">
-        <v>13920107</v>
+        <v>10920107</v>
       </c>
       <c r="B1528" s="26">
         <v>1</v>
@@ -47324,12 +47376,12 @@
         <v>1</v>
       </c>
       <c r="I1528">
-        <v>1</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1529" customFormat="1" spans="1:9">
       <c r="A1529">
-        <v>920108</v>
+        <v>11920107</v>
       </c>
       <c r="B1529" s="26">
         <v>1</v>
@@ -47341,7 +47393,7 @@
         <v>1130</v>
       </c>
       <c r="E1529" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1529">
         <v>10</v>
@@ -47350,12 +47402,12 @@
         <v>1</v>
       </c>
       <c r="I1529">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1530" customFormat="1" spans="1:9">
       <c r="A1530">
-        <v>2920108</v>
+        <v>13920107</v>
       </c>
       <c r="B1530" s="26">
         <v>1</v>
@@ -47376,12 +47428,12 @@
         <v>1</v>
       </c>
       <c r="I1530">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1531" customFormat="1" spans="1:9">
       <c r="A1531">
-        <v>3920108</v>
+        <v>820098</v>
       </c>
       <c r="B1531" s="26">
         <v>1</v>
@@ -47389,11 +47441,11 @@
       <c r="C1531">
         <v>0</v>
       </c>
-      <c r="D1531" s="28" t="s">
+      <c r="D1531" s="30" t="s">
         <v>1132</v>
       </c>
-      <c r="E1531" s="29" t="s">
-        <v>769</v>
+      <c r="E1531" s="30" t="s">
+        <v>1044</v>
       </c>
       <c r="G1531">
         <v>10</v>
@@ -47407,7 +47459,7 @@
     </row>
     <row r="1532" customFormat="1" spans="1:9">
       <c r="A1532">
-        <v>4920108</v>
+        <v>920108</v>
       </c>
       <c r="B1532" s="26">
         <v>1</v>
@@ -47419,7 +47471,7 @@
         <v>1133</v>
       </c>
       <c r="E1532" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1532">
         <v>10</v>
@@ -47428,12 +47480,12 @@
         <v>1</v>
       </c>
       <c r="I1532">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1533" customFormat="1" spans="1:9">
       <c r="A1533">
-        <v>6920108</v>
+        <v>2920108</v>
       </c>
       <c r="B1533" s="26">
         <v>1</v>
@@ -47459,7 +47511,7 @@
     </row>
     <row r="1534" customFormat="1" spans="1:9">
       <c r="A1534">
-        <v>7920108</v>
+        <v>3920108</v>
       </c>
       <c r="B1534" s="26">
         <v>1</v>
@@ -47477,7 +47529,7 @@
         <v>10</v>
       </c>
       <c r="H1534">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1534">
         <v>0</v>
@@ -47485,7 +47537,7 @@
     </row>
     <row r="1535" customFormat="1" spans="1:9">
       <c r="A1535">
-        <v>8920108</v>
+        <v>4920108</v>
       </c>
       <c r="B1535" s="26">
         <v>1</v>
@@ -47506,12 +47558,12 @@
         <v>1</v>
       </c>
       <c r="I1535">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1536" customFormat="1" spans="1:9">
       <c r="A1536">
-        <v>9920108</v>
+        <v>6920108</v>
       </c>
       <c r="B1536" s="26">
         <v>1</v>
@@ -47529,7 +47581,7 @@
         <v>10</v>
       </c>
       <c r="H1536">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1536">
         <v>0</v>
@@ -47537,7 +47589,7 @@
     </row>
     <row r="1537" customFormat="1" spans="1:9">
       <c r="A1537">
-        <v>13920108</v>
+        <v>7920108</v>
       </c>
       <c r="B1537" s="26">
         <v>1</v>
@@ -47555,15 +47607,15 @@
         <v>10</v>
       </c>
       <c r="H1537">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1537">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1538" customFormat="1" spans="1:9">
       <c r="A1538">
-        <v>920109</v>
+        <v>8920108</v>
       </c>
       <c r="B1538" s="26">
         <v>1</v>
@@ -47575,7 +47627,7 @@
         <v>1139</v>
       </c>
       <c r="E1538" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1538">
         <v>10</v>
@@ -47589,7 +47641,7 @@
     </row>
     <row r="1539" customFormat="1" spans="1:9">
       <c r="A1539">
-        <v>2920109</v>
+        <v>9920108</v>
       </c>
       <c r="B1539" s="26">
         <v>1</v>
@@ -47607,7 +47659,7 @@
         <v>10</v>
       </c>
       <c r="H1539">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1539">
         <v>0</v>
@@ -47615,7 +47667,7 @@
     </row>
     <row r="1540" customFormat="1" spans="1:9">
       <c r="A1540">
-        <v>3920109</v>
+        <v>13920108</v>
       </c>
       <c r="B1540" s="26">
         <v>1</v>
@@ -47636,12 +47688,12 @@
         <v>1</v>
       </c>
       <c r="I1540">
-        <v>6000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1541" customFormat="1" spans="1:9">
       <c r="A1541">
-        <v>4920109</v>
+        <v>920109</v>
       </c>
       <c r="B1541" s="26">
         <v>1</v>
@@ -47653,7 +47705,7 @@
         <v>1142</v>
       </c>
       <c r="E1541" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1541">
         <v>10</v>
@@ -47662,12 +47714,12 @@
         <v>1</v>
       </c>
       <c r="I1541">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1542" customFormat="1" spans="1:9">
       <c r="A1542">
-        <v>6920109</v>
+        <v>2920109</v>
       </c>
       <c r="B1542" s="26">
         <v>1</v>
@@ -47693,7 +47745,7 @@
     </row>
     <row r="1543" customFormat="1" spans="1:9">
       <c r="A1543">
-        <v>7920109</v>
+        <v>3920109</v>
       </c>
       <c r="B1543" s="26">
         <v>1</v>
@@ -47711,15 +47763,15 @@
         <v>10</v>
       </c>
       <c r="H1543">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1543">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1544" customFormat="1" spans="1:9">
       <c r="A1544">
-        <v>8920109</v>
+        <v>4920109</v>
       </c>
       <c r="B1544" s="26">
         <v>1</v>
@@ -47740,12 +47792,12 @@
         <v>1</v>
       </c>
       <c r="I1544">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1545" customFormat="1" spans="1:9">
       <c r="A1545">
-        <v>9920109</v>
+        <v>6920109</v>
       </c>
       <c r="B1545" s="26">
         <v>1</v>
@@ -47763,7 +47815,7 @@
         <v>10</v>
       </c>
       <c r="H1545">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1545">
         <v>0</v>
@@ -47771,7 +47823,7 @@
     </row>
     <row r="1546" customFormat="1" spans="1:9">
       <c r="A1546">
-        <v>13920109</v>
+        <v>7920109</v>
       </c>
       <c r="B1546" s="26">
         <v>1</v>
@@ -47789,15 +47841,15 @@
         <v>10</v>
       </c>
       <c r="H1546">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1546">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1547" customFormat="1" spans="1:9">
       <c r="A1547">
-        <v>920110</v>
+        <v>8920109</v>
       </c>
       <c r="B1547" s="26">
         <v>1</v>
@@ -47809,7 +47861,7 @@
         <v>1148</v>
       </c>
       <c r="E1547" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1547">
         <v>10</v>
@@ -47823,7 +47875,7 @@
     </row>
     <row r="1548" customFormat="1" spans="1:9">
       <c r="A1548">
-        <v>1920110</v>
+        <v>9920109</v>
       </c>
       <c r="B1548" s="26">
         <v>1</v>
@@ -47841,15 +47893,15 @@
         <v>10</v>
       </c>
       <c r="H1548">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1548">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1549" customFormat="1" spans="1:9">
       <c r="A1549">
-        <v>2920110</v>
+        <v>13920109</v>
       </c>
       <c r="B1549" s="26">
         <v>1</v>
@@ -47870,12 +47922,12 @@
         <v>1</v>
       </c>
       <c r="I1549">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1550" customFormat="1" spans="1:9">
       <c r="A1550">
-        <v>3920110</v>
+        <v>16920101</v>
       </c>
       <c r="B1550" s="26">
         <v>1</v>
@@ -47889,6 +47941,7 @@
       <c r="E1550" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1550" s="28"/>
       <c r="G1550">
         <v>10</v>
       </c>
@@ -47896,12 +47949,12 @@
         <v>1</v>
       </c>
       <c r="I1550">
-        <v>6000</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1551" customFormat="1" spans="1:9">
       <c r="A1551">
-        <v>4920110</v>
+        <v>920110</v>
       </c>
       <c r="B1551" s="26">
         <v>1</v>
@@ -47913,7 +47966,7 @@
         <v>1152</v>
       </c>
       <c r="E1551" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1551">
         <v>10</v>
@@ -47922,12 +47975,12 @@
         <v>1</v>
       </c>
       <c r="I1551">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1552" customFormat="1" spans="1:9">
       <c r="A1552">
-        <v>6920110</v>
+        <v>1920110</v>
       </c>
       <c r="B1552" s="26">
         <v>1</v>
@@ -47948,12 +48001,12 @@
         <v>1</v>
       </c>
       <c r="I1552">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1553" customFormat="1" spans="1:9">
       <c r="A1553">
-        <v>7920110</v>
+        <v>2920110</v>
       </c>
       <c r="B1553" s="26">
         <v>1</v>
@@ -47971,15 +48024,15 @@
         <v>10</v>
       </c>
       <c r="H1553">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1553">
-        <v>24000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1554" customFormat="1" spans="1:9">
       <c r="A1554">
-        <v>8920110</v>
+        <v>3920110</v>
       </c>
       <c r="B1554" s="26">
         <v>1</v>
@@ -48000,12 +48053,12 @@
         <v>1</v>
       </c>
       <c r="I1554">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1555" customFormat="1" spans="1:9">
       <c r="A1555">
-        <v>9920110</v>
+        <v>4920110</v>
       </c>
       <c r="B1555" s="26">
         <v>1</v>
@@ -48023,15 +48076,15 @@
         <v>10</v>
       </c>
       <c r="H1555">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1555">
-        <v>24000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1556" customFormat="1" spans="1:9">
       <c r="A1556">
-        <v>13920110</v>
+        <v>6920110</v>
       </c>
       <c r="B1556" s="26">
         <v>1</v>
@@ -48052,12 +48105,12 @@
         <v>1</v>
       </c>
       <c r="I1556">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1557" customFormat="1" spans="1:9">
       <c r="A1557">
-        <v>920111</v>
+        <v>7920110</v>
       </c>
       <c r="B1557" s="26">
         <v>1</v>
@@ -48069,21 +48122,21 @@
         <v>1158</v>
       </c>
       <c r="E1557" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1557">
         <v>10</v>
       </c>
       <c r="H1557">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1557">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1558" customFormat="1" spans="1:9">
       <c r="A1558">
-        <v>1920111</v>
+        <v>8920110</v>
       </c>
       <c r="B1558" s="26">
         <v>1</v>
@@ -48104,12 +48157,12 @@
         <v>1</v>
       </c>
       <c r="I1558">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1559" customFormat="1" spans="1:9">
       <c r="A1559">
-        <v>2920111</v>
+        <v>9920110</v>
       </c>
       <c r="B1559" s="26">
         <v>1</v>
@@ -48127,15 +48180,15 @@
         <v>10</v>
       </c>
       <c r="H1559">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1559">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1560" customFormat="1" spans="1:9">
       <c r="A1560">
-        <v>3920111</v>
+        <v>13920110</v>
       </c>
       <c r="B1560" s="26">
         <v>1</v>
@@ -48156,12 +48209,12 @@
         <v>1</v>
       </c>
       <c r="I1560">
-        <v>6000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1561" customFormat="1" spans="1:9">
       <c r="A1561">
-        <v>492011</v>
+        <v>920115</v>
       </c>
       <c r="B1561" s="26">
         <v>1</v>
@@ -48173,8 +48226,9 @@
         <v>1162</v>
       </c>
       <c r="E1561" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1561" s="28"/>
       <c r="G1561">
         <v>10</v>
       </c>
@@ -48182,12 +48236,12 @@
         <v>1</v>
       </c>
       <c r="I1561">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1562" customFormat="1" spans="1:9">
       <c r="A1562">
-        <v>6920111</v>
+        <v>820096</v>
       </c>
       <c r="B1562" s="26">
         <v>1</v>
@@ -48195,11 +48249,11 @@
       <c r="C1562">
         <v>0</v>
       </c>
-      <c r="D1562" s="28" t="s">
+      <c r="D1562" s="30" t="s">
         <v>1163</v>
       </c>
-      <c r="E1562" s="29" t="s">
-        <v>769</v>
+      <c r="E1562" s="30" t="s">
+        <v>1120</v>
       </c>
       <c r="G1562">
         <v>10</v>
@@ -48213,7 +48267,7 @@
     </row>
     <row r="1563" customFormat="1" spans="1:9">
       <c r="A1563">
-        <v>7920111</v>
+        <v>920116</v>
       </c>
       <c r="B1563" s="26">
         <v>1</v>
@@ -48225,21 +48279,22 @@
         <v>1164</v>
       </c>
       <c r="E1563" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1563" s="28"/>
       <c r="G1563">
         <v>10</v>
       </c>
       <c r="H1563">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1563">
-        <v>24000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1564" customFormat="1" spans="1:9">
       <c r="A1564">
-        <v>8920111</v>
+        <v>820097</v>
       </c>
       <c r="B1564" s="26">
         <v>1</v>
@@ -48247,11 +48302,11 @@
       <c r="C1564">
         <v>0</v>
       </c>
-      <c r="D1564" s="28" t="s">
+      <c r="D1564" s="30" t="s">
         <v>1165</v>
       </c>
-      <c r="E1564" s="29" t="s">
-        <v>769</v>
+      <c r="E1564" s="30" t="s">
+        <v>1120</v>
       </c>
       <c r="G1564">
         <v>10</v>
@@ -48265,7 +48320,7 @@
     </row>
     <row r="1565" customFormat="1" spans="1:9">
       <c r="A1565">
-        <v>9920111</v>
+        <v>920111</v>
       </c>
       <c r="B1565" s="26">
         <v>1</v>
@@ -48277,21 +48332,21 @@
         <v>1166</v>
       </c>
       <c r="E1565" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1565">
         <v>10</v>
       </c>
       <c r="H1565">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1565">
-        <v>24000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1566" customFormat="1" spans="1:9">
       <c r="A1566">
-        <v>10920111</v>
+        <v>1920111</v>
       </c>
       <c r="B1566" s="26">
         <v>1</v>
@@ -48312,12 +48367,12 @@
         <v>1</v>
       </c>
       <c r="I1566">
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1567" customFormat="1" spans="1:9">
       <c r="A1567">
-        <v>11920111</v>
+        <v>2920111</v>
       </c>
       <c r="B1567" s="26">
         <v>1</v>
@@ -48338,12 +48393,12 @@
         <v>1</v>
       </c>
       <c r="I1567">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1568" customFormat="1" spans="1:9">
       <c r="A1568">
-        <v>13920111</v>
+        <v>3920111</v>
       </c>
       <c r="B1568" s="26">
         <v>1</v>
@@ -48364,12 +48419,12 @@
         <v>1</v>
       </c>
       <c r="I1568">
-        <v>1</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1569" customFormat="1" spans="1:9">
       <c r="A1569">
-        <v>920112</v>
+        <v>492011</v>
       </c>
       <c r="B1569" s="26">
         <v>1</v>
@@ -48381,7 +48436,7 @@
         <v>1170</v>
       </c>
       <c r="E1569" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1569">
         <v>10</v>
@@ -48390,12 +48445,12 @@
         <v>1</v>
       </c>
       <c r="I1569">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1570" customFormat="1" spans="1:9">
       <c r="A1570">
-        <v>1920112</v>
+        <v>6920111</v>
       </c>
       <c r="B1570" s="26">
         <v>1</v>
@@ -48416,12 +48471,12 @@
         <v>1</v>
       </c>
       <c r="I1570">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1571" customFormat="1" spans="1:9">
       <c r="A1571">
-        <v>2920112</v>
+        <v>7920111</v>
       </c>
       <c r="B1571" s="26">
         <v>1</v>
@@ -48439,15 +48494,15 @@
         <v>10</v>
       </c>
       <c r="H1571">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1571">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1572" customFormat="1" spans="1:9">
       <c r="A1572">
-        <v>3920112</v>
+        <v>8920111</v>
       </c>
       <c r="B1572" s="26">
         <v>1</v>
@@ -48468,12 +48523,12 @@
         <v>1</v>
       </c>
       <c r="I1572">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1573" customFormat="1" spans="1:9">
       <c r="A1573">
-        <v>4920112</v>
+        <v>9920111</v>
       </c>
       <c r="B1573" s="26">
         <v>1</v>
@@ -48491,15 +48546,15 @@
         <v>10</v>
       </c>
       <c r="H1573">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1573">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1574" customFormat="1" spans="1:9">
       <c r="A1574">
-        <v>6920112</v>
+        <v>10920111</v>
       </c>
       <c r="B1574" s="26">
         <v>1</v>
@@ -48520,12 +48575,12 @@
         <v>1</v>
       </c>
       <c r="I1574">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1575" customFormat="1" spans="1:9">
       <c r="A1575">
-        <v>7920112</v>
+        <v>11920111</v>
       </c>
       <c r="B1575" s="26">
         <v>1</v>
@@ -48543,15 +48598,15 @@
         <v>10</v>
       </c>
       <c r="H1575">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1575">
-        <v>24000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1576" customFormat="1" spans="1:9">
       <c r="A1576">
-        <v>8920112</v>
+        <v>13920111</v>
       </c>
       <c r="B1576" s="26">
         <v>1</v>
@@ -48572,12 +48627,12 @@
         <v>1</v>
       </c>
       <c r="I1576">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1577" customFormat="1" spans="1:9">
       <c r="A1577">
-        <v>9920112</v>
+        <v>920118</v>
       </c>
       <c r="B1577" s="26">
         <v>1</v>
@@ -48589,42 +48644,501 @@
         <v>1178</v>
       </c>
       <c r="E1577" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1577" s="28"/>
       <c r="G1577">
         <v>10</v>
       </c>
       <c r="H1577">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1577">
-        <v>24000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1578" customFormat="1" spans="1:9">
       <c r="A1578">
+        <v>820100</v>
+      </c>
+      <c r="B1578" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1578">
+        <v>0</v>
+      </c>
+      <c r="D1578" s="30" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E1578" s="30" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G1578">
+        <v>10</v>
+      </c>
+      <c r="H1578">
+        <v>1</v>
+      </c>
+      <c r="I1578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579" customFormat="1" spans="1:9">
+      <c r="A1579">
+        <v>920112</v>
+      </c>
+      <c r="B1579" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1579">
+        <v>0</v>
+      </c>
+      <c r="D1579" s="28" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E1579" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="G1579">
+        <v>10</v>
+      </c>
+      <c r="H1579">
+        <v>1</v>
+      </c>
+      <c r="I1579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580" customFormat="1" spans="1:9">
+      <c r="A1580">
+        <v>1920112</v>
+      </c>
+      <c r="B1580" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1580">
+        <v>0</v>
+      </c>
+      <c r="D1580" s="28" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E1580" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1580">
+        <v>10</v>
+      </c>
+      <c r="H1580">
+        <v>1</v>
+      </c>
+      <c r="I1580">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1581" customFormat="1" spans="1:9">
+      <c r="A1581">
+        <v>2920112</v>
+      </c>
+      <c r="B1581" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1581">
+        <v>0</v>
+      </c>
+      <c r="D1581" s="28" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E1581" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1581">
+        <v>10</v>
+      </c>
+      <c r="H1581">
+        <v>1</v>
+      </c>
+      <c r="I1581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1582" customFormat="1" spans="1:9">
+      <c r="A1582">
+        <v>3920112</v>
+      </c>
+      <c r="B1582" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1582">
+        <v>0</v>
+      </c>
+      <c r="D1582" s="28" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E1582" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1582">
+        <v>10</v>
+      </c>
+      <c r="H1582">
+        <v>1</v>
+      </c>
+      <c r="I1582">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1583" customFormat="1" spans="1:9">
+      <c r="A1583">
+        <v>4920112</v>
+      </c>
+      <c r="B1583" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1583">
+        <v>0</v>
+      </c>
+      <c r="D1583" s="28" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E1583" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1583">
+        <v>10</v>
+      </c>
+      <c r="H1583">
+        <v>1</v>
+      </c>
+      <c r="I1583">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="1584" customFormat="1" spans="1:9">
+      <c r="A1584">
+        <v>6920112</v>
+      </c>
+      <c r="B1584" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1584">
+        <v>0</v>
+      </c>
+      <c r="D1584" s="28" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E1584" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1584">
+        <v>10</v>
+      </c>
+      <c r="H1584">
+        <v>1</v>
+      </c>
+      <c r="I1584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1585" customFormat="1" spans="1:9">
+      <c r="A1585">
+        <v>7920112</v>
+      </c>
+      <c r="B1585" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1585">
+        <v>0</v>
+      </c>
+      <c r="D1585" s="28" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E1585" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1585">
+        <v>10</v>
+      </c>
+      <c r="H1585">
+        <v>2</v>
+      </c>
+      <c r="I1585">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="1586" customFormat="1" spans="1:9">
+      <c r="A1586">
+        <v>8920112</v>
+      </c>
+      <c r="B1586" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1586">
+        <v>0</v>
+      </c>
+      <c r="D1586" s="28" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E1586" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1586">
+        <v>10</v>
+      </c>
+      <c r="H1586">
+        <v>1</v>
+      </c>
+      <c r="I1586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1587" customFormat="1" spans="1:9">
+      <c r="A1587">
+        <v>9920112</v>
+      </c>
+      <c r="B1587" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1587">
+        <v>0</v>
+      </c>
+      <c r="D1587" s="28" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E1587" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1587">
+        <v>10</v>
+      </c>
+      <c r="H1587">
+        <v>2</v>
+      </c>
+      <c r="I1587">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="1588" customFormat="1" spans="1:9">
+      <c r="A1588">
         <v>13920112</v>
       </c>
-      <c r="B1578" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1578">
-        <v>0</v>
-      </c>
-      <c r="D1578" s="28" t="s">
-        <v>1179</v>
-      </c>
-      <c r="E1578" s="29" t="s">
+      <c r="B1588" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1588">
+        <v>0</v>
+      </c>
+      <c r="D1588" s="28" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1588" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="G1578">
-        <v>10</v>
-      </c>
-      <c r="H1578">
-        <v>1</v>
-      </c>
-      <c r="I1578">
-        <v>1</v>
+      <c r="G1588">
+        <v>10</v>
+      </c>
+      <c r="H1588">
+        <v>1</v>
+      </c>
+      <c r="I1588">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1589" customFormat="1" spans="1:9">
+      <c r="A1589">
+        <v>920117</v>
+      </c>
+      <c r="B1589" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1589">
+        <v>0</v>
+      </c>
+      <c r="D1589" s="28" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E1589" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1589" s="28"/>
+      <c r="G1589">
+        <v>10</v>
+      </c>
+      <c r="H1589">
+        <v>1</v>
+      </c>
+      <c r="I1589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1590" customFormat="1" spans="1:9">
+      <c r="A1590">
+        <v>820099</v>
+      </c>
+      <c r="B1590" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1590">
+        <v>0</v>
+      </c>
+      <c r="D1590" s="30" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1590" s="30" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G1590">
+        <v>10</v>
+      </c>
+      <c r="H1590">
+        <v>1</v>
+      </c>
+      <c r="I1590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:9">
+      <c r="A1591" s="26">
+        <v>5101721</v>
+      </c>
+      <c r="B1591" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1591" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1591" s="27" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E1591" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1591" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1591" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1591" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:9">
+      <c r="A1592" s="26">
+        <v>5101722</v>
+      </c>
+      <c r="B1592" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1592" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1592" s="27" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1592" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1592" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1592" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1592" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:9">
+      <c r="A1593" s="26">
+        <v>5101723</v>
+      </c>
+      <c r="B1593" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1593" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1593" s="27" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E1593" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1593" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1593" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1593" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:9">
+      <c r="A1594" s="26">
+        <v>5101724</v>
+      </c>
+      <c r="B1594" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1594" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1594" s="27" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E1594" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1594" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1594" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1594" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:9">
+      <c r="A1595" s="26">
+        <v>5101725</v>
+      </c>
+      <c r="B1595" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1595" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1595" s="27" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1595" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1595" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1595" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1595" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1595">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -48689,7 +49203,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -48701,10 +49215,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -48718,90 +49232,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1181</v>
+        <v>1198</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1182</v>
+        <v>1199</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1184</v>
+        <v>1201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1185</v>
+        <v>1202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1186</v>
+        <v>1203</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1188</v>
+        <v>1205</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1189</v>
+        <v>1206</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1190</v>
+        <v>1207</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1191</v>
+        <v>1208</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1194</v>
+        <v>1211</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1195</v>
+        <v>1212</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1196</v>
+        <v>1213</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1197</v>
+        <v>1214</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1198</v>
+        <v>1215</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1199</v>
+        <v>1216</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1200</v>
+        <v>1217</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1201</v>
+        <v>1218</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1202</v>
+        <v>1219</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>1203</v>
+        <v>1220</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>1204</v>
+        <v>1221</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>1205</v>
+        <v>1222</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>1206</v>
+        <v>1223</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>1196</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -48812,7 +49326,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1207</v>
+        <v>1224</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -48833,7 +49347,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1208</v>
+        <v>1225</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -48845,7 +49359,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1209</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -48856,7 +49370,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1210</v>
+        <v>1227</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -48897,7 +49411,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1211</v>
+        <v>1228</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -48938,7 +49452,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1212</v>
+        <v>1229</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -48959,7 +49473,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1213</v>
+        <v>1230</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -48971,7 +49485,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1214</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -48982,7 +49496,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1215</v>
+        <v>1232</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49003,7 +49517,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1216</v>
+        <v>1233</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49015,7 +49529,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1217</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49026,7 +49540,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1218</v>
+        <v>1235</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49047,7 +49561,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1219</v>
+        <v>1236</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -37644,7 +37644,7 @@
         <v>1</v>
       </c>
       <c r="I1159">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1160" spans="1:9">
@@ -37696,7 +37696,7 @@
         <v>2</v>
       </c>
       <c r="I1161">
-        <v>15000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1162" spans="1:9">
@@ -37748,7 +37748,7 @@
         <v>2</v>
       </c>
       <c r="I1163">
-        <v>15000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1164" spans="1:9">
@@ -37853,7 +37853,7 @@
         <v>1</v>
       </c>
       <c r="I1167">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1168" spans="1:9">
@@ -37931,7 +37931,7 @@
         <v>1</v>
       </c>
       <c r="I1170">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1171" spans="1:9">
@@ -38217,7 +38217,7 @@
         <v>1</v>
       </c>
       <c r="I1181">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1182" spans="1:9">
@@ -38295,7 +38295,7 @@
         <v>2</v>
       </c>
       <c r="I1184">
-        <v>14000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="1185" spans="1:9">
@@ -38347,7 +38347,7 @@
         <v>2</v>
       </c>
       <c r="I1186">
-        <v>14000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="1187" spans="1:9">
@@ -38719,7 +38719,7 @@
         <v>1</v>
       </c>
       <c r="I1200">
-        <v>4500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1201" spans="1:9">
@@ -38797,7 +38797,7 @@
         <v>2</v>
       </c>
       <c r="I1203">
-        <v>15500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1204" spans="1:9">
@@ -38849,7 +38849,7 @@
         <v>2</v>
       </c>
       <c r="I1205">
-        <v>15500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1206" spans="1:9">
@@ -39086,7 +39086,7 @@
         <v>1</v>
       </c>
       <c r="I1214">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1215" spans="1:9">
@@ -39478,7 +39478,7 @@
         <v>2</v>
       </c>
       <c r="I1229">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1230" spans="1:9">
@@ -39530,7 +39530,7 @@
         <v>2</v>
       </c>
       <c r="I1231">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1232" spans="1:9">
@@ -39584,7 +39584,7 @@
         <v>1</v>
       </c>
       <c r="I1233">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1234" spans="1:9">
@@ -40089,7 +40089,7 @@
         <v>2</v>
       </c>
       <c r="I1252">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1253" spans="1:9">
@@ -40141,7 +40141,7 @@
         <v>2</v>
       </c>
       <c r="I1254">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1255" spans="1:9">
@@ -40384,7 +40384,7 @@
         <v>1</v>
       </c>
       <c r="I1263">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1264" spans="1:9">
@@ -41123,7 +41123,7 @@
         <v>2</v>
       </c>
       <c r="I1291">
-        <v>12000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1292" spans="1:9">
@@ -41175,7 +41175,7 @@
         <v>2</v>
       </c>
       <c r="I1293">
-        <v>12000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1294" spans="1:9">
@@ -41462,7 +41462,7 @@
         <v>2</v>
       </c>
       <c r="I1304">
-        <v>12000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1305" spans="1:9">
@@ -41514,7 +41514,7 @@
         <v>2</v>
       </c>
       <c r="I1306">
-        <v>12000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1307" spans="1:9">
@@ -42098,7 +42098,7 @@
         <v>1</v>
       </c>
       <c r="I1328">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1329" spans="1:9">
@@ -42411,7 +42411,7 @@
         <v>1</v>
       </c>
       <c r="I1340">
-        <v>1600</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1341" spans="1:9">
@@ -42489,7 +42489,7 @@
         <v>2</v>
       </c>
       <c r="I1343">
-        <v>24000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1344" spans="1:9">
@@ -42541,7 +42541,7 @@
         <v>2</v>
       </c>
       <c r="I1345">
-        <v>24000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1346" spans="1:9">
@@ -43278,7 +43278,7 @@
         <v>2</v>
       </c>
       <c r="I1372">
-        <v>22000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1373" spans="1:9">
@@ -43330,7 +43330,7 @@
         <v>2</v>
       </c>
       <c r="I1374">
-        <v>22000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1375" spans="1:9">
@@ -43876,7 +43876,7 @@
         <v>1</v>
       </c>
       <c r="I1395">
-        <v>2200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1396" spans="1:9">
@@ -44268,7 +44268,7 @@
         <v>2</v>
       </c>
       <c r="I1410">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1411" spans="1:9">
@@ -44320,7 +44320,7 @@
         <v>2</v>
       </c>
       <c r="I1412">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1413" spans="1:9">
@@ -44609,7 +44609,7 @@
         <v>2</v>
       </c>
       <c r="I1423">
-        <v>4000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="1424" spans="1:9">
@@ -44661,7 +44661,7 @@
         <v>2</v>
       </c>
       <c r="I1425">
-        <v>4000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="1426" spans="1:9">
@@ -45573,7 +45573,7 @@
         <v>2</v>
       </c>
       <c r="I1460">
-        <v>12000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1461" spans="1:9">
@@ -45625,7 +45625,7 @@
         <v>2</v>
       </c>
       <c r="I1462">
-        <v>12000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1463" spans="1:9">
@@ -45651,7 +45651,7 @@
         <v>1</v>
       </c>
       <c r="I1463">
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1464" spans="1:9">
@@ -45833,7 +45833,7 @@
         <v>1</v>
       </c>
       <c r="I1470">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1471" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="1237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="1241">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1661,7 +1661,7 @@
     <t>普攻概率附加麻痹</t>
   </si>
   <si>
-    <t>击杀回血</t>
+    <t>血瓶恢复效果</t>
   </si>
   <si>
     <t>攻击击中回血</t>
@@ -3512,6 +3512,9 @@
     <t>毒沼_技能等级</t>
   </si>
   <si>
+    <t>传染_获得</t>
+  </si>
+  <si>
     <t>传染被动_获得</t>
   </si>
   <si>
@@ -3551,9 +3554,15 @@
     <t>毒雨_技能等级</t>
   </si>
   <si>
+    <t>毒雨被动_获得</t>
+  </si>
+  <si>
     <t>毒雨被动-逻辑id</t>
   </si>
   <si>
+    <t>毒雨对自身被动-逻辑id</t>
+  </si>
+  <si>
     <t>毒刃_获得</t>
   </si>
   <si>
@@ -3645,6 +3654,9 @@
   </si>
   <si>
     <t>毒性爆发被动-逻辑id</t>
+  </si>
+  <si>
+    <t>精神错乱_获得</t>
   </si>
   <si>
     <t>精神错乱被动_获得</t>
@@ -4157,7 +4169,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799584948271126"/>
+        <fgColor theme="9" tint="0.79955442976165"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4193,7 +4205,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799584948271126"/>
+        <fgColor theme="4" tint="0.79955442976165"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5075,7 +5087,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1595"/>
+  <dimension ref="A1:I1599"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -37644,7 +37656,7 @@
         <v>1</v>
       </c>
       <c r="I1159">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1160" spans="1:9">
@@ -37696,7 +37708,7 @@
         <v>2</v>
       </c>
       <c r="I1161">
-        <v>16000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1162" spans="1:9">
@@ -37748,7 +37760,7 @@
         <v>2</v>
       </c>
       <c r="I1163">
-        <v>16000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1164" spans="1:9">
@@ -40089,7 +40101,7 @@
         <v>2</v>
       </c>
       <c r="I1252">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1253" spans="1:9">
@@ -40141,7 +40153,7 @@
         <v>2</v>
       </c>
       <c r="I1254">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1255" spans="1:9">
@@ -40168,7 +40180,7 @@
         <v>1</v>
       </c>
       <c r="I1255">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1256" spans="1:9">
@@ -40195,7 +40207,7 @@
         <v>1</v>
       </c>
       <c r="I1256">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1257" spans="1:9">
@@ -40384,7 +40396,7 @@
         <v>1</v>
       </c>
       <c r="I1263">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1264" spans="1:9">
@@ -40438,7 +40450,7 @@
         <v>2</v>
       </c>
       <c r="I1265">
-        <v>18000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1266" spans="1:9">
@@ -43278,7 +43290,7 @@
         <v>2</v>
       </c>
       <c r="I1372">
-        <v>24000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1373" spans="1:9">
@@ -43330,7 +43342,7 @@
         <v>2</v>
       </c>
       <c r="I1374">
-        <v>24000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1375" spans="1:9">
@@ -43616,7 +43628,7 @@
         <v>2</v>
       </c>
       <c r="I1385">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1386" spans="1:9">
@@ -43668,7 +43680,7 @@
         <v>2</v>
       </c>
       <c r="I1387">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1388" spans="1:9">
@@ -43694,7 +43706,7 @@
         <v>1</v>
       </c>
       <c r="I1388">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1389" spans="1:9">
@@ -46754,7 +46766,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="1505" customFormat="1" spans="1:9">
+    <row r="1505" spans="1:9">
       <c r="A1505">
         <v>920106</v>
       </c>
@@ -46780,7 +46792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1506" customFormat="1" spans="1:9">
+    <row r="1506" spans="1:9">
       <c r="A1506">
         <v>1920106</v>
       </c>
@@ -46806,7 +46818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1507" customFormat="1" spans="1:9">
+    <row r="1507" spans="1:9">
       <c r="A1507">
         <v>2920106</v>
       </c>
@@ -46832,7 +46844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1508" customFormat="1" spans="1:9">
+    <row r="1508" spans="1:9">
       <c r="A1508">
         <v>3920106</v>
       </c>
@@ -46858,7 +46870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1509" customFormat="1" spans="1:9">
+    <row r="1509" spans="1:9">
       <c r="A1509">
         <v>4920106</v>
       </c>
@@ -46884,7 +46896,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1510" customFormat="1" spans="1:9">
+    <row r="1510" spans="1:9">
       <c r="A1510">
         <v>5920106</v>
       </c>
@@ -46910,7 +46922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1511" customFormat="1" spans="1:9">
+    <row r="1511" spans="1:9">
       <c r="A1511">
         <v>6920106</v>
       </c>
@@ -46936,7 +46948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1512" customFormat="1" spans="1:9">
+    <row r="1512" spans="1:9">
       <c r="A1512">
         <v>7920106</v>
       </c>
@@ -46962,7 +46974,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="1513" customFormat="1" spans="1:9">
+    <row r="1513" spans="1:9">
       <c r="A1513">
         <v>8920106</v>
       </c>
@@ -46988,7 +47000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1514" customFormat="1" spans="1:9">
+    <row r="1514" spans="1:9">
       <c r="A1514">
         <v>9920106</v>
       </c>
@@ -47014,7 +47026,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="1515" customFormat="1" spans="1:9">
+    <row r="1515" spans="1:9">
       <c r="A1515">
         <v>10920106</v>
       </c>
@@ -47040,7 +47052,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="1516" customFormat="1" spans="1:9">
+    <row r="1516" spans="1:9">
       <c r="A1516">
         <v>11920106</v>
       </c>
@@ -47066,7 +47078,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="1517" customFormat="1" spans="1:9">
+    <row r="1517" spans="1:9">
       <c r="A1517">
         <v>13920106</v>
       </c>
@@ -47092,9 +47104,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1518" customFormat="1" spans="1:9">
+    <row r="1518" spans="1:9">
       <c r="A1518">
-        <v>920113</v>
+        <v>920115</v>
       </c>
       <c r="B1518" s="26">
         <v>1</v>
@@ -47119,61 +47131,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1519" customFormat="1" spans="1:9">
+    <row r="1519" spans="1:9">
       <c r="A1519">
+        <v>920113</v>
+      </c>
+      <c r="B1519" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1519">
+        <v>0</v>
+      </c>
+      <c r="D1519" s="28" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E1519" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1519" s="28"/>
+      <c r="G1519">
+        <v>10</v>
+      </c>
+      <c r="H1519">
+        <v>1</v>
+      </c>
+      <c r="I1519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:9">
+      <c r="A1520">
         <v>820095</v>
       </c>
-      <c r="B1519" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1519">
-        <v>0</v>
-      </c>
-      <c r="D1519" s="30" t="s">
-        <v>1120</v>
-      </c>
-      <c r="E1519" s="30" t="s">
-        <v>1120</v>
-      </c>
-      <c r="G1519">
-        <v>10</v>
-      </c>
-      <c r="H1519">
-        <v>1</v>
-      </c>
-      <c r="I1519">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1520" customFormat="1" spans="1:9">
-      <c r="A1520">
+      <c r="B1520" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1520">
+        <v>0</v>
+      </c>
+      <c r="D1520" s="30" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E1520" s="30" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G1520">
+        <v>10</v>
+      </c>
+      <c r="H1520">
+        <v>1</v>
+      </c>
+      <c r="I1520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:9">
+      <c r="A1521">
         <v>920107</v>
-      </c>
-      <c r="B1520" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1520">
-        <v>0</v>
-      </c>
-      <c r="D1520" s="28" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E1520" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="G1520">
-        <v>10</v>
-      </c>
-      <c r="H1520">
-        <v>1</v>
-      </c>
-      <c r="I1520">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1521" customFormat="1" spans="1:9">
-      <c r="A1521">
-        <v>2920107</v>
       </c>
       <c r="B1521" s="26">
         <v>1</v>
@@ -47185,7 +47198,7 @@
         <v>1122</v>
       </c>
       <c r="E1521" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1521">
         <v>10</v>
@@ -47197,9 +47210,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1522" customFormat="1" spans="1:9">
+    <row r="1522" spans="1:9">
       <c r="A1522">
-        <v>39201057</v>
+        <v>2920107</v>
       </c>
       <c r="B1522" s="26">
         <v>1</v>
@@ -47223,9 +47236,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1523" customFormat="1" spans="1:9">
+    <row r="1523" spans="1:9">
       <c r="A1523">
-        <v>4920107</v>
+        <v>39201057</v>
       </c>
       <c r="B1523" s="26">
         <v>1</v>
@@ -47246,12 +47259,12 @@
         <v>1</v>
       </c>
       <c r="I1523">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="1524" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:9">
       <c r="A1524">
-        <v>6920107</v>
+        <v>4920107</v>
       </c>
       <c r="B1524" s="26">
         <v>1</v>
@@ -47272,12 +47285,12 @@
         <v>1</v>
       </c>
       <c r="I1524">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1525" customFormat="1" spans="1:9">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:9">
       <c r="A1525">
-        <v>7920107</v>
+        <v>6920107</v>
       </c>
       <c r="B1525" s="26">
         <v>1</v>
@@ -47295,15 +47308,15 @@
         <v>10</v>
       </c>
       <c r="H1525">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1525">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="1526" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:9">
       <c r="A1526">
-        <v>8920107</v>
+        <v>7920107</v>
       </c>
       <c r="B1526" s="26">
         <v>1</v>
@@ -47321,15 +47334,15 @@
         <v>10</v>
       </c>
       <c r="H1526">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1526">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1527" customFormat="1" spans="1:9">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:9">
       <c r="A1527">
-        <v>9920107</v>
+        <v>8920107</v>
       </c>
       <c r="B1527" s="26">
         <v>1</v>
@@ -47347,15 +47360,15 @@
         <v>10</v>
       </c>
       <c r="H1527">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1527">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="1528" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:9">
       <c r="A1528">
-        <v>10920107</v>
+        <v>9920107</v>
       </c>
       <c r="B1528" s="26">
         <v>1</v>
@@ -47373,15 +47386,15 @@
         <v>10</v>
       </c>
       <c r="H1528">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1528">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="1529" customFormat="1" spans="1:9">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:9">
       <c r="A1529">
-        <v>11920107</v>
+        <v>10920107</v>
       </c>
       <c r="B1529" s="26">
         <v>1</v>
@@ -47402,12 +47415,12 @@
         <v>1</v>
       </c>
       <c r="I1529">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="1530" customFormat="1" spans="1:9">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:9">
       <c r="A1530">
-        <v>13920107</v>
+        <v>11920107</v>
       </c>
       <c r="B1530" s="26">
         <v>1</v>
@@ -47428,12 +47441,12 @@
         <v>1</v>
       </c>
       <c r="I1530">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1531" customFormat="1" spans="1:9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:9">
       <c r="A1531">
-        <v>820098</v>
+        <v>13920107</v>
       </c>
       <c r="B1531" s="26">
         <v>1</v>
@@ -47441,11 +47454,11 @@
       <c r="C1531">
         <v>0</v>
       </c>
-      <c r="D1531" s="30" t="s">
+      <c r="D1531" s="28" t="s">
         <v>1132</v>
       </c>
-      <c r="E1531" s="30" t="s">
-        <v>1044</v>
+      <c r="E1531" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1531">
         <v>10</v>
@@ -47454,10 +47467,10 @@
         <v>1</v>
       </c>
       <c r="I1531">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1532" customFormat="1" spans="1:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:9">
       <c r="A1532">
         <v>920108</v>
       </c>
@@ -47473,6 +47486,7 @@
       <c r="E1532" s="29" t="s">
         <v>767</v>
       </c>
+      <c r="F1532" s="28"/>
       <c r="G1532">
         <v>10</v>
       </c>
@@ -47483,9 +47497,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1533" customFormat="1" spans="1:9">
+    <row r="1533" spans="1:9">
       <c r="A1533">
-        <v>2920108</v>
+        <v>820098</v>
       </c>
       <c r="B1533" s="26">
         <v>1</v>
@@ -47493,11 +47507,11 @@
       <c r="C1533">
         <v>0</v>
       </c>
-      <c r="D1533" s="28" t="s">
+      <c r="D1533" s="30" t="s">
         <v>1134</v>
       </c>
-      <c r="E1533" s="29" t="s">
-        <v>769</v>
+      <c r="E1533" s="30" t="s">
+        <v>1134</v>
       </c>
       <c r="G1533">
         <v>10</v>
@@ -47509,9 +47523,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1534" customFormat="1" spans="1:9">
+    <row r="1534" spans="1:9">
       <c r="A1534">
-        <v>3920108</v>
+        <v>820110</v>
       </c>
       <c r="B1534" s="26">
         <v>1</v>
@@ -47519,11 +47533,11 @@
       <c r="C1534">
         <v>0</v>
       </c>
-      <c r="D1534" s="28" t="s">
+      <c r="D1534" s="30" t="s">
         <v>1135</v>
       </c>
-      <c r="E1534" s="29" t="s">
-        <v>769</v>
+      <c r="E1534" s="30" t="s">
+        <v>1134</v>
       </c>
       <c r="G1534">
         <v>10</v>
@@ -47535,9 +47549,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1535" customFormat="1" spans="1:9">
+    <row r="1535" spans="1:9">
       <c r="A1535">
-        <v>4920108</v>
+        <v>920108</v>
       </c>
       <c r="B1535" s="26">
         <v>1</v>
@@ -47549,7 +47563,7 @@
         <v>1136</v>
       </c>
       <c r="E1535" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1535">
         <v>10</v>
@@ -47558,12 +47572,12 @@
         <v>1</v>
       </c>
       <c r="I1535">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="1536" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:9">
       <c r="A1536">
-        <v>6920108</v>
+        <v>2920108</v>
       </c>
       <c r="B1536" s="26">
         <v>1</v>
@@ -47587,9 +47601,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1537" customFormat="1" spans="1:9">
+    <row r="1537" spans="1:9">
       <c r="A1537">
-        <v>7920108</v>
+        <v>3920108</v>
       </c>
       <c r="B1537" s="26">
         <v>1</v>
@@ -47607,15 +47621,15 @@
         <v>10</v>
       </c>
       <c r="H1537">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1537">
         <v>0</v>
       </c>
     </row>
-    <row r="1538" customFormat="1" spans="1:9">
+    <row r="1538" spans="1:9">
       <c r="A1538">
-        <v>8920108</v>
+        <v>4920108</v>
       </c>
       <c r="B1538" s="26">
         <v>1</v>
@@ -47636,12 +47650,12 @@
         <v>1</v>
       </c>
       <c r="I1538">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1539" customFormat="1" spans="1:9">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:9">
       <c r="A1539">
-        <v>9920108</v>
+        <v>6920108</v>
       </c>
       <c r="B1539" s="26">
         <v>1</v>
@@ -47659,15 +47673,15 @@
         <v>10</v>
       </c>
       <c r="H1539">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1539">
         <v>0</v>
       </c>
     </row>
-    <row r="1540" customFormat="1" spans="1:9">
+    <row r="1540" spans="1:9">
       <c r="A1540">
-        <v>13920108</v>
+        <v>7920108</v>
       </c>
       <c r="B1540" s="26">
         <v>1</v>
@@ -47685,15 +47699,15 @@
         <v>10</v>
       </c>
       <c r="H1540">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1540">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1541" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:9">
       <c r="A1541">
-        <v>920109</v>
+        <v>8920108</v>
       </c>
       <c r="B1541" s="26">
         <v>1</v>
@@ -47705,7 +47719,7 @@
         <v>1142</v>
       </c>
       <c r="E1541" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1541">
         <v>10</v>
@@ -47717,9 +47731,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1542" customFormat="1" spans="1:9">
+    <row r="1542" spans="1:9">
       <c r="A1542">
-        <v>2920109</v>
+        <v>9920108</v>
       </c>
       <c r="B1542" s="26">
         <v>1</v>
@@ -47737,15 +47751,15 @@
         <v>10</v>
       </c>
       <c r="H1542">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1542">
         <v>0</v>
       </c>
     </row>
-    <row r="1543" customFormat="1" spans="1:9">
+    <row r="1543" spans="1:9">
       <c r="A1543">
-        <v>3920109</v>
+        <v>13920108</v>
       </c>
       <c r="B1543" s="26">
         <v>1</v>
@@ -47766,12 +47780,12 @@
         <v>1</v>
       </c>
       <c r="I1543">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="1544" customFormat="1" spans="1:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:9">
       <c r="A1544">
-        <v>4920109</v>
+        <v>920109</v>
       </c>
       <c r="B1544" s="26">
         <v>1</v>
@@ -47783,7 +47797,7 @@
         <v>1145</v>
       </c>
       <c r="E1544" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1544">
         <v>10</v>
@@ -47792,12 +47806,12 @@
         <v>1</v>
       </c>
       <c r="I1544">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="1545" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:9">
       <c r="A1545">
-        <v>6920109</v>
+        <v>2920109</v>
       </c>
       <c r="B1545" s="26">
         <v>1</v>
@@ -47821,9 +47835,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1546" customFormat="1" spans="1:9">
+    <row r="1546" spans="1:9">
       <c r="A1546">
-        <v>7920109</v>
+        <v>3920109</v>
       </c>
       <c r="B1546" s="26">
         <v>1</v>
@@ -47841,15 +47855,15 @@
         <v>10</v>
       </c>
       <c r="H1546">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1546">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1547" customFormat="1" spans="1:9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:9">
       <c r="A1547">
-        <v>8920109</v>
+        <v>4920109</v>
       </c>
       <c r="B1547" s="26">
         <v>1</v>
@@ -47870,12 +47884,12 @@
         <v>1</v>
       </c>
       <c r="I1547">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1548" customFormat="1" spans="1:9">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:9">
       <c r="A1548">
-        <v>9920109</v>
+        <v>6920109</v>
       </c>
       <c r="B1548" s="26">
         <v>1</v>
@@ -47893,15 +47907,15 @@
         <v>10</v>
       </c>
       <c r="H1548">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1548">
         <v>0</v>
       </c>
     </row>
-    <row r="1549" customFormat="1" spans="1:9">
+    <row r="1549" spans="1:9">
       <c r="A1549">
-        <v>13920109</v>
+        <v>7920109</v>
       </c>
       <c r="B1549" s="26">
         <v>1</v>
@@ -47919,15 +47933,15 @@
         <v>10</v>
       </c>
       <c r="H1549">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1549">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1550" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:9">
       <c r="A1550">
-        <v>16920101</v>
+        <v>8920109</v>
       </c>
       <c r="B1550" s="26">
         <v>1</v>
@@ -47941,7 +47955,6 @@
       <c r="E1550" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1550" s="28"/>
       <c r="G1550">
         <v>10</v>
       </c>
@@ -47949,12 +47962,12 @@
         <v>1</v>
       </c>
       <c r="I1550">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="1551" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:9">
       <c r="A1551">
-        <v>920110</v>
+        <v>9920109</v>
       </c>
       <c r="B1551" s="26">
         <v>1</v>
@@ -47966,21 +47979,21 @@
         <v>1152</v>
       </c>
       <c r="E1551" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1551">
         <v>10</v>
       </c>
       <c r="H1551">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1551">
         <v>0</v>
       </c>
     </row>
-    <row r="1552" customFormat="1" spans="1:9">
+    <row r="1552" spans="1:9">
       <c r="A1552">
-        <v>1920110</v>
+        <v>13920109</v>
       </c>
       <c r="B1552" s="26">
         <v>1</v>
@@ -48001,12 +48014,12 @@
         <v>1</v>
       </c>
       <c r="I1552">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="1553" customFormat="1" spans="1:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:9">
       <c r="A1553">
-        <v>2920110</v>
+        <v>16920101</v>
       </c>
       <c r="B1553" s="26">
         <v>1</v>
@@ -48020,6 +48033,7 @@
       <c r="E1553" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1553" s="28"/>
       <c r="G1553">
         <v>10</v>
       </c>
@@ -48027,12 +48041,12 @@
         <v>1</v>
       </c>
       <c r="I1553">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1554" customFormat="1" spans="1:9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:9">
       <c r="A1554">
-        <v>3920110</v>
+        <v>920110</v>
       </c>
       <c r="B1554" s="26">
         <v>1</v>
@@ -48044,7 +48058,7 @@
         <v>1155</v>
       </c>
       <c r="E1554" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1554">
         <v>10</v>
@@ -48053,12 +48067,12 @@
         <v>1</v>
       </c>
       <c r="I1554">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="1555" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:9">
       <c r="A1555">
-        <v>4920110</v>
+        <v>1920110</v>
       </c>
       <c r="B1555" s="26">
         <v>1</v>
@@ -48079,12 +48093,12 @@
         <v>1</v>
       </c>
       <c r="I1555">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="1556" customFormat="1" spans="1:9">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:9">
       <c r="A1556">
-        <v>6920110</v>
+        <v>2920110</v>
       </c>
       <c r="B1556" s="26">
         <v>1</v>
@@ -48108,9 +48122,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1557" customFormat="1" spans="1:9">
+    <row r="1557" spans="1:9">
       <c r="A1557">
-        <v>7920110</v>
+        <v>3920110</v>
       </c>
       <c r="B1557" s="26">
         <v>1</v>
@@ -48128,15 +48142,15 @@
         <v>10</v>
       </c>
       <c r="H1557">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1557">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="1558" customFormat="1" spans="1:9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:9">
       <c r="A1558">
-        <v>8920110</v>
+        <v>4920110</v>
       </c>
       <c r="B1558" s="26">
         <v>1</v>
@@ -48157,12 +48171,12 @@
         <v>1</v>
       </c>
       <c r="I1558">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1559" customFormat="1" spans="1:9">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:9">
       <c r="A1559">
-        <v>9920110</v>
+        <v>6920110</v>
       </c>
       <c r="B1559" s="26">
         <v>1</v>
@@ -48180,15 +48194,15 @@
         <v>10</v>
       </c>
       <c r="H1559">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1559">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="1560" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:9">
       <c r="A1560">
-        <v>13920110</v>
+        <v>7920110</v>
       </c>
       <c r="B1560" s="26">
         <v>1</v>
@@ -48206,15 +48220,15 @@
         <v>10</v>
       </c>
       <c r="H1560">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1560">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1561" customFormat="1" spans="1:9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:9">
       <c r="A1561">
-        <v>920115</v>
+        <v>8920110</v>
       </c>
       <c r="B1561" s="26">
         <v>1</v>
@@ -48226,9 +48240,8 @@
         <v>1162</v>
       </c>
       <c r="E1561" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1561" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1561">
         <v>10</v>
       </c>
@@ -48239,9 +48252,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1562" customFormat="1" spans="1:9">
+    <row r="1562" spans="1:9">
       <c r="A1562">
-        <v>820096</v>
+        <v>9920110</v>
       </c>
       <c r="B1562" s="26">
         <v>1</v>
@@ -48249,25 +48262,25 @@
       <c r="C1562">
         <v>0</v>
       </c>
-      <c r="D1562" s="30" t="s">
+      <c r="D1562" s="28" t="s">
         <v>1163</v>
       </c>
-      <c r="E1562" s="30" t="s">
-        <v>1120</v>
+      <c r="E1562" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1562">
         <v>10</v>
       </c>
       <c r="H1562">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1562">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1563" customFormat="1" spans="1:9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:9">
       <c r="A1563">
-        <v>920116</v>
+        <v>13920110</v>
       </c>
       <c r="B1563" s="26">
         <v>1</v>
@@ -48279,35 +48292,35 @@
         <v>1164</v>
       </c>
       <c r="E1563" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1563">
+        <v>10</v>
+      </c>
+      <c r="H1563">
+        <v>1</v>
+      </c>
+      <c r="I1563">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:9">
+      <c r="A1564">
+        <v>920115</v>
+      </c>
+      <c r="B1564" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1564">
+        <v>0</v>
+      </c>
+      <c r="D1564" s="28" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E1564" s="29" t="s">
         <v>767</v>
       </c>
-      <c r="F1563" s="28"/>
-      <c r="G1563">
-        <v>10</v>
-      </c>
-      <c r="H1563">
-        <v>1</v>
-      </c>
-      <c r="I1563">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1564" customFormat="1" spans="1:9">
-      <c r="A1564">
-        <v>820097</v>
-      </c>
-      <c r="B1564" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1564">
-        <v>0</v>
-      </c>
-      <c r="D1564" s="30" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E1564" s="30" t="s">
-        <v>1120</v>
-      </c>
+      <c r="F1564" s="28"/>
       <c r="G1564">
         <v>10</v>
       </c>
@@ -48318,9 +48331,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1565" customFormat="1" spans="1:9">
+    <row r="1565" spans="1:9">
       <c r="A1565">
-        <v>920111</v>
+        <v>820096</v>
       </c>
       <c r="B1565" s="26">
         <v>1</v>
@@ -48328,11 +48341,11 @@
       <c r="C1565">
         <v>0</v>
       </c>
-      <c r="D1565" s="28" t="s">
+      <c r="D1565" s="30" t="s">
         <v>1166</v>
       </c>
-      <c r="E1565" s="29" t="s">
-        <v>767</v>
+      <c r="E1565" s="30" t="s">
+        <v>1121</v>
       </c>
       <c r="G1565">
         <v>10</v>
@@ -48344,9 +48357,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1566" customFormat="1" spans="1:9">
+    <row r="1566" spans="1:9">
       <c r="A1566">
-        <v>1920111</v>
+        <v>920114</v>
       </c>
       <c r="B1566" s="26">
         <v>1</v>
@@ -48358,8 +48371,9 @@
         <v>1167</v>
       </c>
       <c r="E1566" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1566" s="28"/>
       <c r="G1566">
         <v>10</v>
       </c>
@@ -48367,12 +48381,12 @@
         <v>1</v>
       </c>
       <c r="I1566">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="1567" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:9">
       <c r="A1567">
-        <v>2920111</v>
+        <v>920116</v>
       </c>
       <c r="B1567" s="26">
         <v>1</v>
@@ -48384,8 +48398,9 @@
         <v>1168</v>
       </c>
       <c r="E1567" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1567" s="28"/>
       <c r="G1567">
         <v>10</v>
       </c>
@@ -48396,9 +48411,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1568" customFormat="1" spans="1:9">
+    <row r="1568" spans="1:9">
       <c r="A1568">
-        <v>3920111</v>
+        <v>820097</v>
       </c>
       <c r="B1568" s="26">
         <v>1</v>
@@ -48406,11 +48421,11 @@
       <c r="C1568">
         <v>0</v>
       </c>
-      <c r="D1568" s="28" t="s">
+      <c r="D1568" s="30" t="s">
         <v>1169</v>
       </c>
-      <c r="E1568" s="29" t="s">
-        <v>769</v>
+      <c r="E1568" s="30" t="s">
+        <v>1121</v>
       </c>
       <c r="G1568">
         <v>10</v>
@@ -48419,12 +48434,12 @@
         <v>1</v>
       </c>
       <c r="I1568">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="1569" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:9">
       <c r="A1569">
-        <v>492011</v>
+        <v>920111</v>
       </c>
       <c r="B1569" s="26">
         <v>1</v>
@@ -48436,7 +48451,7 @@
         <v>1170</v>
       </c>
       <c r="E1569" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1569">
         <v>10</v>
@@ -48445,12 +48460,12 @@
         <v>1</v>
       </c>
       <c r="I1569">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="1570" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:9">
       <c r="A1570">
-        <v>6920111</v>
+        <v>1920111</v>
       </c>
       <c r="B1570" s="26">
         <v>1</v>
@@ -48471,12 +48486,12 @@
         <v>1</v>
       </c>
       <c r="I1570">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1571" customFormat="1" spans="1:9">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:9">
       <c r="A1571">
-        <v>7920111</v>
+        <v>2920111</v>
       </c>
       <c r="B1571" s="26">
         <v>1</v>
@@ -48494,15 +48509,15 @@
         <v>10</v>
       </c>
       <c r="H1571">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1571">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="1572" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:9">
       <c r="A1572">
-        <v>8920111</v>
+        <v>3920111</v>
       </c>
       <c r="B1572" s="26">
         <v>1</v>
@@ -48523,12 +48538,12 @@
         <v>1</v>
       </c>
       <c r="I1572">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1573" customFormat="1" spans="1:9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:9">
       <c r="A1573">
-        <v>9920111</v>
+        <v>492011</v>
       </c>
       <c r="B1573" s="26">
         <v>1</v>
@@ -48546,15 +48561,15 @@
         <v>10</v>
       </c>
       <c r="H1573">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1573">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="1574" customFormat="1" spans="1:9">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:9">
       <c r="A1574">
-        <v>10920111</v>
+        <v>6920111</v>
       </c>
       <c r="B1574" s="26">
         <v>1</v>
@@ -48575,12 +48590,12 @@
         <v>1</v>
       </c>
       <c r="I1574">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="1575" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:9">
       <c r="A1575">
-        <v>11920111</v>
+        <v>7920111</v>
       </c>
       <c r="B1575" s="26">
         <v>1</v>
@@ -48598,15 +48613,15 @@
         <v>10</v>
       </c>
       <c r="H1575">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1575">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="1576" customFormat="1" spans="1:9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:9">
       <c r="A1576">
-        <v>13920111</v>
+        <v>8920111</v>
       </c>
       <c r="B1576" s="26">
         <v>1</v>
@@ -48627,12 +48642,12 @@
         <v>1</v>
       </c>
       <c r="I1576">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1577" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:9">
       <c r="A1577">
-        <v>920118</v>
+        <v>9920111</v>
       </c>
       <c r="B1577" s="26">
         <v>1</v>
@@ -48644,22 +48659,21 @@
         <v>1178</v>
       </c>
       <c r="E1577" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1577" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1577">
         <v>10</v>
       </c>
       <c r="H1577">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1577">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1578" customFormat="1" spans="1:9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:9">
       <c r="A1578">
-        <v>820100</v>
+        <v>10920111</v>
       </c>
       <c r="B1578" s="26">
         <v>1</v>
@@ -48667,11 +48681,11 @@
       <c r="C1578">
         <v>0</v>
       </c>
-      <c r="D1578" s="30" t="s">
+      <c r="D1578" s="28" t="s">
         <v>1179</v>
       </c>
-      <c r="E1578" s="30" t="s">
-        <v>1120</v>
+      <c r="E1578" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1578">
         <v>10</v>
@@ -48680,12 +48694,12 @@
         <v>1</v>
       </c>
       <c r="I1578">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1579" customFormat="1" spans="1:9">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:9">
       <c r="A1579">
-        <v>920112</v>
+        <v>11920111</v>
       </c>
       <c r="B1579" s="26">
         <v>1</v>
@@ -48697,7 +48711,7 @@
         <v>1180</v>
       </c>
       <c r="E1579" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1579">
         <v>10</v>
@@ -48706,12 +48720,12 @@
         <v>1</v>
       </c>
       <c r="I1579">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1580" customFormat="1" spans="1:9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:9">
       <c r="A1580">
-        <v>1920112</v>
+        <v>13920111</v>
       </c>
       <c r="B1580" s="26">
         <v>1</v>
@@ -48732,12 +48746,12 @@
         <v>1</v>
       </c>
       <c r="I1580">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="1581" customFormat="1" spans="1:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:9">
       <c r="A1581">
-        <v>2920112</v>
+        <v>920118</v>
       </c>
       <c r="B1581" s="26">
         <v>1</v>
@@ -48749,8 +48763,9 @@
         <v>1182</v>
       </c>
       <c r="E1581" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1581" s="28"/>
       <c r="G1581">
         <v>10</v>
       </c>
@@ -48761,9 +48776,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1582" customFormat="1" spans="1:9">
+    <row r="1582" spans="1:9">
       <c r="A1582">
-        <v>3920112</v>
+        <v>820100</v>
       </c>
       <c r="B1582" s="26">
         <v>1</v>
@@ -48771,11 +48786,11 @@
       <c r="C1582">
         <v>0</v>
       </c>
-      <c r="D1582" s="28" t="s">
+      <c r="D1582" s="30" t="s">
         <v>1183</v>
       </c>
-      <c r="E1582" s="29" t="s">
-        <v>769</v>
+      <c r="E1582" s="30" t="s">
+        <v>1121</v>
       </c>
       <c r="G1582">
         <v>10</v>
@@ -48784,12 +48799,12 @@
         <v>1</v>
       </c>
       <c r="I1582">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="1583" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:9">
       <c r="A1583">
-        <v>4920112</v>
+        <v>920112</v>
       </c>
       <c r="B1583" s="26">
         <v>1</v>
@@ -48801,7 +48816,7 @@
         <v>1184</v>
       </c>
       <c r="E1583" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1583">
         <v>10</v>
@@ -48810,12 +48825,12 @@
         <v>1</v>
       </c>
       <c r="I1583">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="1584" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:9">
       <c r="A1584">
-        <v>6920112</v>
+        <v>1920112</v>
       </c>
       <c r="B1584" s="26">
         <v>1</v>
@@ -48836,12 +48851,12 @@
         <v>1</v>
       </c>
       <c r="I1584">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1585" customFormat="1" spans="1:9">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:9">
       <c r="A1585">
-        <v>7920112</v>
+        <v>2920112</v>
       </c>
       <c r="B1585" s="26">
         <v>1</v>
@@ -48859,15 +48874,15 @@
         <v>10</v>
       </c>
       <c r="H1585">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1585">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="1586" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:9">
       <c r="A1586">
-        <v>8920112</v>
+        <v>3920112</v>
       </c>
       <c r="B1586" s="26">
         <v>1</v>
@@ -48888,12 +48903,12 @@
         <v>1</v>
       </c>
       <c r="I1586">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1587" customFormat="1" spans="1:9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:9">
       <c r="A1587">
-        <v>9920112</v>
+        <v>4920112</v>
       </c>
       <c r="B1587" s="26">
         <v>1</v>
@@ -48911,15 +48926,15 @@
         <v>10</v>
       </c>
       <c r="H1587">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1587">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="1588" customFormat="1" spans="1:9">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:9">
       <c r="A1588">
-        <v>13920112</v>
+        <v>6920112</v>
       </c>
       <c r="B1588" s="26">
         <v>1</v>
@@ -48940,12 +48955,12 @@
         <v>1</v>
       </c>
       <c r="I1588">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1589" customFormat="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:9">
       <c r="A1589">
-        <v>920117</v>
+        <v>7920112</v>
       </c>
       <c r="B1589" s="26">
         <v>1</v>
@@ -48957,156 +48972,144 @@
         <v>1190</v>
       </c>
       <c r="E1589" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1589">
+        <v>10</v>
+      </c>
+      <c r="H1589">
+        <v>2</v>
+      </c>
+      <c r="I1589">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:9">
+      <c r="A1590">
+        <v>8920112</v>
+      </c>
+      <c r="B1590" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1590">
+        <v>0</v>
+      </c>
+      <c r="D1590" s="28" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1590" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1590">
+        <v>10</v>
+      </c>
+      <c r="H1590">
+        <v>1</v>
+      </c>
+      <c r="I1590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:9">
+      <c r="A1591">
+        <v>9920112</v>
+      </c>
+      <c r="B1591" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1591">
+        <v>0</v>
+      </c>
+      <c r="D1591" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E1591" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1591">
+        <v>10</v>
+      </c>
+      <c r="H1591">
+        <v>2</v>
+      </c>
+      <c r="I1591">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:9">
+      <c r="A1592">
+        <v>13920112</v>
+      </c>
+      <c r="B1592" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1592">
+        <v>0</v>
+      </c>
+      <c r="D1592" s="28" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1592" s="29" t="s">
+        <v>769</v>
+      </c>
+      <c r="G1592">
+        <v>10</v>
+      </c>
+      <c r="H1592">
+        <v>1</v>
+      </c>
+      <c r="I1592">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:9">
+      <c r="A1593">
+        <v>920117</v>
+      </c>
+      <c r="B1593" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1593">
+        <v>0</v>
+      </c>
+      <c r="D1593" s="28" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E1593" s="29" t="s">
         <v>767</v>
       </c>
-      <c r="F1589" s="28"/>
-      <c r="G1589">
-        <v>10</v>
-      </c>
-      <c r="H1589">
-        <v>1</v>
-      </c>
-      <c r="I1589">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1590" customFormat="1" spans="1:9">
-      <c r="A1590">
+      <c r="F1593" s="28"/>
+      <c r="G1593">
+        <v>10</v>
+      </c>
+      <c r="H1593">
+        <v>1</v>
+      </c>
+      <c r="I1593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:9">
+      <c r="A1594">
         <v>820099</v>
       </c>
-      <c r="B1590" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1590">
-        <v>0</v>
-      </c>
-      <c r="D1590" s="30" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E1590" s="30" t="s">
-        <v>1120</v>
-      </c>
-      <c r="G1590">
-        <v>10</v>
-      </c>
-      <c r="H1590">
-        <v>1</v>
-      </c>
-      <c r="I1590">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1591" spans="1:9">
-      <c r="A1591" s="26">
-        <v>5101721</v>
-      </c>
-      <c r="B1591" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1591" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1591" s="27" t="s">
-        <v>1192</v>
-      </c>
-      <c r="E1591" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1591" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1591" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1591" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1591">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1592" spans="1:9">
-      <c r="A1592" s="26">
-        <v>5101722</v>
-      </c>
-      <c r="B1592" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1592" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1592" s="27" t="s">
-        <v>1193</v>
-      </c>
-      <c r="E1592" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1592" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1592" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1592" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1592">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1593" spans="1:9">
-      <c r="A1593" s="26">
-        <v>5101723</v>
-      </c>
-      <c r="B1593" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1593" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1593" s="27" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E1593" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1593" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1593" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1593" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1593">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1594" spans="1:9">
-      <c r="A1594" s="26">
-        <v>5101724</v>
-      </c>
       <c r="B1594" s="26">
         <v>1</v>
       </c>
-      <c r="C1594" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1594" s="27" t="s">
+      <c r="C1594">
+        <v>0</v>
+      </c>
+      <c r="D1594" s="30" t="s">
         <v>1195</v>
       </c>
-      <c r="E1594" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1594" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1594" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1594" s="26">
-        <v>2</v>
+      <c r="E1594" s="30" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G1594">
+        <v>10</v>
+      </c>
+      <c r="H1594">
+        <v>1</v>
       </c>
       <c r="I1594">
         <v>0</v>
@@ -49114,7 +49117,7 @@
     </row>
     <row r="1595" spans="1:9">
       <c r="A1595" s="26">
-        <v>5101725</v>
+        <v>5101721</v>
       </c>
       <c r="B1595" s="26">
         <v>1</v>
@@ -49135,9 +49138,125 @@
         <v>10</v>
       </c>
       <c r="H1595" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:9">
+      <c r="A1596" s="26">
+        <v>5101722</v>
+      </c>
+      <c r="B1596" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1596" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1596" s="27" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E1596" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1596" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1596" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1596" s="26">
         <v>2</v>
       </c>
-      <c r="I1595">
+      <c r="I1596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:9">
+      <c r="A1597" s="26">
+        <v>5101723</v>
+      </c>
+      <c r="B1597" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1597" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1597" s="27" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E1597" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1597" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1597" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1597" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:9">
+      <c r="A1598" s="26">
+        <v>5101724</v>
+      </c>
+      <c r="B1598" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1598" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1598" s="27" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E1598" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1598" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1598" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1598" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:9">
+      <c r="A1599" s="26">
+        <v>5101725</v>
+      </c>
+      <c r="B1599" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1599" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1599" s="27" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1599" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1599" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1599" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1599" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1599">
         <v>0</v>
       </c>
     </row>
@@ -49203,7 +49322,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -49215,10 +49334,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -49232,90 +49351,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1217</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1218</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1220</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1221</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1222</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1223</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -49326,7 +49445,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -49347,7 +49466,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -49359,7 +49478,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49370,7 +49489,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -49411,7 +49530,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -49452,7 +49571,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -49473,7 +49592,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -49485,7 +49604,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49496,7 +49615,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49517,7 +49636,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49529,7 +49648,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49540,7 +49659,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49561,7 +49680,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -46611,7 +46611,7 @@
     </row>
     <row r="1499" spans="1:9">
       <c r="A1499">
-        <v>10920105</v>
+        <v>11030105</v>
       </c>
       <c r="B1499" s="26">
         <v>1</v>
@@ -47028,7 +47028,7 @@
     </row>
     <row r="1515" spans="1:9">
       <c r="A1515">
-        <v>10920106</v>
+        <v>11030106</v>
       </c>
       <c r="B1515" s="26">
         <v>1</v>
@@ -47394,7 +47394,7 @@
     </row>
     <row r="1529" spans="1:9">
       <c r="A1529">
-        <v>10920107</v>
+        <v>11030107</v>
       </c>
       <c r="B1529" s="26">
         <v>1</v>
@@ -48673,7 +48673,7 @@
     </row>
     <row r="1578" spans="1:9">
       <c r="A1578">
-        <v>10920111</v>
+        <v>11030111</v>
       </c>
       <c r="B1578" s="26">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="1241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="1238">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3563,33 +3563,6 @@
     <t>毒雨对自身被动-逻辑id</t>
   </si>
   <si>
-    <t>毒刃_获得</t>
-  </si>
-  <si>
-    <t>毒刃_最近释放距离</t>
-  </si>
-  <si>
-    <t>毒刃_最远释放距离</t>
-  </si>
-  <si>
-    <t>毒刃_技能效果半径</t>
-  </si>
-  <si>
-    <t>毒刃_主目标直接伤害固定值</t>
-  </si>
-  <si>
-    <t>毒刃_主目标直接伤害系数</t>
-  </si>
-  <si>
-    <t>毒刃_非主目标直接伤害固定值</t>
-  </si>
-  <si>
-    <t>毒刃_非主目标直接伤害系数</t>
-  </si>
-  <si>
-    <t>毒刃_技能等级</t>
-  </si>
-  <si>
     <t>淬毒_获得</t>
   </si>
   <si>
@@ -3756,6 +3729,24 @@
   </si>
   <si>
     <t>精神错乱被动-持续时间</t>
+  </si>
+  <si>
+    <t>尸爆中毒状态</t>
+  </si>
+  <si>
+    <t>尸爆-中毒伤害系数万分比</t>
+  </si>
+  <si>
+    <t>尸爆-中毒伤害系数固定值</t>
+  </si>
+  <si>
+    <t>尸爆-中毒持续时间</t>
+  </si>
+  <si>
+    <t>尸爆-中毒的命中率</t>
+  </si>
+  <si>
+    <t>尸爆-中毒伤害结算间隔</t>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S</t>
@@ -4143,12 +4134,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5087,7 +5078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1599"/>
+  <dimension ref="A1:I1596"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -47551,7 +47542,7 @@
     </row>
     <row r="1535" spans="1:9">
       <c r="A1535">
-        <v>920108</v>
+        <v>920109</v>
       </c>
       <c r="B1535" s="26">
         <v>1</v>
@@ -47577,7 +47568,7 @@
     </row>
     <row r="1536" spans="1:9">
       <c r="A1536">
-        <v>2920108</v>
+        <v>2920109</v>
       </c>
       <c r="B1536" s="26">
         <v>1</v>
@@ -47603,7 +47594,7 @@
     </row>
     <row r="1537" spans="1:9">
       <c r="A1537">
-        <v>3920108</v>
+        <v>3920109</v>
       </c>
       <c r="B1537" s="26">
         <v>1</v>
@@ -47624,12 +47615,12 @@
         <v>1</v>
       </c>
       <c r="I1537">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1538" spans="1:9">
       <c r="A1538">
-        <v>4920108</v>
+        <v>4920109</v>
       </c>
       <c r="B1538" s="26">
         <v>1</v>
@@ -47655,7 +47646,7 @@
     </row>
     <row r="1539" spans="1:9">
       <c r="A1539">
-        <v>6920108</v>
+        <v>6920109</v>
       </c>
       <c r="B1539" s="26">
         <v>1</v>
@@ -47681,7 +47672,7 @@
     </row>
     <row r="1540" spans="1:9">
       <c r="A1540">
-        <v>7920108</v>
+        <v>7920109</v>
       </c>
       <c r="B1540" s="26">
         <v>1</v>
@@ -47707,7 +47698,7 @@
     </row>
     <row r="1541" spans="1:9">
       <c r="A1541">
-        <v>8920108</v>
+        <v>8920109</v>
       </c>
       <c r="B1541" s="26">
         <v>1</v>
@@ -47733,7 +47724,7 @@
     </row>
     <row r="1542" spans="1:9">
       <c r="A1542">
-        <v>9920108</v>
+        <v>9920109</v>
       </c>
       <c r="B1542" s="26">
         <v>1</v>
@@ -47759,7 +47750,7 @@
     </row>
     <row r="1543" spans="1:9">
       <c r="A1543">
-        <v>13920108</v>
+        <v>13920109</v>
       </c>
       <c r="B1543" s="26">
         <v>1</v>
@@ -47785,7 +47776,7 @@
     </row>
     <row r="1544" spans="1:9">
       <c r="A1544">
-        <v>920109</v>
+        <v>16920101</v>
       </c>
       <c r="B1544" s="26">
         <v>1</v>
@@ -47797,8 +47788,9 @@
         <v>1145</v>
       </c>
       <c r="E1544" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1544" s="28"/>
       <c r="G1544">
         <v>10</v>
       </c>
@@ -47806,12 +47798,12 @@
         <v>1</v>
       </c>
       <c r="I1544">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1545" spans="1:9">
       <c r="A1545">
-        <v>2920109</v>
+        <v>920110</v>
       </c>
       <c r="B1545" s="26">
         <v>1</v>
@@ -47823,7 +47815,7 @@
         <v>1146</v>
       </c>
       <c r="E1545" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1545">
         <v>10</v>
@@ -47837,7 +47829,7 @@
     </row>
     <row r="1546" spans="1:9">
       <c r="A1546">
-        <v>3920109</v>
+        <v>1920110</v>
       </c>
       <c r="B1546" s="26">
         <v>1</v>
@@ -47858,12 +47850,12 @@
         <v>1</v>
       </c>
       <c r="I1546">
-        <v>6000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1547" spans="1:9">
       <c r="A1547">
-        <v>4920109</v>
+        <v>2920110</v>
       </c>
       <c r="B1547" s="26">
         <v>1</v>
@@ -47884,12 +47876,12 @@
         <v>1</v>
       </c>
       <c r="I1547">
-        <v>1600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1548" spans="1:9">
       <c r="A1548">
-        <v>6920109</v>
+        <v>3920110</v>
       </c>
       <c r="B1548" s="26">
         <v>1</v>
@@ -47910,12 +47902,12 @@
         <v>1</v>
       </c>
       <c r="I1548">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1549" spans="1:9">
       <c r="A1549">
-        <v>7920109</v>
+        <v>4920110</v>
       </c>
       <c r="B1549" s="26">
         <v>1</v>
@@ -47933,15 +47925,15 @@
         <v>10</v>
       </c>
       <c r="H1549">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1549">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1550" spans="1:9">
       <c r="A1550">
-        <v>8920109</v>
+        <v>6920110</v>
       </c>
       <c r="B1550" s="26">
         <v>1</v>
@@ -47967,7 +47959,7 @@
     </row>
     <row r="1551" spans="1:9">
       <c r="A1551">
-        <v>9920109</v>
+        <v>7920110</v>
       </c>
       <c r="B1551" s="26">
         <v>1</v>
@@ -47988,12 +47980,12 @@
         <v>2</v>
       </c>
       <c r="I1551">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1552" spans="1:9">
       <c r="A1552">
-        <v>13920109</v>
+        <v>8920110</v>
       </c>
       <c r="B1552" s="26">
         <v>1</v>
@@ -48014,12 +48006,12 @@
         <v>1</v>
       </c>
       <c r="I1552">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1553" spans="1:9">
       <c r="A1553">
-        <v>16920101</v>
+        <v>9920110</v>
       </c>
       <c r="B1553" s="26">
         <v>1</v>
@@ -48033,20 +48025,19 @@
       <c r="E1553" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1553" s="28"/>
       <c r="G1553">
         <v>10</v>
       </c>
       <c r="H1553">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1553">
-        <v>180</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1554" spans="1:9">
       <c r="A1554">
-        <v>920110</v>
+        <v>13920110</v>
       </c>
       <c r="B1554" s="26">
         <v>1</v>
@@ -48058,7 +48049,7 @@
         <v>1155</v>
       </c>
       <c r="E1554" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1554">
         <v>10</v>
@@ -48067,12 +48058,12 @@
         <v>1</v>
       </c>
       <c r="I1554">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1555" spans="1:9">
       <c r="A1555">
-        <v>1920110</v>
+        <v>920115</v>
       </c>
       <c r="B1555" s="26">
         <v>1</v>
@@ -48084,8 +48075,9 @@
         <v>1156</v>
       </c>
       <c r="E1555" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1555" s="28"/>
       <c r="G1555">
         <v>10</v>
       </c>
@@ -48093,12 +48085,12 @@
         <v>1</v>
       </c>
       <c r="I1555">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1556" spans="1:9">
       <c r="A1556">
-        <v>2920110</v>
+        <v>820096</v>
       </c>
       <c r="B1556" s="26">
         <v>1</v>
@@ -48106,11 +48098,11 @@
       <c r="C1556">
         <v>0</v>
       </c>
-      <c r="D1556" s="28" t="s">
+      <c r="D1556" s="30" t="s">
         <v>1157</v>
       </c>
-      <c r="E1556" s="29" t="s">
-        <v>769</v>
+      <c r="E1556" s="30" t="s">
+        <v>1121</v>
       </c>
       <c r="G1556">
         <v>10</v>
@@ -48124,7 +48116,7 @@
     </row>
     <row r="1557" spans="1:9">
       <c r="A1557">
-        <v>3920110</v>
+        <v>920114</v>
       </c>
       <c r="B1557" s="26">
         <v>1</v>
@@ -48136,8 +48128,9 @@
         <v>1158</v>
       </c>
       <c r="E1557" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1557" s="28"/>
       <c r="G1557">
         <v>10</v>
       </c>
@@ -48145,12 +48138,12 @@
         <v>1</v>
       </c>
       <c r="I1557">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1558" spans="1:9">
       <c r="A1558">
-        <v>4920110</v>
+        <v>920116</v>
       </c>
       <c r="B1558" s="26">
         <v>1</v>
@@ -48162,8 +48155,9 @@
         <v>1159</v>
       </c>
       <c r="E1558" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1558" s="28"/>
       <c r="G1558">
         <v>10</v>
       </c>
@@ -48171,12 +48165,12 @@
         <v>1</v>
       </c>
       <c r="I1558">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1559" spans="1:9">
       <c r="A1559">
-        <v>6920110</v>
+        <v>820097</v>
       </c>
       <c r="B1559" s="26">
         <v>1</v>
@@ -48184,11 +48178,11 @@
       <c r="C1559">
         <v>0</v>
       </c>
-      <c r="D1559" s="28" t="s">
+      <c r="D1559" s="30" t="s">
         <v>1160</v>
       </c>
-      <c r="E1559" s="29" t="s">
-        <v>769</v>
+      <c r="E1559" s="30" t="s">
+        <v>1121</v>
       </c>
       <c r="G1559">
         <v>10</v>
@@ -48202,7 +48196,7 @@
     </row>
     <row r="1560" spans="1:9">
       <c r="A1560">
-        <v>7920110</v>
+        <v>920111</v>
       </c>
       <c r="B1560" s="26">
         <v>1</v>
@@ -48214,21 +48208,21 @@
         <v>1161</v>
       </c>
       <c r="E1560" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1560">
         <v>10</v>
       </c>
       <c r="H1560">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1560">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1561" spans="1:9">
       <c r="A1561">
-        <v>8920110</v>
+        <v>1920111</v>
       </c>
       <c r="B1561" s="26">
         <v>1</v>
@@ -48249,12 +48243,12 @@
         <v>1</v>
       </c>
       <c r="I1561">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1562" spans="1:9">
       <c r="A1562">
-        <v>9920110</v>
+        <v>2920111</v>
       </c>
       <c r="B1562" s="26">
         <v>1</v>
@@ -48272,15 +48266,15 @@
         <v>10</v>
       </c>
       <c r="H1562">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1562">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1563" spans="1:9">
       <c r="A1563">
-        <v>13920110</v>
+        <v>3920111</v>
       </c>
       <c r="B1563" s="26">
         <v>1</v>
@@ -48301,12 +48295,12 @@
         <v>1</v>
       </c>
       <c r="I1563">
-        <v>1</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1564" spans="1:9">
       <c r="A1564">
-        <v>920115</v>
+        <v>492011</v>
       </c>
       <c r="B1564" s="26">
         <v>1</v>
@@ -48318,9 +48312,8 @@
         <v>1165</v>
       </c>
       <c r="E1564" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1564" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1564">
         <v>10</v>
       </c>
@@ -48328,12 +48321,12 @@
         <v>1</v>
       </c>
       <c r="I1564">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1565" spans="1:9">
       <c r="A1565">
-        <v>820096</v>
+        <v>6920111</v>
       </c>
       <c r="B1565" s="26">
         <v>1</v>
@@ -48341,11 +48334,11 @@
       <c r="C1565">
         <v>0</v>
       </c>
-      <c r="D1565" s="30" t="s">
+      <c r="D1565" s="28" t="s">
         <v>1166</v>
       </c>
-      <c r="E1565" s="30" t="s">
-        <v>1121</v>
+      <c r="E1565" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1565">
         <v>10</v>
@@ -48359,7 +48352,7 @@
     </row>
     <row r="1566" spans="1:9">
       <c r="A1566">
-        <v>920114</v>
+        <v>7920111</v>
       </c>
       <c r="B1566" s="26">
         <v>1</v>
@@ -48371,22 +48364,21 @@
         <v>1167</v>
       </c>
       <c r="E1566" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1566" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1566">
         <v>10</v>
       </c>
       <c r="H1566">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1566">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1567" spans="1:9">
       <c r="A1567">
-        <v>920116</v>
+        <v>8920111</v>
       </c>
       <c r="B1567" s="26">
         <v>1</v>
@@ -48398,9 +48390,8 @@
         <v>1168</v>
       </c>
       <c r="E1567" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1567" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1567">
         <v>10</v>
       </c>
@@ -48413,7 +48404,7 @@
     </row>
     <row r="1568" spans="1:9">
       <c r="A1568">
-        <v>820097</v>
+        <v>9920111</v>
       </c>
       <c r="B1568" s="26">
         <v>1</v>
@@ -48421,25 +48412,25 @@
       <c r="C1568">
         <v>0</v>
       </c>
-      <c r="D1568" s="30" t="s">
+      <c r="D1568" s="28" t="s">
         <v>1169</v>
       </c>
-      <c r="E1568" s="30" t="s">
-        <v>1121</v>
+      <c r="E1568" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1568">
         <v>10</v>
       </c>
       <c r="H1568">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1568">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1569" spans="1:9">
       <c r="A1569">
-        <v>920111</v>
+        <v>11030111</v>
       </c>
       <c r="B1569" s="26">
         <v>1</v>
@@ -48451,7 +48442,7 @@
         <v>1170</v>
       </c>
       <c r="E1569" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1569">
         <v>10</v>
@@ -48460,12 +48451,12 @@
         <v>1</v>
       </c>
       <c r="I1569">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1570" spans="1:9">
       <c r="A1570">
-        <v>1920111</v>
+        <v>11920111</v>
       </c>
       <c r="B1570" s="26">
         <v>1</v>
@@ -48486,12 +48477,12 @@
         <v>1</v>
       </c>
       <c r="I1570">
-        <v>4000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1571" spans="1:9">
       <c r="A1571">
-        <v>2920111</v>
+        <v>13920111</v>
       </c>
       <c r="B1571" s="26">
         <v>1</v>
@@ -48512,12 +48503,12 @@
         <v>1</v>
       </c>
       <c r="I1571">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1572" spans="1:9">
       <c r="A1572">
-        <v>3920111</v>
+        <v>920118</v>
       </c>
       <c r="B1572" s="26">
         <v>1</v>
@@ -48529,8 +48520,9 @@
         <v>1173</v>
       </c>
       <c r="E1572" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1572" s="28"/>
       <c r="G1572">
         <v>10</v>
       </c>
@@ -48538,12 +48530,12 @@
         <v>1</v>
       </c>
       <c r="I1572">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1573" spans="1:9">
       <c r="A1573">
-        <v>492011</v>
+        <v>820100</v>
       </c>
       <c r="B1573" s="26">
         <v>1</v>
@@ -48551,11 +48543,11 @@
       <c r="C1573">
         <v>0</v>
       </c>
-      <c r="D1573" s="28" t="s">
+      <c r="D1573" s="30" t="s">
         <v>1174</v>
       </c>
-      <c r="E1573" s="29" t="s">
-        <v>769</v>
+      <c r="E1573" s="30" t="s">
+        <v>1121</v>
       </c>
       <c r="G1573">
         <v>10</v>
@@ -48564,12 +48556,12 @@
         <v>1</v>
       </c>
       <c r="I1573">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1574" spans="1:9">
       <c r="A1574">
-        <v>6920111</v>
+        <v>920112</v>
       </c>
       <c r="B1574" s="26">
         <v>1</v>
@@ -48581,7 +48573,7 @@
         <v>1175</v>
       </c>
       <c r="E1574" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1574">
         <v>10</v>
@@ -48595,7 +48587,7 @@
     </row>
     <row r="1575" spans="1:9">
       <c r="A1575">
-        <v>7920111</v>
+        <v>1920112</v>
       </c>
       <c r="B1575" s="26">
         <v>1</v>
@@ -48613,15 +48605,15 @@
         <v>10</v>
       </c>
       <c r="H1575">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1575">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1576" spans="1:9">
       <c r="A1576">
-        <v>8920111</v>
+        <v>2920112</v>
       </c>
       <c r="B1576" s="26">
         <v>1</v>
@@ -48647,7 +48639,7 @@
     </row>
     <row r="1577" spans="1:9">
       <c r="A1577">
-        <v>9920111</v>
+        <v>3920112</v>
       </c>
       <c r="B1577" s="26">
         <v>1</v>
@@ -48665,15 +48657,15 @@
         <v>10</v>
       </c>
       <c r="H1577">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1577">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1578" spans="1:9">
       <c r="A1578">
-        <v>11030111</v>
+        <v>4920112</v>
       </c>
       <c r="B1578" s="26">
         <v>1</v>
@@ -48694,12 +48686,12 @@
         <v>1</v>
       </c>
       <c r="I1578">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1579" spans="1:9">
       <c r="A1579">
-        <v>11920111</v>
+        <v>6920112</v>
       </c>
       <c r="B1579" s="26">
         <v>1</v>
@@ -48720,12 +48712,12 @@
         <v>1</v>
       </c>
       <c r="I1579">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1580" spans="1:9">
       <c r="A1580">
-        <v>13920111</v>
+        <v>7920112</v>
       </c>
       <c r="B1580" s="26">
         <v>1</v>
@@ -48743,15 +48735,15 @@
         <v>10</v>
       </c>
       <c r="H1580">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1580">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1581" spans="1:9">
       <c r="A1581">
-        <v>920118</v>
+        <v>8920112</v>
       </c>
       <c r="B1581" s="26">
         <v>1</v>
@@ -48763,9 +48755,8 @@
         <v>1182</v>
       </c>
       <c r="E1581" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1581" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1581">
         <v>10</v>
       </c>
@@ -48778,7 +48769,7 @@
     </row>
     <row r="1582" spans="1:9">
       <c r="A1582">
-        <v>820100</v>
+        <v>9920112</v>
       </c>
       <c r="B1582" s="26">
         <v>1</v>
@@ -48786,25 +48777,25 @@
       <c r="C1582">
         <v>0</v>
       </c>
-      <c r="D1582" s="30" t="s">
+      <c r="D1582" s="28" t="s">
         <v>1183</v>
       </c>
-      <c r="E1582" s="30" t="s">
-        <v>1121</v>
+      <c r="E1582" s="29" t="s">
+        <v>769</v>
       </c>
       <c r="G1582">
         <v>10</v>
       </c>
       <c r="H1582">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1582">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1583" spans="1:9">
       <c r="A1583">
-        <v>920112</v>
+        <v>13920112</v>
       </c>
       <c r="B1583" s="26">
         <v>1</v>
@@ -48816,7 +48807,7 @@
         <v>1184</v>
       </c>
       <c r="E1583" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1583">
         <v>10</v>
@@ -48825,12 +48816,12 @@
         <v>1</v>
       </c>
       <c r="I1583">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1584" spans="1:9">
       <c r="A1584">
-        <v>1920112</v>
+        <v>920117</v>
       </c>
       <c r="B1584" s="26">
         <v>1</v>
@@ -48842,8 +48833,9 @@
         <v>1185</v>
       </c>
       <c r="E1584" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1584" s="28"/>
       <c r="G1584">
         <v>10</v>
       </c>
@@ -48851,12 +48843,12 @@
         <v>1</v>
       </c>
       <c r="I1584">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1585" spans="1:9">
       <c r="A1585">
-        <v>2920112</v>
+        <v>820099</v>
       </c>
       <c r="B1585" s="26">
         <v>1</v>
@@ -48864,11 +48856,11 @@
       <c r="C1585">
         <v>0</v>
       </c>
-      <c r="D1585" s="28" t="s">
+      <c r="D1585" s="30" t="s">
         <v>1186</v>
       </c>
-      <c r="E1585" s="29" t="s">
-        <v>769</v>
+      <c r="E1585" s="30" t="s">
+        <v>1121</v>
       </c>
       <c r="G1585">
         <v>10</v>
@@ -48881,208 +48873,231 @@
       </c>
     </row>
     <row r="1586" spans="1:9">
-      <c r="A1586">
-        <v>3920112</v>
+      <c r="A1586" s="26">
+        <v>5101721</v>
       </c>
       <c r="B1586" s="26">
         <v>1</v>
       </c>
-      <c r="C1586">
-        <v>0</v>
-      </c>
-      <c r="D1586" s="28" t="s">
+      <c r="C1586" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1586" s="27" t="s">
         <v>1187</v>
       </c>
-      <c r="E1586" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1586">
-        <v>10</v>
-      </c>
-      <c r="H1586">
+      <c r="E1586" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1586" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1586" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1586" s="26">
         <v>1</v>
       </c>
       <c r="I1586">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1587" spans="1:9">
-      <c r="A1587">
-        <v>4920112</v>
+      <c r="A1587" s="26">
+        <v>5101722</v>
       </c>
       <c r="B1587" s="26">
         <v>1</v>
       </c>
-      <c r="C1587">
-        <v>0</v>
-      </c>
-      <c r="D1587" s="28" t="s">
+      <c r="C1587" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1587" s="27" t="s">
         <v>1188</v>
       </c>
-      <c r="E1587" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1587">
-        <v>10</v>
-      </c>
-      <c r="H1587">
-        <v>1</v>
+      <c r="E1587" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1587" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1587" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1587" s="26">
+        <v>2</v>
       </c>
       <c r="I1587">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1588" spans="1:9">
-      <c r="A1588">
-        <v>6920112</v>
+      <c r="A1588" s="26">
+        <v>5101723</v>
       </c>
       <c r="B1588" s="26">
         <v>1</v>
       </c>
-      <c r="C1588">
-        <v>0</v>
-      </c>
-      <c r="D1588" s="28" t="s">
+      <c r="C1588" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1588" s="27" t="s">
         <v>1189</v>
       </c>
-      <c r="E1588" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1588">
-        <v>10</v>
-      </c>
-      <c r="H1588">
-        <v>1</v>
+      <c r="E1588" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1588" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1588" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1588" s="26">
+        <v>2</v>
       </c>
       <c r="I1588">
         <v>0</v>
       </c>
     </row>
     <row r="1589" spans="1:9">
-      <c r="A1589">
-        <v>7920112</v>
+      <c r="A1589" s="26">
+        <v>5101724</v>
       </c>
       <c r="B1589" s="26">
         <v>1</v>
       </c>
-      <c r="C1589">
-        <v>0</v>
-      </c>
-      <c r="D1589" s="28" t="s">
+      <c r="C1589" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1589" s="27" t="s">
         <v>1190</v>
       </c>
-      <c r="E1589" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1589">
-        <v>10</v>
-      </c>
-      <c r="H1589">
+      <c r="E1589" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1589" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1589" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1589" s="26">
         <v>2</v>
       </c>
       <c r="I1589">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1590" spans="1:9">
-      <c r="A1590">
-        <v>8920112</v>
+      <c r="A1590" s="26">
+        <v>5101725</v>
       </c>
       <c r="B1590" s="26">
         <v>1</v>
       </c>
-      <c r="C1590">
-        <v>0</v>
-      </c>
-      <c r="D1590" s="28" t="s">
+      <c r="C1590" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1590" s="27" t="s">
         <v>1191</v>
       </c>
-      <c r="E1590" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1590">
-        <v>10</v>
-      </c>
-      <c r="H1590">
-        <v>1</v>
+      <c r="E1590" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1590" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1590" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1590" s="26">
+        <v>2</v>
       </c>
       <c r="I1590">
         <v>0</v>
       </c>
     </row>
     <row r="1591" spans="1:9">
-      <c r="A1591">
-        <v>9920112</v>
+      <c r="A1591" s="26">
+        <v>5101726</v>
       </c>
       <c r="B1591" s="26">
         <v>1</v>
       </c>
-      <c r="C1591">
-        <v>0</v>
-      </c>
-      <c r="D1591" s="28" t="s">
+      <c r="C1591" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1591" s="27" t="s">
         <v>1192</v>
       </c>
-      <c r="E1591" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1591">
-        <v>10</v>
-      </c>
-      <c r="H1591">
+      <c r="E1591" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="F1591" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1591" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1591" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:9">
+      <c r="A1592" s="26">
+        <v>5101727</v>
+      </c>
+      <c r="B1592" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1592" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1592" s="27" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1592" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1592" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1592" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1592" s="26">
         <v>2</v>
       </c>
-      <c r="I1591">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="1592" spans="1:9">
-      <c r="A1592">
-        <v>13920112</v>
-      </c>
-      <c r="B1592" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1592">
-        <v>0</v>
-      </c>
-      <c r="D1592" s="28" t="s">
-        <v>1193</v>
-      </c>
-      <c r="E1592" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="G1592">
-        <v>10</v>
-      </c>
-      <c r="H1592">
-        <v>1</v>
-      </c>
       <c r="I1592">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1593" spans="1:9">
-      <c r="A1593">
-        <v>920117</v>
+      <c r="A1593" s="26">
+        <v>5101728</v>
       </c>
       <c r="B1593" s="26">
         <v>1</v>
       </c>
-      <c r="C1593">
-        <v>0</v>
-      </c>
-      <c r="D1593" s="28" t="s">
+      <c r="C1593" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1593" s="27" t="s">
         <v>1194</v>
       </c>
-      <c r="E1593" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1593" s="28"/>
-      <c r="G1593">
-        <v>10</v>
-      </c>
-      <c r="H1593">
+      <c r="E1593" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1593" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1593" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1593" s="26">
         <v>1</v>
       </c>
       <c r="I1593">
@@ -49090,25 +49105,28 @@
       </c>
     </row>
     <row r="1594" spans="1:9">
-      <c r="A1594">
-        <v>820099</v>
+      <c r="A1594" s="26">
+        <v>5101729</v>
       </c>
       <c r="B1594" s="26">
         <v>1</v>
       </c>
-      <c r="C1594">
-        <v>0</v>
-      </c>
-      <c r="D1594" s="30" t="s">
+      <c r="C1594" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1594" s="27" t="s">
         <v>1195</v>
       </c>
-      <c r="E1594" s="30" t="s">
-        <v>1121</v>
-      </c>
-      <c r="G1594">
-        <v>10</v>
-      </c>
-      <c r="H1594">
+      <c r="E1594" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1594" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1594" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1594" s="26">
         <v>1</v>
       </c>
       <c r="I1594">
@@ -49117,7 +49135,7 @@
     </row>
     <row r="1595" spans="1:9">
       <c r="A1595" s="26">
-        <v>5101721</v>
+        <v>5101730</v>
       </c>
       <c r="B1595" s="26">
         <v>1</v>
@@ -49129,7 +49147,7 @@
         <v>1196</v>
       </c>
       <c r="E1595" s="26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1595" s="9" t="s">
         <v>100</v>
@@ -49138,7 +49156,7 @@
         <v>10</v>
       </c>
       <c r="H1595" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1595">
         <v>0</v>
@@ -49146,7 +49164,7 @@
     </row>
     <row r="1596" spans="1:9">
       <c r="A1596" s="26">
-        <v>5101722</v>
+        <v>5101731</v>
       </c>
       <c r="B1596" s="26">
         <v>1</v>
@@ -49158,7 +49176,7 @@
         <v>1197</v>
       </c>
       <c r="E1596" s="26" t="s">
-        <v>329</v>
+        <v>971</v>
       </c>
       <c r="F1596" s="9" t="s">
         <v>100</v>
@@ -49167,96 +49185,9 @@
         <v>10</v>
       </c>
       <c r="H1596" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1596">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1597" spans="1:9">
-      <c r="A1597" s="26">
-        <v>5101723</v>
-      </c>
-      <c r="B1597" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1597" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1597" s="27" t="s">
-        <v>1198</v>
-      </c>
-      <c r="E1597" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1597" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1597" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1597" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1597">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1598" spans="1:9">
-      <c r="A1598" s="26">
-        <v>5101724</v>
-      </c>
-      <c r="B1598" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1598" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1598" s="27" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E1598" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1598" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1598" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1598" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1598">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1599" spans="1:9">
-      <c r="A1599" s="26">
-        <v>5101725</v>
-      </c>
-      <c r="B1599" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1599" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1599" s="27" t="s">
-        <v>1200</v>
-      </c>
-      <c r="E1599" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1599" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1599" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1599" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1599">
         <v>0</v>
       </c>
     </row>
@@ -49322,7 +49253,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -49334,10 +49265,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -49351,90 +49282,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>1203</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>1204</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>1205</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>1206</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>1207</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>1208</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>1209</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>1210</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>1211</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>1213</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>1215</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>1216</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>1217</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>1218</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>1219</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>1220</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>1221</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>1222</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>1223</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>1224</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>1225</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1226</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1227</v>
-      </c>
       <c r="N4" s="4" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -49445,7 +49376,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -49466,7 +49397,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -49478,7 +49409,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49489,7 +49420,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -49530,7 +49461,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -49571,7 +49502,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -49592,7 +49523,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -49604,7 +49535,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49615,7 +49546,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49636,7 +49567,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49648,7 +49579,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49659,7 +49590,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49680,7 +49611,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4134,12 +4134,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -46467,7 +46467,7 @@
         <v>1</v>
       </c>
       <c r="I1493">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1494" spans="1:9">
@@ -46884,7 +46884,7 @@
         <v>1</v>
       </c>
       <c r="I1509">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1510" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="1238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="1233">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3731,22 +3731,7 @@
     <t>精神错乱被动-持续时间</t>
   </si>
   <si>
-    <t>尸爆中毒状态</t>
-  </si>
-  <si>
-    <t>尸爆-中毒伤害系数万分比</t>
-  </si>
-  <si>
-    <t>尸爆-中毒伤害系数固定值</t>
-  </si>
-  <si>
-    <t>尸爆-中毒持续时间</t>
-  </si>
-  <si>
     <t>尸爆-中毒的命中率</t>
-  </si>
-  <si>
-    <t>尸爆-中毒伤害结算间隔</t>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S</t>
@@ -5078,7 +5063,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1596"/>
+  <dimension ref="A1:I1591"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -48988,7 +48973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1590" spans="1:9">
+    <row r="1590" ht="14" customHeight="1" spans="1:9">
       <c r="A1590" s="26">
         <v>5101725</v>
       </c>
@@ -49019,7 +49004,7 @@
     </row>
     <row r="1591" spans="1:9">
       <c r="A1591" s="26">
-        <v>5101726</v>
+        <v>5101730</v>
       </c>
       <c r="B1591" s="26">
         <v>1</v>
@@ -49031,7 +49016,7 @@
         <v>1192</v>
       </c>
       <c r="E1591" s="26" t="s">
-        <v>243</v>
+        <v>329</v>
       </c>
       <c r="F1591" s="9" t="s">
         <v>100</v>
@@ -49040,154 +49025,9 @@
         <v>10</v>
       </c>
       <c r="H1591" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1591">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1592" spans="1:9">
-      <c r="A1592" s="26">
-        <v>5101727</v>
-      </c>
-      <c r="B1592" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1592" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1592" s="27" t="s">
-        <v>1193</v>
-      </c>
-      <c r="E1592" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="F1592" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1592" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1592" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1592">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1593" spans="1:9">
-      <c r="A1593" s="26">
-        <v>5101728</v>
-      </c>
-      <c r="B1593" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1593" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1593" s="27" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E1593" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="F1593" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1593" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1593" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1593">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1594" spans="1:9">
-      <c r="A1594" s="26">
-        <v>5101729</v>
-      </c>
-      <c r="B1594" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1594" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1594" s="27" t="s">
-        <v>1195</v>
-      </c>
-      <c r="E1594" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1594" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1594" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1594" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1594">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1595" spans="1:9">
-      <c r="A1595" s="26">
-        <v>5101730</v>
-      </c>
-      <c r="B1595" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1595" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1595" s="27" t="s">
-        <v>1196</v>
-      </c>
-      <c r="E1595" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1595" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1595" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1595" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1595">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1596" spans="1:9">
-      <c r="A1596" s="26">
-        <v>5101731</v>
-      </c>
-      <c r="B1596" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1596" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1596" s="27" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E1596" s="26" t="s">
-        <v>971</v>
-      </c>
-      <c r="F1596" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1596" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1596" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1596">
         <v>0</v>
       </c>
     </row>
@@ -49253,7 +49093,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -49265,10 +49105,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -49282,90 +49122,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>1200</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>1201</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>1202</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>1203</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>1204</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>1205</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>1206</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>1207</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>1208</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>1209</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>1210</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>1212</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>1213</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>1214</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>1215</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>1216</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>1217</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>1218</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>1219</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>1220</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1221</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1222</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1223</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1224</v>
-      </c>
       <c r="N4" s="4" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -49376,7 +49216,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -49397,7 +49237,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -49409,7 +49249,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49420,7 +49260,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -49461,7 +49301,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -49502,7 +49342,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -49523,7 +49363,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -49535,7 +49375,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49546,7 +49386,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49567,7 +49407,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49579,7 +49419,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49590,7 +49430,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49611,7 +49451,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="1233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4148" uniqueCount="1235">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3732,6 +3732,12 @@
   </si>
   <si>
     <t>尸爆-中毒的命中率</t>
+  </si>
+  <si>
+    <t>尸爆-中毒持续时间</t>
+  </si>
+  <si>
+    <t>尸爆-中毒伤害结算间隔</t>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S</t>
@@ -5063,7 +5069,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1591"/>
+  <dimension ref="A1:I1593"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -48285,7 +48291,7 @@
     </row>
     <row r="1564" spans="1:9">
       <c r="A1564">
-        <v>492011</v>
+        <v>4920111</v>
       </c>
       <c r="B1564" s="26">
         <v>1</v>
@@ -49028,6 +49034,64 @@
         <v>2</v>
       </c>
       <c r="I1591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:9">
+      <c r="A1592" s="26">
+        <v>5101731</v>
+      </c>
+      <c r="B1592" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1592" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1592" s="27" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E1592" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1592" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1592" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1592" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:9">
+      <c r="A1593" s="26">
+        <v>5101732</v>
+      </c>
+      <c r="B1593" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1593" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1593" s="27" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E1593" s="26" t="s">
+        <v>971</v>
+      </c>
+      <c r="F1593" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1593" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1593" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1593">
         <v>0</v>
       </c>
     </row>
@@ -49093,7 +49157,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -49105,10 +49169,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -49122,90 +49186,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1211</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1212</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1213</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1214</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1215</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1216</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1218</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -49216,7 +49280,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -49237,7 +49301,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -49249,7 +49313,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49260,7 +49324,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -49301,7 +49365,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -49342,7 +49406,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -49363,7 +49427,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -49375,7 +49439,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49386,7 +49450,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49407,7 +49471,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49419,7 +49483,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49430,7 +49494,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49451,7 +49515,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4148" uniqueCount="1235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="1238">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3560,9 +3560,6 @@
     <t>毒雨被动-逻辑id</t>
   </si>
   <si>
-    <t>毒雨对自身被动-逻辑id</t>
-  </si>
-  <si>
     <t>淬毒_获得</t>
   </si>
   <si>
@@ -3638,6 +3635,9 @@
     <t>精神错乱被动-逻辑id</t>
   </si>
   <si>
+    <t>精神错乱给敌方被动-逻辑id</t>
+  </si>
+  <si>
     <t>流毒_获得</t>
   </si>
   <si>
@@ -3738,6 +3738,15 @@
   </si>
   <si>
     <t>尸爆-中毒伤害结算间隔</t>
+  </si>
+  <si>
+    <t>尸爆-中毒伤害系数万分比</t>
+  </si>
+  <si>
+    <t>尸爆-中毒伤害系数固定值</t>
+  </si>
+  <si>
+    <t>精神错乱对怪被动-持续时间</t>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S</t>
@@ -5069,7 +5078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1593"/>
+  <dimension ref="A1:I1596"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -47507,7 +47516,7 @@
     </row>
     <row r="1534" spans="1:9">
       <c r="A1534">
-        <v>820110</v>
+        <v>920109</v>
       </c>
       <c r="B1534" s="26">
         <v>1</v>
@@ -47515,11 +47524,11 @@
       <c r="C1534">
         <v>0</v>
       </c>
-      <c r="D1534" s="30" t="s">
+      <c r="D1534" s="28" t="s">
         <v>1135</v>
       </c>
-      <c r="E1534" s="30" t="s">
-        <v>1134</v>
+      <c r="E1534" s="29" t="s">
+        <v>767</v>
       </c>
       <c r="G1534">
         <v>10</v>
@@ -47533,7 +47542,7 @@
     </row>
     <row r="1535" spans="1:9">
       <c r="A1535">
-        <v>920109</v>
+        <v>2920109</v>
       </c>
       <c r="B1535" s="26">
         <v>1</v>
@@ -47545,7 +47554,7 @@
         <v>1136</v>
       </c>
       <c r="E1535" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1535">
         <v>10</v>
@@ -47559,7 +47568,7 @@
     </row>
     <row r="1536" spans="1:9">
       <c r="A1536">
-        <v>2920109</v>
+        <v>3920109</v>
       </c>
       <c r="B1536" s="26">
         <v>1</v>
@@ -47580,12 +47589,12 @@
         <v>1</v>
       </c>
       <c r="I1536">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1537" spans="1:9">
       <c r="A1537">
-        <v>3920109</v>
+        <v>4920109</v>
       </c>
       <c r="B1537" s="26">
         <v>1</v>
@@ -47606,12 +47615,12 @@
         <v>1</v>
       </c>
       <c r="I1537">
-        <v>6000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1538" spans="1:9">
       <c r="A1538">
-        <v>4920109</v>
+        <v>6920109</v>
       </c>
       <c r="B1538" s="26">
         <v>1</v>
@@ -47632,12 +47641,12 @@
         <v>1</v>
       </c>
       <c r="I1538">
-        <v>1600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1539" spans="1:9">
       <c r="A1539">
-        <v>6920109</v>
+        <v>7920109</v>
       </c>
       <c r="B1539" s="26">
         <v>1</v>
@@ -47655,7 +47664,7 @@
         <v>10</v>
       </c>
       <c r="H1539">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1539">
         <v>0</v>
@@ -47663,7 +47672,7 @@
     </row>
     <row r="1540" spans="1:9">
       <c r="A1540">
-        <v>7920109</v>
+        <v>8920109</v>
       </c>
       <c r="B1540" s="26">
         <v>1</v>
@@ -47681,7 +47690,7 @@
         <v>10</v>
       </c>
       <c r="H1540">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1540">
         <v>0</v>
@@ -47689,7 +47698,7 @@
     </row>
     <row r="1541" spans="1:9">
       <c r="A1541">
-        <v>8920109</v>
+        <v>9920109</v>
       </c>
       <c r="B1541" s="26">
         <v>1</v>
@@ -47707,7 +47716,7 @@
         <v>10</v>
       </c>
       <c r="H1541">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1541">
         <v>0</v>
@@ -47715,7 +47724,7 @@
     </row>
     <row r="1542" spans="1:9">
       <c r="A1542">
-        <v>9920109</v>
+        <v>13920109</v>
       </c>
       <c r="B1542" s="26">
         <v>1</v>
@@ -47733,15 +47742,15 @@
         <v>10</v>
       </c>
       <c r="H1542">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1542">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1543" spans="1:9">
       <c r="A1543">
-        <v>13920109</v>
+        <v>16920101</v>
       </c>
       <c r="B1543" s="26">
         <v>1</v>
@@ -47755,6 +47764,7 @@
       <c r="E1543" s="29" t="s">
         <v>769</v>
       </c>
+      <c r="F1543" s="28"/>
       <c r="G1543">
         <v>10</v>
       </c>
@@ -47762,12 +47772,12 @@
         <v>1</v>
       </c>
       <c r="I1543">
-        <v>1</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1544" spans="1:9">
       <c r="A1544">
-        <v>16920101</v>
+        <v>920110</v>
       </c>
       <c r="B1544" s="26">
         <v>1</v>
@@ -47779,9 +47789,8 @@
         <v>1145</v>
       </c>
       <c r="E1544" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="F1544" s="28"/>
+        <v>767</v>
+      </c>
       <c r="G1544">
         <v>10</v>
       </c>
@@ -47789,12 +47798,12 @@
         <v>1</v>
       </c>
       <c r="I1544">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1545" spans="1:9">
       <c r="A1545">
-        <v>920110</v>
+        <v>1920110</v>
       </c>
       <c r="B1545" s="26">
         <v>1</v>
@@ -47806,7 +47815,7 @@
         <v>1146</v>
       </c>
       <c r="E1545" s="29" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G1545">
         <v>10</v>
@@ -47815,12 +47824,12 @@
         <v>1</v>
       </c>
       <c r="I1545">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1546" spans="1:9">
       <c r="A1546">
-        <v>1920110</v>
+        <v>2920110</v>
       </c>
       <c r="B1546" s="26">
         <v>1</v>
@@ -47841,12 +47850,12 @@
         <v>1</v>
       </c>
       <c r="I1546">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1547" spans="1:9">
       <c r="A1547">
-        <v>2920110</v>
+        <v>3920110</v>
       </c>
       <c r="B1547" s="26">
         <v>1</v>
@@ -47867,12 +47876,12 @@
         <v>1</v>
       </c>
       <c r="I1547">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1548" spans="1:9">
       <c r="A1548">
-        <v>3920110</v>
+        <v>4920110</v>
       </c>
       <c r="B1548" s="26">
         <v>1</v>
@@ -47893,12 +47902,12 @@
         <v>1</v>
       </c>
       <c r="I1548">
-        <v>6000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1549" spans="1:9">
       <c r="A1549">
-        <v>4920110</v>
+        <v>6920110</v>
       </c>
       <c r="B1549" s="26">
         <v>1</v>
@@ -47919,12 +47928,12 @@
         <v>1</v>
       </c>
       <c r="I1549">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1550" spans="1:9">
       <c r="A1550">
-        <v>6920110</v>
+        <v>7920110</v>
       </c>
       <c r="B1550" s="26">
         <v>1</v>
@@ -47942,15 +47951,15 @@
         <v>10</v>
       </c>
       <c r="H1550">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1550">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1551" spans="1:9">
       <c r="A1551">
-        <v>7920110</v>
+        <v>8920110</v>
       </c>
       <c r="B1551" s="26">
         <v>1</v>
@@ -47968,15 +47977,15 @@
         <v>10</v>
       </c>
       <c r="H1551">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1551">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1552" spans="1:9">
       <c r="A1552">
-        <v>8920110</v>
+        <v>9920110</v>
       </c>
       <c r="B1552" s="26">
         <v>1</v>
@@ -47994,15 +48003,15 @@
         <v>10</v>
       </c>
       <c r="H1552">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1552">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1553" spans="1:9">
       <c r="A1553">
-        <v>9920110</v>
+        <v>13920110</v>
       </c>
       <c r="B1553" s="26">
         <v>1</v>
@@ -48020,15 +48029,15 @@
         <v>10</v>
       </c>
       <c r="H1553">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1553">
-        <v>20000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1554" spans="1:9">
       <c r="A1554">
-        <v>13920110</v>
+        <v>920115</v>
       </c>
       <c r="B1554" s="26">
         <v>1</v>
@@ -48040,8 +48049,9 @@
         <v>1155</v>
       </c>
       <c r="E1554" s="29" t="s">
-        <v>769</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="F1554" s="28"/>
       <c r="G1554">
         <v>10</v>
       </c>
@@ -48049,12 +48059,12 @@
         <v>1</v>
       </c>
       <c r="I1554">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1555" spans="1:9">
       <c r="A1555">
-        <v>920115</v>
+        <v>820096</v>
       </c>
       <c r="B1555" s="26">
         <v>1</v>
@@ -48062,13 +48072,12 @@
       <c r="C1555">
         <v>0</v>
       </c>
-      <c r="D1555" s="28" t="s">
+      <c r="D1555" s="30" t="s">
         <v>1156</v>
       </c>
-      <c r="E1555" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1555" s="28"/>
+      <c r="E1555" s="30" t="s">
+        <v>1156</v>
+      </c>
       <c r="G1555">
         <v>10</v>
       </c>
@@ -48081,7 +48090,7 @@
     </row>
     <row r="1556" spans="1:9">
       <c r="A1556">
-        <v>820096</v>
+        <v>920114</v>
       </c>
       <c r="B1556" s="26">
         <v>1</v>
@@ -48089,12 +48098,13 @@
       <c r="C1556">
         <v>0</v>
       </c>
-      <c r="D1556" s="30" t="s">
+      <c r="D1556" s="28" t="s">
         <v>1157</v>
       </c>
-      <c r="E1556" s="30" t="s">
-        <v>1121</v>
-      </c>
+      <c r="E1556" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1556" s="28"/>
       <c r="G1556">
         <v>10</v>
       </c>
@@ -48107,7 +48117,7 @@
     </row>
     <row r="1557" spans="1:9">
       <c r="A1557">
-        <v>920114</v>
+        <v>920116</v>
       </c>
       <c r="B1557" s="26">
         <v>1</v>
@@ -48134,7 +48144,7 @@
     </row>
     <row r="1558" spans="1:9">
       <c r="A1558">
-        <v>920116</v>
+        <v>820097</v>
       </c>
       <c r="B1558" s="26">
         <v>1</v>
@@ -48142,13 +48152,12 @@
       <c r="C1558">
         <v>0</v>
       </c>
-      <c r="D1558" s="28" t="s">
+      <c r="D1558" s="30" t="s">
         <v>1159</v>
       </c>
-      <c r="E1558" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1558" s="28"/>
+      <c r="E1558" s="30" t="s">
+        <v>1159</v>
+      </c>
       <c r="G1558">
         <v>10</v>
       </c>
@@ -48159,9 +48168,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1559" spans="1:9">
+    <row r="1559" customFormat="1" spans="1:9">
       <c r="A1559">
-        <v>820097</v>
+        <v>820111</v>
       </c>
       <c r="B1559" s="26">
         <v>1</v>
@@ -48173,7 +48182,7 @@
         <v>1160</v>
       </c>
       <c r="E1559" s="30" t="s">
-        <v>1121</v>
+        <v>1159</v>
       </c>
       <c r="G1559">
         <v>10</v>
@@ -48538,7 +48547,7 @@
         <v>1174</v>
       </c>
       <c r="E1573" s="30" t="s">
-        <v>1121</v>
+        <v>1174</v>
       </c>
       <c r="G1573">
         <v>10</v>
@@ -48851,7 +48860,7 @@
         <v>1186</v>
       </c>
       <c r="E1585" s="30" t="s">
-        <v>1121</v>
+        <v>1186</v>
       </c>
       <c r="G1585">
         <v>10</v>
@@ -49092,6 +49101,93 @@
         <v>1</v>
       </c>
       <c r="I1593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:9">
+      <c r="A1594" s="26">
+        <v>5101734</v>
+      </c>
+      <c r="B1594" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1594" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1594" s="27" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E1594" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1594" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1594" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1594" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:9">
+      <c r="A1595" s="26">
+        <v>5101735</v>
+      </c>
+      <c r="B1595" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1595" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1595" s="27" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1595" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1595" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1595" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1595" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1596" ht="14" customHeight="1" spans="1:9">
+      <c r="A1596" s="26">
+        <v>5101733</v>
+      </c>
+      <c r="B1596" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1596" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1596" s="27" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E1596" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1596" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1596" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1596" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1596">
         <v>0</v>
       </c>
     </row>
@@ -49157,7 +49253,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -49169,10 +49265,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -49186,90 +49282,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1214</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1215</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1216</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1218</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1220</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1221</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -49280,7 +49376,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -49301,7 +49397,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -49313,7 +49409,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49324,7 +49420,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -49365,7 +49461,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -49406,7 +49502,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -49427,7 +49523,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -49439,7 +49535,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49450,7 +49546,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49471,7 +49567,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49483,7 +49579,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49494,7 +49590,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49515,7 +49611,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4157" uniqueCount="1238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4171" uniqueCount="1243">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3521,6 +3521,12 @@
     <t>传染被动-逻辑id</t>
   </si>
   <si>
+    <t>传染给敌方被动-逻辑id</t>
+  </si>
+  <si>
+    <t>精神错乱被动-逻辑id</t>
+  </si>
+  <si>
     <t>毒雨_获得</t>
   </si>
   <si>
@@ -3632,9 +3638,6 @@
     <t>精神错乱被动_获得</t>
   </si>
   <si>
-    <t>精神错乱被动-逻辑id</t>
-  </si>
-  <si>
     <t>精神错乱给敌方被动-逻辑id</t>
   </si>
   <si>
@@ -3747,6 +3750,18 @@
   </si>
   <si>
     <t>精神错乱对怪被动-持续时间</t>
+  </si>
+  <si>
+    <t>传染-中毒持续时间</t>
+  </si>
+  <si>
+    <t>传染-中毒伤害结算间隔</t>
+  </si>
+  <si>
+    <t>传染-中毒伤害系数万分比</t>
+  </si>
+  <si>
+    <t>传染-中毒伤害系数固定值</t>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S</t>
@@ -5078,7 +5093,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1596"/>
+  <dimension ref="A1:I1601"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -47175,9 +47190,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1521" spans="1:9">
+    <row r="1521" customFormat="1" spans="1:9">
       <c r="A1521">
-        <v>920107</v>
+        <v>820112</v>
       </c>
       <c r="B1521" s="26">
         <v>1</v>
@@ -47185,11 +47200,11 @@
       <c r="C1521">
         <v>0</v>
       </c>
-      <c r="D1521" s="28" t="s">
+      <c r="D1521" s="30" t="s">
         <v>1122</v>
       </c>
-      <c r="E1521" s="29" t="s">
-        <v>767</v>
+      <c r="E1521" s="30" t="s">
+        <v>1123</v>
       </c>
       <c r="G1521">
         <v>10</v>
@@ -47203,7 +47218,7 @@
     </row>
     <row r="1522" spans="1:9">
       <c r="A1522">
-        <v>2920107</v>
+        <v>920107</v>
       </c>
       <c r="B1522" s="26">
         <v>1</v>
@@ -47212,10 +47227,10 @@
         <v>0</v>
       </c>
       <c r="D1522" s="28" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="E1522" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1522">
         <v>10</v>
@@ -47229,7 +47244,7 @@
     </row>
     <row r="1523" spans="1:9">
       <c r="A1523">
-        <v>39201057</v>
+        <v>2920107</v>
       </c>
       <c r="B1523" s="26">
         <v>1</v>
@@ -47238,7 +47253,7 @@
         <v>0</v>
       </c>
       <c r="D1523" s="28" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E1523" s="29" t="s">
         <v>769</v>
@@ -47255,7 +47270,7 @@
     </row>
     <row r="1524" spans="1:9">
       <c r="A1524">
-        <v>4920107</v>
+        <v>39201057</v>
       </c>
       <c r="B1524" s="26">
         <v>1</v>
@@ -47264,7 +47279,7 @@
         <v>0</v>
       </c>
       <c r="D1524" s="28" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="E1524" s="29" t="s">
         <v>769</v>
@@ -47276,12 +47291,12 @@
         <v>1</v>
       </c>
       <c r="I1524">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1525" spans="1:9">
       <c r="A1525">
-        <v>6920107</v>
+        <v>4920107</v>
       </c>
       <c r="B1525" s="26">
         <v>1</v>
@@ -47290,7 +47305,7 @@
         <v>0</v>
       </c>
       <c r="D1525" s="28" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E1525" s="29" t="s">
         <v>769</v>
@@ -47302,12 +47317,12 @@
         <v>1</v>
       </c>
       <c r="I1525">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1526" spans="1:9">
       <c r="A1526">
-        <v>7920107</v>
+        <v>6920107</v>
       </c>
       <c r="B1526" s="26">
         <v>1</v>
@@ -47316,7 +47331,7 @@
         <v>0</v>
       </c>
       <c r="D1526" s="28" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E1526" s="29" t="s">
         <v>769</v>
@@ -47325,15 +47340,15 @@
         <v>10</v>
       </c>
       <c r="H1526">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1526">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1527" spans="1:9">
       <c r="A1527">
-        <v>8920107</v>
+        <v>7920107</v>
       </c>
       <c r="B1527" s="26">
         <v>1</v>
@@ -47342,7 +47357,7 @@
         <v>0</v>
       </c>
       <c r="D1527" s="28" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="E1527" s="29" t="s">
         <v>769</v>
@@ -47351,15 +47366,15 @@
         <v>10</v>
       </c>
       <c r="H1527">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1527">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1528" spans="1:9">
       <c r="A1528">
-        <v>9920107</v>
+        <v>8920107</v>
       </c>
       <c r="B1528" s="26">
         <v>1</v>
@@ -47368,7 +47383,7 @@
         <v>0</v>
       </c>
       <c r="D1528" s="28" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E1528" s="29" t="s">
         <v>769</v>
@@ -47377,15 +47392,15 @@
         <v>10</v>
       </c>
       <c r="H1528">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1528">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1529" spans="1:9">
       <c r="A1529">
-        <v>11030107</v>
+        <v>9920107</v>
       </c>
       <c r="B1529" s="26">
         <v>1</v>
@@ -47394,7 +47409,7 @@
         <v>0</v>
       </c>
       <c r="D1529" s="28" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="E1529" s="29" t="s">
         <v>769</v>
@@ -47403,15 +47418,15 @@
         <v>10</v>
       </c>
       <c r="H1529">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1529">
-        <v>2000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1530" spans="1:9">
       <c r="A1530">
-        <v>11920107</v>
+        <v>11030107</v>
       </c>
       <c r="B1530" s="26">
         <v>1</v>
@@ -47420,7 +47435,7 @@
         <v>0</v>
       </c>
       <c r="D1530" s="28" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E1530" s="29" t="s">
         <v>769</v>
@@ -47432,12 +47447,12 @@
         <v>1</v>
       </c>
       <c r="I1530">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1531" spans="1:9">
       <c r="A1531">
-        <v>13920107</v>
+        <v>11920107</v>
       </c>
       <c r="B1531" s="26">
         <v>1</v>
@@ -47446,7 +47461,7 @@
         <v>0</v>
       </c>
       <c r="D1531" s="28" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E1531" s="29" t="s">
         <v>769</v>
@@ -47458,12 +47473,12 @@
         <v>1</v>
       </c>
       <c r="I1531">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1532" spans="1:9">
       <c r="A1532">
-        <v>920108</v>
+        <v>13920107</v>
       </c>
       <c r="B1532" s="26">
         <v>1</v>
@@ -47472,12 +47487,11 @@
         <v>0</v>
       </c>
       <c r="D1532" s="28" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E1532" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1532" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1532">
         <v>10</v>
       </c>
@@ -47485,12 +47499,12 @@
         <v>1</v>
       </c>
       <c r="I1532">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1533" spans="1:9">
       <c r="A1533">
-        <v>820098</v>
+        <v>920108</v>
       </c>
       <c r="B1533" s="26">
         <v>1</v>
@@ -47498,12 +47512,13 @@
       <c r="C1533">
         <v>0</v>
       </c>
-      <c r="D1533" s="30" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E1533" s="30" t="s">
-        <v>1134</v>
-      </c>
+      <c r="D1533" s="28" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E1533" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1533" s="28"/>
       <c r="G1533">
         <v>10</v>
       </c>
@@ -47516,7 +47531,7 @@
     </row>
     <row r="1534" spans="1:9">
       <c r="A1534">
-        <v>920109</v>
+        <v>820098</v>
       </c>
       <c r="B1534" s="26">
         <v>1</v>
@@ -47524,11 +47539,11 @@
       <c r="C1534">
         <v>0</v>
       </c>
-      <c r="D1534" s="28" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E1534" s="29" t="s">
-        <v>767</v>
+      <c r="D1534" s="30" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E1534" s="30" t="s">
+        <v>1136</v>
       </c>
       <c r="G1534">
         <v>10</v>
@@ -47542,7 +47557,7 @@
     </row>
     <row r="1535" spans="1:9">
       <c r="A1535">
-        <v>2920109</v>
+        <v>920109</v>
       </c>
       <c r="B1535" s="26">
         <v>1</v>
@@ -47551,10 +47566,10 @@
         <v>0</v>
       </c>
       <c r="D1535" s="28" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="E1535" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1535">
         <v>10</v>
@@ -47568,7 +47583,7 @@
     </row>
     <row r="1536" spans="1:9">
       <c r="A1536">
-        <v>3920109</v>
+        <v>2920109</v>
       </c>
       <c r="B1536" s="26">
         <v>1</v>
@@ -47577,7 +47592,7 @@
         <v>0</v>
       </c>
       <c r="D1536" s="28" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E1536" s="29" t="s">
         <v>769</v>
@@ -47589,12 +47604,12 @@
         <v>1</v>
       </c>
       <c r="I1536">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1537" spans="1:9">
       <c r="A1537">
-        <v>4920109</v>
+        <v>3920109</v>
       </c>
       <c r="B1537" s="26">
         <v>1</v>
@@ -47603,7 +47618,7 @@
         <v>0</v>
       </c>
       <c r="D1537" s="28" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E1537" s="29" t="s">
         <v>769</v>
@@ -47615,12 +47630,12 @@
         <v>1</v>
       </c>
       <c r="I1537">
-        <v>1600</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1538" spans="1:9">
       <c r="A1538">
-        <v>6920109</v>
+        <v>4920109</v>
       </c>
       <c r="B1538" s="26">
         <v>1</v>
@@ -47629,7 +47644,7 @@
         <v>0</v>
       </c>
       <c r="D1538" s="28" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E1538" s="29" t="s">
         <v>769</v>
@@ -47641,12 +47656,12 @@
         <v>1</v>
       </c>
       <c r="I1538">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1539" spans="1:9">
       <c r="A1539">
-        <v>7920109</v>
+        <v>6920109</v>
       </c>
       <c r="B1539" s="26">
         <v>1</v>
@@ -47655,7 +47670,7 @@
         <v>0</v>
       </c>
       <c r="D1539" s="28" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E1539" s="29" t="s">
         <v>769</v>
@@ -47664,7 +47679,7 @@
         <v>10</v>
       </c>
       <c r="H1539">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1539">
         <v>0</v>
@@ -47672,7 +47687,7 @@
     </row>
     <row r="1540" spans="1:9">
       <c r="A1540">
-        <v>8920109</v>
+        <v>7920109</v>
       </c>
       <c r="B1540" s="26">
         <v>1</v>
@@ -47681,7 +47696,7 @@
         <v>0</v>
       </c>
       <c r="D1540" s="28" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E1540" s="29" t="s">
         <v>769</v>
@@ -47690,7 +47705,7 @@
         <v>10</v>
       </c>
       <c r="H1540">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1540">
         <v>0</v>
@@ -47698,7 +47713,7 @@
     </row>
     <row r="1541" spans="1:9">
       <c r="A1541">
-        <v>9920109</v>
+        <v>8920109</v>
       </c>
       <c r="B1541" s="26">
         <v>1</v>
@@ -47707,7 +47722,7 @@
         <v>0</v>
       </c>
       <c r="D1541" s="28" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="E1541" s="29" t="s">
         <v>769</v>
@@ -47716,7 +47731,7 @@
         <v>10</v>
       </c>
       <c r="H1541">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1541">
         <v>0</v>
@@ -47724,7 +47739,7 @@
     </row>
     <row r="1542" spans="1:9">
       <c r="A1542">
-        <v>13920109</v>
+        <v>9920109</v>
       </c>
       <c r="B1542" s="26">
         <v>1</v>
@@ -47733,7 +47748,7 @@
         <v>0</v>
       </c>
       <c r="D1542" s="28" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="E1542" s="29" t="s">
         <v>769</v>
@@ -47742,15 +47757,15 @@
         <v>10</v>
       </c>
       <c r="H1542">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1542">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1543" spans="1:9">
       <c r="A1543">
-        <v>16920101</v>
+        <v>13920109</v>
       </c>
       <c r="B1543" s="26">
         <v>1</v>
@@ -47759,12 +47774,11 @@
         <v>0</v>
       </c>
       <c r="D1543" s="28" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="E1543" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1543" s="28"/>
       <c r="G1543">
         <v>10</v>
       </c>
@@ -47772,12 +47786,12 @@
         <v>1</v>
       </c>
       <c r="I1543">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1544" spans="1:9">
       <c r="A1544">
-        <v>920110</v>
+        <v>16920101</v>
       </c>
       <c r="B1544" s="26">
         <v>1</v>
@@ -47786,11 +47800,12 @@
         <v>0</v>
       </c>
       <c r="D1544" s="28" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="E1544" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1544" s="28"/>
       <c r="G1544">
         <v>10</v>
       </c>
@@ -47798,12 +47813,12 @@
         <v>1</v>
       </c>
       <c r="I1544">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1545" spans="1:9">
       <c r="A1545">
-        <v>1920110</v>
+        <v>920110</v>
       </c>
       <c r="B1545" s="26">
         <v>1</v>
@@ -47812,10 +47827,10 @@
         <v>0</v>
       </c>
       <c r="D1545" s="28" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E1545" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1545">
         <v>10</v>
@@ -47824,12 +47839,12 @@
         <v>1</v>
       </c>
       <c r="I1545">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1546" spans="1:9">
       <c r="A1546">
-        <v>2920110</v>
+        <v>1920110</v>
       </c>
       <c r="B1546" s="26">
         <v>1</v>
@@ -47838,7 +47853,7 @@
         <v>0</v>
       </c>
       <c r="D1546" s="28" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="E1546" s="29" t="s">
         <v>769</v>
@@ -47850,12 +47865,12 @@
         <v>1</v>
       </c>
       <c r="I1546">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1547" spans="1:9">
       <c r="A1547">
-        <v>3920110</v>
+        <v>2920110</v>
       </c>
       <c r="B1547" s="26">
         <v>1</v>
@@ -47864,7 +47879,7 @@
         <v>0</v>
       </c>
       <c r="D1547" s="28" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="E1547" s="29" t="s">
         <v>769</v>
@@ -47876,12 +47891,12 @@
         <v>1</v>
       </c>
       <c r="I1547">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1548" spans="1:9">
       <c r="A1548">
-        <v>4920110</v>
+        <v>3920110</v>
       </c>
       <c r="B1548" s="26">
         <v>1</v>
@@ -47890,7 +47905,7 @@
         <v>0</v>
       </c>
       <c r="D1548" s="28" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E1548" s="29" t="s">
         <v>769</v>
@@ -47902,12 +47917,12 @@
         <v>1</v>
       </c>
       <c r="I1548">
-        <v>2500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1549" spans="1:9">
       <c r="A1549">
-        <v>6920110</v>
+        <v>4920110</v>
       </c>
       <c r="B1549" s="26">
         <v>1</v>
@@ -47916,7 +47931,7 @@
         <v>0</v>
       </c>
       <c r="D1549" s="28" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E1549" s="29" t="s">
         <v>769</v>
@@ -47928,12 +47943,12 @@
         <v>1</v>
       </c>
       <c r="I1549">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1550" spans="1:9">
       <c r="A1550">
-        <v>7920110</v>
+        <v>6920110</v>
       </c>
       <c r="B1550" s="26">
         <v>1</v>
@@ -47942,7 +47957,7 @@
         <v>0</v>
       </c>
       <c r="D1550" s="28" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="E1550" s="29" t="s">
         <v>769</v>
@@ -47951,15 +47966,15 @@
         <v>10</v>
       </c>
       <c r="H1550">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1550">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1551" spans="1:9">
       <c r="A1551">
-        <v>8920110</v>
+        <v>7920110</v>
       </c>
       <c r="B1551" s="26">
         <v>1</v>
@@ -47968,7 +47983,7 @@
         <v>0</v>
       </c>
       <c r="D1551" s="28" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E1551" s="29" t="s">
         <v>769</v>
@@ -47977,15 +47992,15 @@
         <v>10</v>
       </c>
       <c r="H1551">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1551">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1552" spans="1:9">
       <c r="A1552">
-        <v>9920110</v>
+        <v>8920110</v>
       </c>
       <c r="B1552" s="26">
         <v>1</v>
@@ -47994,7 +48009,7 @@
         <v>0</v>
       </c>
       <c r="D1552" s="28" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="E1552" s="29" t="s">
         <v>769</v>
@@ -48003,15 +48018,15 @@
         <v>10</v>
       </c>
       <c r="H1552">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1552">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1553" spans="1:9">
       <c r="A1553">
-        <v>13920110</v>
+        <v>9920110</v>
       </c>
       <c r="B1553" s="26">
         <v>1</v>
@@ -48020,7 +48035,7 @@
         <v>0</v>
       </c>
       <c r="D1553" s="28" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="E1553" s="29" t="s">
         <v>769</v>
@@ -48029,15 +48044,15 @@
         <v>10</v>
       </c>
       <c r="H1553">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1553">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1554" spans="1:9">
       <c r="A1554">
-        <v>920115</v>
+        <v>13920110</v>
       </c>
       <c r="B1554" s="26">
         <v>1</v>
@@ -48046,12 +48061,11 @@
         <v>0</v>
       </c>
       <c r="D1554" s="28" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="E1554" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1554" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1554">
         <v>10</v>
       </c>
@@ -48059,12 +48073,12 @@
         <v>1</v>
       </c>
       <c r="I1554">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1555" spans="1:9">
       <c r="A1555">
-        <v>820096</v>
+        <v>920115</v>
       </c>
       <c r="B1555" s="26">
         <v>1</v>
@@ -48072,12 +48086,13 @@
       <c r="C1555">
         <v>0</v>
       </c>
-      <c r="D1555" s="30" t="s">
-        <v>1156</v>
-      </c>
-      <c r="E1555" s="30" t="s">
-        <v>1156</v>
-      </c>
+      <c r="D1555" s="28" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E1555" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1555" s="28"/>
       <c r="G1555">
         <v>10</v>
       </c>
@@ -48090,7 +48105,7 @@
     </row>
     <row r="1556" spans="1:9">
       <c r="A1556">
-        <v>920114</v>
+        <v>820096</v>
       </c>
       <c r="B1556" s="26">
         <v>1</v>
@@ -48098,13 +48113,12 @@
       <c r="C1556">
         <v>0</v>
       </c>
-      <c r="D1556" s="28" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E1556" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1556" s="28"/>
+      <c r="D1556" s="30" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E1556" s="30" t="s">
+        <v>1158</v>
+      </c>
       <c r="G1556">
         <v>10</v>
       </c>
@@ -48117,7 +48131,7 @@
     </row>
     <row r="1557" spans="1:9">
       <c r="A1557">
-        <v>920116</v>
+        <v>920114</v>
       </c>
       <c r="B1557" s="26">
         <v>1</v>
@@ -48126,7 +48140,7 @@
         <v>0</v>
       </c>
       <c r="D1557" s="28" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="E1557" s="29" t="s">
         <v>767</v>
@@ -48144,71 +48158,72 @@
     </row>
     <row r="1558" spans="1:9">
       <c r="A1558">
+        <v>920116</v>
+      </c>
+      <c r="B1558" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1558">
+        <v>0</v>
+      </c>
+      <c r="D1558" s="28" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E1558" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1558" s="28"/>
+      <c r="G1558">
+        <v>10</v>
+      </c>
+      <c r="H1558">
+        <v>1</v>
+      </c>
+      <c r="I1558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:9">
+      <c r="A1559">
         <v>820097</v>
       </c>
-      <c r="B1558" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1558">
-        <v>0</v>
-      </c>
-      <c r="D1558" s="30" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E1558" s="30" t="s">
-        <v>1159</v>
-      </c>
-      <c r="G1558">
-        <v>10</v>
-      </c>
-      <c r="H1558">
-        <v>1</v>
-      </c>
-      <c r="I1558">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1559" customFormat="1" spans="1:9">
-      <c r="A1559">
+      <c r="B1559" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1559">
+        <v>0</v>
+      </c>
+      <c r="D1559" s="30" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E1559" s="30" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G1559">
+        <v>10</v>
+      </c>
+      <c r="H1559">
+        <v>1</v>
+      </c>
+      <c r="I1559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1560" customFormat="1" spans="1:9">
+      <c r="A1560">
         <v>820111</v>
       </c>
-      <c r="B1559" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1559">
-        <v>0</v>
-      </c>
-      <c r="D1559" s="30" t="s">
-        <v>1160</v>
-      </c>
-      <c r="E1559" s="30" t="s">
-        <v>1159</v>
-      </c>
-      <c r="G1559">
-        <v>10</v>
-      </c>
-      <c r="H1559">
-        <v>1</v>
-      </c>
-      <c r="I1559">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1560" spans="1:9">
-      <c r="A1560">
-        <v>920111</v>
-      </c>
       <c r="B1560" s="26">
         <v>1</v>
       </c>
       <c r="C1560">
         <v>0</v>
       </c>
-      <c r="D1560" s="28" t="s">
+      <c r="D1560" s="30" t="s">
         <v>1161</v>
       </c>
-      <c r="E1560" s="29" t="s">
-        <v>767</v>
+      <c r="E1560" s="30" t="s">
+        <v>1123</v>
       </c>
       <c r="G1560">
         <v>10</v>
@@ -48222,7 +48237,7 @@
     </row>
     <row r="1561" spans="1:9">
       <c r="A1561">
-        <v>1920111</v>
+        <v>920111</v>
       </c>
       <c r="B1561" s="26">
         <v>1</v>
@@ -48234,7 +48249,7 @@
         <v>1162</v>
       </c>
       <c r="E1561" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1561">
         <v>10</v>
@@ -48243,12 +48258,12 @@
         <v>1</v>
       </c>
       <c r="I1561">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1562" spans="1:9">
       <c r="A1562">
-        <v>2920111</v>
+        <v>1920111</v>
       </c>
       <c r="B1562" s="26">
         <v>1</v>
@@ -48269,12 +48284,12 @@
         <v>1</v>
       </c>
       <c r="I1562">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1563" spans="1:9">
       <c r="A1563">
-        <v>3920111</v>
+        <v>2920111</v>
       </c>
       <c r="B1563" s="26">
         <v>1</v>
@@ -48295,12 +48310,12 @@
         <v>1</v>
       </c>
       <c r="I1563">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1564" spans="1:9">
       <c r="A1564">
-        <v>4920111</v>
+        <v>3920111</v>
       </c>
       <c r="B1564" s="26">
         <v>1</v>
@@ -48321,12 +48336,12 @@
         <v>1</v>
       </c>
       <c r="I1564">
-        <v>2200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1565" spans="1:9">
       <c r="A1565">
-        <v>6920111</v>
+        <v>4920111</v>
       </c>
       <c r="B1565" s="26">
         <v>1</v>
@@ -48347,12 +48362,12 @@
         <v>1</v>
       </c>
       <c r="I1565">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1566" spans="1:9">
       <c r="A1566">
-        <v>7920111</v>
+        <v>6920111</v>
       </c>
       <c r="B1566" s="26">
         <v>1</v>
@@ -48370,15 +48385,15 @@
         <v>10</v>
       </c>
       <c r="H1566">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1566">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1567" spans="1:9">
       <c r="A1567">
-        <v>8920111</v>
+        <v>7920111</v>
       </c>
       <c r="B1567" s="26">
         <v>1</v>
@@ -48396,15 +48411,15 @@
         <v>10</v>
       </c>
       <c r="H1567">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1567">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1568" spans="1:9">
       <c r="A1568">
-        <v>9920111</v>
+        <v>8920111</v>
       </c>
       <c r="B1568" s="26">
         <v>1</v>
@@ -48422,15 +48437,15 @@
         <v>10</v>
       </c>
       <c r="H1568">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1568">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1569" spans="1:9">
       <c r="A1569">
-        <v>11030111</v>
+        <v>9920111</v>
       </c>
       <c r="B1569" s="26">
         <v>1</v>
@@ -48448,15 +48463,15 @@
         <v>10</v>
       </c>
       <c r="H1569">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1569">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1570" spans="1:9">
       <c r="A1570">
-        <v>11920111</v>
+        <v>11030111</v>
       </c>
       <c r="B1570" s="26">
         <v>1</v>
@@ -48477,12 +48492,12 @@
         <v>1</v>
       </c>
       <c r="I1570">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1571" spans="1:9">
       <c r="A1571">
-        <v>13920111</v>
+        <v>11920111</v>
       </c>
       <c r="B1571" s="26">
         <v>1</v>
@@ -48503,12 +48518,12 @@
         <v>1</v>
       </c>
       <c r="I1571">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1572" spans="1:9">
       <c r="A1572">
-        <v>920118</v>
+        <v>13920111</v>
       </c>
       <c r="B1572" s="26">
         <v>1</v>
@@ -48520,9 +48535,8 @@
         <v>1173</v>
       </c>
       <c r="E1572" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1572" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1572">
         <v>10</v>
       </c>
@@ -48530,12 +48544,12 @@
         <v>1</v>
       </c>
       <c r="I1572">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1573" spans="1:9">
       <c r="A1573">
-        <v>820100</v>
+        <v>920118</v>
       </c>
       <c r="B1573" s="26">
         <v>1</v>
@@ -48543,12 +48557,13 @@
       <c r="C1573">
         <v>0</v>
       </c>
-      <c r="D1573" s="30" t="s">
+      <c r="D1573" s="28" t="s">
         <v>1174</v>
       </c>
-      <c r="E1573" s="30" t="s">
-        <v>1174</v>
-      </c>
+      <c r="E1573" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1573" s="28"/>
       <c r="G1573">
         <v>10</v>
       </c>
@@ -48561,7 +48576,7 @@
     </row>
     <row r="1574" spans="1:9">
       <c r="A1574">
-        <v>920112</v>
+        <v>820100</v>
       </c>
       <c r="B1574" s="26">
         <v>1</v>
@@ -48569,11 +48584,11 @@
       <c r="C1574">
         <v>0</v>
       </c>
-      <c r="D1574" s="28" t="s">
+      <c r="D1574" s="30" t="s">
         <v>1175</v>
       </c>
-      <c r="E1574" s="29" t="s">
-        <v>767</v>
+      <c r="E1574" s="30" t="s">
+        <v>1175</v>
       </c>
       <c r="G1574">
         <v>10</v>
@@ -48587,7 +48602,7 @@
     </row>
     <row r="1575" spans="1:9">
       <c r="A1575">
-        <v>1920112</v>
+        <v>920112</v>
       </c>
       <c r="B1575" s="26">
         <v>1</v>
@@ -48599,7 +48614,7 @@
         <v>1176</v>
       </c>
       <c r="E1575" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1575">
         <v>10</v>
@@ -48608,12 +48623,12 @@
         <v>1</v>
       </c>
       <c r="I1575">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1576" spans="1:9">
       <c r="A1576">
-        <v>2920112</v>
+        <v>1920112</v>
       </c>
       <c r="B1576" s="26">
         <v>1</v>
@@ -48634,12 +48649,12 @@
         <v>1</v>
       </c>
       <c r="I1576">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1577" spans="1:9">
       <c r="A1577">
-        <v>3920112</v>
+        <v>2920112</v>
       </c>
       <c r="B1577" s="26">
         <v>1</v>
@@ -48660,12 +48675,12 @@
         <v>1</v>
       </c>
       <c r="I1577">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1578" spans="1:9">
       <c r="A1578">
-        <v>4920112</v>
+        <v>3920112</v>
       </c>
       <c r="B1578" s="26">
         <v>1</v>
@@ -48686,12 +48701,12 @@
         <v>1</v>
       </c>
       <c r="I1578">
-        <v>2200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1579" spans="1:9">
       <c r="A1579">
-        <v>6920112</v>
+        <v>4920112</v>
       </c>
       <c r="B1579" s="26">
         <v>1</v>
@@ -48712,12 +48727,12 @@
         <v>1</v>
       </c>
       <c r="I1579">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1580" spans="1:9">
       <c r="A1580">
-        <v>7920112</v>
+        <v>6920112</v>
       </c>
       <c r="B1580" s="26">
         <v>1</v>
@@ -48735,15 +48750,15 @@
         <v>10</v>
       </c>
       <c r="H1580">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1580">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1581" spans="1:9">
       <c r="A1581">
-        <v>8920112</v>
+        <v>7920112</v>
       </c>
       <c r="B1581" s="26">
         <v>1</v>
@@ -48761,15 +48776,15 @@
         <v>10</v>
       </c>
       <c r="H1581">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1581">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1582" spans="1:9">
       <c r="A1582">
-        <v>9920112</v>
+        <v>8920112</v>
       </c>
       <c r="B1582" s="26">
         <v>1</v>
@@ -48787,15 +48802,15 @@
         <v>10</v>
       </c>
       <c r="H1582">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1582">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1583" spans="1:9">
       <c r="A1583">
-        <v>13920112</v>
+        <v>9920112</v>
       </c>
       <c r="B1583" s="26">
         <v>1</v>
@@ -48813,15 +48828,15 @@
         <v>10</v>
       </c>
       <c r="H1583">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1583">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1584" spans="1:9">
       <c r="A1584">
-        <v>920117</v>
+        <v>13920112</v>
       </c>
       <c r="B1584" s="26">
         <v>1</v>
@@ -48833,9 +48848,8 @@
         <v>1185</v>
       </c>
       <c r="E1584" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1584" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1584">
         <v>10</v>
       </c>
@@ -48843,58 +48857,56 @@
         <v>1</v>
       </c>
       <c r="I1584">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1585" spans="1:9">
       <c r="A1585">
+        <v>920117</v>
+      </c>
+      <c r="B1585" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1585">
+        <v>0</v>
+      </c>
+      <c r="D1585" s="28" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E1585" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1585" s="28"/>
+      <c r="G1585">
+        <v>10</v>
+      </c>
+      <c r="H1585">
+        <v>1</v>
+      </c>
+      <c r="I1585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:9">
+      <c r="A1586">
         <v>820099</v>
       </c>
-      <c r="B1585" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1585">
-        <v>0</v>
-      </c>
-      <c r="D1585" s="30" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E1585" s="30" t="s">
-        <v>1186</v>
-      </c>
-      <c r="G1585">
-        <v>10</v>
-      </c>
-      <c r="H1585">
-        <v>1</v>
-      </c>
-      <c r="I1585">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1586" spans="1:9">
-      <c r="A1586" s="26">
-        <v>5101721</v>
-      </c>
       <c r="B1586" s="26">
         <v>1</v>
       </c>
-      <c r="C1586" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1586" s="27" t="s">
+      <c r="C1586">
+        <v>0</v>
+      </c>
+      <c r="D1586" s="30" t="s">
         <v>1187</v>
       </c>
-      <c r="E1586" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1586" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1586" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1586" s="26">
+      <c r="E1586" s="30" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G1586">
+        <v>10</v>
+      </c>
+      <c r="H1586">
         <v>1</v>
       </c>
       <c r="I1586">
@@ -48903,7 +48915,7 @@
     </row>
     <row r="1587" spans="1:9">
       <c r="A1587" s="26">
-        <v>5101722</v>
+        <v>5101721</v>
       </c>
       <c r="B1587" s="26">
         <v>1</v>
@@ -48915,7 +48927,7 @@
         <v>1188</v>
       </c>
       <c r="E1587" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1587" s="9" t="s">
         <v>100</v>
@@ -48924,7 +48936,7 @@
         <v>10</v>
       </c>
       <c r="H1587" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1587">
         <v>0</v>
@@ -48932,7 +48944,7 @@
     </row>
     <row r="1588" spans="1:9">
       <c r="A1588" s="26">
-        <v>5101723</v>
+        <v>5101722</v>
       </c>
       <c r="B1588" s="26">
         <v>1</v>
@@ -48961,7 +48973,7 @@
     </row>
     <row r="1589" spans="1:9">
       <c r="A1589" s="26">
-        <v>5101724</v>
+        <v>5101723</v>
       </c>
       <c r="B1589" s="26">
         <v>1</v>
@@ -48988,9 +49000,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1590" ht="14" customHeight="1" spans="1:9">
+    <row r="1590" spans="1:9">
       <c r="A1590" s="26">
-        <v>5101725</v>
+        <v>5101724</v>
       </c>
       <c r="B1590" s="26">
         <v>1</v>
@@ -49002,7 +49014,7 @@
         <v>1191</v>
       </c>
       <c r="E1590" s="26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1590" s="9" t="s">
         <v>100</v>
@@ -49017,9 +49029,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1591" spans="1:9">
+    <row r="1591" ht="14" customHeight="1" spans="1:9">
       <c r="A1591" s="26">
-        <v>5101730</v>
+        <v>5101725</v>
       </c>
       <c r="B1591" s="26">
         <v>1</v>
@@ -49031,7 +49043,7 @@
         <v>1192</v>
       </c>
       <c r="E1591" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1591" s="9" t="s">
         <v>100</v>
@@ -49048,7 +49060,7 @@
     </row>
     <row r="1592" spans="1:9">
       <c r="A1592" s="26">
-        <v>5101731</v>
+        <v>5101730</v>
       </c>
       <c r="B1592" s="26">
         <v>1</v>
@@ -49060,7 +49072,7 @@
         <v>1193</v>
       </c>
       <c r="E1592" s="26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1592" s="9" t="s">
         <v>100</v>
@@ -49069,7 +49081,7 @@
         <v>10</v>
       </c>
       <c r="H1592" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1592">
         <v>0</v>
@@ -49077,7 +49089,7 @@
     </row>
     <row r="1593" spans="1:9">
       <c r="A1593" s="26">
-        <v>5101732</v>
+        <v>5101731</v>
       </c>
       <c r="B1593" s="26">
         <v>1</v>
@@ -49089,7 +49101,7 @@
         <v>1194</v>
       </c>
       <c r="E1593" s="26" t="s">
-        <v>971</v>
+        <v>327</v>
       </c>
       <c r="F1593" s="9" t="s">
         <v>100</v>
@@ -49106,7 +49118,7 @@
     </row>
     <row r="1594" spans="1:9">
       <c r="A1594" s="26">
-        <v>5101734</v>
+        <v>5101732</v>
       </c>
       <c r="B1594" s="26">
         <v>1</v>
@@ -49118,7 +49130,7 @@
         <v>1195</v>
       </c>
       <c r="E1594" s="26" t="s">
-        <v>245</v>
+        <v>971</v>
       </c>
       <c r="F1594" s="9" t="s">
         <v>100</v>
@@ -49127,7 +49139,7 @@
         <v>10</v>
       </c>
       <c r="H1594" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1594">
         <v>0</v>
@@ -49135,7 +49147,7 @@
     </row>
     <row r="1595" spans="1:9">
       <c r="A1595" s="26">
-        <v>5101735</v>
+        <v>5101734</v>
       </c>
       <c r="B1595" s="26">
         <v>1</v>
@@ -49147,7 +49159,7 @@
         <v>1196</v>
       </c>
       <c r="E1595" s="26" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1595" s="9" t="s">
         <v>100</v>
@@ -49156,15 +49168,15 @@
         <v>10</v>
       </c>
       <c r="H1595" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1595">
         <v>0</v>
       </c>
     </row>
-    <row r="1596" ht="14" customHeight="1" spans="1:9">
+    <row r="1596" spans="1:9">
       <c r="A1596" s="26">
-        <v>5101733</v>
+        <v>5101735</v>
       </c>
       <c r="B1596" s="26">
         <v>1</v>
@@ -49176,18 +49188,163 @@
         <v>1197</v>
       </c>
       <c r="E1596" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1596" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1596" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1596" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1597" ht="14" customHeight="1" spans="1:9">
+      <c r="A1597" s="26">
+        <v>5101733</v>
+      </c>
+      <c r="B1597" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1597" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1597" s="27" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E1597" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="F1596" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1596" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1596" s="26">
+      <c r="F1597" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1597" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1597" s="26">
         <v>2</v>
       </c>
-      <c r="I1596">
+      <c r="I1597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:9">
+      <c r="A1598" s="26">
+        <v>5101734</v>
+      </c>
+      <c r="B1598" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1598" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1598" s="27" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E1598" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1598" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1598" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1598" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:9">
+      <c r="A1599" s="26">
+        <v>5101735</v>
+      </c>
+      <c r="B1599" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1599" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1599" s="27" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1599" s="26" t="s">
+        <v>971</v>
+      </c>
+      <c r="F1599" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1599" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1599" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:9">
+      <c r="A1600" s="26">
+        <v>5101736</v>
+      </c>
+      <c r="B1600" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1600" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1600" s="27" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E1600" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1600" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1600" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1600" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:9">
+      <c r="A1601" s="26">
+        <v>5101737</v>
+      </c>
+      <c r="B1601" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1601" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1601" s="27" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E1601" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1601" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1601" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1601" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1601">
         <v>0</v>
       </c>
     </row>
@@ -49253,7 +49410,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -49265,10 +49422,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -49282,90 +49439,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1219</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1220</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1221</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1222</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1223</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1224</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -49376,7 +49533,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -49397,7 +49554,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -49409,7 +49566,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49420,7 +49577,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -49461,7 +49618,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -49502,7 +49659,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -49523,7 +49680,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -49535,7 +49692,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49546,7 +49703,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49567,7 +49724,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49579,7 +49736,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49590,7 +49747,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49611,7 +49768,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -47920,7 +47920,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="1549" spans="1:9">
+    <row r="1549" ht="12" customHeight="1" spans="1:9">
       <c r="A1549">
         <v>4920110</v>
       </c>
@@ -47943,7 +47943,7 @@
         <v>1</v>
       </c>
       <c r="I1549">
-        <v>2500</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1550" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4171" uniqueCount="1243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4173" uniqueCount="1244">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3513,6 +3513,9 @@
   </si>
   <si>
     <t>传染_获得</t>
+  </si>
+  <si>
+    <t>传染_技能效果半径</t>
   </si>
   <si>
     <t>传染被动_获得</t>
@@ -5093,7 +5096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1601"/>
+  <dimension ref="A1:I1602"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -47137,9 +47140,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1519" spans="1:9">
+    <row r="1519" customFormat="1" spans="1:9">
       <c r="A1519">
-        <v>920113</v>
+        <v>4920115</v>
       </c>
       <c r="B1519" s="26">
         <v>1</v>
@@ -47151,9 +47154,9 @@
         <v>1120</v>
       </c>
       <c r="E1519" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1519" s="28"/>
+        <v>769</v>
+      </c>
+      <c r="F1519"/>
       <c r="G1519">
         <v>10</v>
       </c>
@@ -47161,38 +47164,39 @@
         <v>1</v>
       </c>
       <c r="I1519">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1520" spans="1:9">
       <c r="A1520">
+        <v>920113</v>
+      </c>
+      <c r="B1520" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1520">
+        <v>0</v>
+      </c>
+      <c r="D1520" s="28" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E1520" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1520" s="28"/>
+      <c r="G1520">
+        <v>10</v>
+      </c>
+      <c r="H1520">
+        <v>1</v>
+      </c>
+      <c r="I1520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:9">
+      <c r="A1521">
         <v>820095</v>
-      </c>
-      <c r="B1520" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1520">
-        <v>0</v>
-      </c>
-      <c r="D1520" s="30" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E1520" s="30" t="s">
-        <v>1121</v>
-      </c>
-      <c r="G1520">
-        <v>10</v>
-      </c>
-      <c r="H1520">
-        <v>1</v>
-      </c>
-      <c r="I1520">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1521" customFormat="1" spans="1:9">
-      <c r="A1521">
-        <v>820112</v>
       </c>
       <c r="B1521" s="26">
         <v>1</v>
@@ -47204,33 +47208,33 @@
         <v>1122</v>
       </c>
       <c r="E1521" s="30" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G1521">
+        <v>10</v>
+      </c>
+      <c r="H1521">
+        <v>1</v>
+      </c>
+      <c r="I1521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1522" customFormat="1" spans="1:9">
+      <c r="A1522">
+        <v>820112</v>
+      </c>
+      <c r="B1522" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1522">
+        <v>0</v>
+      </c>
+      <c r="D1522" s="30" t="s">
         <v>1123</v>
       </c>
-      <c r="G1521">
-        <v>10</v>
-      </c>
-      <c r="H1521">
-        <v>1</v>
-      </c>
-      <c r="I1521">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1522" spans="1:9">
-      <c r="A1522">
-        <v>920107</v>
-      </c>
-      <c r="B1522" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1522">
-        <v>0</v>
-      </c>
-      <c r="D1522" s="28" t="s">
+      <c r="E1522" s="30" t="s">
         <v>1124</v>
-      </c>
-      <c r="E1522" s="29" t="s">
-        <v>767</v>
       </c>
       <c r="G1522">
         <v>10</v>
@@ -47244,7 +47248,7 @@
     </row>
     <row r="1523" spans="1:9">
       <c r="A1523">
-        <v>2920107</v>
+        <v>920107</v>
       </c>
       <c r="B1523" s="26">
         <v>1</v>
@@ -47256,7 +47260,7 @@
         <v>1125</v>
       </c>
       <c r="E1523" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1523">
         <v>10</v>
@@ -47270,7 +47274,7 @@
     </row>
     <row r="1524" spans="1:9">
       <c r="A1524">
-        <v>39201057</v>
+        <v>2920107</v>
       </c>
       <c r="B1524" s="26">
         <v>1</v>
@@ -47296,7 +47300,7 @@
     </row>
     <row r="1525" spans="1:9">
       <c r="A1525">
-        <v>4920107</v>
+        <v>39201057</v>
       </c>
       <c r="B1525" s="26">
         <v>1</v>
@@ -47317,12 +47321,12 @@
         <v>1</v>
       </c>
       <c r="I1525">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1526" spans="1:9">
       <c r="A1526">
-        <v>6920107</v>
+        <v>4920107</v>
       </c>
       <c r="B1526" s="26">
         <v>1</v>
@@ -47343,12 +47347,12 @@
         <v>1</v>
       </c>
       <c r="I1526">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1527" spans="1:9">
       <c r="A1527">
-        <v>7920107</v>
+        <v>6920107</v>
       </c>
       <c r="B1527" s="26">
         <v>1</v>
@@ -47366,15 +47370,15 @@
         <v>10</v>
       </c>
       <c r="H1527">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1527">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1528" spans="1:9">
       <c r="A1528">
-        <v>8920107</v>
+        <v>7920107</v>
       </c>
       <c r="B1528" s="26">
         <v>1</v>
@@ -47392,15 +47396,15 @@
         <v>10</v>
       </c>
       <c r="H1528">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1528">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1529" spans="1:9">
       <c r="A1529">
-        <v>9920107</v>
+        <v>8920107</v>
       </c>
       <c r="B1529" s="26">
         <v>1</v>
@@ -47418,15 +47422,15 @@
         <v>10</v>
       </c>
       <c r="H1529">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1529">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1530" spans="1:9">
       <c r="A1530">
-        <v>11030107</v>
+        <v>9920107</v>
       </c>
       <c r="B1530" s="26">
         <v>1</v>
@@ -47444,15 +47448,15 @@
         <v>10</v>
       </c>
       <c r="H1530">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1530">
-        <v>2000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1531" spans="1:9">
       <c r="A1531">
-        <v>11920107</v>
+        <v>11030107</v>
       </c>
       <c r="B1531" s="26">
         <v>1</v>
@@ -47473,12 +47477,12 @@
         <v>1</v>
       </c>
       <c r="I1531">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1532" spans="1:9">
       <c r="A1532">
-        <v>13920107</v>
+        <v>11920107</v>
       </c>
       <c r="B1532" s="26">
         <v>1</v>
@@ -47499,12 +47503,12 @@
         <v>1</v>
       </c>
       <c r="I1532">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1533" spans="1:9">
       <c r="A1533">
-        <v>920108</v>
+        <v>13920107</v>
       </c>
       <c r="B1533" s="26">
         <v>1</v>
@@ -47516,9 +47520,8 @@
         <v>1135</v>
       </c>
       <c r="E1533" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1533" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1533">
         <v>10</v>
       </c>
@@ -47526,12 +47529,12 @@
         <v>1</v>
       </c>
       <c r="I1533">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1534" spans="1:9">
       <c r="A1534">
-        <v>820098</v>
+        <v>920108</v>
       </c>
       <c r="B1534" s="26">
         <v>1</v>
@@ -47539,12 +47542,13 @@
       <c r="C1534">
         <v>0</v>
       </c>
-      <c r="D1534" s="30" t="s">
+      <c r="D1534" s="28" t="s">
         <v>1136</v>
       </c>
-      <c r="E1534" s="30" t="s">
-        <v>1136</v>
-      </c>
+      <c r="E1534" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1534" s="28"/>
       <c r="G1534">
         <v>10</v>
       </c>
@@ -47557,7 +47561,7 @@
     </row>
     <row r="1535" spans="1:9">
       <c r="A1535">
-        <v>920109</v>
+        <v>820098</v>
       </c>
       <c r="B1535" s="26">
         <v>1</v>
@@ -47565,11 +47569,11 @@
       <c r="C1535">
         <v>0</v>
       </c>
-      <c r="D1535" s="28" t="s">
+      <c r="D1535" s="30" t="s">
         <v>1137</v>
       </c>
-      <c r="E1535" s="29" t="s">
-        <v>767</v>
+      <c r="E1535" s="30" t="s">
+        <v>1137</v>
       </c>
       <c r="G1535">
         <v>10</v>
@@ -47583,7 +47587,7 @@
     </row>
     <row r="1536" spans="1:9">
       <c r="A1536">
-        <v>2920109</v>
+        <v>920109</v>
       </c>
       <c r="B1536" s="26">
         <v>1</v>
@@ -47595,7 +47599,7 @@
         <v>1138</v>
       </c>
       <c r="E1536" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1536">
         <v>10</v>
@@ -47609,7 +47613,7 @@
     </row>
     <row r="1537" spans="1:9">
       <c r="A1537">
-        <v>3920109</v>
+        <v>2920109</v>
       </c>
       <c r="B1537" s="26">
         <v>1</v>
@@ -47630,12 +47634,12 @@
         <v>1</v>
       </c>
       <c r="I1537">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1538" spans="1:9">
       <c r="A1538">
-        <v>4920109</v>
+        <v>3920109</v>
       </c>
       <c r="B1538" s="26">
         <v>1</v>
@@ -47656,12 +47660,12 @@
         <v>1</v>
       </c>
       <c r="I1538">
-        <v>1600</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1539" spans="1:9">
       <c r="A1539">
-        <v>6920109</v>
+        <v>4920109</v>
       </c>
       <c r="B1539" s="26">
         <v>1</v>
@@ -47682,12 +47686,12 @@
         <v>1</v>
       </c>
       <c r="I1539">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1540" spans="1:9">
       <c r="A1540">
-        <v>7920109</v>
+        <v>6920109</v>
       </c>
       <c r="B1540" s="26">
         <v>1</v>
@@ -47705,7 +47709,7 @@
         <v>10</v>
       </c>
       <c r="H1540">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1540">
         <v>0</v>
@@ -47713,7 +47717,7 @@
     </row>
     <row r="1541" spans="1:9">
       <c r="A1541">
-        <v>8920109</v>
+        <v>7920109</v>
       </c>
       <c r="B1541" s="26">
         <v>1</v>
@@ -47731,7 +47735,7 @@
         <v>10</v>
       </c>
       <c r="H1541">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1541">
         <v>0</v>
@@ -47739,7 +47743,7 @@
     </row>
     <row r="1542" spans="1:9">
       <c r="A1542">
-        <v>9920109</v>
+        <v>8920109</v>
       </c>
       <c r="B1542" s="26">
         <v>1</v>
@@ -47757,7 +47761,7 @@
         <v>10</v>
       </c>
       <c r="H1542">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1542">
         <v>0</v>
@@ -47765,7 +47769,7 @@
     </row>
     <row r="1543" spans="1:9">
       <c r="A1543">
-        <v>13920109</v>
+        <v>9920109</v>
       </c>
       <c r="B1543" s="26">
         <v>1</v>
@@ -47783,15 +47787,15 @@
         <v>10</v>
       </c>
       <c r="H1543">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1543">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1544" spans="1:9">
       <c r="A1544">
-        <v>16920101</v>
+        <v>13920109</v>
       </c>
       <c r="B1544" s="26">
         <v>1</v>
@@ -47805,7 +47809,6 @@
       <c r="E1544" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1544" s="28"/>
       <c r="G1544">
         <v>10</v>
       </c>
@@ -47813,12 +47816,12 @@
         <v>1</v>
       </c>
       <c r="I1544">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1545" spans="1:9">
       <c r="A1545">
-        <v>920110</v>
+        <v>16920101</v>
       </c>
       <c r="B1545" s="26">
         <v>1</v>
@@ -47830,8 +47833,9 @@
         <v>1147</v>
       </c>
       <c r="E1545" s="29" t="s">
-        <v>767</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F1545" s="28"/>
       <c r="G1545">
         <v>10</v>
       </c>
@@ -47839,12 +47843,12 @@
         <v>1</v>
       </c>
       <c r="I1545">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1546" spans="1:9">
       <c r="A1546">
-        <v>1920110</v>
+        <v>920110</v>
       </c>
       <c r="B1546" s="26">
         <v>1</v>
@@ -47856,7 +47860,7 @@
         <v>1148</v>
       </c>
       <c r="E1546" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1546">
         <v>10</v>
@@ -47865,12 +47869,12 @@
         <v>1</v>
       </c>
       <c r="I1546">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1547" spans="1:9">
       <c r="A1547">
-        <v>2920110</v>
+        <v>1920110</v>
       </c>
       <c r="B1547" s="26">
         <v>1</v>
@@ -47891,12 +47895,12 @@
         <v>1</v>
       </c>
       <c r="I1547">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1548" spans="1:9">
       <c r="A1548">
-        <v>3920110</v>
+        <v>2920110</v>
       </c>
       <c r="B1548" s="26">
         <v>1</v>
@@ -47917,12 +47921,12 @@
         <v>1</v>
       </c>
       <c r="I1548">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="1549" ht="12" customHeight="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:9">
       <c r="A1549">
-        <v>4920110</v>
+        <v>3920110</v>
       </c>
       <c r="B1549" s="26">
         <v>1</v>
@@ -47943,12 +47947,12 @@
         <v>1</v>
       </c>
       <c r="I1549">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="1550" spans="1:9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1550" ht="12" customHeight="1" spans="1:9">
       <c r="A1550">
-        <v>6920110</v>
+        <v>4920110</v>
       </c>
       <c r="B1550" s="26">
         <v>1</v>
@@ -47969,12 +47973,12 @@
         <v>1</v>
       </c>
       <c r="I1550">
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1551" spans="1:9">
       <c r="A1551">
-        <v>7920110</v>
+        <v>6920110</v>
       </c>
       <c r="B1551" s="26">
         <v>1</v>
@@ -47992,15 +47996,15 @@
         <v>10</v>
       </c>
       <c r="H1551">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1551">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1552" spans="1:9">
       <c r="A1552">
-        <v>8920110</v>
+        <v>7920110</v>
       </c>
       <c r="B1552" s="26">
         <v>1</v>
@@ -48018,15 +48022,15 @@
         <v>10</v>
       </c>
       <c r="H1552">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1552">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1553" spans="1:9">
       <c r="A1553">
-        <v>9920110</v>
+        <v>8920110</v>
       </c>
       <c r="B1553" s="26">
         <v>1</v>
@@ -48044,15 +48048,15 @@
         <v>10</v>
       </c>
       <c r="H1553">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1553">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1554" spans="1:9">
       <c r="A1554">
-        <v>13920110</v>
+        <v>9920110</v>
       </c>
       <c r="B1554" s="26">
         <v>1</v>
@@ -48070,15 +48074,15 @@
         <v>10</v>
       </c>
       <c r="H1554">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1554">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1555" spans="1:9">
       <c r="A1555">
-        <v>920115</v>
+        <v>13920110</v>
       </c>
       <c r="B1555" s="26">
         <v>1</v>
@@ -48090,9 +48094,8 @@
         <v>1157</v>
       </c>
       <c r="E1555" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1555" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1555">
         <v>10</v>
       </c>
@@ -48100,12 +48103,12 @@
         <v>1</v>
       </c>
       <c r="I1555">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1556" spans="1:9">
       <c r="A1556">
-        <v>820096</v>
+        <v>920115</v>
       </c>
       <c r="B1556" s="26">
         <v>1</v>
@@ -48113,12 +48116,13 @@
       <c r="C1556">
         <v>0</v>
       </c>
-      <c r="D1556" s="30" t="s">
+      <c r="D1556" s="28" t="s">
         <v>1158</v>
       </c>
-      <c r="E1556" s="30" t="s">
-        <v>1158</v>
-      </c>
+      <c r="E1556" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1556" s="28"/>
       <c r="G1556">
         <v>10</v>
       </c>
@@ -48131,7 +48135,7 @@
     </row>
     <row r="1557" spans="1:9">
       <c r="A1557">
-        <v>920114</v>
+        <v>820096</v>
       </c>
       <c r="B1557" s="26">
         <v>1</v>
@@ -48139,13 +48143,12 @@
       <c r="C1557">
         <v>0</v>
       </c>
-      <c r="D1557" s="28" t="s">
+      <c r="D1557" s="30" t="s">
         <v>1159</v>
       </c>
-      <c r="E1557" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1557" s="28"/>
+      <c r="E1557" s="30" t="s">
+        <v>1159</v>
+      </c>
       <c r="G1557">
         <v>10</v>
       </c>
@@ -48158,7 +48161,7 @@
     </row>
     <row r="1558" spans="1:9">
       <c r="A1558">
-        <v>920116</v>
+        <v>920114</v>
       </c>
       <c r="B1558" s="26">
         <v>1</v>
@@ -48185,71 +48188,72 @@
     </row>
     <row r="1559" spans="1:9">
       <c r="A1559">
+        <v>920116</v>
+      </c>
+      <c r="B1559" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1559">
+        <v>0</v>
+      </c>
+      <c r="D1559" s="28" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E1559" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1559" s="28"/>
+      <c r="G1559">
+        <v>10</v>
+      </c>
+      <c r="H1559">
+        <v>1</v>
+      </c>
+      <c r="I1559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:9">
+      <c r="A1560">
         <v>820097</v>
       </c>
-      <c r="B1559" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1559">
-        <v>0</v>
-      </c>
-      <c r="D1559" s="30" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E1559" s="30" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G1559">
-        <v>10</v>
-      </c>
-      <c r="H1559">
-        <v>1</v>
-      </c>
-      <c r="I1559">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1560" customFormat="1" spans="1:9">
-      <c r="A1560">
+      <c r="B1560" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1560">
+        <v>0</v>
+      </c>
+      <c r="D1560" s="30" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E1560" s="30" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G1560">
+        <v>10</v>
+      </c>
+      <c r="H1560">
+        <v>1</v>
+      </c>
+      <c r="I1560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1561" customFormat="1" spans="1:9">
+      <c r="A1561">
         <v>820111</v>
       </c>
-      <c r="B1560" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1560">
-        <v>0</v>
-      </c>
-      <c r="D1560" s="30" t="s">
-        <v>1161</v>
-      </c>
-      <c r="E1560" s="30" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G1560">
-        <v>10</v>
-      </c>
-      <c r="H1560">
-        <v>1</v>
-      </c>
-      <c r="I1560">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1561" spans="1:9">
-      <c r="A1561">
-        <v>920111</v>
-      </c>
       <c r="B1561" s="26">
         <v>1</v>
       </c>
       <c r="C1561">
         <v>0</v>
       </c>
-      <c r="D1561" s="28" t="s">
+      <c r="D1561" s="30" t="s">
         <v>1162</v>
       </c>
-      <c r="E1561" s="29" t="s">
-        <v>767</v>
+      <c r="E1561" s="30" t="s">
+        <v>1124</v>
       </c>
       <c r="G1561">
         <v>10</v>
@@ -48263,7 +48267,7 @@
     </row>
     <row r="1562" spans="1:9">
       <c r="A1562">
-        <v>1920111</v>
+        <v>920111</v>
       </c>
       <c r="B1562" s="26">
         <v>1</v>
@@ -48275,7 +48279,7 @@
         <v>1163</v>
       </c>
       <c r="E1562" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1562">
         <v>10</v>
@@ -48284,12 +48288,12 @@
         <v>1</v>
       </c>
       <c r="I1562">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1563" spans="1:9">
       <c r="A1563">
-        <v>2920111</v>
+        <v>1920111</v>
       </c>
       <c r="B1563" s="26">
         <v>1</v>
@@ -48310,12 +48314,12 @@
         <v>1</v>
       </c>
       <c r="I1563">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1564" spans="1:9">
       <c r="A1564">
-        <v>3920111</v>
+        <v>2920111</v>
       </c>
       <c r="B1564" s="26">
         <v>1</v>
@@ -48336,12 +48340,12 @@
         <v>1</v>
       </c>
       <c r="I1564">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1565" spans="1:9">
       <c r="A1565">
-        <v>4920111</v>
+        <v>3920111</v>
       </c>
       <c r="B1565" s="26">
         <v>1</v>
@@ -48362,12 +48366,12 @@
         <v>1</v>
       </c>
       <c r="I1565">
-        <v>2200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1566" spans="1:9">
       <c r="A1566">
-        <v>6920111</v>
+        <v>4920111</v>
       </c>
       <c r="B1566" s="26">
         <v>1</v>
@@ -48388,12 +48392,12 @@
         <v>1</v>
       </c>
       <c r="I1566">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1567" spans="1:9">
       <c r="A1567">
-        <v>7920111</v>
+        <v>6920111</v>
       </c>
       <c r="B1567" s="26">
         <v>1</v>
@@ -48411,15 +48415,15 @@
         <v>10</v>
       </c>
       <c r="H1567">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1567">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1568" spans="1:9">
       <c r="A1568">
-        <v>8920111</v>
+        <v>7920111</v>
       </c>
       <c r="B1568" s="26">
         <v>1</v>
@@ -48437,15 +48441,15 @@
         <v>10</v>
       </c>
       <c r="H1568">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1568">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1569" spans="1:9">
       <c r="A1569">
-        <v>9920111</v>
+        <v>8920111</v>
       </c>
       <c r="B1569" s="26">
         <v>1</v>
@@ -48463,15 +48467,15 @@
         <v>10</v>
       </c>
       <c r="H1569">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1569">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1570" spans="1:9">
       <c r="A1570">
-        <v>11030111</v>
+        <v>9920111</v>
       </c>
       <c r="B1570" s="26">
         <v>1</v>
@@ -48489,15 +48493,15 @@
         <v>10</v>
       </c>
       <c r="H1570">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1570">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1571" spans="1:9">
       <c r="A1571">
-        <v>11920111</v>
+        <v>11030111</v>
       </c>
       <c r="B1571" s="26">
         <v>1</v>
@@ -48518,12 +48522,12 @@
         <v>1</v>
       </c>
       <c r="I1571">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1572" spans="1:9">
       <c r="A1572">
-        <v>13920111</v>
+        <v>11920111</v>
       </c>
       <c r="B1572" s="26">
         <v>1</v>
@@ -48544,12 +48548,12 @@
         <v>1</v>
       </c>
       <c r="I1572">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1573" spans="1:9">
       <c r="A1573">
-        <v>920118</v>
+        <v>13920111</v>
       </c>
       <c r="B1573" s="26">
         <v>1</v>
@@ -48561,9 +48565,8 @@
         <v>1174</v>
       </c>
       <c r="E1573" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1573" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1573">
         <v>10</v>
       </c>
@@ -48571,12 +48574,12 @@
         <v>1</v>
       </c>
       <c r="I1573">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1574" spans="1:9">
       <c r="A1574">
-        <v>820100</v>
+        <v>920118</v>
       </c>
       <c r="B1574" s="26">
         <v>1</v>
@@ -48584,12 +48587,13 @@
       <c r="C1574">
         <v>0</v>
       </c>
-      <c r="D1574" s="30" t="s">
+      <c r="D1574" s="28" t="s">
         <v>1175</v>
       </c>
-      <c r="E1574" s="30" t="s">
-        <v>1175</v>
-      </c>
+      <c r="E1574" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1574" s="28"/>
       <c r="G1574">
         <v>10</v>
       </c>
@@ -48602,7 +48606,7 @@
     </row>
     <row r="1575" spans="1:9">
       <c r="A1575">
-        <v>920112</v>
+        <v>820100</v>
       </c>
       <c r="B1575" s="26">
         <v>1</v>
@@ -48610,11 +48614,11 @@
       <c r="C1575">
         <v>0</v>
       </c>
-      <c r="D1575" s="28" t="s">
+      <c r="D1575" s="30" t="s">
         <v>1176</v>
       </c>
-      <c r="E1575" s="29" t="s">
-        <v>767</v>
+      <c r="E1575" s="30" t="s">
+        <v>1176</v>
       </c>
       <c r="G1575">
         <v>10</v>
@@ -48628,7 +48632,7 @@
     </row>
     <row r="1576" spans="1:9">
       <c r="A1576">
-        <v>1920112</v>
+        <v>920112</v>
       </c>
       <c r="B1576" s="26">
         <v>1</v>
@@ -48640,7 +48644,7 @@
         <v>1177</v>
       </c>
       <c r="E1576" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1576">
         <v>10</v>
@@ -48649,12 +48653,12 @@
         <v>1</v>
       </c>
       <c r="I1576">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1577" spans="1:9">
       <c r="A1577">
-        <v>2920112</v>
+        <v>1920112</v>
       </c>
       <c r="B1577" s="26">
         <v>1</v>
@@ -48675,12 +48679,12 @@
         <v>1</v>
       </c>
       <c r="I1577">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1578" spans="1:9">
       <c r="A1578">
-        <v>3920112</v>
+        <v>2920112</v>
       </c>
       <c r="B1578" s="26">
         <v>1</v>
@@ -48701,12 +48705,12 @@
         <v>1</v>
       </c>
       <c r="I1578">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1579" spans="1:9">
       <c r="A1579">
-        <v>4920112</v>
+        <v>3920112</v>
       </c>
       <c r="B1579" s="26">
         <v>1</v>
@@ -48727,12 +48731,12 @@
         <v>1</v>
       </c>
       <c r="I1579">
-        <v>2200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1580" spans="1:9">
       <c r="A1580">
-        <v>6920112</v>
+        <v>4920112</v>
       </c>
       <c r="B1580" s="26">
         <v>1</v>
@@ -48753,12 +48757,12 @@
         <v>1</v>
       </c>
       <c r="I1580">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1581" spans="1:9">
       <c r="A1581">
-        <v>7920112</v>
+        <v>6920112</v>
       </c>
       <c r="B1581" s="26">
         <v>1</v>
@@ -48776,15 +48780,15 @@
         <v>10</v>
       </c>
       <c r="H1581">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1581">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1582" spans="1:9">
       <c r="A1582">
-        <v>8920112</v>
+        <v>7920112</v>
       </c>
       <c r="B1582" s="26">
         <v>1</v>
@@ -48802,15 +48806,15 @@
         <v>10</v>
       </c>
       <c r="H1582">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1582">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1583" spans="1:9">
       <c r="A1583">
-        <v>9920112</v>
+        <v>8920112</v>
       </c>
       <c r="B1583" s="26">
         <v>1</v>
@@ -48828,15 +48832,15 @@
         <v>10</v>
       </c>
       <c r="H1583">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1583">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1584" spans="1:9">
       <c r="A1584">
-        <v>13920112</v>
+        <v>9920112</v>
       </c>
       <c r="B1584" s="26">
         <v>1</v>
@@ -48854,15 +48858,15 @@
         <v>10</v>
       </c>
       <c r="H1584">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1584">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1585" spans="1:9">
       <c r="A1585">
-        <v>920117</v>
+        <v>13920112</v>
       </c>
       <c r="B1585" s="26">
         <v>1</v>
@@ -48874,9 +48878,8 @@
         <v>1186</v>
       </c>
       <c r="E1585" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1585" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1585">
         <v>10</v>
       </c>
@@ -48884,58 +48887,56 @@
         <v>1</v>
       </c>
       <c r="I1585">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1586" spans="1:9">
       <c r="A1586">
+        <v>920117</v>
+      </c>
+      <c r="B1586" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1586">
+        <v>0</v>
+      </c>
+      <c r="D1586" s="28" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E1586" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1586" s="28"/>
+      <c r="G1586">
+        <v>10</v>
+      </c>
+      <c r="H1586">
+        <v>1</v>
+      </c>
+      <c r="I1586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:9">
+      <c r="A1587">
         <v>820099</v>
       </c>
-      <c r="B1586" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1586">
-        <v>0</v>
-      </c>
-      <c r="D1586" s="30" t="s">
-        <v>1187</v>
-      </c>
-      <c r="E1586" s="30" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G1586">
-        <v>10</v>
-      </c>
-      <c r="H1586">
-        <v>1</v>
-      </c>
-      <c r="I1586">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1587" spans="1:9">
-      <c r="A1587" s="26">
-        <v>5101721</v>
-      </c>
       <c r="B1587" s="26">
         <v>1</v>
       </c>
-      <c r="C1587" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1587" s="27" t="s">
+      <c r="C1587">
+        <v>0</v>
+      </c>
+      <c r="D1587" s="30" t="s">
         <v>1188</v>
       </c>
-      <c r="E1587" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1587" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1587" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1587" s="26">
+      <c r="E1587" s="30" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G1587">
+        <v>10</v>
+      </c>
+      <c r="H1587">
         <v>1</v>
       </c>
       <c r="I1587">
@@ -48944,7 +48945,7 @@
     </row>
     <row r="1588" spans="1:9">
       <c r="A1588" s="26">
-        <v>5101722</v>
+        <v>5101721</v>
       </c>
       <c r="B1588" s="26">
         <v>1</v>
@@ -48956,7 +48957,7 @@
         <v>1189</v>
       </c>
       <c r="E1588" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1588" s="9" t="s">
         <v>100</v>
@@ -48965,7 +48966,7 @@
         <v>10</v>
       </c>
       <c r="H1588" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1588">
         <v>0</v>
@@ -48973,7 +48974,7 @@
     </row>
     <row r="1589" spans="1:9">
       <c r="A1589" s="26">
-        <v>5101723</v>
+        <v>5101722</v>
       </c>
       <c r="B1589" s="26">
         <v>1</v>
@@ -49002,7 +49003,7 @@
     </row>
     <row r="1590" spans="1:9">
       <c r="A1590" s="26">
-        <v>5101724</v>
+        <v>5101723</v>
       </c>
       <c r="B1590" s="26">
         <v>1</v>
@@ -49029,9 +49030,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1591" ht="14" customHeight="1" spans="1:9">
+    <row r="1591" spans="1:9">
       <c r="A1591" s="26">
-        <v>5101725</v>
+        <v>5101724</v>
       </c>
       <c r="B1591" s="26">
         <v>1</v>
@@ -49043,7 +49044,7 @@
         <v>1192</v>
       </c>
       <c r="E1591" s="26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1591" s="9" t="s">
         <v>100</v>
@@ -49058,9 +49059,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1592" spans="1:9">
+    <row r="1592" ht="14" customHeight="1" spans="1:9">
       <c r="A1592" s="26">
-        <v>5101730</v>
+        <v>5101725</v>
       </c>
       <c r="B1592" s="26">
         <v>1</v>
@@ -49072,7 +49073,7 @@
         <v>1193</v>
       </c>
       <c r="E1592" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1592" s="9" t="s">
         <v>100</v>
@@ -49089,7 +49090,7 @@
     </row>
     <row r="1593" spans="1:9">
       <c r="A1593" s="26">
-        <v>5101731</v>
+        <v>5101730</v>
       </c>
       <c r="B1593" s="26">
         <v>1</v>
@@ -49101,7 +49102,7 @@
         <v>1194</v>
       </c>
       <c r="E1593" s="26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1593" s="9" t="s">
         <v>100</v>
@@ -49110,7 +49111,7 @@
         <v>10</v>
       </c>
       <c r="H1593" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1593">
         <v>0</v>
@@ -49118,7 +49119,7 @@
     </row>
     <row r="1594" spans="1:9">
       <c r="A1594" s="26">
-        <v>5101732</v>
+        <v>5101731</v>
       </c>
       <c r="B1594" s="26">
         <v>1</v>
@@ -49130,7 +49131,7 @@
         <v>1195</v>
       </c>
       <c r="E1594" s="26" t="s">
-        <v>971</v>
+        <v>327</v>
       </c>
       <c r="F1594" s="9" t="s">
         <v>100</v>
@@ -49147,7 +49148,7 @@
     </row>
     <row r="1595" spans="1:9">
       <c r="A1595" s="26">
-        <v>5101734</v>
+        <v>5101732</v>
       </c>
       <c r="B1595" s="26">
         <v>1</v>
@@ -49159,7 +49160,7 @@
         <v>1196</v>
       </c>
       <c r="E1595" s="26" t="s">
-        <v>245</v>
+        <v>971</v>
       </c>
       <c r="F1595" s="9" t="s">
         <v>100</v>
@@ -49168,7 +49169,7 @@
         <v>10</v>
       </c>
       <c r="H1595" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1595">
         <v>0</v>
@@ -49176,7 +49177,7 @@
     </row>
     <row r="1596" spans="1:9">
       <c r="A1596" s="26">
-        <v>5101735</v>
+        <v>5101734</v>
       </c>
       <c r="B1596" s="26">
         <v>1</v>
@@ -49188,7 +49189,7 @@
         <v>1197</v>
       </c>
       <c r="E1596" s="26" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1596" s="9" t="s">
         <v>100</v>
@@ -49197,15 +49198,15 @@
         <v>10</v>
       </c>
       <c r="H1596" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1596">
         <v>0</v>
       </c>
     </row>
-    <row r="1597" ht="14" customHeight="1" spans="1:9">
+    <row r="1597" spans="1:9">
       <c r="A1597" s="26">
-        <v>5101733</v>
+        <v>5101735</v>
       </c>
       <c r="B1597" s="26">
         <v>1</v>
@@ -49217,7 +49218,7 @@
         <v>1198</v>
       </c>
       <c r="E1597" s="26" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="F1597" s="9" t="s">
         <v>100</v>
@@ -49226,15 +49227,15 @@
         <v>10</v>
       </c>
       <c r="H1597" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1597">
         <v>0</v>
       </c>
     </row>
-    <row r="1598" spans="1:9">
+    <row r="1598" ht="14" customHeight="1" spans="1:9">
       <c r="A1598" s="26">
-        <v>5101734</v>
+        <v>5101733</v>
       </c>
       <c r="B1598" s="26">
         <v>1</v>
@@ -49255,7 +49256,7 @@
         <v>10</v>
       </c>
       <c r="H1598" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1598">
         <v>0</v>
@@ -49263,7 +49264,7 @@
     </row>
     <row r="1599" spans="1:9">
       <c r="A1599" s="26">
-        <v>5101735</v>
+        <v>5101734</v>
       </c>
       <c r="B1599" s="26">
         <v>1</v>
@@ -49275,7 +49276,7 @@
         <v>1200</v>
       </c>
       <c r="E1599" s="26" t="s">
-        <v>971</v>
+        <v>327</v>
       </c>
       <c r="F1599" s="9" t="s">
         <v>100</v>
@@ -49292,7 +49293,7 @@
     </row>
     <row r="1600" spans="1:9">
       <c r="A1600" s="26">
-        <v>5101736</v>
+        <v>5101735</v>
       </c>
       <c r="B1600" s="26">
         <v>1</v>
@@ -49304,7 +49305,7 @@
         <v>1201</v>
       </c>
       <c r="E1600" s="26" t="s">
-        <v>245</v>
+        <v>971</v>
       </c>
       <c r="F1600" s="9" t="s">
         <v>100</v>
@@ -49313,7 +49314,7 @@
         <v>10</v>
       </c>
       <c r="H1600" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1600">
         <v>0</v>
@@ -49321,7 +49322,7 @@
     </row>
     <row r="1601" spans="1:9">
       <c r="A1601" s="26">
-        <v>5101737</v>
+        <v>5101736</v>
       </c>
       <c r="B1601" s="26">
         <v>1</v>
@@ -49333,18 +49334,47 @@
         <v>1202</v>
       </c>
       <c r="E1601" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1601" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1601" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1601" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:9">
+      <c r="A1602" s="26">
+        <v>5101737</v>
+      </c>
+      <c r="B1602" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1602" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1602" s="27" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E1602" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="F1601" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1601" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1601" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1601">
+      <c r="F1602" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1602" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1602" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1602">
         <v>0</v>
       </c>
     </row>
@@ -49410,7 +49440,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -49422,10 +49452,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -49439,90 +49469,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1220</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1221</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1223</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1225</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1226</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1227</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1228</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1229</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -49533,7 +49563,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -49554,7 +49584,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -49566,7 +49596,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49577,7 +49607,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -49618,7 +49648,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -49659,7 +49689,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -49680,7 +49710,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -49692,7 +49722,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49703,7 +49733,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49724,7 +49754,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49736,7 +49766,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49747,7 +49777,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49768,7 +49798,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -2723,19 +2723,19 @@
     <t>普攻附带物理伤害系数</t>
   </si>
   <si>
-    <t>普攻附带冰元素溅射标记</t>
+    <t>普攻附带冰元素溅射标记（废弃）</t>
   </si>
   <si>
     <t>参数-元素类型标记</t>
   </si>
   <si>
-    <t>普攻附带火元素溅射标记</t>
-  </si>
-  <si>
-    <t>普攻附带毒元素溅射标记</t>
-  </si>
-  <si>
-    <t>普攻附带电元素溅射标记</t>
+    <t>普攻附带火元素溅射标记（废弃）</t>
+  </si>
+  <si>
+    <t>普攻附带毒元素溅射标记（废弃）</t>
+  </si>
+  <si>
+    <t>普攻附带电元素溅射标记（废弃）</t>
   </si>
   <si>
     <t>暴风雪_获得</t>
@@ -4178,7 +4178,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79955442976165"/>
+        <fgColor theme="9" tint="0.799523911252174"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4214,7 +4214,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79955442976165"/>
+        <fgColor theme="4" tint="0.799523911252174"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4666,7 +4666,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4740,7 +4740,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
@@ -39798,110 +39812,110 @@
       </c>
     </row>
     <row r="1241" spans="1:9">
-      <c r="A1241" s="30">
+      <c r="A1241" s="31">
         <v>7000311</v>
       </c>
-      <c r="B1241" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1241" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1241" s="27" t="s">
+      <c r="B1241" s="32">
+        <v>1</v>
+      </c>
+      <c r="C1241" s="32">
+        <v>0</v>
+      </c>
+      <c r="D1241" s="33" t="s">
         <v>856</v>
       </c>
-      <c r="E1241" s="26" t="s">
+      <c r="E1241" s="32" t="s">
         <v>857</v>
       </c>
-      <c r="F1241" s="9"/>
-      <c r="G1241" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1241" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1241">
+      <c r="F1241" s="34"/>
+      <c r="G1241" s="32">
+        <v>10</v>
+      </c>
+      <c r="H1241" s="32">
+        <v>1</v>
+      </c>
+      <c r="I1241" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="1242" spans="1:9">
-      <c r="A1242" s="30">
+      <c r="A1242" s="31">
         <v>7000312</v>
       </c>
-      <c r="B1242" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1242" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1242" s="27" t="s">
+      <c r="B1242" s="32">
+        <v>1</v>
+      </c>
+      <c r="C1242" s="32">
+        <v>0</v>
+      </c>
+      <c r="D1242" s="33" t="s">
         <v>858</v>
       </c>
-      <c r="E1242" s="26" t="s">
+      <c r="E1242" s="32" t="s">
         <v>857</v>
       </c>
-      <c r="F1242" s="9"/>
-      <c r="G1242" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1242" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1242">
+      <c r="F1242" s="34"/>
+      <c r="G1242" s="32">
+        <v>10</v>
+      </c>
+      <c r="H1242" s="32">
+        <v>1</v>
+      </c>
+      <c r="I1242" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="1243" spans="1:9">
-      <c r="A1243" s="30">
+      <c r="A1243" s="31">
         <v>7000313</v>
       </c>
-      <c r="B1243" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1243" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1243" s="27" t="s">
+      <c r="B1243" s="32">
+        <v>1</v>
+      </c>
+      <c r="C1243" s="32">
+        <v>0</v>
+      </c>
+      <c r="D1243" s="33" t="s">
         <v>859</v>
       </c>
-      <c r="E1243" s="26" t="s">
+      <c r="E1243" s="32" t="s">
         <v>857</v>
       </c>
-      <c r="F1243" s="9"/>
-      <c r="G1243" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1243" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1243">
+      <c r="F1243" s="34"/>
+      <c r="G1243" s="32">
+        <v>10</v>
+      </c>
+      <c r="H1243" s="32">
+        <v>1</v>
+      </c>
+      <c r="I1243" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="1244" spans="1:9">
-      <c r="A1244" s="30">
+      <c r="A1244" s="31">
         <v>7000314</v>
       </c>
-      <c r="B1244" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1244" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1244" s="27" t="s">
+      <c r="B1244" s="32">
+        <v>1</v>
+      </c>
+      <c r="C1244" s="32">
+        <v>0</v>
+      </c>
+      <c r="D1244" s="33" t="s">
         <v>860</v>
       </c>
-      <c r="E1244" s="26" t="s">
+      <c r="E1244" s="32" t="s">
         <v>857</v>
       </c>
-      <c r="F1244" s="9"/>
-      <c r="G1244" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1244" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1244">
+      <c r="F1244" s="34"/>
+      <c r="G1244" s="32">
+        <v>10</v>
+      </c>
+      <c r="H1244" s="32">
+        <v>1</v>
+      </c>
+      <c r="I1244" s="35">
         <v>0</v>
       </c>
     </row>
@@ -41700,7 +41714,7 @@
       </c>
     </row>
     <row r="1313" spans="1:9">
-      <c r="A1313" s="31">
+      <c r="A1313" s="36">
         <v>920082</v>
       </c>
       <c r="B1313" s="26">
@@ -47140,7 +47154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1519" customFormat="1" spans="1:9">
+    <row r="1519" spans="1:9">
       <c r="A1519">
         <v>4920115</v>
       </c>
@@ -47156,7 +47170,6 @@
       <c r="E1519" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="F1519"/>
       <c r="G1519">
         <v>10</v>
       </c>
@@ -47220,7 +47233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1522" customFormat="1" spans="1:9">
+    <row r="1522" spans="1:9">
       <c r="A1522">
         <v>820112</v>
       </c>
@@ -47820,8 +47833,8 @@
       </c>
     </row>
     <row r="1545" spans="1:9">
-      <c r="A1545">
-        <v>16920101</v>
+      <c r="A1545" s="37">
+        <v>16920109</v>
       </c>
       <c r="B1545" s="26">
         <v>1</v>
@@ -48239,7 +48252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1561" customFormat="1" spans="1:9">
+    <row r="1561" spans="1:9">
       <c r="A1561">
         <v>820111</v>
       </c>
@@ -49059,7 +49072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1592" ht="14" customHeight="1" spans="1:9">
+    <row r="1592" ht="14.1" customHeight="1" spans="1:9">
       <c r="A1592" s="26">
         <v>5101725</v>
       </c>
@@ -49233,7 +49246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1598" ht="14" customHeight="1" spans="1:9">
+    <row r="1598" ht="14.1" customHeight="1" spans="1:9">
       <c r="A1598" s="26">
         <v>5101733</v>
       </c>
@@ -49583,7 +49596,7 @@
       <c r="I5" s="3">
         <v>0</v>
       </c>
-      <c r="J5" s="32" t="s">
+      <c r="J5" s="38" t="s">
         <v>1232</v>
       </c>
       <c r="K5" s="3">
@@ -49709,7 +49722,7 @@
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="38" t="s">
         <v>1237</v>
       </c>
       <c r="K8" s="3">
@@ -49753,7 +49766,7 @@
       <c r="I9" s="3">
         <v>0</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="38" t="s">
         <v>1240</v>
       </c>
       <c r="K9" s="3">
@@ -49797,7 +49810,7 @@
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="38" t="s">
         <v>1243</v>
       </c>
       <c r="K10" s="3">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -48121,7 +48121,7 @@
     </row>
     <row r="1556" spans="1:9">
       <c r="A1556">
-        <v>920115</v>
+        <v>920119</v>
       </c>
       <c r="B1556" s="26">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -47177,7 +47177,7 @@
         <v>1</v>
       </c>
       <c r="I1519">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1520" spans="1:9">
@@ -47360,7 +47360,7 @@
         <v>1</v>
       </c>
       <c r="I1526">
-        <v>4000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1527" spans="1:9">
@@ -47986,7 +47986,7 @@
         <v>1</v>
       </c>
       <c r="I1550">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1551" spans="1:9">
@@ -48405,7 +48405,7 @@
         <v>1</v>
       </c>
       <c r="I1566">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1567" spans="1:9">
@@ -48770,7 +48770,7 @@
         <v>1</v>
       </c>
       <c r="I1580">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1581" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -39121,7 +39121,7 @@
         <v>1</v>
       </c>
       <c r="I1214">
-        <v>1600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1215" spans="1:9">
@@ -39305,7 +39305,7 @@
         <v>1</v>
       </c>
       <c r="I1221">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1222" spans="1:9">
@@ -42133,7 +42133,7 @@
         <v>1</v>
       </c>
       <c r="I1328">
-        <v>1600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1329" spans="1:9">
@@ -42316,7 +42316,7 @@
         <v>1</v>
       </c>
       <c r="I1335">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1336" spans="1:9">
@@ -43911,7 +43911,7 @@
         <v>1</v>
       </c>
       <c r="I1395">
-        <v>1600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1396" spans="1:9">
@@ -44095,7 +44095,7 @@
         <v>1</v>
       </c>
       <c r="I1402">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1403" spans="1:9">
@@ -47699,7 +47699,7 @@
         <v>1</v>
       </c>
       <c r="I1539">
-        <v>1600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1540" spans="1:9">
@@ -47856,7 +47856,7 @@
         <v>1</v>
       </c>
       <c r="I1545">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1546" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4173" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4175" uniqueCount="1245">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3636,6 +3636,9 @@
   </si>
   <si>
     <t>精神错乱_获得</t>
+  </si>
+  <si>
+    <t>精神错乱_技能效果半径</t>
   </si>
   <si>
     <t>精神错乱被动_获得</t>
@@ -5110,7 +5113,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1602"/>
+  <dimension ref="A1:I1603"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -47908,7 +47911,7 @@
         <v>1</v>
       </c>
       <c r="I1547">
-        <v>4000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1548" spans="1:9">
@@ -48199,9 +48202,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1559" spans="1:9">
+    <row r="1559" customFormat="1" spans="1:9">
       <c r="A1559">
-        <v>920116</v>
+        <v>4920114</v>
       </c>
       <c r="B1559" s="26">
         <v>1</v>
@@ -48213,9 +48216,9 @@
         <v>1161</v>
       </c>
       <c r="E1559" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1559" s="28"/>
+        <v>769</v>
+      </c>
+      <c r="F1559"/>
       <c r="G1559">
         <v>10</v>
       </c>
@@ -48223,12 +48226,12 @@
         <v>1</v>
       </c>
       <c r="I1559">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1560" spans="1:9">
       <c r="A1560">
-        <v>820097</v>
+        <v>920116</v>
       </c>
       <c r="B1560" s="26">
         <v>1</v>
@@ -48236,12 +48239,13 @@
       <c r="C1560">
         <v>0</v>
       </c>
-      <c r="D1560" s="30" t="s">
-        <v>1124</v>
-      </c>
-      <c r="E1560" s="30" t="s">
-        <v>1124</v>
-      </c>
+      <c r="D1560" s="28" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E1560" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1560" s="28"/>
       <c r="G1560">
         <v>10</v>
       </c>
@@ -48254,7 +48258,7 @@
     </row>
     <row r="1561" spans="1:9">
       <c r="A1561">
-        <v>820111</v>
+        <v>820097</v>
       </c>
       <c r="B1561" s="26">
         <v>1</v>
@@ -48263,7 +48267,7 @@
         <v>0</v>
       </c>
       <c r="D1561" s="30" t="s">
-        <v>1162</v>
+        <v>1124</v>
       </c>
       <c r="E1561" s="30" t="s">
         <v>1124</v>
@@ -48280,7 +48284,7 @@
     </row>
     <row r="1562" spans="1:9">
       <c r="A1562">
-        <v>920111</v>
+        <v>820111</v>
       </c>
       <c r="B1562" s="26">
         <v>1</v>
@@ -48288,11 +48292,11 @@
       <c r="C1562">
         <v>0</v>
       </c>
-      <c r="D1562" s="28" t="s">
+      <c r="D1562" s="30" t="s">
         <v>1163</v>
       </c>
-      <c r="E1562" s="29" t="s">
-        <v>767</v>
+      <c r="E1562" s="30" t="s">
+        <v>1124</v>
       </c>
       <c r="G1562">
         <v>10</v>
@@ -48306,7 +48310,7 @@
     </row>
     <row r="1563" spans="1:9">
       <c r="A1563">
-        <v>1920111</v>
+        <v>920111</v>
       </c>
       <c r="B1563" s="26">
         <v>1</v>
@@ -48318,7 +48322,7 @@
         <v>1164</v>
       </c>
       <c r="E1563" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1563">
         <v>10</v>
@@ -48327,12 +48331,12 @@
         <v>1</v>
       </c>
       <c r="I1563">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1564" spans="1:9">
       <c r="A1564">
-        <v>2920111</v>
+        <v>1920111</v>
       </c>
       <c r="B1564" s="26">
         <v>1</v>
@@ -48353,12 +48357,12 @@
         <v>1</v>
       </c>
       <c r="I1564">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1565" spans="1:9">
       <c r="A1565">
-        <v>3920111</v>
+        <v>2920111</v>
       </c>
       <c r="B1565" s="26">
         <v>1</v>
@@ -48379,12 +48383,12 @@
         <v>1</v>
       </c>
       <c r="I1565">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1566" spans="1:9">
       <c r="A1566">
-        <v>4920111</v>
+        <v>3920111</v>
       </c>
       <c r="B1566" s="26">
         <v>1</v>
@@ -48405,12 +48409,12 @@
         <v>1</v>
       </c>
       <c r="I1566">
-        <v>1800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1567" spans="1:9">
       <c r="A1567">
-        <v>6920111</v>
+        <v>4920111</v>
       </c>
       <c r="B1567" s="26">
         <v>1</v>
@@ -48431,12 +48435,12 @@
         <v>1</v>
       </c>
       <c r="I1567">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1568" spans="1:9">
       <c r="A1568">
-        <v>7920111</v>
+        <v>6920111</v>
       </c>
       <c r="B1568" s="26">
         <v>1</v>
@@ -48454,15 +48458,15 @@
         <v>10</v>
       </c>
       <c r="H1568">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1568">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1569" spans="1:9">
       <c r="A1569">
-        <v>8920111</v>
+        <v>7920111</v>
       </c>
       <c r="B1569" s="26">
         <v>1</v>
@@ -48480,15 +48484,15 @@
         <v>10</v>
       </c>
       <c r="H1569">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1569">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1570" spans="1:9">
       <c r="A1570">
-        <v>9920111</v>
+        <v>8920111</v>
       </c>
       <c r="B1570" s="26">
         <v>1</v>
@@ -48506,15 +48510,15 @@
         <v>10</v>
       </c>
       <c r="H1570">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1570">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1571" spans="1:9">
       <c r="A1571">
-        <v>11030111</v>
+        <v>9920111</v>
       </c>
       <c r="B1571" s="26">
         <v>1</v>
@@ -48532,15 +48536,15 @@
         <v>10</v>
       </c>
       <c r="H1571">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1571">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1572" spans="1:9">
       <c r="A1572">
-        <v>11920111</v>
+        <v>11030111</v>
       </c>
       <c r="B1572" s="26">
         <v>1</v>
@@ -48561,12 +48565,12 @@
         <v>1</v>
       </c>
       <c r="I1572">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1573" spans="1:9">
       <c r="A1573">
-        <v>13920111</v>
+        <v>11920111</v>
       </c>
       <c r="B1573" s="26">
         <v>1</v>
@@ -48587,12 +48591,12 @@
         <v>1</v>
       </c>
       <c r="I1573">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1574" spans="1:9">
       <c r="A1574">
-        <v>920118</v>
+        <v>13920111</v>
       </c>
       <c r="B1574" s="26">
         <v>1</v>
@@ -48604,9 +48608,8 @@
         <v>1175</v>
       </c>
       <c r="E1574" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1574" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1574">
         <v>10</v>
       </c>
@@ -48614,12 +48617,12 @@
         <v>1</v>
       </c>
       <c r="I1574">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1575" spans="1:9">
       <c r="A1575">
-        <v>820100</v>
+        <v>920118</v>
       </c>
       <c r="B1575" s="26">
         <v>1</v>
@@ -48627,12 +48630,13 @@
       <c r="C1575">
         <v>0</v>
       </c>
-      <c r="D1575" s="30" t="s">
+      <c r="D1575" s="28" t="s">
         <v>1176</v>
       </c>
-      <c r="E1575" s="30" t="s">
-        <v>1176</v>
-      </c>
+      <c r="E1575" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1575" s="28"/>
       <c r="G1575">
         <v>10</v>
       </c>
@@ -48645,7 +48649,7 @@
     </row>
     <row r="1576" spans="1:9">
       <c r="A1576">
-        <v>920112</v>
+        <v>820100</v>
       </c>
       <c r="B1576" s="26">
         <v>1</v>
@@ -48653,11 +48657,11 @@
       <c r="C1576">
         <v>0</v>
       </c>
-      <c r="D1576" s="28" t="s">
+      <c r="D1576" s="30" t="s">
         <v>1177</v>
       </c>
-      <c r="E1576" s="29" t="s">
-        <v>767</v>
+      <c r="E1576" s="30" t="s">
+        <v>1177</v>
       </c>
       <c r="G1576">
         <v>10</v>
@@ -48671,7 +48675,7 @@
     </row>
     <row r="1577" spans="1:9">
       <c r="A1577">
-        <v>1920112</v>
+        <v>920112</v>
       </c>
       <c r="B1577" s="26">
         <v>1</v>
@@ -48683,7 +48687,7 @@
         <v>1178</v>
       </c>
       <c r="E1577" s="29" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G1577">
         <v>10</v>
@@ -48692,12 +48696,12 @@
         <v>1</v>
       </c>
       <c r="I1577">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1578" spans="1:9">
       <c r="A1578">
-        <v>2920112</v>
+        <v>1920112</v>
       </c>
       <c r="B1578" s="26">
         <v>1</v>
@@ -48718,12 +48722,12 @@
         <v>1</v>
       </c>
       <c r="I1578">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1579" spans="1:9">
       <c r="A1579">
-        <v>3920112</v>
+        <v>2920112</v>
       </c>
       <c r="B1579" s="26">
         <v>1</v>
@@ -48744,12 +48748,12 @@
         <v>1</v>
       </c>
       <c r="I1579">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1580" spans="1:9">
       <c r="A1580">
-        <v>4920112</v>
+        <v>3920112</v>
       </c>
       <c r="B1580" s="26">
         <v>1</v>
@@ -48770,12 +48774,12 @@
         <v>1</v>
       </c>
       <c r="I1580">
-        <v>1800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1581" spans="1:9">
       <c r="A1581">
-        <v>6920112</v>
+        <v>4920112</v>
       </c>
       <c r="B1581" s="26">
         <v>1</v>
@@ -48796,12 +48800,12 @@
         <v>1</v>
       </c>
       <c r="I1581">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1582" spans="1:9">
       <c r="A1582">
-        <v>7920112</v>
+        <v>6920112</v>
       </c>
       <c r="B1582" s="26">
         <v>1</v>
@@ -48819,15 +48823,15 @@
         <v>10</v>
       </c>
       <c r="H1582">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1582">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1583" spans="1:9">
       <c r="A1583">
-        <v>8920112</v>
+        <v>7920112</v>
       </c>
       <c r="B1583" s="26">
         <v>1</v>
@@ -48845,15 +48849,15 @@
         <v>10</v>
       </c>
       <c r="H1583">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1583">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1584" spans="1:9">
       <c r="A1584">
-        <v>9920112</v>
+        <v>8920112</v>
       </c>
       <c r="B1584" s="26">
         <v>1</v>
@@ -48871,15 +48875,15 @@
         <v>10</v>
       </c>
       <c r="H1584">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1584">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1585" spans="1:9">
       <c r="A1585">
-        <v>13920112</v>
+        <v>9920112</v>
       </c>
       <c r="B1585" s="26">
         <v>1</v>
@@ -48897,15 +48901,15 @@
         <v>10</v>
       </c>
       <c r="H1585">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1585">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1586" spans="1:9">
       <c r="A1586">
-        <v>920117</v>
+        <v>13920112</v>
       </c>
       <c r="B1586" s="26">
         <v>1</v>
@@ -48917,9 +48921,8 @@
         <v>1187</v>
       </c>
       <c r="E1586" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="F1586" s="28"/>
+        <v>769</v>
+      </c>
       <c r="G1586">
         <v>10</v>
       </c>
@@ -48927,58 +48930,56 @@
         <v>1</v>
       </c>
       <c r="I1586">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1587" spans="1:9">
       <c r="A1587">
+        <v>920117</v>
+      </c>
+      <c r="B1587" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1587">
+        <v>0</v>
+      </c>
+      <c r="D1587" s="28" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E1587" s="29" t="s">
+        <v>767</v>
+      </c>
+      <c r="F1587" s="28"/>
+      <c r="G1587">
+        <v>10</v>
+      </c>
+      <c r="H1587">
+        <v>1</v>
+      </c>
+      <c r="I1587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:9">
+      <c r="A1588">
         <v>820099</v>
       </c>
-      <c r="B1587" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1587">
-        <v>0</v>
-      </c>
-      <c r="D1587" s="30" t="s">
-        <v>1188</v>
-      </c>
-      <c r="E1587" s="30" t="s">
-        <v>1188</v>
-      </c>
-      <c r="G1587">
-        <v>10</v>
-      </c>
-      <c r="H1587">
-        <v>1</v>
-      </c>
-      <c r="I1587">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1588" spans="1:9">
-      <c r="A1588" s="26">
-        <v>5101721</v>
-      </c>
       <c r="B1588" s="26">
         <v>1</v>
       </c>
-      <c r="C1588" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1588" s="27" t="s">
+      <c r="C1588">
+        <v>0</v>
+      </c>
+      <c r="D1588" s="30" t="s">
         <v>1189</v>
       </c>
-      <c r="E1588" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1588" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1588" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1588" s="26">
+      <c r="E1588" s="30" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G1588">
+        <v>10</v>
+      </c>
+      <c r="H1588">
         <v>1</v>
       </c>
       <c r="I1588">
@@ -48987,7 +48988,7 @@
     </row>
     <row r="1589" spans="1:9">
       <c r="A1589" s="26">
-        <v>5101722</v>
+        <v>5101721</v>
       </c>
       <c r="B1589" s="26">
         <v>1</v>
@@ -48999,7 +49000,7 @@
         <v>1190</v>
       </c>
       <c r="E1589" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1589" s="9" t="s">
         <v>100</v>
@@ -49008,7 +49009,7 @@
         <v>10</v>
       </c>
       <c r="H1589" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1589">
         <v>0</v>
@@ -49016,7 +49017,7 @@
     </row>
     <row r="1590" spans="1:9">
       <c r="A1590" s="26">
-        <v>5101723</v>
+        <v>5101722</v>
       </c>
       <c r="B1590" s="26">
         <v>1</v>
@@ -49045,7 +49046,7 @@
     </row>
     <row r="1591" spans="1:9">
       <c r="A1591" s="26">
-        <v>5101724</v>
+        <v>5101723</v>
       </c>
       <c r="B1591" s="26">
         <v>1</v>
@@ -49072,9 +49073,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1592" ht="14.1" customHeight="1" spans="1:9">
+    <row r="1592" spans="1:9">
       <c r="A1592" s="26">
-        <v>5101725</v>
+        <v>5101724</v>
       </c>
       <c r="B1592" s="26">
         <v>1</v>
@@ -49086,7 +49087,7 @@
         <v>1193</v>
       </c>
       <c r="E1592" s="26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1592" s="9" t="s">
         <v>100</v>
@@ -49101,9 +49102,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1593" spans="1:9">
+    <row r="1593" ht="14.1" customHeight="1" spans="1:9">
       <c r="A1593" s="26">
-        <v>5101730</v>
+        <v>5101725</v>
       </c>
       <c r="B1593" s="26">
         <v>1</v>
@@ -49115,7 +49116,7 @@
         <v>1194</v>
       </c>
       <c r="E1593" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1593" s="9" t="s">
         <v>100</v>
@@ -49132,7 +49133,7 @@
     </row>
     <row r="1594" spans="1:9">
       <c r="A1594" s="26">
-        <v>5101731</v>
+        <v>5101730</v>
       </c>
       <c r="B1594" s="26">
         <v>1</v>
@@ -49144,7 +49145,7 @@
         <v>1195</v>
       </c>
       <c r="E1594" s="26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1594" s="9" t="s">
         <v>100</v>
@@ -49153,7 +49154,7 @@
         <v>10</v>
       </c>
       <c r="H1594" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1594">
         <v>0</v>
@@ -49161,7 +49162,7 @@
     </row>
     <row r="1595" spans="1:9">
       <c r="A1595" s="26">
-        <v>5101732</v>
+        <v>5101731</v>
       </c>
       <c r="B1595" s="26">
         <v>1</v>
@@ -49173,7 +49174,7 @@
         <v>1196</v>
       </c>
       <c r="E1595" s="26" t="s">
-        <v>971</v>
+        <v>327</v>
       </c>
       <c r="F1595" s="9" t="s">
         <v>100</v>
@@ -49190,7 +49191,7 @@
     </row>
     <row r="1596" spans="1:9">
       <c r="A1596" s="26">
-        <v>5101734</v>
+        <v>5101732</v>
       </c>
       <c r="B1596" s="26">
         <v>1</v>
@@ -49202,7 +49203,7 @@
         <v>1197</v>
       </c>
       <c r="E1596" s="26" t="s">
-        <v>245</v>
+        <v>971</v>
       </c>
       <c r="F1596" s="9" t="s">
         <v>100</v>
@@ -49211,7 +49212,7 @@
         <v>10</v>
       </c>
       <c r="H1596" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1596">
         <v>0</v>
@@ -49219,7 +49220,7 @@
     </row>
     <row r="1597" spans="1:9">
       <c r="A1597" s="26">
-        <v>5101735</v>
+        <v>5101734</v>
       </c>
       <c r="B1597" s="26">
         <v>1</v>
@@ -49231,7 +49232,7 @@
         <v>1198</v>
       </c>
       <c r="E1597" s="26" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1597" s="9" t="s">
         <v>100</v>
@@ -49240,15 +49241,15 @@
         <v>10</v>
       </c>
       <c r="H1597" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1597">
         <v>0</v>
       </c>
     </row>
-    <row r="1598" ht="14.1" customHeight="1" spans="1:9">
+    <row r="1598" spans="1:9">
       <c r="A1598" s="26">
-        <v>5101733</v>
+        <v>5101735</v>
       </c>
       <c r="B1598" s="26">
         <v>1</v>
@@ -49260,7 +49261,7 @@
         <v>1199</v>
       </c>
       <c r="E1598" s="26" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="F1598" s="9" t="s">
         <v>100</v>
@@ -49269,15 +49270,15 @@
         <v>10</v>
       </c>
       <c r="H1598" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1598">
         <v>0</v>
       </c>
     </row>
-    <row r="1599" spans="1:9">
+    <row r="1599" ht="14.1" customHeight="1" spans="1:9">
       <c r="A1599" s="26">
-        <v>5101734</v>
+        <v>5101733</v>
       </c>
       <c r="B1599" s="26">
         <v>1</v>
@@ -49298,7 +49299,7 @@
         <v>10</v>
       </c>
       <c r="H1599" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1599">
         <v>0</v>
@@ -49306,7 +49307,7 @@
     </row>
     <row r="1600" spans="1:9">
       <c r="A1600" s="26">
-        <v>5101735</v>
+        <v>5101734</v>
       </c>
       <c r="B1600" s="26">
         <v>1</v>
@@ -49318,7 +49319,7 @@
         <v>1201</v>
       </c>
       <c r="E1600" s="26" t="s">
-        <v>971</v>
+        <v>327</v>
       </c>
       <c r="F1600" s="9" t="s">
         <v>100</v>
@@ -49335,7 +49336,7 @@
     </row>
     <row r="1601" spans="1:9">
       <c r="A1601" s="26">
-        <v>5101736</v>
+        <v>5101735</v>
       </c>
       <c r="B1601" s="26">
         <v>1</v>
@@ -49347,7 +49348,7 @@
         <v>1202</v>
       </c>
       <c r="E1601" s="26" t="s">
-        <v>245</v>
+        <v>971</v>
       </c>
       <c r="F1601" s="9" t="s">
         <v>100</v>
@@ -49356,7 +49357,7 @@
         <v>10</v>
       </c>
       <c r="H1601" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1601">
         <v>0</v>
@@ -49364,7 +49365,7 @@
     </row>
     <row r="1602" spans="1:9">
       <c r="A1602" s="26">
-        <v>5101737</v>
+        <v>5101736</v>
       </c>
       <c r="B1602" s="26">
         <v>1</v>
@@ -49376,18 +49377,47 @@
         <v>1203</v>
       </c>
       <c r="E1602" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1602" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1602" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1602" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:9">
+      <c r="A1603" s="26">
+        <v>5101737</v>
+      </c>
+      <c r="B1603" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1603" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1603" s="27" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E1603" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="F1602" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1602" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1602" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1602">
+      <c r="F1603" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1603" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1603" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1603">
         <v>0</v>
       </c>
     </row>
@@ -49453,7 +49483,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -49465,10 +49495,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -49482,90 +49512,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1221</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1224</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1225</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1228</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1229</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1230</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -49576,7 +49606,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -49597,7 +49627,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -49609,7 +49639,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49620,7 +49650,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -49661,7 +49691,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -49702,7 +49732,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -49723,7 +49753,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -49735,7 +49765,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49746,7 +49776,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49767,7 +49797,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49779,7 +49809,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49790,7 +49820,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49811,7 +49841,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4175" uniqueCount="1245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4178" uniqueCount="1247">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3732,6 +3732,12 @@
   </si>
   <si>
     <t>毒性爆发被动-传染的命中率</t>
+  </si>
+  <si>
+    <t>毒性爆发被动-效果触发间隔</t>
+  </si>
+  <si>
+    <t>参数-参数8-效果触发间隔</t>
   </si>
   <si>
     <t>精神错乱被动-传染的命中率</t>
@@ -5113,7 +5119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1603"/>
+  <dimension ref="A1:I1604"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -46580,7 +46586,7 @@
         <v>2</v>
       </c>
       <c r="I1496">
-        <v>8500</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1497" spans="1:9">
@@ -46632,7 +46638,7 @@
         <v>2</v>
       </c>
       <c r="I1498">
-        <v>8500</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1499" spans="1:9">
@@ -46997,7 +47003,7 @@
         <v>2</v>
       </c>
       <c r="I1512">
-        <v>22000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1513" spans="1:9">
@@ -47049,7 +47055,7 @@
         <v>2</v>
       </c>
       <c r="I1514">
-        <v>22000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1515" spans="1:9">
@@ -47180,7 +47186,7 @@
         <v>1</v>
       </c>
       <c r="I1519">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1520" spans="1:9">
@@ -47911,7 +47917,7 @@
         <v>1</v>
       </c>
       <c r="I1547">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1548" spans="1:9">
@@ -49075,7 +49081,7 @@
     </row>
     <row r="1592" spans="1:9">
       <c r="A1592" s="26">
-        <v>5101724</v>
+        <v>51017232</v>
       </c>
       <c r="B1592" s="26">
         <v>1</v>
@@ -49087,36 +49093,36 @@
         <v>1193</v>
       </c>
       <c r="E1592" s="26" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F1592" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1592" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1592" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:9">
+      <c r="A1593" s="26">
+        <v>5101724</v>
+      </c>
+      <c r="B1593" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1593" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1593" s="27" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E1593" s="26" t="s">
         <v>329</v>
-      </c>
-      <c r="F1592" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1592" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1592" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1592">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1593" ht="14.1" customHeight="1" spans="1:9">
-      <c r="A1593" s="26">
-        <v>5101725</v>
-      </c>
-      <c r="B1593" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1593" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1593" s="27" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E1593" s="26" t="s">
-        <v>327</v>
       </c>
       <c r="F1593" s="9" t="s">
         <v>100</v>
@@ -49131,9 +49137,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1594" spans="1:9">
+    <row r="1594" ht="14.1" customHeight="1" spans="1:9">
       <c r="A1594" s="26">
-        <v>5101730</v>
+        <v>5101725</v>
       </c>
       <c r="B1594" s="26">
         <v>1</v>
@@ -49142,10 +49148,10 @@
         <v>0</v>
       </c>
       <c r="D1594" s="27" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="E1594" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1594" s="9" t="s">
         <v>100</v>
@@ -49162,7 +49168,7 @@
     </row>
     <row r="1595" spans="1:9">
       <c r="A1595" s="26">
-        <v>5101731</v>
+        <v>5101730</v>
       </c>
       <c r="B1595" s="26">
         <v>1</v>
@@ -49171,10 +49177,10 @@
         <v>0</v>
       </c>
       <c r="D1595" s="27" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="E1595" s="26" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1595" s="9" t="s">
         <v>100</v>
@@ -49183,7 +49189,7 @@
         <v>10</v>
       </c>
       <c r="H1595" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1595">
         <v>0</v>
@@ -49191,7 +49197,7 @@
     </row>
     <row r="1596" spans="1:9">
       <c r="A1596" s="26">
-        <v>5101732</v>
+        <v>5101731</v>
       </c>
       <c r="B1596" s="26">
         <v>1</v>
@@ -49200,10 +49206,10 @@
         <v>0</v>
       </c>
       <c r="D1596" s="27" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E1596" s="26" t="s">
-        <v>971</v>
+        <v>327</v>
       </c>
       <c r="F1596" s="9" t="s">
         <v>100</v>
@@ -49220,7 +49226,7 @@
     </row>
     <row r="1597" spans="1:9">
       <c r="A1597" s="26">
-        <v>5101734</v>
+        <v>5101732</v>
       </c>
       <c r="B1597" s="26">
         <v>1</v>
@@ -49229,10 +49235,10 @@
         <v>0</v>
       </c>
       <c r="D1597" s="27" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="E1597" s="26" t="s">
-        <v>245</v>
+        <v>971</v>
       </c>
       <c r="F1597" s="9" t="s">
         <v>100</v>
@@ -49241,7 +49247,7 @@
         <v>10</v>
       </c>
       <c r="H1597" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1597">
         <v>0</v>
@@ -49249,66 +49255,66 @@
     </row>
     <row r="1598" spans="1:9">
       <c r="A1598" s="26">
+        <v>5101734</v>
+      </c>
+      <c r="B1598" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1598" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1598" s="27" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1598" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1598" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1598" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1598" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:9">
+      <c r="A1599" s="26">
         <v>5101735</v>
       </c>
-      <c r="B1598" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1598" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1598" s="27" t="s">
-        <v>1199</v>
-      </c>
-      <c r="E1598" s="26" t="s">
+      <c r="B1599" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1599" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1599" s="27" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E1599" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="F1598" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1598" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1598" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1598">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1599" ht="14.1" customHeight="1" spans="1:9">
-      <c r="A1599" s="26">
+      <c r="F1599" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1599" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1599" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1600" ht="14.1" customHeight="1" spans="1:9">
+      <c r="A1600" s="26">
         <v>5101733</v>
       </c>
-      <c r="B1599" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1599" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1599" s="27" t="s">
-        <v>1200</v>
-      </c>
-      <c r="E1599" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1599" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1599" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1599" s="26">
-        <v>2</v>
-      </c>
-      <c r="I1599">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1600" spans="1:9">
-      <c r="A1600" s="26">
-        <v>5101734</v>
-      </c>
       <c r="B1600" s="26">
         <v>1</v>
       </c>
@@ -49316,7 +49322,7 @@
         <v>0</v>
       </c>
       <c r="D1600" s="27" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E1600" s="26" t="s">
         <v>327</v>
@@ -49328,7 +49334,7 @@
         <v>10</v>
       </c>
       <c r="H1600" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1600">
         <v>0</v>
@@ -49336,7 +49342,7 @@
     </row>
     <row r="1601" spans="1:9">
       <c r="A1601" s="26">
-        <v>5101735</v>
+        <v>5101734</v>
       </c>
       <c r="B1601" s="26">
         <v>1</v>
@@ -49345,10 +49351,10 @@
         <v>0</v>
       </c>
       <c r="D1601" s="27" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="E1601" s="26" t="s">
-        <v>971</v>
+        <v>327</v>
       </c>
       <c r="F1601" s="9" t="s">
         <v>100</v>
@@ -49365,7 +49371,7 @@
     </row>
     <row r="1602" spans="1:9">
       <c r="A1602" s="26">
-        <v>5101736</v>
+        <v>5101735</v>
       </c>
       <c r="B1602" s="26">
         <v>1</v>
@@ -49374,10 +49380,10 @@
         <v>0</v>
       </c>
       <c r="D1602" s="27" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="E1602" s="26" t="s">
-        <v>245</v>
+        <v>971</v>
       </c>
       <c r="F1602" s="9" t="s">
         <v>100</v>
@@ -49386,7 +49392,7 @@
         <v>10</v>
       </c>
       <c r="H1602" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1602">
         <v>0</v>
@@ -49394,30 +49400,59 @@
     </row>
     <row r="1603" spans="1:9">
       <c r="A1603" s="26">
+        <v>5101736</v>
+      </c>
+      <c r="B1603" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1603" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1603" s="27" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E1603" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1603" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1603" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1603" s="26">
+        <v>2</v>
+      </c>
+      <c r="I1603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:9">
+      <c r="A1604" s="26">
         <v>5101737</v>
       </c>
-      <c r="B1603" s="26">
-        <v>1</v>
-      </c>
-      <c r="C1603" s="26">
-        <v>0</v>
-      </c>
-      <c r="D1603" s="27" t="s">
-        <v>1204</v>
-      </c>
-      <c r="E1603" s="26" t="s">
+      <c r="B1604" s="26">
+        <v>1</v>
+      </c>
+      <c r="C1604" s="26">
+        <v>0</v>
+      </c>
+      <c r="D1604" s="27" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E1604" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="F1603" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1603" s="26">
-        <v>10</v>
-      </c>
-      <c r="H1603" s="26">
-        <v>1</v>
-      </c>
-      <c r="I1603">
+      <c r="F1604" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1604" s="26">
+        <v>10</v>
+      </c>
+      <c r="H1604" s="26">
+        <v>1</v>
+      </c>
+      <c r="I1604">
         <v>0</v>
       </c>
     </row>
@@ -49483,7 +49518,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -49495,10 +49530,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -49512,90 +49547,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1223</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1224</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1225</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1226</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1228</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1229</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1230</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -49606,7 +49641,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -49627,7 +49662,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -49639,7 +49674,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -49650,7 +49685,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -49691,7 +49726,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -49732,7 +49767,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -49753,7 +49788,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -49765,7 +49800,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49776,7 +49811,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -49797,7 +49832,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -49809,7 +49844,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -49820,7 +49855,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -49841,7 +49876,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4380" uniqueCount="1338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4382" uniqueCount="1339">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3564,6 +3564,9 @@
   </si>
   <si>
     <t>召唤火龙_非主目标直接伤害系数</t>
+  </si>
+  <si>
+    <t>召唤火龙_技能持续时间</t>
   </si>
   <si>
     <t>召唤火龙_技能伤害或效果生效间隔</t>
@@ -4179,14 +4182,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4452,7 +4448,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4545,12 +4541,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -4570,12 +4560,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4831,13 +4815,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4846,55 +4833,58 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4903,10 +4893,10 @@
     <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4915,10 +4905,10 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4927,10 +4917,10 @@
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4939,10 +4929,10 @@
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4951,19 +4941,13 @@
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4971,27 +4955,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4999,107 +4995,95 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5452,7 +5436,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I1695"/>
+  <dimension ref="A1:I1696"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" style="8" customWidth="1"/>
@@ -47951,7 +47935,7 @@
     </row>
     <row r="1535" spans="1:9">
       <c r="A1535" s="8">
-        <v>11920096</v>
+        <v>10920096</v>
       </c>
       <c r="B1535" s="38">
         <v>1</v>
@@ -47972,12 +47956,12 @@
         <v>1</v>
       </c>
       <c r="I1535">
-        <v>1000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1536" spans="1:9">
       <c r="A1536" s="8">
-        <v>15920096</v>
+        <v>11920096</v>
       </c>
       <c r="B1536" s="38">
         <v>1</v>
@@ -47998,12 +47982,12 @@
         <v>1</v>
       </c>
       <c r="I1536">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1537" spans="1:9">
       <c r="A1537" s="8">
-        <v>920104</v>
+        <v>15920096</v>
       </c>
       <c r="B1537" s="38">
         <v>1</v>
@@ -48024,12 +48008,12 @@
         <v>1</v>
       </c>
       <c r="I1537">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1538" spans="1:9">
       <c r="A1538" s="8">
-        <v>1920104</v>
+        <v>920104</v>
       </c>
       <c r="B1538" s="38">
         <v>1</v>
@@ -48055,7 +48039,7 @@
     </row>
     <row r="1539" spans="1:9">
       <c r="A1539" s="8">
-        <v>2920104</v>
+        <v>1920104</v>
       </c>
       <c r="B1539" s="38">
         <v>1</v>
@@ -48081,7 +48065,7 @@
     </row>
     <row r="1540" spans="1:9">
       <c r="A1540" s="8">
-        <v>3920104</v>
+        <v>2920104</v>
       </c>
       <c r="B1540" s="38">
         <v>1</v>
@@ -48107,7 +48091,7 @@
     </row>
     <row r="1541" spans="1:9">
       <c r="A1541" s="8">
-        <v>4920104</v>
+        <v>3920104</v>
       </c>
       <c r="B1541" s="38">
         <v>1</v>
@@ -48128,12 +48112,12 @@
         <v>1</v>
       </c>
       <c r="I1541">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1542" spans="1:9">
       <c r="A1542" s="8">
-        <v>5920104</v>
+        <v>4920104</v>
       </c>
       <c r="B1542" s="38">
         <v>1</v>
@@ -48154,12 +48138,12 @@
         <v>1</v>
       </c>
       <c r="I1542">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1543" spans="1:9">
       <c r="A1543" s="8">
-        <v>6920104</v>
+        <v>5920104</v>
       </c>
       <c r="B1543" s="38">
         <v>1</v>
@@ -48185,7 +48169,7 @@
     </row>
     <row r="1544" spans="1:9">
       <c r="A1544" s="8">
-        <v>7920104</v>
+        <v>6920104</v>
       </c>
       <c r="B1544" s="38">
         <v>1</v>
@@ -48203,15 +48187,15 @@
         <v>10</v>
       </c>
       <c r="H1544">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1544">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1545" spans="1:9">
       <c r="A1545" s="8">
-        <v>8920104</v>
+        <v>7920104</v>
       </c>
       <c r="B1545" s="38">
         <v>1</v>
@@ -48229,15 +48213,15 @@
         <v>10</v>
       </c>
       <c r="H1545">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1545">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1546" spans="1:9">
       <c r="A1546" s="8">
-        <v>9920104</v>
+        <v>8920104</v>
       </c>
       <c r="B1546" s="38">
         <v>1</v>
@@ -48255,15 +48239,15 @@
         <v>10</v>
       </c>
       <c r="H1546">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1546">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1547" spans="1:9">
       <c r="A1547" s="8">
-        <v>11030104</v>
+        <v>9920104</v>
       </c>
       <c r="B1547" s="38">
         <v>1</v>
@@ -48281,15 +48265,15 @@
         <v>10</v>
       </c>
       <c r="H1547">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1547">
-        <v>8000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1548" spans="1:9">
       <c r="A1548" s="8">
-        <v>11920104</v>
+        <v>11030104</v>
       </c>
       <c r="B1548" s="38">
         <v>1</v>
@@ -48310,41 +48294,38 @@
         <v>1</v>
       </c>
       <c r="I1548">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:9">
+      <c r="A1549" s="8">
+        <v>11920104</v>
+      </c>
+      <c r="B1549" s="38">
+        <v>1</v>
+      </c>
+      <c r="C1549">
+        <v>0</v>
+      </c>
+      <c r="D1549" s="41" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E1549" s="42" t="s">
+        <v>841</v>
+      </c>
+      <c r="G1549">
+        <v>10</v>
+      </c>
+      <c r="H1549">
+        <v>1</v>
+      </c>
+      <c r="I1549">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="1549" spans="1:9">
-      <c r="A1549" s="37">
-        <v>5101700</v>
-      </c>
-      <c r="B1549" s="38">
-        <v>1</v>
-      </c>
-      <c r="C1549" s="38">
-        <v>0</v>
-      </c>
-      <c r="D1549" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="E1549" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="F1549" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1549" s="38">
-        <v>10</v>
-      </c>
-      <c r="H1549" s="38">
-        <v>1</v>
-      </c>
-      <c r="I1549">
-        <v>0</v>
       </c>
     </row>
     <row r="1550" spans="1:9">
       <c r="A1550" s="37">
-        <v>5101701</v>
+        <v>5101700</v>
       </c>
       <c r="B1550" s="38">
         <v>1</v>
@@ -48353,10 +48334,10 @@
         <v>0</v>
       </c>
       <c r="D1550" s="39" t="s">
-        <v>1151</v>
+        <v>370</v>
       </c>
       <c r="E1550" s="38" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F1550" s="11" t="s">
         <v>100</v>
@@ -48365,7 +48346,7 @@
         <v>10</v>
       </c>
       <c r="H1550" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1550">
         <v>0</v>
@@ -48373,7 +48354,7 @@
     </row>
     <row r="1551" spans="1:9">
       <c r="A1551" s="37">
-        <v>5101702</v>
+        <v>5101701</v>
       </c>
       <c r="B1551" s="38">
         <v>1</v>
@@ -48385,7 +48366,7 @@
         <v>1152</v>
       </c>
       <c r="E1551" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1551" s="11" t="s">
         <v>100</v>
@@ -48394,7 +48375,7 @@
         <v>10</v>
       </c>
       <c r="H1551" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1551">
         <v>0</v>
@@ -48402,7 +48383,7 @@
     </row>
     <row r="1552" spans="1:9">
       <c r="A1552" s="37">
-        <v>5101705</v>
+        <v>5101702</v>
       </c>
       <c r="B1552" s="38">
         <v>1</v>
@@ -48414,7 +48395,7 @@
         <v>1153</v>
       </c>
       <c r="E1552" s="38" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="F1552" s="11" t="s">
         <v>100</v>
@@ -48431,7 +48412,7 @@
     </row>
     <row r="1553" spans="1:9">
       <c r="A1553" s="37">
-        <v>5101706</v>
+        <v>5101705</v>
       </c>
       <c r="B1553" s="38">
         <v>1</v>
@@ -48443,7 +48424,7 @@
         <v>1154</v>
       </c>
       <c r="E1553" s="38" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1553" s="11" t="s">
         <v>100</v>
@@ -48452,7 +48433,7 @@
         <v>10</v>
       </c>
       <c r="H1553" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1553">
         <v>0</v>
@@ -48460,7 +48441,7 @@
     </row>
     <row r="1554" spans="1:9">
       <c r="A1554" s="37">
-        <v>5101708</v>
+        <v>5101706</v>
       </c>
       <c r="B1554" s="38">
         <v>1</v>
@@ -48472,7 +48453,7 @@
         <v>1155</v>
       </c>
       <c r="E1554" s="38" t="s">
-        <v>1043</v>
+        <v>329</v>
       </c>
       <c r="F1554" s="11" t="s">
         <v>100</v>
@@ -48481,7 +48462,7 @@
         <v>10</v>
       </c>
       <c r="H1554" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1554">
         <v>0</v>
@@ -48489,7 +48470,7 @@
     </row>
     <row r="1555" spans="1:9">
       <c r="A1555" s="37">
-        <v>5101711</v>
+        <v>5101708</v>
       </c>
       <c r="B1555" s="38">
         <v>1</v>
@@ -48501,7 +48482,7 @@
         <v>1156</v>
       </c>
       <c r="E1555" s="38" t="s">
-        <v>245</v>
+        <v>1043</v>
       </c>
       <c r="F1555" s="11" t="s">
         <v>100</v>
@@ -48510,7 +48491,7 @@
         <v>10</v>
       </c>
       <c r="H1555" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1555">
         <v>0</v>
@@ -48518,7 +48499,7 @@
     </row>
     <row r="1556" spans="1:9">
       <c r="A1556" s="37">
-        <v>5101712</v>
+        <v>5101711</v>
       </c>
       <c r="B1556" s="38">
         <v>1</v>
@@ -48530,7 +48511,7 @@
         <v>1157</v>
       </c>
       <c r="E1556" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1556" s="11" t="s">
         <v>100</v>
@@ -48539,7 +48520,7 @@
         <v>10</v>
       </c>
       <c r="H1556" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1556">
         <v>0</v>
@@ -48547,7 +48528,7 @@
     </row>
     <row r="1557" spans="1:9">
       <c r="A1557" s="37">
-        <v>5101715</v>
+        <v>5101712</v>
       </c>
       <c r="B1557" s="38">
         <v>1</v>
@@ -48559,7 +48540,7 @@
         <v>1158</v>
       </c>
       <c r="E1557" s="38" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="F1557" s="11" t="s">
         <v>100</v>
@@ -48576,7 +48557,7 @@
     </row>
     <row r="1558" spans="1:9">
       <c r="A1558" s="37">
-        <v>5101716</v>
+        <v>5101715</v>
       </c>
       <c r="B1558" s="38">
         <v>1</v>
@@ -48588,7 +48569,7 @@
         <v>1159</v>
       </c>
       <c r="E1558" s="38" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1558" s="11" t="s">
         <v>100</v>
@@ -48597,7 +48578,7 @@
         <v>10</v>
       </c>
       <c r="H1558" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1558">
         <v>0</v>
@@ -48605,7 +48586,7 @@
     </row>
     <row r="1559" spans="1:9">
       <c r="A1559" s="37">
-        <v>5101718</v>
+        <v>5101716</v>
       </c>
       <c r="B1559" s="38">
         <v>1</v>
@@ -48617,41 +48598,44 @@
         <v>1160</v>
       </c>
       <c r="E1559" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1559" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1559" s="38">
+        <v>10</v>
+      </c>
+      <c r="H1559" s="38">
+        <v>2</v>
+      </c>
+      <c r="I1559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:9">
+      <c r="A1560" s="37">
+        <v>5101718</v>
+      </c>
+      <c r="B1560" s="38">
+        <v>1</v>
+      </c>
+      <c r="C1560" s="38">
+        <v>0</v>
+      </c>
+      <c r="D1560" s="39" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E1560" s="38" t="s">
         <v>1043</v>
       </c>
-      <c r="F1559" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1559" s="38">
-        <v>10</v>
-      </c>
-      <c r="H1559" s="38">
-        <v>1</v>
-      </c>
-      <c r="I1559">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1560" spans="1:9">
-      <c r="A1560" s="8">
-        <v>920105</v>
-      </c>
-      <c r="B1560" s="38">
-        <v>1</v>
-      </c>
-      <c r="C1560">
-        <v>0</v>
-      </c>
-      <c r="D1560" s="41" t="s">
-        <v>1161</v>
-      </c>
-      <c r="E1560" s="42" t="s">
-        <v>839</v>
-      </c>
-      <c r="G1560">
-        <v>10</v>
-      </c>
-      <c r="H1560">
+      <c r="F1560" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1560" s="38">
+        <v>10</v>
+      </c>
+      <c r="H1560" s="38">
         <v>1</v>
       </c>
       <c r="I1560">
@@ -48660,7 +48644,7 @@
     </row>
     <row r="1561" spans="1:9">
       <c r="A1561" s="8">
-        <v>1920105</v>
+        <v>920105</v>
       </c>
       <c r="B1561" s="38">
         <v>1</v>
@@ -48672,7 +48656,7 @@
         <v>1162</v>
       </c>
       <c r="E1561" s="42" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G1561">
         <v>10</v>
@@ -48681,12 +48665,12 @@
         <v>1</v>
       </c>
       <c r="I1561">
-        <v>7000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1562" spans="1:9">
       <c r="A1562" s="8">
-        <v>2920105</v>
+        <v>1920105</v>
       </c>
       <c r="B1562" s="38">
         <v>1</v>
@@ -48707,12 +48691,12 @@
         <v>1</v>
       </c>
       <c r="I1562">
-        <v>0</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1563" spans="1:9">
       <c r="A1563" s="8">
-        <v>3920105</v>
+        <v>2920105</v>
       </c>
       <c r="B1563" s="38">
         <v>1</v>
@@ -48733,12 +48717,12 @@
         <v>1</v>
       </c>
       <c r="I1563">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1564" spans="1:9">
       <c r="A1564" s="8">
-        <v>4920105</v>
+        <v>3920105</v>
       </c>
       <c r="B1564" s="38">
         <v>1</v>
@@ -48759,12 +48743,12 @@
         <v>1</v>
       </c>
       <c r="I1564">
-        <v>2000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1565" spans="1:9">
       <c r="A1565" s="8">
-        <v>5920105</v>
+        <v>4920105</v>
       </c>
       <c r="B1565" s="38">
         <v>1</v>
@@ -48785,12 +48769,12 @@
         <v>1</v>
       </c>
       <c r="I1565">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1566" spans="1:9">
       <c r="A1566" s="8">
-        <v>6920105</v>
+        <v>5920105</v>
       </c>
       <c r="B1566" s="38">
         <v>1</v>
@@ -48816,7 +48800,7 @@
     </row>
     <row r="1567" spans="1:9">
       <c r="A1567" s="8">
-        <v>7920105</v>
+        <v>6920105</v>
       </c>
       <c r="B1567" s="38">
         <v>1</v>
@@ -48834,15 +48818,15 @@
         <v>10</v>
       </c>
       <c r="H1567">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1567">
-        <v>7000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1568" spans="1:9">
       <c r="A1568" s="8">
-        <v>8920105</v>
+        <v>7920105</v>
       </c>
       <c r="B1568" s="38">
         <v>1</v>
@@ -48860,15 +48844,15 @@
         <v>10</v>
       </c>
       <c r="H1568">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1568">
-        <v>0</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1569" spans="1:9">
       <c r="A1569" s="8">
-        <v>9920105</v>
+        <v>8920105</v>
       </c>
       <c r="B1569" s="38">
         <v>1</v>
@@ -48886,15 +48870,15 @@
         <v>10</v>
       </c>
       <c r="H1569">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1569">
-        <v>7000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1570" spans="1:9">
       <c r="A1570" s="8">
-        <v>11030105</v>
+        <v>9920105</v>
       </c>
       <c r="B1570" s="38">
         <v>1</v>
@@ -48912,15 +48896,15 @@
         <v>10</v>
       </c>
       <c r="H1570">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1570">
-        <v>3000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1571" spans="1:9">
       <c r="A1571" s="8">
-        <v>11920105</v>
+        <v>11030105</v>
       </c>
       <c r="B1571" s="38">
         <v>1</v>
@@ -48941,12 +48925,12 @@
         <v>1</v>
       </c>
       <c r="I1571">
-        <v>500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1572" spans="1:9">
       <c r="A1572" s="8">
-        <v>13920105</v>
+        <v>11920105</v>
       </c>
       <c r="B1572" s="38">
         <v>1</v>
@@ -48967,12 +48951,12 @@
         <v>1</v>
       </c>
       <c r="I1572">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1573" spans="1:9">
       <c r="A1573" s="8">
-        <v>14920105</v>
+        <v>13920105</v>
       </c>
       <c r="B1573" s="38">
         <v>1</v>
@@ -48998,7 +48982,7 @@
     </row>
     <row r="1574" spans="1:9">
       <c r="A1574" s="8">
-        <v>15920105</v>
+        <v>14920105</v>
       </c>
       <c r="B1574" s="38">
         <v>1</v>
@@ -49019,12 +49003,12 @@
         <v>1</v>
       </c>
       <c r="I1574">
-        <v>200</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1575" spans="1:9">
       <c r="A1575" s="8">
-        <v>16920105</v>
+        <v>15920105</v>
       </c>
       <c r="B1575" s="38">
         <v>1</v>
@@ -49038,7 +49022,6 @@
       <c r="E1575" s="42" t="s">
         <v>841</v>
       </c>
-      <c r="F1575" s="41"/>
       <c r="G1575">
         <v>10</v>
       </c>
@@ -49046,12 +49029,12 @@
         <v>1</v>
       </c>
       <c r="I1575">
-        <v>2000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1576" spans="1:9">
       <c r="A1576" s="8">
-        <v>920106</v>
+        <v>16920105</v>
       </c>
       <c r="B1576" s="38">
         <v>1</v>
@@ -49063,8 +49046,9 @@
         <v>1177</v>
       </c>
       <c r="E1576" s="42" t="s">
-        <v>839</v>
-      </c>
+        <v>841</v>
+      </c>
+      <c r="F1576" s="41"/>
       <c r="G1576">
         <v>10</v>
       </c>
@@ -49072,12 +49056,12 @@
         <v>1</v>
       </c>
       <c r="I1576">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1577" spans="1:9">
       <c r="A1577" s="8">
-        <v>1920106</v>
+        <v>920106</v>
       </c>
       <c r="B1577" s="38">
         <v>1</v>
@@ -49089,7 +49073,7 @@
         <v>1178</v>
       </c>
       <c r="E1577" s="42" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G1577">
         <v>10</v>
@@ -49103,7 +49087,7 @@
     </row>
     <row r="1578" spans="1:9">
       <c r="A1578" s="8">
-        <v>2920106</v>
+        <v>1920106</v>
       </c>
       <c r="B1578" s="38">
         <v>1</v>
@@ -49129,7 +49113,7 @@
     </row>
     <row r="1579" spans="1:9">
       <c r="A1579" s="8">
-        <v>3920106</v>
+        <v>2920106</v>
       </c>
       <c r="B1579" s="38">
         <v>1</v>
@@ -49155,7 +49139,7 @@
     </row>
     <row r="1580" spans="1:9">
       <c r="A1580" s="8">
-        <v>4920106</v>
+        <v>3920106</v>
       </c>
       <c r="B1580" s="38">
         <v>1</v>
@@ -49176,12 +49160,12 @@
         <v>1</v>
       </c>
       <c r="I1580">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1581" spans="1:9">
       <c r="A1581" s="8">
-        <v>5920106</v>
+        <v>4920106</v>
       </c>
       <c r="B1581" s="38">
         <v>1</v>
@@ -49202,12 +49186,12 @@
         <v>1</v>
       </c>
       <c r="I1581">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1582" spans="1:9">
       <c r="A1582" s="8">
-        <v>6920106</v>
+        <v>5920106</v>
       </c>
       <c r="B1582" s="38">
         <v>1</v>
@@ -49233,7 +49217,7 @@
     </row>
     <row r="1583" spans="1:9">
       <c r="A1583" s="8">
-        <v>7920106</v>
+        <v>6920106</v>
       </c>
       <c r="B1583" s="38">
         <v>1</v>
@@ -49251,15 +49235,15 @@
         <v>10</v>
       </c>
       <c r="H1583">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1583">
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1584" spans="1:9">
       <c r="A1584" s="8">
-        <v>8920106</v>
+        <v>7920106</v>
       </c>
       <c r="B1584" s="38">
         <v>1</v>
@@ -49277,15 +49261,15 @@
         <v>10</v>
       </c>
       <c r="H1584">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1584">
-        <v>0</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1585" spans="1:9">
       <c r="A1585" s="8">
-        <v>9920106</v>
+        <v>8920106</v>
       </c>
       <c r="B1585" s="38">
         <v>1</v>
@@ -49303,15 +49287,15 @@
         <v>10</v>
       </c>
       <c r="H1585">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1585">
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1586" spans="1:9">
       <c r="A1586" s="8">
-        <v>11030106</v>
+        <v>9920106</v>
       </c>
       <c r="B1586" s="38">
         <v>1</v>
@@ -49329,15 +49313,15 @@
         <v>10</v>
       </c>
       <c r="H1586">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1586">
-        <v>3000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1587" spans="1:9">
       <c r="A1587" s="8">
-        <v>11920106</v>
+        <v>11030106</v>
       </c>
       <c r="B1587" s="38">
         <v>1</v>
@@ -49358,12 +49342,12 @@
         <v>1</v>
       </c>
       <c r="I1587">
-        <v>500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1588" spans="1:9">
       <c r="A1588" s="8">
-        <v>13920106</v>
+        <v>11920106</v>
       </c>
       <c r="B1588" s="38">
         <v>1</v>
@@ -49384,12 +49368,12 @@
         <v>1</v>
       </c>
       <c r="I1588">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1589" spans="1:9">
       <c r="A1589" s="8">
-        <v>920115</v>
+        <v>13920106</v>
       </c>
       <c r="B1589" s="38">
         <v>1</v>
@@ -49401,9 +49385,8 @@
         <v>1190</v>
       </c>
       <c r="E1589" s="42" t="s">
-        <v>839</v>
-      </c>
-      <c r="F1589" s="41"/>
+        <v>841</v>
+      </c>
       <c r="G1589">
         <v>10</v>
       </c>
@@ -49411,12 +49394,12 @@
         <v>1</v>
       </c>
       <c r="I1589">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1590" spans="1:9">
       <c r="A1590" s="8">
-        <v>4920115</v>
+        <v>920115</v>
       </c>
       <c r="B1590" s="38">
         <v>1</v>
@@ -49428,8 +49411,9 @@
         <v>1191</v>
       </c>
       <c r="E1590" s="42" t="s">
-        <v>841</v>
-      </c>
+        <v>839</v>
+      </c>
+      <c r="F1590" s="41"/>
       <c r="G1590">
         <v>10</v>
       </c>
@@ -49437,12 +49421,12 @@
         <v>1</v>
       </c>
       <c r="I1590">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1591" spans="1:9">
       <c r="A1591" s="8">
-        <v>920113</v>
+        <v>4920115</v>
       </c>
       <c r="B1591" s="38">
         <v>1</v>
@@ -49454,9 +49438,8 @@
         <v>1192</v>
       </c>
       <c r="E1591" s="42" t="s">
-        <v>839</v>
-      </c>
-      <c r="F1591" s="41"/>
+        <v>841</v>
+      </c>
       <c r="G1591">
         <v>10</v>
       </c>
@@ -49464,12 +49447,12 @@
         <v>1</v>
       </c>
       <c r="I1591">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1592" spans="1:9">
       <c r="A1592" s="8">
-        <v>820095</v>
+        <v>920113</v>
       </c>
       <c r="B1592" s="38">
         <v>1</v>
@@ -49477,12 +49460,13 @@
       <c r="C1592">
         <v>0</v>
       </c>
-      <c r="D1592" s="44" t="s">
+      <c r="D1592" s="41" t="s">
         <v>1193</v>
       </c>
-      <c r="E1592" s="44" t="s">
-        <v>1193</v>
-      </c>
+      <c r="E1592" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="F1592" s="41"/>
       <c r="G1592">
         <v>10</v>
       </c>
@@ -49495,7 +49479,7 @@
     </row>
     <row r="1593" spans="1:9">
       <c r="A1593" s="8">
-        <v>820112</v>
+        <v>820095</v>
       </c>
       <c r="B1593" s="38">
         <v>1</v>
@@ -49507,7 +49491,7 @@
         <v>1194</v>
       </c>
       <c r="E1593" s="44" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G1593">
         <v>10</v>
@@ -49521,7 +49505,7 @@
     </row>
     <row r="1594" spans="1:9">
       <c r="A1594" s="8">
-        <v>920107</v>
+        <v>820112</v>
       </c>
       <c r="B1594" s="38">
         <v>1</v>
@@ -49529,11 +49513,11 @@
       <c r="C1594">
         <v>0</v>
       </c>
-      <c r="D1594" s="41" t="s">
+      <c r="D1594" s="44" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E1594" s="44" t="s">
         <v>1196</v>
-      </c>
-      <c r="E1594" s="42" t="s">
-        <v>839</v>
       </c>
       <c r="G1594">
         <v>10</v>
@@ -49547,7 +49531,7 @@
     </row>
     <row r="1595" spans="1:9">
       <c r="A1595" s="8">
-        <v>2920107</v>
+        <v>920107</v>
       </c>
       <c r="B1595" s="38">
         <v>1</v>
@@ -49559,7 +49543,7 @@
         <v>1197</v>
       </c>
       <c r="E1595" s="42" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G1595">
         <v>10</v>
@@ -49573,7 +49557,7 @@
     </row>
     <row r="1596" spans="1:9">
       <c r="A1596" s="8">
-        <v>39201057</v>
+        <v>2920107</v>
       </c>
       <c r="B1596" s="38">
         <v>1</v>
@@ -49599,7 +49583,7 @@
     </row>
     <row r="1597" spans="1:9">
       <c r="A1597" s="8">
-        <v>4920107</v>
+        <v>39201057</v>
       </c>
       <c r="B1597" s="38">
         <v>1</v>
@@ -49620,12 +49604,12 @@
         <v>1</v>
       </c>
       <c r="I1597">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1598" spans="1:9">
       <c r="A1598" s="8">
-        <v>6920107</v>
+        <v>4920107</v>
       </c>
       <c r="B1598" s="38">
         <v>1</v>
@@ -49646,12 +49630,12 @@
         <v>1</v>
       </c>
       <c r="I1598">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1599" spans="1:9">
       <c r="A1599" s="8">
-        <v>7920107</v>
+        <v>6920107</v>
       </c>
       <c r="B1599" s="38">
         <v>1</v>
@@ -49669,15 +49653,15 @@
         <v>10</v>
       </c>
       <c r="H1599">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1599">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1600" spans="1:9">
       <c r="A1600" s="8">
-        <v>8920107</v>
+        <v>7920107</v>
       </c>
       <c r="B1600" s="38">
         <v>1</v>
@@ -49695,15 +49679,15 @@
         <v>10</v>
       </c>
       <c r="H1600">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1600">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1601" spans="1:9">
       <c r="A1601" s="8">
-        <v>9920107</v>
+        <v>8920107</v>
       </c>
       <c r="B1601" s="38">
         <v>1</v>
@@ -49721,15 +49705,15 @@
         <v>10</v>
       </c>
       <c r="H1601">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1601">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1602" spans="1:9">
       <c r="A1602" s="8">
-        <v>11030107</v>
+        <v>9920107</v>
       </c>
       <c r="B1602" s="38">
         <v>1</v>
@@ -49747,15 +49731,15 @@
         <v>10</v>
       </c>
       <c r="H1602">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1602">
-        <v>2000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1603" spans="1:9">
       <c r="A1603" s="8">
-        <v>11920107</v>
+        <v>11030107</v>
       </c>
       <c r="B1603" s="38">
         <v>1</v>
@@ -49776,12 +49760,12 @@
         <v>1</v>
       </c>
       <c r="I1603">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1604" spans="1:9">
       <c r="A1604" s="8">
-        <v>13920107</v>
+        <v>11920107</v>
       </c>
       <c r="B1604" s="38">
         <v>1</v>
@@ -49802,12 +49786,12 @@
         <v>1</v>
       </c>
       <c r="I1604">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="1605" spans="1:9">
       <c r="A1605" s="8">
-        <v>920108</v>
+        <v>13920107</v>
       </c>
       <c r="B1605" s="38">
         <v>1</v>
@@ -49819,9 +49803,8 @@
         <v>1207</v>
       </c>
       <c r="E1605" s="42" t="s">
-        <v>839</v>
-      </c>
-      <c r="F1605" s="41"/>
+        <v>841</v>
+      </c>
       <c r="G1605">
         <v>10</v>
       </c>
@@ -49829,12 +49812,12 @@
         <v>1</v>
       </c>
       <c r="I1605">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1606" spans="1:9">
       <c r="A1606" s="8">
-        <v>820098</v>
+        <v>920108</v>
       </c>
       <c r="B1606" s="38">
         <v>1</v>
@@ -49842,12 +49825,13 @@
       <c r="C1606">
         <v>0</v>
       </c>
-      <c r="D1606" s="44" t="s">
+      <c r="D1606" s="41" t="s">
         <v>1208</v>
       </c>
-      <c r="E1606" s="44" t="s">
-        <v>1208</v>
-      </c>
+      <c r="E1606" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="F1606" s="41"/>
       <c r="G1606">
         <v>10</v>
       </c>
@@ -49860,7 +49844,7 @@
     </row>
     <row r="1607" spans="1:9">
       <c r="A1607" s="8">
-        <v>920109</v>
+        <v>820098</v>
       </c>
       <c r="B1607" s="38">
         <v>1</v>
@@ -49868,11 +49852,11 @@
       <c r="C1607">
         <v>0</v>
       </c>
-      <c r="D1607" s="41" t="s">
+      <c r="D1607" s="44" t="s">
         <v>1209</v>
       </c>
-      <c r="E1607" s="42" t="s">
-        <v>839</v>
+      <c r="E1607" s="44" t="s">
+        <v>1209</v>
       </c>
       <c r="G1607">
         <v>10</v>
@@ -49886,7 +49870,7 @@
     </row>
     <row r="1608" spans="1:9">
       <c r="A1608" s="8">
-        <v>2920109</v>
+        <v>920109</v>
       </c>
       <c r="B1608" s="38">
         <v>1</v>
@@ -49898,7 +49882,7 @@
         <v>1210</v>
       </c>
       <c r="E1608" s="42" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G1608">
         <v>10</v>
@@ -49912,7 +49896,7 @@
     </row>
     <row r="1609" spans="1:9">
       <c r="A1609" s="8">
-        <v>3920109</v>
+        <v>2920109</v>
       </c>
       <c r="B1609" s="38">
         <v>1</v>
@@ -49933,12 +49917,12 @@
         <v>1</v>
       </c>
       <c r="I1609">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1610" spans="1:9">
       <c r="A1610" s="8">
-        <v>4920109</v>
+        <v>3920109</v>
       </c>
       <c r="B1610" s="38">
         <v>1</v>
@@ -49959,12 +49943,12 @@
         <v>1</v>
       </c>
       <c r="I1610">
-        <v>2200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1611" spans="1:9">
       <c r="A1611" s="8">
-        <v>6920109</v>
+        <v>4920109</v>
       </c>
       <c r="B1611" s="38">
         <v>1</v>
@@ -49985,12 +49969,12 @@
         <v>1</v>
       </c>
       <c r="I1611">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1612" spans="1:9">
       <c r="A1612" s="8">
-        <v>7920109</v>
+        <v>6920109</v>
       </c>
       <c r="B1612" s="38">
         <v>1</v>
@@ -50008,7 +49992,7 @@
         <v>10</v>
       </c>
       <c r="H1612">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1612">
         <v>0</v>
@@ -50016,7 +50000,7 @@
     </row>
     <row r="1613" spans="1:9">
       <c r="A1613" s="8">
-        <v>8920109</v>
+        <v>7920109</v>
       </c>
       <c r="B1613" s="38">
         <v>1</v>
@@ -50034,7 +50018,7 @@
         <v>10</v>
       </c>
       <c r="H1613">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1613">
         <v>0</v>
@@ -50042,7 +50026,7 @@
     </row>
     <row r="1614" spans="1:9">
       <c r="A1614" s="8">
-        <v>9920109</v>
+        <v>8920109</v>
       </c>
       <c r="B1614" s="38">
         <v>1</v>
@@ -50060,7 +50044,7 @@
         <v>10</v>
       </c>
       <c r="H1614">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1614">
         <v>0</v>
@@ -50068,7 +50052,7 @@
     </row>
     <row r="1615" spans="1:9">
       <c r="A1615" s="8">
-        <v>13920109</v>
+        <v>9920109</v>
       </c>
       <c r="B1615" s="38">
         <v>1</v>
@@ -50086,15 +50070,15 @@
         <v>10</v>
       </c>
       <c r="H1615">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1615">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1616" spans="1:9">
       <c r="A1616" s="8">
-        <v>16920109</v>
+        <v>13920109</v>
       </c>
       <c r="B1616" s="38">
         <v>1</v>
@@ -50108,7 +50092,6 @@
       <c r="E1616" s="42" t="s">
         <v>841</v>
       </c>
-      <c r="F1616" s="41"/>
       <c r="G1616">
         <v>10</v>
       </c>
@@ -50116,12 +50099,12 @@
         <v>1</v>
       </c>
       <c r="I1616">
-        <v>120</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1617" spans="1:9">
       <c r="A1617" s="8">
-        <v>920110</v>
+        <v>16920109</v>
       </c>
       <c r="B1617" s="38">
         <v>1</v>
@@ -50133,8 +50116,9 @@
         <v>1219</v>
       </c>
       <c r="E1617" s="42" t="s">
-        <v>839</v>
-      </c>
+        <v>841</v>
+      </c>
+      <c r="F1617" s="41"/>
       <c r="G1617">
         <v>10</v>
       </c>
@@ -50142,12 +50126,12 @@
         <v>1</v>
       </c>
       <c r="I1617">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1618" spans="1:9">
       <c r="A1618" s="8">
-        <v>1920110</v>
+        <v>920110</v>
       </c>
       <c r="B1618" s="38">
         <v>1</v>
@@ -50159,7 +50143,7 @@
         <v>1220</v>
       </c>
       <c r="E1618" s="42" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G1618">
         <v>10</v>
@@ -50173,7 +50157,7 @@
     </row>
     <row r="1619" spans="1:9">
       <c r="A1619" s="8">
-        <v>2920110</v>
+        <v>1920110</v>
       </c>
       <c r="B1619" s="38">
         <v>1</v>
@@ -50199,7 +50183,7 @@
     </row>
     <row r="1620" spans="1:9">
       <c r="A1620" s="8">
-        <v>3920110</v>
+        <v>2920110</v>
       </c>
       <c r="B1620" s="38">
         <v>1</v>
@@ -50220,12 +50204,12 @@
         <v>1</v>
       </c>
       <c r="I1620">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="1621" ht="12" customHeight="1" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:9">
       <c r="A1621" s="8">
-        <v>4920110</v>
+        <v>3920110</v>
       </c>
       <c r="B1621" s="38">
         <v>1</v>
@@ -50246,12 +50230,12 @@
         <v>1</v>
       </c>
       <c r="I1621">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="1622" spans="1:9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="1622" ht="12" customHeight="1" spans="1:9">
       <c r="A1622" s="8">
-        <v>6920110</v>
+        <v>4920110</v>
       </c>
       <c r="B1622" s="38">
         <v>1</v>
@@ -50272,12 +50256,12 @@
         <v>1</v>
       </c>
       <c r="I1622">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1623" spans="1:9">
       <c r="A1623" s="8">
-        <v>7920110</v>
+        <v>6920110</v>
       </c>
       <c r="B1623" s="38">
         <v>1</v>
@@ -50295,15 +50279,15 @@
         <v>10</v>
       </c>
       <c r="H1623">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1623">
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1624" spans="1:9">
       <c r="A1624" s="8">
-        <v>8920110</v>
+        <v>7920110</v>
       </c>
       <c r="B1624" s="38">
         <v>1</v>
@@ -50321,15 +50305,15 @@
         <v>10</v>
       </c>
       <c r="H1624">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1624">
-        <v>0</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1625" spans="1:9">
       <c r="A1625" s="8">
-        <v>9920110</v>
+        <v>8920110</v>
       </c>
       <c r="B1625" s="38">
         <v>1</v>
@@ -50347,15 +50331,15 @@
         <v>10</v>
       </c>
       <c r="H1625">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1625">
-        <v>12000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1626" spans="1:9">
       <c r="A1626" s="8">
-        <v>13920110</v>
+        <v>9920110</v>
       </c>
       <c r="B1626" s="38">
         <v>1</v>
@@ -50373,15 +50357,15 @@
         <v>10</v>
       </c>
       <c r="H1626">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1626">
-        <v>1</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1627" spans="1:9">
       <c r="A1627" s="8">
-        <v>920119</v>
+        <v>13920110</v>
       </c>
       <c r="B1627" s="38">
         <v>1</v>
@@ -50393,9 +50377,8 @@
         <v>1229</v>
       </c>
       <c r="E1627" s="42" t="s">
-        <v>839</v>
-      </c>
-      <c r="F1627" s="41"/>
+        <v>841</v>
+      </c>
       <c r="G1627">
         <v>10</v>
       </c>
@@ -50403,12 +50386,12 @@
         <v>1</v>
       </c>
       <c r="I1627">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1628" spans="1:9">
       <c r="A1628" s="8">
-        <v>820096</v>
+        <v>920119</v>
       </c>
       <c r="B1628" s="38">
         <v>1</v>
@@ -50416,12 +50399,13 @@
       <c r="C1628">
         <v>0</v>
       </c>
-      <c r="D1628" s="44" t="s">
+      <c r="D1628" s="41" t="s">
         <v>1230</v>
       </c>
-      <c r="E1628" s="44" t="s">
-        <v>1230</v>
-      </c>
+      <c r="E1628" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="F1628" s="41"/>
       <c r="G1628">
         <v>10</v>
       </c>
@@ -50434,7 +50418,7 @@
     </row>
     <row r="1629" spans="1:9">
       <c r="A1629" s="8">
-        <v>920114</v>
+        <v>820096</v>
       </c>
       <c r="B1629" s="38">
         <v>1</v>
@@ -50442,13 +50426,12 @@
       <c r="C1629">
         <v>0</v>
       </c>
-      <c r="D1629" s="41" t="s">
+      <c r="D1629" s="44" t="s">
         <v>1231</v>
       </c>
-      <c r="E1629" s="42" t="s">
-        <v>839</v>
-      </c>
-      <c r="F1629" s="41"/>
+      <c r="E1629" s="44" t="s">
+        <v>1231</v>
+      </c>
       <c r="G1629">
         <v>10</v>
       </c>
@@ -50461,7 +50444,7 @@
     </row>
     <row r="1630" spans="1:9">
       <c r="A1630" s="8">
-        <v>4920114</v>
+        <v>920114</v>
       </c>
       <c r="B1630" s="38">
         <v>1</v>
@@ -50473,8 +50456,9 @@
         <v>1232</v>
       </c>
       <c r="E1630" s="42" t="s">
-        <v>841</v>
-      </c>
+        <v>839</v>
+      </c>
+      <c r="F1630" s="41"/>
       <c r="G1630">
         <v>10</v>
       </c>
@@ -50482,12 +50466,12 @@
         <v>1</v>
       </c>
       <c r="I1630">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1631" spans="1:9">
       <c r="A1631" s="8">
-        <v>920116</v>
+        <v>4920114</v>
       </c>
       <c r="B1631" s="38">
         <v>1</v>
@@ -50499,9 +50483,8 @@
         <v>1233</v>
       </c>
       <c r="E1631" s="42" t="s">
-        <v>839</v>
-      </c>
-      <c r="F1631" s="41"/>
+        <v>841</v>
+      </c>
       <c r="G1631">
         <v>10</v>
       </c>
@@ -50509,12 +50492,12 @@
         <v>1</v>
       </c>
       <c r="I1631">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1632" spans="1:9">
       <c r="A1632" s="8">
-        <v>820097</v>
+        <v>920116</v>
       </c>
       <c r="B1632" s="38">
         <v>1</v>
@@ -50522,12 +50505,13 @@
       <c r="C1632">
         <v>0</v>
       </c>
-      <c r="D1632" s="44" t="s">
-        <v>1195</v>
-      </c>
-      <c r="E1632" s="44" t="s">
-        <v>1195</v>
-      </c>
+      <c r="D1632" s="41" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E1632" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="F1632" s="41"/>
       <c r="G1632">
         <v>10</v>
       </c>
@@ -50540,7 +50524,7 @@
     </row>
     <row r="1633" spans="1:9">
       <c r="A1633" s="8">
-        <v>820111</v>
+        <v>820097</v>
       </c>
       <c r="B1633" s="38">
         <v>1</v>
@@ -50549,10 +50533,10 @@
         <v>0</v>
       </c>
       <c r="D1633" s="44" t="s">
-        <v>1234</v>
+        <v>1196</v>
       </c>
       <c r="E1633" s="44" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G1633">
         <v>10</v>
@@ -50566,7 +50550,7 @@
     </row>
     <row r="1634" spans="1:9">
       <c r="A1634" s="8">
-        <v>920111</v>
+        <v>820111</v>
       </c>
       <c r="B1634" s="38">
         <v>1</v>
@@ -50574,11 +50558,11 @@
       <c r="C1634">
         <v>0</v>
       </c>
-      <c r="D1634" s="41" t="s">
+      <c r="D1634" s="44" t="s">
         <v>1235</v>
       </c>
-      <c r="E1634" s="42" t="s">
-        <v>839</v>
+      <c r="E1634" s="44" t="s">
+        <v>1196</v>
       </c>
       <c r="G1634">
         <v>10</v>
@@ -50592,7 +50576,7 @@
     </row>
     <row r="1635" spans="1:9">
       <c r="A1635" s="8">
-        <v>1920111</v>
+        <v>920111</v>
       </c>
       <c r="B1635" s="38">
         <v>1</v>
@@ -50604,7 +50588,7 @@
         <v>1236</v>
       </c>
       <c r="E1635" s="42" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G1635">
         <v>10</v>
@@ -50613,12 +50597,12 @@
         <v>1</v>
       </c>
       <c r="I1635">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1636" spans="1:9">
       <c r="A1636" s="8">
-        <v>2920111</v>
+        <v>1920111</v>
       </c>
       <c r="B1636" s="38">
         <v>1</v>
@@ -50639,12 +50623,12 @@
         <v>1</v>
       </c>
       <c r="I1636">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1637" spans="1:9">
       <c r="A1637" s="8">
-        <v>3920111</v>
+        <v>2920111</v>
       </c>
       <c r="B1637" s="38">
         <v>1</v>
@@ -50665,12 +50649,12 @@
         <v>1</v>
       </c>
       <c r="I1637">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1638" spans="1:9">
       <c r="A1638" s="8">
-        <v>4920111</v>
+        <v>3920111</v>
       </c>
       <c r="B1638" s="38">
         <v>1</v>
@@ -50691,12 +50675,12 @@
         <v>1</v>
       </c>
       <c r="I1638">
-        <v>1800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1639" spans="1:9">
       <c r="A1639" s="8">
-        <v>6920111</v>
+        <v>4920111</v>
       </c>
       <c r="B1639" s="38">
         <v>1</v>
@@ -50717,12 +50701,12 @@
         <v>1</v>
       </c>
       <c r="I1639">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1640" spans="1:9">
       <c r="A1640" s="8">
-        <v>7920111</v>
+        <v>6920111</v>
       </c>
       <c r="B1640" s="38">
         <v>1</v>
@@ -50740,15 +50724,15 @@
         <v>10</v>
       </c>
       <c r="H1640">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1640">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1641" spans="1:9">
       <c r="A1641" s="8">
-        <v>8920111</v>
+        <v>7920111</v>
       </c>
       <c r="B1641" s="38">
         <v>1</v>
@@ -50766,15 +50750,15 @@
         <v>10</v>
       </c>
       <c r="H1641">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1641">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1642" spans="1:9">
       <c r="A1642" s="8">
-        <v>9920111</v>
+        <v>8920111</v>
       </c>
       <c r="B1642" s="38">
         <v>1</v>
@@ -50792,15 +50776,15 @@
         <v>10</v>
       </c>
       <c r="H1642">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1642">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1643" spans="1:9">
       <c r="A1643" s="8">
-        <v>11030111</v>
+        <v>9920111</v>
       </c>
       <c r="B1643" s="38">
         <v>1</v>
@@ -50818,15 +50802,15 @@
         <v>10</v>
       </c>
       <c r="H1643">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1643">
-        <v>3000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1644" spans="1:9">
       <c r="A1644" s="8">
-        <v>11920111</v>
+        <v>11030111</v>
       </c>
       <c r="B1644" s="38">
         <v>1</v>
@@ -50847,12 +50831,12 @@
         <v>1</v>
       </c>
       <c r="I1644">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1645" spans="1:9">
       <c r="A1645" s="8">
-        <v>13920111</v>
+        <v>11920111</v>
       </c>
       <c r="B1645" s="38">
         <v>1</v>
@@ -50873,12 +50857,12 @@
         <v>1</v>
       </c>
       <c r="I1645">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1646" spans="1:9">
       <c r="A1646" s="8">
-        <v>920118</v>
+        <v>13920111</v>
       </c>
       <c r="B1646" s="38">
         <v>1</v>
@@ -50890,9 +50874,8 @@
         <v>1247</v>
       </c>
       <c r="E1646" s="42" t="s">
-        <v>839</v>
-      </c>
-      <c r="F1646" s="41"/>
+        <v>841</v>
+      </c>
       <c r="G1646">
         <v>10</v>
       </c>
@@ -50900,12 +50883,12 @@
         <v>1</v>
       </c>
       <c r="I1646">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1647" spans="1:9">
       <c r="A1647" s="8">
-        <v>820100</v>
+        <v>920118</v>
       </c>
       <c r="B1647" s="38">
         <v>1</v>
@@ -50913,12 +50896,13 @@
       <c r="C1647">
         <v>0</v>
       </c>
-      <c r="D1647" s="44" t="s">
+      <c r="D1647" s="41" t="s">
         <v>1248</v>
       </c>
-      <c r="E1647" s="44" t="s">
-        <v>1248</v>
-      </c>
+      <c r="E1647" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="F1647" s="41"/>
       <c r="G1647">
         <v>10</v>
       </c>
@@ -50931,7 +50915,7 @@
     </row>
     <row r="1648" spans="1:9">
       <c r="A1648" s="8">
-        <v>920112</v>
+        <v>820100</v>
       </c>
       <c r="B1648" s="38">
         <v>1</v>
@@ -50939,11 +50923,11 @@
       <c r="C1648">
         <v>0</v>
       </c>
-      <c r="D1648" s="41" t="s">
+      <c r="D1648" s="44" t="s">
         <v>1249</v>
       </c>
-      <c r="E1648" s="42" t="s">
-        <v>839</v>
+      <c r="E1648" s="44" t="s">
+        <v>1249</v>
       </c>
       <c r="G1648">
         <v>10</v>
@@ -50957,7 +50941,7 @@
     </row>
     <row r="1649" spans="1:9">
       <c r="A1649" s="8">
-        <v>1920112</v>
+        <v>920112</v>
       </c>
       <c r="B1649" s="38">
         <v>1</v>
@@ -50969,7 +50953,7 @@
         <v>1250</v>
       </c>
       <c r="E1649" s="42" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G1649">
         <v>10</v>
@@ -50978,12 +50962,12 @@
         <v>1</v>
       </c>
       <c r="I1649">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1650" spans="1:9">
       <c r="A1650" s="8">
-        <v>2920112</v>
+        <v>1920112</v>
       </c>
       <c r="B1650" s="38">
         <v>1</v>
@@ -51004,12 +50988,12 @@
         <v>1</v>
       </c>
       <c r="I1650">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1651" spans="1:9">
       <c r="A1651" s="8">
-        <v>3920112</v>
+        <v>2920112</v>
       </c>
       <c r="B1651" s="38">
         <v>1</v>
@@ -51030,12 +51014,12 @@
         <v>1</v>
       </c>
       <c r="I1651">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1652" spans="1:9">
       <c r="A1652" s="8">
-        <v>4920112</v>
+        <v>3920112</v>
       </c>
       <c r="B1652" s="38">
         <v>1</v>
@@ -51056,12 +51040,12 @@
         <v>1</v>
       </c>
       <c r="I1652">
-        <v>1800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1653" spans="1:9">
       <c r="A1653" s="8">
-        <v>6920112</v>
+        <v>4920112</v>
       </c>
       <c r="B1653" s="38">
         <v>1</v>
@@ -51082,12 +51066,12 @@
         <v>1</v>
       </c>
       <c r="I1653">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1654" spans="1:9">
       <c r="A1654" s="8">
-        <v>7920112</v>
+        <v>6920112</v>
       </c>
       <c r="B1654" s="38">
         <v>1</v>
@@ -51105,15 +51089,15 @@
         <v>10</v>
       </c>
       <c r="H1654">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1654">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1655" spans="1:9">
       <c r="A1655" s="8">
-        <v>8920112</v>
+        <v>7920112</v>
       </c>
       <c r="B1655" s="38">
         <v>1</v>
@@ -51131,15 +51115,15 @@
         <v>10</v>
       </c>
       <c r="H1655">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1655">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1656" spans="1:9">
       <c r="A1656" s="8">
-        <v>9920112</v>
+        <v>8920112</v>
       </c>
       <c r="B1656" s="38">
         <v>1</v>
@@ -51157,15 +51141,15 @@
         <v>10</v>
       </c>
       <c r="H1656">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1656">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1657" spans="1:9">
       <c r="A1657" s="8">
-        <v>13920112</v>
+        <v>9920112</v>
       </c>
       <c r="B1657" s="38">
         <v>1</v>
@@ -51183,15 +51167,15 @@
         <v>10</v>
       </c>
       <c r="H1657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1657">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1658" spans="1:9">
       <c r="A1658" s="8">
-        <v>920117</v>
+        <v>13920112</v>
       </c>
       <c r="B1658" s="38">
         <v>1</v>
@@ -51203,9 +51187,8 @@
         <v>1259</v>
       </c>
       <c r="E1658" s="42" t="s">
-        <v>839</v>
-      </c>
-      <c r="F1658" s="41"/>
+        <v>841</v>
+      </c>
       <c r="G1658">
         <v>10</v>
       </c>
@@ -51213,58 +51196,56 @@
         <v>1</v>
       </c>
       <c r="I1658">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1659" spans="1:9">
       <c r="A1659" s="8">
+        <v>920117</v>
+      </c>
+      <c r="B1659" s="38">
+        <v>1</v>
+      </c>
+      <c r="C1659">
+        <v>0</v>
+      </c>
+      <c r="D1659" s="41" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E1659" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="F1659" s="41"/>
+      <c r="G1659">
+        <v>10</v>
+      </c>
+      <c r="H1659">
+        <v>1</v>
+      </c>
+      <c r="I1659">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:9">
+      <c r="A1660" s="8">
         <v>820099</v>
       </c>
-      <c r="B1659" s="38">
-        <v>1</v>
-      </c>
-      <c r="C1659">
-        <v>0</v>
-      </c>
-      <c r="D1659" s="44" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E1659" s="44" t="s">
-        <v>1260</v>
-      </c>
-      <c r="G1659">
-        <v>10</v>
-      </c>
-      <c r="H1659">
-        <v>1</v>
-      </c>
-      <c r="I1659">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1660" spans="1:9">
-      <c r="A1660" s="37">
-        <v>5101721</v>
-      </c>
       <c r="B1660" s="38">
         <v>1</v>
       </c>
-      <c r="C1660" s="38">
-        <v>0</v>
-      </c>
-      <c r="D1660" s="39" t="s">
+      <c r="C1660">
+        <v>0</v>
+      </c>
+      <c r="D1660" s="44" t="s">
         <v>1261</v>
       </c>
-      <c r="E1660" s="38" t="s">
-        <v>327</v>
-      </c>
-      <c r="F1660" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1660" s="38">
-        <v>10</v>
-      </c>
-      <c r="H1660" s="38">
+      <c r="E1660" s="44" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G1660">
+        <v>10</v>
+      </c>
+      <c r="H1660">
         <v>1</v>
       </c>
       <c r="I1660">
@@ -51273,7 +51254,7 @@
     </row>
     <row r="1661" spans="1:9">
       <c r="A1661" s="37">
-        <v>5101722</v>
+        <v>5101721</v>
       </c>
       <c r="B1661" s="38">
         <v>1</v>
@@ -51285,7 +51266,7 @@
         <v>1262</v>
       </c>
       <c r="E1661" s="38" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1661" s="11" t="s">
         <v>100</v>
@@ -51294,7 +51275,7 @@
         <v>10</v>
       </c>
       <c r="H1661" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1661">
         <v>0</v>
@@ -51302,7 +51283,7 @@
     </row>
     <row r="1662" spans="1:9">
       <c r="A1662" s="37">
-        <v>5101723</v>
+        <v>5101722</v>
       </c>
       <c r="B1662" s="38">
         <v>1</v>
@@ -51331,7 +51312,7 @@
     </row>
     <row r="1663" spans="1:9">
       <c r="A1663" s="37">
-        <v>51017232</v>
+        <v>5101723</v>
       </c>
       <c r="B1663" s="38">
         <v>1</v>
@@ -51343,7 +51324,7 @@
         <v>1264</v>
       </c>
       <c r="E1663" s="38" t="s">
-        <v>1265</v>
+        <v>329</v>
       </c>
       <c r="F1663" s="11" t="s">
         <v>100</v>
@@ -51352,7 +51333,7 @@
         <v>10</v>
       </c>
       <c r="H1663" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1663">
         <v>0</v>
@@ -51360,36 +51341,36 @@
     </row>
     <row r="1664" spans="1:9">
       <c r="A1664" s="37">
+        <v>51017232</v>
+      </c>
+      <c r="B1664" s="38">
+        <v>1</v>
+      </c>
+      <c r="C1664" s="38">
+        <v>0</v>
+      </c>
+      <c r="D1664" s="39" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E1664" s="38" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F1664" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1664" s="38">
+        <v>10</v>
+      </c>
+      <c r="H1664" s="38">
+        <v>1</v>
+      </c>
+      <c r="I1664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:9">
+      <c r="A1665" s="37">
         <v>5101724</v>
-      </c>
-      <c r="B1664" s="38">
-        <v>1</v>
-      </c>
-      <c r="C1664" s="38">
-        <v>0</v>
-      </c>
-      <c r="D1664" s="39" t="s">
-        <v>1266</v>
-      </c>
-      <c r="E1664" s="38" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1664" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1664" s="38">
-        <v>10</v>
-      </c>
-      <c r="H1664" s="38">
-        <v>2</v>
-      </c>
-      <c r="I1664">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1665" ht="14.1" customHeight="1" spans="1:9">
-      <c r="A1665" s="37">
-        <v>5101725</v>
       </c>
       <c r="B1665" s="38">
         <v>1</v>
@@ -51401,7 +51382,7 @@
         <v>1267</v>
       </c>
       <c r="E1665" s="38" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1665" s="11" t="s">
         <v>100</v>
@@ -51416,9 +51397,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1666" spans="1:9">
+    <row r="1666" ht="14.1" customHeight="1" spans="1:9">
       <c r="A1666" s="37">
-        <v>5101730</v>
+        <v>5101725</v>
       </c>
       <c r="B1666" s="38">
         <v>1</v>
@@ -51430,7 +51411,7 @@
         <v>1268</v>
       </c>
       <c r="E1666" s="38" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F1666" s="11" t="s">
         <v>100</v>
@@ -51447,7 +51428,7 @@
     </row>
     <row r="1667" spans="1:9">
       <c r="A1667" s="37">
-        <v>5101731</v>
+        <v>5101730</v>
       </c>
       <c r="B1667" s="38">
         <v>1</v>
@@ -51459,7 +51440,7 @@
         <v>1269</v>
       </c>
       <c r="E1667" s="38" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1667" s="11" t="s">
         <v>100</v>
@@ -51468,7 +51449,7 @@
         <v>10</v>
       </c>
       <c r="H1667" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1667">
         <v>0</v>
@@ -51476,7 +51457,7 @@
     </row>
     <row r="1668" spans="1:9">
       <c r="A1668" s="37">
-        <v>5101732</v>
+        <v>5101731</v>
       </c>
       <c r="B1668" s="38">
         <v>1</v>
@@ -51488,7 +51469,7 @@
         <v>1270</v>
       </c>
       <c r="E1668" s="38" t="s">
-        <v>1043</v>
+        <v>327</v>
       </c>
       <c r="F1668" s="11" t="s">
         <v>100</v>
@@ -51505,7 +51486,7 @@
     </row>
     <row r="1669" spans="1:9">
       <c r="A1669" s="37">
-        <v>5101734</v>
+        <v>5101732</v>
       </c>
       <c r="B1669" s="38">
         <v>1</v>
@@ -51517,7 +51498,7 @@
         <v>1271</v>
       </c>
       <c r="E1669" s="38" t="s">
-        <v>245</v>
+        <v>1043</v>
       </c>
       <c r="F1669" s="11" t="s">
         <v>100</v>
@@ -51526,7 +51507,7 @@
         <v>10</v>
       </c>
       <c r="H1669" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1669">
         <v>0</v>
@@ -51534,7 +51515,7 @@
     </row>
     <row r="1670" spans="1:9">
       <c r="A1670" s="37">
-        <v>5101735</v>
+        <v>5101734</v>
       </c>
       <c r="B1670" s="38">
         <v>1</v>
@@ -51546,7 +51527,7 @@
         <v>1272</v>
       </c>
       <c r="E1670" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1670" s="11" t="s">
         <v>100</v>
@@ -51555,15 +51536,15 @@
         <v>10</v>
       </c>
       <c r="H1670" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1670">
         <v>0</v>
       </c>
     </row>
-    <row r="1671" ht="14.1" customHeight="1" spans="1:9">
+    <row r="1671" spans="1:9">
       <c r="A1671" s="37">
-        <v>5101733</v>
+        <v>5101735</v>
       </c>
       <c r="B1671" s="38">
         <v>1</v>
@@ -51575,7 +51556,7 @@
         <v>1273</v>
       </c>
       <c r="E1671" s="38" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="F1671" s="11" t="s">
         <v>100</v>
@@ -51584,15 +51565,15 @@
         <v>10</v>
       </c>
       <c r="H1671" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1671">
         <v>0</v>
       </c>
     </row>
-    <row r="1672" spans="1:9">
+    <row r="1672" ht="14.1" customHeight="1" spans="1:9">
       <c r="A1672" s="37">
-        <v>5101734</v>
+        <v>5101733</v>
       </c>
       <c r="B1672" s="38">
         <v>1</v>
@@ -51613,7 +51594,7 @@
         <v>10</v>
       </c>
       <c r="H1672" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1672">
         <v>0</v>
@@ -51621,7 +51602,7 @@
     </row>
     <row r="1673" spans="1:9">
       <c r="A1673" s="37">
-        <v>5101735</v>
+        <v>5101734</v>
       </c>
       <c r="B1673" s="38">
         <v>1</v>
@@ -51633,7 +51614,7 @@
         <v>1275</v>
       </c>
       <c r="E1673" s="38" t="s">
-        <v>1043</v>
+        <v>327</v>
       </c>
       <c r="F1673" s="11" t="s">
         <v>100</v>
@@ -51650,7 +51631,7 @@
     </row>
     <row r="1674" spans="1:9">
       <c r="A1674" s="37">
-        <v>5101736</v>
+        <v>5101735</v>
       </c>
       <c r="B1674" s="38">
         <v>1</v>
@@ -51662,7 +51643,7 @@
         <v>1276</v>
       </c>
       <c r="E1674" s="38" t="s">
-        <v>245</v>
+        <v>1043</v>
       </c>
       <c r="F1674" s="11" t="s">
         <v>100</v>
@@ -51671,7 +51652,7 @@
         <v>10</v>
       </c>
       <c r="H1674" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1674">
         <v>0</v>
@@ -51679,7 +51660,7 @@
     </row>
     <row r="1675" spans="1:9">
       <c r="A1675" s="37">
-        <v>5101737</v>
+        <v>5101736</v>
       </c>
       <c r="B1675" s="38">
         <v>1</v>
@@ -51691,7 +51672,7 @@
         <v>1277</v>
       </c>
       <c r="E1675" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1675" s="11" t="s">
         <v>100</v>
@@ -51700,7 +51681,7 @@
         <v>10</v>
       </c>
       <c r="H1675" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1675">
         <v>0</v>
@@ -51708,7 +51689,7 @@
     </row>
     <row r="1676" spans="1:9">
       <c r="A1676" s="37">
-        <v>51017381</v>
+        <v>5101737</v>
       </c>
       <c r="B1676" s="38">
         <v>1</v>
@@ -51720,7 +51701,7 @@
         <v>1278</v>
       </c>
       <c r="E1676" s="38" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="F1676" s="11" t="s">
         <v>100</v>
@@ -51729,7 +51710,7 @@
         <v>10</v>
       </c>
       <c r="H1676" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1676">
         <v>0</v>
@@ -51737,7 +51718,7 @@
     </row>
     <row r="1677" spans="1:9">
       <c r="A1677" s="37">
-        <v>51017382</v>
+        <v>51017381</v>
       </c>
       <c r="B1677" s="38">
         <v>1</v>
@@ -51749,7 +51730,7 @@
         <v>1279</v>
       </c>
       <c r="E1677" s="38" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1677" s="11" t="s">
         <v>100</v>
@@ -51758,7 +51739,7 @@
         <v>10</v>
       </c>
       <c r="H1677" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1677">
         <v>0</v>
@@ -51766,7 +51747,7 @@
     </row>
     <row r="1678" spans="1:9">
       <c r="A1678" s="37">
-        <v>51017383</v>
+        <v>51017382</v>
       </c>
       <c r="B1678" s="38">
         <v>1</v>
@@ -51778,7 +51759,7 @@
         <v>1280</v>
       </c>
       <c r="E1678" s="38" t="s">
-        <v>1043</v>
+        <v>327</v>
       </c>
       <c r="F1678" s="11" t="s">
         <v>100</v>
@@ -51795,7 +51776,7 @@
     </row>
     <row r="1679" spans="1:9">
       <c r="A1679" s="37">
-        <v>51017384</v>
+        <v>51017383</v>
       </c>
       <c r="B1679" s="38">
         <v>1</v>
@@ -51807,7 +51788,7 @@
         <v>1281</v>
       </c>
       <c r="E1679" s="38" t="s">
-        <v>245</v>
+        <v>1043</v>
       </c>
       <c r="F1679" s="11" t="s">
         <v>100</v>
@@ -51816,7 +51797,7 @@
         <v>10</v>
       </c>
       <c r="H1679" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1679">
         <v>0</v>
@@ -51824,7 +51805,7 @@
     </row>
     <row r="1680" spans="1:9">
       <c r="A1680" s="37">
-        <v>51017385</v>
+        <v>51017384</v>
       </c>
       <c r="B1680" s="38">
         <v>1</v>
@@ -51836,7 +51817,7 @@
         <v>1282</v>
       </c>
       <c r="E1680" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1680" s="11" t="s">
         <v>100</v>
@@ -51845,7 +51826,7 @@
         <v>10</v>
       </c>
       <c r="H1680" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1680">
         <v>0</v>
@@ -51853,7 +51834,7 @@
     </row>
     <row r="1681" spans="1:9">
       <c r="A1681" s="37">
-        <v>51017391</v>
+        <v>51017385</v>
       </c>
       <c r="B1681" s="38">
         <v>1</v>
@@ -51865,7 +51846,7 @@
         <v>1283</v>
       </c>
       <c r="E1681" s="38" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="F1681" s="11" t="s">
         <v>100</v>
@@ -51874,7 +51855,7 @@
         <v>10</v>
       </c>
       <c r="H1681" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1681">
         <v>0</v>
@@ -51882,7 +51863,7 @@
     </row>
     <row r="1682" spans="1:9">
       <c r="A1682" s="37">
-        <v>51017392</v>
+        <v>51017391</v>
       </c>
       <c r="B1682" s="38">
         <v>1</v>
@@ -51894,7 +51875,7 @@
         <v>1284</v>
       </c>
       <c r="E1682" s="38" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1682" s="11" t="s">
         <v>100</v>
@@ -51903,7 +51884,7 @@
         <v>10</v>
       </c>
       <c r="H1682" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1682">
         <v>0</v>
@@ -51911,7 +51892,7 @@
     </row>
     <row r="1683" spans="1:9">
       <c r="A1683" s="37">
-        <v>51017393</v>
+        <v>51017392</v>
       </c>
       <c r="B1683" s="38">
         <v>1</v>
@@ -51923,7 +51904,7 @@
         <v>1285</v>
       </c>
       <c r="E1683" s="38" t="s">
-        <v>1043</v>
+        <v>327</v>
       </c>
       <c r="F1683" s="11" t="s">
         <v>100</v>
@@ -51940,7 +51921,7 @@
     </row>
     <row r="1684" spans="1:9">
       <c r="A1684" s="37">
-        <v>51017394</v>
+        <v>51017393</v>
       </c>
       <c r="B1684" s="38">
         <v>1</v>
@@ -51952,7 +51933,7 @@
         <v>1286</v>
       </c>
       <c r="E1684" s="38" t="s">
-        <v>245</v>
+        <v>1043</v>
       </c>
       <c r="F1684" s="11" t="s">
         <v>100</v>
@@ -51961,7 +51942,7 @@
         <v>10</v>
       </c>
       <c r="H1684" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1684">
         <v>0</v>
@@ -51969,7 +51950,7 @@
     </row>
     <row r="1685" spans="1:9">
       <c r="A1685" s="37">
-        <v>51017395</v>
+        <v>51017394</v>
       </c>
       <c r="B1685" s="38">
         <v>1</v>
@@ -51981,7 +51962,7 @@
         <v>1287</v>
       </c>
       <c r="E1685" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1685" s="11" t="s">
         <v>100</v>
@@ -51990,7 +51971,7 @@
         <v>10</v>
       </c>
       <c r="H1685" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1685">
         <v>0</v>
@@ -51998,7 +51979,7 @@
     </row>
     <row r="1686" spans="1:9">
       <c r="A1686" s="37">
-        <v>51017401</v>
+        <v>51017395</v>
       </c>
       <c r="B1686" s="38">
         <v>1</v>
@@ -52010,7 +51991,7 @@
         <v>1288</v>
       </c>
       <c r="E1686" s="38" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="F1686" s="11" t="s">
         <v>100</v>
@@ -52019,7 +52000,7 @@
         <v>10</v>
       </c>
       <c r="H1686" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1686">
         <v>0</v>
@@ -52027,7 +52008,7 @@
     </row>
     <row r="1687" spans="1:9">
       <c r="A1687" s="37">
-        <v>51017402</v>
+        <v>51017401</v>
       </c>
       <c r="B1687" s="38">
         <v>1</v>
@@ -52039,7 +52020,7 @@
         <v>1289</v>
       </c>
       <c r="E1687" s="38" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1687" s="11" t="s">
         <v>100</v>
@@ -52048,7 +52029,7 @@
         <v>10</v>
       </c>
       <c r="H1687" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1687">
         <v>0</v>
@@ -52056,7 +52037,7 @@
     </row>
     <row r="1688" spans="1:9">
       <c r="A1688" s="37">
-        <v>51017403</v>
+        <v>51017402</v>
       </c>
       <c r="B1688" s="38">
         <v>1</v>
@@ -52068,7 +52049,7 @@
         <v>1290</v>
       </c>
       <c r="E1688" s="38" t="s">
-        <v>1043</v>
+        <v>327</v>
       </c>
       <c r="F1688" s="11" t="s">
         <v>100</v>
@@ -52085,7 +52066,7 @@
     </row>
     <row r="1689" spans="1:9">
       <c r="A1689" s="37">
-        <v>51017404</v>
+        <v>51017403</v>
       </c>
       <c r="B1689" s="38">
         <v>1</v>
@@ -52097,7 +52078,7 @@
         <v>1291</v>
       </c>
       <c r="E1689" s="38" t="s">
-        <v>245</v>
+        <v>1043</v>
       </c>
       <c r="F1689" s="11" t="s">
         <v>100</v>
@@ -52106,7 +52087,7 @@
         <v>10</v>
       </c>
       <c r="H1689" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1689">
         <v>0</v>
@@ -52114,7 +52095,7 @@
     </row>
     <row r="1690" spans="1:9">
       <c r="A1690" s="37">
-        <v>51017405</v>
+        <v>51017404</v>
       </c>
       <c r="B1690" s="38">
         <v>1</v>
@@ -52126,7 +52107,7 @@
         <v>1292</v>
       </c>
       <c r="E1690" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F1690" s="11" t="s">
         <v>100</v>
@@ -52135,7 +52116,7 @@
         <v>10</v>
       </c>
       <c r="H1690" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1690">
         <v>0</v>
@@ -52143,7 +52124,7 @@
     </row>
     <row r="1691" spans="1:9">
       <c r="A1691" s="37">
-        <v>51017411</v>
+        <v>51017405</v>
       </c>
       <c r="B1691" s="38">
         <v>1</v>
@@ -52155,7 +52136,7 @@
         <v>1293</v>
       </c>
       <c r="E1691" s="38" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="F1691" s="11" t="s">
         <v>100</v>
@@ -52164,7 +52145,7 @@
         <v>10</v>
       </c>
       <c r="H1691" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1691">
         <v>0</v>
@@ -52172,7 +52153,7 @@
     </row>
     <row r="1692" spans="1:9">
       <c r="A1692" s="37">
-        <v>51017412</v>
+        <v>51017411</v>
       </c>
       <c r="B1692" s="38">
         <v>1</v>
@@ -52184,7 +52165,7 @@
         <v>1294</v>
       </c>
       <c r="E1692" s="38" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F1692" s="11" t="s">
         <v>100</v>
@@ -52193,7 +52174,7 @@
         <v>10</v>
       </c>
       <c r="H1692" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1692">
         <v>0</v>
@@ -52201,7 +52182,7 @@
     </row>
     <row r="1693" spans="1:9">
       <c r="A1693" s="37">
-        <v>51017413</v>
+        <v>51017412</v>
       </c>
       <c r="B1693" s="38">
         <v>1</v>
@@ -52213,7 +52194,7 @@
         <v>1295</v>
       </c>
       <c r="E1693" s="38" t="s">
-        <v>1043</v>
+        <v>327</v>
       </c>
       <c r="F1693" s="11" t="s">
         <v>100</v>
@@ -52230,7 +52211,7 @@
     </row>
     <row r="1694" spans="1:9">
       <c r="A1694" s="37">
-        <v>51017414</v>
+        <v>51017413</v>
       </c>
       <c r="B1694" s="38">
         <v>1</v>
@@ -52242,7 +52223,7 @@
         <v>1296</v>
       </c>
       <c r="E1694" s="38" t="s">
-        <v>245</v>
+        <v>1043</v>
       </c>
       <c r="F1694" s="11" t="s">
         <v>100</v>
@@ -52251,7 +52232,7 @@
         <v>10</v>
       </c>
       <c r="H1694" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1694">
         <v>0</v>
@@ -52259,7 +52240,7 @@
     </row>
     <row r="1695" spans="1:9">
       <c r="A1695" s="37">
-        <v>51017415</v>
+        <v>51017414</v>
       </c>
       <c r="B1695" s="38">
         <v>1</v>
@@ -52271,18 +52252,47 @@
         <v>1297</v>
       </c>
       <c r="E1695" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1695" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1695" s="38">
+        <v>10</v>
+      </c>
+      <c r="H1695" s="38">
+        <v>2</v>
+      </c>
+      <c r="I1695">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:9">
+      <c r="A1696" s="37">
+        <v>51017415</v>
+      </c>
+      <c r="B1696" s="38">
+        <v>1</v>
+      </c>
+      <c r="C1696" s="38">
+        <v>0</v>
+      </c>
+      <c r="D1696" s="39" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E1696" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="F1695" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1695" s="38">
-        <v>10</v>
-      </c>
-      <c r="H1695" s="38">
-        <v>1</v>
-      </c>
-      <c r="I1695">
+      <c r="F1696" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1696" s="38">
+        <v>10</v>
+      </c>
+      <c r="H1696" s="38">
+        <v>1</v>
+      </c>
+      <c r="I1696">
         <v>0</v>
       </c>
     </row>
@@ -52348,7 +52358,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -52360,10 +52370,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -52377,90 +52387,90 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1315</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1316</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1317</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1318</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1319</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1320</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1321</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1322</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1323</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -52471,7 +52481,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -52492,7 +52502,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="51" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -52504,7 +52514,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -52515,7 +52525,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -52556,7 +52566,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -52597,7 +52607,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -52618,7 +52628,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="51" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -52630,7 +52640,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -52641,7 +52651,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -52662,7 +52672,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="51" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -52674,7 +52684,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -52685,7 +52695,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -52706,7 +52716,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="51" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -40600,7 +40600,7 @@
         <v>2</v>
       </c>
       <c r="I1256">
-        <v>9000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1257" spans="1:9">
@@ -40652,7 +40652,7 @@
         <v>2</v>
       </c>
       <c r="I1258">
-        <v>9000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1259" spans="1:9">
@@ -41102,7 +41102,7 @@
         <v>2</v>
       </c>
       <c r="I1275">
-        <v>18000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1276" spans="1:9">
@@ -41154,7 +41154,7 @@
         <v>2</v>
       </c>
       <c r="I1277">
-        <v>18000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="1278" spans="1:9">
@@ -42689,7 +42689,7 @@
         <v>1</v>
       </c>
       <c r="I1335">
-        <v>2500</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="1336" spans="1:9">
@@ -42716,7 +42716,7 @@
         <v>1</v>
       </c>
       <c r="I1336">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1337" spans="1:9">
@@ -42743,7 +42743,7 @@
         <v>2</v>
       </c>
       <c r="I1337">
-        <v>14000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="1338" spans="1:9">
@@ -46573,7 +46573,7 @@
         <v>2</v>
       </c>
       <c r="I1482">
-        <v>18000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1483" spans="1:9">
@@ -46625,7 +46625,7 @@
         <v>2</v>
       </c>
       <c r="I1484">
-        <v>18000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1485" spans="1:9">
@@ -47878,7 +47878,7 @@
         <v>2</v>
       </c>
       <c r="I1532">
-        <v>16000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1533" spans="1:9">
@@ -47930,7 +47930,7 @@
         <v>2</v>
       </c>
       <c r="I1534">
-        <v>16000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1535" spans="1:9">
@@ -49447,7 +49447,7 @@
         <v>1</v>
       </c>
       <c r="I1591">
-        <v>2200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1592" spans="1:9">
@@ -50701,7 +50701,7 @@
         <v>1</v>
       </c>
       <c r="I1639">
-        <v>1800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1640" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -4209,14 +4209,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4482,7 +4475,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4575,12 +4568,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -4600,12 +4587,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4861,13 +4842,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4876,55 +4860,58 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4933,10 +4920,10 @@
     <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4945,10 +4932,10 @@
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4957,10 +4944,10 @@
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4969,10 +4956,10 @@
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4981,19 +4968,13 @@
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5001,27 +4982,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5029,107 +5022,95 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="16" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="16" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="16" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="16" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="24" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="8" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -42523,7 +42504,7 @@
         <v>1</v>
       </c>
       <c r="I1327">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1328" spans="1:9">
@@ -44759,7 +44740,6 @@
       <c r="E1412" s="42" t="s">
         <v>846</v>
       </c>
-      <c r="F1412"/>
       <c r="G1412">
         <v>10</v>
       </c>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -40084,7 +40084,7 @@
         <v>1</v>
       </c>
       <c r="I1235">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1236" spans="1:9">
@@ -40136,7 +40136,7 @@
         <v>2</v>
       </c>
       <c r="I1237">
-        <v>18000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1238" spans="1:9">
@@ -40188,7 +40188,7 @@
         <v>2</v>
       </c>
       <c r="I1239">
-        <v>18000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1240" spans="1:9">
@@ -40371,7 +40371,7 @@
         <v>1</v>
       </c>
       <c r="I1246">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1247" spans="1:9">
@@ -40397,7 +40397,7 @@
         <v>1</v>
       </c>
       <c r="I1247">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1248" spans="1:9">
@@ -40449,7 +40449,7 @@
         <v>2</v>
       </c>
       <c r="I1249">
-        <v>20000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="1250" spans="1:9">
@@ -40501,7 +40501,7 @@
         <v>2</v>
       </c>
       <c r="I1251">
-        <v>20000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="1252" spans="1:9">
@@ -40683,7 +40683,7 @@
         <v>1</v>
       </c>
       <c r="I1258">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1259" spans="1:9">
@@ -42556,7 +42556,7 @@
         <v>2</v>
       </c>
       <c r="I1329">
-        <v>8000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1330" spans="1:9">
@@ -42608,7 +42608,7 @@
         <v>2</v>
       </c>
       <c r="I1331">
-        <v>8000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="1332" spans="1:9">
@@ -42635,7 +42635,7 @@
         <v>1</v>
       </c>
       <c r="I1332">
-        <v>2500</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="1333" spans="1:9">
@@ -42662,7 +42662,7 @@
         <v>1</v>
       </c>
       <c r="I1333">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1334" spans="1:9">
@@ -42824,7 +42824,7 @@
         <v>1</v>
       </c>
       <c r="I1339">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1340" spans="1:9">
@@ -42851,7 +42851,7 @@
         <v>1</v>
       </c>
       <c r="I1340">
-        <v>2700</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="1341" spans="1:9">
@@ -42905,7 +42905,7 @@
         <v>2</v>
       </c>
       <c r="I1342">
-        <v>12000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="1343" spans="1:9">
@@ -43512,7 +43512,7 @@
         <v>1</v>
       </c>
       <c r="I1365">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1366" spans="1:9">
@@ -43538,7 +43538,7 @@
         <v>1</v>
       </c>
       <c r="I1366">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1367" spans="1:9">
@@ -43590,7 +43590,7 @@
         <v>2</v>
       </c>
       <c r="I1368">
-        <v>15000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="1369" spans="1:9">
@@ -43642,7 +43642,7 @@
         <v>2</v>
       </c>
       <c r="I1370">
-        <v>15000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="1371" spans="1:9">
@@ -44328,7 +44328,7 @@
         <v>2</v>
       </c>
       <c r="I1396">
-        <v>10000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1397" spans="1:9">
@@ -44355,7 +44355,7 @@
         <v>2</v>
       </c>
       <c r="I1397">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1398" spans="1:9">
@@ -44382,7 +44382,7 @@
         <v>2</v>
       </c>
       <c r="I1398">
-        <v>10000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1399" spans="1:9">
@@ -45693,7 +45693,7 @@
         <v>1</v>
       </c>
       <c r="I1447">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1448" spans="1:9">
@@ -45719,7 +45719,7 @@
         <v>1</v>
       </c>
       <c r="I1448">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1449" spans="1:9">
@@ -45771,7 +45771,7 @@
         <v>2</v>
       </c>
       <c r="I1450">
-        <v>16000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1451" spans="1:9">
@@ -45823,7 +45823,7 @@
         <v>2</v>
       </c>
       <c r="I1452">
-        <v>16000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1453" spans="1:9">
@@ -46057,7 +46057,7 @@
         <v>1</v>
       </c>
       <c r="I1461">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1462" spans="1:9">
@@ -46109,7 +46109,7 @@
         <v>2</v>
       </c>
       <c r="I1463">
-        <v>7000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1464" spans="1:9">
@@ -46161,7 +46161,7 @@
         <v>2</v>
       </c>
       <c r="I1465">
-        <v>7000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1466" spans="1:9">
@@ -46187,7 +46187,7 @@
         <v>1</v>
       </c>
       <c r="I1466">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1467" spans="1:9">
@@ -47415,7 +47415,7 @@
         <v>1</v>
       </c>
       <c r="I1513">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1514" spans="1:9">
@@ -47989,7 +47989,7 @@
         <v>1</v>
       </c>
       <c r="I1535">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1536" spans="1:9">
@@ -48015,7 +48015,7 @@
         <v>1</v>
       </c>
       <c r="I1536">
-        <v>3500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1537" spans="1:9">
@@ -48041,7 +48041,7 @@
         <v>1</v>
       </c>
       <c r="I1537">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1538" spans="1:9">
@@ -48171,7 +48171,7 @@
         <v>1</v>
       </c>
       <c r="I1542">
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1543" spans="1:9">
@@ -48379,7 +48379,7 @@
         <v>1</v>
       </c>
       <c r="I1550">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1551" spans="1:9">
@@ -48431,7 +48431,7 @@
         <v>2</v>
       </c>
       <c r="I1552">
-        <v>20000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="1553" spans="1:9">
@@ -48483,7 +48483,7 @@
         <v>2</v>
       </c>
       <c r="I1554">
-        <v>20000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="1555" spans="1:9">
@@ -49010,7 +49010,7 @@
         <v>1</v>
       </c>
       <c r="I1573">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1574" spans="1:9">
@@ -49062,7 +49062,7 @@
         <v>2</v>
       </c>
       <c r="I1575">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1576" spans="1:9">
@@ -49114,7 +49114,7 @@
         <v>2</v>
       </c>
       <c r="I1577">
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1578" spans="1:9">
@@ -49140,7 +49140,7 @@
         <v>1</v>
       </c>
       <c r="I1578">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1579" spans="1:9">
@@ -49427,7 +49427,7 @@
         <v>1</v>
       </c>
       <c r="I1589">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1590" spans="1:9">
@@ -49479,7 +49479,7 @@
         <v>2</v>
       </c>
       <c r="I1591">
-        <v>14000</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="1592" spans="1:9">
@@ -49531,7 +49531,7 @@
         <v>2</v>
       </c>
       <c r="I1593">
-        <v>14000</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="1594" spans="1:9">
@@ -49557,7 +49557,7 @@
         <v>1</v>
       </c>
       <c r="I1594">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1595" spans="1:9">
@@ -49845,7 +49845,7 @@
         <v>1</v>
       </c>
       <c r="I1605">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1606" spans="1:9">
@@ -49897,7 +49897,7 @@
         <v>2</v>
       </c>
       <c r="I1607">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1608" spans="1:9">
@@ -49949,7 +49949,7 @@
         <v>2</v>
       </c>
       <c r="I1609">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1610" spans="1:9">
@@ -49975,7 +49975,7 @@
         <v>1</v>
       </c>
       <c r="I1610">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1611" spans="1:9">
@@ -50001,7 +50001,7 @@
         <v>1</v>
       </c>
       <c r="I1611">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1612" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AD70C1-4BDB-40E1-9BF3-D048D565BFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA7F8CE-EA2D-4E54-94F3-CFA8B2C3C010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -44781,7 +44781,7 @@
         <v>1</v>
       </c>
       <c r="I1432">
-        <v>5000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1433" spans="1:9" x14ac:dyDescent="0.15">
@@ -44807,7 +44807,7 @@
         <v>1</v>
       </c>
       <c r="I1433">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1434" spans="1:9" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA7F8CE-EA2D-4E54-94F3-CFA8B2C3C010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0308B84C-C7B6-4077-91B4-55F5D0FFA3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -44781,7 +44781,7 @@
         <v>1</v>
       </c>
       <c r="I1432">
-        <v>2500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1433" spans="1:9" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0308B84C-C7B6-4077-91B4-55F5D0FFA3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3CEF2E-0E21-41CB-9BC1-F215C6C2CAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_attribute_v8" sheetId="1" r:id="rId1"/>
@@ -3301,6 +3301,12 @@
     <t>maze_barires_drop_condition_v8，调整条件逻辑id=2，调整值=原值*（10000+属性890022）/10000向上取整</t>
   </si>
   <si>
+    <t>血瓶使用CD（毫秒）</t>
+  </si>
+  <si>
+    <t>血瓶上限</t>
+  </si>
+  <si>
     <t>陨石-燃烧伤害系数万分比</t>
   </si>
   <si>
@@ -4208,14 +4214,6 @@
   </si>
   <si>
     <t>3030401,3030502,3030603,3030704,3030805</t>
-  </si>
-  <si>
-    <t>血瓶使用CD（毫秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>血瓶上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4400,7 +4398,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7993713187047945"/>
+        <fgColor theme="9" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4436,7 +4434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7993713187047945"/>
+        <fgColor theme="4" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -39908,7 +39906,7 @@
         <v>1</v>
       </c>
       <c r="I1247">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1248" spans="1:9" x14ac:dyDescent="0.15">
@@ -40090,7 +40088,7 @@
         <v>1</v>
       </c>
       <c r="I1254">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1255" spans="1:9" x14ac:dyDescent="0.15">
@@ -40696,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="I1277">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1278" spans="1:9" x14ac:dyDescent="0.15">
@@ -41063,7 +41061,7 @@
         <v>1</v>
       </c>
       <c r="I1291">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1292" spans="1:9" x14ac:dyDescent="0.15">
@@ -41404,7 +41402,7 @@
         <v>1</v>
       </c>
       <c r="I1304">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1305" spans="1:9" x14ac:dyDescent="0.15">
@@ -41911,7 +41909,7 @@
         <v>1</v>
       </c>
       <c r="I1323">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1324" spans="1:9" x14ac:dyDescent="0.15">
@@ -42015,7 +42013,7 @@
         <v>1</v>
       </c>
       <c r="I1327">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1328" spans="1:9" x14ac:dyDescent="0.15">
@@ -43388,7 +43386,7 @@
         <v>1</v>
       </c>
       <c r="I1379">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1380" spans="1:9" x14ac:dyDescent="0.15">
@@ -44102,7 +44100,7 @@
         <v>1</v>
       </c>
       <c r="I1406">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1407" spans="1:9" x14ac:dyDescent="0.15">
@@ -44769,10 +44767,10 @@
         <v>0</v>
       </c>
       <c r="D1432" s="41" t="s">
-        <v>1348</v>
+        <v>1045</v>
       </c>
       <c r="E1432" s="41" t="s">
-        <v>1348</v>
+        <v>1045</v>
       </c>
       <c r="G1432">
         <v>10</v>
@@ -44781,7 +44779,7 @@
         <v>1</v>
       </c>
       <c r="I1432">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1433" spans="1:9" x14ac:dyDescent="0.15">
@@ -44795,10 +44793,10 @@
         <v>0</v>
       </c>
       <c r="D1433" s="41" t="s">
-        <v>1349</v>
+        <v>1046</v>
       </c>
       <c r="E1433" s="41" t="s">
-        <v>1349</v>
+        <v>1046</v>
       </c>
       <c r="G1433">
         <v>10</v>
@@ -44850,7 +44848,7 @@
         <v>0</v>
       </c>
       <c r="D1435" s="39" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E1435" s="38" t="s">
         <v>245</v>
@@ -44879,7 +44877,7 @@
         <v>0</v>
       </c>
       <c r="D1436" s="39" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="E1436" s="38" t="s">
         <v>253</v>
@@ -44908,7 +44906,7 @@
         <v>0</v>
       </c>
       <c r="D1437" s="39" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="E1437" s="38" t="s">
         <v>327</v>
@@ -44937,7 +44935,7 @@
         <v>0</v>
       </c>
       <c r="D1438" s="39" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="E1438" s="38" t="s">
         <v>329</v>
@@ -44966,10 +44964,10 @@
         <v>0</v>
       </c>
       <c r="D1439" s="39" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E1439" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1439" s="11" t="s">
         <v>100</v>
@@ -44995,7 +44993,7 @@
         <v>0</v>
       </c>
       <c r="D1440" s="39" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E1440" s="38" t="s">
         <v>245</v>
@@ -45024,7 +45022,7 @@
         <v>0</v>
       </c>
       <c r="D1441" s="39" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="E1441" s="38" t="s">
         <v>253</v>
@@ -45053,7 +45051,7 @@
         <v>0</v>
       </c>
       <c r="D1442" s="39" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="E1442" s="38" t="s">
         <v>327</v>
@@ -45082,7 +45080,7 @@
         <v>0</v>
       </c>
       <c r="D1443" s="39" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E1443" s="38" t="s">
         <v>329</v>
@@ -45111,10 +45109,10 @@
         <v>0</v>
       </c>
       <c r="D1444" s="39" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="E1444" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1444" s="11" t="s">
         <v>100</v>
@@ -45178,7 +45176,7 @@
         <v>1</v>
       </c>
       <c r="I1446">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1447" spans="1:9" x14ac:dyDescent="0.15">
@@ -45282,7 +45280,7 @@
         <v>1</v>
       </c>
       <c r="I1450">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1451" spans="1:9" x14ac:dyDescent="0.15">
@@ -45400,7 +45398,7 @@
         <v>0</v>
       </c>
       <c r="D1455" s="41" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="E1455" s="42" t="s">
         <v>846</v>
@@ -45426,7 +45424,7 @@
         <v>0</v>
       </c>
       <c r="D1456" s="41" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E1456" s="42" t="s">
         <v>846</v>
@@ -45452,7 +45450,7 @@
         <v>0</v>
       </c>
       <c r="D1457" s="41" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="E1457" s="42" t="s">
         <v>846</v>
@@ -45478,7 +45476,7 @@
         <v>0</v>
       </c>
       <c r="D1458" s="41" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E1458" s="42" t="s">
         <v>844</v>
@@ -45504,7 +45502,7 @@
         <v>0</v>
       </c>
       <c r="D1459" s="41" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E1459" s="42" t="s">
         <v>846</v>
@@ -45530,7 +45528,7 @@
         <v>0</v>
       </c>
       <c r="D1460" s="41" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="E1460" s="42" t="s">
         <v>846</v>
@@ -45556,7 +45554,7 @@
         <v>0</v>
       </c>
       <c r="D1461" s="41" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E1461" s="42" t="s">
         <v>846</v>
@@ -45582,7 +45580,7 @@
         <v>0</v>
       </c>
       <c r="D1462" s="41" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E1462" s="42" t="s">
         <v>846</v>
@@ -45608,7 +45606,7 @@
         <v>0</v>
       </c>
       <c r="D1463" s="41" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E1463" s="42" t="s">
         <v>846</v>
@@ -45620,7 +45618,7 @@
         <v>1</v>
       </c>
       <c r="I1463">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1464" spans="1:9" x14ac:dyDescent="0.15">
@@ -45634,7 +45632,7 @@
         <v>0</v>
       </c>
       <c r="D1464" s="41" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="E1464" s="42" t="s">
         <v>846</v>
@@ -45660,7 +45658,7 @@
         <v>0</v>
       </c>
       <c r="D1465" s="41" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="E1465" s="42" t="s">
         <v>846</v>
@@ -45686,7 +45684,7 @@
         <v>0</v>
       </c>
       <c r="D1466" s="41" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="E1466" s="42" t="s">
         <v>846</v>
@@ -45712,7 +45710,7 @@
         <v>0</v>
       </c>
       <c r="D1467" s="41" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="E1467" s="42" t="s">
         <v>846</v>
@@ -45738,7 +45736,7 @@
         <v>0</v>
       </c>
       <c r="D1468" s="41" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="E1468" s="42" t="s">
         <v>846</v>
@@ -45764,7 +45762,7 @@
         <v>0</v>
       </c>
       <c r="D1469" s="41" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E1469" s="42" t="s">
         <v>846</v>
@@ -45790,7 +45788,7 @@
         <v>0</v>
       </c>
       <c r="D1470" s="41" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="E1470" s="42" t="s">
         <v>846</v>
@@ -45816,7 +45814,7 @@
         <v>0</v>
       </c>
       <c r="D1471" s="41" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="E1471" s="42" t="s">
         <v>844</v>
@@ -45842,7 +45840,7 @@
         <v>0</v>
       </c>
       <c r="D1472" s="41" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="E1472" s="42" t="s">
         <v>846</v>
@@ -45868,7 +45866,7 @@
         <v>0</v>
       </c>
       <c r="D1473" s="41" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="E1473" s="42" t="s">
         <v>846</v>
@@ -45894,7 +45892,7 @@
         <v>0</v>
       </c>
       <c r="D1474" s="41" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E1474" s="42" t="s">
         <v>846</v>
@@ -45920,7 +45918,7 @@
         <v>0</v>
       </c>
       <c r="D1475" s="41" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="E1475" s="42" t="s">
         <v>846</v>
@@ -45946,7 +45944,7 @@
         <v>0</v>
       </c>
       <c r="D1476" s="41" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="E1476" s="42" t="s">
         <v>846</v>
@@ -45958,7 +45956,7 @@
         <v>1</v>
       </c>
       <c r="I1476">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1477" spans="1:9" x14ac:dyDescent="0.15">
@@ -45972,7 +45970,7 @@
         <v>0</v>
       </c>
       <c r="D1477" s="41" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="E1477" s="42" t="s">
         <v>846</v>
@@ -45998,7 +45996,7 @@
         <v>0</v>
       </c>
       <c r="D1478" s="41" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="E1478" s="42" t="s">
         <v>846</v>
@@ -46024,7 +46022,7 @@
         <v>0</v>
       </c>
       <c r="D1479" s="41" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="E1479" s="42" t="s">
         <v>846</v>
@@ -46050,7 +46048,7 @@
         <v>0</v>
       </c>
       <c r="D1480" s="41" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="E1480" s="42" t="s">
         <v>846</v>
@@ -46076,7 +46074,7 @@
         <v>0</v>
       </c>
       <c r="D1481" s="41" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="E1481" s="42" t="s">
         <v>846</v>
@@ -46103,7 +46101,7 @@
         <v>0</v>
       </c>
       <c r="D1482" s="41" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="E1482" s="42" t="s">
         <v>846</v>
@@ -46130,7 +46128,7 @@
         <v>0</v>
       </c>
       <c r="D1483" s="41" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="E1483" s="42" t="s">
         <v>846</v>
@@ -46157,7 +46155,7 @@
         <v>0</v>
       </c>
       <c r="D1484" s="41" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="E1484" s="42" t="s">
         <v>844</v>
@@ -46183,7 +46181,7 @@
         <v>0</v>
       </c>
       <c r="D1485" s="41" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="E1485" s="42" t="s">
         <v>846</v>
@@ -46209,7 +46207,7 @@
         <v>0</v>
       </c>
       <c r="D1486" s="41" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="E1486" s="42" t="s">
         <v>846</v>
@@ -46235,7 +46233,7 @@
         <v>0</v>
       </c>
       <c r="D1487" s="41" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="E1487" s="42" t="s">
         <v>846</v>
@@ -46261,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="D1488" s="41" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="E1488" s="42" t="s">
         <v>846</v>
@@ -46287,7 +46285,7 @@
         <v>0</v>
       </c>
       <c r="D1489" s="41" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="E1489" s="42" t="s">
         <v>846</v>
@@ -46299,7 +46297,7 @@
         <v>1</v>
       </c>
       <c r="I1489">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1490" spans="1:9" x14ac:dyDescent="0.15">
@@ -46313,7 +46311,7 @@
         <v>0</v>
       </c>
       <c r="D1490" s="41" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="E1490" s="42" t="s">
         <v>846</v>
@@ -46339,7 +46337,7 @@
         <v>0</v>
       </c>
       <c r="D1491" s="41" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="E1491" s="42" t="s">
         <v>846</v>
@@ -46365,7 +46363,7 @@
         <v>0</v>
       </c>
       <c r="D1492" s="41" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="E1492" s="42" t="s">
         <v>846</v>
@@ -46391,7 +46389,7 @@
         <v>0</v>
       </c>
       <c r="D1493" s="41" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E1493" s="42" t="s">
         <v>846</v>
@@ -46417,7 +46415,7 @@
         <v>0</v>
       </c>
       <c r="D1494" s="41" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="E1494" s="42" t="s">
         <v>846</v>
@@ -46444,7 +46442,7 @@
         <v>0</v>
       </c>
       <c r="D1495" s="41" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="E1495" s="42" t="s">
         <v>846</v>
@@ -46471,7 +46469,7 @@
         <v>0</v>
       </c>
       <c r="D1496" s="41" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="E1496" s="42" t="s">
         <v>846</v>
@@ -46498,7 +46496,7 @@
         <v>0</v>
       </c>
       <c r="D1497" s="41" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="E1497" s="42" t="s">
         <v>844</v>
@@ -46524,7 +46522,7 @@
         <v>0</v>
       </c>
       <c r="D1498" s="41" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="E1498" s="42" t="s">
         <v>846</v>
@@ -46550,7 +46548,7 @@
         <v>0</v>
       </c>
       <c r="D1499" s="41" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="E1499" s="42" t="s">
         <v>846</v>
@@ -46576,7 +46574,7 @@
         <v>0</v>
       </c>
       <c r="D1500" s="41" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E1500" s="42" t="s">
         <v>846</v>
@@ -46602,7 +46600,7 @@
         <v>0</v>
       </c>
       <c r="D1501" s="41" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="E1501" s="42" t="s">
         <v>846</v>
@@ -46628,7 +46626,7 @@
         <v>0</v>
       </c>
       <c r="D1502" s="41" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E1502" s="42" t="s">
         <v>846</v>
@@ -46640,7 +46638,7 @@
         <v>1</v>
       </c>
       <c r="I1502">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1503" spans="1:9" x14ac:dyDescent="0.15">
@@ -46654,7 +46652,7 @@
         <v>0</v>
       </c>
       <c r="D1503" s="41" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="E1503" s="42" t="s">
         <v>846</v>
@@ -46680,7 +46678,7 @@
         <v>0</v>
       </c>
       <c r="D1504" s="41" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="E1504" s="42" t="s">
         <v>846</v>
@@ -46706,7 +46704,7 @@
         <v>0</v>
       </c>
       <c r="D1505" s="41" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="E1505" s="42" t="s">
         <v>846</v>
@@ -46732,7 +46730,7 @@
         <v>0</v>
       </c>
       <c r="D1506" s="41" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E1506" s="42" t="s">
         <v>846</v>
@@ -46758,7 +46756,7 @@
         <v>0</v>
       </c>
       <c r="D1507" s="41" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="E1507" s="42" t="s">
         <v>846</v>
@@ -46784,7 +46782,7 @@
         <v>0</v>
       </c>
       <c r="D1508" s="41" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="E1508" s="42" t="s">
         <v>846</v>
@@ -46810,7 +46808,7 @@
         <v>0</v>
       </c>
       <c r="D1509" s="41" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E1509" s="42" t="s">
         <v>846</v>
@@ -46836,7 +46834,7 @@
         <v>0</v>
       </c>
       <c r="D1510" s="41" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="E1510" s="42" t="s">
         <v>844</v>
@@ -46862,7 +46860,7 @@
         <v>0</v>
       </c>
       <c r="D1511" s="41" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="E1511" s="42" t="s">
         <v>846</v>
@@ -46888,7 +46886,7 @@
         <v>0</v>
       </c>
       <c r="D1512" s="41" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="E1512" s="42" t="s">
         <v>846</v>
@@ -46914,7 +46912,7 @@
         <v>0</v>
       </c>
       <c r="D1513" s="41" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="E1513" s="42" t="s">
         <v>846</v>
@@ -46940,7 +46938,7 @@
         <v>0</v>
       </c>
       <c r="D1514" s="41" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="E1514" s="42" t="s">
         <v>846</v>
@@ -46966,7 +46964,7 @@
         <v>0</v>
       </c>
       <c r="D1515" s="41" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E1515" s="42" t="s">
         <v>846</v>
@@ -46978,7 +46976,7 @@
         <v>1</v>
       </c>
       <c r="I1515">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1516" spans="1:9" x14ac:dyDescent="0.15">
@@ -46992,7 +46990,7 @@
         <v>0</v>
       </c>
       <c r="D1516" s="41" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="E1516" s="42" t="s">
         <v>846</v>
@@ -47018,7 +47016,7 @@
         <v>0</v>
       </c>
       <c r="D1517" s="41" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="E1517" s="42" t="s">
         <v>846</v>
@@ -47044,7 +47042,7 @@
         <v>0</v>
       </c>
       <c r="D1518" s="41" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E1518" s="42" t="s">
         <v>846</v>
@@ -47070,7 +47068,7 @@
         <v>0</v>
       </c>
       <c r="D1519" s="41" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E1519" s="42" t="s">
         <v>846</v>
@@ -47096,7 +47094,7 @@
         <v>0</v>
       </c>
       <c r="D1520" s="41" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="E1520" s="42" t="s">
         <v>846</v>
@@ -47122,7 +47120,7 @@
         <v>0</v>
       </c>
       <c r="D1521" s="41" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="E1521" s="42" t="s">
         <v>846</v>
@@ -47149,7 +47147,7 @@
         <v>0</v>
       </c>
       <c r="D1522" s="41" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="E1522" s="42" t="s">
         <v>844</v>
@@ -47176,10 +47174,10 @@
         <v>0</v>
       </c>
       <c r="D1523" s="44" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="E1523" s="44" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="G1523">
         <v>10</v>
@@ -47202,7 +47200,7 @@
         <v>0</v>
       </c>
       <c r="D1524" s="41" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="E1524" s="42" t="s">
         <v>844</v>
@@ -47228,7 +47226,7 @@
         <v>0</v>
       </c>
       <c r="D1525" s="41" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E1525" s="42" t="s">
         <v>846</v>
@@ -47254,7 +47252,7 @@
         <v>0</v>
       </c>
       <c r="D1526" s="41" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E1526" s="42" t="s">
         <v>846</v>
@@ -47280,7 +47278,7 @@
         <v>0</v>
       </c>
       <c r="D1527" s="41" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E1527" s="42" t="s">
         <v>846</v>
@@ -47306,7 +47304,7 @@
         <v>0</v>
       </c>
       <c r="D1528" s="41" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="E1528" s="42" t="s">
         <v>846</v>
@@ -47332,7 +47330,7 @@
         <v>0</v>
       </c>
       <c r="D1529" s="41" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E1529" s="42" t="s">
         <v>846</v>
@@ -47344,7 +47342,7 @@
         <v>1</v>
       </c>
       <c r="I1529">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1530" spans="1:9" x14ac:dyDescent="0.15">
@@ -47358,7 +47356,7 @@
         <v>0</v>
       </c>
       <c r="D1530" s="41" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="E1530" s="42" t="s">
         <v>846</v>
@@ -47384,7 +47382,7 @@
         <v>0</v>
       </c>
       <c r="D1531" s="41" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E1531" s="42" t="s">
         <v>846</v>
@@ -47410,7 +47408,7 @@
         <v>0</v>
       </c>
       <c r="D1532" s="41" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="E1532" s="42" t="s">
         <v>846</v>
@@ -47436,7 +47434,7 @@
         <v>0</v>
       </c>
       <c r="D1533" s="41" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="E1533" s="42" t="s">
         <v>846</v>
@@ -47462,7 +47460,7 @@
         <v>0</v>
       </c>
       <c r="D1534" s="41" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E1534" s="42" t="s">
         <v>844</v>
@@ -47488,7 +47486,7 @@
         <v>0</v>
       </c>
       <c r="D1535" s="41" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="E1535" s="42" t="s">
         <v>846</v>
@@ -47500,7 +47498,7 @@
         <v>1</v>
       </c>
       <c r="I1535">
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="1536" spans="1:9" x14ac:dyDescent="0.15">
@@ -47514,7 +47512,7 @@
         <v>0</v>
       </c>
       <c r="D1536" s="41" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="E1536" s="42" t="s">
         <v>846</v>
@@ -47540,7 +47538,7 @@
         <v>0</v>
       </c>
       <c r="D1537" s="41" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E1537" s="42" t="s">
         <v>846</v>
@@ -47566,7 +47564,7 @@
         <v>0</v>
       </c>
       <c r="D1538" s="41" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="E1538" s="42" t="s">
         <v>846</v>
@@ -47592,7 +47590,7 @@
         <v>0</v>
       </c>
       <c r="D1539" s="41" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E1539" s="42" t="s">
         <v>846</v>
@@ -47604,7 +47602,7 @@
         <v>1</v>
       </c>
       <c r="I1539">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1540" spans="1:9" x14ac:dyDescent="0.15">
@@ -47618,7 +47616,7 @@
         <v>0</v>
       </c>
       <c r="D1540" s="41" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="E1540" s="42" t="s">
         <v>846</v>
@@ -47644,7 +47642,7 @@
         <v>0</v>
       </c>
       <c r="D1541" s="41" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E1541" s="42" t="s">
         <v>846</v>
@@ -47670,7 +47668,7 @@
         <v>0</v>
       </c>
       <c r="D1542" s="41" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="E1542" s="42" t="s">
         <v>846</v>
@@ -47696,7 +47694,7 @@
         <v>0</v>
       </c>
       <c r="D1543" s="41" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E1543" s="42" t="s">
         <v>846</v>
@@ -47722,7 +47720,7 @@
         <v>0</v>
       </c>
       <c r="D1544" s="41" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="E1544" s="42" t="s">
         <v>846</v>
@@ -47748,7 +47746,7 @@
         <v>0</v>
       </c>
       <c r="D1545" s="41" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="E1545" s="42" t="s">
         <v>846</v>
@@ -47774,7 +47772,7 @@
         <v>0</v>
       </c>
       <c r="D1546" s="41" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="E1546" s="42" t="s">
         <v>846</v>
@@ -47800,7 +47798,7 @@
         <v>0</v>
       </c>
       <c r="D1547" s="41" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E1547" s="42" t="s">
         <v>846</v>
@@ -47826,7 +47824,7 @@
         <v>0</v>
       </c>
       <c r="D1548" s="41" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="E1548" s="42" t="s">
         <v>846</v>
@@ -47852,7 +47850,7 @@
         <v>0</v>
       </c>
       <c r="D1549" s="41" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="E1549" s="42" t="s">
         <v>846</v>
@@ -47878,7 +47876,7 @@
         <v>0</v>
       </c>
       <c r="D1550" s="41" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="E1550" s="42" t="s">
         <v>846</v>
@@ -47904,7 +47902,7 @@
         <v>0</v>
       </c>
       <c r="D1551" s="41" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="E1551" s="42" t="s">
         <v>846</v>
@@ -47930,7 +47928,7 @@
         <v>0</v>
       </c>
       <c r="D1552" s="41" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="E1552" s="42" t="s">
         <v>846</v>
@@ -47942,7 +47940,7 @@
         <v>1</v>
       </c>
       <c r="I1552">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1553" spans="1:9" x14ac:dyDescent="0.15">
@@ -47956,7 +47954,7 @@
         <v>0</v>
       </c>
       <c r="D1553" s="41" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="E1553" s="42" t="s">
         <v>846</v>
@@ -47982,7 +47980,7 @@
         <v>0</v>
       </c>
       <c r="D1554" s="41" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="E1554" s="42" t="s">
         <v>846</v>
@@ -48008,7 +48006,7 @@
         <v>0</v>
       </c>
       <c r="D1555" s="41" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="E1555" s="42" t="s">
         <v>846</v>
@@ -48034,7 +48032,7 @@
         <v>0</v>
       </c>
       <c r="D1556" s="41" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="E1556" s="42" t="s">
         <v>846</v>
@@ -48060,7 +48058,7 @@
         <v>0</v>
       </c>
       <c r="D1557" s="41" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="E1557" s="42" t="s">
         <v>846</v>
@@ -48086,7 +48084,7 @@
         <v>0</v>
       </c>
       <c r="D1558" s="41" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="E1558" s="42" t="s">
         <v>846</v>
@@ -48141,7 +48139,7 @@
         <v>0</v>
       </c>
       <c r="D1560" s="39" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="E1560" s="38" t="s">
         <v>245</v>
@@ -48170,7 +48168,7 @@
         <v>0</v>
       </c>
       <c r="D1561" s="39" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E1561" s="38" t="s">
         <v>253</v>
@@ -48199,7 +48197,7 @@
         <v>0</v>
       </c>
       <c r="D1562" s="39" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E1562" s="38" t="s">
         <v>327</v>
@@ -48228,7 +48226,7 @@
         <v>0</v>
       </c>
       <c r="D1563" s="39" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E1563" s="38" t="s">
         <v>329</v>
@@ -48257,10 +48255,10 @@
         <v>0</v>
       </c>
       <c r="D1564" s="39" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="E1564" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1564" s="11" t="s">
         <v>100</v>
@@ -48286,7 +48284,7 @@
         <v>0</v>
       </c>
       <c r="D1565" s="39" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E1565" s="38" t="s">
         <v>245</v>
@@ -48315,7 +48313,7 @@
         <v>0</v>
       </c>
       <c r="D1566" s="39" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="E1566" s="38" t="s">
         <v>253</v>
@@ -48344,7 +48342,7 @@
         <v>0</v>
       </c>
       <c r="D1567" s="39" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E1567" s="38" t="s">
         <v>327</v>
@@ -48373,7 +48371,7 @@
         <v>0</v>
       </c>
       <c r="D1568" s="39" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="E1568" s="38" t="s">
         <v>329</v>
@@ -48402,10 +48400,10 @@
         <v>0</v>
       </c>
       <c r="D1569" s="39" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="E1569" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1569" s="11" t="s">
         <v>100</v>
@@ -48431,7 +48429,7 @@
         <v>0</v>
       </c>
       <c r="D1570" s="41" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="E1570" s="42" t="s">
         <v>844</v>
@@ -48457,7 +48455,7 @@
         <v>0</v>
       </c>
       <c r="D1571" s="41" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E1571" s="42" t="s">
         <v>846</v>
@@ -48469,7 +48467,7 @@
         <v>1</v>
       </c>
       <c r="I1571">
-        <v>7000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="1572" spans="1:9" x14ac:dyDescent="0.15">
@@ -48483,7 +48481,7 @@
         <v>0</v>
       </c>
       <c r="D1572" s="41" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="E1572" s="42" t="s">
         <v>846</v>
@@ -48509,7 +48507,7 @@
         <v>0</v>
       </c>
       <c r="D1573" s="41" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="E1573" s="42" t="s">
         <v>846</v>
@@ -48535,7 +48533,7 @@
         <v>0</v>
       </c>
       <c r="D1574" s="41" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="E1574" s="42" t="s">
         <v>846</v>
@@ -48561,7 +48559,7 @@
         <v>0</v>
       </c>
       <c r="D1575" s="41" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="E1575" s="42" t="s">
         <v>846</v>
@@ -48573,7 +48571,7 @@
         <v>1</v>
       </c>
       <c r="I1575">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1576" spans="1:9" x14ac:dyDescent="0.15">
@@ -48587,7 +48585,7 @@
         <v>0</v>
       </c>
       <c r="D1576" s="41" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="E1576" s="42" t="s">
         <v>846</v>
@@ -48613,7 +48611,7 @@
         <v>0</v>
       </c>
       <c r="D1577" s="41" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="E1577" s="42" t="s">
         <v>846</v>
@@ -48639,7 +48637,7 @@
         <v>0</v>
       </c>
       <c r="D1578" s="41" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="E1578" s="42" t="s">
         <v>846</v>
@@ -48665,7 +48663,7 @@
         <v>0</v>
       </c>
       <c r="D1579" s="41" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="E1579" s="42" t="s">
         <v>846</v>
@@ -48691,7 +48689,7 @@
         <v>0</v>
       </c>
       <c r="D1580" s="41" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="E1580" s="42" t="s">
         <v>846</v>
@@ -48703,7 +48701,7 @@
         <v>1</v>
       </c>
       <c r="I1580">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1581" spans="1:9" x14ac:dyDescent="0.15">
@@ -48717,7 +48715,7 @@
         <v>0</v>
       </c>
       <c r="D1581" s="41" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="E1581" s="42" t="s">
         <v>846</v>
@@ -48743,7 +48741,7 @@
         <v>0</v>
       </c>
       <c r="D1582" s="41" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="E1582" s="42" t="s">
         <v>846</v>
@@ -48769,7 +48767,7 @@
         <v>0</v>
       </c>
       <c r="D1583" s="41" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="E1583" s="42" t="s">
         <v>846</v>
@@ -48795,7 +48793,7 @@
         <v>0</v>
       </c>
       <c r="D1584" s="41" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="E1584" s="42" t="s">
         <v>846</v>
@@ -48821,7 +48819,7 @@
         <v>0</v>
       </c>
       <c r="D1585" s="41" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E1585" s="42" t="s">
         <v>846</v>
@@ -48848,7 +48846,7 @@
         <v>0</v>
       </c>
       <c r="D1586" s="41" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E1586" s="42" t="s">
         <v>844</v>
@@ -48874,7 +48872,7 @@
         <v>0</v>
       </c>
       <c r="D1587" s="41" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="E1587" s="42" t="s">
         <v>846</v>
@@ -48900,7 +48898,7 @@
         <v>0</v>
       </c>
       <c r="D1588" s="41" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="E1588" s="42" t="s">
         <v>846</v>
@@ -48926,7 +48924,7 @@
         <v>0</v>
       </c>
       <c r="D1589" s="41" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E1589" s="42" t="s">
         <v>846</v>
@@ -48952,7 +48950,7 @@
         <v>0</v>
       </c>
       <c r="D1590" s="41" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="E1590" s="42" t="s">
         <v>846</v>
@@ -48978,7 +48976,7 @@
         <v>0</v>
       </c>
       <c r="D1591" s="41" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E1591" s="42" t="s">
         <v>846</v>
@@ -48990,7 +48988,7 @@
         <v>1</v>
       </c>
       <c r="I1591">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1592" spans="1:9" x14ac:dyDescent="0.15">
@@ -49004,7 +49002,7 @@
         <v>0</v>
       </c>
       <c r="D1592" s="41" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="E1592" s="42" t="s">
         <v>846</v>
@@ -49030,7 +49028,7 @@
         <v>0</v>
       </c>
       <c r="D1593" s="41" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="E1593" s="42" t="s">
         <v>846</v>
@@ -49056,7 +49054,7 @@
         <v>0</v>
       </c>
       <c r="D1594" s="41" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="E1594" s="42" t="s">
         <v>846</v>
@@ -49082,7 +49080,7 @@
         <v>0</v>
       </c>
       <c r="D1595" s="41" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="E1595" s="42" t="s">
         <v>846</v>
@@ -49108,7 +49106,7 @@
         <v>0</v>
       </c>
       <c r="D1596" s="41" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E1596" s="42" t="s">
         <v>846</v>
@@ -49134,7 +49132,7 @@
         <v>0</v>
       </c>
       <c r="D1597" s="41" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="E1597" s="42" t="s">
         <v>846</v>
@@ -49160,7 +49158,7 @@
         <v>0</v>
       </c>
       <c r="D1598" s="41" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="E1598" s="42" t="s">
         <v>846</v>
@@ -49186,7 +49184,7 @@
         <v>0</v>
       </c>
       <c r="D1599" s="41" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="E1599" s="42" t="s">
         <v>844</v>
@@ -49213,7 +49211,7 @@
         <v>0</v>
       </c>
       <c r="D1600" s="41" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="E1600" s="42" t="s">
         <v>846</v>
@@ -49239,7 +49237,7 @@
         <v>0</v>
       </c>
       <c r="D1601" s="41" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="E1601" s="42" t="s">
         <v>844</v>
@@ -49266,10 +49264,10 @@
         <v>0</v>
       </c>
       <c r="D1602" s="44" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="E1602" s="44" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="G1602">
         <v>10</v>
@@ -49292,10 +49290,10 @@
         <v>0</v>
       </c>
       <c r="D1603" s="44" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E1603" s="44" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="G1603">
         <v>10</v>
@@ -49318,7 +49316,7 @@
         <v>0</v>
       </c>
       <c r="D1604" s="41" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="E1604" s="42" t="s">
         <v>844</v>
@@ -49344,7 +49342,7 @@
         <v>0</v>
       </c>
       <c r="D1605" s="41" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="E1605" s="42" t="s">
         <v>846</v>
@@ -49370,7 +49368,7 @@
         <v>0</v>
       </c>
       <c r="D1606" s="41" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="E1606" s="42" t="s">
         <v>846</v>
@@ -49396,7 +49394,7 @@
         <v>0</v>
       </c>
       <c r="D1607" s="41" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="E1607" s="42" t="s">
         <v>846</v>
@@ -49422,7 +49420,7 @@
         <v>0</v>
       </c>
       <c r="D1608" s="41" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E1608" s="42" t="s">
         <v>846</v>
@@ -49448,7 +49446,7 @@
         <v>0</v>
       </c>
       <c r="D1609" s="41" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="E1609" s="42" t="s">
         <v>846</v>
@@ -49474,7 +49472,7 @@
         <v>0</v>
       </c>
       <c r="D1610" s="41" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E1610" s="42" t="s">
         <v>846</v>
@@ -49500,7 +49498,7 @@
         <v>0</v>
       </c>
       <c r="D1611" s="41" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E1611" s="42" t="s">
         <v>846</v>
@@ -49526,7 +49524,7 @@
         <v>0</v>
       </c>
       <c r="D1612" s="41" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="E1612" s="42" t="s">
         <v>846</v>
@@ -49552,7 +49550,7 @@
         <v>0</v>
       </c>
       <c r="D1613" s="41" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E1613" s="42" t="s">
         <v>846</v>
@@ -49578,7 +49576,7 @@
         <v>0</v>
       </c>
       <c r="D1614" s="41" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="E1614" s="42" t="s">
         <v>846</v>
@@ -49604,7 +49602,7 @@
         <v>0</v>
       </c>
       <c r="D1615" s="41" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="E1615" s="42" t="s">
         <v>844</v>
@@ -49631,10 +49629,10 @@
         <v>0</v>
       </c>
       <c r="D1616" s="44" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E1616" s="44" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="G1616">
         <v>10</v>
@@ -49657,7 +49655,7 @@
         <v>0</v>
       </c>
       <c r="D1617" s="41" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="E1617" s="42" t="s">
         <v>844</v>
@@ -49683,7 +49681,7 @@
         <v>0</v>
       </c>
       <c r="D1618" s="41" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="E1618" s="42" t="s">
         <v>846</v>
@@ -49709,7 +49707,7 @@
         <v>0</v>
       </c>
       <c r="D1619" s="41" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E1619" s="42" t="s">
         <v>846</v>
@@ -49735,7 +49733,7 @@
         <v>0</v>
       </c>
       <c r="D1620" s="41" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="E1620" s="42" t="s">
         <v>846</v>
@@ -49761,7 +49759,7 @@
         <v>0</v>
       </c>
       <c r="D1621" s="41" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E1621" s="42" t="s">
         <v>846</v>
@@ -49787,7 +49785,7 @@
         <v>0</v>
       </c>
       <c r="D1622" s="41" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="E1622" s="42" t="s">
         <v>846</v>
@@ -49813,7 +49811,7 @@
         <v>0</v>
       </c>
       <c r="D1623" s="41" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="E1623" s="42" t="s">
         <v>846</v>
@@ -49839,7 +49837,7 @@
         <v>0</v>
       </c>
       <c r="D1624" s="41" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E1624" s="42" t="s">
         <v>846</v>
@@ -49865,7 +49863,7 @@
         <v>0</v>
       </c>
       <c r="D1625" s="41" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="E1625" s="42" t="s">
         <v>846</v>
@@ -49891,7 +49889,7 @@
         <v>0</v>
       </c>
       <c r="D1626" s="41" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="E1626" s="42" t="s">
         <v>846</v>
@@ -49917,7 +49915,7 @@
         <v>0</v>
       </c>
       <c r="D1627" s="41" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E1627" s="42" t="s">
         <v>846</v>
@@ -49944,7 +49942,7 @@
         <v>0</v>
       </c>
       <c r="D1628" s="41" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="E1628" s="42" t="s">
         <v>844</v>
@@ -49970,7 +49968,7 @@
         <v>0</v>
       </c>
       <c r="D1629" s="41" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="E1629" s="42" t="s">
         <v>846</v>
@@ -49996,7 +49994,7 @@
         <v>0</v>
       </c>
       <c r="D1630" s="41" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="E1630" s="42" t="s">
         <v>846</v>
@@ -50022,7 +50020,7 @@
         <v>0</v>
       </c>
       <c r="D1631" s="41" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E1631" s="42" t="s">
         <v>846</v>
@@ -50048,7 +50046,7 @@
         <v>0</v>
       </c>
       <c r="D1632" s="41" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="E1632" s="42" t="s">
         <v>846</v>
@@ -50074,7 +50072,7 @@
         <v>0</v>
       </c>
       <c r="D1633" s="41" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="E1633" s="42" t="s">
         <v>846</v>
@@ -50100,7 +50098,7 @@
         <v>0</v>
       </c>
       <c r="D1634" s="41" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="E1634" s="42" t="s">
         <v>846</v>
@@ -50126,7 +50124,7 @@
         <v>0</v>
       </c>
       <c r="D1635" s="41" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E1635" s="42" t="s">
         <v>846</v>
@@ -50152,7 +50150,7 @@
         <v>0</v>
       </c>
       <c r="D1636" s="41" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="E1636" s="42" t="s">
         <v>846</v>
@@ -50178,7 +50176,7 @@
         <v>0</v>
       </c>
       <c r="D1637" s="41" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E1637" s="42" t="s">
         <v>846</v>
@@ -50204,7 +50202,7 @@
         <v>0</v>
       </c>
       <c r="D1638" s="41" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="E1638" s="42" t="s">
         <v>844</v>
@@ -50231,10 +50229,10 @@
         <v>0</v>
       </c>
       <c r="D1639" s="44" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E1639" s="44" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="G1639">
         <v>10</v>
@@ -50257,7 +50255,7 @@
         <v>0</v>
       </c>
       <c r="D1640" s="41" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="E1640" s="42" t="s">
         <v>844</v>
@@ -50284,7 +50282,7 @@
         <v>0</v>
       </c>
       <c r="D1641" s="41" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="E1641" s="42" t="s">
         <v>846</v>
@@ -50296,7 +50294,7 @@
         <v>1</v>
       </c>
       <c r="I1641">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1642" spans="1:9" x14ac:dyDescent="0.15">
@@ -50310,7 +50308,7 @@
         <v>0</v>
       </c>
       <c r="D1642" s="41" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="E1642" s="42" t="s">
         <v>844</v>
@@ -50337,10 +50335,10 @@
         <v>0</v>
       </c>
       <c r="D1643" s="44" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="E1643" s="44" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="G1643">
         <v>10</v>
@@ -50363,10 +50361,10 @@
         <v>0</v>
       </c>
       <c r="D1644" s="44" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="E1644" s="44" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="G1644">
         <v>10</v>
@@ -50389,7 +50387,7 @@
         <v>0</v>
       </c>
       <c r="D1645" s="41" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="E1645" s="42" t="s">
         <v>844</v>
@@ -50415,7 +50413,7 @@
         <v>0</v>
       </c>
       <c r="D1646" s="41" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E1646" s="42" t="s">
         <v>846</v>
@@ -50441,7 +50439,7 @@
         <v>0</v>
       </c>
       <c r="D1647" s="41" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="E1647" s="42" t="s">
         <v>846</v>
@@ -50467,7 +50465,7 @@
         <v>0</v>
       </c>
       <c r="D1648" s="41" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E1648" s="42" t="s">
         <v>846</v>
@@ -50493,7 +50491,7 @@
         <v>0</v>
       </c>
       <c r="D1649" s="41" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="E1649" s="42" t="s">
         <v>846</v>
@@ -50519,7 +50517,7 @@
         <v>0</v>
       </c>
       <c r="D1650" s="41" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E1650" s="42" t="s">
         <v>846</v>
@@ -50545,7 +50543,7 @@
         <v>0</v>
       </c>
       <c r="D1651" s="41" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="E1651" s="42" t="s">
         <v>846</v>
@@ -50571,7 +50569,7 @@
         <v>0</v>
       </c>
       <c r="D1652" s="41" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="E1652" s="42" t="s">
         <v>846</v>
@@ -50597,7 +50595,7 @@
         <v>0</v>
       </c>
       <c r="D1653" s="41" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E1653" s="42" t="s">
         <v>846</v>
@@ -50623,7 +50621,7 @@
         <v>0</v>
       </c>
       <c r="D1654" s="41" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="E1654" s="42" t="s">
         <v>846</v>
@@ -50649,7 +50647,7 @@
         <v>0</v>
       </c>
       <c r="D1655" s="41" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E1655" s="42" t="s">
         <v>846</v>
@@ -50675,7 +50673,7 @@
         <v>0</v>
       </c>
       <c r="D1656" s="41" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="E1656" s="42" t="s">
         <v>846</v>
@@ -50701,7 +50699,7 @@
         <v>0</v>
       </c>
       <c r="D1657" s="41" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E1657" s="42" t="s">
         <v>844</v>
@@ -50728,10 +50726,10 @@
         <v>0</v>
       </c>
       <c r="D1658" s="44" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E1658" s="44" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="G1658">
         <v>10</v>
@@ -50754,7 +50752,7 @@
         <v>0</v>
       </c>
       <c r="D1659" s="41" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="E1659" s="42" t="s">
         <v>844</v>
@@ -50780,7 +50778,7 @@
         <v>0</v>
       </c>
       <c r="D1660" s="41" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E1660" s="42" t="s">
         <v>846</v>
@@ -50806,7 +50804,7 @@
         <v>0</v>
       </c>
       <c r="D1661" s="41" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="E1661" s="42" t="s">
         <v>846</v>
@@ -50832,7 +50830,7 @@
         <v>0</v>
       </c>
       <c r="D1662" s="41" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E1662" s="42" t="s">
         <v>846</v>
@@ -50858,7 +50856,7 @@
         <v>0</v>
       </c>
       <c r="D1663" s="41" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="E1663" s="42" t="s">
         <v>846</v>
@@ -50884,7 +50882,7 @@
         <v>0</v>
       </c>
       <c r="D1664" s="41" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E1664" s="42" t="s">
         <v>846</v>
@@ -50910,7 +50908,7 @@
         <v>0</v>
       </c>
       <c r="D1665" s="41" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="E1665" s="42" t="s">
         <v>846</v>
@@ -50936,7 +50934,7 @@
         <v>0</v>
       </c>
       <c r="D1666" s="41" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="E1666" s="42" t="s">
         <v>846</v>
@@ -50962,7 +50960,7 @@
         <v>0</v>
       </c>
       <c r="D1667" s="41" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="E1667" s="42" t="s">
         <v>846</v>
@@ -50988,7 +50986,7 @@
         <v>0</v>
       </c>
       <c r="D1668" s="41" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="E1668" s="42" t="s">
         <v>846</v>
@@ -51014,7 +51012,7 @@
         <v>0</v>
       </c>
       <c r="D1669" s="41" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E1669" s="42" t="s">
         <v>844</v>
@@ -51041,10 +51039,10 @@
         <v>0</v>
       </c>
       <c r="D1670" s="44" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="E1670" s="44" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="G1670">
         <v>10</v>
@@ -51067,7 +51065,7 @@
         <v>0</v>
       </c>
       <c r="D1671" s="39" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E1671" s="38" t="s">
         <v>327</v>
@@ -51096,7 +51094,7 @@
         <v>0</v>
       </c>
       <c r="D1672" s="39" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="E1672" s="38" t="s">
         <v>329</v>
@@ -51125,7 +51123,7 @@
         <v>0</v>
       </c>
       <c r="D1673" s="39" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E1673" s="38" t="s">
         <v>329</v>
@@ -51154,10 +51152,10 @@
         <v>0</v>
       </c>
       <c r="D1674" s="39" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="E1674" s="38" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="F1674" s="11" t="s">
         <v>100</v>
@@ -51183,7 +51181,7 @@
         <v>0</v>
       </c>
       <c r="D1675" s="39" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E1675" s="38" t="s">
         <v>329</v>
@@ -51212,7 +51210,7 @@
         <v>0</v>
       </c>
       <c r="D1676" s="39" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="E1676" s="38" t="s">
         <v>327</v>
@@ -51241,7 +51239,7 @@
         <v>0</v>
       </c>
       <c r="D1677" s="39" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="E1677" s="38" t="s">
         <v>329</v>
@@ -51270,7 +51268,7 @@
         <v>0</v>
       </c>
       <c r="D1678" s="39" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="E1678" s="38" t="s">
         <v>327</v>
@@ -51299,10 +51297,10 @@
         <v>0</v>
       </c>
       <c r="D1679" s="39" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="E1679" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1679" s="11" t="s">
         <v>100</v>
@@ -51328,7 +51326,7 @@
         <v>0</v>
       </c>
       <c r="D1680" s="39" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E1680" s="38" t="s">
         <v>245</v>
@@ -51357,7 +51355,7 @@
         <v>0</v>
       </c>
       <c r="D1681" s="39" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="E1681" s="38" t="s">
         <v>253</v>
@@ -51386,7 +51384,7 @@
         <v>0</v>
       </c>
       <c r="D1682" s="39" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E1682" s="38" t="s">
         <v>327</v>
@@ -51415,7 +51413,7 @@
         <v>0</v>
       </c>
       <c r="D1683" s="39" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="E1683" s="38" t="s">
         <v>327</v>
@@ -51444,10 +51442,10 @@
         <v>0</v>
       </c>
       <c r="D1684" s="39" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="E1684" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1684" s="11" t="s">
         <v>100</v>
@@ -51473,7 +51471,7 @@
         <v>0</v>
       </c>
       <c r="D1685" s="39" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="E1685" s="38" t="s">
         <v>245</v>
@@ -51502,7 +51500,7 @@
         <v>0</v>
       </c>
       <c r="D1686" s="39" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="E1686" s="38" t="s">
         <v>253</v>
@@ -51531,7 +51529,7 @@
         <v>0</v>
       </c>
       <c r="D1687" s="39" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E1687" s="38" t="s">
         <v>329</v>
@@ -51560,7 +51558,7 @@
         <v>0</v>
       </c>
       <c r="D1688" s="39" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="E1688" s="38" t="s">
         <v>327</v>
@@ -51589,10 +51587,10 @@
         <v>0</v>
       </c>
       <c r="D1689" s="39" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E1689" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1689" s="11" t="s">
         <v>100</v>
@@ -51618,7 +51616,7 @@
         <v>0</v>
       </c>
       <c r="D1690" s="39" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="E1690" s="38" t="s">
         <v>245</v>
@@ -51647,7 +51645,7 @@
         <v>0</v>
       </c>
       <c r="D1691" s="39" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E1691" s="38" t="s">
         <v>253</v>
@@ -51676,7 +51674,7 @@
         <v>0</v>
       </c>
       <c r="D1692" s="39" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="E1692" s="38" t="s">
         <v>329</v>
@@ -51705,7 +51703,7 @@
         <v>0</v>
       </c>
       <c r="D1693" s="39" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="E1693" s="38" t="s">
         <v>327</v>
@@ -51734,10 +51732,10 @@
         <v>0</v>
       </c>
       <c r="D1694" s="39" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E1694" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1694" s="11" t="s">
         <v>100</v>
@@ -51763,7 +51761,7 @@
         <v>0</v>
       </c>
       <c r="D1695" s="39" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="E1695" s="38" t="s">
         <v>245</v>
@@ -51792,7 +51790,7 @@
         <v>0</v>
       </c>
       <c r="D1696" s="39" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="E1696" s="38" t="s">
         <v>253</v>
@@ -51821,7 +51819,7 @@
         <v>0</v>
       </c>
       <c r="D1697" s="39" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="E1697" s="38" t="s">
         <v>329</v>
@@ -51850,7 +51848,7 @@
         <v>0</v>
       </c>
       <c r="D1698" s="39" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="E1698" s="38" t="s">
         <v>327</v>
@@ -51879,10 +51877,10 @@
         <v>0</v>
       </c>
       <c r="D1699" s="39" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="E1699" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1699" s="11" t="s">
         <v>100</v>
@@ -51908,7 +51906,7 @@
         <v>0</v>
       </c>
       <c r="D1700" s="39" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="E1700" s="38" t="s">
         <v>245</v>
@@ -51937,7 +51935,7 @@
         <v>0</v>
       </c>
       <c r="D1701" s="39" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="E1701" s="38" t="s">
         <v>253</v>
@@ -51966,7 +51964,7 @@
         <v>0</v>
       </c>
       <c r="D1702" s="39" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="E1702" s="38" t="s">
         <v>329</v>
@@ -51995,7 +51993,7 @@
         <v>0</v>
       </c>
       <c r="D1703" s="39" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="E1703" s="38" t="s">
         <v>327</v>
@@ -52024,10 +52022,10 @@
         <v>0</v>
       </c>
       <c r="D1704" s="39" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="E1704" s="38" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F1704" s="11" t="s">
         <v>100</v>
@@ -52053,7 +52051,7 @@
         <v>0</v>
       </c>
       <c r="D1705" s="39" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E1705" s="38" t="s">
         <v>245</v>
@@ -52082,7 +52080,7 @@
         <v>0</v>
       </c>
       <c r="D1706" s="39" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E1706" s="38" t="s">
         <v>253</v>
@@ -52161,7 +52159,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
@@ -52173,10 +52171,10 @@
         <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>2</v>
@@ -52190,90 +52188,90 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>1326</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1327</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1328</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1329</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1330</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1331</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1332</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1334</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.15">
@@ -52284,7 +52282,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="D5" s="3">
         <v>9101</v>
@@ -52305,7 +52303,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="51" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="K5" s="3">
         <v>9501</v>
@@ -52317,7 +52315,7 @@
         <v>9701</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.15">
@@ -52328,7 +52326,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="D6" s="1">
         <v>10258</v>
@@ -52369,7 +52367,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="D7" s="1">
         <v>10261</v>
@@ -52410,7 +52408,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="D8" s="3">
         <v>3010101</v>
@@ -52431,7 +52429,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="51" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="K8" s="3">
         <v>3010501</v>
@@ -52443,7 +52441,7 @@
         <v>3010701</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.15">
@@ -52454,7 +52452,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="D9" s="3">
         <v>3020101</v>
@@ -52475,7 +52473,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="51" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="K9" s="3">
         <v>3020501</v>
@@ -52487,7 +52485,7 @@
         <v>3020701</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.15">
@@ -52498,7 +52496,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="D10" s="3">
         <v>3030101</v>
@@ -52519,7 +52517,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="51" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="K10" s="3">
         <v>3030501</v>

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -36760,7 +36760,7 @@
         <v>1</v>
       </c>
       <c r="I1093">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1094" spans="1:9">
@@ -36784,7 +36784,7 @@
         <v>1</v>
       </c>
       <c r="I1094">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1095" spans="1:9">
@@ -36808,7 +36808,7 @@
         <v>1</v>
       </c>
       <c r="I1095">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1096" spans="1:9">
@@ -36832,7 +36832,7 @@
         <v>1</v>
       </c>
       <c r="I1096">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1097" spans="1:9">
@@ -36856,7 +36856,7 @@
         <v>1</v>
       </c>
       <c r="I1097">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1098" spans="1:9">
@@ -36880,7 +36880,7 @@
         <v>1</v>
       </c>
       <c r="I1098">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1099" spans="1:9">
@@ -37192,7 +37192,7 @@
         <v>2</v>
       </c>
       <c r="I1111">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1112" spans="1:9">
@@ -37216,7 +37216,7 @@
         <v>2</v>
       </c>
       <c r="I1112">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1113" spans="1:9">
@@ -37240,7 +37240,7 @@
         <v>2</v>
       </c>
       <c r="I1113">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1114" spans="1:9">
@@ -37264,7 +37264,7 @@
         <v>2</v>
       </c>
       <c r="I1114">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1115" spans="1:9">
@@ -37288,7 +37288,7 @@
         <v>2</v>
       </c>
       <c r="I1115">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1116" spans="1:9">
@@ -37312,7 +37312,7 @@
         <v>2</v>
       </c>
       <c r="I1116">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="1117" spans="1:9">
@@ -37624,7 +37624,7 @@
         <v>2</v>
       </c>
       <c r="I1129">
-        <v>10000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="1130" spans="1:9">
@@ -37648,7 +37648,7 @@
         <v>2</v>
       </c>
       <c r="I1130">
-        <v>10000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="1131" spans="1:9">
@@ -37672,7 +37672,7 @@
         <v>2</v>
       </c>
       <c r="I1131">
-        <v>10000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="1132" spans="1:9">
@@ -37696,7 +37696,7 @@
         <v>2</v>
       </c>
       <c r="I1132">
-        <v>10000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="1133" spans="1:9">
@@ -37720,7 +37720,7 @@
         <v>2</v>
       </c>
       <c r="I1133">
-        <v>10000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="1134" spans="1:9">
@@ -37744,7 +37744,7 @@
         <v>2</v>
       </c>
       <c r="I1134">
-        <v>10000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="1135" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_attribute_v8【迷宫-属性】.xlsx
@@ -37192,7 +37192,7 @@
         <v>2</v>
       </c>
       <c r="I1111">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1112" spans="1:9">
@@ -37216,7 +37216,7 @@
         <v>2</v>
       </c>
       <c r="I1112">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1113" spans="1:9">
@@ -37240,7 +37240,7 @@
         <v>2</v>
       </c>
       <c r="I1113">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1114" spans="1:9">
@@ -37264,7 +37264,7 @@
         <v>2</v>
       </c>
       <c r="I1114">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1115" spans="1:9">
@@ -37288,7 +37288,7 @@
         <v>2</v>
       </c>
       <c r="I1115">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1116" spans="1:9">
@@ -37312,7 +37312,7 @@
         <v>2</v>
       </c>
       <c r="I1116">
-        <v>8000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1117" spans="1:9">
@@ -37624,7 +37624,7 @@
         <v>2</v>
       </c>
       <c r="I1129">
-        <v>4400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1130" spans="1:9">
@@ -37648,7 +37648,7 @@
         <v>2</v>
       </c>
       <c r="I1130">
-        <v>4400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1131" spans="1:9">
@@ -37672,7 +37672,7 @@
         <v>2</v>
       </c>
       <c r="I1131">
-        <v>4400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1132" spans="1:9">
@@ -37696,7 +37696,7 @@
         <v>2</v>
       </c>
       <c r="I1132">
-        <v>4400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1133" spans="1:9">
@@ -37720,7 +37720,7 @@
         <v>2</v>
       </c>
       <c r="I1133">
-        <v>4400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1134" spans="1:9">
@@ -37744,7 +37744,7 @@
         <v>2</v>
       </c>
       <c r="I1134">
-        <v>4400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1135" spans="1:9">
